--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -347,7 +347,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -359,19 +359,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -383,7 +377,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -986,7 +986,7 @@
         <v>89</v>
       </c>
       <c r="O2" s="6">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
@@ -995,7 +995,7 @@
         <v>0</v>
       </c>
       <c r="R2" s="8">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1051,7 +1051,7 @@
         <v>0</v>
       </c>
       <c r="R3" s="10">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1098,16 +1098,16 @@
         <v>89</v>
       </c>
       <c r="O4" s="9">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
       </c>
-      <c r="Q4" s="11">
-        <v>3</v>
-      </c>
-      <c r="R4" s="12">
-        <v>81</v>
+      <c r="Q4" s="7">
+        <v>0</v>
+      </c>
+      <c r="R4" s="11">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1153,7 +1153,7 @@
       <c r="N5" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="O5" s="13">
+      <c r="O5" s="12">
         <v>0</v>
       </c>
       <c r="P5" s="7">
@@ -1209,8 +1209,8 @@
       <c r="N6" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="O6" s="13">
-        <v>0</v>
+      <c r="O6" s="12">
+        <v>1</v>
       </c>
       <c r="P6" s="7">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="R6" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1265,8 +1265,8 @@
       <c r="N7" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="O7" s="6">
-        <v>16</v>
+      <c r="O7" s="9">
+        <v>65</v>
       </c>
       <c r="P7" s="7">
         <v>0</v>
@@ -1274,8 +1274,8 @@
       <c r="Q7" s="7">
         <v>0</v>
       </c>
-      <c r="R7" s="11">
-        <v>5</v>
+      <c r="R7" s="13">
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1322,7 +1322,7 @@
         <v>89</v>
       </c>
       <c r="O8" s="9">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="P8" s="7">
         <v>0</v>
@@ -1331,7 +1331,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="14">
-        <v>68</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="72">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260522--01</t>
-  </si>
-  <si>
-    <t>20260522--02</t>
-  </si>
-  <si>
     <t>20260523--01</t>
   </si>
   <si>
@@ -91,25 +85,19 @@
     <t>20260526--01</t>
   </si>
   <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>02:19</t>
+  </si>
+  <si>
     <t>04:46</t>
   </si>
   <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>06:51</t>
-  </si>
-  <si>
-    <t>06:46</t>
-  </si>
-  <si>
-    <t>02:19</t>
-  </si>
-  <si>
-    <t>05:56</t>
-  </si>
-  <si>
-    <t>01:53</t>
+    <t>05:55</t>
   </si>
   <si>
     <t>03:58</t>
@@ -127,12 +115,6 @@
     <t>05:38</t>
   </si>
   <si>
-    <t>20:26:55</t>
-  </si>
-  <si>
-    <t>22:04:17</t>
-  </si>
-  <si>
     <t>21:20:19</t>
   </si>
   <si>
@@ -142,16 +124,10 @@
     <t>22:14:40</t>
   </si>
   <si>
-    <t>21:30:18</t>
-  </si>
-  <si>
-    <t>20:46:01</t>
-  </si>
-  <si>
-    <t>20:29:34</t>
-  </si>
-  <si>
-    <t>22:06:26</t>
+    <t>21:30:17</t>
+  </si>
+  <si>
+    <t>20:46:00</t>
   </si>
   <si>
     <t>21:22:26</t>
@@ -160,61 +136,43 @@
     <t>20:38:30</t>
   </si>
   <si>
-    <t>22:18:02</t>
-  </si>
-  <si>
-    <t>21:32:53</t>
-  </si>
-  <si>
-    <t>20:48:19</t>
-  </si>
-  <si>
-    <t>20:31:57</t>
-  </si>
-  <si>
-    <t>22:09:46</t>
+    <t>22:18:01</t>
+  </si>
+  <si>
+    <t>21:32:52</t>
+  </si>
+  <si>
+    <t>20:48:18</t>
   </si>
   <si>
     <t>21:25:52</t>
   </si>
   <si>
-    <t>20:41:54</t>
+    <t>20:41:53</t>
   </si>
   <si>
     <t>22:19:11</t>
   </si>
   <si>
-    <t>21:35:16</t>
-  </si>
-  <si>
-    <t>20:51:18</t>
-  </si>
-  <si>
-    <t>20:34:20</t>
-  </si>
-  <si>
-    <t>22:13:06</t>
-  </si>
-  <si>
-    <t>21:29:17</t>
-  </si>
-  <si>
-    <t>20:45:16</t>
-  </si>
-  <si>
-    <t>22:20:21</t>
-  </si>
-  <si>
-    <t>21:37:39</t>
-  </si>
-  <si>
-    <t>20:54:15</t>
-  </si>
-  <si>
-    <t>20:36:57</t>
-  </si>
-  <si>
-    <t>22:15:14</t>
+    <t>21:35:15</t>
+  </si>
+  <si>
+    <t>20:51:16</t>
+  </si>
+  <si>
+    <t>21:29:16</t>
+  </si>
+  <si>
+    <t>20:45:15</t>
+  </si>
+  <si>
+    <t>22:20:20</t>
+  </si>
+  <si>
+    <t>21:37:38</t>
+  </si>
+  <si>
+    <t>20:54:13</t>
   </si>
   <si>
     <t>21:31:23</t>
@@ -226,16 +184,10 @@
     <t>22:23:41</t>
   </si>
   <si>
-    <t>21:40:13</t>
-  </si>
-  <si>
-    <t>20:56:32</t>
-  </si>
-  <si>
-    <t>7°</t>
-  </si>
-  <si>
-    <t>29°</t>
+    <t>21:40:12</t>
+  </si>
+  <si>
+    <t>20:56:31</t>
   </si>
   <si>
     <t>61°</t>
@@ -253,28 +205,19 @@
     <t>12°</t>
   </si>
   <si>
-    <t>20:35:07</t>
-  </si>
-  <si>
-    <t>22:08:19</t>
-  </si>
-  <si>
     <t>21:26:24</t>
   </si>
   <si>
     <t>20:44:29</t>
   </si>
   <si>
-    <t>22:17:42</t>
-  </si>
-  <si>
-    <t>21:35:49</t>
-  </si>
-  <si>
-    <t>20:53:57</t>
-  </si>
-  <si>
-    <t>A</t>
+    <t>22:17:41</t>
+  </si>
+  <si>
+    <t>21:35:48</t>
+  </si>
+  <si>
+    <t>20:53:56</t>
   </si>
   <si>
     <t>A+B</t>
@@ -320,7 +263,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -335,7 +278,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -347,13 +290,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -365,25 +314,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -424,7 +355,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -460,12 +391,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -869,7 +794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -947,46 +872,46 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="L2" s="4">
-        <v>-8.5</v>
+        <v>-18.3</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="O2" s="6">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
@@ -995,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="R2" s="8">
-        <v>21</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1003,46 +928,46 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="L3" s="4">
-        <v>-25.7</v>
+        <v>-10.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="O3" s="9">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
@@ -1050,8 +975,8 @@
       <c r="Q3" s="7">
         <v>0</v>
       </c>
-      <c r="R3" s="10">
-        <v>49</v>
+      <c r="R3" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1059,46 +984,46 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>87</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="L4" s="4">
-        <v>-18.3</v>
+        <v>-26.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="O4" s="9">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
@@ -1106,8 +1031,8 @@
       <c r="Q4" s="7">
         <v>0</v>
       </c>
-      <c r="R4" s="11">
-        <v>100</v>
+      <c r="R4" s="10">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1115,46 +1040,46 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="K5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-19.6</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-10.2</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="N5" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="O5" s="12">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="O5" s="6">
+        <v>70</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
@@ -1162,8 +1087,8 @@
       <c r="Q5" s="7">
         <v>0</v>
       </c>
-      <c r="R5" s="7">
-        <v>0</v>
+      <c r="R5" s="11">
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1171,226 +1096,114 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="K6" s="1" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="L6" s="4">
-        <v>-26.9</v>
+        <v>-11.7</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="O6" s="12">
-        <v>1</v>
+        <v>70</v>
+      </c>
+      <c r="O6" s="6">
+        <v>62</v>
       </c>
       <c r="P6" s="7">
         <v>0</v>
       </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="2">
-        <v>18</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-19.6</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="O7" s="9">
-        <v>65</v>
-      </c>
-      <c r="P7" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-      <c r="R7" s="13">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="2">
-        <v>27</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="L8" s="4">
-        <v>-11.7</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="O8" s="9">
-        <v>40</v>
-      </c>
-      <c r="P8" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-      <c r="R8" s="14">
-        <v>15</v>
+      <c r="Q6" s="10">
+        <v>3</v>
+      </c>
+      <c r="R6" s="12">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A8">
+  <conditionalFormatting sqref="A2:A6">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B8">
+  <conditionalFormatting sqref="B2:B6">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C8">
+  <conditionalFormatting sqref="C2:C6">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D8">
+  <conditionalFormatting sqref="D2:D6">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E8">
+  <conditionalFormatting sqref="E2:E6">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F8">
+  <conditionalFormatting sqref="F2:F6">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G8">
+  <conditionalFormatting sqref="G2:G6">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H8">
+  <conditionalFormatting sqref="H2:H6">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I8">
+  <conditionalFormatting sqref="I2:I6">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J8">
+  <conditionalFormatting sqref="J2:J6">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K8">
+  <conditionalFormatting sqref="K2:K6">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L8">
+  <conditionalFormatting sqref="L2:L6">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1409,12 +1222,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M8">
+  <conditionalFormatting sqref="M2:M6">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N8">
+  <conditionalFormatting sqref="N2:N6">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1431,22 +1244,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O8">
+  <conditionalFormatting sqref="O2:O6">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P8">
+  <conditionalFormatting sqref="P2:P6">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q8">
+  <conditionalFormatting sqref="Q2:Q6">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R8">
+  <conditionalFormatting sqref="R2:R6">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="62">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260523--01</t>
-  </si>
-  <si>
     <t>20260524--01</t>
   </si>
   <si>
@@ -85,9 +82,6 @@
     <t>20260526--01</t>
   </si>
   <si>
-    <t>06:50</t>
-  </si>
-  <si>
     <t>06:45</t>
   </si>
   <si>
@@ -97,10 +91,7 @@
     <t>04:46</t>
   </si>
   <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>03:58</t>
+    <t>05:56</t>
   </si>
   <si>
     <t>05:59</t>
@@ -109,15 +100,12 @@
     <t>00:00</t>
   </si>
   <si>
-    <t>02:56</t>
+    <t>02:55</t>
   </si>
   <si>
     <t>05:38</t>
   </si>
   <si>
-    <t>21:20:19</t>
-  </si>
-  <si>
     <t>20:36:21</t>
   </si>
   <si>
@@ -127,10 +115,7 @@
     <t>21:30:17</t>
   </si>
   <si>
-    <t>20:46:00</t>
-  </si>
-  <si>
-    <t>21:22:26</t>
+    <t>20:45:59</t>
   </si>
   <si>
     <t>20:38:30</t>
@@ -142,25 +127,19 @@
     <t>21:32:52</t>
   </si>
   <si>
-    <t>20:48:18</t>
-  </si>
-  <si>
-    <t>21:25:52</t>
+    <t>20:48:17</t>
   </si>
   <si>
     <t>20:41:53</t>
   </si>
   <si>
-    <t>22:19:11</t>
+    <t>22:19:10</t>
   </si>
   <si>
     <t>21:35:15</t>
   </si>
   <si>
-    <t>20:51:16</t>
-  </si>
-  <si>
-    <t>21:29:16</t>
+    <t>20:51:15</t>
   </si>
   <si>
     <t>20:45:15</t>
@@ -175,22 +154,16 @@
     <t>20:54:13</t>
   </si>
   <si>
-    <t>21:31:23</t>
-  </si>
-  <si>
     <t>20:47:23</t>
   </si>
   <si>
-    <t>22:23:41</t>
+    <t>22:23:40</t>
   </si>
   <si>
     <t>21:40:12</t>
   </si>
   <si>
-    <t>20:56:31</t>
-  </si>
-  <si>
-    <t>61°</t>
+    <t>20:56:30</t>
   </si>
   <si>
     <t>16°</t>
@@ -205,19 +178,16 @@
     <t>12°</t>
   </si>
   <si>
-    <t>21:26:24</t>
-  </si>
-  <si>
     <t>20:44:29</t>
   </si>
   <si>
     <t>22:17:41</t>
   </si>
   <si>
-    <t>21:35:48</t>
-  </si>
-  <si>
-    <t>20:53:56</t>
+    <t>21:35:47</t>
+  </si>
+  <si>
+    <t>20:53:55</t>
   </si>
   <si>
     <t>A+B</t>
@@ -278,7 +248,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -290,31 +260,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -794,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -872,46 +842,46 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="H2" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-10.2</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-18.3</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="N2" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="O2" s="6">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
@@ -920,7 +890,7 @@
         <v>0</v>
       </c>
       <c r="R2" s="8">
-        <v>65</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -928,46 +898,46 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-26.9</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O3" s="6">
         <v>29</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-10.2</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="O3" s="9">
-        <v>2</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
@@ -975,8 +945,8 @@
       <c r="Q3" s="7">
         <v>0</v>
       </c>
-      <c r="R3" s="7">
-        <v>2</v>
+      <c r="R3" s="9">
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -984,46 +954,46 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="H4" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-19.6</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-26.9</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O4" s="9">
-        <v>7</v>
+      <c r="O4" s="6">
+        <v>23</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
@@ -1031,8 +1001,8 @@
       <c r="Q4" s="7">
         <v>0</v>
       </c>
-      <c r="R4" s="10">
-        <v>7</v>
+      <c r="R4" s="9">
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1040,170 +1010,114 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="H5" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="L5" s="4">
-        <v>-19.6</v>
+        <v>-11.7</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="O5" s="6">
-        <v>70</v>
+        <v>60</v>
+      </c>
+      <c r="O5" s="10">
+        <v>90</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
       </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="11">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="A6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="2">
-        <v>27</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K6" s="1" t="s">
+      <c r="Q5" s="11">
         <v>67</v>
       </c>
-      <c r="L6" s="4">
-        <v>-11.7</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="O6" s="6">
-        <v>62</v>
-      </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="10">
-        <v>3</v>
-      </c>
-      <c r="R6" s="12">
-        <v>62</v>
+      <c r="R5" s="12">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A6">
+  <conditionalFormatting sqref="A2:A5">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B6">
+  <conditionalFormatting sqref="B2:B5">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C6">
+  <conditionalFormatting sqref="C2:C5">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D6">
+  <conditionalFormatting sqref="D2:D5">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E6">
+  <conditionalFormatting sqref="E2:E5">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
+  <conditionalFormatting sqref="F2:F5">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G6">
+  <conditionalFormatting sqref="G2:G5">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H6">
+  <conditionalFormatting sqref="H2:H5">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6">
+  <conditionalFormatting sqref="I2:I5">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
+  <conditionalFormatting sqref="J2:J5">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
+  <conditionalFormatting sqref="K2:K5">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
+  <conditionalFormatting sqref="L2:L5">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1222,12 +1136,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M6">
+  <conditionalFormatting sqref="M2:M5">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N6">
+  <conditionalFormatting sqref="N2:N5">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1244,22 +1158,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O6">
+  <conditionalFormatting sqref="O2:O5">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P6">
+  <conditionalFormatting sqref="P2:P5">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q6">
+  <conditionalFormatting sqref="Q2:Q5">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R6">
+  <conditionalFormatting sqref="R2:R5">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="40">
   <si>
     <t>Datum</t>
   </si>
@@ -70,106 +70,52 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260524--01</t>
-  </si>
-  <si>
-    <t>20260524--02</t>
-  </si>
-  <si>
     <t>20260525--01</t>
   </si>
   <si>
     <t>20260526--01</t>
   </si>
   <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>02:19</t>
-  </si>
-  <si>
     <t>04:46</t>
   </si>
   <si>
     <t>05:56</t>
   </si>
   <si>
-    <t>05:59</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
     <t>02:55</t>
   </si>
   <si>
     <t>05:38</t>
   </si>
   <si>
-    <t>20:36:21</t>
-  </si>
-  <si>
-    <t>22:14:40</t>
-  </si>
-  <si>
-    <t>21:30:17</t>
-  </si>
-  <si>
-    <t>20:45:59</t>
-  </si>
-  <si>
-    <t>20:38:30</t>
-  </si>
-  <si>
-    <t>22:18:01</t>
-  </si>
-  <si>
-    <t>21:32:52</t>
-  </si>
-  <si>
-    <t>20:48:17</t>
-  </si>
-  <si>
-    <t>20:41:53</t>
-  </si>
-  <si>
-    <t>22:19:10</t>
-  </si>
-  <si>
-    <t>21:35:15</t>
-  </si>
-  <si>
-    <t>20:51:15</t>
-  </si>
-  <si>
-    <t>20:45:15</t>
-  </si>
-  <si>
-    <t>22:20:20</t>
-  </si>
-  <si>
-    <t>21:37:38</t>
-  </si>
-  <si>
-    <t>20:54:13</t>
-  </si>
-  <si>
-    <t>20:47:23</t>
-  </si>
-  <si>
-    <t>22:23:40</t>
-  </si>
-  <si>
-    <t>21:40:12</t>
-  </si>
-  <si>
-    <t>20:56:30</t>
-  </si>
-  <si>
-    <t>16°</t>
-  </si>
-  <si>
-    <t>9°</t>
+    <t>21:30:16</t>
+  </si>
+  <si>
+    <t>20:45:57</t>
+  </si>
+  <si>
+    <t>21:32:51</t>
+  </si>
+  <si>
+    <t>20:48:15</t>
+  </si>
+  <si>
+    <t>21:35:14</t>
+  </si>
+  <si>
+    <t>20:51:13</t>
+  </si>
+  <si>
+    <t>21:37:37</t>
+  </si>
+  <si>
+    <t>20:54:11</t>
+  </si>
+  <si>
+    <t>21:40:11</t>
+  </si>
+  <si>
+    <t>20:56:28</t>
   </si>
   <si>
     <t>17°</t>
@@ -178,28 +124,16 @@
     <t>12°</t>
   </si>
   <si>
-    <t>20:44:29</t>
-  </si>
-  <si>
-    <t>22:17:41</t>
-  </si>
-  <si>
-    <t>21:35:47</t>
-  </si>
-  <si>
-    <t>20:53:55</t>
+    <t>21:35:46</t>
+  </si>
+  <si>
+    <t>20:53:53</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -233,7 +167,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -248,7 +182,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -260,31 +194,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -325,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -352,15 +268,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -764,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -842,55 +749,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="I2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="K2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-19.6</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-10.2</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="N2" s="1" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="O2" s="6">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>19</v>
+      <c r="Q2" s="8">
+        <v>11</v>
+      </c>
+      <c r="R2" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -898,226 +805,114 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="I3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="K3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-11.7</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-26.9</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="O3" s="6">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
-      <c r="Q3" s="7">
-        <v>0</v>
+      <c r="Q3" s="9">
+        <v>100</v>
       </c>
       <c r="R3" s="9">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
-      <c r="A4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="2">
-        <v>18</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-19.6</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="O4" s="6">
-        <v>23</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>0</v>
-      </c>
-      <c r="R4" s="9">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="2">
-        <v>27</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-11.7</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="O5" s="10">
-        <v>90</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="11">
-        <v>67</v>
-      </c>
-      <c r="R5" s="12">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A5">
+  <conditionalFormatting sqref="A2:A3">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B5">
+  <conditionalFormatting sqref="B2:B3">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C5">
+  <conditionalFormatting sqref="C2:C3">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D5">
+  <conditionalFormatting sqref="D2:D3">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E5">
+  <conditionalFormatting sqref="E2:E3">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F5">
+  <conditionalFormatting sqref="F2:F3">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G5">
+  <conditionalFormatting sqref="G2:G3">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H5">
+  <conditionalFormatting sqref="H2:H3">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I5">
+  <conditionalFormatting sqref="I2:I3">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J5">
+  <conditionalFormatting sqref="J2:J3">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K5">
+  <conditionalFormatting sqref="K2:K3">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L5">
+  <conditionalFormatting sqref="L2:L3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1136,12 +931,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M5">
+  <conditionalFormatting sqref="M2:M3">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N5">
+  <conditionalFormatting sqref="N2:N3">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1158,22 +953,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O5">
+  <conditionalFormatting sqref="O2:O3">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P5">
+  <conditionalFormatting sqref="P2:P3">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q5">
+  <conditionalFormatting sqref="Q2:Q3">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R5">
+  <conditionalFormatting sqref="R2:R3">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
   <si>
     <t>Datum</t>
   </si>
@@ -70,61 +70,31 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260525--01</t>
-  </si>
-  <si>
     <t>20260526--01</t>
   </si>
   <si>
-    <t>04:46</t>
-  </si>
-  <si>
-    <t>05:56</t>
-  </si>
-  <si>
-    <t>02:55</t>
+    <t>05:55</t>
   </si>
   <si>
     <t>05:38</t>
   </si>
   <si>
-    <t>21:30:16</t>
-  </si>
-  <si>
     <t>20:45:57</t>
   </si>
   <si>
-    <t>21:32:51</t>
-  </si>
-  <si>
     <t>20:48:15</t>
   </si>
   <si>
-    <t>21:35:14</t>
-  </si>
-  <si>
     <t>20:51:13</t>
   </si>
   <si>
-    <t>21:37:37</t>
-  </si>
-  <si>
-    <t>20:54:11</t>
-  </si>
-  <si>
-    <t>21:40:11</t>
+    <t>20:54:10</t>
   </si>
   <si>
     <t>20:56:28</t>
   </si>
   <si>
-    <t>17°</t>
-  </si>
-  <si>
     <t>12°</t>
-  </si>
-  <si>
-    <t>21:35:46</t>
   </si>
   <si>
     <t>20:53:53</t>
@@ -194,13 +164,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -671,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -749,170 +719,114 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="I2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="K2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-11.7</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-19.6</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="N2" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="O2" s="6">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
       <c r="Q2" s="8">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="R2" s="9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
-      <c r="A3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="2">
-        <v>28</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-11.7</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="6">
-        <v>100</v>
-      </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="9">
-        <v>100</v>
-      </c>
-      <c r="R3" s="9">
-        <v>100</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A3">
+  <conditionalFormatting sqref="A2">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B3">
+  <conditionalFormatting sqref="B2">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C3">
+  <conditionalFormatting sqref="C2">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D3">
+  <conditionalFormatting sqref="D2">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E3">
+  <conditionalFormatting sqref="E2">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F3">
+  <conditionalFormatting sqref="F2">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G3">
+  <conditionalFormatting sqref="G2">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H3">
+  <conditionalFormatting sqref="H2">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I3">
+  <conditionalFormatting sqref="I2">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J3">
+  <conditionalFormatting sqref="J2">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K3">
+  <conditionalFormatting sqref="K2">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L3">
+  <conditionalFormatting sqref="L2">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -931,12 +845,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M3">
+  <conditionalFormatting sqref="M2">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N3">
+  <conditionalFormatting sqref="N2">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -953,22 +867,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O3">
+  <conditionalFormatting sqref="O2">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P3">
+  <conditionalFormatting sqref="P2">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q3">
+  <conditionalFormatting sqref="Q2">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R3">
+  <conditionalFormatting sqref="R2">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
   <si>
     <t>Datum</t>
   </si>
@@ -68,42 +68,6 @@
   </si>
   <si>
     <t>Vysoká</t>
-  </si>
-  <si>
-    <t>20260526--01</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>05:38</t>
-  </si>
-  <si>
-    <t>20:45:57</t>
-  </si>
-  <si>
-    <t>20:48:15</t>
-  </si>
-  <si>
-    <t>20:51:13</t>
-  </si>
-  <si>
-    <t>20:54:10</t>
-  </si>
-  <si>
-    <t>20:56:28</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>20:53:53</t>
-  </si>
-  <si>
-    <t>A+B</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
 </sst>
 </file>
@@ -113,7 +77,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0&quot;°&quot;"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,15 +93,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF333333"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -147,30 +104,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD7E4BC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -211,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -227,18 +160,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -641,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -714,119 +635,63 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
-      <c r="A2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="2">
-        <v>28</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-11.7</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2" s="6">
-        <v>67</v>
-      </c>
-      <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>65</v>
-      </c>
-      <c r="R2" s="9">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2">
+  <conditionalFormatting sqref="A1:A2">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
+  <conditionalFormatting sqref="B1:B2">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2">
+  <conditionalFormatting sqref="C1:C2">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2">
+  <conditionalFormatting sqref="D1:D2">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2">
+  <conditionalFormatting sqref="E1:E2">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
+  <conditionalFormatting sqref="F1:F2">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2">
+  <conditionalFormatting sqref="G1:G2">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2">
+  <conditionalFormatting sqref="H1:H2">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2">
+  <conditionalFormatting sqref="I1:I2">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2">
+  <conditionalFormatting sqref="J1:J2">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2">
+  <conditionalFormatting sqref="K1:K2">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2">
+  <conditionalFormatting sqref="L1:L2">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -845,12 +710,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2">
+  <conditionalFormatting sqref="M1:M2">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2">
+  <conditionalFormatting sqref="N1:N2">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -867,22 +732,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2">
+  <conditionalFormatting sqref="O1:O2">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2">
+  <conditionalFormatting sqref="P1:P2">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2">
+  <conditionalFormatting sqref="Q1:Q2">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2">
+  <conditionalFormatting sqref="R1:R2">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
   <si>
     <t>Datum</t>
   </si>
@@ -68,6 +68,39 @@
   </si>
   <si>
     <t>Vysoká</t>
+  </si>
+  <si>
+    <t>20260609--01</t>
+  </si>
+  <si>
+    <t>04:47</t>
+  </si>
+  <si>
+    <t>05:24:36</t>
+  </si>
+  <si>
+    <t>05:27:09</t>
+  </si>
+  <si>
+    <t>05:29:33</t>
+  </si>
+  <si>
+    <t>05:31:56</t>
+  </si>
+  <si>
+    <t>05:34:31</t>
+  </si>
+  <si>
+    <t>4°</t>
+  </si>
+  <si>
+    <t>05:25:45</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
 </sst>
 </file>
@@ -77,7 +110,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0&quot;°&quot;"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,8 +126,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -104,6 +144,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD7E4BC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -144,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -160,6 +212,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -562,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -635,63 +693,119 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2">
+        <v>18</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-8.4</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="6">
+        <v>0</v>
+      </c>
+      <c r="P2" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A2">
+  <conditionalFormatting sqref="A2">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B2">
+  <conditionalFormatting sqref="B2">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C2">
+  <conditionalFormatting sqref="C2">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D2">
+  <conditionalFormatting sqref="D2">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E2">
+  <conditionalFormatting sqref="E2">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F2">
+  <conditionalFormatting sqref="F2">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G1:G2">
+  <conditionalFormatting sqref="G2">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H2">
+  <conditionalFormatting sqref="H2">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I2">
+  <conditionalFormatting sqref="I2">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J2">
+  <conditionalFormatting sqref="J2">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K2">
+  <conditionalFormatting sqref="K2">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L1:L2">
+  <conditionalFormatting sqref="L2">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -710,12 +824,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1:M2">
+  <conditionalFormatting sqref="M2">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1:N2">
+  <conditionalFormatting sqref="N2">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -732,22 +846,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O1:O2">
+  <conditionalFormatting sqref="O2">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P1:P2">
+  <conditionalFormatting sqref="P2">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1:Q2">
+  <conditionalFormatting sqref="Q2">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R2">
+  <conditionalFormatting sqref="R2">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="39">
   <si>
     <t>Datum</t>
   </si>
@@ -73,34 +73,64 @@
     <t>20260609--01</t>
   </si>
   <si>
+    <t>20260610--01</t>
+  </si>
+  <si>
     <t>04:47</t>
   </si>
   <si>
-    <t>05:24:36</t>
-  </si>
-  <si>
-    <t>05:27:09</t>
+    <t>02:04</t>
+  </si>
+  <si>
+    <t>05:24:37</t>
+  </si>
+  <si>
+    <t>04:40:03</t>
+  </si>
+  <si>
+    <t>05:27:10</t>
+  </si>
+  <si>
+    <t>04:43:29</t>
   </si>
   <si>
     <t>05:29:33</t>
   </si>
   <si>
-    <t>05:31:56</t>
-  </si>
-  <si>
-    <t>05:34:31</t>
+    <t>04:44:31</t>
+  </si>
+  <si>
+    <t>05:31:57</t>
+  </si>
+  <si>
+    <t>04:45:33</t>
+  </si>
+  <si>
+    <t>05:34:32</t>
+  </si>
+  <si>
+    <t>04:49:00</t>
   </si>
   <si>
     <t>4°</t>
   </si>
   <si>
+    <t>9°</t>
+  </si>
+  <si>
     <t>05:25:45</t>
   </si>
   <si>
+    <t>04:42:54</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
 </sst>
 </file>
@@ -620,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -701,40 +731,40 @@
         <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L2" s="4">
         <v>-8.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="O2" s="6">
         <v>0</v>
@@ -749,63 +779,119 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-16.4</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O3" s="6">
+        <v>0</v>
+      </c>
+      <c r="P3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="7">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2">
+  <conditionalFormatting sqref="A2:A3">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
+  <conditionalFormatting sqref="B2:B3">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2">
+  <conditionalFormatting sqref="C2:C3">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2">
+  <conditionalFormatting sqref="D2:D3">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2">
+  <conditionalFormatting sqref="E2:E3">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
+  <conditionalFormatting sqref="F2:F3">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2">
+  <conditionalFormatting sqref="G2:G3">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2">
+  <conditionalFormatting sqref="H2:H3">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2">
+  <conditionalFormatting sqref="I2:I3">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2">
+  <conditionalFormatting sqref="J2:J3">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2">
+  <conditionalFormatting sqref="K2:K3">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2">
+  <conditionalFormatting sqref="L2:L3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -824,12 +910,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2">
+  <conditionalFormatting sqref="M2:M3">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2">
+  <conditionalFormatting sqref="N2:N3">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -846,22 +932,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2">
+  <conditionalFormatting sqref="O2:O3">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2">
+  <conditionalFormatting sqref="P2:P3">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2">
+  <conditionalFormatting sqref="Q2:Q3">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2">
+  <conditionalFormatting sqref="R2:R3">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="81">
   <si>
     <t>Datum</t>
   </si>
@@ -76,16 +76,64 @@
     <t>20260610--01</t>
   </si>
   <si>
+    <t>20260612--01</t>
+  </si>
+  <si>
+    <t>20260613--01</t>
+  </si>
+  <si>
+    <t>20260614--01</t>
+  </si>
+  <si>
+    <t>20260614--02</t>
+  </si>
+  <si>
     <t>04:47</t>
   </si>
   <si>
-    <t>02:04</t>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>05:59</t>
+  </si>
+  <si>
+    <t>04:48</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>04:41</t>
+  </si>
+  <si>
+    <t>02:21</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>04:53</t>
   </si>
   <si>
     <t>05:24:37</t>
   </si>
   <si>
-    <t>04:40:03</t>
+    <t>04:40:04</t>
+  </si>
+  <si>
+    <t>04:45:51</t>
+  </si>
+  <si>
+    <t>04:00:46</t>
+  </si>
+  <si>
+    <t>03:15:45</t>
+  </si>
+  <si>
+    <t>04:52:39</t>
   </si>
   <si>
     <t>05:27:10</t>
@@ -94,22 +142,70 @@
     <t>04:43:29</t>
   </si>
   <si>
+    <t>04:48:00</t>
+  </si>
+  <si>
+    <t>04:03:01</t>
+  </si>
+  <si>
+    <t>03:18:18</t>
+  </si>
+  <si>
+    <t>04:54:51</t>
+  </si>
+  <si>
     <t>05:29:33</t>
   </si>
   <si>
-    <t>04:44:31</t>
+    <t>04:44:32</t>
+  </si>
+  <si>
+    <t>04:51:17</t>
+  </si>
+  <si>
+    <t>04:06:00</t>
+  </si>
+  <si>
+    <t>03:20:41</t>
+  </si>
+  <si>
+    <t>04:58:02</t>
   </si>
   <si>
     <t>05:31:57</t>
   </si>
   <si>
-    <t>04:45:33</t>
+    <t>04:45:34</t>
+  </si>
+  <si>
+    <t>04:54:35</t>
+  </si>
+  <si>
+    <t>04:09:00</t>
+  </si>
+  <si>
+    <t>03:23:06</t>
+  </si>
+  <si>
+    <t>05:01:14</t>
   </si>
   <si>
     <t>05:34:32</t>
   </si>
   <si>
-    <t>04:49:00</t>
+    <t>04:49:01</t>
+  </si>
+  <si>
+    <t>04:56:45</t>
+  </si>
+  <si>
+    <t>04:11:17</t>
+  </si>
+  <si>
+    <t>03:25:40</t>
+  </si>
+  <si>
+    <t>05:03:28</t>
   </si>
   <si>
     <t>4°</t>
@@ -118,19 +214,49 @@
     <t>9°</t>
   </si>
   <si>
+    <t>29°</t>
+  </si>
+  <si>
+    <t>27°</t>
+  </si>
+  <si>
+    <t>22°</t>
+  </si>
+  <si>
     <t>05:25:45</t>
   </si>
   <si>
     <t>04:42:54</t>
   </si>
   <si>
+    <t>04:49:54</t>
+  </si>
+  <si>
+    <t>04:06:39</t>
+  </si>
+  <si>
+    <t>03:23:15</t>
+  </si>
+  <si>
+    <t>04:56:21</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
+    <t>A+B</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -164,7 +290,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -186,6 +312,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -226,7 +382,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -247,6 +403,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -650,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -731,40 +902,40 @@
         <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="L2" s="4">
         <v>-8.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="O2" s="6">
         <v>0</v>
@@ -787,111 +958,335 @@
         <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="L3" s="4">
         <v>-16.4</v>
       </c>
       <c r="M3" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O3" s="6">
+        <v>1</v>
+      </c>
+      <c r="P3" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2">
+        <v>48</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="F4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-15.2</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O4" s="8">
+        <v>39</v>
+      </c>
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>5</v>
+      </c>
+      <c r="R4" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="2">
+        <v>29</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-22.7</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O5" s="11">
+        <v>68</v>
+      </c>
+      <c r="P5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>0</v>
+      </c>
+      <c r="R5" s="12">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="2">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="O3" s="6">
-        <v>0</v>
-      </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="7">
+      <c r="F6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-29</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="O6" s="6">
+        <v>0</v>
+      </c>
+      <c r="P6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>0</v>
+      </c>
+      <c r="R6" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="2">
+        <v>37</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-14.1</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O7" s="6">
+        <v>0</v>
+      </c>
+      <c r="P7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A3">
+  <conditionalFormatting sqref="A2:A7">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B3">
+  <conditionalFormatting sqref="B2:B7">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C3">
+  <conditionalFormatting sqref="C2:C7">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D3">
+  <conditionalFormatting sqref="D2:D7">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E3">
+  <conditionalFormatting sqref="E2:E7">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F3">
+  <conditionalFormatting sqref="F2:F7">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G3">
+  <conditionalFormatting sqref="G2:G7">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H3">
+  <conditionalFormatting sqref="H2:H7">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I3">
+  <conditionalFormatting sqref="I2:I7">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J3">
+  <conditionalFormatting sqref="J2:J7">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K3">
+  <conditionalFormatting sqref="K2:K7">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L3">
+  <conditionalFormatting sqref="L2:L7">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -910,12 +1305,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M3">
+  <conditionalFormatting sqref="M2:M7">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N3">
+  <conditionalFormatting sqref="N2:N7">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -932,22 +1327,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O3">
+  <conditionalFormatting sqref="O2:O7">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P3">
+  <conditionalFormatting sqref="P2:P7">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q3">
+  <conditionalFormatting sqref="Q2:Q7">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R3">
+  <conditionalFormatting sqref="R2:R7">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="100">
   <si>
     <t>Datum</t>
   </si>
@@ -88,13 +88,19 @@
     <t>20260614--02</t>
   </si>
   <si>
+    <t>20260615--01</t>
+  </si>
+  <si>
+    <t>20260615--02</t>
+  </si>
+  <si>
     <t>04:47</t>
   </si>
   <si>
     <t>02:05</t>
   </si>
   <si>
-    <t>06:35</t>
+    <t>06:36</t>
   </si>
   <si>
     <t>05:59</t>
@@ -106,10 +112,16 @@
     <t>06:23</t>
   </si>
   <si>
+    <t>02:07</t>
+  </si>
+  <si>
+    <t>06:42</t>
+  </si>
+  <si>
     <t>04:41</t>
   </si>
   <si>
-    <t>02:21</t>
+    <t>02:22</t>
   </si>
   <si>
     <t>00:00</t>
@@ -118,94 +130,127 @@
     <t>04:53</t>
   </si>
   <si>
+    <t>03:04</t>
+  </si>
+  <si>
     <t>05:24:37</t>
   </si>
   <si>
-    <t>04:40:04</t>
-  </si>
-  <si>
-    <t>04:45:51</t>
-  </si>
-  <si>
-    <t>04:00:46</t>
-  </si>
-  <si>
-    <t>03:15:45</t>
-  </si>
-  <si>
-    <t>04:52:39</t>
-  </si>
-  <si>
-    <t>05:27:10</t>
-  </si>
-  <si>
-    <t>04:43:29</t>
-  </si>
-  <si>
-    <t>04:48:00</t>
-  </si>
-  <si>
-    <t>04:03:01</t>
-  </si>
-  <si>
-    <t>03:18:18</t>
-  </si>
-  <si>
-    <t>04:54:51</t>
-  </si>
-  <si>
-    <t>05:29:33</t>
+    <t>04:40:05</t>
+  </si>
+  <si>
+    <t>04:45:53</t>
+  </si>
+  <si>
+    <t>04:00:48</t>
+  </si>
+  <si>
+    <t>03:15:48</t>
+  </si>
+  <si>
+    <t>04:52:42</t>
+  </si>
+  <si>
+    <t>02:30:57</t>
+  </si>
+  <si>
+    <t>04:07:07</t>
+  </si>
+  <si>
+    <t>05:27:11</t>
+  </si>
+  <si>
+    <t>04:43:30</t>
+  </si>
+  <si>
+    <t>04:48:01</t>
+  </si>
+  <si>
+    <t>04:03:04</t>
+  </si>
+  <si>
+    <t>03:18:21</t>
+  </si>
+  <si>
+    <t>04:54:54</t>
+  </si>
+  <si>
+    <t>02:34:21</t>
+  </si>
+  <si>
+    <t>04:09:15</t>
+  </si>
+  <si>
+    <t>05:29:34</t>
   </si>
   <si>
     <t>04:44:32</t>
   </si>
   <si>
-    <t>04:51:17</t>
-  </si>
-  <si>
-    <t>04:06:00</t>
-  </si>
-  <si>
-    <t>03:20:41</t>
-  </si>
-  <si>
-    <t>04:58:02</t>
-  </si>
-  <si>
-    <t>05:31:57</t>
-  </si>
-  <si>
-    <t>04:45:34</t>
-  </si>
-  <si>
-    <t>04:54:35</t>
-  </si>
-  <si>
-    <t>04:09:00</t>
-  </si>
-  <si>
-    <t>03:23:06</t>
-  </si>
-  <si>
-    <t>05:01:14</t>
+    <t>04:51:18</t>
+  </si>
+  <si>
+    <t>04:06:02</t>
+  </si>
+  <si>
+    <t>03:20:44</t>
+  </si>
+  <si>
+    <t>04:58:05</t>
+  </si>
+  <si>
+    <t>02:35:24</t>
+  </si>
+  <si>
+    <t>04:12:35</t>
+  </si>
+  <si>
+    <t>05:31:58</t>
+  </si>
+  <si>
+    <t>04:45:35</t>
+  </si>
+  <si>
+    <t>04:54:37</t>
+  </si>
+  <si>
+    <t>04:09:03</t>
+  </si>
+  <si>
+    <t>03:23:09</t>
+  </si>
+  <si>
+    <t>05:01:17</t>
+  </si>
+  <si>
+    <t>02:36:28</t>
+  </si>
+  <si>
+    <t>04:15:57</t>
   </si>
   <si>
     <t>05:34:32</t>
   </si>
   <si>
-    <t>04:49:01</t>
-  </si>
-  <si>
-    <t>04:56:45</t>
-  </si>
-  <si>
-    <t>04:11:17</t>
-  </si>
-  <si>
-    <t>03:25:40</t>
-  </si>
-  <si>
-    <t>05:03:28</t>
+    <t>04:49:02</t>
+  </si>
+  <si>
+    <t>04:56:47</t>
+  </si>
+  <si>
+    <t>04:11:20</t>
+  </si>
+  <si>
+    <t>03:25:42</t>
+  </si>
+  <si>
+    <t>05:03:31</t>
+  </si>
+  <si>
+    <t>02:39:52</t>
+  </si>
+  <si>
+    <t>04:18:06</t>
   </si>
   <si>
     <t>4°</t>
@@ -223,22 +268,34 @@
     <t>22°</t>
   </si>
   <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>56°</t>
+  </si>
+  <si>
     <t>05:25:45</t>
   </si>
   <si>
-    <t>04:42:54</t>
-  </si>
-  <si>
-    <t>04:49:54</t>
-  </si>
-  <si>
-    <t>04:06:39</t>
-  </si>
-  <si>
-    <t>03:23:15</t>
-  </si>
-  <si>
-    <t>04:56:21</t>
+    <t>04:42:55</t>
+  </si>
+  <si>
+    <t>04:49:56</t>
+  </si>
+  <si>
+    <t>04:06:41</t>
+  </si>
+  <si>
+    <t>03:23:18</t>
+  </si>
+  <si>
+    <t>04:56:24</t>
+  </si>
+  <si>
+    <t>02:39:48</t>
+  </si>
+  <si>
+    <t>04:12:53</t>
   </si>
   <si>
     <t>A</t>
@@ -290,7 +347,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -305,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -317,31 +380,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -382,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -415,9 +466,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -821,7 +869,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -902,51 +950,51 @@
         <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="L2" s="4">
         <v>-8.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="O2" s="6">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="7">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
         <v>0</v>
       </c>
     </row>
@@ -958,51 +1006,51 @@
         <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="L3" s="4">
         <v>-16.4</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O3" s="6">
-        <v>1</v>
-      </c>
-      <c r="P3" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="7">
+        <v>98</v>
+      </c>
+      <c r="O3" s="9">
+        <v>40</v>
+      </c>
+      <c r="P3" s="10">
+        <v>40</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>0</v>
+      </c>
+      <c r="R3" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1014,52 +1062,52 @@
         <v>48</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="L4" s="4">
         <v>-15.2</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="O4" s="8">
-        <v>39</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="9">
-        <v>5</v>
-      </c>
-      <c r="R4" s="10">
-        <v>15</v>
+        <v>97</v>
+      </c>
+      <c r="O4" s="11">
+        <v>2</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1070,52 +1118,52 @@
         <v>29</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="L5" s="4">
         <v>-22.7</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="O5" s="11">
-        <v>68</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="12">
-        <v>49</v>
+        <v>2</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="R5" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1126,51 +1174,51 @@
         <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="L6" s="4">
         <v>-29</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="7">
+        <v>99</v>
+      </c>
+      <c r="O6" s="11">
+        <v>0</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1182,111 +1230,223 @@
         <v>37</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="L7" s="4">
         <v>-14.1</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="N7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="O7" s="11">
+        <v>0</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
+      <c r="R7" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="2">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-34</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="O8" s="11">
+        <v>2</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2">
+        <v>59</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="O7" s="6">
-        <v>0</v>
-      </c>
-      <c r="P7" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-      <c r="R7" s="7">
-        <v>0</v>
+      <c r="J9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-21.6</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="O9" s="11">
+        <v>1</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A7">
+  <conditionalFormatting sqref="A2:A9">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B7">
+  <conditionalFormatting sqref="B2:B9">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C7">
+  <conditionalFormatting sqref="C2:C9">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D7">
+  <conditionalFormatting sqref="D2:D9">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E7">
+  <conditionalFormatting sqref="E2:E9">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F7">
+  <conditionalFormatting sqref="F2:F9">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G7">
+  <conditionalFormatting sqref="G2:G9">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H7">
+  <conditionalFormatting sqref="H2:H9">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I7">
+  <conditionalFormatting sqref="I2:I9">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J7">
+  <conditionalFormatting sqref="J2:J9">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K7">
+  <conditionalFormatting sqref="K2:K9">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L7">
+  <conditionalFormatting sqref="L2:L9">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1305,12 +1465,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M7">
+  <conditionalFormatting sqref="M2:M9">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N7">
+  <conditionalFormatting sqref="N2:N9">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1327,22 +1487,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O7">
+  <conditionalFormatting sqref="O2:O9">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P7">
+  <conditionalFormatting sqref="P2:P9">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q7">
+  <conditionalFormatting sqref="Q2:Q9">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R7">
+  <conditionalFormatting sqref="R2:R9">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="110">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260609--01</t>
-  </si>
-  <si>
     <t>20260610--01</t>
   </si>
   <si>
@@ -94,13 +91,16 @@
     <t>20260615--02</t>
   </si>
   <si>
-    <t>04:47</t>
+    <t>20260616--01</t>
+  </si>
+  <si>
+    <t>20260616--02</t>
   </si>
   <si>
     <t>02:05</t>
   </si>
   <si>
-    <t>06:36</t>
+    <t>06:35</t>
   </si>
   <si>
     <t>05:59</t>
@@ -115,7 +115,13 @@
     <t>02:07</t>
   </si>
   <si>
-    <t>06:42</t>
+    <t>06:43</t>
+  </si>
+  <si>
+    <t>06:47</t>
+  </si>
+  <si>
+    <t>03:39</t>
   </si>
   <si>
     <t>04:41</t>
@@ -133,7 +139,7 @@
     <t>03:04</t>
   </si>
   <si>
-    <t>05:24:37</t>
+    <t>01:12</t>
   </si>
   <si>
     <t>04:40:05</t>
@@ -151,19 +157,22 @@
     <t>04:52:42</t>
   </si>
   <si>
-    <t>02:30:57</t>
+    <t>02:30:56</t>
   </si>
   <si>
     <t>04:07:07</t>
   </si>
   <si>
-    <t>05:27:11</t>
+    <t>03:21:34</t>
+  </si>
+  <si>
+    <t>05:00:09</t>
   </si>
   <si>
     <t>04:43:30</t>
   </si>
   <si>
-    <t>04:48:01</t>
+    <t>04:48:02</t>
   </si>
   <si>
     <t>04:03:04</t>
@@ -175,22 +184,25 @@
     <t>04:54:54</t>
   </si>
   <si>
-    <t>02:34:21</t>
-  </si>
-  <si>
-    <t>04:09:15</t>
-  </si>
-  <si>
-    <t>05:29:34</t>
+    <t>02:34:20</t>
+  </si>
+  <si>
+    <t>04:09:14</t>
+  </si>
+  <si>
+    <t>03:23:40</t>
+  </si>
+  <si>
+    <t>05:03:05</t>
   </si>
   <si>
     <t>04:44:32</t>
   </si>
   <si>
-    <t>04:51:18</t>
-  </si>
-  <si>
-    <t>04:06:02</t>
+    <t>04:51:19</t>
+  </si>
+  <si>
+    <t>04:06:03</t>
   </si>
   <si>
     <t>03:20:44</t>
@@ -205,7 +217,10 @@
     <t>04:12:35</t>
   </si>
   <si>
-    <t>05:31:58</t>
+    <t>03:27:03</t>
+  </si>
+  <si>
+    <t>05:04:54</t>
   </si>
   <si>
     <t>04:45:35</t>
@@ -223,13 +238,16 @@
     <t>05:01:17</t>
   </si>
   <si>
-    <t>02:36:28</t>
+    <t>02:36:27</t>
   </si>
   <si>
     <t>04:15:57</t>
   </si>
   <si>
-    <t>05:34:32</t>
+    <t>03:30:27</t>
+  </si>
+  <si>
+    <t>05:06:44</t>
   </si>
   <si>
     <t>04:49:02</t>
@@ -253,7 +271,10 @@
     <t>04:18:06</t>
   </si>
   <si>
-    <t>4°</t>
+    <t>03:32:34</t>
+  </si>
+  <si>
+    <t>05:09:42</t>
   </si>
   <si>
     <t>9°</t>
@@ -274,7 +295,10 @@
     <t>56°</t>
   </si>
   <si>
-    <t>05:25:45</t>
+    <t>20°</t>
+  </si>
+  <si>
+    <t>7°</t>
   </si>
   <si>
     <t>04:42:55</t>
@@ -292,12 +316,18 @@
     <t>04:56:24</t>
   </si>
   <si>
-    <t>02:39:48</t>
+    <t>02:39:47</t>
   </si>
   <si>
     <t>04:12:53</t>
   </si>
   <si>
+    <t>03:29:15</t>
+  </si>
+  <si>
+    <t>05:02:20</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
@@ -307,10 +337,10 @@
     <t>B</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>3</t>
@@ -347,7 +377,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -362,13 +392,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,19 +410,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -433,7 +457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -463,9 +487,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -869,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -947,49 +968,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L2" s="4">
-        <v>-8.4</v>
+        <v>-16.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="O2" s="6">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="P2" s="7">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1003,49 +1024,49 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="L3" s="4">
-        <v>-16.4</v>
+        <v>-15.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="O3" s="9">
-        <v>40</v>
-      </c>
-      <c r="P3" s="10">
-        <v>40</v>
+        <v>0</v>
+      </c>
+      <c r="P3" s="8">
+        <v>0</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1059,46 +1080,46 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="L4" s="4">
-        <v>-15.2</v>
+        <v>-22.7</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="O4" s="11">
-        <v>2</v>
+        <v>108</v>
+      </c>
+      <c r="O4" s="9">
+        <v>7</v>
       </c>
       <c r="P4" s="8">
         <v>0</v>
@@ -1106,8 +1127,8 @@
       <c r="Q4" s="8">
         <v>0</v>
       </c>
-      <c r="R4" s="8">
-        <v>2</v>
+      <c r="R4" s="10">
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1115,46 +1136,46 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="L5" s="4">
-        <v>-22.7</v>
+        <v>-29</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="O5" s="11">
-        <v>2</v>
+        <v>109</v>
+      </c>
+      <c r="O5" s="9">
+        <v>0</v>
       </c>
       <c r="P5" s="8">
         <v>0</v>
@@ -1163,7 +1184,7 @@
         <v>0</v>
       </c>
       <c r="R5" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1171,45 +1192,45 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="L6" s="4">
-        <v>-29</v>
+        <v>-14.1</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="O6" s="11">
+        <v>108</v>
+      </c>
+      <c r="O6" s="9">
         <v>0</v>
       </c>
       <c r="P6" s="8">
@@ -1227,45 +1248,45 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="L7" s="4">
-        <v>-14.1</v>
+        <v>-34</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="O7" s="11">
+        <v>107</v>
+      </c>
+      <c r="O7" s="9">
         <v>0</v>
       </c>
       <c r="P7" s="8">
@@ -1283,46 +1304,46 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="L8" s="4">
-        <v>-34</v>
+        <v>-21.6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="O8" s="11">
-        <v>2</v>
+        <v>108</v>
+      </c>
+      <c r="O8" s="9">
+        <v>0</v>
       </c>
       <c r="P8" s="8">
         <v>0</v>
@@ -1331,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1339,114 +1360,170 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>83</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-28.2</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="O9" s="9">
+        <v>0</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="2">
+        <v>14</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-21.6</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="O9" s="11">
-        <v>1</v>
-      </c>
-      <c r="P9" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8">
-        <v>1</v>
+      <c r="G10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-12.9</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="O10" s="9">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A9">
+  <conditionalFormatting sqref="A2:A10">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B9">
+  <conditionalFormatting sqref="B2:B10">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C9">
+  <conditionalFormatting sqref="C2:C10">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
+  <conditionalFormatting sqref="D2:D10">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E9">
+  <conditionalFormatting sqref="E2:E10">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
+  <conditionalFormatting sqref="F2:F10">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G9">
+  <conditionalFormatting sqref="G2:G10">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H9">
+  <conditionalFormatting sqref="H2:H10">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I9">
+  <conditionalFormatting sqref="I2:I10">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J9">
+  <conditionalFormatting sqref="J2:J10">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K9">
+  <conditionalFormatting sqref="K2:K10">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L9">
+  <conditionalFormatting sqref="L2:L10">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1465,12 +1542,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M9">
+  <conditionalFormatting sqref="M2:M10">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N9">
+  <conditionalFormatting sqref="N2:N10">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1487,22 +1564,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O9">
+  <conditionalFormatting sqref="O2:O10">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P9">
+  <conditionalFormatting sqref="P2:P10">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q9">
+  <conditionalFormatting sqref="Q2:Q10">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R9">
+  <conditionalFormatting sqref="R2:R10">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="121">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260610--01</t>
-  </si>
-  <si>
     <t>20260612--01</t>
   </si>
   <si>
@@ -97,7 +94,10 @@
     <t>20260616--02</t>
   </si>
   <si>
-    <t>02:05</t>
+    <t>20260617--01</t>
+  </si>
+  <si>
+    <t>20260617--02</t>
   </si>
   <si>
     <t>06:35</t>
@@ -124,6 +124,12 @@
     <t>03:39</t>
   </si>
   <si>
+    <t>06:33</t>
+  </si>
+  <si>
+    <t>04:54</t>
+  </si>
+  <si>
     <t>04:41</t>
   </si>
   <si>
@@ -142,7 +148,7 @@
     <t>01:12</t>
   </si>
   <si>
-    <t>04:40:05</t>
+    <t>03:02</t>
   </si>
   <si>
     <t>04:45:53</t>
@@ -169,7 +175,10 @@
     <t>05:00:09</t>
   </si>
   <si>
-    <t>04:43:30</t>
+    <t>02:36:05</t>
+  </si>
+  <si>
+    <t>04:14:09</t>
   </si>
   <si>
     <t>04:48:02</t>
@@ -196,7 +205,10 @@
     <t>05:03:05</t>
   </si>
   <si>
-    <t>04:44:32</t>
+    <t>02:38:13</t>
+  </si>
+  <si>
+    <t>04:16:43</t>
   </si>
   <si>
     <t>04:51:19</t>
@@ -223,7 +235,10 @@
     <t>05:04:54</t>
   </si>
   <si>
-    <t>04:45:35</t>
+    <t>02:41:29</t>
+  </si>
+  <si>
+    <t>04:19:09</t>
   </si>
   <si>
     <t>04:54:37</t>
@@ -250,7 +265,10 @@
     <t>05:06:44</t>
   </si>
   <si>
-    <t>04:49:02</t>
+    <t>02:44:46</t>
+  </si>
+  <si>
+    <t>04:21:37</t>
   </si>
   <si>
     <t>04:56:47</t>
@@ -277,15 +295,21 @@
     <t>05:09:42</t>
   </si>
   <si>
+    <t>02:46:56</t>
+  </si>
+  <si>
+    <t>04:24:12</t>
+  </si>
+  <si>
+    <t>29°</t>
+  </si>
+  <si>
+    <t>27°</t>
+  </si>
+  <si>
     <t>9°</t>
   </si>
   <si>
-    <t>29°</t>
-  </si>
-  <si>
-    <t>27°</t>
-  </si>
-  <si>
     <t>22°</t>
   </si>
   <si>
@@ -301,7 +325,10 @@
     <t>7°</t>
   </si>
   <si>
-    <t>04:42:55</t>
+    <t>6°</t>
+  </si>
+  <si>
+    <t>18°</t>
   </si>
   <si>
     <t>04:49:56</t>
@@ -328,22 +355,28 @@
     <t>05:02:20</t>
   </si>
   <si>
+    <t>02:45:30</t>
+  </si>
+  <si>
+    <t>04:18:35</t>
+  </si>
+  <si>
+    <t>A+B</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
-    <t>A+B</t>
-  </si>
-  <si>
-    <t>B</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -377,7 +410,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -392,13 +425,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,13 +437,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -457,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -487,6 +526,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -890,7 +932,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -968,54 +1010,54 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="L2" s="4">
-        <v>-16.4</v>
+        <v>-15.2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="O2" s="6">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="P2" s="7">
-        <v>84</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1024,55 +1066,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="L3" s="4">
-        <v>-15.2</v>
+        <v>-22.7</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="O3" s="9">
-        <v>0</v>
-      </c>
-      <c r="P3" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>0</v>
-      </c>
-      <c r="R3" s="8">
-        <v>0</v>
+        <v>118</v>
+      </c>
+      <c r="O3" s="8">
+        <v>58</v>
+      </c>
+      <c r="P3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="9">
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1080,55 +1122,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-29</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="O4" s="8">
+        <v>66</v>
+      </c>
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>0</v>
+      </c>
+      <c r="R4" s="9">
         <v>62</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-22.7</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="O4" s="9">
-        <v>7</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="10">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1136,55 +1178,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-14.1</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="O5" s="10">
         <v>30</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-29</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="O5" s="9">
-        <v>0</v>
-      </c>
-      <c r="P5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>0</v>
-      </c>
-      <c r="R5" s="8">
-        <v>0</v>
+      <c r="P5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>0</v>
+      </c>
+      <c r="R5" s="11">
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1192,55 +1234,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="L6" s="4">
-        <v>-14.1</v>
+        <v>-34</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="O6" s="9">
-        <v>0</v>
-      </c>
-      <c r="P6" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>0</v>
-      </c>
-      <c r="R6" s="8">
-        <v>0</v>
+        <v>120</v>
+      </c>
+      <c r="O6" s="6">
+        <v>2</v>
+      </c>
+      <c r="P6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>0</v>
+      </c>
+      <c r="R6" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1248,54 +1290,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="L7" s="4">
-        <v>-34</v>
+        <v>-21.6</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="O7" s="9">
-        <v>0</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>0</v>
-      </c>
-      <c r="R7" s="8">
+        <v>118</v>
+      </c>
+      <c r="O7" s="6">
+        <v>1</v>
+      </c>
+      <c r="P7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1304,54 +1346,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="L8" s="4">
-        <v>-21.6</v>
+        <v>-28.2</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="O8" s="9">
-        <v>0</v>
-      </c>
-      <c r="P8" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>0</v>
-      </c>
-      <c r="R8" s="8">
+        <v>118</v>
+      </c>
+      <c r="O8" s="6">
+        <v>0</v>
+      </c>
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1360,54 +1402,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L9" s="4">
-        <v>-28.2</v>
+        <v>-12.9</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="O9" s="9">
-        <v>0</v>
-      </c>
-      <c r="P9" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8">
+        <v>120</v>
+      </c>
+      <c r="O9" s="6">
+        <v>0</v>
+      </c>
+      <c r="P9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1416,114 +1458,170 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-33.4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="O10" s="6">
+        <v>1</v>
+      </c>
+      <c r="P10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>0</v>
+      </c>
+      <c r="R10" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="2">
+        <v>18</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="L10" s="4">
-        <v>-12.9</v>
-      </c>
-      <c r="M10" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N10" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="O10" s="9">
-        <v>0</v>
-      </c>
-      <c r="P10" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>0</v>
-      </c>
-      <c r="R10" s="8">
+      <c r="K11" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-20.6</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="O11" s="6">
+        <v>0</v>
+      </c>
+      <c r="P11" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>0</v>
+      </c>
+      <c r="R11" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A10">
+  <conditionalFormatting sqref="A2:A11">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B10">
+  <conditionalFormatting sqref="B2:B11">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C10">
+  <conditionalFormatting sqref="C2:C11">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D10">
+  <conditionalFormatting sqref="D2:D11">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E10">
+  <conditionalFormatting sqref="E2:E11">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F10">
+  <conditionalFormatting sqref="F2:F11">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G10">
+  <conditionalFormatting sqref="G2:G11">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H10">
+  <conditionalFormatting sqref="H2:H11">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I10">
+  <conditionalFormatting sqref="I2:I11">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J10">
+  <conditionalFormatting sqref="J2:J11">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K10">
+  <conditionalFormatting sqref="K2:K11">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L10">
+  <conditionalFormatting sqref="L2:L11">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1542,12 +1640,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M10">
+  <conditionalFormatting sqref="M2:M11">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N10">
+  <conditionalFormatting sqref="N2:N11">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1564,22 +1662,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O10">
+  <conditionalFormatting sqref="O2:O11">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P10">
+  <conditionalFormatting sqref="P2:P11">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q10">
+  <conditionalFormatting sqref="Q2:Q11">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R10">
+  <conditionalFormatting sqref="R2:R11">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="137">
   <si>
     <t>Datum</t>
   </si>
@@ -100,6 +100,12 @@
     <t>20260617--02</t>
   </si>
   <si>
+    <t>20260618--01</t>
+  </si>
+  <si>
+    <t>20260618--02</t>
+  </si>
+  <si>
     <t>06:35</t>
   </si>
   <si>
@@ -130,6 +136,12 @@
     <t>04:54</t>
   </si>
   <si>
+    <t>05:56</t>
+  </si>
+  <si>
+    <t>05:46</t>
+  </si>
+  <si>
     <t>04:41</t>
   </si>
   <si>
@@ -151,6 +163,9 @@
     <t>03:02</t>
   </si>
   <si>
+    <t>01:33</t>
+  </si>
+  <si>
     <t>04:45:53</t>
   </si>
   <si>
@@ -181,6 +196,12 @@
     <t>04:14:09</t>
   </si>
   <si>
+    <t>01:50:40</t>
+  </si>
+  <si>
+    <t>03:28:10</t>
+  </si>
+  <si>
     <t>04:48:02</t>
   </si>
   <si>
@@ -211,6 +232,12 @@
     <t>04:16:43</t>
   </si>
   <si>
+    <t>01:52:56</t>
+  </si>
+  <si>
+    <t>03:30:30</t>
+  </si>
+  <si>
     <t>04:51:19</t>
   </si>
   <si>
@@ -241,6 +268,12 @@
     <t>04:19:09</t>
   </si>
   <si>
+    <t>01:55:53</t>
+  </si>
+  <si>
+    <t>03:33:23</t>
+  </si>
+  <si>
     <t>04:54:37</t>
   </si>
   <si>
@@ -271,6 +304,12 @@
     <t>04:21:37</t>
   </si>
   <si>
+    <t>01:58:52</t>
+  </si>
+  <si>
+    <t>03:36:16</t>
+  </si>
+  <si>
     <t>04:56:47</t>
   </si>
   <si>
@@ -301,6 +340,12 @@
     <t>04:24:12</t>
   </si>
   <si>
+    <t>02:01:09</t>
+  </si>
+  <si>
+    <t>03:38:38</t>
+  </si>
+  <si>
     <t>29°</t>
   </si>
   <si>
@@ -359,6 +404,9 @@
   </si>
   <si>
     <t>04:18:35</t>
+  </si>
+  <si>
+    <t>03:34:43</t>
   </si>
   <si>
     <t>A+B</t>
@@ -410,7 +458,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -425,7 +473,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -437,25 +491,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -496,7 +556,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -529,6 +589,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -932,7 +998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1013,51 +1079,51 @@
         <v>48</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="L2" s="4">
         <v>-15.2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="O2" s="6">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="7">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1069,52 +1135,52 @@
         <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="L3" s="4">
         <v>-22.7</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="O3" s="8">
-        <v>58</v>
-      </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="9">
-        <v>58</v>
+        <v>134</v>
+      </c>
+      <c r="O3" s="9">
+        <v>5</v>
+      </c>
+      <c r="P3" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>0</v>
+      </c>
+      <c r="R3" s="10">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1125,52 +1191,52 @@
         <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="L4" s="4">
         <v>-29</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="O4" s="8">
-        <v>66</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>0</v>
-      </c>
-      <c r="R4" s="9">
-        <v>62</v>
+        <v>135</v>
+      </c>
+      <c r="O4" s="9">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1181,52 +1247,52 @@
         <v>37</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="L5" s="4">
         <v>-14.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="O5" s="10">
-        <v>30</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="11">
-        <v>28</v>
+        <v>134</v>
+      </c>
+      <c r="O5" s="9">
+        <v>0</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="R5" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1237,52 +1303,52 @@
         <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="L6" s="4">
         <v>-34</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="O6" s="6">
-        <v>2</v>
-      </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="7">
-        <v>1</v>
+        <v>19</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="11">
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1293,52 +1359,52 @@
         <v>59</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="L7" s="4">
         <v>-21.6</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="O7" s="6">
-        <v>1</v>
-      </c>
-      <c r="P7" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-      <c r="R7" s="7">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
+      <c r="R7" s="12">
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1349,51 +1415,51 @@
         <v>83</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="L8" s="4">
         <v>-28.2</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-      <c r="R8" s="7">
+        <v>134</v>
+      </c>
+      <c r="O8" s="9">
+        <v>1</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1405,52 +1471,52 @@
         <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="L9" s="4">
         <v>-12.9</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="O9" s="6">
-        <v>0</v>
-      </c>
-      <c r="P9" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>0</v>
-      </c>
-      <c r="R9" s="7">
-        <v>0</v>
+        <v>136</v>
+      </c>
+      <c r="O9" s="9">
+        <v>2</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1461,52 +1527,52 @@
         <v>48</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="L10" s="4">
         <v>-33.4</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="O10" s="6">
-        <v>1</v>
-      </c>
-      <c r="P10" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>0</v>
-      </c>
-      <c r="R10" s="7">
-        <v>1</v>
+        <v>135</v>
+      </c>
+      <c r="O10" s="9">
+        <v>9</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>0</v>
+      </c>
+      <c r="R10" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1517,111 +1583,223 @@
         <v>18</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="L11" s="4">
         <v>-20.6</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="O11" s="6">
-        <v>0</v>
-      </c>
-      <c r="P11" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>0</v>
-      </c>
-      <c r="R11" s="7">
+        <v>134</v>
+      </c>
+      <c r="O11" s="9">
+        <v>0</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>0</v>
+      </c>
+      <c r="R11" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="2">
+        <v>28</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L12" s="4">
+        <v>-37</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="O12" s="9">
+        <v>0</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="2">
+        <v>25</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-27.4</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="O13" s="9">
+        <v>0</v>
+      </c>
+      <c r="P13" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>0</v>
+      </c>
+      <c r="R13" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A11">
+  <conditionalFormatting sqref="A2:A13">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B11">
+  <conditionalFormatting sqref="B2:B13">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C11">
+  <conditionalFormatting sqref="C2:C13">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D11">
+  <conditionalFormatting sqref="D2:D13">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E11">
+  <conditionalFormatting sqref="E2:E13">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F11">
+  <conditionalFormatting sqref="F2:F13">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G11">
+  <conditionalFormatting sqref="G2:G13">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H11">
+  <conditionalFormatting sqref="H2:H13">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I11">
+  <conditionalFormatting sqref="I2:I13">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J11">
+  <conditionalFormatting sqref="J2:J13">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K11">
+  <conditionalFormatting sqref="K2:K13">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L11">
+  <conditionalFormatting sqref="L2:L13">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1640,12 +1818,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M11">
+  <conditionalFormatting sqref="M2:M13">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N11">
+  <conditionalFormatting sqref="N2:N13">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1662,22 +1840,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O11">
+  <conditionalFormatting sqref="O2:O13">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P11">
+  <conditionalFormatting sqref="P2:P13">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q11">
+  <conditionalFormatting sqref="Q2:Q13">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R11">
+  <conditionalFormatting sqref="R2:R13">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="144">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260612--01</t>
-  </si>
-  <si>
     <t>20260613--01</t>
   </si>
   <si>
@@ -106,7 +103,10 @@
     <t>20260618--02</t>
   </si>
   <si>
-    <t>06:35</t>
+    <t>20260619--01</t>
+  </si>
+  <si>
+    <t>20260619--02</t>
   </si>
   <si>
     <t>05:59</t>
@@ -115,7 +115,7 @@
     <t>04:48</t>
   </si>
   <si>
-    <t>06:23</t>
+    <t>06:22</t>
   </si>
   <si>
     <t>02:07</t>
@@ -130,7 +130,7 @@
     <t>03:39</t>
   </si>
   <si>
-    <t>06:33</t>
+    <t>06:34</t>
   </si>
   <si>
     <t>04:54</t>
@@ -142,7 +142,10 @@
     <t>05:46</t>
   </si>
   <si>
-    <t>04:41</t>
+    <t>04:43</t>
+  </si>
+  <si>
+    <t>06:21</t>
   </si>
   <si>
     <t>02:22</t>
@@ -157,7 +160,7 @@
     <t>03:04</t>
   </si>
   <si>
-    <t>01:12</t>
+    <t>01:13</t>
   </si>
   <si>
     <t>03:02</t>
@@ -166,247 +169,265 @@
     <t>01:33</t>
   </si>
   <si>
-    <t>04:45:53</t>
-  </si>
-  <si>
-    <t>04:00:48</t>
-  </si>
-  <si>
-    <t>03:15:48</t>
-  </si>
-  <si>
-    <t>04:52:42</t>
-  </si>
-  <si>
-    <t>02:30:56</t>
-  </si>
-  <si>
-    <t>04:07:07</t>
-  </si>
-  <si>
-    <t>03:21:34</t>
-  </si>
-  <si>
-    <t>05:00:09</t>
-  </si>
-  <si>
-    <t>02:36:05</t>
-  </si>
-  <si>
-    <t>04:14:09</t>
-  </si>
-  <si>
-    <t>01:50:40</t>
-  </si>
-  <si>
-    <t>03:28:10</t>
-  </si>
-  <si>
-    <t>04:48:02</t>
-  </si>
-  <si>
-    <t>04:03:04</t>
-  </si>
-  <si>
-    <t>03:18:21</t>
-  </si>
-  <si>
-    <t>04:54:54</t>
-  </si>
-  <si>
-    <t>02:34:20</t>
-  </si>
-  <si>
-    <t>04:09:14</t>
-  </si>
-  <si>
-    <t>03:23:40</t>
-  </si>
-  <si>
-    <t>05:03:05</t>
-  </si>
-  <si>
-    <t>02:38:13</t>
-  </si>
-  <si>
-    <t>04:16:43</t>
-  </si>
-  <si>
-    <t>01:52:56</t>
-  </si>
-  <si>
-    <t>03:30:30</t>
-  </si>
-  <si>
-    <t>04:51:19</t>
-  </si>
-  <si>
-    <t>04:06:03</t>
-  </si>
-  <si>
-    <t>03:20:44</t>
-  </si>
-  <si>
-    <t>04:58:05</t>
-  </si>
-  <si>
-    <t>02:35:24</t>
-  </si>
-  <si>
-    <t>04:12:35</t>
-  </si>
-  <si>
-    <t>03:27:03</t>
-  </si>
-  <si>
-    <t>05:04:54</t>
-  </si>
-  <si>
-    <t>02:41:29</t>
-  </si>
-  <si>
-    <t>04:19:09</t>
-  </si>
-  <si>
-    <t>01:55:53</t>
-  </si>
-  <si>
-    <t>03:33:23</t>
-  </si>
-  <si>
-    <t>04:54:37</t>
-  </si>
-  <si>
-    <t>04:09:03</t>
-  </si>
-  <si>
-    <t>03:23:09</t>
-  </si>
-  <si>
-    <t>05:01:17</t>
-  </si>
-  <si>
-    <t>02:36:27</t>
-  </si>
-  <si>
-    <t>04:15:57</t>
-  </si>
-  <si>
-    <t>03:30:27</t>
-  </si>
-  <si>
-    <t>05:06:44</t>
-  </si>
-  <si>
-    <t>02:44:46</t>
-  </si>
-  <si>
-    <t>04:21:37</t>
-  </si>
-  <si>
-    <t>01:58:52</t>
-  </si>
-  <si>
-    <t>03:36:16</t>
-  </si>
-  <si>
-    <t>04:56:47</t>
-  </si>
-  <si>
-    <t>04:11:20</t>
-  </si>
-  <si>
-    <t>03:25:42</t>
-  </si>
-  <si>
-    <t>05:03:31</t>
+    <t>00:01</t>
+  </si>
+  <si>
+    <t>04:00:50</t>
+  </si>
+  <si>
+    <t>03:15:51</t>
+  </si>
+  <si>
+    <t>04:52:46</t>
+  </si>
+  <si>
+    <t>02:31:01</t>
+  </si>
+  <si>
+    <t>04:07:12</t>
+  </si>
+  <si>
+    <t>03:21:41</t>
+  </si>
+  <si>
+    <t>05:00:16</t>
+  </si>
+  <si>
+    <t>02:36:14</t>
+  </si>
+  <si>
+    <t>04:14:19</t>
+  </si>
+  <si>
+    <t>01:50:52</t>
+  </si>
+  <si>
+    <t>03:28:22</t>
+  </si>
+  <si>
+    <t>01:05:36</t>
+  </si>
+  <si>
+    <t>02:42:28</t>
+  </si>
+  <si>
+    <t>04:03:06</t>
+  </si>
+  <si>
+    <t>03:18:24</t>
+  </si>
+  <si>
+    <t>04:54:58</t>
+  </si>
+  <si>
+    <t>02:34:25</t>
+  </si>
+  <si>
+    <t>04:09:19</t>
+  </si>
+  <si>
+    <t>03:23:47</t>
+  </si>
+  <si>
+    <t>05:03:12</t>
+  </si>
+  <si>
+    <t>02:38:22</t>
+  </si>
+  <si>
+    <t>04:16:52</t>
+  </si>
+  <si>
+    <t>01:53:08</t>
+  </si>
+  <si>
+    <t>03:30:42</t>
+  </si>
+  <si>
+    <t>01:08:09</t>
+  </si>
+  <si>
+    <t>02:44:40</t>
+  </si>
+  <si>
+    <t>04:06:04</t>
+  </si>
+  <si>
+    <t>03:20:47</t>
+  </si>
+  <si>
+    <t>04:58:08</t>
+  </si>
+  <si>
+    <t>02:35:28</t>
+  </si>
+  <si>
+    <t>04:12:40</t>
+  </si>
+  <si>
+    <t>03:27:10</t>
+  </si>
+  <si>
+    <t>05:05:02</t>
+  </si>
+  <si>
+    <t>02:41:38</t>
+  </si>
+  <si>
+    <t>04:19:19</t>
+  </si>
+  <si>
+    <t>01:56:05</t>
+  </si>
+  <si>
+    <t>03:33:35</t>
+  </si>
+  <si>
+    <t>01:10:30</t>
+  </si>
+  <si>
+    <t>02:47:49</t>
+  </si>
+  <si>
+    <t>04:09:05</t>
+  </si>
+  <si>
+    <t>03:23:12</t>
+  </si>
+  <si>
+    <t>05:01:20</t>
+  </si>
+  <si>
+    <t>02:36:32</t>
+  </si>
+  <si>
+    <t>04:16:02</t>
+  </si>
+  <si>
+    <t>03:30:34</t>
+  </si>
+  <si>
+    <t>05:06:51</t>
+  </si>
+  <si>
+    <t>02:44:56</t>
+  </si>
+  <si>
+    <t>04:21:46</t>
+  </si>
+  <si>
+    <t>01:59:04</t>
+  </si>
+  <si>
+    <t>03:36:28</t>
+  </si>
+  <si>
+    <t>01:12:52</t>
+  </si>
+  <si>
+    <t>02:51:01</t>
+  </si>
+  <si>
+    <t>04:11:22</t>
+  </si>
+  <si>
+    <t>03:25:46</t>
+  </si>
+  <si>
+    <t>05:03:34</t>
+  </si>
+  <si>
+    <t>02:39:57</t>
+  </si>
+  <si>
+    <t>04:18:11</t>
+  </si>
+  <si>
+    <t>03:32:41</t>
+  </si>
+  <si>
+    <t>05:09:49</t>
+  </si>
+  <si>
+    <t>02:47:05</t>
+  </si>
+  <si>
+    <t>04:24:21</t>
+  </si>
+  <si>
+    <t>02:01:21</t>
+  </si>
+  <si>
+    <t>03:38:50</t>
+  </si>
+  <si>
+    <t>01:15:26</t>
+  </si>
+  <si>
+    <t>02:53:14</t>
+  </si>
+  <si>
+    <t>27°</t>
+  </si>
+  <si>
+    <t>9°</t>
+  </si>
+  <si>
+    <t>22°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>56°</t>
+  </si>
+  <si>
+    <t>20°</t>
+  </si>
+  <si>
+    <t>7°</t>
+  </si>
+  <si>
+    <t>6°</t>
+  </si>
+  <si>
+    <t>18°</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>04:06:43</t>
+  </si>
+  <si>
+    <t>03:23:21</t>
+  </si>
+  <si>
+    <t>04:56:27</t>
   </si>
   <si>
     <t>02:39:52</t>
   </si>
   <si>
-    <t>04:18:06</t>
-  </si>
-  <si>
-    <t>03:32:34</t>
-  </si>
-  <si>
-    <t>05:09:42</t>
-  </si>
-  <si>
-    <t>02:46:56</t>
-  </si>
-  <si>
-    <t>04:24:12</t>
-  </si>
-  <si>
-    <t>02:01:09</t>
-  </si>
-  <si>
-    <t>03:38:38</t>
-  </si>
-  <si>
-    <t>29°</t>
-  </si>
-  <si>
-    <t>27°</t>
-  </si>
-  <si>
-    <t>9°</t>
-  </si>
-  <si>
-    <t>22°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>56°</t>
-  </si>
-  <si>
-    <t>20°</t>
-  </si>
-  <si>
-    <t>7°</t>
-  </si>
-  <si>
-    <t>6°</t>
-  </si>
-  <si>
-    <t>18°</t>
-  </si>
-  <si>
-    <t>04:49:56</t>
-  </si>
-  <si>
-    <t>04:06:41</t>
-  </si>
-  <si>
-    <t>03:23:18</t>
-  </si>
-  <si>
-    <t>04:56:24</t>
-  </si>
-  <si>
-    <t>02:39:47</t>
-  </si>
-  <si>
-    <t>04:12:53</t>
-  </si>
-  <si>
-    <t>03:29:15</t>
-  </si>
-  <si>
-    <t>05:02:20</t>
-  </si>
-  <si>
-    <t>02:45:30</t>
-  </si>
-  <si>
-    <t>04:18:35</t>
-  </si>
-  <si>
-    <t>03:34:43</t>
+    <t>04:12:58</t>
+  </si>
+  <si>
+    <t>03:29:21</t>
+  </si>
+  <si>
+    <t>05:02:27</t>
+  </si>
+  <si>
+    <t>02:45:39</t>
+  </si>
+  <si>
+    <t>04:18:44</t>
+  </si>
+  <si>
+    <t>03:34:55</t>
+  </si>
+  <si>
+    <t>02:51:00</t>
   </si>
   <si>
     <t>A+B</t>
@@ -458,7 +479,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -473,19 +494,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -503,19 +530,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -556,7 +589,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -595,6 +628,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -998,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1076,55 +1115,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="L2" s="4">
-        <v>-15.2</v>
+        <v>-22.7</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="O2" s="6">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="P2" s="7">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
       </c>
-      <c r="R2" s="8">
-        <v>0</v>
+      <c r="R2" s="9">
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1132,46 +1171,46 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="L3" s="4">
-        <v>-22.7</v>
+        <v>-29</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="O3" s="9">
-        <v>5</v>
+        <v>142</v>
+      </c>
+      <c r="O3" s="10">
+        <v>3</v>
       </c>
       <c r="P3" s="8">
         <v>0</v>
@@ -1179,8 +1218,8 @@
       <c r="Q3" s="8">
         <v>0</v>
       </c>
-      <c r="R3" s="10">
-        <v>4</v>
+      <c r="R3" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1188,46 +1227,46 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="L4" s="4">
-        <v>-29</v>
+        <v>-14</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O4" s="9">
-        <v>0</v>
+        <v>141</v>
+      </c>
+      <c r="O4" s="10">
+        <v>3</v>
       </c>
       <c r="P4" s="8">
         <v>0</v>
@@ -1235,8 +1274,8 @@
       <c r="Q4" s="8">
         <v>0</v>
       </c>
-      <c r="R4" s="8">
-        <v>0</v>
+      <c r="R4" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1244,55 +1283,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-34</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="O5" s="6">
         <v>65</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-14.1</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="O5" s="9">
-        <v>0</v>
-      </c>
       <c r="P5" s="8">
         <v>0</v>
       </c>
       <c r="Q5" s="8">
         <v>0</v>
       </c>
-      <c r="R5" s="8">
-        <v>0</v>
+      <c r="R5" s="12">
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1300,46 +1339,46 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="L6" s="4">
-        <v>-34</v>
+        <v>-21.6</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O6" s="6">
-        <v>19</v>
+        <v>141</v>
+      </c>
+      <c r="O6" s="10">
+        <v>4</v>
       </c>
       <c r="P6" s="8">
         <v>0</v>
@@ -1348,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="R6" s="11">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1356,46 +1395,46 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="L7" s="4">
-        <v>-21.6</v>
+        <v>-28.2</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="O7" s="6">
-        <v>21</v>
+        <v>141</v>
+      </c>
+      <c r="O7" s="10">
+        <v>2</v>
       </c>
       <c r="P7" s="8">
         <v>0</v>
@@ -1403,8 +1442,8 @@
       <c r="Q7" s="8">
         <v>0</v>
       </c>
-      <c r="R7" s="12">
-        <v>18</v>
+      <c r="R7" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1412,46 +1451,46 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="L8" s="4">
-        <v>-28.2</v>
+        <v>-12.9</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="O8" s="9">
-        <v>1</v>
+        <v>143</v>
+      </c>
+      <c r="O8" s="10">
+        <v>0</v>
       </c>
       <c r="P8" s="8">
         <v>0</v>
@@ -1468,46 +1507,46 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="L9" s="4">
-        <v>-12.9</v>
+        <v>-33.4</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O9" s="9">
-        <v>2</v>
+        <v>142</v>
+      </c>
+      <c r="O9" s="10">
+        <v>0</v>
       </c>
       <c r="P9" s="8">
         <v>0</v>
@@ -1516,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1524,46 +1563,46 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="L10" s="4">
-        <v>-33.4</v>
+        <v>-20.6</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O10" s="9">
-        <v>9</v>
+        <v>141</v>
+      </c>
+      <c r="O10" s="10">
+        <v>6</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
@@ -1571,8 +1610,8 @@
       <c r="Q10" s="8">
         <v>0</v>
       </c>
-      <c r="R10" s="13">
-        <v>9</v>
+      <c r="R10" s="11">
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1580,46 +1619,46 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="L11" s="4">
-        <v>-20.6</v>
+        <v>-37</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="O11" s="9">
-        <v>0</v>
+        <v>142</v>
+      </c>
+      <c r="O11" s="10">
+        <v>9</v>
       </c>
       <c r="P11" s="8">
         <v>0</v>
@@ -1627,8 +1666,8 @@
       <c r="Q11" s="8">
         <v>0</v>
       </c>
-      <c r="R11" s="8">
-        <v>0</v>
+      <c r="R11" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1636,55 +1675,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
+        <v>25</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="L12" s="4">
+        <v>-27.4</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="O12" s="14">
         <v>28</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L12" s="4">
-        <v>-37</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O12" s="9">
-        <v>0</v>
-      </c>
       <c r="P12" s="8">
         <v>0</v>
       </c>
       <c r="Q12" s="8">
         <v>0</v>
       </c>
-      <c r="R12" s="8">
-        <v>0</v>
+      <c r="R12" s="15">
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1692,114 +1731,170 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="J13" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-38.3</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="O13" s="10">
+        <v>4</v>
+      </c>
+      <c r="P13" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>0</v>
+      </c>
+      <c r="R13" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="2">
+        <v>37</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-27.4</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="O13" s="9">
-        <v>0</v>
-      </c>
-      <c r="P13" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>0</v>
-      </c>
-      <c r="R13" s="8">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="L14" s="4">
+        <v>-32.8</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="O14" s="10">
+        <v>7</v>
+      </c>
+      <c r="P14" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>0</v>
+      </c>
+      <c r="R14" s="11">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A13">
+  <conditionalFormatting sqref="A2:A14">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B13">
+  <conditionalFormatting sqref="B2:B14">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C13">
+  <conditionalFormatting sqref="C2:C14">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D13">
+  <conditionalFormatting sqref="D2:D14">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E13">
+  <conditionalFormatting sqref="E2:E14">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F13">
+  <conditionalFormatting sqref="F2:F14">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G13">
+  <conditionalFormatting sqref="G2:G14">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H13">
+  <conditionalFormatting sqref="H2:H14">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I13">
+  <conditionalFormatting sqref="I2:I14">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J13">
+  <conditionalFormatting sqref="J2:J14">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K13">
+  <conditionalFormatting sqref="K2:K14">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L13">
+  <conditionalFormatting sqref="L2:L14">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1818,12 +1913,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M13">
+  <conditionalFormatting sqref="M2:M14">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N13">
+  <conditionalFormatting sqref="N2:N14">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1840,22 +1935,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O13">
+  <conditionalFormatting sqref="O2:O14">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P13">
+  <conditionalFormatting sqref="P2:P14">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q13">
+  <conditionalFormatting sqref="Q2:Q14">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R13">
+  <conditionalFormatting sqref="R2:R14">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="156">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260613--01</t>
-  </si>
-  <si>
     <t>20260614--01</t>
   </si>
   <si>
@@ -109,19 +106,25 @@
     <t>20260619--02</t>
   </si>
   <si>
-    <t>05:59</t>
+    <t>20260620--01</t>
+  </si>
+  <si>
+    <t>20260620--02</t>
+  </si>
+  <si>
+    <t>20260620--03</t>
   </si>
   <si>
     <t>04:48</t>
   </si>
   <si>
-    <t>06:22</t>
-  </si>
-  <si>
-    <t>02:07</t>
-  </si>
-  <si>
-    <t>06:43</t>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>02:06</t>
+  </si>
+  <si>
+    <t>06:42</t>
   </si>
   <si>
     <t>06:47</t>
@@ -130,7 +133,7 @@
     <t>03:39</t>
   </si>
   <si>
-    <t>06:34</t>
+    <t>06:33</t>
   </si>
   <si>
     <t>04:54</t>
@@ -139,24 +142,27 @@
     <t>05:56</t>
   </si>
   <si>
-    <t>05:46</t>
-  </si>
-  <si>
-    <t>04:43</t>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>04:42</t>
   </si>
   <si>
     <t>06:21</t>
   </si>
   <si>
-    <t>02:22</t>
+    <t>01:46</t>
+  </si>
+  <si>
+    <t>06:41</t>
+  </si>
+  <si>
+    <t>01:28</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>04:53</t>
-  </si>
-  <si>
     <t>03:04</t>
   </si>
   <si>
@@ -169,205 +175,232 @@
     <t>01:33</t>
   </si>
   <si>
-    <t>00:01</t>
-  </si>
-  <si>
-    <t>04:00:50</t>
+    <t>00:44</t>
   </si>
   <si>
     <t>03:15:51</t>
   </si>
   <si>
-    <t>04:52:46</t>
-  </si>
-  <si>
-    <t>02:31:01</t>
-  </si>
-  <si>
-    <t>04:07:12</t>
-  </si>
-  <si>
-    <t>03:21:41</t>
-  </si>
-  <si>
-    <t>05:00:16</t>
-  </si>
-  <si>
-    <t>02:36:14</t>
-  </si>
-  <si>
-    <t>04:14:19</t>
-  </si>
-  <si>
-    <t>01:50:52</t>
-  </si>
-  <si>
-    <t>03:28:22</t>
-  </si>
-  <si>
-    <t>01:05:36</t>
-  </si>
-  <si>
-    <t>02:42:28</t>
-  </si>
-  <si>
-    <t>04:03:06</t>
-  </si>
-  <si>
-    <t>03:18:24</t>
-  </si>
-  <si>
-    <t>04:54:58</t>
-  </si>
-  <si>
-    <t>02:34:25</t>
-  </si>
-  <si>
-    <t>04:09:19</t>
-  </si>
-  <si>
-    <t>03:23:47</t>
-  </si>
-  <si>
-    <t>05:03:12</t>
-  </si>
-  <si>
-    <t>02:38:22</t>
-  </si>
-  <si>
-    <t>04:16:52</t>
-  </si>
-  <si>
-    <t>01:53:08</t>
-  </si>
-  <si>
-    <t>03:30:42</t>
-  </si>
-  <si>
-    <t>01:08:09</t>
-  </si>
-  <si>
-    <t>02:44:40</t>
-  </si>
-  <si>
-    <t>04:06:04</t>
+    <t>04:52:45</t>
+  </si>
+  <si>
+    <t>02:31:00</t>
+  </si>
+  <si>
+    <t>04:07:10</t>
+  </si>
+  <si>
+    <t>03:21:39</t>
+  </si>
+  <si>
+    <t>05:00:14</t>
+  </si>
+  <si>
+    <t>02:36:11</t>
+  </si>
+  <si>
+    <t>04:14:16</t>
+  </si>
+  <si>
+    <t>01:50:48</t>
+  </si>
+  <si>
+    <t>03:28:18</t>
+  </si>
+  <si>
+    <t>01:05:32</t>
+  </si>
+  <si>
+    <t>02:42:23</t>
+  </si>
+  <si>
+    <t>00:20:24</t>
+  </si>
+  <si>
+    <t>01:56:31</t>
+  </si>
+  <si>
+    <t>03:35:31</t>
+  </si>
+  <si>
+    <t>03:18:23</t>
+  </si>
+  <si>
+    <t>04:54:57</t>
+  </si>
+  <si>
+    <t>02:34:24</t>
+  </si>
+  <si>
+    <t>04:09:18</t>
+  </si>
+  <si>
+    <t>03:23:45</t>
+  </si>
+  <si>
+    <t>05:03:10</t>
+  </si>
+  <si>
+    <t>02:38:20</t>
+  </si>
+  <si>
+    <t>04:16:49</t>
+  </si>
+  <si>
+    <t>01:53:04</t>
+  </si>
+  <si>
+    <t>03:30:39</t>
+  </si>
+  <si>
+    <t>01:08:05</t>
+  </si>
+  <si>
+    <t>02:44:35</t>
+  </si>
+  <si>
+    <t>00:23:55</t>
+  </si>
+  <si>
+    <t>01:58:38</t>
+  </si>
+  <si>
+    <t>03:39:15</t>
   </si>
   <si>
     <t>03:20:47</t>
   </si>
   <si>
-    <t>04:58:08</t>
-  </si>
-  <si>
-    <t>02:35:28</t>
-  </si>
-  <si>
-    <t>04:12:40</t>
-  </si>
-  <si>
-    <t>03:27:10</t>
-  </si>
-  <si>
-    <t>05:05:02</t>
-  </si>
-  <si>
-    <t>02:41:38</t>
-  </si>
-  <si>
-    <t>04:19:19</t>
-  </si>
-  <si>
-    <t>01:56:05</t>
-  </si>
-  <si>
-    <t>03:33:35</t>
-  </si>
-  <si>
-    <t>01:10:30</t>
-  </si>
-  <si>
-    <t>02:47:49</t>
-  </si>
-  <si>
-    <t>04:09:05</t>
-  </si>
-  <si>
-    <t>03:23:12</t>
+    <t>04:58:07</t>
+  </si>
+  <si>
+    <t>02:35:27</t>
+  </si>
+  <si>
+    <t>04:12:38</t>
+  </si>
+  <si>
+    <t>03:27:08</t>
+  </si>
+  <si>
+    <t>05:04:59</t>
+  </si>
+  <si>
+    <t>02:41:35</t>
+  </si>
+  <si>
+    <t>04:19:16</t>
+  </si>
+  <si>
+    <t>01:56:02</t>
+  </si>
+  <si>
+    <t>03:33:31</t>
+  </si>
+  <si>
+    <t>01:10:26</t>
+  </si>
+  <si>
+    <t>02:47:45</t>
+  </si>
+  <si>
+    <t>00:24:48</t>
+  </si>
+  <si>
+    <t>02:01:57</t>
+  </si>
+  <si>
+    <t>03:39:59</t>
+  </si>
+  <si>
+    <t>03:23:11</t>
   </si>
   <si>
     <t>05:01:20</t>
   </si>
   <si>
-    <t>02:36:32</t>
-  </si>
-  <si>
-    <t>04:16:02</t>
-  </si>
-  <si>
-    <t>03:30:34</t>
-  </si>
-  <si>
-    <t>05:06:51</t>
-  </si>
-  <si>
-    <t>02:44:56</t>
-  </si>
-  <si>
-    <t>04:21:46</t>
-  </si>
-  <si>
-    <t>01:59:04</t>
-  </si>
-  <si>
-    <t>03:36:28</t>
-  </si>
-  <si>
-    <t>01:12:52</t>
-  </si>
-  <si>
-    <t>02:51:01</t>
-  </si>
-  <si>
-    <t>04:11:22</t>
-  </si>
-  <si>
-    <t>03:25:46</t>
-  </si>
-  <si>
-    <t>05:03:34</t>
-  </si>
-  <si>
-    <t>02:39:57</t>
-  </si>
-  <si>
-    <t>04:18:11</t>
-  </si>
-  <si>
-    <t>03:32:41</t>
-  </si>
-  <si>
-    <t>05:09:49</t>
-  </si>
-  <si>
-    <t>02:47:05</t>
-  </si>
-  <si>
-    <t>04:24:21</t>
-  </si>
-  <si>
-    <t>02:01:21</t>
-  </si>
-  <si>
-    <t>03:38:50</t>
-  </si>
-  <si>
-    <t>01:15:26</t>
-  </si>
-  <si>
-    <t>02:53:14</t>
-  </si>
-  <si>
-    <t>27°</t>
+    <t>02:36:30</t>
+  </si>
+  <si>
+    <t>04:16:00</t>
+  </si>
+  <si>
+    <t>03:30:32</t>
+  </si>
+  <si>
+    <t>05:06:49</t>
+  </si>
+  <si>
+    <t>02:44:53</t>
+  </si>
+  <si>
+    <t>04:21:43</t>
+  </si>
+  <si>
+    <t>01:59:00</t>
+  </si>
+  <si>
+    <t>03:36:24</t>
+  </si>
+  <si>
+    <t>01:12:47</t>
+  </si>
+  <si>
+    <t>02:50:56</t>
+  </si>
+  <si>
+    <t>00:25:41</t>
+  </si>
+  <si>
+    <t>02:05:19</t>
+  </si>
+  <si>
+    <t>03:40:43</t>
+  </si>
+  <si>
+    <t>03:25:45</t>
+  </si>
+  <si>
+    <t>05:03:33</t>
+  </si>
+  <si>
+    <t>02:39:55</t>
+  </si>
+  <si>
+    <t>04:18:09</t>
+  </si>
+  <si>
+    <t>03:32:39</t>
+  </si>
+  <si>
+    <t>05:09:47</t>
+  </si>
+  <si>
+    <t>02:47:02</t>
+  </si>
+  <si>
+    <t>04:24:18</t>
+  </si>
+  <si>
+    <t>02:01:17</t>
+  </si>
+  <si>
+    <t>03:38:46</t>
+  </si>
+  <si>
+    <t>01:15:22</t>
+  </si>
+  <si>
+    <t>02:53:09</t>
+  </si>
+  <si>
+    <t>00:29:13</t>
+  </si>
+  <si>
+    <t>02:07:27</t>
+  </si>
+  <si>
+    <t>03:44:28</t>
   </si>
   <si>
     <t>9°</t>
@@ -397,52 +430,55 @@
     <t>10°</t>
   </si>
   <si>
-    <t>04:06:43</t>
-  </si>
-  <si>
-    <t>03:23:21</t>
-  </si>
-  <si>
-    <t>04:56:27</t>
-  </si>
-  <si>
-    <t>02:39:52</t>
-  </si>
-  <si>
-    <t>04:12:58</t>
-  </si>
-  <si>
-    <t>03:29:21</t>
-  </si>
-  <si>
-    <t>05:02:27</t>
-  </si>
-  <si>
-    <t>02:45:39</t>
-  </si>
-  <si>
-    <t>04:18:44</t>
-  </si>
-  <si>
-    <t>03:34:55</t>
-  </si>
-  <si>
-    <t>02:51:00</t>
+    <t>2°</t>
+  </si>
+  <si>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>03:23:20</t>
+  </si>
+  <si>
+    <t>04:56:26</t>
+  </si>
+  <si>
+    <t>02:39:50</t>
+  </si>
+  <si>
+    <t>04:12:56</t>
+  </si>
+  <si>
+    <t>03:29:19</t>
+  </si>
+  <si>
+    <t>05:02:25</t>
+  </si>
+  <si>
+    <t>02:45:36</t>
+  </si>
+  <si>
+    <t>04:18:41</t>
+  </si>
+  <si>
+    <t>03:34:51</t>
+  </si>
+  <si>
+    <t>02:06:55</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>4</t>
@@ -479,7 +515,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -494,13 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,25 +548,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,13 +560,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -589,7 +607,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -625,15 +643,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1037,7 +1046,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1115,55 +1124,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="L2" s="4">
-        <v>-22.7</v>
+        <v>-29</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="O2" s="6">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="P2" s="7">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
       </c>
-      <c r="R2" s="9">
-        <v>69</v>
+      <c r="R2" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1171,55 +1180,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="L3" s="4">
-        <v>-29</v>
+        <v>-14</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O3" s="10">
-        <v>3</v>
-      </c>
-      <c r="P3" s="8">
-        <v>0</v>
+        <v>154</v>
+      </c>
+      <c r="O3" s="6">
+        <v>47</v>
+      </c>
+      <c r="P3" s="7">
+        <v>36</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
       </c>
-      <c r="R3" s="11">
-        <v>3</v>
+      <c r="R3" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1227,46 +1236,46 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="L4" s="4">
-        <v>-14</v>
+        <v>-34</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="O4" s="10">
-        <v>3</v>
+        <v>155</v>
+      </c>
+      <c r="O4" s="9">
+        <v>11</v>
       </c>
       <c r="P4" s="8">
         <v>0</v>
@@ -1274,8 +1283,8 @@
       <c r="Q4" s="8">
         <v>0</v>
       </c>
-      <c r="R4" s="11">
-        <v>3</v>
+      <c r="R4" s="10">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1283,46 +1292,46 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="L5" s="4">
-        <v>-34</v>
+        <v>-21.6</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O5" s="6">
-        <v>65</v>
+        <v>154</v>
+      </c>
+      <c r="O5" s="11">
+        <v>67</v>
       </c>
       <c r="P5" s="8">
         <v>0</v>
@@ -1331,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="R5" s="12">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1339,46 +1348,46 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="L6" s="4">
-        <v>-21.6</v>
+        <v>-28.2</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="O6" s="10">
-        <v>4</v>
+        <v>154</v>
+      </c>
+      <c r="O6" s="9">
+        <v>0</v>
       </c>
       <c r="P6" s="8">
         <v>0</v>
@@ -1386,8 +1395,8 @@
       <c r="Q6" s="8">
         <v>0</v>
       </c>
-      <c r="R6" s="11">
-        <v>3</v>
+      <c r="R6" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1395,46 +1404,46 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="L7" s="4">
-        <v>-28.2</v>
+        <v>-12.9</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="O7" s="10">
-        <v>2</v>
+        <v>155</v>
+      </c>
+      <c r="O7" s="9">
+        <v>0</v>
       </c>
       <c r="P7" s="8">
         <v>0</v>
@@ -1443,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="R7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1451,45 +1460,45 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="L8" s="4">
-        <v>-12.9</v>
+        <v>-33.4</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O8" s="10">
+        <v>153</v>
+      </c>
+      <c r="O8" s="9">
         <v>0</v>
       </c>
       <c r="P8" s="8">
@@ -1507,45 +1516,45 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="L9" s="4">
-        <v>-33.4</v>
+        <v>-20.6</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O9" s="10">
+        <v>154</v>
+      </c>
+      <c r="O9" s="9">
         <v>0</v>
       </c>
       <c r="P9" s="8">
@@ -1563,46 +1572,46 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="L10" s="4">
-        <v>-20.6</v>
+        <v>-37</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="O10" s="10">
-        <v>6</v>
+        <v>153</v>
+      </c>
+      <c r="O10" s="9">
+        <v>0</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
@@ -1610,8 +1619,8 @@
       <c r="Q10" s="8">
         <v>0</v>
       </c>
-      <c r="R10" s="11">
-        <v>6</v>
+      <c r="R10" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1619,46 +1628,46 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="L11" s="4">
-        <v>-37</v>
+        <v>-27.4</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O11" s="10">
-        <v>9</v>
+        <v>154</v>
+      </c>
+      <c r="O11" s="9">
+        <v>0</v>
       </c>
       <c r="P11" s="8">
         <v>0</v>
@@ -1666,8 +1675,8 @@
       <c r="Q11" s="8">
         <v>0</v>
       </c>
-      <c r="R11" s="13">
-        <v>9</v>
+      <c r="R11" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1675,46 +1684,46 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="L12" s="4">
-        <v>-27.4</v>
+        <v>-38.3</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="O12" s="14">
-        <v>28</v>
+        <v>153</v>
+      </c>
+      <c r="O12" s="9">
+        <v>0</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
@@ -1722,8 +1731,8 @@
       <c r="Q12" s="8">
         <v>0</v>
       </c>
-      <c r="R12" s="15">
-        <v>28</v>
+      <c r="R12" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1731,46 +1740,46 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
       <c r="L13" s="4">
-        <v>-38.3</v>
+        <v>-32.8</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O13" s="10">
-        <v>4</v>
+        <v>154</v>
+      </c>
+      <c r="O13" s="9">
+        <v>0</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
@@ -1778,8 +1787,8 @@
       <c r="Q13" s="8">
         <v>0</v>
       </c>
-      <c r="R13" s="11">
-        <v>4</v>
+      <c r="R13" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1787,114 +1796,226 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>137</v>
+        <v>66</v>
       </c>
       <c r="L14" s="4">
-        <v>-32.8</v>
+        <v>-37.2</v>
       </c>
       <c r="M14" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="O14" s="9">
+        <v>1</v>
+      </c>
+      <c r="P14" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>0</v>
+      </c>
+      <c r="R14" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="2">
+        <v>60</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="N14" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="O14" s="10">
-        <v>7</v>
-      </c>
-      <c r="P14" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>0</v>
-      </c>
-      <c r="R14" s="11">
-        <v>6</v>
+      <c r="K15" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="L15" s="4">
+        <v>-36.6</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="O15" s="9">
+        <v>1</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+      <c r="R15" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="2">
+        <v>11</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L16" s="4">
+        <v>-26.6</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="O16" s="9">
+        <v>1</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>0</v>
+      </c>
+      <c r="R16" s="8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A14">
+  <conditionalFormatting sqref="A2:A16">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B14">
+  <conditionalFormatting sqref="B2:B16">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C14">
+  <conditionalFormatting sqref="C2:C16">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D14">
+  <conditionalFormatting sqref="D2:D16">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E14">
+  <conditionalFormatting sqref="E2:E16">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F14">
+  <conditionalFormatting sqref="F2:F16">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G14">
+  <conditionalFormatting sqref="G2:G16">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H14">
+  <conditionalFormatting sqref="H2:H16">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I14">
+  <conditionalFormatting sqref="I2:I16">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J14">
+  <conditionalFormatting sqref="J2:J16">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K14">
+  <conditionalFormatting sqref="K2:K16">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L14">
+  <conditionalFormatting sqref="L2:L16">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1913,12 +2034,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M14">
+  <conditionalFormatting sqref="M2:M16">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N14">
+  <conditionalFormatting sqref="N2:N16">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1935,22 +2056,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O14">
+  <conditionalFormatting sqref="O2:O16">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P14">
+  <conditionalFormatting sqref="P2:P16">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q14">
+  <conditionalFormatting sqref="Q2:Q16">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R14">
+  <conditionalFormatting sqref="R2:R16">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="152">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260614--01</t>
-  </si>
-  <si>
-    <t>20260614--02</t>
-  </si>
-  <si>
     <t>20260615--01</t>
   </si>
   <si>
@@ -115,10 +109,10 @@
     <t>20260620--03</t>
   </si>
   <si>
-    <t>04:48</t>
-  </si>
-  <si>
-    <t>06:23</t>
+    <t>20260621--01</t>
+  </si>
+  <si>
+    <t>20260621--02</t>
   </si>
   <si>
     <t>02:06</t>
@@ -160,6 +154,12 @@
     <t>01:28</t>
   </si>
   <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>03:41</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
@@ -178,12 +178,6 @@
     <t>00:44</t>
   </si>
   <si>
-    <t>03:15:51</t>
-  </si>
-  <si>
-    <t>04:52:45</t>
-  </si>
-  <si>
     <t>02:31:00</t>
   </si>
   <si>
@@ -223,10 +217,10 @@
     <t>03:35:31</t>
   </si>
   <si>
-    <t>03:18:23</t>
-  </si>
-  <si>
-    <t>04:54:57</t>
+    <t>01:10:41</t>
+  </si>
+  <si>
+    <t>02:49:14</t>
   </si>
   <si>
     <t>02:34:24</t>
@@ -268,10 +262,10 @@
     <t>03:39:15</t>
   </si>
   <si>
-    <t>03:20:47</t>
-  </si>
-  <si>
-    <t>04:58:07</t>
+    <t>01:12:47</t>
+  </si>
+  <si>
+    <t>02:52:08</t>
   </si>
   <si>
     <t>02:35:27</t>
@@ -313,10 +307,10 @@
     <t>03:39:59</t>
   </si>
   <si>
-    <t>03:23:11</t>
-  </si>
-  <si>
-    <t>05:01:20</t>
+    <t>01:16:09</t>
+  </si>
+  <si>
+    <t>02:53:58</t>
   </si>
   <si>
     <t>02:36:30</t>
@@ -343,9 +337,6 @@
     <t>03:36:24</t>
   </si>
   <si>
-    <t>01:12:47</t>
-  </si>
-  <si>
     <t>02:50:56</t>
   </si>
   <si>
@@ -358,10 +349,10 @@
     <t>03:40:43</t>
   </si>
   <si>
-    <t>03:25:45</t>
-  </si>
-  <si>
-    <t>05:03:33</t>
+    <t>01:19:32</t>
+  </si>
+  <si>
+    <t>02:55:49</t>
   </si>
   <si>
     <t>02:39:55</t>
@@ -403,10 +394,10 @@
     <t>03:44:28</t>
   </si>
   <si>
-    <t>9°</t>
-  </si>
-  <si>
-    <t>22°</t>
+    <t>01:21:39</t>
+  </si>
+  <si>
+    <t>02:58:45</t>
   </si>
   <si>
     <t>0°</t>
@@ -436,12 +427,6 @@
     <t>11°</t>
   </si>
   <si>
-    <t>03:23:20</t>
-  </si>
-  <si>
-    <t>04:56:26</t>
-  </si>
-  <si>
     <t>02:39:50</t>
   </si>
   <si>
@@ -466,6 +451,9 @@
     <t>02:06:55</t>
   </si>
   <si>
+    <t>02:55:53</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
@@ -475,13 +463,13 @@
     <t>A</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -515,7 +503,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -530,13 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -560,13 +548,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -607,7 +607,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -643,6 +643,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1124,7 +1130,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>33</v>
@@ -1145,34 +1151,34 @@
         <v>99</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="L2" s="4">
-        <v>-29</v>
+        <v>-34</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="O2" s="6">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="P2" s="7">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
       </c>
       <c r="R2" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1180,13 +1186,13 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>55</v>
@@ -1201,28 +1207,28 @@
         <v>100</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="L3" s="4">
-        <v>-14</v>
+        <v>-21.6</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="O3" s="6">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="P3" s="7">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1236,13 +1242,13 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>56</v>
@@ -1257,25 +1263,25 @@
         <v>101</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="L4" s="4">
-        <v>-34</v>
+        <v>-28.2</v>
       </c>
       <c r="M4" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="N4" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="O4" s="9">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P4" s="8">
         <v>0</v>
@@ -1283,8 +1289,8 @@
       <c r="Q4" s="8">
         <v>0</v>
       </c>
-      <c r="R4" s="10">
-        <v>9</v>
+      <c r="R4" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1292,13 +1298,13 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>57</v>
@@ -1313,25 +1319,25 @@
         <v>102</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="L5" s="4">
-        <v>-21.6</v>
+        <v>-12.9</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="O5" s="11">
-        <v>67</v>
+        <v>149</v>
+      </c>
+      <c r="O5" s="9">
+        <v>0</v>
       </c>
       <c r="P5" s="8">
         <v>0</v>
@@ -1339,8 +1345,8 @@
       <c r="Q5" s="8">
         <v>0</v>
       </c>
-      <c r="R5" s="12">
-        <v>58</v>
+      <c r="R5" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1348,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>58</v>
@@ -1369,22 +1375,22 @@
         <v>103</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L6" s="4">
-        <v>-28.2</v>
+        <v>-33.4</v>
       </c>
       <c r="M6" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="O6" s="9">
         <v>0</v>
@@ -1404,13 +1410,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>59</v>
@@ -1425,25 +1431,25 @@
         <v>104</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="L7" s="4">
-        <v>-12.9</v>
+        <v>-20.6</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="O7" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P7" s="8">
         <v>0</v>
@@ -1452,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="R7" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1460,7 +1466,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>39</v>
@@ -1481,22 +1487,22 @@
         <v>105</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="K8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-37</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="L8" s="4">
-        <v>-33.4</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="N8" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O8" s="9">
         <v>0</v>
@@ -1516,13 +1522,13 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>61</v>
@@ -1537,25 +1543,25 @@
         <v>106</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="K9" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-27.4</v>
+      </c>
+      <c r="M9" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="L9" s="4">
-        <v>-20.6</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="N9" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="O9" s="9">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P9" s="8">
         <v>0</v>
@@ -1563,8 +1569,8 @@
       <c r="Q9" s="8">
         <v>0</v>
       </c>
-      <c r="R9" s="8">
-        <v>0</v>
+      <c r="R9" s="10">
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1572,7 +1578,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>41</v>
@@ -1590,28 +1596,28 @@
         <v>92</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>62</v>
       </c>
       <c r="L10" s="4">
-        <v>-37</v>
+        <v>-38.3</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="O10" s="9">
-        <v>0</v>
+        <v>151</v>
+      </c>
+      <c r="O10" s="11">
+        <v>37</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
@@ -1619,8 +1625,8 @@
       <c r="Q10" s="8">
         <v>0</v>
       </c>
-      <c r="R10" s="8">
-        <v>0</v>
+      <c r="R10" s="10">
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1628,13 +1634,13 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>63</v>
@@ -1646,28 +1652,28 @@
         <v>93</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>148</v>
+        <v>107</v>
       </c>
       <c r="L11" s="4">
-        <v>-27.4</v>
+        <v>-32.8</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="O11" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P11" s="8">
         <v>0</v>
@@ -1676,7 +1682,7 @@
         <v>0</v>
       </c>
       <c r="R11" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1684,7 +1690,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>43</v>
@@ -1702,28 +1708,28 @@
         <v>94</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>64</v>
       </c>
       <c r="L12" s="4">
-        <v>-38.3</v>
+        <v>-37.2</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="O12" s="9">
-        <v>0</v>
+        <v>149</v>
+      </c>
+      <c r="O12" s="11">
+        <v>39</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
@@ -1731,8 +1737,8 @@
       <c r="Q12" s="8">
         <v>0</v>
       </c>
-      <c r="R12" s="8">
-        <v>0</v>
+      <c r="R12" s="12">
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1740,7 +1746,7 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>44</v>
@@ -1758,28 +1764,28 @@
         <v>95</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="L13" s="4">
-        <v>-32.8</v>
+        <v>-36.6</v>
       </c>
       <c r="M13" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="N13" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="N13" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="O13" s="9">
-        <v>0</v>
+      <c r="O13" s="11">
+        <v>25</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
@@ -1787,8 +1793,8 @@
       <c r="Q13" s="8">
         <v>0</v>
       </c>
-      <c r="R13" s="8">
-        <v>0</v>
+      <c r="R13" s="13">
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1802,7 +1808,7 @@
         <v>45</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>66</v>
@@ -1814,28 +1820,28 @@
         <v>96</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="L14" s="4">
-        <v>-37.2</v>
+        <v>-26.6</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="O14" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="P14" s="8">
         <v>0</v>
@@ -1843,8 +1849,8 @@
       <c r="Q14" s="8">
         <v>0</v>
       </c>
-      <c r="R14" s="8">
-        <v>1</v>
+      <c r="R14" s="14">
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1852,7 +1858,7 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>46</v>
@@ -1870,28 +1876,28 @@
         <v>97</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>149</v>
+        <v>67</v>
       </c>
       <c r="L15" s="4">
-        <v>-36.6</v>
+        <v>-38.2</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O15" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P15" s="8">
         <v>0</v>
@@ -1900,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="R15" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1908,13 +1914,13 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>68</v>
@@ -1926,28 +1932,28 @@
         <v>98</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="L16" s="4">
-        <v>-26.6</v>
+        <v>-32.3</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="O16" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P16" s="8">
         <v>0</v>
@@ -1956,7 +1962,7 @@
         <v>0</v>
       </c>
       <c r="R16" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="157">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260615--01</t>
-  </si>
-  <si>
-    <t>20260615--02</t>
-  </si>
-  <si>
     <t>20260616--01</t>
   </si>
   <si>
@@ -115,10 +109,13 @@
     <t>20260621--02</t>
   </si>
   <si>
-    <t>02:06</t>
-  </si>
-  <si>
-    <t>06:42</t>
+    <t>20260622--01</t>
+  </si>
+  <si>
+    <t>20260622--02</t>
+  </si>
+  <si>
+    <t>20260622--03</t>
   </si>
   <si>
     <t>06:47</t>
@@ -160,15 +157,21 @@
     <t>03:41</t>
   </si>
   <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>04:56</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>01:13</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:04</t>
-  </si>
-  <si>
-    <t>01:13</t>
-  </si>
-  <si>
     <t>03:02</t>
   </si>
   <si>
@@ -178,12 +181,6 @@
     <t>00:44</t>
   </si>
   <si>
-    <t>02:31:00</t>
-  </si>
-  <si>
-    <t>04:07:10</t>
-  </si>
-  <si>
     <t>03:21:39</t>
   </si>
   <si>
@@ -223,10 +220,13 @@
     <t>02:49:14</t>
   </si>
   <si>
-    <t>02:34:24</t>
-  </si>
-  <si>
-    <t>04:09:18</t>
+    <t>00:24:56</t>
+  </si>
+  <si>
+    <t>02:02:56</t>
+  </si>
+  <si>
+    <t>23:39:15</t>
   </si>
   <si>
     <t>03:23:45</t>
@@ -268,10 +268,13 @@
     <t>02:52:08</t>
   </si>
   <si>
-    <t>02:35:27</t>
-  </si>
-  <si>
-    <t>04:12:38</t>
+    <t>00:27:04</t>
+  </si>
+  <si>
+    <t>02:05:29</t>
+  </si>
+  <si>
+    <t>23:41:32</t>
   </si>
   <si>
     <t>03:27:08</t>
@@ -313,10 +316,13 @@
     <t>02:53:58</t>
   </si>
   <si>
-    <t>02:36:30</t>
-  </si>
-  <si>
-    <t>04:16:00</t>
+    <t>00:30:18</t>
+  </si>
+  <si>
+    <t>02:07:57</t>
+  </si>
+  <si>
+    <t>23:44:27</t>
   </si>
   <si>
     <t>03:30:32</t>
@@ -355,10 +361,13 @@
     <t>02:55:49</t>
   </si>
   <si>
-    <t>02:39:55</t>
-  </si>
-  <si>
-    <t>04:18:09</t>
+    <t>00:33:34</t>
+  </si>
+  <si>
+    <t>02:10:25</t>
+  </si>
+  <si>
+    <t>23:47:22</t>
   </si>
   <si>
     <t>03:32:39</t>
@@ -400,24 +409,30 @@
     <t>02:58:45</t>
   </si>
   <si>
+    <t>00:35:43</t>
+  </si>
+  <si>
+    <t>02:12:59</t>
+  </si>
+  <si>
+    <t>23:49:40</t>
+  </si>
+  <si>
+    <t>20°</t>
+  </si>
+  <si>
+    <t>7°</t>
+  </si>
+  <si>
+    <t>6°</t>
+  </si>
+  <si>
+    <t>18°</t>
+  </si>
+  <si>
     <t>0°</t>
   </si>
   <si>
-    <t>56°</t>
-  </si>
-  <si>
-    <t>20°</t>
-  </si>
-  <si>
-    <t>7°</t>
-  </si>
-  <si>
-    <t>6°</t>
-  </si>
-  <si>
-    <t>18°</t>
-  </si>
-  <si>
     <t>10°</t>
   </si>
   <si>
@@ -427,10 +442,7 @@
     <t>11°</t>
   </si>
   <si>
-    <t>02:39:50</t>
-  </si>
-  <si>
-    <t>04:12:56</t>
+    <t>5°</t>
   </si>
   <si>
     <t>03:29:19</t>
@@ -454,19 +466,22 @@
     <t>02:55:53</t>
   </si>
   <si>
+    <t>02:11:43</t>
+  </si>
+  <si>
+    <t>A+B</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
-    <t>A+B</t>
-  </si>
-  <si>
-    <t>A</t>
+    <t>2</t>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>3</t>
@@ -524,7 +539,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,25 +557,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1052,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1130,49 +1145,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="L2" s="4">
-        <v>-34</v>
+        <v>-28.2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="O2" s="6">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P2" s="7">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1186,49 +1201,49 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="L3" s="4">
-        <v>-21.6</v>
+        <v>-12.9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="O3" s="6">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="P3" s="7">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1242,46 +1257,46 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="L4" s="4">
-        <v>-28.2</v>
+        <v>-33.4</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="O4" s="9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P4" s="8">
         <v>0</v>
@@ -1290,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="R4" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1298,55 +1313,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-20.6</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="O5" s="10">
         <v>36</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-12.9</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="O5" s="9">
-        <v>0</v>
-      </c>
       <c r="P5" s="8">
         <v>0</v>
       </c>
       <c r="Q5" s="8">
         <v>0</v>
       </c>
-      <c r="R5" s="8">
-        <v>0</v>
+      <c r="R5" s="11">
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1354,43 +1369,43 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>141</v>
+        <v>59</v>
       </c>
       <c r="L6" s="4">
-        <v>-33.4</v>
+        <v>-37</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="O6" s="9">
         <v>0</v>
@@ -1410,46 +1425,46 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="L7" s="4">
-        <v>-20.6</v>
+        <v>-27.4</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="O7" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P7" s="8">
         <v>0</v>
@@ -1458,7 +1473,7 @@
         <v>0</v>
       </c>
       <c r="R7" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1466,46 +1481,46 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L8" s="4">
-        <v>-37</v>
+        <v>-38.3</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O8" s="9">
-        <v>0</v>
+        <v>156</v>
+      </c>
+      <c r="O8" s="6">
+        <v>63</v>
       </c>
       <c r="P8" s="8">
         <v>0</v>
@@ -1513,8 +1528,8 @@
       <c r="Q8" s="8">
         <v>0</v>
       </c>
-      <c r="R8" s="8">
-        <v>0</v>
+      <c r="R8" s="12">
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1522,46 +1537,46 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="L9" s="4">
-        <v>-27.4</v>
+        <v>-32.8</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="O9" s="9">
-        <v>8</v>
+        <v>154</v>
+      </c>
+      <c r="O9" s="10">
+        <v>46</v>
       </c>
       <c r="P9" s="8">
         <v>0</v>
@@ -1569,8 +1584,8 @@
       <c r="Q9" s="8">
         <v>0</v>
       </c>
-      <c r="R9" s="10">
-        <v>8</v>
+      <c r="R9" s="13">
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1578,46 +1593,46 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L10" s="4">
-        <v>-38.3</v>
+        <v>-37.2</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O10" s="11">
-        <v>37</v>
+        <v>155</v>
+      </c>
+      <c r="O10" s="9">
+        <v>2</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
@@ -1625,8 +1640,8 @@
       <c r="Q10" s="8">
         <v>0</v>
       </c>
-      <c r="R10" s="10">
-        <v>8</v>
+      <c r="R10" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1634,46 +1649,46 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="L11" s="4">
-        <v>-32.8</v>
+        <v>-36.6</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="O11" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P11" s="8">
         <v>0</v>
@@ -1693,43 +1708,43 @@
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="L12" s="4">
-        <v>-37.2</v>
+        <v>-26.6</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="O12" s="11">
-        <v>39</v>
+        <v>155</v>
+      </c>
+      <c r="O12" s="9">
+        <v>15</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
@@ -1737,8 +1752,8 @@
       <c r="Q12" s="8">
         <v>0</v>
       </c>
-      <c r="R12" s="12">
-        <v>39</v>
+      <c r="R12" s="14">
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1746,46 +1761,46 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>144</v>
+        <v>66</v>
       </c>
       <c r="L13" s="4">
-        <v>-36.6</v>
+        <v>-38.2</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O13" s="11">
-        <v>25</v>
+        <v>156</v>
+      </c>
+      <c r="O13" s="9">
+        <v>4</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
@@ -1793,8 +1808,8 @@
       <c r="Q13" s="8">
         <v>0</v>
       </c>
-      <c r="R13" s="13">
-        <v>15</v>
+      <c r="R13" s="14">
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1802,46 +1817,46 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>96</v>
+        <v>149</v>
       </c>
       <c r="L14" s="4">
-        <v>-26.6</v>
+        <v>-32.3</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="O14" s="9">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="P14" s="8">
         <v>0</v>
@@ -1850,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="R14" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1858,46 +1873,46 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L15" s="4">
-        <v>-38.2</v>
+        <v>-37.5</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="O15" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P15" s="8">
         <v>0</v>
@@ -1906,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="R15" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1914,46 +1929,46 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="L16" s="4">
-        <v>-32.3</v>
+        <v>-36.2</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="O16" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P16" s="8">
         <v>0</v>
@@ -1962,66 +1977,122 @@
         <v>0</v>
       </c>
       <c r="R16" s="8">
-        <v>2</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2">
+        <v>27</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-34.5</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="O17" s="9">
+        <v>8</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0</v>
+      </c>
+      <c r="R17" s="14">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A16">
+  <conditionalFormatting sqref="A2:A17">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B16">
+  <conditionalFormatting sqref="B2:B17">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C16">
+  <conditionalFormatting sqref="C2:C17">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D16">
+  <conditionalFormatting sqref="D2:D17">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E16">
+  <conditionalFormatting sqref="E2:E17">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F16">
+  <conditionalFormatting sqref="F2:F17">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G16">
+  <conditionalFormatting sqref="G2:G17">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H16">
+  <conditionalFormatting sqref="H2:H17">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I16">
+  <conditionalFormatting sqref="I2:I17">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J16">
+  <conditionalFormatting sqref="J2:J17">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K16">
+  <conditionalFormatting sqref="K2:K17">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L16">
+  <conditionalFormatting sqref="L2:L17">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2040,12 +2111,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M16">
+  <conditionalFormatting sqref="M2:M17">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N16">
+  <conditionalFormatting sqref="N2:N17">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2062,22 +2133,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O16">
+  <conditionalFormatting sqref="O2:O17">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P16">
+  <conditionalFormatting sqref="P2:P17">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q16">
+  <conditionalFormatting sqref="Q2:Q17">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R16">
+  <conditionalFormatting sqref="R2:R17">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="154">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260616--01</t>
-  </si>
-  <si>
-    <t>20260616--02</t>
-  </si>
-  <si>
     <t>20260617--01</t>
   </si>
   <si>
@@ -118,10 +112,10 @@
     <t>20260622--03</t>
   </si>
   <si>
-    <t>06:47</t>
-  </si>
-  <si>
-    <t>03:39</t>
+    <t>20260623--01</t>
+  </si>
+  <si>
+    <t>20260623--02</t>
   </si>
   <si>
     <t>06:33</t>
@@ -130,10 +124,10 @@
     <t>04:54</t>
   </si>
   <si>
-    <t>05:56</t>
-  </si>
-  <si>
-    <t>05:45</t>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>05:46</t>
   </si>
   <si>
     <t>04:42</t>
@@ -142,297 +136,300 @@
     <t>06:21</t>
   </si>
   <si>
-    <t>01:46</t>
+    <t>01:48</t>
   </si>
   <si>
     <t>06:41</t>
   </si>
   <si>
-    <t>01:28</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>03:41</t>
+    <t>01:27</t>
+  </si>
+  <si>
+    <t>06:44</t>
+  </si>
+  <si>
+    <t>03:40</t>
   </si>
   <si>
     <t>06:30</t>
   </si>
   <si>
-    <t>04:56</t>
+    <t>04:55</t>
   </si>
   <si>
     <t>05:50</t>
   </si>
   <si>
-    <t>01:13</t>
+    <t>04:32</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:02</t>
-  </si>
-  <si>
-    <t>01:33</t>
+    <t>03:03</t>
+  </si>
+  <si>
+    <t>01:34</t>
+  </si>
+  <si>
+    <t>00:01</t>
   </si>
   <si>
     <t>00:44</t>
   </si>
   <si>
-    <t>03:21:39</t>
-  </si>
-  <si>
-    <t>05:00:14</t>
-  </si>
-  <si>
-    <t>02:36:11</t>
-  </si>
-  <si>
-    <t>04:14:16</t>
-  </si>
-  <si>
-    <t>01:50:48</t>
-  </si>
-  <si>
-    <t>03:28:18</t>
-  </si>
-  <si>
-    <t>01:05:32</t>
-  </si>
-  <si>
-    <t>02:42:23</t>
-  </si>
-  <si>
-    <t>00:20:24</t>
-  </si>
-  <si>
-    <t>01:56:31</t>
-  </si>
-  <si>
-    <t>03:35:31</t>
-  </si>
-  <si>
-    <t>01:10:41</t>
-  </si>
-  <si>
-    <t>02:49:14</t>
-  </si>
-  <si>
-    <t>00:24:56</t>
-  </si>
-  <si>
-    <t>02:02:56</t>
-  </si>
-  <si>
-    <t>23:39:15</t>
-  </si>
-  <si>
-    <t>03:23:45</t>
-  </si>
-  <si>
-    <t>05:03:10</t>
-  </si>
-  <si>
-    <t>02:38:20</t>
-  </si>
-  <si>
-    <t>04:16:49</t>
-  </si>
-  <si>
-    <t>01:53:04</t>
-  </si>
-  <si>
-    <t>03:30:39</t>
-  </si>
-  <si>
-    <t>01:08:05</t>
-  </si>
-  <si>
-    <t>02:44:35</t>
-  </si>
-  <si>
-    <t>00:23:55</t>
-  </si>
-  <si>
-    <t>01:58:38</t>
-  </si>
-  <si>
-    <t>03:39:15</t>
-  </si>
-  <si>
-    <t>01:12:47</t>
-  </si>
-  <si>
-    <t>02:52:08</t>
-  </si>
-  <si>
-    <t>00:27:04</t>
-  </si>
-  <si>
-    <t>02:05:29</t>
-  </si>
-  <si>
-    <t>23:41:32</t>
-  </si>
-  <si>
-    <t>03:27:08</t>
-  </si>
-  <si>
-    <t>05:04:59</t>
-  </si>
-  <si>
-    <t>02:41:35</t>
-  </si>
-  <si>
-    <t>04:19:16</t>
-  </si>
-  <si>
-    <t>01:56:02</t>
-  </si>
-  <si>
-    <t>03:33:31</t>
-  </si>
-  <si>
-    <t>01:10:26</t>
-  </si>
-  <si>
-    <t>02:47:45</t>
-  </si>
-  <si>
-    <t>00:24:48</t>
-  </si>
-  <si>
-    <t>02:01:57</t>
-  </si>
-  <si>
-    <t>03:39:59</t>
-  </si>
-  <si>
-    <t>01:16:09</t>
-  </si>
-  <si>
-    <t>02:53:58</t>
-  </si>
-  <si>
-    <t>00:30:18</t>
-  </si>
-  <si>
-    <t>02:07:57</t>
-  </si>
-  <si>
-    <t>23:44:27</t>
-  </si>
-  <si>
-    <t>03:30:32</t>
-  </si>
-  <si>
-    <t>05:06:49</t>
-  </si>
-  <si>
-    <t>02:44:53</t>
-  </si>
-  <si>
-    <t>04:21:43</t>
-  </si>
-  <si>
-    <t>01:59:00</t>
-  </si>
-  <si>
-    <t>03:36:24</t>
-  </si>
-  <si>
-    <t>02:50:56</t>
-  </si>
-  <si>
-    <t>00:25:41</t>
-  </si>
-  <si>
-    <t>02:05:19</t>
-  </si>
-  <si>
-    <t>03:40:43</t>
-  </si>
-  <si>
-    <t>01:19:32</t>
-  </si>
-  <si>
-    <t>02:55:49</t>
-  </si>
-  <si>
-    <t>00:33:34</t>
-  </si>
-  <si>
-    <t>02:10:25</t>
-  </si>
-  <si>
-    <t>23:47:22</t>
-  </si>
-  <si>
-    <t>03:32:39</t>
-  </si>
-  <si>
-    <t>05:09:47</t>
-  </si>
-  <si>
-    <t>02:47:02</t>
-  </si>
-  <si>
-    <t>04:24:18</t>
-  </si>
-  <si>
-    <t>02:01:17</t>
-  </si>
-  <si>
-    <t>03:38:46</t>
-  </si>
-  <si>
-    <t>01:15:22</t>
-  </si>
-  <si>
-    <t>02:53:09</t>
-  </si>
-  <si>
-    <t>00:29:13</t>
-  </si>
-  <si>
-    <t>02:07:27</t>
-  </si>
-  <si>
-    <t>03:44:28</t>
-  </si>
-  <si>
-    <t>01:21:39</t>
-  </si>
-  <si>
-    <t>02:58:45</t>
-  </si>
-  <si>
-    <t>00:35:43</t>
-  </si>
-  <si>
-    <t>02:12:59</t>
-  </si>
-  <si>
-    <t>23:49:40</t>
+    <t>02:36:13</t>
+  </si>
+  <si>
+    <t>04:14:17</t>
+  </si>
+  <si>
+    <t>01:50:52</t>
+  </si>
+  <si>
+    <t>03:28:22</t>
+  </si>
+  <si>
+    <t>01:05:37</t>
+  </si>
+  <si>
+    <t>02:42:29</t>
+  </si>
+  <si>
+    <t>00:20:32</t>
+  </si>
+  <si>
+    <t>01:56:40</t>
+  </si>
+  <si>
+    <t>03:35:41</t>
+  </si>
+  <si>
+    <t>01:10:55</t>
+  </si>
+  <si>
+    <t>02:49:27</t>
+  </si>
+  <si>
+    <t>00:25:14</t>
+  </si>
+  <si>
+    <t>02:03:15</t>
+  </si>
+  <si>
+    <t>23:39:39</t>
+  </si>
+  <si>
+    <t>01:17:05</t>
+  </si>
+  <si>
+    <t>22:54:10</t>
+  </si>
+  <si>
+    <t>02:38:21</t>
+  </si>
+  <si>
+    <t>04:16:51</t>
+  </si>
+  <si>
+    <t>01:53:08</t>
+  </si>
+  <si>
+    <t>03:30:42</t>
+  </si>
+  <si>
+    <t>01:08:11</t>
+  </si>
+  <si>
+    <t>02:44:41</t>
+  </si>
+  <si>
+    <t>00:24:03</t>
+  </si>
+  <si>
+    <t>01:58:47</t>
+  </si>
+  <si>
+    <t>03:39:25</t>
+  </si>
+  <si>
+    <t>01:13:01</t>
+  </si>
+  <si>
+    <t>02:52:22</t>
+  </si>
+  <si>
+    <t>00:27:22</t>
+  </si>
+  <si>
+    <t>02:05:48</t>
+  </si>
+  <si>
+    <t>23:41:55</t>
+  </si>
+  <si>
+    <t>01:19:25</t>
+  </si>
+  <si>
+    <t>22:56:46</t>
+  </si>
+  <si>
+    <t>02:41:37</t>
+  </si>
+  <si>
+    <t>04:19:17</t>
+  </si>
+  <si>
+    <t>01:56:05</t>
+  </si>
+  <si>
+    <t>03:33:34</t>
+  </si>
+  <si>
+    <t>01:10:31</t>
+  </si>
+  <si>
+    <t>02:47:51</t>
+  </si>
+  <si>
+    <t>00:24:57</t>
+  </si>
+  <si>
+    <t>02:02:07</t>
+  </si>
+  <si>
+    <t>03:40:08</t>
+  </si>
+  <si>
+    <t>01:16:22</t>
+  </si>
+  <si>
+    <t>02:54:12</t>
+  </si>
+  <si>
+    <t>00:30:37</t>
+  </si>
+  <si>
+    <t>02:08:15</t>
+  </si>
+  <si>
+    <t>23:44:50</t>
+  </si>
+  <si>
+    <t>01:22:18</t>
+  </si>
+  <si>
+    <t>22:59:02</t>
+  </si>
+  <si>
+    <t>02:44:54</t>
+  </si>
+  <si>
+    <t>04:21:45</t>
+  </si>
+  <si>
+    <t>01:59:03</t>
+  </si>
+  <si>
+    <t>03:36:28</t>
+  </si>
+  <si>
+    <t>01:12:53</t>
+  </si>
+  <si>
+    <t>02:51:02</t>
+  </si>
+  <si>
+    <t>00:25:51</t>
+  </si>
+  <si>
+    <t>02:05:28</t>
+  </si>
+  <si>
+    <t>03:40:52</t>
+  </si>
+  <si>
+    <t>01:19:45</t>
+  </si>
+  <si>
+    <t>02:56:02</t>
+  </si>
+  <si>
+    <t>00:33:52</t>
+  </si>
+  <si>
+    <t>02:10:43</t>
+  </si>
+  <si>
+    <t>23:47:45</t>
+  </si>
+  <si>
+    <t>01:25:11</t>
+  </si>
+  <si>
+    <t>23:01:18</t>
+  </si>
+  <si>
+    <t>02:47:04</t>
+  </si>
+  <si>
+    <t>04:24:20</t>
+  </si>
+  <si>
+    <t>02:01:20</t>
+  </si>
+  <si>
+    <t>03:38:50</t>
+  </si>
+  <si>
+    <t>01:15:28</t>
+  </si>
+  <si>
+    <t>02:53:15</t>
+  </si>
+  <si>
+    <t>00:29:23</t>
+  </si>
+  <si>
+    <t>02:07:37</t>
+  </si>
+  <si>
+    <t>03:44:38</t>
+  </si>
+  <si>
+    <t>01:21:52</t>
+  </si>
+  <si>
+    <t>02:58:59</t>
+  </si>
+  <si>
+    <t>00:36:02</t>
+  </si>
+  <si>
+    <t>02:13:17</t>
+  </si>
+  <si>
+    <t>23:50:03</t>
+  </si>
+  <si>
+    <t>01:27:32</t>
+  </si>
+  <si>
+    <t>23:03:55</t>
+  </si>
+  <si>
+    <t>6°</t>
+  </si>
+  <si>
+    <t>18°</t>
+  </si>
+  <si>
+    <t>0°</t>
   </si>
   <si>
     <t>20°</t>
   </si>
   <si>
-    <t>7°</t>
-  </si>
-  <si>
-    <t>6°</t>
-  </si>
-  <si>
-    <t>18°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
     <t>10°</t>
   </si>
   <si>
@@ -445,46 +442,40 @@
     <t>5°</t>
   </si>
   <si>
-    <t>03:29:19</t>
-  </si>
-  <si>
-    <t>05:02:25</t>
-  </si>
-  <si>
-    <t>02:45:36</t>
-  </si>
-  <si>
-    <t>04:18:41</t>
-  </si>
-  <si>
-    <t>03:34:51</t>
-  </si>
-  <si>
-    <t>02:06:55</t>
-  </si>
-  <si>
-    <t>02:55:53</t>
-  </si>
-  <si>
-    <t>02:11:43</t>
+    <t>02:45:37</t>
+  </si>
+  <si>
+    <t>04:18:42</t>
+  </si>
+  <si>
+    <t>03:34:54</t>
+  </si>
+  <si>
+    <t>02:51:01</t>
+  </si>
+  <si>
+    <t>02:07:04</t>
+  </si>
+  <si>
+    <t>02:56:06</t>
+  </si>
+  <si>
+    <t>02:12:00</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
+    <t>3</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -518,7 +509,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -533,13 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -551,37 +542,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -622,7 +607,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -661,9 +646,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1145,25 +1127,25 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>118</v>
@@ -1172,22 +1154,22 @@
         <v>134</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L2" s="4">
-        <v>-28.2</v>
+        <v>-33.4</v>
       </c>
       <c r="M2" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="O2" s="6">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="P2" s="7">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1201,25 +1183,25 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>119</v>
@@ -1228,22 +1210,22 @@
         <v>135</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L3" s="4">
-        <v>-12.9</v>
+        <v>-20.6</v>
       </c>
       <c r="M3" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="O3" s="6">
-        <v>79</v>
-      </c>
-      <c r="P3" s="7">
-        <v>81</v>
+      <c r="O3" s="9">
+        <v>75</v>
+      </c>
+      <c r="P3" s="10">
+        <v>75</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1257,25 +1239,25 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>120</v>
@@ -1284,19 +1266,19 @@
         <v>136</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>145</v>
+        <v>56</v>
       </c>
       <c r="L4" s="4">
-        <v>-33.4</v>
+        <v>-37</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="O4" s="9">
-        <v>3</v>
+        <v>151</v>
+      </c>
+      <c r="O4" s="11">
+        <v>1</v>
       </c>
       <c r="P4" s="8">
         <v>0</v>
@@ -1305,7 +1287,7 @@
         <v>0</v>
       </c>
       <c r="R4" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1313,25 +1295,25 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>121</v>
@@ -1340,19 +1322,19 @@
         <v>137</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L5" s="4">
-        <v>-20.6</v>
+        <v>-27.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="O5" s="10">
-        <v>36</v>
+        <v>152</v>
+      </c>
+      <c r="O5" s="11">
+        <v>0</v>
       </c>
       <c r="P5" s="8">
         <v>0</v>
@@ -1360,8 +1342,8 @@
       <c r="Q5" s="8">
         <v>0</v>
       </c>
-      <c r="R5" s="11">
-        <v>34</v>
+      <c r="R5" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1369,46 +1351,46 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>122</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L6" s="4">
-        <v>-37</v>
+        <v>-38.3</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="O6" s="9">
-        <v>0</v>
+        <v>151</v>
+      </c>
+      <c r="O6" s="11">
+        <v>4</v>
       </c>
       <c r="P6" s="8">
         <v>0</v>
@@ -1416,8 +1398,8 @@
       <c r="Q6" s="8">
         <v>0</v>
       </c>
-      <c r="R6" s="8">
-        <v>0</v>
+      <c r="R6" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1425,46 +1407,46 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>39</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>123</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="L7" s="4">
-        <v>-27.4</v>
+        <v>-32.8</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="O7" s="9">
-        <v>0</v>
+        <v>152</v>
+      </c>
+      <c r="O7" s="6">
+        <v>29</v>
       </c>
       <c r="P7" s="8">
         <v>0</v>
@@ -1472,8 +1454,8 @@
       <c r="Q7" s="8">
         <v>0</v>
       </c>
-      <c r="R7" s="8">
-        <v>0</v>
+      <c r="R7" s="7">
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1481,46 +1463,46 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>124</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L8" s="4">
-        <v>-38.3</v>
+        <v>-37.3</v>
       </c>
       <c r="M8" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="N8" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="O8" s="6">
-        <v>63</v>
+      <c r="O8" s="11">
+        <v>0</v>
       </c>
       <c r="P8" s="8">
         <v>0</v>
@@ -1528,8 +1510,8 @@
       <c r="Q8" s="8">
         <v>0</v>
       </c>
-      <c r="R8" s="12">
-        <v>57</v>
+      <c r="R8" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1537,22 +1519,22 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>109</v>
@@ -1564,19 +1546,19 @@
         <v>139</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="L9" s="4">
-        <v>-32.8</v>
+        <v>-36.6</v>
       </c>
       <c r="M9" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="N9" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="O9" s="10">
-        <v>46</v>
+      <c r="O9" s="11">
+        <v>5</v>
       </c>
       <c r="P9" s="8">
         <v>0</v>
@@ -1584,8 +1566,8 @@
       <c r="Q9" s="8">
         <v>0</v>
       </c>
-      <c r="R9" s="13">
-        <v>42</v>
+      <c r="R9" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1599,16 +1581,16 @@
         <v>42</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>110</v>
@@ -1617,22 +1599,22 @@
         <v>126</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="L10" s="4">
-        <v>-37.2</v>
+        <v>-26.5</v>
       </c>
       <c r="M10" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="N10" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="N10" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="O10" s="9">
-        <v>2</v>
+      <c r="O10" s="11">
+        <v>6</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
@@ -1649,22 +1631,22 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>111</v>
@@ -1673,22 +1655,22 @@
         <v>127</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>148</v>
+        <v>63</v>
       </c>
       <c r="L11" s="4">
-        <v>-36.6</v>
+        <v>-38.2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="O11" s="9">
-        <v>4</v>
+        <v>151</v>
+      </c>
+      <c r="O11" s="11">
+        <v>0</v>
       </c>
       <c r="P11" s="8">
         <v>0</v>
@@ -1697,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="R11" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1705,22 +1687,22 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>112</v>
@@ -1729,22 +1711,22 @@
         <v>128</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="L12" s="4">
-        <v>-26.6</v>
+        <v>-32.2</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="O12" s="9">
-        <v>15</v>
+        <v>153</v>
+      </c>
+      <c r="O12" s="11">
+        <v>0</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
@@ -1752,8 +1734,8 @@
       <c r="Q12" s="8">
         <v>0</v>
       </c>
-      <c r="R12" s="14">
-        <v>5</v>
+      <c r="R12" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1761,22 +1743,22 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>113</v>
@@ -1785,22 +1767,22 @@
         <v>129</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L13" s="4">
-        <v>-38.2</v>
+        <v>-37.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="O13" s="9">
-        <v>4</v>
+        <v>151</v>
+      </c>
+      <c r="O13" s="11">
+        <v>0</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
@@ -1808,8 +1790,8 @@
       <c r="Q13" s="8">
         <v>0</v>
       </c>
-      <c r="R13" s="14">
-        <v>4</v>
+      <c r="R13" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1817,22 +1799,22 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>114</v>
@@ -1841,22 +1823,22 @@
         <v>130</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K14" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="L14" s="4">
+        <v>-36.2</v>
+      </c>
+      <c r="M14" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="L14" s="4">
-        <v>-32.3</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="N14" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="O14" s="9">
-        <v>5</v>
+        <v>151</v>
+      </c>
+      <c r="O14" s="11">
+        <v>0</v>
       </c>
       <c r="P14" s="8">
         <v>0</v>
@@ -1864,8 +1846,8 @@
       <c r="Q14" s="8">
         <v>0</v>
       </c>
-      <c r="R14" s="14">
-        <v>4</v>
+      <c r="R14" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1873,22 +1855,22 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>115</v>
@@ -1897,31 +1879,31 @@
         <v>131</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L15" s="4">
-        <v>-37.5</v>
+        <v>-34.5</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="O15" s="9">
-        <v>0</v>
-      </c>
-      <c r="P15" s="8">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="P15" s="13">
+        <v>14</v>
       </c>
       <c r="Q15" s="8">
         <v>0</v>
       </c>
-      <c r="R15" s="8">
-        <v>0</v>
+      <c r="R15" s="10">
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1929,22 +1911,22 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>116</v>
@@ -1953,54 +1935,42 @@
         <v>132</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>150</v>
+        <v>68</v>
       </c>
       <c r="L16" s="4">
-        <v>-36.2</v>
+        <v>-38.2</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="O16" s="9">
-        <v>0</v>
-      </c>
-      <c r="P16" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>0</v>
-      </c>
-      <c r="R16" s="8">
-        <v>0</v>
+        <v>151</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:14">
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="E17" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>117</v>
@@ -2009,31 +1979,19 @@
         <v>133</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L17" s="4">
-        <v>-34.5</v>
+        <v>-29.6</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="O17" s="9">
-        <v>8</v>
-      </c>
-      <c r="P17" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>0</v>
-      </c>
-      <c r="R17" s="14">
-        <v>5</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="154">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260617--01</t>
-  </si>
-  <si>
-    <t>20260617--02</t>
-  </si>
-  <si>
-    <t>20260618--01</t>
-  </si>
-  <si>
-    <t>20260618--02</t>
-  </si>
-  <si>
     <t>20260619--01</t>
   </si>
   <si>
@@ -118,16 +106,19 @@
     <t>20260623--02</t>
   </si>
   <si>
-    <t>06:33</t>
-  </si>
-  <si>
-    <t>04:54</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>05:46</t>
+    <t>20260624--01</t>
+  </si>
+  <si>
+    <t>20260624--02</t>
+  </si>
+  <si>
+    <t>20260624--03</t>
+  </si>
+  <si>
+    <t>20260625--01</t>
+  </si>
+  <si>
+    <t>20260625--02</t>
   </si>
   <si>
     <t>04:42</t>
@@ -151,7 +142,7 @@
     <t>03:40</t>
   </si>
   <si>
-    <t>06:30</t>
+    <t>06:29</t>
   </si>
   <si>
     <t>04:55</t>
@@ -160,43 +151,40 @@
     <t>05:50</t>
   </si>
   <si>
+    <t>05:47</t>
+  </si>
+  <si>
     <t>04:32</t>
   </si>
   <si>
+    <t>06:22</t>
+  </si>
+  <si>
+    <t>00:28</t>
+  </si>
+  <si>
+    <t>01:41</t>
+  </si>
+  <si>
+    <t>06:43</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:03</t>
-  </si>
-  <si>
-    <t>01:34</t>
-  </si>
-  <si>
     <t>00:01</t>
   </si>
   <si>
     <t>00:44</t>
   </si>
   <si>
-    <t>02:36:13</t>
-  </si>
-  <si>
-    <t>04:14:17</t>
-  </si>
-  <si>
-    <t>01:50:52</t>
-  </si>
-  <si>
-    <t>03:28:22</t>
-  </si>
-  <si>
-    <t>01:05:37</t>
+    <t>01:05:38</t>
   </si>
   <si>
     <t>02:42:29</t>
   </si>
   <si>
-    <t>00:20:32</t>
+    <t>00:20:33</t>
   </si>
   <si>
     <t>01:56:40</t>
@@ -208,7 +196,7 @@
     <t>01:10:55</t>
   </si>
   <si>
-    <t>02:49:27</t>
+    <t>02:49:28</t>
   </si>
   <si>
     <t>00:25:14</t>
@@ -223,19 +211,22 @@
     <t>01:17:05</t>
   </si>
   <si>
-    <t>22:54:10</t>
-  </si>
-  <si>
-    <t>02:38:21</t>
-  </si>
-  <si>
-    <t>04:16:51</t>
-  </si>
-  <si>
-    <t>01:53:08</t>
-  </si>
-  <si>
-    <t>03:30:42</t>
+    <t>22:54:11</t>
+  </si>
+  <si>
+    <t>00:30:58</t>
+  </si>
+  <si>
+    <t>22:08:53</t>
+  </si>
+  <si>
+    <t>23:44:55</t>
+  </si>
+  <si>
+    <t>01:23:52</t>
+  </si>
+  <si>
+    <t>22:58:55</t>
   </si>
   <si>
     <t>01:08:11</t>
@@ -259,31 +250,34 @@
     <t>02:52:22</t>
   </si>
   <si>
-    <t>00:27:22</t>
+    <t>00:27:23</t>
   </si>
   <si>
     <t>02:05:48</t>
   </si>
   <si>
-    <t>23:41:55</t>
+    <t>23:41:56</t>
   </si>
   <si>
     <t>01:19:25</t>
   </si>
   <si>
-    <t>22:56:46</t>
-  </si>
-  <si>
-    <t>02:41:37</t>
-  </si>
-  <si>
-    <t>04:19:17</t>
-  </si>
-  <si>
-    <t>01:56:05</t>
-  </si>
-  <si>
-    <t>03:33:34</t>
+    <t>22:56:47</t>
+  </si>
+  <si>
+    <t>00:33:09</t>
+  </si>
+  <si>
+    <t>22:13:13</t>
+  </si>
+  <si>
+    <t>23:47:01</t>
+  </si>
+  <si>
+    <t>01:27:30</t>
+  </si>
+  <si>
+    <t>23:01:01</t>
   </si>
   <si>
     <t>01:10:31</t>
@@ -322,16 +316,16 @@
     <t>22:59:02</t>
   </si>
   <si>
-    <t>02:44:54</t>
-  </si>
-  <si>
-    <t>04:21:45</t>
-  </si>
-  <si>
-    <t>01:59:03</t>
-  </si>
-  <si>
-    <t>03:36:28</t>
+    <t>00:36:20</t>
+  </si>
+  <si>
+    <t>23:50:21</t>
+  </si>
+  <si>
+    <t>01:28:21</t>
+  </si>
+  <si>
+    <t>23:04:22</t>
   </si>
   <si>
     <t>01:12:53</t>
@@ -361,25 +355,28 @@
     <t>02:10:43</t>
   </si>
   <si>
-    <t>23:47:45</t>
-  </si>
-  <si>
-    <t>01:25:11</t>
-  </si>
-  <si>
-    <t>23:01:18</t>
-  </si>
-  <si>
-    <t>02:47:04</t>
-  </si>
-  <si>
-    <t>04:24:20</t>
-  </si>
-  <si>
-    <t>02:01:20</t>
-  </si>
-  <si>
-    <t>03:38:50</t>
+    <t>23:47:46</t>
+  </si>
+  <si>
+    <t>01:25:12</t>
+  </si>
+  <si>
+    <t>23:01:19</t>
+  </si>
+  <si>
+    <t>00:39:31</t>
+  </si>
+  <si>
+    <t>22:13:41</t>
+  </si>
+  <si>
+    <t>23:53:42</t>
+  </si>
+  <si>
+    <t>01:29:11</t>
+  </si>
+  <si>
+    <t>23:07:44</t>
   </si>
   <si>
     <t>01:15:28</t>
@@ -418,18 +415,24 @@
     <t>23:03:55</t>
   </si>
   <si>
-    <t>6°</t>
-  </si>
-  <si>
-    <t>18°</t>
+    <t>00:41:44</t>
+  </si>
+  <si>
+    <t>22:17:34</t>
+  </si>
+  <si>
+    <t>23:55:50</t>
+  </si>
+  <si>
+    <t>01:32:50</t>
+  </si>
+  <si>
+    <t>23:09:51</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>20°</t>
-  </si>
-  <si>
     <t>10°</t>
   </si>
   <si>
@@ -442,13 +445,7 @@
     <t>5°</t>
   </si>
   <si>
-    <t>02:45:37</t>
-  </si>
-  <si>
-    <t>04:18:42</t>
-  </si>
-  <si>
-    <t>03:34:54</t>
+    <t>1°</t>
   </si>
   <si>
     <t>02:51:01</t>
@@ -461,6 +458,9 @@
   </si>
   <si>
     <t>02:12:00</t>
+  </si>
+  <si>
+    <t>01:32:29</t>
   </si>
   <si>
     <t>B</t>
@@ -509,7 +509,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -524,13 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,13 +542,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -566,7 +572,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -607,7 +631,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -646,6 +670,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1049,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1127,37 +1163,37 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>54</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>142</v>
+        <v>54</v>
       </c>
       <c r="L2" s="4">
-        <v>-33.4</v>
+        <v>-38.3</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>149</v>
@@ -1166,10 +1202,10 @@
         <v>151</v>
       </c>
       <c r="O2" s="6">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="P2" s="7">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1183,37 +1219,37 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L3" s="4">
-        <v>-20.6</v>
+        <v>-32.8</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>150</v>
@@ -1221,11 +1257,11 @@
       <c r="N3" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="O3" s="9">
-        <v>75</v>
-      </c>
-      <c r="P3" s="10">
-        <v>75</v>
+      <c r="O3" s="6">
+        <v>78</v>
+      </c>
+      <c r="P3" s="7">
+        <v>82</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1239,55 +1275,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>56</v>
       </c>
       <c r="L4" s="4">
-        <v>-37</v>
+        <v>-37.3</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>149</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O4" s="11">
-        <v>1</v>
+        <v>153</v>
+      </c>
+      <c r="O4" s="6">
+        <v>66</v>
       </c>
       <c r="P4" s="8">
         <v>0</v>
       </c>
       <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="8">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="R4" s="9">
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1295,10 +1331,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>51</v>
@@ -1307,34 +1343,34 @@
         <v>57</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L5" s="4">
-        <v>-27.4</v>
+        <v>-36.6</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="O5" s="11">
-        <v>0</v>
+        <v>151</v>
+      </c>
+      <c r="O5" s="6">
+        <v>70</v>
       </c>
       <c r="P5" s="8">
         <v>0</v>
@@ -1342,8 +1378,8 @@
       <c r="Q5" s="8">
         <v>0</v>
       </c>
-      <c r="R5" s="8">
-        <v>0</v>
+      <c r="R5" s="10">
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1351,55 +1387,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="L6" s="4">
-        <v>-38.3</v>
+        <v>-26.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O6" s="11">
-        <v>4</v>
+        <v>153</v>
+      </c>
+      <c r="O6" s="6">
+        <v>76</v>
       </c>
       <c r="P6" s="8">
         <v>0</v>
       </c>
       <c r="Q6" s="8">
-        <v>0</v>
-      </c>
-      <c r="R6" s="12">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="R6" s="11">
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1407,46 +1443,46 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>59</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>145</v>
+        <v>59</v>
       </c>
       <c r="L7" s="4">
-        <v>-32.8</v>
+        <v>-38.2</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="O7" s="6">
-        <v>29</v>
+        <v>151</v>
+      </c>
+      <c r="O7" s="12">
+        <v>3</v>
       </c>
       <c r="P7" s="8">
         <v>0</v>
@@ -1454,8 +1490,8 @@
       <c r="Q7" s="8">
         <v>0</v>
       </c>
-      <c r="R7" s="7">
-        <v>24</v>
+      <c r="R7" s="13">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1463,37 +1499,37 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>60</v>
+        <v>146</v>
       </c>
       <c r="L8" s="4">
-        <v>-37.3</v>
+        <v>-32.2</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>149</v>
@@ -1501,8 +1537,8 @@
       <c r="N8" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="O8" s="11">
-        <v>0</v>
+      <c r="O8" s="12">
+        <v>3</v>
       </c>
       <c r="P8" s="8">
         <v>0</v>
@@ -1510,8 +1546,8 @@
       <c r="Q8" s="8">
         <v>0</v>
       </c>
-      <c r="R8" s="8">
-        <v>0</v>
+      <c r="R8" s="13">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1519,37 +1555,37 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>61</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>146</v>
+        <v>61</v>
       </c>
       <c r="L9" s="4">
-        <v>-36.6</v>
+        <v>-37.5</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>149</v>
@@ -1557,8 +1593,8 @@
       <c r="N9" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="O9" s="11">
-        <v>5</v>
+      <c r="O9" s="14">
+        <v>35</v>
       </c>
       <c r="P9" s="8">
         <v>0</v>
@@ -1566,8 +1602,8 @@
       <c r="Q9" s="8">
         <v>0</v>
       </c>
-      <c r="R9" s="8">
-        <v>1</v>
+      <c r="R9" s="15">
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1575,46 +1611,46 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>62</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>94</v>
+        <v>147</v>
       </c>
       <c r="L10" s="4">
-        <v>-26.5</v>
+        <v>-36.2</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="O10" s="11">
-        <v>6</v>
+        <v>151</v>
+      </c>
+      <c r="O10" s="6">
+        <v>70</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
@@ -1622,8 +1658,8 @@
       <c r="Q10" s="8">
         <v>0</v>
       </c>
-      <c r="R10" s="8">
-        <v>1</v>
+      <c r="R10" s="11">
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1631,37 +1667,37 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>63</v>
       </c>
       <c r="L11" s="4">
-        <v>-38.2</v>
+        <v>-34.5</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>149</v>
@@ -1669,8 +1705,8 @@
       <c r="N11" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="O11" s="11">
-        <v>0</v>
+      <c r="O11" s="14">
+        <v>36</v>
       </c>
       <c r="P11" s="8">
         <v>0</v>
@@ -1678,8 +1714,8 @@
       <c r="Q11" s="8">
         <v>0</v>
       </c>
-      <c r="R11" s="8">
-        <v>0</v>
+      <c r="R11" s="16">
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1687,46 +1723,46 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="L12" s="4">
-        <v>-32.2</v>
+        <v>-38.2</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>149</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="O12" s="11">
-        <v>0</v>
+        <v>151</v>
+      </c>
+      <c r="O12" s="14">
+        <v>35</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
@@ -1734,8 +1770,8 @@
       <c r="Q12" s="8">
         <v>0</v>
       </c>
-      <c r="R12" s="8">
-        <v>0</v>
+      <c r="R12" s="16">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1743,37 +1779,37 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
+        <v>17</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="D13" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>65</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>65</v>
       </c>
       <c r="L13" s="4">
-        <v>-37.5</v>
+        <v>-29.6</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>149</v>
@@ -1781,11 +1817,11 @@
       <c r="N13" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="O13" s="11">
-        <v>0</v>
-      </c>
-      <c r="P13" s="8">
-        <v>0</v>
+      <c r="O13" s="6">
+        <v>46</v>
+      </c>
+      <c r="P13" s="15">
+        <v>31</v>
       </c>
       <c r="Q13" s="8">
         <v>0</v>
@@ -1799,37 +1835,37 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="L14" s="4">
-        <v>-36.2</v>
+        <v>-37.7</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>149</v>
@@ -1837,11 +1873,11 @@
       <c r="N14" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="O14" s="11">
-        <v>0</v>
-      </c>
-      <c r="P14" s="8">
-        <v>0</v>
+      <c r="O14" s="14">
+        <v>27</v>
+      </c>
+      <c r="P14" s="17">
+        <v>21</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
@@ -1855,55 +1891,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>67</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>67</v>
       </c>
       <c r="L15" s="4">
-        <v>-34.5</v>
+        <v>-23.2</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>149</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O15" s="9">
-        <v>79</v>
-      </c>
-      <c r="P15" s="13">
-        <v>14</v>
+        <v>153</v>
+      </c>
+      <c r="O15" s="12">
+        <v>0</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0</v>
       </c>
       <c r="Q15" s="8">
         <v>0</v>
       </c>
-      <c r="R15" s="10">
-        <v>75</v>
+      <c r="R15" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1911,37 +1947,37 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>68</v>
       </c>
       <c r="L16" s="4">
-        <v>-38.2</v>
+        <v>-35</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>149</v>
@@ -1949,108 +1985,188 @@
       <c r="N16" s="1" t="s">
         <v>151</v>
       </c>
+      <c r="O16" s="12">
+        <v>1</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>0</v>
+      </c>
+      <c r="R16" s="8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:18">
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>69</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>69</v>
+        <v>148</v>
       </c>
       <c r="L17" s="4">
-        <v>-29.6</v>
+        <v>-38.1</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>149</v>
       </c>
       <c r="N17" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="O17" s="12">
+        <v>1</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0</v>
+      </c>
+      <c r="R17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="2">
+        <v>77</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L18" s="4">
+        <v>-30.3</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="N18" s="1" t="s">
         <v>151</v>
+      </c>
+      <c r="O18" s="12">
+        <v>1</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>0</v>
+      </c>
+      <c r="R18" s="8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A17">
+  <conditionalFormatting sqref="A2:A18">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B17">
+  <conditionalFormatting sqref="B2:B18">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C17">
+  <conditionalFormatting sqref="C2:C18">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D17">
+  <conditionalFormatting sqref="D2:D18">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E17">
+  <conditionalFormatting sqref="E2:E18">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F17">
+  <conditionalFormatting sqref="F2:F18">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G17">
+  <conditionalFormatting sqref="G2:G18">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H17">
+  <conditionalFormatting sqref="H2:H18">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I17">
+  <conditionalFormatting sqref="I2:I18">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J17">
+  <conditionalFormatting sqref="J2:J18">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K17">
+  <conditionalFormatting sqref="K2:K18">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L17">
+  <conditionalFormatting sqref="L2:L18">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2069,12 +2185,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M17">
+  <conditionalFormatting sqref="M2:M18">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N17">
+  <conditionalFormatting sqref="N2:N18">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2091,22 +2207,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O17">
+  <conditionalFormatting sqref="O2:O18">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P17">
+  <conditionalFormatting sqref="P2:P18">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q17">
+  <conditionalFormatting sqref="Q2:Q18">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R17">
+  <conditionalFormatting sqref="R2:R18">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="167">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260619--01</t>
-  </si>
-  <si>
-    <t>20260619--02</t>
-  </si>
-  <si>
     <t>20260620--01</t>
   </si>
   <si>
@@ -121,13 +115,19 @@
     <t>20260625--02</t>
   </si>
   <si>
-    <t>04:42</t>
-  </si>
-  <si>
-    <t>06:21</t>
-  </si>
-  <si>
-    <t>01:48</t>
+    <t>20260626--01</t>
+  </si>
+  <si>
+    <t>20260626--02</t>
+  </si>
+  <si>
+    <t>20260626--03</t>
+  </si>
+  <si>
+    <t>20260626--04</t>
+  </si>
+  <si>
+    <t>01:46</t>
   </si>
   <si>
     <t>06:41</t>
@@ -142,7 +142,7 @@
     <t>03:40</t>
   </si>
   <si>
-    <t>06:29</t>
+    <t>06:30</t>
   </si>
   <si>
     <t>04:55</t>
@@ -160,100 +160,109 @@
     <t>06:22</t>
   </si>
   <si>
-    <t>00:28</t>
-  </si>
-  <si>
-    <t>01:41</t>
+    <t>00:26</t>
+  </si>
+  <si>
+    <t>01:42</t>
   </si>
   <si>
     <t>06:43</t>
   </si>
   <si>
+    <t>03:47</t>
+  </si>
+  <si>
+    <t>05:23</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>05:01</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:01</t>
-  </si>
-  <si>
     <t>00:44</t>
   </si>
   <si>
-    <t>01:05:38</t>
-  </si>
-  <si>
-    <t>02:42:29</t>
-  </si>
-  <si>
-    <t>00:20:33</t>
-  </si>
-  <si>
-    <t>01:56:40</t>
-  </si>
-  <si>
-    <t>03:35:41</t>
-  </si>
-  <si>
-    <t>01:10:55</t>
+    <t>00:20:34</t>
+  </si>
+  <si>
+    <t>01:56:41</t>
+  </si>
+  <si>
+    <t>03:35:42</t>
+  </si>
+  <si>
+    <t>01:10:56</t>
   </si>
   <si>
     <t>02:49:28</t>
   </si>
   <si>
-    <t>00:25:14</t>
-  </si>
-  <si>
-    <t>02:03:15</t>
+    <t>00:25:15</t>
+  </si>
+  <si>
+    <t>02:03:16</t>
   </si>
   <si>
     <t>23:39:39</t>
   </si>
   <si>
-    <t>01:17:05</t>
-  </si>
-  <si>
-    <t>22:54:11</t>
+    <t>01:17:06</t>
+  </si>
+  <si>
+    <t>22:54:10</t>
   </si>
   <si>
     <t>00:30:58</t>
   </si>
   <si>
-    <t>22:08:53</t>
-  </si>
-  <si>
-    <t>23:44:55</t>
-  </si>
-  <si>
-    <t>01:23:52</t>
-  </si>
-  <si>
-    <t>22:58:55</t>
-  </si>
-  <si>
-    <t>01:08:11</t>
-  </si>
-  <si>
-    <t>02:44:41</t>
-  </si>
-  <si>
-    <t>00:24:03</t>
-  </si>
-  <si>
-    <t>01:58:47</t>
-  </si>
-  <si>
-    <t>03:39:25</t>
-  </si>
-  <si>
-    <t>01:13:01</t>
-  </si>
-  <si>
-    <t>02:52:22</t>
+    <t>22:08:51</t>
+  </si>
+  <si>
+    <t>23:44:53</t>
+  </si>
+  <si>
+    <t>01:23:51</t>
+  </si>
+  <si>
+    <t>22:58:52</t>
+  </si>
+  <si>
+    <t>00:37:21</t>
+  </si>
+  <si>
+    <t>05:33:07</t>
+  </si>
+  <si>
+    <t>22:12:56</t>
+  </si>
+  <si>
+    <t>23:50:52</t>
+  </si>
+  <si>
+    <t>00:24:05</t>
+  </si>
+  <si>
+    <t>01:58:48</t>
+  </si>
+  <si>
+    <t>03:39:26</t>
+  </si>
+  <si>
+    <t>01:13:02</t>
+  </si>
+  <si>
+    <t>02:52:23</t>
   </si>
   <si>
     <t>00:27:23</t>
   </si>
   <si>
-    <t>02:05:48</t>
+    <t>02:05:49</t>
   </si>
   <si>
     <t>23:41:56</t>
@@ -262,49 +271,55 @@
     <t>01:19:25</t>
   </si>
   <si>
-    <t>22:56:47</t>
+    <t>22:56:46</t>
   </si>
   <si>
     <t>00:33:09</t>
   </si>
   <si>
-    <t>22:13:13</t>
-  </si>
-  <si>
-    <t>23:47:01</t>
-  </si>
-  <si>
-    <t>01:27:30</t>
-  </si>
-  <si>
-    <t>23:01:01</t>
-  </si>
-  <si>
-    <t>01:10:31</t>
-  </si>
-  <si>
-    <t>02:47:51</t>
-  </si>
-  <si>
-    <t>00:24:57</t>
-  </si>
-  <si>
-    <t>02:02:07</t>
-  </si>
-  <si>
-    <t>03:40:08</t>
-  </si>
-  <si>
-    <t>01:16:22</t>
-  </si>
-  <si>
-    <t>02:54:12</t>
+    <t>22:13:12</t>
+  </si>
+  <si>
+    <t>23:47:00</t>
+  </si>
+  <si>
+    <t>01:27:28</t>
+  </si>
+  <si>
+    <t>23:00:58</t>
+  </si>
+  <si>
+    <t>00:40:13</t>
+  </si>
+  <si>
+    <t>05:35:34</t>
+  </si>
+  <si>
+    <t>22:15:05</t>
+  </si>
+  <si>
+    <t>23:53:23</t>
+  </si>
+  <si>
+    <t>00:24:58</t>
+  </si>
+  <si>
+    <t>02:02:08</t>
+  </si>
+  <si>
+    <t>03:40:09</t>
+  </si>
+  <si>
+    <t>01:16:23</t>
+  </si>
+  <si>
+    <t>02:54:13</t>
   </si>
   <si>
     <t>00:30:37</t>
   </si>
   <si>
-    <t>02:08:15</t>
+    <t>02:08:16</t>
   </si>
   <si>
     <t>23:44:50</t>
@@ -316,43 +331,49 @@
     <t>22:59:02</t>
   </si>
   <si>
-    <t>00:36:20</t>
-  </si>
-  <si>
-    <t>23:50:21</t>
-  </si>
-  <si>
-    <t>01:28:21</t>
-  </si>
-  <si>
-    <t>23:04:22</t>
-  </si>
-  <si>
-    <t>01:12:53</t>
-  </si>
-  <si>
-    <t>02:51:02</t>
+    <t>00:36:19</t>
+  </si>
+  <si>
+    <t>23:50:20</t>
+  </si>
+  <si>
+    <t>01:28:19</t>
+  </si>
+  <si>
+    <t>23:04:19</t>
+  </si>
+  <si>
+    <t>00:42:07</t>
+  </si>
+  <si>
+    <t>05:38:15</t>
+  </si>
+  <si>
+    <t>22:18:18</t>
+  </si>
+  <si>
+    <t>23:55:53</t>
   </si>
   <si>
     <t>00:25:51</t>
   </si>
   <si>
-    <t>02:05:28</t>
-  </si>
-  <si>
-    <t>03:40:52</t>
-  </si>
-  <si>
-    <t>01:19:45</t>
-  </si>
-  <si>
-    <t>02:56:02</t>
-  </si>
-  <si>
-    <t>00:33:52</t>
-  </si>
-  <si>
-    <t>02:10:43</t>
+    <t>02:05:29</t>
+  </si>
+  <si>
+    <t>03:40:53</t>
+  </si>
+  <si>
+    <t>01:19:46</t>
+  </si>
+  <si>
+    <t>02:56:03</t>
+  </si>
+  <si>
+    <t>00:33:53</t>
+  </si>
+  <si>
+    <t>02:10:44</t>
   </si>
   <si>
     <t>23:47:46</t>
@@ -361,28 +382,34 @@
     <t>01:25:12</t>
   </si>
   <si>
-    <t>23:01:19</t>
+    <t>23:01:18</t>
   </si>
   <si>
     <t>00:39:31</t>
   </si>
   <si>
-    <t>22:13:41</t>
-  </si>
-  <si>
-    <t>23:53:42</t>
-  </si>
-  <si>
-    <t>01:29:11</t>
-  </si>
-  <si>
-    <t>23:07:44</t>
-  </si>
-  <si>
-    <t>01:15:28</t>
-  </si>
-  <si>
-    <t>02:53:15</t>
+    <t>22:13:38</t>
+  </si>
+  <si>
+    <t>23:53:41</t>
+  </si>
+  <si>
+    <t>01:29:10</t>
+  </si>
+  <si>
+    <t>23:07:41</t>
+  </si>
+  <si>
+    <t>00:44:00</t>
+  </si>
+  <si>
+    <t>05:40:57</t>
+  </si>
+  <si>
+    <t>22:21:30</t>
+  </si>
+  <si>
+    <t>23:58:24</t>
   </si>
   <si>
     <t>00:29:23</t>
@@ -391,76 +418,88 @@
     <t>02:07:37</t>
   </si>
   <si>
-    <t>03:44:38</t>
-  </si>
-  <si>
-    <t>01:21:52</t>
-  </si>
-  <si>
-    <t>02:58:59</t>
+    <t>03:44:39</t>
+  </si>
+  <si>
+    <t>01:21:53</t>
+  </si>
+  <si>
+    <t>02:59:00</t>
   </si>
   <si>
     <t>00:36:02</t>
   </si>
   <si>
-    <t>02:13:17</t>
+    <t>02:13:18</t>
   </si>
   <si>
     <t>23:50:03</t>
   </si>
   <si>
-    <t>01:27:32</t>
+    <t>01:27:33</t>
   </si>
   <si>
     <t>23:03:55</t>
   </si>
   <si>
-    <t>00:41:44</t>
-  </si>
-  <si>
-    <t>22:17:34</t>
-  </si>
-  <si>
-    <t>23:55:50</t>
-  </si>
-  <si>
-    <t>01:32:50</t>
-  </si>
-  <si>
-    <t>23:09:51</t>
+    <t>00:41:43</t>
+  </si>
+  <si>
+    <t>22:17:32</t>
+  </si>
+  <si>
+    <t>23:55:48</t>
+  </si>
+  <si>
+    <t>01:32:48</t>
+  </si>
+  <si>
+    <t>23:09:48</t>
+  </si>
+  <si>
+    <t>00:46:54</t>
+  </si>
+  <si>
+    <t>05:43:24</t>
+  </si>
+  <si>
+    <t>22:23:40</t>
+  </si>
+  <si>
+    <t>00:00:56</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
+    <t>2°</t>
+  </si>
+  <si>
+    <t>11°</t>
+  </si>
+  <si>
     <t>10°</t>
   </si>
   <si>
-    <t>2°</t>
-  </si>
-  <si>
-    <t>11°</t>
-  </si>
-  <si>
     <t>5°</t>
   </si>
   <si>
     <t>1°</t>
   </si>
   <si>
-    <t>02:51:01</t>
-  </si>
-  <si>
-    <t>02:07:04</t>
-  </si>
-  <si>
-    <t>02:56:06</t>
-  </si>
-  <si>
-    <t>02:12:00</t>
-  </si>
-  <si>
-    <t>01:32:29</t>
+    <t>-</t>
+  </si>
+  <si>
+    <t>02:07:05</t>
+  </si>
+  <si>
+    <t>02:56:07</t>
+  </si>
+  <si>
+    <t>02:12:01</t>
+  </si>
+  <si>
+    <t>01:32:27</t>
   </si>
   <si>
     <t>B</t>
@@ -469,13 +508,13 @@
     <t>A+B</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -509,7 +548,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -530,13 +569,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -560,13 +617,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,19 +635,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -631,7 +676,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -682,6 +727,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1085,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1163,55 +1211,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L2" s="4">
-        <v>-38.3</v>
+        <v>-37.3</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="O2" s="6">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P2" s="7">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
       </c>
-      <c r="R2" s="8">
-        <v>0</v>
+      <c r="R2" s="9">
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1219,55 +1267,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="L3" s="4">
-        <v>-32.8</v>
+        <v>-36.6</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="O3" s="6">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P3" s="7">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
       </c>
-      <c r="R3" s="8">
-        <v>0</v>
+      <c r="R3" s="7">
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1278,52 +1326,52 @@
         <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="L4" s="4">
-        <v>-37.3</v>
+        <v>-26.5</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="O4" s="6">
-        <v>66</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
+        <v>67</v>
+      </c>
+      <c r="P4" s="7">
+        <v>23</v>
       </c>
       <c r="Q4" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R4" s="9">
-        <v>57</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1331,46 +1379,46 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>81</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>145</v>
+        <v>60</v>
       </c>
       <c r="L5" s="4">
-        <v>-36.6</v>
+        <v>-38.2</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O5" s="6">
-        <v>70</v>
+        <v>165</v>
+      </c>
+      <c r="O5" s="10">
+        <v>4</v>
       </c>
       <c r="P5" s="8">
         <v>0</v>
@@ -1378,8 +1426,8 @@
       <c r="Q5" s="8">
         <v>0</v>
       </c>
-      <c r="R5" s="10">
-        <v>60</v>
+      <c r="R5" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1387,55 +1435,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="L6" s="4">
-        <v>-26.5</v>
+        <v>-32.2</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="O6" s="6">
-        <v>76</v>
+        <v>164</v>
+      </c>
+      <c r="O6" s="10">
+        <v>4</v>
       </c>
       <c r="P6" s="8">
         <v>0</v>
       </c>
       <c r="Q6" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" s="11">
-        <v>65</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1443,46 +1491,46 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>46</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L7" s="4">
-        <v>-38.2</v>
+        <v>-37.5</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O7" s="12">
-        <v>3</v>
+        <v>165</v>
+      </c>
+      <c r="O7" s="6">
+        <v>55</v>
       </c>
       <c r="P7" s="8">
         <v>0</v>
@@ -1490,8 +1538,8 @@
       <c r="Q7" s="8">
         <v>0</v>
       </c>
-      <c r="R7" s="13">
-        <v>3</v>
+      <c r="R7" s="12">
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1499,47 +1547,47 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-36.2</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="O8" s="6">
         <v>60</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="L8" s="4">
-        <v>-32.2</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="O8" s="12">
-        <v>3</v>
-      </c>
       <c r="P8" s="8">
         <v>0</v>
       </c>
@@ -1547,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="13">
-        <v>3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1555,46 +1603,46 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L9" s="4">
-        <v>-37.5</v>
+        <v>-34.5</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O9" s="14">
-        <v>35</v>
+        <v>165</v>
+      </c>
+      <c r="O9" s="6">
+        <v>70</v>
       </c>
       <c r="P9" s="8">
         <v>0</v>
@@ -1602,8 +1650,8 @@
       <c r="Q9" s="8">
         <v>0</v>
       </c>
-      <c r="R9" s="15">
-        <v>32</v>
+      <c r="R9" s="13">
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1611,46 +1659,46 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>147</v>
+        <v>65</v>
       </c>
       <c r="L10" s="4">
-        <v>-36.2</v>
+        <v>-38.2</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="O10" s="6">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
@@ -1658,8 +1706,8 @@
       <c r="Q10" s="8">
         <v>0</v>
       </c>
-      <c r="R10" s="11">
-        <v>65</v>
+      <c r="R10" s="14">
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1667,55 +1715,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L11" s="4">
-        <v>-34.5</v>
+        <v>-29.6</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O11" s="14">
-        <v>36</v>
-      </c>
-      <c r="P11" s="8">
-        <v>0</v>
+        <v>165</v>
+      </c>
+      <c r="O11" s="6">
+        <v>65</v>
+      </c>
+      <c r="P11" s="13">
+        <v>61</v>
       </c>
       <c r="Q11" s="8">
         <v>0</v>
       </c>
-      <c r="R11" s="16">
-        <v>12</v>
+      <c r="R11" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1723,55 +1771,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L12" s="4">
-        <v>-38.2</v>
+        <v>-37.7</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O12" s="14">
-        <v>35</v>
-      </c>
-      <c r="P12" s="8">
-        <v>0</v>
+        <v>165</v>
+      </c>
+      <c r="O12" s="6">
+        <v>50</v>
+      </c>
+      <c r="P12" s="15">
+        <v>47</v>
       </c>
       <c r="Q12" s="8">
         <v>0</v>
       </c>
-      <c r="R12" s="16">
-        <v>10</v>
+      <c r="R12" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1779,49 +1827,49 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L13" s="4">
-        <v>-29.6</v>
+        <v>-23.2</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O13" s="6">
-        <v>46</v>
-      </c>
-      <c r="P13" s="15">
-        <v>31</v>
+        <v>164</v>
+      </c>
+      <c r="O13" s="10">
+        <v>13</v>
+      </c>
+      <c r="P13" s="16">
+        <v>9</v>
       </c>
       <c r="Q13" s="8">
         <v>0</v>
@@ -1835,55 +1883,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
+        <v>63</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="D14" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L14" s="4">
-        <v>-37.7</v>
+        <v>-35</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O14" s="14">
-        <v>27</v>
-      </c>
-      <c r="P14" s="17">
-        <v>21</v>
+        <v>165</v>
+      </c>
+      <c r="O14" s="10">
+        <v>7</v>
+      </c>
+      <c r="P14" s="11">
+        <v>4</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
       </c>
       <c r="R14" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1891,46 +1939,46 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>67</v>
+        <v>161</v>
       </c>
       <c r="L15" s="4">
-        <v>-23.2</v>
+        <v>-38.1</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="O15" s="12">
-        <v>0</v>
+        <v>164</v>
+      </c>
+      <c r="O15" s="10">
+        <v>3</v>
       </c>
       <c r="P15" s="8">
         <v>0</v>
@@ -1938,8 +1986,8 @@
       <c r="Q15" s="8">
         <v>0</v>
       </c>
-      <c r="R15" s="8">
-        <v>0</v>
+      <c r="R15" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1947,49 +1995,49 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L16" s="4">
-        <v>-35</v>
+        <v>-30.3</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O16" s="12">
-        <v>1</v>
-      </c>
-      <c r="P16" s="8">
-        <v>0</v>
+        <v>165</v>
+      </c>
+      <c r="O16" s="17">
+        <v>15</v>
+      </c>
+      <c r="P16" s="16">
+        <v>8</v>
       </c>
       <c r="Q16" s="8">
         <v>0</v>
@@ -2003,46 +2051,46 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>148</v>
+        <v>72</v>
       </c>
       <c r="L17" s="4">
-        <v>-38.1</v>
+        <v>-37.9</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="O17" s="12">
-        <v>1</v>
+        <v>164</v>
+      </c>
+      <c r="O17" s="10">
+        <v>0</v>
       </c>
       <c r="P17" s="8">
         <v>0</v>
@@ -2059,114 +2107,226 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>70</v>
+        <v>157</v>
       </c>
       <c r="L18" s="4">
-        <v>-30.3</v>
+        <v>-7.1</v>
       </c>
       <c r="M18" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="O18" s="17">
+        <v>12</v>
+      </c>
+      <c r="P18" s="11">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>0</v>
+      </c>
+      <c r="R18" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="2">
+        <v>43</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="N18" s="1" t="s">
+      <c r="J19" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="O18" s="12">
-        <v>1</v>
-      </c>
-      <c r="P18" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>0</v>
-      </c>
-      <c r="R18" s="8">
-        <v>0</v>
+      <c r="K19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L19" s="4">
+        <v>-24</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="O19" s="17">
+        <v>24</v>
+      </c>
+      <c r="P19" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>0</v>
+      </c>
+      <c r="R19" s="18">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="2">
+        <v>19</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L20" s="4">
+        <v>-35.4</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="O20" s="10">
+        <v>15</v>
+      </c>
+      <c r="P20" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="8">
+        <v>0</v>
+      </c>
+      <c r="R20" s="16">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A18">
+  <conditionalFormatting sqref="A2:A20">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B18">
+  <conditionalFormatting sqref="B2:B20">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C18">
+  <conditionalFormatting sqref="C2:C20">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D18">
+  <conditionalFormatting sqref="D2:D20">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E18">
+  <conditionalFormatting sqref="E2:E20">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F18">
+  <conditionalFormatting sqref="F2:F20">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G18">
+  <conditionalFormatting sqref="G2:G20">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H18">
+  <conditionalFormatting sqref="H2:H20">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I18">
+  <conditionalFormatting sqref="I2:I20">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J18">
+  <conditionalFormatting sqref="J2:J20">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K18">
+  <conditionalFormatting sqref="K2:K20">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L18">
+  <conditionalFormatting sqref="L2:L20">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2185,12 +2345,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M18">
+  <conditionalFormatting sqref="M2:M20">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N18">
+  <conditionalFormatting sqref="N2:N20">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2207,22 +2367,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O18">
+  <conditionalFormatting sqref="O2:O20">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P18">
+  <conditionalFormatting sqref="P2:P20">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q18">
+  <conditionalFormatting sqref="Q2:Q20">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R18">
+  <conditionalFormatting sqref="R2:R20">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="166">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260620--01</t>
-  </si>
-  <si>
-    <t>20260620--02</t>
-  </si>
-  <si>
-    <t>20260620--03</t>
-  </si>
-  <si>
     <t>20260621--01</t>
   </si>
   <si>
@@ -127,13 +118,13 @@
     <t>20260626--04</t>
   </si>
   <si>
-    <t>01:46</t>
-  </si>
-  <si>
-    <t>06:41</t>
-  </si>
-  <si>
-    <t>01:27</t>
+    <t>20260627--01</t>
+  </si>
+  <si>
+    <t>20260627--02</t>
+  </si>
+  <si>
+    <t>20260627--03</t>
   </si>
   <si>
     <t>06:44</t>
@@ -142,7 +133,7 @@
     <t>03:40</t>
   </si>
   <si>
-    <t>06:30</t>
+    <t>06:29</t>
   </si>
   <si>
     <t>04:55</t>
@@ -151,25 +142,28 @@
     <t>05:50</t>
   </si>
   <si>
-    <t>05:47</t>
+    <t>05:46</t>
   </si>
   <si>
     <t>04:32</t>
   </si>
   <si>
-    <t>06:22</t>
+    <t>06:21</t>
   </si>
   <si>
     <t>00:26</t>
   </si>
   <si>
+    <t>06:40</t>
+  </si>
+  <si>
     <t>01:42</t>
   </si>
   <si>
     <t>06:43</t>
   </si>
   <si>
-    <t>03:47</t>
+    <t>03:48</t>
   </si>
   <si>
     <t>05:23</t>
@@ -181,25 +175,22 @@
     <t>05:01</t>
   </si>
   <si>
+    <t>04:18</t>
+  </si>
+  <si>
+    <t>05:41</t>
+  </si>
+  <si>
+    <t>05:51</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:44</t>
-  </si>
-  <si>
-    <t>00:20:34</t>
-  </si>
-  <si>
-    <t>01:56:41</t>
-  </si>
-  <si>
-    <t>03:35:42</t>
-  </si>
-  <si>
     <t>01:10:56</t>
   </si>
   <si>
-    <t>02:49:28</t>
+    <t>02:49:29</t>
   </si>
   <si>
     <t>00:25:15</t>
@@ -208,58 +199,58 @@
     <t>02:03:16</t>
   </si>
   <si>
-    <t>23:39:39</t>
+    <t>23:39:40</t>
   </si>
   <si>
     <t>01:17:06</t>
   </si>
   <si>
-    <t>22:54:10</t>
-  </si>
-  <si>
-    <t>00:30:58</t>
-  </si>
-  <si>
-    <t>22:08:51</t>
-  </si>
-  <si>
-    <t>23:44:53</t>
-  </si>
-  <si>
-    <t>01:23:51</t>
-  </si>
-  <si>
-    <t>22:58:52</t>
-  </si>
-  <si>
-    <t>00:37:21</t>
-  </si>
-  <si>
-    <t>05:33:07</t>
-  </si>
-  <si>
-    <t>22:12:56</t>
-  </si>
-  <si>
-    <t>23:50:52</t>
-  </si>
-  <si>
-    <t>00:24:05</t>
-  </si>
-  <si>
-    <t>01:58:48</t>
-  </si>
-  <si>
-    <t>03:39:26</t>
+    <t>22:54:11</t>
+  </si>
+  <si>
+    <t>00:30:59</t>
+  </si>
+  <si>
+    <t>22:08:52</t>
+  </si>
+  <si>
+    <t>23:44:54</t>
+  </si>
+  <si>
+    <t>01:23:52</t>
+  </si>
+  <si>
+    <t>22:58:54</t>
+  </si>
+  <si>
+    <t>00:37:22</t>
+  </si>
+  <si>
+    <t>05:33:08</t>
+  </si>
+  <si>
+    <t>22:12:58</t>
+  </si>
+  <si>
+    <t>23:50:54</t>
+  </si>
+  <si>
+    <t>04:47:11</t>
+  </si>
+  <si>
+    <t>21:27:07</t>
+  </si>
+  <si>
+    <t>23:04:28</t>
   </si>
   <si>
     <t>01:13:02</t>
   </si>
   <si>
-    <t>02:52:23</t>
-  </si>
-  <si>
-    <t>00:27:23</t>
+    <t>02:52:24</t>
+  </si>
+  <si>
+    <t>00:27:24</t>
   </si>
   <si>
     <t>02:05:49</t>
@@ -268,46 +259,46 @@
     <t>23:41:56</t>
   </si>
   <si>
-    <t>01:19:25</t>
-  </si>
-  <si>
-    <t>22:56:46</t>
-  </si>
-  <si>
-    <t>00:33:09</t>
-  </si>
-  <si>
-    <t>22:13:12</t>
-  </si>
-  <si>
-    <t>23:47:00</t>
-  </si>
-  <si>
-    <t>01:27:28</t>
-  </si>
-  <si>
-    <t>23:00:58</t>
-  </si>
-  <si>
-    <t>00:40:13</t>
-  </si>
-  <si>
-    <t>05:35:34</t>
-  </si>
-  <si>
-    <t>22:15:05</t>
-  </si>
-  <si>
-    <t>23:53:23</t>
-  </si>
-  <si>
-    <t>00:24:58</t>
-  </si>
-  <si>
-    <t>02:02:08</t>
-  </si>
-  <si>
-    <t>03:40:09</t>
+    <t>01:19:26</t>
+  </si>
+  <si>
+    <t>22:56:47</t>
+  </si>
+  <si>
+    <t>00:33:10</t>
+  </si>
+  <si>
+    <t>22:13:13</t>
+  </si>
+  <si>
+    <t>23:47:01</t>
+  </si>
+  <si>
+    <t>01:27:29</t>
+  </si>
+  <si>
+    <t>23:00:59</t>
+  </si>
+  <si>
+    <t>00:40:14</t>
+  </si>
+  <si>
+    <t>05:35:35</t>
+  </si>
+  <si>
+    <t>22:15:07</t>
+  </si>
+  <si>
+    <t>23:53:25</t>
+  </si>
+  <si>
+    <t>04:49:55</t>
+  </si>
+  <si>
+    <t>21:29:26</t>
+  </si>
+  <si>
+    <t>23:06:46</t>
   </si>
   <si>
     <t>01:16:23</t>
@@ -316,58 +307,58 @@
     <t>02:54:13</t>
   </si>
   <si>
-    <t>00:30:37</t>
+    <t>00:30:38</t>
   </si>
   <si>
     <t>02:08:16</t>
   </si>
   <si>
-    <t>23:44:50</t>
+    <t>23:44:51</t>
   </si>
   <si>
     <t>01:22:18</t>
   </si>
   <si>
-    <t>22:59:02</t>
-  </si>
-  <si>
-    <t>00:36:19</t>
-  </si>
-  <si>
-    <t>23:50:20</t>
-  </si>
-  <si>
-    <t>01:28:19</t>
-  </si>
-  <si>
-    <t>23:04:19</t>
-  </si>
-  <si>
-    <t>00:42:07</t>
-  </si>
-  <si>
-    <t>05:38:15</t>
-  </si>
-  <si>
-    <t>22:18:18</t>
-  </si>
-  <si>
-    <t>23:55:53</t>
-  </si>
-  <si>
-    <t>00:25:51</t>
-  </si>
-  <si>
-    <t>02:05:29</t>
-  </si>
-  <si>
-    <t>03:40:53</t>
+    <t>22:59:03</t>
+  </si>
+  <si>
+    <t>00:36:20</t>
+  </si>
+  <si>
+    <t>23:50:21</t>
+  </si>
+  <si>
+    <t>01:28:20</t>
+  </si>
+  <si>
+    <t>23:04:20</t>
+  </si>
+  <si>
+    <t>00:42:08</t>
+  </si>
+  <si>
+    <t>05:38:17</t>
+  </si>
+  <si>
+    <t>22:18:19</t>
+  </si>
+  <si>
+    <t>23:55:55</t>
+  </si>
+  <si>
+    <t>04:52:04</t>
+  </si>
+  <si>
+    <t>21:32:16</t>
+  </si>
+  <si>
+    <t>23:09:41</t>
   </si>
   <si>
     <t>01:19:46</t>
   </si>
   <si>
-    <t>02:56:03</t>
+    <t>02:56:04</t>
   </si>
   <si>
     <t>00:33:53</t>
@@ -382,43 +373,43 @@
     <t>01:25:12</t>
   </si>
   <si>
-    <t>23:01:18</t>
+    <t>23:01:19</t>
   </si>
   <si>
     <t>00:39:31</t>
   </si>
   <si>
-    <t>22:13:38</t>
+    <t>22:13:39</t>
   </si>
   <si>
     <t>23:53:41</t>
   </si>
   <si>
-    <t>01:29:10</t>
-  </si>
-  <si>
-    <t>23:07:41</t>
-  </si>
-  <si>
-    <t>00:44:00</t>
-  </si>
-  <si>
-    <t>05:40:57</t>
-  </si>
-  <si>
-    <t>22:21:30</t>
-  </si>
-  <si>
-    <t>23:58:24</t>
-  </si>
-  <si>
-    <t>00:29:23</t>
-  </si>
-  <si>
-    <t>02:07:37</t>
-  </si>
-  <si>
-    <t>03:44:39</t>
+    <t>01:29:11</t>
+  </si>
+  <si>
+    <t>23:07:42</t>
+  </si>
+  <si>
+    <t>00:44:02</t>
+  </si>
+  <si>
+    <t>05:40:58</t>
+  </si>
+  <si>
+    <t>22:21:32</t>
+  </si>
+  <si>
+    <t>23:58:26</t>
+  </si>
+  <si>
+    <t>04:54:13</t>
+  </si>
+  <si>
+    <t>21:35:07</t>
+  </si>
+  <si>
+    <t>23:12:37</t>
   </si>
   <si>
     <t>01:21:53</t>
@@ -427,13 +418,13 @@
     <t>02:59:00</t>
   </si>
   <si>
-    <t>00:36:02</t>
+    <t>00:36:03</t>
   </si>
   <si>
     <t>02:13:18</t>
   </si>
   <si>
-    <t>23:50:03</t>
+    <t>23:50:04</t>
   </si>
   <si>
     <t>01:27:33</t>
@@ -442,42 +433,45 @@
     <t>23:03:55</t>
   </si>
   <si>
-    <t>00:41:43</t>
-  </si>
-  <si>
-    <t>22:17:32</t>
-  </si>
-  <si>
-    <t>23:55:48</t>
-  </si>
-  <si>
-    <t>01:32:48</t>
-  </si>
-  <si>
-    <t>23:09:48</t>
-  </si>
-  <si>
-    <t>00:46:54</t>
-  </si>
-  <si>
-    <t>05:43:24</t>
-  </si>
-  <si>
-    <t>22:23:40</t>
-  </si>
-  <si>
-    <t>00:00:56</t>
+    <t>00:41:44</t>
+  </si>
+  <si>
+    <t>22:17:33</t>
+  </si>
+  <si>
+    <t>23:55:49</t>
+  </si>
+  <si>
+    <t>01:32:49</t>
+  </si>
+  <si>
+    <t>23:09:49</t>
+  </si>
+  <si>
+    <t>00:46:55</t>
+  </si>
+  <si>
+    <t>05:43:25</t>
+  </si>
+  <si>
+    <t>22:23:42</t>
+  </si>
+  <si>
+    <t>00:00:58</t>
+  </si>
+  <si>
+    <t>04:56:57</t>
+  </si>
+  <si>
+    <t>21:37:27</t>
+  </si>
+  <si>
+    <t>23:14:57</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>2°</t>
-  </si>
-  <si>
-    <t>11°</t>
-  </si>
-  <si>
     <t>10°</t>
   </si>
   <si>
@@ -490,7 +484,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>02:07:05</t>
+    <t>6°</t>
   </si>
   <si>
     <t>02:56:07</t>
@@ -499,7 +493,10 @@
     <t>02:12:01</t>
   </si>
   <si>
-    <t>01:32:27</t>
+    <t>01:32:28</t>
+  </si>
+  <si>
+    <t>21:28:42</t>
   </si>
   <si>
     <t>B</t>
@@ -508,10 +505,10 @@
     <t>A+B</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>2</t>
@@ -548,7 +545,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -558,30 +555,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD7E4BC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -599,7 +572,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -611,13 +596,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -629,13 +626,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -676,7 +685,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -730,6 +739,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1211,13 +1226,13 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>57</v>
@@ -1241,25 +1256,25 @@
         <v>57</v>
       </c>
       <c r="L2" s="4">
-        <v>-37.3</v>
+        <v>-38.2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O2" s="6">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="P2" s="7">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
       </c>
-      <c r="R2" s="9">
-        <v>20</v>
+      <c r="R2" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1267,13 +1282,13 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>58</v>
@@ -1294,28 +1309,28 @@
         <v>152</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L3" s="4">
-        <v>-36.6</v>
+        <v>-32.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O3" s="6">
-        <v>77</v>
-      </c>
-      <c r="P3" s="7">
-        <v>25</v>
+        <v>17</v>
+      </c>
+      <c r="P3" s="8">
+        <v>2</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
       </c>
-      <c r="R3" s="7">
-        <v>23</v>
+      <c r="R3" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1323,7 +1338,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>39</v>
@@ -1347,31 +1362,31 @@
         <v>134</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="L4" s="4">
-        <v>-26.5</v>
+        <v>-37.5</v>
       </c>
       <c r="M4" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="N4" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="O4" s="6">
-        <v>67</v>
-      </c>
-      <c r="P4" s="7">
-        <v>23</v>
+        <v>5</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
       </c>
-      <c r="R4" s="9">
-        <v>20</v>
+      <c r="R4" s="7">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1379,13 +1394,13 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>60</v>
@@ -1403,21 +1418,21 @@
         <v>135</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>60</v>
+        <v>158</v>
       </c>
       <c r="L5" s="4">
-        <v>-38.2</v>
+        <v>-36.2</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O5" s="10">
+        <v>163</v>
+      </c>
+      <c r="O5" s="6">
         <v>4</v>
       </c>
       <c r="P5" s="8">
@@ -1426,7 +1441,7 @@
       <c r="Q5" s="8">
         <v>0</v>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="7">
         <v>3</v>
       </c>
     </row>
@@ -1435,13 +1450,13 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>61</v>
@@ -1459,22 +1474,22 @@
         <v>136</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>159</v>
+        <v>61</v>
       </c>
       <c r="L6" s="4">
-        <v>-32.2</v>
+        <v>-34.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O6" s="10">
-        <v>4</v>
+        <v>163</v>
+      </c>
+      <c r="O6" s="9">
+        <v>100</v>
       </c>
       <c r="P6" s="8">
         <v>0</v>
@@ -1482,8 +1497,8 @@
       <c r="Q6" s="8">
         <v>0</v>
       </c>
-      <c r="R6" s="11">
-        <v>3</v>
+      <c r="R6" s="10">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1491,13 +1506,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>62</v>
@@ -1521,16 +1536,16 @@
         <v>62</v>
       </c>
       <c r="L7" s="4">
-        <v>-37.5</v>
+        <v>-38.2</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O7" s="6">
-        <v>55</v>
+        <v>163</v>
+      </c>
+      <c r="O7" s="9">
+        <v>60</v>
       </c>
       <c r="P7" s="8">
         <v>0</v>
@@ -1538,8 +1553,8 @@
       <c r="Q7" s="8">
         <v>0</v>
       </c>
-      <c r="R7" s="12">
-        <v>55</v>
+      <c r="R7" s="11">
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1547,13 +1562,13 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>63</v>
@@ -1571,31 +1586,31 @@
         <v>138</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="L8" s="4">
-        <v>-36.2</v>
+        <v>-29.6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O8" s="6">
-        <v>60</v>
-      </c>
-      <c r="P8" s="8">
-        <v>0</v>
+        <v>163</v>
+      </c>
+      <c r="O8" s="9">
+        <v>54</v>
+      </c>
+      <c r="P8" s="12">
+        <v>42</v>
       </c>
       <c r="Q8" s="8">
         <v>0</v>
       </c>
-      <c r="R8" s="13">
-        <v>60</v>
+      <c r="R8" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1603,13 +1618,13 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>64</v>
@@ -1633,25 +1648,25 @@
         <v>64</v>
       </c>
       <c r="L9" s="4">
-        <v>-34.5</v>
+        <v>-37.7</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O9" s="6">
-        <v>70</v>
-      </c>
-      <c r="P9" s="8">
-        <v>0</v>
+        <v>163</v>
+      </c>
+      <c r="O9" s="9">
+        <v>34</v>
+      </c>
+      <c r="P9" s="13">
+        <v>19</v>
       </c>
       <c r="Q9" s="8">
         <v>0</v>
       </c>
-      <c r="R9" s="13">
-        <v>60</v>
+      <c r="R9" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1659,13 +1674,13 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>65</v>
@@ -1674,7 +1689,7 @@
         <v>84</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>121</v>
@@ -1689,25 +1704,25 @@
         <v>65</v>
       </c>
       <c r="L10" s="4">
-        <v>-38.2</v>
+        <v>-23.2</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O10" s="6">
-        <v>68</v>
-      </c>
-      <c r="P10" s="8">
-        <v>0</v>
+        <v>164</v>
+      </c>
+      <c r="O10" s="14">
+        <v>36</v>
+      </c>
+      <c r="P10" s="15">
+        <v>25</v>
       </c>
       <c r="Q10" s="8">
         <v>0</v>
       </c>
-      <c r="R10" s="14">
-        <v>63</v>
+      <c r="R10" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1715,13 +1730,13 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>66</v>
@@ -1730,7 +1745,7 @@
         <v>85</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>122</v>
@@ -1745,19 +1760,19 @@
         <v>66</v>
       </c>
       <c r="L11" s="4">
-        <v>-29.6</v>
+        <v>-35</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O11" s="6">
-        <v>65</v>
-      </c>
-      <c r="P11" s="13">
-        <v>61</v>
+        <v>163</v>
+      </c>
+      <c r="O11" s="14">
+        <v>18</v>
+      </c>
+      <c r="P11" s="16">
+        <v>12</v>
       </c>
       <c r="Q11" s="8">
         <v>0</v>
@@ -1771,13 +1786,13 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>67</v>
@@ -1786,7 +1801,7 @@
         <v>86</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>123</v>
@@ -1795,25 +1810,25 @@
         <v>142</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>67</v>
+        <v>159</v>
       </c>
       <c r="L12" s="4">
-        <v>-37.7</v>
+        <v>-38.1</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O12" s="6">
-        <v>50</v>
-      </c>
-      <c r="P12" s="15">
-        <v>47</v>
+        <v>0</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0</v>
       </c>
       <c r="Q12" s="8">
         <v>0</v>
@@ -1827,13 +1842,13 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>68</v>
@@ -1842,7 +1857,7 @@
         <v>87</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>124</v>
@@ -1857,19 +1872,19 @@
         <v>68</v>
       </c>
       <c r="L13" s="4">
-        <v>-23.2</v>
+        <v>-30.3</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O13" s="10">
-        <v>13</v>
-      </c>
-      <c r="P13" s="16">
+        <v>163</v>
+      </c>
+      <c r="O13" s="6">
         <v>9</v>
+      </c>
+      <c r="P13" s="7">
+        <v>7</v>
       </c>
       <c r="Q13" s="8">
         <v>0</v>
@@ -1883,13 +1898,13 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>69</v>
@@ -1913,25 +1928,25 @@
         <v>69</v>
       </c>
       <c r="L14" s="4">
-        <v>-35</v>
+        <v>-37.9</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O14" s="10">
-        <v>7</v>
-      </c>
-      <c r="P14" s="11">
-        <v>4</v>
+        <v>164</v>
+      </c>
+      <c r="O14" s="6">
+        <v>0</v>
+      </c>
+      <c r="P14" s="8">
+        <v>0</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
       </c>
       <c r="R14" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1939,13 +1954,13 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>70</v>
@@ -1963,22 +1978,22 @@
         <v>145</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="L15" s="4">
-        <v>-38.1</v>
+        <v>-7.1</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>162</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O15" s="10">
-        <v>3</v>
+        <v>165</v>
+      </c>
+      <c r="O15" s="6">
+        <v>2</v>
       </c>
       <c r="P15" s="8">
         <v>0</v>
@@ -1986,8 +2001,8 @@
       <c r="Q15" s="8">
         <v>0</v>
       </c>
-      <c r="R15" s="11">
-        <v>3</v>
+      <c r="R15" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1995,13 +2010,13 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>71</v>
@@ -2025,25 +2040,25 @@
         <v>71</v>
       </c>
       <c r="L16" s="4">
-        <v>-30.3</v>
+        <v>-24</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O16" s="17">
-        <v>15</v>
-      </c>
-      <c r="P16" s="16">
-        <v>8</v>
+        <v>163</v>
+      </c>
+      <c r="O16" s="9">
+        <v>79</v>
+      </c>
+      <c r="P16" s="8">
+        <v>1</v>
       </c>
       <c r="Q16" s="8">
         <v>0</v>
       </c>
-      <c r="R16" s="8">
-        <v>0</v>
+      <c r="R16" s="17">
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2051,13 +2066,13 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>72</v>
@@ -2081,25 +2096,25 @@
         <v>72</v>
       </c>
       <c r="L17" s="4">
-        <v>-37.9</v>
+        <v>-35.4</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O17" s="10">
-        <v>0</v>
+        <v>163</v>
+      </c>
+      <c r="O17" s="9">
+        <v>84</v>
       </c>
       <c r="P17" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="8">
         <v>0</v>
       </c>
-      <c r="R17" s="8">
-        <v>0</v>
+      <c r="R17" s="18">
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2107,13 +2122,13 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>73</v>
@@ -2131,31 +2146,31 @@
         <v>148</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L18" s="4">
-        <v>-7.1</v>
+        <v>-15.5</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="O18" s="17">
+        <v>165</v>
+      </c>
+      <c r="O18" s="9">
+        <v>81</v>
+      </c>
+      <c r="P18" s="16">
         <v>12</v>
       </c>
-      <c r="P18" s="11">
-        <v>4</v>
-      </c>
       <c r="Q18" s="8">
         <v>0</v>
       </c>
-      <c r="R18" s="11">
-        <v>6</v>
+      <c r="R18" s="19">
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2163,13 +2178,13 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>74</v>
@@ -2187,31 +2202,31 @@
         <v>149</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="L19" s="4">
-        <v>-24</v>
+        <v>-16.5</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O19" s="17">
-        <v>24</v>
-      </c>
-      <c r="P19" s="8">
-        <v>0</v>
+        <v>163</v>
+      </c>
+      <c r="O19" s="14">
+        <v>39</v>
+      </c>
+      <c r="P19" s="20">
+        <v>36</v>
       </c>
       <c r="Q19" s="8">
         <v>0</v>
       </c>
-      <c r="R19" s="18">
-        <v>14</v>
+      <c r="R19" s="7">
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2219,13 +2234,13 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>75</v>
@@ -2249,25 +2264,25 @@
         <v>75</v>
       </c>
       <c r="L20" s="4">
-        <v>-35.4</v>
+        <v>-30.9</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O20" s="10">
-        <v>15</v>
-      </c>
-      <c r="P20" s="8">
-        <v>0</v>
+        <v>163</v>
+      </c>
+      <c r="O20" s="14">
+        <v>21</v>
+      </c>
+      <c r="P20" s="13">
+        <v>18</v>
       </c>
       <c r="Q20" s="8">
         <v>0</v>
       </c>
-      <c r="R20" s="16">
-        <v>9</v>
+      <c r="R20" s="8">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="176">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260621--01</t>
-  </si>
-  <si>
-    <t>20260621--02</t>
-  </si>
-  <si>
     <t>20260622--01</t>
   </si>
   <si>
@@ -127,10 +121,13 @@
     <t>20260627--03</t>
   </si>
   <si>
-    <t>06:44</t>
-  </si>
-  <si>
-    <t>03:40</t>
+    <t>20260628--01</t>
+  </si>
+  <si>
+    <t>20260628--02</t>
+  </si>
+  <si>
+    <t>20260628--03</t>
   </si>
   <si>
     <t>06:29</t>
@@ -184,13 +181,16 @@
     <t>05:51</t>
   </si>
   <si>
+    <t>02:37</t>
+  </si>
+  <si>
+    <t>04:14</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:10:56</t>
-  </si>
-  <si>
-    <t>02:49:29</t>
+    <t>02:01</t>
   </si>
   <si>
     <t>00:25:15</t>
@@ -244,10 +244,13 @@
     <t>23:04:28</t>
   </si>
   <si>
-    <t>01:13:02</t>
-  </si>
-  <si>
-    <t>02:52:24</t>
+    <t>04:01:10</t>
+  </si>
+  <si>
+    <t>20:41:24</t>
+  </si>
+  <si>
+    <t>22:18:05</t>
   </si>
   <si>
     <t>00:27:24</t>
@@ -301,10 +304,13 @@
     <t>23:06:46</t>
   </si>
   <si>
-    <t>01:16:23</t>
-  </si>
-  <si>
-    <t>02:54:13</t>
+    <t>04:04:27</t>
+  </si>
+  <si>
+    <t>20:44:05</t>
+  </si>
+  <si>
+    <t>22:20:15</t>
   </si>
   <si>
     <t>00:30:38</t>
@@ -355,10 +361,13 @@
     <t>23:09:41</t>
   </si>
   <si>
-    <t>01:19:46</t>
-  </si>
-  <si>
-    <t>02:56:04</t>
+    <t>04:05:46</t>
+  </si>
+  <si>
+    <t>20:46:12</t>
+  </si>
+  <si>
+    <t>22:23:27</t>
   </si>
   <si>
     <t>00:33:53</t>
@@ -412,10 +421,13 @@
     <t>23:12:37</t>
   </si>
   <si>
-    <t>01:21:53</t>
-  </si>
-  <si>
-    <t>02:59:00</t>
+    <t>04:07:04</t>
+  </si>
+  <si>
+    <t>20:48:19</t>
+  </si>
+  <si>
+    <t>22:26:40</t>
   </si>
   <si>
     <t>00:36:03</t>
@@ -469,12 +481,18 @@
     <t>23:14:57</t>
   </si>
   <si>
+    <t>04:10:21</t>
+  </si>
+  <si>
+    <t>20:51:01</t>
+  </si>
+  <si>
+    <t>22:28:51</t>
+  </si>
+  <si>
     <t>0°</t>
   </si>
   <si>
-    <t>10°</t>
-  </si>
-  <si>
     <t>5°</t>
   </si>
   <si>
@@ -487,7 +505,10 @@
     <t>6°</t>
   </si>
   <si>
-    <t>02:56:07</t>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>29°</t>
   </si>
   <si>
     <t>02:12:01</t>
@@ -499,10 +520,19 @@
     <t>21:28:42</t>
   </si>
   <si>
+    <t>20:48:55</t>
+  </si>
+  <si>
+    <t>22:22:16</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
     <t>A+B</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
   <si>
     <t>3</t>
@@ -545,7 +575,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -566,12 +596,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -584,19 +608,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -608,43 +644,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -685,7 +697,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -736,15 +748,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1148,7 +1151,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1226,55 +1229,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L2" s="4">
-        <v>-38.2</v>
+        <v>-37.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="O2" s="6">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="P2" s="7">
-        <v>3</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1282,55 +1285,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="L3" s="4">
-        <v>-32.2</v>
+        <v>-36.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="O3" s="6">
-        <v>17</v>
-      </c>
-      <c r="P3" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>0</v>
-      </c>
-      <c r="R3" s="8">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1338,55 +1341,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L4" s="4">
-        <v>-37.5</v>
+        <v>-34.5</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O4" s="6">
-        <v>5</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="7">
-        <v>3</v>
+        <v>173</v>
+      </c>
+      <c r="O4" s="8">
+        <v>70</v>
+      </c>
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>0</v>
+      </c>
+      <c r="R4" s="9">
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1394,55 +1397,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="L5" s="4">
-        <v>-36.2</v>
+        <v>-38.2</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O5" s="6">
-        <v>4</v>
-      </c>
-      <c r="P5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>0</v>
-      </c>
-      <c r="R5" s="7">
-        <v>3</v>
+        <v>173</v>
+      </c>
+      <c r="O5" s="8">
+        <v>72</v>
+      </c>
+      <c r="P5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>0</v>
+      </c>
+      <c r="R5" s="10">
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1450,55 +1453,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>17</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-29.6</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="O6" s="11">
         <v>27</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-34.5</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O6" s="9">
-        <v>100</v>
-      </c>
-      <c r="P6" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>0</v>
-      </c>
-      <c r="R6" s="10">
-        <v>100</v>
+      <c r="P6" s="12">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>0</v>
+      </c>
+      <c r="R6" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1506,55 +1509,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L7" s="4">
-        <v>-38.2</v>
+        <v>-37.7</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O7" s="9">
-        <v>60</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>0</v>
-      </c>
-      <c r="R7" s="11">
-        <v>60</v>
+        <v>173</v>
+      </c>
+      <c r="O7" s="11">
+        <v>24</v>
+      </c>
+      <c r="P7" s="12">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1562,55 +1565,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L8" s="4">
-        <v>-29.6</v>
+        <v>-23.2</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O8" s="9">
-        <v>54</v>
+        <v>174</v>
+      </c>
+      <c r="O8" s="11">
+        <v>14</v>
       </c>
       <c r="P8" s="12">
-        <v>42</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>0</v>
-      </c>
-      <c r="R8" s="8">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="12">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1618,55 +1621,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L9" s="4">
-        <v>-37.7</v>
+        <v>-35</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O9" s="9">
-        <v>34</v>
-      </c>
-      <c r="P9" s="13">
-        <v>19</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8">
-        <v>0</v>
+        <v>173</v>
+      </c>
+      <c r="O9" s="6">
+        <v>4</v>
+      </c>
+      <c r="P9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="12">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1674,55 +1677,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>65</v>
+        <v>166</v>
       </c>
       <c r="L10" s="4">
-        <v>-23.2</v>
+        <v>-38.1</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O10" s="14">
-        <v>36</v>
-      </c>
-      <c r="P10" s="15">
-        <v>25</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>0</v>
-      </c>
-      <c r="R10" s="8">
-        <v>0</v>
+        <v>174</v>
+      </c>
+      <c r="O10" s="6">
+        <v>6</v>
+      </c>
+      <c r="P10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>0</v>
+      </c>
+      <c r="R10" s="12">
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1730,54 +1733,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L11" s="4">
-        <v>-35</v>
+        <v>-30.3</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O11" s="14">
-        <v>18</v>
-      </c>
-      <c r="P11" s="16">
-        <v>12</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>0</v>
-      </c>
-      <c r="R11" s="8">
+        <v>173</v>
+      </c>
+      <c r="O11" s="6">
+        <v>0</v>
+      </c>
+      <c r="P11" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>0</v>
+      </c>
+      <c r="R11" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1786,54 +1789,54 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>159</v>
+        <v>69</v>
       </c>
       <c r="L12" s="4">
-        <v>-38.1</v>
+        <v>-37.9</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="O12" s="6">
         <v>0</v>
       </c>
-      <c r="P12" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>0</v>
-      </c>
-      <c r="R12" s="8">
+      <c r="P12" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>0</v>
+      </c>
+      <c r="R12" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1842,54 +1845,54 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>68</v>
+        <v>161</v>
       </c>
       <c r="L13" s="4">
-        <v>-30.3</v>
+        <v>-7.1</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="O13" s="6">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P13" s="7">
-        <v>7</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>0</v>
-      </c>
-      <c r="R13" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>0</v>
+      </c>
+      <c r="R13" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1898,55 +1901,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
+        <v>43</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L14" s="4">
+        <v>-24</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="O14" s="11">
         <v>14</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="L14" s="4">
-        <v>-37.9</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O14" s="6">
-        <v>0</v>
-      </c>
-      <c r="P14" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>0</v>
-      </c>
-      <c r="R14" s="8">
-        <v>0</v>
+      <c r="P14" s="13">
+        <v>14</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>0</v>
+      </c>
+      <c r="R14" s="12">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1954,55 +1957,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="L15" s="4">
-        <v>-7.1</v>
+        <v>-35.4</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O15" s="6">
-        <v>2</v>
-      </c>
-      <c r="P15" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>0</v>
-      </c>
-      <c r="R15" s="8">
-        <v>1</v>
+        <v>173</v>
+      </c>
+      <c r="O15" s="11">
+        <v>19</v>
+      </c>
+      <c r="P15" s="14">
+        <v>19</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>0</v>
+      </c>
+      <c r="R15" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2010,55 +2013,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>71</v>
+        <v>161</v>
       </c>
       <c r="L16" s="4">
-        <v>-24</v>
+        <v>-15.5</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O16" s="9">
-        <v>79</v>
-      </c>
-      <c r="P16" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>0</v>
-      </c>
-      <c r="R16" s="17">
-        <v>79</v>
+        <v>175</v>
+      </c>
+      <c r="O16" s="8">
+        <v>48</v>
+      </c>
+      <c r="P16" s="13">
+        <v>13</v>
+      </c>
+      <c r="Q16" s="7">
+        <v>0</v>
+      </c>
+      <c r="R16" s="15">
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2066,55 +2069,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
       <c r="L17" s="4">
-        <v>-35.4</v>
+        <v>-16.5</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O17" s="9">
-        <v>84</v>
-      </c>
-      <c r="P17" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>0</v>
-      </c>
-      <c r="R17" s="18">
-        <v>84</v>
+        <v>173</v>
+      </c>
+      <c r="O17" s="8">
+        <v>54</v>
+      </c>
+      <c r="P17" s="15">
+        <v>28</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>0</v>
+      </c>
+      <c r="R17" s="16">
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2122,55 +2125,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L18" s="4">
+        <v>-30.9</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="O18" s="8">
         <v>56</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="L18" s="4">
-        <v>-15.5</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O18" s="9">
-        <v>81</v>
-      </c>
-      <c r="P18" s="16">
-        <v>12</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>0</v>
-      </c>
-      <c r="R18" s="19">
-        <v>56</v>
+      <c r="P18" s="14">
+        <v>19</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>0</v>
+      </c>
+      <c r="R18" s="17">
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2178,55 +2181,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="L19" s="4">
+        <v>-23.2</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="O19" s="8">
         <v>56</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="L19" s="4">
-        <v>-16.5</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O19" s="14">
-        <v>39</v>
-      </c>
-      <c r="P19" s="20">
-        <v>36</v>
-      </c>
-      <c r="Q19" s="8">
-        <v>0</v>
-      </c>
-      <c r="R19" s="7">
-        <v>3</v>
+      <c r="P19" s="14">
+        <v>19</v>
+      </c>
+      <c r="Q19" s="7">
+        <v>0</v>
+      </c>
+      <c r="R19" s="14">
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2234,114 +2237,170 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>75</v>
+        <v>168</v>
       </c>
       <c r="L20" s="4">
-        <v>-30.9</v>
+        <v>-8.4</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O20" s="14">
-        <v>21</v>
-      </c>
-      <c r="P20" s="13">
-        <v>18</v>
-      </c>
-      <c r="Q20" s="8">
-        <v>0</v>
-      </c>
-      <c r="R20" s="8">
-        <v>2</v>
+        <v>175</v>
+      </c>
+      <c r="O20" s="8">
+        <v>43</v>
+      </c>
+      <c r="P20" s="17">
+        <v>39</v>
+      </c>
+      <c r="Q20" s="7">
+        <v>0</v>
+      </c>
+      <c r="R20" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="2">
+        <v>41</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="L21" s="4">
+        <v>-24.7</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="O21" s="11">
+        <v>35</v>
+      </c>
+      <c r="P21" s="16">
+        <v>35</v>
+      </c>
+      <c r="Q21" s="7">
+        <v>0</v>
+      </c>
+      <c r="R21" s="7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A20">
+  <conditionalFormatting sqref="A2:A21">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B20">
+  <conditionalFormatting sqref="B2:B21">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C20">
+  <conditionalFormatting sqref="C2:C21">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D20">
+  <conditionalFormatting sqref="D2:D21">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E20">
+  <conditionalFormatting sqref="E2:E21">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F20">
+  <conditionalFormatting sqref="F2:F21">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G20">
+  <conditionalFormatting sqref="G2:G21">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H20">
+  <conditionalFormatting sqref="H2:H21">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I20">
+  <conditionalFormatting sqref="I2:I21">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J20">
+  <conditionalFormatting sqref="J2:J21">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K20">
+  <conditionalFormatting sqref="K2:K21">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L20">
+  <conditionalFormatting sqref="L2:L21">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2360,12 +2419,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M20">
+  <conditionalFormatting sqref="M2:M21">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N20">
+  <conditionalFormatting sqref="N2:N21">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2382,22 +2441,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O20">
+  <conditionalFormatting sqref="O2:O21">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P20">
+  <conditionalFormatting sqref="P2:P21">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q20">
+  <conditionalFormatting sqref="Q2:Q21">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R20">
+  <conditionalFormatting sqref="R2:R21">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="180">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260622--01</t>
-  </si>
-  <si>
-    <t>20260622--02</t>
-  </si>
-  <si>
-    <t>20260622--03</t>
-  </si>
-  <si>
     <t>20260623--01</t>
   </si>
   <si>
@@ -130,16 +121,16 @@
     <t>20260628--03</t>
   </si>
   <si>
-    <t>06:29</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>05:50</t>
-  </si>
-  <si>
-    <t>05:46</t>
+    <t>20260629--01</t>
+  </si>
+  <si>
+    <t>20260629--02</t>
+  </si>
+  <si>
+    <t>20260629--03</t>
+  </si>
+  <si>
+    <t>05:47</t>
   </si>
   <si>
     <t>04:32</t>
@@ -148,354 +139,363 @@
     <t>06:21</t>
   </si>
   <si>
-    <t>00:26</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>01:42</t>
+    <t>00:27</t>
+  </si>
+  <si>
+    <t>06:41</t>
+  </si>
+  <si>
+    <t>01:41</t>
   </si>
   <si>
     <t>06:43</t>
   </si>
   <si>
-    <t>03:48</t>
-  </si>
-  <si>
-    <t>05:23</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>05:01</t>
-  </si>
-  <si>
-    <t>04:18</t>
-  </si>
-  <si>
-    <t>05:41</t>
+    <t>03:47</t>
+  </si>
+  <si>
+    <t>05:24</t>
+  </si>
+  <si>
+    <t>06:26</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>04:19</t>
+  </si>
+  <si>
+    <t>05:42</t>
   </si>
   <si>
     <t>05:51</t>
   </si>
   <si>
-    <t>02:37</t>
-  </si>
-  <si>
-    <t>04:14</t>
+    <t>02:39</t>
+  </si>
+  <si>
+    <t>04:15</t>
+  </si>
+  <si>
+    <t>06:24</t>
+  </si>
+  <si>
+    <t>06:32</t>
+  </si>
+  <si>
+    <t>06:42</t>
+  </si>
+  <si>
+    <t>02:05</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:01</t>
-  </si>
-  <si>
-    <t>00:25:15</t>
-  </si>
-  <si>
-    <t>02:03:16</t>
-  </si>
-  <si>
-    <t>23:39:40</t>
-  </si>
-  <si>
-    <t>01:17:06</t>
-  </si>
-  <si>
-    <t>22:54:11</t>
-  </si>
-  <si>
-    <t>00:30:59</t>
-  </si>
-  <si>
-    <t>22:08:52</t>
-  </si>
-  <si>
-    <t>23:44:54</t>
-  </si>
-  <si>
-    <t>01:23:52</t>
-  </si>
-  <si>
-    <t>22:58:54</t>
-  </si>
-  <si>
-    <t>00:37:22</t>
-  </si>
-  <si>
-    <t>05:33:08</t>
-  </si>
-  <si>
-    <t>22:12:58</t>
-  </si>
-  <si>
-    <t>23:50:54</t>
-  </si>
-  <si>
-    <t>04:47:11</t>
-  </si>
-  <si>
-    <t>21:27:07</t>
+    <t>01:59</t>
+  </si>
+  <si>
+    <t>01:18</t>
+  </si>
+  <si>
+    <t>01:17:08</t>
+  </si>
+  <si>
+    <t>22:54:14</t>
+  </si>
+  <si>
+    <t>00:31:02</t>
+  </si>
+  <si>
+    <t>22:08:57</t>
+  </si>
+  <si>
+    <t>23:44:59</t>
+  </si>
+  <si>
+    <t>01:23:57</t>
+  </si>
+  <si>
+    <t>22:59:01</t>
+  </si>
+  <si>
+    <t>00:37:30</t>
+  </si>
+  <si>
+    <t>05:33:16</t>
+  </si>
+  <si>
+    <t>22:13:08</t>
+  </si>
+  <si>
+    <t>23:51:05</t>
+  </si>
+  <si>
+    <t>04:47:22</t>
+  </si>
+  <si>
+    <t>21:27:21</t>
+  </si>
+  <si>
+    <t>23:04:42</t>
+  </si>
+  <si>
+    <t>04:01:25</t>
+  </si>
+  <si>
+    <t>20:41:42</t>
+  </si>
+  <si>
+    <t>22:18:23</t>
+  </si>
+  <si>
+    <t>04:52:21</t>
+  </si>
+  <si>
+    <t>21:32:08</t>
+  </si>
+  <si>
+    <t>23:11:01</t>
+  </si>
+  <si>
+    <t>01:19:27</t>
+  </si>
+  <si>
+    <t>22:56:50</t>
+  </si>
+  <si>
+    <t>00:33:13</t>
+  </si>
+  <si>
+    <t>22:13:18</t>
+  </si>
+  <si>
+    <t>23:47:06</t>
+  </si>
+  <si>
+    <t>01:27:35</t>
+  </si>
+  <si>
+    <t>23:01:07</t>
+  </si>
+  <si>
+    <t>00:40:22</t>
+  </si>
+  <si>
+    <t>05:35:43</t>
+  </si>
+  <si>
+    <t>22:15:17</t>
+  </si>
+  <si>
+    <t>23:53:36</t>
+  </si>
+  <si>
+    <t>04:50:06</t>
+  </si>
+  <si>
+    <t>21:29:40</t>
+  </si>
+  <si>
+    <t>23:07:01</t>
+  </si>
+  <si>
+    <t>04:04:41</t>
+  </si>
+  <si>
+    <t>20:44:23</t>
+  </si>
+  <si>
+    <t>22:20:34</t>
+  </si>
+  <si>
+    <t>04:54:31</t>
+  </si>
+  <si>
+    <t>21:34:14</t>
+  </si>
+  <si>
+    <t>23:14:29</t>
+  </si>
+  <si>
+    <t>01:22:20</t>
+  </si>
+  <si>
+    <t>22:59:06</t>
+  </si>
+  <si>
+    <t>00:36:23</t>
+  </si>
+  <si>
+    <t>23:50:26</t>
+  </si>
+  <si>
+    <t>01:28:25</t>
   </si>
   <si>
     <t>23:04:28</t>
   </si>
   <si>
-    <t>04:01:10</t>
-  </si>
-  <si>
-    <t>20:41:24</t>
-  </si>
-  <si>
-    <t>22:18:05</t>
-  </si>
-  <si>
-    <t>00:27:24</t>
-  </si>
-  <si>
-    <t>02:05:49</t>
-  </si>
-  <si>
-    <t>23:41:56</t>
-  </si>
-  <si>
-    <t>01:19:26</t>
-  </si>
-  <si>
-    <t>22:56:47</t>
-  </si>
-  <si>
-    <t>00:33:10</t>
-  </si>
-  <si>
-    <t>22:13:13</t>
-  </si>
-  <si>
-    <t>23:47:01</t>
-  </si>
-  <si>
-    <t>01:27:29</t>
-  </si>
-  <si>
-    <t>23:00:59</t>
-  </si>
-  <si>
-    <t>00:40:14</t>
-  </si>
-  <si>
-    <t>05:35:35</t>
-  </si>
-  <si>
-    <t>22:15:07</t>
-  </si>
-  <si>
-    <t>23:53:25</t>
-  </si>
-  <si>
-    <t>04:49:55</t>
-  </si>
-  <si>
-    <t>21:29:26</t>
-  </si>
-  <si>
-    <t>23:06:46</t>
-  </si>
-  <si>
-    <t>04:04:27</t>
-  </si>
-  <si>
-    <t>20:44:05</t>
-  </si>
-  <si>
-    <t>22:20:15</t>
-  </si>
-  <si>
-    <t>00:30:38</t>
-  </si>
-  <si>
-    <t>02:08:16</t>
-  </si>
-  <si>
-    <t>23:44:51</t>
-  </si>
-  <si>
-    <t>01:22:18</t>
-  </si>
-  <si>
-    <t>22:59:03</t>
-  </si>
-  <si>
-    <t>00:36:20</t>
-  </si>
-  <si>
-    <t>23:50:21</t>
-  </si>
-  <si>
-    <t>01:28:20</t>
-  </si>
-  <si>
-    <t>23:04:20</t>
-  </si>
-  <si>
-    <t>00:42:08</t>
-  </si>
-  <si>
-    <t>05:38:17</t>
-  </si>
-  <si>
-    <t>22:18:19</t>
-  </si>
-  <si>
-    <t>23:55:55</t>
-  </si>
-  <si>
-    <t>04:52:04</t>
-  </si>
-  <si>
-    <t>21:32:16</t>
-  </si>
-  <si>
-    <t>23:09:41</t>
-  </si>
-  <si>
-    <t>04:05:46</t>
-  </si>
-  <si>
-    <t>20:46:12</t>
-  </si>
-  <si>
-    <t>22:23:27</t>
-  </si>
-  <si>
-    <t>00:33:53</t>
-  </si>
-  <si>
-    <t>02:10:44</t>
-  </si>
-  <si>
-    <t>23:47:46</t>
-  </si>
-  <si>
-    <t>01:25:12</t>
-  </si>
-  <si>
-    <t>23:01:19</t>
-  </si>
-  <si>
-    <t>00:39:31</t>
-  </si>
-  <si>
-    <t>22:13:39</t>
-  </si>
-  <si>
-    <t>23:53:41</t>
-  </si>
-  <si>
-    <t>01:29:11</t>
-  </si>
-  <si>
-    <t>23:07:42</t>
-  </si>
-  <si>
-    <t>00:44:02</t>
-  </si>
-  <si>
-    <t>05:40:58</t>
-  </si>
-  <si>
-    <t>22:21:32</t>
-  </si>
-  <si>
-    <t>23:58:26</t>
-  </si>
-  <si>
-    <t>04:54:13</t>
-  </si>
-  <si>
-    <t>21:35:07</t>
-  </si>
-  <si>
-    <t>23:12:37</t>
-  </si>
-  <si>
-    <t>04:07:04</t>
-  </si>
-  <si>
-    <t>20:48:19</t>
-  </si>
-  <si>
-    <t>22:26:40</t>
-  </si>
-  <si>
-    <t>00:36:03</t>
-  </si>
-  <si>
-    <t>02:13:18</t>
-  </si>
-  <si>
-    <t>23:50:04</t>
-  </si>
-  <si>
-    <t>01:27:33</t>
-  </si>
-  <si>
-    <t>23:03:55</t>
-  </si>
-  <si>
-    <t>00:41:44</t>
-  </si>
-  <si>
-    <t>22:17:33</t>
-  </si>
-  <si>
-    <t>23:55:49</t>
-  </si>
-  <si>
-    <t>01:32:49</t>
-  </si>
-  <si>
-    <t>23:09:49</t>
-  </si>
-  <si>
-    <t>00:46:55</t>
-  </si>
-  <si>
-    <t>05:43:25</t>
-  </si>
-  <si>
-    <t>22:23:42</t>
-  </si>
-  <si>
-    <t>00:00:58</t>
-  </si>
-  <si>
-    <t>04:56:57</t>
-  </si>
-  <si>
-    <t>21:37:27</t>
-  </si>
-  <si>
-    <t>23:14:57</t>
-  </si>
-  <si>
-    <t>04:10:21</t>
-  </si>
-  <si>
-    <t>20:51:01</t>
-  </si>
-  <si>
-    <t>22:28:51</t>
+    <t>00:42:16</t>
+  </si>
+  <si>
+    <t>05:38:25</t>
+  </si>
+  <si>
+    <t>22:18:30</t>
+  </si>
+  <si>
+    <t>23:56:05</t>
+  </si>
+  <si>
+    <t>04:52:15</t>
+  </si>
+  <si>
+    <t>21:32:30</t>
+  </si>
+  <si>
+    <t>23:09:55</t>
+  </si>
+  <si>
+    <t>04:06:01</t>
+  </si>
+  <si>
+    <t>20:46:30</t>
+  </si>
+  <si>
+    <t>22:23:46</t>
+  </si>
+  <si>
+    <t>04:57:47</t>
+  </si>
+  <si>
+    <t>21:37:35</t>
+  </si>
+  <si>
+    <t>23:15:31</t>
+  </si>
+  <si>
+    <t>01:25:14</t>
+  </si>
+  <si>
+    <t>23:01:22</t>
+  </si>
+  <si>
+    <t>00:39:34</t>
+  </si>
+  <si>
+    <t>22:13:45</t>
+  </si>
+  <si>
+    <t>23:53:47</t>
+  </si>
+  <si>
+    <t>01:29:16</t>
+  </si>
+  <si>
+    <t>23:07:50</t>
+  </si>
+  <si>
+    <t>00:44:09</t>
+  </si>
+  <si>
+    <t>05:41:07</t>
+  </si>
+  <si>
+    <t>22:21:43</t>
+  </si>
+  <si>
+    <t>23:58:36</t>
+  </si>
+  <si>
+    <t>04:54:25</t>
+  </si>
+  <si>
+    <t>21:35:22</t>
+  </si>
+  <si>
+    <t>23:12:52</t>
+  </si>
+  <si>
+    <t>04:07:20</t>
+  </si>
+  <si>
+    <t>20:48:38</t>
+  </si>
+  <si>
+    <t>22:26:58</t>
+  </si>
+  <si>
+    <t>05:01:03</t>
+  </si>
+  <si>
+    <t>21:40:56</t>
+  </si>
+  <si>
+    <t>23:16:34</t>
+  </si>
+  <si>
+    <t>23:03:58</t>
+  </si>
+  <si>
+    <t>00:41:47</t>
+  </si>
+  <si>
+    <t>22:17:38</t>
+  </si>
+  <si>
+    <t>23:55:54</t>
+  </si>
+  <si>
+    <t>01:32:55</t>
+  </si>
+  <si>
+    <t>23:09:57</t>
+  </si>
+  <si>
+    <t>00:47:03</t>
+  </si>
+  <si>
+    <t>05:43:34</t>
+  </si>
+  <si>
+    <t>22:23:53</t>
+  </si>
+  <si>
+    <t>00:01:08</t>
+  </si>
+  <si>
+    <t>04:57:09</t>
+  </si>
+  <si>
+    <t>21:37:41</t>
+  </si>
+  <si>
+    <t>23:15:11</t>
+  </si>
+  <si>
+    <t>04:10:37</t>
+  </si>
+  <si>
+    <t>20:51:19</t>
+  </si>
+  <si>
+    <t>22:29:09</t>
+  </si>
+  <si>
+    <t>05:03:13</t>
+  </si>
+  <si>
+    <t>21:43:03</t>
+  </si>
+  <si>
+    <t>23:20:03</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>5°</t>
-  </si>
-  <si>
     <t>1°</t>
   </si>
   <si>
@@ -511,19 +511,28 @@
     <t>29°</t>
   </si>
   <si>
-    <t>02:12:01</t>
-  </si>
-  <si>
-    <t>01:32:28</t>
-  </si>
-  <si>
-    <t>21:28:42</t>
-  </si>
-  <si>
-    <t>20:48:55</t>
-  </si>
-  <si>
-    <t>22:22:16</t>
+    <t>2°</t>
+  </si>
+  <si>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>01:32:33</t>
+  </si>
+  <si>
+    <t>21:28:55</t>
+  </si>
+  <si>
+    <t>20:49:12</t>
+  </si>
+  <si>
+    <t>22:22:33</t>
+  </si>
+  <si>
+    <t>21:42:30</t>
+  </si>
+  <si>
+    <t>23:15:47</t>
   </si>
   <si>
     <t>B</t>
@@ -542,6 +551,9 @@
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
@@ -590,7 +602,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -602,7 +620,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -614,49 +668,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1229,55 +1241,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>138</v>
+        <v>86</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L2" s="4">
-        <v>-37.5</v>
+        <v>-38.2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="O2" s="6">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="7">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>0</v>
+      </c>
+      <c r="R2" s="9">
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1285,54 +1297,54 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>159</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>165</v>
+        <v>62</v>
       </c>
       <c r="L3" s="4">
-        <v>-36.2</v>
+        <v>-29.6</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="O3" s="6">
-        <v>0</v>
-      </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="7">
+        <v>176</v>
+      </c>
+      <c r="O3" s="10">
+        <v>36</v>
+      </c>
+      <c r="P3" s="11">
+        <v>33</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>0</v>
+      </c>
+      <c r="R3" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1341,55 +1353,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L4" s="4">
-        <v>-34.5</v>
+        <v>-37.7</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="O4" s="8">
-        <v>70</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>0</v>
-      </c>
-      <c r="R4" s="9">
-        <v>60</v>
+        <v>176</v>
+      </c>
+      <c r="O4" s="12">
+        <v>4</v>
+      </c>
+      <c r="P4" s="13">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1397,55 +1409,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L5" s="4">
-        <v>-38.2</v>
+        <v>-23.2</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="O5" s="8">
-        <v>72</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="10">
-        <v>68</v>
+        <v>177</v>
+      </c>
+      <c r="O5" s="12">
+        <v>0</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="R5" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1453,55 +1465,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L6" s="4">
-        <v>-29.6</v>
+        <v>-35</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="O6" s="11">
-        <v>27</v>
-      </c>
-      <c r="P6" s="12">
-        <v>5</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="7">
-        <v>0</v>
+        <v>176</v>
+      </c>
+      <c r="O6" s="12">
+        <v>3</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="13">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1509,55 +1521,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>64</v>
+        <v>167</v>
       </c>
       <c r="L7" s="4">
-        <v>-37.7</v>
+        <v>-38.1</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="O7" s="11">
-        <v>24</v>
-      </c>
-      <c r="P7" s="12">
-        <v>5</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-      <c r="R7" s="7">
-        <v>0</v>
+        <v>177</v>
+      </c>
+      <c r="O7" s="12">
+        <v>1</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
+      <c r="R7" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1565,55 +1577,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L8" s="4">
-        <v>-23.2</v>
+        <v>-30.3</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="O8" s="11">
-        <v>14</v>
-      </c>
-      <c r="P8" s="12">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-      <c r="R8" s="12">
-        <v>3</v>
+        <v>176</v>
+      </c>
+      <c r="O8" s="12">
+        <v>0</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1621,55 +1633,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L9" s="4">
-        <v>-35</v>
+        <v>-37.9</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="O9" s="6">
-        <v>4</v>
-      </c>
-      <c r="P9" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>0</v>
-      </c>
-      <c r="R9" s="12">
-        <v>3</v>
+        <v>177</v>
+      </c>
+      <c r="O9" s="12">
+        <v>0</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1677,55 +1689,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="L10" s="4">
-        <v>-38.1</v>
+        <v>-7.1</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="O10" s="6">
-        <v>6</v>
-      </c>
-      <c r="P10" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>0</v>
-      </c>
-      <c r="R10" s="12">
-        <v>6</v>
+        <v>178</v>
+      </c>
+      <c r="O10" s="12">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1733,55 +1745,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L11" s="4">
-        <v>-30.3</v>
+        <v>-24</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="O11" s="6">
-        <v>0</v>
-      </c>
-      <c r="P11" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>0</v>
-      </c>
-      <c r="R11" s="7">
-        <v>0</v>
+        <v>49</v>
+      </c>
+      <c r="P11" s="14">
+        <v>9</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>2</v>
+      </c>
+      <c r="R11" s="15">
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1789,55 +1801,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L12" s="4">
-        <v>-37.9</v>
+        <v>-35.5</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="O12" s="6">
-        <v>0</v>
-      </c>
-      <c r="P12" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>0</v>
-      </c>
-      <c r="R12" s="7">
-        <v>0</v>
+        <v>176</v>
+      </c>
+      <c r="O12" s="10">
+        <v>20</v>
+      </c>
+      <c r="P12" s="13">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>2</v>
+      </c>
+      <c r="R12" s="13">
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1845,28 +1857,28 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>161</v>
@@ -1875,24 +1887,24 @@
         <v>161</v>
       </c>
       <c r="L13" s="4">
-        <v>-7.1</v>
+        <v>-15.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="O13" s="6">
-        <v>0</v>
-      </c>
-      <c r="P13" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="7">
-        <v>0</v>
-      </c>
-      <c r="R13" s="7">
+        <v>178</v>
+      </c>
+      <c r="O13" s="12">
+        <v>5</v>
+      </c>
+      <c r="P13" s="8">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>0</v>
+      </c>
+      <c r="R13" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1901,55 +1913,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>71</v>
+        <v>168</v>
       </c>
       <c r="L14" s="4">
-        <v>-24</v>
+        <v>-16.5</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="O14" s="11">
-        <v>14</v>
-      </c>
-      <c r="P14" s="13">
-        <v>14</v>
-      </c>
-      <c r="Q14" s="7">
-        <v>0</v>
-      </c>
-      <c r="R14" s="12">
-        <v>3</v>
+        <v>176</v>
+      </c>
+      <c r="O14" s="6">
+        <v>63</v>
+      </c>
+      <c r="P14" s="16">
+        <v>60</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>0</v>
+      </c>
+      <c r="R14" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1957,55 +1969,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L15" s="4">
-        <v>-35.4</v>
+        <v>-30.9</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="O15" s="11">
-        <v>19</v>
-      </c>
-      <c r="P15" s="14">
-        <v>19</v>
-      </c>
-      <c r="Q15" s="7">
-        <v>0</v>
-      </c>
-      <c r="R15" s="12">
-        <v>4</v>
+        <v>176</v>
+      </c>
+      <c r="O15" s="10">
+        <v>31</v>
+      </c>
+      <c r="P15" s="17">
+        <v>31</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+      <c r="R15" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2013,28 +2025,28 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>161</v>
@@ -2043,25 +2055,25 @@
         <v>161</v>
       </c>
       <c r="L16" s="4">
-        <v>-15.5</v>
+        <v>-23.1</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="O16" s="8">
-        <v>48</v>
-      </c>
-      <c r="P16" s="13">
-        <v>13</v>
-      </c>
-      <c r="Q16" s="7">
-        <v>0</v>
-      </c>
-      <c r="R16" s="15">
-        <v>29</v>
+        <v>177</v>
+      </c>
+      <c r="O16" s="10">
+        <v>21</v>
+      </c>
+      <c r="P16" s="9">
+        <v>20</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>0</v>
+      </c>
+      <c r="R16" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2069,55 +2081,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="L17" s="4">
-        <v>-16.5</v>
+        <v>-8.5</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="O17" s="8">
-        <v>54</v>
-      </c>
-      <c r="P17" s="15">
-        <v>28</v>
-      </c>
-      <c r="Q17" s="7">
-        <v>0</v>
-      </c>
-      <c r="R17" s="16">
-        <v>34</v>
+        <v>178</v>
+      </c>
+      <c r="O17" s="10">
+        <v>21</v>
+      </c>
+      <c r="P17" s="9">
+        <v>20</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0</v>
+      </c>
+      <c r="R17" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2125,55 +2137,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="L18" s="4">
-        <v>-30.9</v>
+        <v>-24.8</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="O18" s="8">
-        <v>56</v>
-      </c>
-      <c r="P18" s="14">
-        <v>19</v>
-      </c>
-      <c r="Q18" s="7">
-        <v>0</v>
-      </c>
-      <c r="R18" s="17">
-        <v>42</v>
+        <v>178</v>
+      </c>
+      <c r="O18" s="10">
+        <v>26</v>
+      </c>
+      <c r="P18" s="15">
+        <v>16</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>0</v>
+      </c>
+      <c r="R18" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2181,28 +2193,28 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>161</v>
@@ -2211,25 +2223,25 @@
         <v>161</v>
       </c>
       <c r="L19" s="4">
-        <v>-23.2</v>
+        <v>-14.7</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="O19" s="8">
-        <v>56</v>
+        <v>178</v>
+      </c>
+      <c r="O19" s="10">
+        <v>30</v>
       </c>
       <c r="P19" s="14">
-        <v>19</v>
-      </c>
-      <c r="Q19" s="7">
-        <v>0</v>
-      </c>
-      <c r="R19" s="14">
-        <v>21</v>
+        <v>12</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>0</v>
+      </c>
+      <c r="R19" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2237,7 +2249,7 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>56</v>
@@ -2246,46 +2258,46 @@
         <v>56</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L20" s="4">
-        <v>-8.4</v>
+        <v>-17.6</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="O20" s="8">
-        <v>43</v>
-      </c>
-      <c r="P20" s="17">
-        <v>39</v>
-      </c>
-      <c r="Q20" s="7">
-        <v>0</v>
-      </c>
-      <c r="R20" s="7">
-        <v>1</v>
+        <v>179</v>
+      </c>
+      <c r="O20" s="12">
+        <v>0</v>
+      </c>
+      <c r="P20" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="8">
+        <v>0</v>
+      </c>
+      <c r="R20" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2293,55 +2305,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L21" s="4">
-        <v>-24.7</v>
+        <v>-31.6</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="O21" s="11">
-        <v>35</v>
-      </c>
-      <c r="P21" s="16">
-        <v>35</v>
-      </c>
-      <c r="Q21" s="7">
-        <v>0</v>
-      </c>
-      <c r="R21" s="7">
-        <v>1</v>
+        <v>177</v>
+      </c>
+      <c r="O21" s="12">
+        <v>0</v>
+      </c>
+      <c r="P21" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>0</v>
+      </c>
+      <c r="R21" s="8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="191">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260623--01</t>
-  </si>
-  <si>
-    <t>20260623--02</t>
-  </si>
-  <si>
     <t>20260624--01</t>
   </si>
   <si>
@@ -130,10 +124,13 @@
     <t>20260629--03</t>
   </si>
   <si>
-    <t>05:47</t>
-  </si>
-  <si>
-    <t>04:32</t>
+    <t>20260630--01</t>
+  </si>
+  <si>
+    <t>20260630--02</t>
+  </si>
+  <si>
+    <t>20260630--03</t>
   </si>
   <si>
     <t>06:21</t>
@@ -142,67 +139,70 @@
     <t>00:27</t>
   </si>
   <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>01:41</t>
+  </si>
+  <si>
+    <t>06:43</t>
+  </si>
+  <si>
+    <t>03:47</t>
+  </si>
+  <si>
+    <t>05:24</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>05:01</t>
+  </si>
+  <si>
+    <t>04:19</t>
+  </si>
+  <si>
+    <t>05:42</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>02:39</t>
+  </si>
+  <si>
+    <t>04:15</t>
+  </si>
+  <si>
+    <t>06:24</t>
+  </si>
+  <si>
+    <t>06:32</t>
+  </si>
+  <si>
+    <t>06:42</t>
+  </si>
+  <si>
+    <t>02:06</t>
+  </si>
+  <si>
+    <t>06:01</t>
+  </si>
+  <si>
     <t>06:41</t>
   </si>
   <si>
-    <t>01:41</t>
-  </si>
-  <si>
-    <t>06:43</t>
-  </si>
-  <si>
-    <t>03:47</t>
-  </si>
-  <si>
-    <t>05:24</t>
-  </si>
-  <si>
-    <t>06:26</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>04:19</t>
-  </si>
-  <si>
-    <t>05:42</t>
-  </si>
-  <si>
-    <t>05:51</t>
-  </si>
-  <si>
-    <t>02:39</t>
-  </si>
-  <si>
-    <t>04:15</t>
-  </si>
-  <si>
-    <t>06:24</t>
-  </si>
-  <si>
-    <t>06:32</t>
-  </si>
-  <si>
-    <t>06:42</t>
-  </si>
-  <si>
-    <t>02:05</t>
+    <t>04:00</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:59</t>
-  </si>
-  <si>
-    <t>01:18</t>
-  </si>
-  <si>
-    <t>01:17:08</t>
-  </si>
-  <si>
-    <t>22:54:14</t>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>01:19</t>
   </si>
   <si>
     <t>00:31:02</t>
@@ -229,46 +229,49 @@
     <t>22:13:08</t>
   </si>
   <si>
-    <t>23:51:05</t>
-  </si>
-  <si>
-    <t>04:47:22</t>
-  </si>
-  <si>
-    <t>21:27:21</t>
-  </si>
-  <si>
-    <t>23:04:42</t>
-  </si>
-  <si>
-    <t>04:01:25</t>
-  </si>
-  <si>
-    <t>20:41:42</t>
-  </si>
-  <si>
-    <t>22:18:23</t>
-  </si>
-  <si>
-    <t>04:52:21</t>
-  </si>
-  <si>
-    <t>21:32:08</t>
-  </si>
-  <si>
-    <t>23:11:01</t>
-  </si>
-  <si>
-    <t>01:19:27</t>
-  </si>
-  <si>
-    <t>22:56:50</t>
+    <t>23:51:04</t>
+  </si>
+  <si>
+    <t>04:47:21</t>
+  </si>
+  <si>
+    <t>21:27:20</t>
+  </si>
+  <si>
+    <t>23:04:41</t>
+  </si>
+  <si>
+    <t>04:01:24</t>
+  </si>
+  <si>
+    <t>20:41:41</t>
+  </si>
+  <si>
+    <t>22:18:22</t>
+  </si>
+  <si>
+    <t>04:52:19</t>
+  </si>
+  <si>
+    <t>21:32:06</t>
+  </si>
+  <si>
+    <t>23:10:59</t>
+  </si>
+  <si>
+    <t>04:06:14</t>
+  </si>
+  <si>
+    <t>20:45:54</t>
+  </si>
+  <si>
+    <t>22:24:18</t>
   </si>
   <si>
     <t>00:33:13</t>
   </si>
   <si>
-    <t>22:13:18</t>
+    <t>22:13:17</t>
   </si>
   <si>
     <t>23:47:06</t>
@@ -289,40 +292,43 @@
     <t>22:15:17</t>
   </si>
   <si>
-    <t>23:53:36</t>
-  </si>
-  <si>
-    <t>04:50:06</t>
-  </si>
-  <si>
-    <t>21:29:40</t>
-  </si>
-  <si>
-    <t>23:07:01</t>
-  </si>
-  <si>
-    <t>04:04:41</t>
-  </si>
-  <si>
-    <t>20:44:23</t>
-  </si>
-  <si>
-    <t>22:20:34</t>
-  </si>
-  <si>
-    <t>04:54:31</t>
-  </si>
-  <si>
-    <t>21:34:14</t>
-  </si>
-  <si>
-    <t>23:14:29</t>
-  </si>
-  <si>
-    <t>01:22:20</t>
-  </si>
-  <si>
-    <t>22:59:06</t>
+    <t>23:53:35</t>
+  </si>
+  <si>
+    <t>04:50:05</t>
+  </si>
+  <si>
+    <t>21:29:39</t>
+  </si>
+  <si>
+    <t>23:07:00</t>
+  </si>
+  <si>
+    <t>04:04:40</t>
+  </si>
+  <si>
+    <t>20:44:21</t>
+  </si>
+  <si>
+    <t>22:20:32</t>
+  </si>
+  <si>
+    <t>04:54:29</t>
+  </si>
+  <si>
+    <t>21:34:12</t>
+  </si>
+  <si>
+    <t>23:14:26</t>
+  </si>
+  <si>
+    <t>04:08:31</t>
+  </si>
+  <si>
+    <t>20:48:01</t>
+  </si>
+  <si>
+    <t>22:27:06</t>
   </si>
   <si>
     <t>00:36:23</t>
@@ -334,16 +340,16 @@
     <t>01:28:25</t>
   </si>
   <si>
-    <t>23:04:28</t>
-  </si>
-  <si>
-    <t>00:42:16</t>
+    <t>23:04:27</t>
+  </si>
+  <si>
+    <t>00:42:15</t>
   </si>
   <si>
     <t>05:38:25</t>
   </si>
   <si>
-    <t>22:18:30</t>
+    <t>22:18:29</t>
   </si>
   <si>
     <t>23:56:05</t>
@@ -352,43 +358,46 @@
     <t>04:52:15</t>
   </si>
   <si>
-    <t>21:32:30</t>
-  </si>
-  <si>
-    <t>23:09:55</t>
-  </si>
-  <si>
-    <t>04:06:01</t>
-  </si>
-  <si>
-    <t>20:46:30</t>
-  </si>
-  <si>
-    <t>22:23:46</t>
-  </si>
-  <si>
-    <t>04:57:47</t>
-  </si>
-  <si>
-    <t>21:37:35</t>
-  </si>
-  <si>
-    <t>23:15:31</t>
-  </si>
-  <si>
-    <t>01:25:14</t>
-  </si>
-  <si>
-    <t>23:01:22</t>
+    <t>21:32:29</t>
+  </si>
+  <si>
+    <t>23:09:54</t>
+  </si>
+  <si>
+    <t>04:05:59</t>
+  </si>
+  <si>
+    <t>20:46:29</t>
+  </si>
+  <si>
+    <t>22:23:44</t>
+  </si>
+  <si>
+    <t>04:57:45</t>
+  </si>
+  <si>
+    <t>21:37:33</t>
+  </si>
+  <si>
+    <t>23:15:29</t>
+  </si>
+  <si>
+    <t>04:11:31</t>
+  </si>
+  <si>
+    <t>20:51:21</t>
+  </si>
+  <si>
+    <t>22:29:05</t>
   </si>
   <si>
     <t>00:39:34</t>
   </si>
   <si>
-    <t>22:13:45</t>
-  </si>
-  <si>
-    <t>23:53:47</t>
+    <t>22:13:44</t>
+  </si>
+  <si>
+    <t>23:53:46</t>
   </si>
   <si>
     <t>01:29:16</t>
@@ -403,40 +412,46 @@
     <t>05:41:07</t>
   </si>
   <si>
-    <t>22:21:43</t>
+    <t>22:21:42</t>
   </si>
   <si>
     <t>23:58:36</t>
   </si>
   <si>
-    <t>04:54:25</t>
-  </si>
-  <si>
-    <t>21:35:22</t>
-  </si>
-  <si>
-    <t>23:12:52</t>
-  </si>
-  <si>
-    <t>04:07:20</t>
-  </si>
-  <si>
-    <t>20:48:38</t>
-  </si>
-  <si>
-    <t>22:26:58</t>
-  </si>
-  <si>
-    <t>05:01:03</t>
-  </si>
-  <si>
-    <t>21:40:56</t>
-  </si>
-  <si>
-    <t>23:16:34</t>
-  </si>
-  <si>
-    <t>23:03:58</t>
+    <t>04:54:24</t>
+  </si>
+  <si>
+    <t>21:35:21</t>
+  </si>
+  <si>
+    <t>23:12:50</t>
+  </si>
+  <si>
+    <t>04:07:19</t>
+  </si>
+  <si>
+    <t>20:48:36</t>
+  </si>
+  <si>
+    <t>22:26:56</t>
+  </si>
+  <si>
+    <t>05:01:01</t>
+  </si>
+  <si>
+    <t>21:40:54</t>
+  </si>
+  <si>
+    <t>23:16:32</t>
+  </si>
+  <si>
+    <t>04:14:32</t>
+  </si>
+  <si>
+    <t>20:54:42</t>
+  </si>
+  <si>
+    <t>22:31:06</t>
   </si>
   <si>
     <t>00:41:47</t>
@@ -451,46 +466,55 @@
     <t>01:32:55</t>
   </si>
   <si>
-    <t>23:09:57</t>
-  </si>
-  <si>
-    <t>00:47:03</t>
-  </si>
-  <si>
-    <t>05:43:34</t>
-  </si>
-  <si>
-    <t>22:23:53</t>
+    <t>23:09:56</t>
+  </si>
+  <si>
+    <t>00:47:02</t>
+  </si>
+  <si>
+    <t>05:43:33</t>
+  </si>
+  <si>
+    <t>22:23:52</t>
   </si>
   <si>
     <t>00:01:08</t>
   </si>
   <si>
-    <t>04:57:09</t>
-  </si>
-  <si>
-    <t>21:37:41</t>
-  </si>
-  <si>
-    <t>23:15:11</t>
-  </si>
-  <si>
-    <t>04:10:37</t>
-  </si>
-  <si>
-    <t>20:51:19</t>
-  </si>
-  <si>
-    <t>22:29:09</t>
-  </si>
-  <si>
-    <t>05:03:13</t>
-  </si>
-  <si>
-    <t>21:43:03</t>
-  </si>
-  <si>
-    <t>23:20:03</t>
+    <t>04:57:08</t>
+  </si>
+  <si>
+    <t>21:37:40</t>
+  </si>
+  <si>
+    <t>23:15:10</t>
+  </si>
+  <si>
+    <t>04:10:35</t>
+  </si>
+  <si>
+    <t>20:51:17</t>
+  </si>
+  <si>
+    <t>22:29:08</t>
+  </si>
+  <si>
+    <t>05:03:11</t>
+  </si>
+  <si>
+    <t>21:43:01</t>
+  </si>
+  <si>
+    <t>23:20:01</t>
+  </si>
+  <si>
+    <t>04:16:49</t>
+  </si>
+  <si>
+    <t>20:56:49</t>
+  </si>
+  <si>
+    <t>22:33:55</t>
   </si>
   <si>
     <t>0°</t>
@@ -517,22 +541,31 @@
     <t>11°</t>
   </si>
   <si>
+    <t>3°</t>
+  </si>
+  <si>
     <t>01:32:33</t>
   </si>
   <si>
-    <t>21:28:55</t>
-  </si>
-  <si>
-    <t>20:49:12</t>
-  </si>
-  <si>
-    <t>22:22:33</t>
-  </si>
-  <si>
-    <t>21:42:30</t>
-  </si>
-  <si>
-    <t>23:15:47</t>
+    <t>21:28:53</t>
+  </si>
+  <si>
+    <t>20:49:10</t>
+  </si>
+  <si>
+    <t>22:22:32</t>
+  </si>
+  <si>
+    <t>21:42:28</t>
+  </si>
+  <si>
+    <t>23:15:45</t>
+  </si>
+  <si>
+    <t>04:07:05</t>
+  </si>
+  <si>
+    <t>22:33:54</t>
   </si>
   <si>
     <t>B</t>
@@ -602,30 +635,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -638,7 +647,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -650,25 +671,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1163,7 +1196,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1241,55 +1274,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>86</v>
+        <v>146</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L2" s="4">
-        <v>-38.2</v>
+        <v>-37.7</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="O2" s="6">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="P2" s="7">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
       </c>
-      <c r="R2" s="9">
-        <v>22</v>
+      <c r="R2" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1297,49 +1330,49 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L3" s="4">
-        <v>-29.6</v>
+        <v>-23.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="O3" s="10">
-        <v>36</v>
-      </c>
-      <c r="P3" s="11">
-        <v>33</v>
+        <v>188</v>
+      </c>
+      <c r="O3" s="9">
+        <v>0</v>
+      </c>
+      <c r="P3" s="8">
+        <v>0</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1353,49 +1386,49 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L4" s="4">
-        <v>-37.7</v>
+        <v>-35</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="O4" s="12">
-        <v>4</v>
-      </c>
-      <c r="P4" s="13">
-        <v>4</v>
+        <v>187</v>
+      </c>
+      <c r="O4" s="9">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
@@ -1409,45 +1442,45 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>64</v>
+        <v>176</v>
       </c>
       <c r="L5" s="4">
-        <v>-23.2</v>
+        <v>-38.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="O5" s="12">
+        <v>188</v>
+      </c>
+      <c r="O5" s="9">
         <v>0</v>
       </c>
       <c r="P5" s="8">
@@ -1465,55 +1498,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L6" s="4">
-        <v>-35</v>
+        <v>-30.3</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="O6" s="12">
-        <v>3</v>
-      </c>
-      <c r="P6" s="8">
-        <v>0</v>
+        <v>187</v>
+      </c>
+      <c r="O6" s="9">
+        <v>14</v>
+      </c>
+      <c r="P6" s="10">
+        <v>14</v>
       </c>
       <c r="Q6" s="8">
         <v>0</v>
       </c>
-      <c r="R6" s="13">
-        <v>3</v>
+      <c r="R6" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1521,55 +1554,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>167</v>
+        <v>68</v>
       </c>
       <c r="L7" s="4">
-        <v>-38.1</v>
+        <v>-37.9</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="O7" s="12">
-        <v>1</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
+        <v>188</v>
+      </c>
+      <c r="O7" s="6">
+        <v>34</v>
+      </c>
+      <c r="P7" s="11">
+        <v>4</v>
       </c>
       <c r="Q7" s="8">
         <v>0</v>
       </c>
-      <c r="R7" s="8">
-        <v>1</v>
+      <c r="R7" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1577,46 +1610,46 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>67</v>
+        <v>169</v>
       </c>
       <c r="L8" s="4">
-        <v>-30.3</v>
+        <v>-7.1</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="O8" s="12">
-        <v>0</v>
+        <v>189</v>
+      </c>
+      <c r="O8" s="6">
+        <v>40</v>
       </c>
       <c r="P8" s="8">
         <v>0</v>
@@ -1633,46 +1666,46 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L9" s="4">
-        <v>-37.9</v>
+        <v>-24</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="O9" s="12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9" s="8">
         <v>0</v>
@@ -1680,8 +1713,8 @@
       <c r="Q9" s="8">
         <v>0</v>
       </c>
-      <c r="R9" s="8">
-        <v>0</v>
+      <c r="R9" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1689,46 +1722,46 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>161</v>
+        <v>71</v>
       </c>
       <c r="L10" s="4">
-        <v>-7.1</v>
+        <v>-35.5</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="O10" s="12">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
@@ -1736,8 +1769,8 @@
       <c r="Q10" s="8">
         <v>0</v>
       </c>
-      <c r="R10" s="8">
-        <v>0</v>
+      <c r="R10" s="14">
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1745,55 +1778,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="L11" s="4">
-        <v>-24</v>
+        <v>-15.5</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="O11" s="6">
-        <v>49</v>
-      </c>
-      <c r="P11" s="14">
-        <v>9</v>
+        <v>189</v>
+      </c>
+      <c r="O11" s="9">
+        <v>0</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0</v>
       </c>
       <c r="Q11" s="8">
-        <v>2</v>
-      </c>
-      <c r="R11" s="15">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="R11" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1801,55 +1834,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>71</v>
+        <v>177</v>
       </c>
       <c r="L12" s="4">
-        <v>-35.5</v>
+        <v>-16.5</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="O12" s="10">
-        <v>20</v>
-      </c>
-      <c r="P12" s="13">
-        <v>5</v>
+        <v>187</v>
+      </c>
+      <c r="O12" s="12">
+        <v>53</v>
+      </c>
+      <c r="P12" s="15">
+        <v>53</v>
       </c>
       <c r="Q12" s="8">
-        <v>2</v>
-      </c>
-      <c r="R12" s="13">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="R12" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1857,49 +1890,49 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>161</v>
+        <v>74</v>
       </c>
       <c r="L13" s="4">
-        <v>-15.5</v>
+        <v>-30.9</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="O13" s="12">
-        <v>5</v>
-      </c>
-      <c r="P13" s="8">
-        <v>2</v>
+        <v>40</v>
+      </c>
+      <c r="P13" s="16">
+        <v>40</v>
       </c>
       <c r="Q13" s="8">
         <v>0</v>
@@ -1913,49 +1946,49 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L14" s="4">
-        <v>-16.5</v>
+        <v>-23.1</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="O14" s="6">
-        <v>63</v>
-      </c>
-      <c r="P14" s="16">
-        <v>60</v>
+        <v>188</v>
+      </c>
+      <c r="O14" s="9">
+        <v>2</v>
+      </c>
+      <c r="P14" s="8">
+        <v>2</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
@@ -1969,49 +2002,49 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>74</v>
+        <v>178</v>
       </c>
       <c r="L15" s="4">
-        <v>-30.9</v>
+        <v>-8.4</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="O15" s="10">
-        <v>31</v>
-      </c>
-      <c r="P15" s="17">
-        <v>31</v>
+        <v>189</v>
+      </c>
+      <c r="O15" s="9">
+        <v>3</v>
+      </c>
+      <c r="P15" s="8">
+        <v>1</v>
       </c>
       <c r="Q15" s="8">
         <v>0</v>
@@ -2025,49 +2058,49 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="L16" s="4">
-        <v>-23.1</v>
+        <v>-24.8</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="O16" s="10">
-        <v>21</v>
-      </c>
-      <c r="P16" s="9">
-        <v>20</v>
+        <v>189</v>
+      </c>
+      <c r="O16" s="9">
+        <v>0</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
       </c>
       <c r="Q16" s="8">
         <v>0</v>
@@ -2081,49 +2114,49 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>169</v>
       </c>
       <c r="L17" s="4">
-        <v>-8.5</v>
+        <v>-14.7</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="O17" s="10">
+        <v>189</v>
+      </c>
+      <c r="O17" s="6">
         <v>21</v>
       </c>
-      <c r="P17" s="9">
-        <v>20</v>
+      <c r="P17" s="17">
+        <v>21</v>
       </c>
       <c r="Q17" s="8">
         <v>0</v>
@@ -2137,52 +2170,52 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="L18" s="4">
-        <v>-24.8</v>
+        <v>-17.6</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="O18" s="10">
-        <v>26</v>
-      </c>
-      <c r="P18" s="15">
-        <v>16</v>
+        <v>190</v>
+      </c>
+      <c r="O18" s="9">
+        <v>2</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0</v>
       </c>
       <c r="Q18" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R18" s="8">
         <v>0</v>
@@ -2193,52 +2226,52 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="L19" s="4">
-        <v>-14.7</v>
+        <v>-31.6</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="O19" s="10">
-        <v>30</v>
-      </c>
-      <c r="P19" s="14">
-        <v>12</v>
+        <v>188</v>
+      </c>
+      <c r="O19" s="9">
+        <v>2</v>
+      </c>
+      <c r="P19" s="8">
+        <v>0</v>
       </c>
       <c r="Q19" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R19" s="8">
         <v>0</v>
@@ -2249,46 +2282,46 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="L20" s="4">
-        <v>-17.6</v>
+        <v>-22.5</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="O20" s="12">
-        <v>0</v>
+        <v>190</v>
+      </c>
+      <c r="O20" s="9">
+        <v>2</v>
       </c>
       <c r="P20" s="8">
         <v>0</v>
@@ -2305,114 +2338,170 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="J21" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="L21" s="4">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="O21" s="9">
+        <v>0</v>
+      </c>
+      <c r="P21" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>0</v>
+      </c>
+      <c r="R21" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="2">
+        <v>15</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="L21" s="4">
-        <v>-31.6</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="O21" s="12">
-        <v>0</v>
-      </c>
-      <c r="P21" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="8">
-        <v>0</v>
-      </c>
-      <c r="R21" s="8">
+      <c r="J22" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="L22" s="4">
+        <v>-25.7</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="O22" s="9">
+        <v>0</v>
+      </c>
+      <c r="P22" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>0</v>
+      </c>
+      <c r="R22" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A21">
+  <conditionalFormatting sqref="A2:A22">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B21">
+  <conditionalFormatting sqref="B2:B22">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C21">
+  <conditionalFormatting sqref="C2:C22">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D21">
+  <conditionalFormatting sqref="D2:D22">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E21">
+  <conditionalFormatting sqref="E2:E22">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F21">
+  <conditionalFormatting sqref="F2:F22">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G21">
+  <conditionalFormatting sqref="G2:G22">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H21">
+  <conditionalFormatting sqref="H2:H22">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I21">
+  <conditionalFormatting sqref="I2:I22">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J21">
+  <conditionalFormatting sqref="J2:J22">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K21">
+  <conditionalFormatting sqref="K2:K22">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L21">
+  <conditionalFormatting sqref="L2:L22">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2431,12 +2520,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M21">
+  <conditionalFormatting sqref="M2:M22">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N21">
+  <conditionalFormatting sqref="N2:N22">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2453,22 +2542,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O21">
+  <conditionalFormatting sqref="O2:O22">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P21">
+  <conditionalFormatting sqref="P2:P22">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q21">
+  <conditionalFormatting sqref="Q2:Q22">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R21">
+  <conditionalFormatting sqref="R2:R22">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="198">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260624--01</t>
-  </si>
-  <si>
-    <t>20260624--02</t>
-  </si>
-  <si>
-    <t>20260624--03</t>
-  </si>
-  <si>
     <t>20260625--01</t>
   </si>
   <si>
@@ -133,13 +124,13 @@
     <t>20260630--03</t>
   </si>
   <si>
-    <t>06:21</t>
-  </si>
-  <si>
-    <t>00:27</t>
-  </si>
-  <si>
-    <t>06:40</t>
+    <t>20260701--01</t>
+  </si>
+  <si>
+    <t>20260701--02</t>
+  </si>
+  <si>
+    <t>20260701--03</t>
   </si>
   <si>
     <t>01:41</t>
@@ -196,6 +187,15 @@
     <t>04:00</t>
   </si>
   <si>
+    <t>05:12</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>05:10</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
@@ -205,13 +205,10 @@
     <t>01:19</t>
   </si>
   <si>
-    <t>00:31:02</t>
-  </si>
-  <si>
-    <t>22:08:57</t>
-  </si>
-  <si>
-    <t>23:44:59</t>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>05:53</t>
   </si>
   <si>
     <t>01:23:57</t>
@@ -268,13 +265,13 @@
     <t>22:24:18</t>
   </si>
   <si>
-    <t>00:33:13</t>
-  </si>
-  <si>
-    <t>22:13:17</t>
-  </si>
-  <si>
-    <t>23:47:06</t>
+    <t>03:20:07</t>
+  </si>
+  <si>
+    <t>04:57:23</t>
+  </si>
+  <si>
+    <t>21:37:38</t>
   </si>
   <si>
     <t>01:27:35</t>
@@ -331,10 +328,13 @@
     <t>22:27:06</t>
   </si>
   <si>
-    <t>00:36:23</t>
-  </si>
-  <si>
-    <t>23:50:26</t>
+    <t>03:22:36</t>
+  </si>
+  <si>
+    <t>04:59:34</t>
+  </si>
+  <si>
+    <t>21:40:07</t>
   </si>
   <si>
     <t>01:28:25</t>
@@ -391,13 +391,13 @@
     <t>22:29:05</t>
   </si>
   <si>
-    <t>00:39:34</t>
-  </si>
-  <si>
-    <t>22:13:44</t>
-  </si>
-  <si>
-    <t>23:53:46</t>
+    <t>03:25:12</t>
+  </si>
+  <si>
+    <t>05:02:46</t>
+  </si>
+  <si>
+    <t>21:42:41</t>
   </si>
   <si>
     <t>01:29:16</t>
@@ -454,13 +454,13 @@
     <t>22:31:06</t>
   </si>
   <si>
-    <t>00:41:47</t>
-  </si>
-  <si>
-    <t>22:17:38</t>
-  </si>
-  <si>
-    <t>23:55:54</t>
+    <t>03:27:48</t>
+  </si>
+  <si>
+    <t>05:05:57</t>
+  </si>
+  <si>
+    <t>21:45:17</t>
   </si>
   <si>
     <t>01:32:55</t>
@@ -517,12 +517,21 @@
     <t>22:33:55</t>
   </si>
   <si>
+    <t>03:30:17</t>
+  </si>
+  <si>
+    <t>05:08:08</t>
+  </si>
+  <si>
+    <t>21:47:46</t>
+  </si>
+  <si>
+    <t>1°</t>
+  </si>
+  <si>
     <t>0°</t>
   </si>
   <si>
-    <t>1°</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -544,6 +553,12 @@
     <t>3°</t>
   </si>
   <si>
+    <t>16°</t>
+  </si>
+  <si>
+    <t>13°</t>
+  </si>
+  <si>
     <t>01:32:33</t>
   </si>
   <si>
@@ -568,6 +583,12 @@
     <t>22:33:54</t>
   </si>
   <si>
+    <t>03:26:43</t>
+  </si>
+  <si>
+    <t>05:00:04</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
@@ -577,10 +598,10 @@
     <t>A</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>2</t>
@@ -620,7 +641,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -641,7 +662,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -653,13 +674,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -671,7 +686,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -683,25 +716,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -742,7 +775,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -793,6 +826,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1274,7 +1313,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>39</v>
@@ -1283,40 +1322,40 @@
         <v>60</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>63</v>
+        <v>181</v>
       </c>
       <c r="L2" s="4">
-        <v>-37.7</v>
+        <v>-38.1</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="O2" s="6">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="P2" s="7">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1330,7 +1369,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>40</v>
@@ -1339,46 +1378,46 @@
         <v>60</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L3" s="4">
-        <v>-23.2</v>
+        <v>-30.3</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="O3" s="9">
-        <v>0</v>
-      </c>
-      <c r="P3" s="8">
-        <v>0</v>
+        <v>195</v>
+      </c>
+      <c r="O3" s="6">
+        <v>39</v>
+      </c>
+      <c r="P3" s="9">
+        <v>36</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
       </c>
       <c r="R3" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1386,7 +1425,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>41</v>
@@ -1395,46 +1434,46 @@
         <v>60</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L4" s="4">
-        <v>-35</v>
+        <v>-37.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="O4" s="9">
-        <v>0</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
+        <v>194</v>
+      </c>
+      <c r="O4" s="6">
+        <v>28</v>
+      </c>
+      <c r="P4" s="7">
+        <v>28</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
       </c>
-      <c r="R4" s="8">
-        <v>0</v>
+      <c r="R4" s="10">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1442,7 +1481,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>42</v>
@@ -1451,37 +1490,37 @@
         <v>60</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="L5" s="4">
-        <v>-38.1</v>
+        <v>-7.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="O5" s="9">
-        <v>0</v>
+        <v>196</v>
+      </c>
+      <c r="O5" s="6">
+        <v>20</v>
       </c>
       <c r="P5" s="8">
         <v>0</v>
@@ -1489,8 +1528,8 @@
       <c r="Q5" s="8">
         <v>0</v>
       </c>
-      <c r="R5" s="8">
-        <v>0</v>
+      <c r="R5" s="11">
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1498,7 +1537,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>43</v>
@@ -1507,46 +1546,46 @@
         <v>60</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L6" s="4">
-        <v>-30.3</v>
+        <v>-24</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="O6" s="9">
-        <v>14</v>
-      </c>
-      <c r="P6" s="10">
-        <v>14</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>0</v>
-      </c>
-      <c r="R6" s="8">
-        <v>1</v>
+        <v>195</v>
+      </c>
+      <c r="O6" s="12">
+        <v>99</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>63</v>
+      </c>
+      <c r="R6" s="14">
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1554,7 +1593,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>44</v>
@@ -1563,46 +1602,46 @@
         <v>60</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L7" s="4">
-        <v>-37.9</v>
+        <v>-35.5</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="O7" s="6">
-        <v>34</v>
-      </c>
-      <c r="P7" s="11">
-        <v>4</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>0</v>
-      </c>
-      <c r="R7" s="11">
-        <v>3</v>
+        <v>195</v>
+      </c>
+      <c r="O7" s="12">
+        <v>100</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="13">
+        <v>67</v>
+      </c>
+      <c r="R7" s="15">
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1610,7 +1649,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>45</v>
@@ -1619,37 +1658,37 @@
         <v>60</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L8" s="4">
-        <v>-7.1</v>
+        <v>-15.5</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O8" s="6">
-        <v>40</v>
+        <v>196</v>
+      </c>
+      <c r="O8" s="16">
+        <v>15</v>
       </c>
       <c r="P8" s="8">
         <v>0</v>
@@ -1666,7 +1705,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>46</v>
@@ -1675,46 +1714,46 @@
         <v>60</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>70</v>
+        <v>182</v>
       </c>
       <c r="L9" s="4">
-        <v>-24</v>
+        <v>-16.5</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="O9" s="12">
-        <v>100</v>
-      </c>
-      <c r="P9" s="8">
-        <v>0</v>
+        <v>54</v>
+      </c>
+      <c r="P9" s="17">
+        <v>51</v>
       </c>
       <c r="Q9" s="8">
         <v>0</v>
       </c>
-      <c r="R9" s="13">
-        <v>100</v>
+      <c r="R9" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1722,7 +1761,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>47</v>
@@ -1731,46 +1770,46 @@
         <v>60</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L10" s="4">
-        <v>-35.5</v>
+        <v>-30.9</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="O10" s="12">
-        <v>86</v>
-      </c>
-      <c r="P10" s="8">
-        <v>0</v>
+        <v>195</v>
+      </c>
+      <c r="O10" s="6">
+        <v>25</v>
+      </c>
+      <c r="P10" s="18">
+        <v>18</v>
       </c>
       <c r="Q10" s="8">
         <v>0</v>
       </c>
-      <c r="R10" s="14">
-        <v>86</v>
+      <c r="R10" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1778,7 +1817,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>48</v>
@@ -1787,40 +1826,40 @@
         <v>60</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L11" s="4">
-        <v>-15.5</v>
+        <v>-23.1</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O11" s="9">
-        <v>0</v>
-      </c>
-      <c r="P11" s="8">
-        <v>0</v>
+        <v>194</v>
+      </c>
+      <c r="O11" s="12">
+        <v>43</v>
+      </c>
+      <c r="P11" s="19">
+        <v>43</v>
       </c>
       <c r="Q11" s="8">
         <v>0</v>
@@ -1834,49 +1873,49 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="L12" s="4">
-        <v>-16.5</v>
+        <v>-8.4</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="O12" s="12">
-        <v>53</v>
-      </c>
-      <c r="P12" s="15">
-        <v>53</v>
+        <v>196</v>
+      </c>
+      <c r="O12" s="16">
+        <v>17</v>
+      </c>
+      <c r="P12" s="11">
+        <v>11</v>
       </c>
       <c r="Q12" s="8">
         <v>0</v>
@@ -1890,49 +1929,49 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>74</v>
+        <v>184</v>
       </c>
       <c r="L13" s="4">
-        <v>-30.9</v>
+        <v>-24.8</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="O13" s="12">
-        <v>40</v>
-      </c>
-      <c r="P13" s="16">
-        <v>40</v>
+        <v>196</v>
+      </c>
+      <c r="O13" s="16">
+        <v>9</v>
+      </c>
+      <c r="P13" s="11">
+        <v>8</v>
       </c>
       <c r="Q13" s="8">
         <v>0</v>
@@ -1946,7 +1985,7 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>51</v>
@@ -1955,40 +1994,40 @@
         <v>60</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L14" s="4">
-        <v>-23.1</v>
+        <v>-14.7</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="O14" s="9">
-        <v>2</v>
-      </c>
-      <c r="P14" s="8">
-        <v>2</v>
+        <v>196</v>
+      </c>
+      <c r="O14" s="16">
+        <v>3</v>
+      </c>
+      <c r="P14" s="10">
+        <v>3</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
@@ -2002,7 +2041,7 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>52</v>
@@ -2011,40 +2050,40 @@
         <v>52</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="L15" s="4">
-        <v>-8.4</v>
+        <v>-17.6</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O15" s="9">
-        <v>3</v>
+        <v>197</v>
+      </c>
+      <c r="O15" s="16">
+        <v>0</v>
       </c>
       <c r="P15" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="8">
         <v>0</v>
@@ -2058,45 +2097,45 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="L16" s="4">
-        <v>-24.8</v>
+        <v>-31.6</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O16" s="9">
+        <v>194</v>
+      </c>
+      <c r="O16" s="16">
         <v>0</v>
       </c>
       <c r="P16" s="8">
@@ -2114,49 +2153,49 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="L17" s="4">
-        <v>-14.7</v>
+        <v>-22.5</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O17" s="6">
-        <v>21</v>
-      </c>
-      <c r="P17" s="17">
-        <v>21</v>
+        <v>197</v>
+      </c>
+      <c r="O17" s="16">
+        <v>0</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
       </c>
       <c r="Q17" s="8">
         <v>0</v>
@@ -2170,52 +2209,52 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="L18" s="4">
-        <v>-17.6</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="O18" s="9">
-        <v>2</v>
+        <v>196</v>
+      </c>
+      <c r="O18" s="16">
+        <v>10</v>
       </c>
       <c r="P18" s="8">
         <v>0</v>
       </c>
       <c r="Q18" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R18" s="8">
         <v>0</v>
@@ -2226,52 +2265,52 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="L19" s="4">
-        <v>-31.6</v>
+        <v>-25.7</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="O19" s="9">
-        <v>2</v>
+        <v>196</v>
+      </c>
+      <c r="O19" s="16">
+        <v>9</v>
       </c>
       <c r="P19" s="8">
         <v>0</v>
       </c>
       <c r="Q19" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R19" s="8">
         <v>0</v>
@@ -2282,46 +2321,46 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="L20" s="4">
-        <v>-22.5</v>
+        <v>-29.1</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="O20" s="9">
-        <v>2</v>
+        <v>196</v>
+      </c>
+      <c r="O20" s="16">
+        <v>18</v>
       </c>
       <c r="P20" s="8">
         <v>0</v>
@@ -2338,46 +2377,46 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="L21" s="4">
-        <v>-9.300000000000001</v>
+        <v>-14</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O21" s="9">
-        <v>0</v>
+        <v>196</v>
+      </c>
+      <c r="O21" s="16">
+        <v>14</v>
       </c>
       <c r="P21" s="8">
         <v>0</v>
@@ -2394,46 +2433,46 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>59</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="L22" s="4">
-        <v>-25.7</v>
+        <v>-18.4</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O22" s="9">
-        <v>0</v>
+        <v>196</v>
+      </c>
+      <c r="O22" s="16">
+        <v>6</v>
       </c>
       <c r="P22" s="8">
         <v>0</v>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="201">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260625--01</t>
-  </si>
-  <si>
-    <t>20260625--02</t>
-  </si>
-  <si>
     <t>20260626--01</t>
   </si>
   <si>
@@ -133,10 +127,13 @@
     <t>20260701--03</t>
   </si>
   <si>
-    <t>01:41</t>
-  </si>
-  <si>
-    <t>06:43</t>
+    <t>20260702--01</t>
+  </si>
+  <si>
+    <t>20260702--02</t>
+  </si>
+  <si>
+    <t>20260702--03</t>
   </si>
   <si>
     <t>03:47</t>
@@ -148,385 +145,397 @@
     <t>06:25</t>
   </si>
   <si>
-    <t>05:01</t>
-  </si>
-  <si>
-    <t>04:19</t>
-  </si>
-  <si>
-    <t>05:42</t>
-  </si>
-  <si>
-    <t>05:50</t>
-  </si>
-  <si>
-    <t>02:39</t>
-  </si>
-  <si>
-    <t>04:15</t>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>04:18</t>
+  </si>
+  <si>
+    <t>05:41</t>
+  </si>
+  <si>
+    <t>05:51</t>
+  </si>
+  <si>
+    <t>02:36</t>
+  </si>
+  <si>
+    <t>04:13</t>
   </si>
   <si>
     <t>06:24</t>
   </si>
   <si>
-    <t>06:32</t>
+    <t>06:31</t>
   </si>
   <si>
     <t>06:42</t>
   </si>
   <si>
-    <t>02:06</t>
-  </si>
-  <si>
-    <t>06:01</t>
+    <t>02:08</t>
+  </si>
+  <si>
+    <t>06:00</t>
   </si>
   <si>
     <t>06:41</t>
   </si>
   <si>
-    <t>04:00</t>
-  </si>
-  <si>
-    <t>05:12</t>
-  </si>
-  <si>
-    <t>06:23</t>
+    <t>04:02</t>
   </si>
   <si>
     <t>05:10</t>
   </si>
   <si>
+    <t>05:11</t>
+  </si>
+  <si>
+    <t>03:58</t>
+  </si>
+  <si>
+    <t>06:44</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>01:19</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>05:53</t>
-  </si>
-  <si>
-    <t>01:23:57</t>
-  </si>
-  <si>
-    <t>22:59:01</t>
-  </si>
-  <si>
-    <t>00:37:30</t>
-  </si>
-  <si>
-    <t>05:33:16</t>
-  </si>
-  <si>
-    <t>22:13:08</t>
-  </si>
-  <si>
-    <t>23:51:04</t>
-  </si>
-  <si>
-    <t>04:47:21</t>
-  </si>
-  <si>
-    <t>21:27:20</t>
-  </si>
-  <si>
-    <t>23:04:41</t>
-  </si>
-  <si>
-    <t>04:01:24</t>
-  </si>
-  <si>
-    <t>20:41:41</t>
-  </si>
-  <si>
-    <t>22:18:22</t>
-  </si>
-  <si>
-    <t>04:52:19</t>
-  </si>
-  <si>
-    <t>21:32:06</t>
-  </si>
-  <si>
-    <t>23:10:59</t>
-  </si>
-  <si>
-    <t>04:06:14</t>
-  </si>
-  <si>
-    <t>20:45:54</t>
-  </si>
-  <si>
-    <t>22:24:18</t>
-  </si>
-  <si>
-    <t>03:20:07</t>
-  </si>
-  <si>
-    <t>04:57:23</t>
-  </si>
-  <si>
-    <t>21:37:38</t>
-  </si>
-  <si>
-    <t>01:27:35</t>
-  </si>
-  <si>
-    <t>23:01:07</t>
-  </si>
-  <si>
-    <t>00:40:22</t>
-  </si>
-  <si>
-    <t>05:35:43</t>
-  </si>
-  <si>
-    <t>22:15:17</t>
-  </si>
-  <si>
-    <t>23:53:35</t>
-  </si>
-  <si>
-    <t>04:50:05</t>
-  </si>
-  <si>
-    <t>21:29:39</t>
-  </si>
-  <si>
-    <t>23:07:00</t>
-  </si>
-  <si>
-    <t>04:04:40</t>
-  </si>
-  <si>
-    <t>20:44:21</t>
-  </si>
-  <si>
-    <t>22:20:32</t>
-  </si>
-  <si>
-    <t>04:54:29</t>
-  </si>
-  <si>
-    <t>21:34:12</t>
-  </si>
-  <si>
-    <t>23:14:26</t>
-  </si>
-  <si>
-    <t>04:08:31</t>
-  </si>
-  <si>
-    <t>20:48:01</t>
-  </si>
-  <si>
-    <t>22:27:06</t>
-  </si>
-  <si>
-    <t>03:22:36</t>
-  </si>
-  <si>
-    <t>04:59:34</t>
-  </si>
-  <si>
-    <t>21:40:07</t>
-  </si>
-  <si>
-    <t>01:28:25</t>
-  </si>
-  <si>
-    <t>23:04:27</t>
-  </si>
-  <si>
-    <t>00:42:15</t>
-  </si>
-  <si>
-    <t>05:38:25</t>
-  </si>
-  <si>
-    <t>22:18:29</t>
-  </si>
-  <si>
-    <t>23:56:05</t>
-  </si>
-  <si>
-    <t>04:52:15</t>
-  </si>
-  <si>
-    <t>21:32:29</t>
-  </si>
-  <si>
-    <t>23:09:54</t>
-  </si>
-  <si>
-    <t>04:05:59</t>
-  </si>
-  <si>
-    <t>20:46:29</t>
-  </si>
-  <si>
-    <t>22:23:44</t>
-  </si>
-  <si>
-    <t>04:57:45</t>
-  </si>
-  <si>
-    <t>21:37:33</t>
-  </si>
-  <si>
-    <t>23:15:29</t>
-  </si>
-  <si>
-    <t>04:11:31</t>
-  </si>
-  <si>
-    <t>20:51:21</t>
-  </si>
-  <si>
-    <t>22:29:05</t>
-  </si>
-  <si>
-    <t>03:25:12</t>
-  </si>
-  <si>
-    <t>05:02:46</t>
-  </si>
-  <si>
-    <t>21:42:41</t>
-  </si>
-  <si>
-    <t>01:29:16</t>
-  </si>
-  <si>
-    <t>23:07:50</t>
-  </si>
-  <si>
-    <t>00:44:09</t>
-  </si>
-  <si>
-    <t>05:41:07</t>
-  </si>
-  <si>
-    <t>22:21:42</t>
-  </si>
-  <si>
-    <t>23:58:36</t>
-  </si>
-  <si>
-    <t>04:54:24</t>
-  </si>
-  <si>
-    <t>21:35:21</t>
-  </si>
-  <si>
-    <t>23:12:50</t>
-  </si>
-  <si>
-    <t>04:07:19</t>
-  </si>
-  <si>
-    <t>20:48:36</t>
-  </si>
-  <si>
-    <t>22:26:56</t>
-  </si>
-  <si>
-    <t>05:01:01</t>
-  </si>
-  <si>
-    <t>21:40:54</t>
-  </si>
-  <si>
-    <t>23:16:32</t>
-  </si>
-  <si>
-    <t>04:14:32</t>
-  </si>
-  <si>
-    <t>20:54:42</t>
-  </si>
-  <si>
-    <t>22:31:06</t>
-  </si>
-  <si>
-    <t>03:27:48</t>
-  </si>
-  <si>
-    <t>05:05:57</t>
-  </si>
-  <si>
-    <t>21:45:17</t>
-  </si>
-  <si>
-    <t>01:32:55</t>
-  </si>
-  <si>
-    <t>23:09:56</t>
-  </si>
-  <si>
-    <t>00:47:02</t>
-  </si>
-  <si>
-    <t>05:43:33</t>
-  </si>
-  <si>
-    <t>22:23:52</t>
-  </si>
-  <si>
-    <t>00:01:08</t>
-  </si>
-  <si>
-    <t>04:57:08</t>
-  </si>
-  <si>
-    <t>21:37:40</t>
-  </si>
-  <si>
-    <t>23:15:10</t>
-  </si>
-  <si>
-    <t>04:10:35</t>
-  </si>
-  <si>
-    <t>20:51:17</t>
-  </si>
-  <si>
-    <t>22:29:08</t>
-  </si>
-  <si>
-    <t>05:03:11</t>
-  </si>
-  <si>
-    <t>21:43:01</t>
-  </si>
-  <si>
-    <t>23:20:01</t>
-  </si>
-  <si>
-    <t>04:16:49</t>
-  </si>
-  <si>
-    <t>20:56:49</t>
-  </si>
-  <si>
-    <t>22:33:55</t>
-  </si>
-  <si>
-    <t>03:30:17</t>
-  </si>
-  <si>
-    <t>05:08:08</t>
-  </si>
-  <si>
-    <t>21:47:46</t>
-  </si>
-  <si>
-    <t>1°</t>
+    <t>01:59</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>01:02</t>
+  </si>
+  <si>
+    <t>00:37:28</t>
+  </si>
+  <si>
+    <t>05:33:14</t>
+  </si>
+  <si>
+    <t>22:13:03</t>
+  </si>
+  <si>
+    <t>23:50:59</t>
+  </si>
+  <si>
+    <t>04:47:16</t>
+  </si>
+  <si>
+    <t>21:27:12</t>
+  </si>
+  <si>
+    <t>23:04:32</t>
+  </si>
+  <si>
+    <t>04:01:13</t>
+  </si>
+  <si>
+    <t>20:41:27</t>
+  </si>
+  <si>
+    <t>22:18:06</t>
+  </si>
+  <si>
+    <t>04:52:02</t>
+  </si>
+  <si>
+    <t>21:31:44</t>
+  </si>
+  <si>
+    <t>23:10:36</t>
+  </si>
+  <si>
+    <t>04:05:50</t>
+  </si>
+  <si>
+    <t>20:45:24</t>
+  </si>
+  <si>
+    <t>22:23:46</t>
+  </si>
+  <si>
+    <t>03:19:34</t>
+  </si>
+  <si>
+    <t>04:56:50</t>
+  </si>
+  <si>
+    <t>21:36:57</t>
+  </si>
+  <si>
+    <t>02:33:15</t>
+  </si>
+  <si>
+    <t>04:10:20</t>
+  </si>
+  <si>
+    <t>20:50:09</t>
+  </si>
+  <si>
+    <t>00:40:20</t>
+  </si>
+  <si>
+    <t>05:35:40</t>
+  </si>
+  <si>
+    <t>22:15:12</t>
+  </si>
+  <si>
+    <t>23:53:30</t>
+  </si>
+  <si>
+    <t>04:50:00</t>
+  </si>
+  <si>
+    <t>21:29:30</t>
+  </si>
+  <si>
+    <t>23:06:50</t>
+  </si>
+  <si>
+    <t>04:04:31</t>
+  </si>
+  <si>
+    <t>20:44:08</t>
+  </si>
+  <si>
+    <t>22:20:17</t>
+  </si>
+  <si>
+    <t>04:54:13</t>
+  </si>
+  <si>
+    <t>21:33:50</t>
+  </si>
+  <si>
+    <t>23:14:02</t>
+  </si>
+  <si>
+    <t>04:08:07</t>
+  </si>
+  <si>
+    <t>20:47:30</t>
+  </si>
+  <si>
+    <t>22:26:33</t>
+  </si>
+  <si>
+    <t>03:22:04</t>
+  </si>
+  <si>
+    <t>04:59:00</t>
+  </si>
+  <si>
+    <t>21:39:25</t>
+  </si>
+  <si>
+    <t>02:36:05</t>
+  </si>
+  <si>
+    <t>04:12:26</t>
+  </si>
+  <si>
+    <t>20:52:25</t>
+  </si>
+  <si>
+    <t>00:42:13</t>
+  </si>
+  <si>
+    <t>05:38:22</t>
+  </si>
+  <si>
+    <t>22:18:24</t>
+  </si>
+  <si>
+    <t>23:56:00</t>
+  </si>
+  <si>
+    <t>04:52:09</t>
+  </si>
+  <si>
+    <t>21:32:20</t>
+  </si>
+  <si>
+    <t>23:09:45</t>
+  </si>
+  <si>
+    <t>04:05:49</t>
+  </si>
+  <si>
+    <t>20:46:14</t>
+  </si>
+  <si>
+    <t>22:23:29</t>
+  </si>
+  <si>
+    <t>04:57:28</t>
+  </si>
+  <si>
+    <t>21:37:10</t>
+  </si>
+  <si>
+    <t>23:15:06</t>
+  </si>
+  <si>
+    <t>04:11:07</t>
+  </si>
+  <si>
+    <t>20:50:50</t>
+  </si>
+  <si>
+    <t>22:28:34</t>
+  </si>
+  <si>
+    <t>03:24:39</t>
+  </si>
+  <si>
+    <t>05:02:12</t>
+  </si>
+  <si>
+    <t>21:42:00</t>
+  </si>
+  <si>
+    <t>02:38:04</t>
+  </si>
+  <si>
+    <t>04:15:48</t>
+  </si>
+  <si>
+    <t>20:55:25</t>
+  </si>
+  <si>
+    <t>00:44:07</t>
+  </si>
+  <si>
+    <t>05:41:04</t>
+  </si>
+  <si>
+    <t>22:21:37</t>
+  </si>
+  <si>
+    <t>23:58:30</t>
+  </si>
+  <si>
+    <t>04:54:18</t>
+  </si>
+  <si>
+    <t>21:35:11</t>
+  </si>
+  <si>
+    <t>23:12:41</t>
+  </si>
+  <si>
+    <t>04:07:07</t>
+  </si>
+  <si>
+    <t>20:48:21</t>
+  </si>
+  <si>
+    <t>22:26:41</t>
+  </si>
+  <si>
+    <t>05:00:44</t>
+  </si>
+  <si>
+    <t>21:40:32</t>
+  </si>
+  <si>
+    <t>23:16:10</t>
+  </si>
+  <si>
+    <t>04:14:07</t>
+  </si>
+  <si>
+    <t>20:54:11</t>
+  </si>
+  <si>
+    <t>22:30:35</t>
+  </si>
+  <si>
+    <t>03:27:14</t>
+  </si>
+  <si>
+    <t>05:05:24</t>
+  </si>
+  <si>
+    <t>21:44:36</t>
+  </si>
+  <si>
+    <t>02:40:03</t>
+  </si>
+  <si>
+    <t>04:19:10</t>
+  </si>
+  <si>
+    <t>20:58:25</t>
+  </si>
+  <si>
+    <t>00:47:00</t>
+  </si>
+  <si>
+    <t>05:43:31</t>
+  </si>
+  <si>
+    <t>22:23:47</t>
+  </si>
+  <si>
+    <t>00:01:03</t>
+  </si>
+  <si>
+    <t>04:57:02</t>
+  </si>
+  <si>
+    <t>21:37:30</t>
+  </si>
+  <si>
+    <t>23:15:00</t>
+  </si>
+  <si>
+    <t>04:10:25</t>
+  </si>
+  <si>
+    <t>20:51:02</t>
+  </si>
+  <si>
+    <t>22:28:53</t>
+  </si>
+  <si>
+    <t>05:02:54</t>
+  </si>
+  <si>
+    <t>21:42:39</t>
+  </si>
+  <si>
+    <t>23:19:38</t>
+  </si>
+  <si>
+    <t>04:16:24</t>
+  </si>
+  <si>
+    <t>20:56:18</t>
+  </si>
+  <si>
+    <t>22:33:23</t>
+  </si>
+  <si>
+    <t>03:29:43</t>
+  </si>
+  <si>
+    <t>05:07:34</t>
+  </si>
+  <si>
+    <t>21:47:05</t>
+  </si>
+  <si>
+    <t>02:42:52</t>
+  </si>
+  <si>
+    <t>04:21:16</t>
+  </si>
+  <si>
+    <t>21:00:42</t>
   </si>
   <si>
     <t>0°</t>
@@ -553,40 +562,40 @@
     <t>3°</t>
   </si>
   <si>
-    <t>16°</t>
-  </si>
-  <si>
-    <t>13°</t>
-  </si>
-  <si>
-    <t>01:32:33</t>
-  </si>
-  <si>
-    <t>21:28:53</t>
-  </si>
-  <si>
-    <t>20:49:10</t>
-  </si>
-  <si>
-    <t>22:22:32</t>
-  </si>
-  <si>
-    <t>21:42:28</t>
-  </si>
-  <si>
-    <t>23:15:45</t>
-  </si>
-  <si>
-    <t>04:07:05</t>
-  </si>
-  <si>
-    <t>22:33:54</t>
-  </si>
-  <si>
-    <t>03:26:43</t>
-  </si>
-  <si>
-    <t>05:00:04</t>
+    <t>15°</t>
+  </si>
+  <si>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>21:28:44</t>
+  </si>
+  <si>
+    <t>20:48:55</t>
+  </si>
+  <si>
+    <t>22:22:16</t>
+  </si>
+  <si>
+    <t>21:42:06</t>
+  </si>
+  <si>
+    <t>23:15:22</t>
+  </si>
+  <si>
+    <t>04:06:42</t>
+  </si>
+  <si>
+    <t>22:33:24</t>
+  </si>
+  <si>
+    <t>03:26:12</t>
+  </si>
+  <si>
+    <t>04:59:33</t>
+  </si>
+  <si>
+    <t>04:19:34</t>
   </si>
   <si>
     <t>B</t>
@@ -601,10 +610,10 @@
     <t>4</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>1</t>
@@ -641,7 +650,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -662,7 +671,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -674,19 +683,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -698,7 +701,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -710,13 +725,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -728,13 +743,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -775,7 +796,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -832,6 +853,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1235,7 +1262,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1313,55 +1340,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>86</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>181</v>
+        <v>64</v>
       </c>
       <c r="L2" s="4">
-        <v>-38.1</v>
+        <v>-37.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="O2" s="6">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="P2" s="7">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
       </c>
-      <c r="R2" s="8">
-        <v>0</v>
+      <c r="R2" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1369,55 +1396,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>66</v>
+        <v>175</v>
       </c>
       <c r="L3" s="4">
-        <v>-30.3</v>
+        <v>-7.1</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="O3" s="6">
-        <v>39</v>
-      </c>
-      <c r="P3" s="9">
-        <v>36</v>
+        <v>45</v>
+      </c>
+      <c r="P3" s="10">
+        <v>41</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
       </c>
       <c r="R3" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1425,55 +1452,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L4" s="4">
-        <v>-37.9</v>
+        <v>-24</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="O4" s="6">
-        <v>28</v>
-      </c>
-      <c r="P4" s="7">
-        <v>28</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="10">
-        <v>4</v>
+        <v>199</v>
+      </c>
+      <c r="O4" s="11">
+        <v>100</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>13</v>
+      </c>
+      <c r="R4" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1481,55 +1508,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>89</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>172</v>
+        <v>67</v>
       </c>
       <c r="L5" s="4">
-        <v>-7.1</v>
+        <v>-35.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O5" s="6">
-        <v>20</v>
+        <v>199</v>
+      </c>
+      <c r="O5" s="11">
+        <v>100</v>
       </c>
       <c r="P5" s="8">
         <v>0</v>
       </c>
-      <c r="Q5" s="8">
-        <v>0</v>
-      </c>
-      <c r="R5" s="11">
-        <v>12</v>
+      <c r="Q5" s="14">
+        <v>88</v>
+      </c>
+      <c r="R5" s="15">
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1537,55 +1564,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>90</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>69</v>
+        <v>175</v>
       </c>
       <c r="L6" s="4">
-        <v>-24</v>
+        <v>-15.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O6" s="12">
-        <v>99</v>
+        <v>198</v>
+      </c>
+      <c r="O6" s="16">
+        <v>0</v>
       </c>
       <c r="P6" s="8">
         <v>0</v>
       </c>
-      <c r="Q6" s="13">
-        <v>63</v>
-      </c>
-      <c r="R6" s="14">
-        <v>97</v>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1593,55 +1620,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>91</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>70</v>
+        <v>184</v>
       </c>
       <c r="L7" s="4">
-        <v>-35.5</v>
+        <v>-16.5</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O7" s="12">
-        <v>100</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="13">
-        <v>67</v>
-      </c>
-      <c r="R7" s="15">
-        <v>100</v>
+        <v>199</v>
+      </c>
+      <c r="O7" s="11">
+        <v>60</v>
+      </c>
+      <c r="P7" s="17">
+        <v>55</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
+      <c r="R7" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1649,49 +1676,49 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>92</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>172</v>
+        <v>70</v>
       </c>
       <c r="L8" s="4">
-        <v>-15.5</v>
+        <v>-30.9</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O8" s="16">
-        <v>15</v>
-      </c>
-      <c r="P8" s="8">
-        <v>0</v>
+        <v>199</v>
+      </c>
+      <c r="O8" s="11">
+        <v>51</v>
+      </c>
+      <c r="P8" s="18">
+        <v>51</v>
       </c>
       <c r="Q8" s="8">
         <v>0</v>
@@ -1705,49 +1732,49 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>93</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="L9" s="4">
-        <v>-16.5</v>
+        <v>-23.2</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O9" s="12">
-        <v>54</v>
-      </c>
-      <c r="P9" s="17">
-        <v>51</v>
+        <v>197</v>
+      </c>
+      <c r="O9" s="6">
+        <v>26</v>
+      </c>
+      <c r="P9" s="19">
+        <v>26</v>
       </c>
       <c r="Q9" s="8">
         <v>0</v>
@@ -1761,49 +1788,49 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>73</v>
+        <v>185</v>
       </c>
       <c r="L10" s="4">
-        <v>-30.9</v>
+        <v>-8.4</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O10" s="6">
-        <v>25</v>
-      </c>
-      <c r="P10" s="18">
-        <v>18</v>
+        <v>198</v>
+      </c>
+      <c r="O10" s="16">
+        <v>11</v>
+      </c>
+      <c r="P10" s="9">
+        <v>5</v>
       </c>
       <c r="Q10" s="8">
         <v>0</v>
@@ -1817,49 +1844,49 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>95</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="L11" s="4">
-        <v>-23.1</v>
+        <v>-24.8</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="O11" s="12">
-        <v>43</v>
-      </c>
-      <c r="P11" s="19">
-        <v>43</v>
+        <v>198</v>
+      </c>
+      <c r="O11" s="16">
+        <v>0</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0</v>
       </c>
       <c r="Q11" s="8">
         <v>0</v>
@@ -1873,49 +1900,49 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>96</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="L12" s="4">
-        <v>-8.4</v>
+        <v>-14.7</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O12" s="16">
-        <v>17</v>
-      </c>
-      <c r="P12" s="11">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0</v>
       </c>
       <c r="Q12" s="8">
         <v>0</v>
@@ -1929,52 +1956,52 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>97</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="L13" s="4">
-        <v>-24.8</v>
+        <v>-17.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O13" s="16">
-        <v>9</v>
-      </c>
-      <c r="P13" s="11">
-        <v>8</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="O13" s="6">
+        <v>38</v>
+      </c>
+      <c r="P13" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>38</v>
       </c>
       <c r="R13" s="8">
         <v>0</v>
@@ -1985,49 +2012,49 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>98</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="L14" s="4">
-        <v>-14.7</v>
+        <v>-31.6</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O14" s="16">
-        <v>3</v>
-      </c>
-      <c r="P14" s="10">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="P14" s="8">
+        <v>0</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
@@ -2041,52 +2068,52 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>99</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L15" s="4">
-        <v>-17.6</v>
+        <v>-22.6</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O15" s="16">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="O15" s="11">
+        <v>75</v>
       </c>
       <c r="P15" s="8">
         <v>0</v>
       </c>
-      <c r="Q15" s="8">
-        <v>0</v>
+      <c r="Q15" s="9">
+        <v>3</v>
       </c>
       <c r="R15" s="8">
         <v>0</v>
@@ -2097,52 +2124,52 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>100</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="L16" s="4">
-        <v>-31.6</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="O16" s="16">
-        <v>0</v>
+        <v>198</v>
+      </c>
+      <c r="O16" s="11">
+        <v>72</v>
       </c>
       <c r="P16" s="8">
         <v>0</v>
       </c>
-      <c r="Q16" s="8">
-        <v>0</v>
+      <c r="Q16" s="17">
+        <v>54</v>
       </c>
       <c r="R16" s="8">
         <v>0</v>
@@ -2153,55 +2180,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>101</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="L17" s="4">
-        <v>-22.5</v>
+        <v>-25.6</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O17" s="16">
-        <v>0</v>
+        <v>198</v>
+      </c>
+      <c r="O17" s="11">
+        <v>58</v>
       </c>
       <c r="P17" s="8">
         <v>0</v>
       </c>
-      <c r="Q17" s="8">
-        <v>0</v>
-      </c>
-      <c r="R17" s="8">
-        <v>0</v>
+      <c r="Q17" s="20">
+        <v>46</v>
+      </c>
+      <c r="R17" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2209,52 +2236,52 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>102</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="L18" s="4">
-        <v>-9.300000000000001</v>
+        <v>-29.2</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O18" s="16">
-        <v>10</v>
+        <v>198</v>
+      </c>
+      <c r="O18" s="11">
+        <v>64</v>
       </c>
       <c r="P18" s="8">
         <v>0</v>
       </c>
-      <c r="Q18" s="8">
-        <v>1</v>
+      <c r="Q18" s="20">
+        <v>44</v>
       </c>
       <c r="R18" s="8">
         <v>0</v>
@@ -2265,52 +2292,52 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>103</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="L19" s="4">
-        <v>-25.7</v>
+        <v>-14.1</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O19" s="16">
-        <v>9</v>
+        <v>198</v>
+      </c>
+      <c r="O19" s="11">
+        <v>62</v>
       </c>
       <c r="P19" s="8">
         <v>0</v>
       </c>
-      <c r="Q19" s="8">
-        <v>0</v>
+      <c r="Q19" s="21">
+        <v>20</v>
       </c>
       <c r="R19" s="8">
         <v>0</v>
@@ -2327,40 +2354,40 @@
         <v>57</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>104</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="L20" s="4">
-        <v>-29.1</v>
+        <v>-18.2</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O20" s="16">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="P20" s="8">
         <v>0</v>
@@ -2377,46 +2404,46 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>105</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="L21" s="4">
-        <v>-14</v>
+        <v>-34.5</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="O21" s="16">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P21" s="8">
         <v>0</v>
@@ -2433,7 +2460,7 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>59</v>
@@ -2442,37 +2469,37 @@
         <v>60</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>106</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="L22" s="4">
-        <v>-18.4</v>
+        <v>-21.8</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="O22" s="16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P22" s="8">
         <v>0</v>
@@ -2481,66 +2508,122 @@
         <v>0</v>
       </c>
       <c r="R22" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="2">
+        <v>29</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="L23" s="4">
+        <v>-10</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="O23" s="16">
+        <v>0</v>
+      </c>
+      <c r="P23" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>0</v>
+      </c>
+      <c r="R23" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A22">
+  <conditionalFormatting sqref="A2:A23">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B22">
+  <conditionalFormatting sqref="B2:B23">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C22">
+  <conditionalFormatting sqref="C2:C23">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D22">
+  <conditionalFormatting sqref="D2:D23">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E22">
+  <conditionalFormatting sqref="E2:E23">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F22">
+  <conditionalFormatting sqref="F2:F23">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G22">
+  <conditionalFormatting sqref="G2:G23">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H22">
+  <conditionalFormatting sqref="H2:H23">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I22">
+  <conditionalFormatting sqref="I2:I23">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J22">
+  <conditionalFormatting sqref="J2:J23">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K22">
+  <conditionalFormatting sqref="K2:K23">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L22">
+  <conditionalFormatting sqref="L2:L23">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2559,12 +2642,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M22">
+  <conditionalFormatting sqref="M2:M23">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N22">
+  <conditionalFormatting sqref="N2:N23">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2581,22 +2664,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O22">
+  <conditionalFormatting sqref="O2:O23">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P22">
+  <conditionalFormatting sqref="P2:P23">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q22">
+  <conditionalFormatting sqref="Q2:Q23">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R22">
+  <conditionalFormatting sqref="R2:R23">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="186">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260626--01</t>
-  </si>
-  <si>
-    <t>20260626--02</t>
-  </si>
-  <si>
-    <t>20260626--03</t>
-  </si>
-  <si>
-    <t>20260626--04</t>
-  </si>
-  <si>
     <t>20260627--01</t>
   </si>
   <si>
@@ -136,421 +124,391 @@
     <t>20260702--03</t>
   </si>
   <si>
-    <t>03:47</t>
-  </si>
-  <si>
-    <t>05:24</t>
+    <t>20260703--01</t>
+  </si>
+  <si>
+    <t>20260703--02</t>
+  </si>
+  <si>
+    <t>04:17</t>
+  </si>
+  <si>
+    <t>05:41</t>
+  </si>
+  <si>
+    <t>05:51</t>
+  </si>
+  <si>
+    <t>02:36</t>
+  </si>
+  <si>
+    <t>04:13</t>
   </si>
   <si>
     <t>06:25</t>
   </si>
   <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>04:18</t>
-  </si>
-  <si>
-    <t>05:41</t>
-  </si>
-  <si>
-    <t>05:51</t>
-  </si>
-  <si>
-    <t>02:36</t>
-  </si>
-  <si>
-    <t>04:13</t>
+    <t>06:31</t>
+  </si>
+  <si>
+    <t>06:41</t>
+  </si>
+  <si>
+    <t>02:07</t>
+  </si>
+  <si>
+    <t>05:59</t>
+  </si>
+  <si>
+    <t>04:01</t>
+  </si>
+  <si>
+    <t>05:11</t>
   </si>
   <si>
     <t>06:24</t>
   </si>
   <si>
-    <t>06:31</t>
-  </si>
-  <si>
-    <t>06:42</t>
-  </si>
-  <si>
-    <t>02:08</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>06:41</t>
-  </si>
-  <si>
-    <t>04:02</t>
-  </si>
-  <si>
-    <t>05:10</t>
-  </si>
-  <si>
-    <t>05:11</t>
-  </si>
-  <si>
     <t>03:58</t>
   </si>
   <si>
     <t>06:44</t>
   </si>
   <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:43</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
     <t>01:59</t>
   </si>
   <si>
-    <t>01:20</t>
+    <t>01:18</t>
   </si>
   <si>
     <t>01:02</t>
   </si>
   <si>
-    <t>00:37:28</t>
-  </si>
-  <si>
-    <t>05:33:14</t>
-  </si>
-  <si>
-    <t>22:13:03</t>
-  </si>
-  <si>
-    <t>23:50:59</t>
+    <t>05:52</t>
   </si>
   <si>
     <t>04:47:16</t>
   </si>
   <si>
-    <t>21:27:12</t>
-  </si>
-  <si>
-    <t>23:04:32</t>
-  </si>
-  <si>
-    <t>04:01:13</t>
-  </si>
-  <si>
-    <t>20:41:27</t>
-  </si>
-  <si>
-    <t>22:18:06</t>
-  </si>
-  <si>
-    <t>04:52:02</t>
-  </si>
-  <si>
-    <t>21:31:44</t>
-  </si>
-  <si>
-    <t>23:10:36</t>
-  </si>
-  <si>
-    <t>04:05:50</t>
-  </si>
-  <si>
-    <t>20:45:24</t>
-  </si>
-  <si>
-    <t>22:23:46</t>
-  </si>
-  <si>
-    <t>03:19:34</t>
-  </si>
-  <si>
-    <t>04:56:50</t>
-  </si>
-  <si>
-    <t>21:36:57</t>
-  </si>
-  <si>
-    <t>02:33:15</t>
-  </si>
-  <si>
-    <t>04:10:20</t>
-  </si>
-  <si>
-    <t>20:50:09</t>
-  </si>
-  <si>
-    <t>00:40:20</t>
-  </si>
-  <si>
-    <t>05:35:40</t>
-  </si>
-  <si>
-    <t>22:15:12</t>
-  </si>
-  <si>
-    <t>23:53:30</t>
-  </si>
-  <si>
-    <t>04:50:00</t>
-  </si>
-  <si>
-    <t>21:29:30</t>
-  </si>
-  <si>
-    <t>23:06:50</t>
-  </si>
-  <si>
-    <t>04:04:31</t>
-  </si>
-  <si>
-    <t>20:44:08</t>
-  </si>
-  <si>
-    <t>22:20:17</t>
-  </si>
-  <si>
-    <t>04:54:13</t>
-  </si>
-  <si>
-    <t>21:33:50</t>
-  </si>
-  <si>
-    <t>23:14:02</t>
-  </si>
-  <si>
-    <t>04:08:07</t>
-  </si>
-  <si>
-    <t>20:47:30</t>
-  </si>
-  <si>
-    <t>22:26:33</t>
-  </si>
-  <si>
-    <t>03:22:04</t>
-  </si>
-  <si>
-    <t>04:59:00</t>
-  </si>
-  <si>
-    <t>21:39:25</t>
-  </si>
-  <si>
-    <t>02:36:05</t>
-  </si>
-  <si>
-    <t>04:12:26</t>
-  </si>
-  <si>
-    <t>20:52:25</t>
-  </si>
-  <si>
-    <t>00:42:13</t>
-  </si>
-  <si>
-    <t>05:38:22</t>
-  </si>
-  <si>
-    <t>22:18:24</t>
-  </si>
-  <si>
-    <t>23:56:00</t>
+    <t>21:27:13</t>
+  </si>
+  <si>
+    <t>23:04:34</t>
+  </si>
+  <si>
+    <t>04:01:15</t>
+  </si>
+  <si>
+    <t>20:41:30</t>
+  </si>
+  <si>
+    <t>22:18:10</t>
+  </si>
+  <si>
+    <t>04:52:06</t>
+  </si>
+  <si>
+    <t>21:31:49</t>
+  </si>
+  <si>
+    <t>23:10:42</t>
+  </si>
+  <si>
+    <t>04:05:56</t>
+  </si>
+  <si>
+    <t>20:45:33</t>
+  </si>
+  <si>
+    <t>22:23:55</t>
+  </si>
+  <si>
+    <t>03:19:44</t>
+  </si>
+  <si>
+    <t>04:57:00</t>
+  </si>
+  <si>
+    <t>21:37:10</t>
+  </si>
+  <si>
+    <t>02:33:29</t>
+  </si>
+  <si>
+    <t>04:10:34</t>
+  </si>
+  <si>
+    <t>20:50:27</t>
+  </si>
+  <si>
+    <t>01:47:10</t>
+  </si>
+  <si>
+    <t>03:24:08</t>
+  </si>
+  <si>
+    <t>04:50:01</t>
+  </si>
+  <si>
+    <t>21:29:32</t>
+  </si>
+  <si>
+    <t>23:06:52</t>
+  </si>
+  <si>
+    <t>04:04:33</t>
+  </si>
+  <si>
+    <t>20:44:11</t>
+  </si>
+  <si>
+    <t>22:20:20</t>
+  </si>
+  <si>
+    <t>04:54:17</t>
+  </si>
+  <si>
+    <t>21:33:56</t>
+  </si>
+  <si>
+    <t>23:14:09</t>
+  </si>
+  <si>
+    <t>04:08:14</t>
+  </si>
+  <si>
+    <t>20:47:39</t>
+  </si>
+  <si>
+    <t>22:26:43</t>
+  </si>
+  <si>
+    <t>03:22:13</t>
+  </si>
+  <si>
+    <t>04:59:10</t>
+  </si>
+  <si>
+    <t>21:39:38</t>
+  </si>
+  <si>
+    <t>02:36:19</t>
+  </si>
+  <si>
+    <t>04:12:40</t>
+  </si>
+  <si>
+    <t>20:52:43</t>
+  </si>
+  <si>
+    <t>01:50:41</t>
+  </si>
+  <si>
+    <t>03:26:15</t>
   </si>
   <si>
     <t>04:52:09</t>
   </si>
   <si>
-    <t>21:32:20</t>
-  </si>
-  <si>
-    <t>23:09:45</t>
-  </si>
-  <si>
-    <t>04:05:49</t>
-  </si>
-  <si>
-    <t>20:46:14</t>
-  </si>
-  <si>
-    <t>22:23:29</t>
-  </si>
-  <si>
-    <t>04:57:28</t>
-  </si>
-  <si>
-    <t>21:37:10</t>
-  </si>
-  <si>
-    <t>23:15:06</t>
-  </si>
-  <si>
-    <t>04:11:07</t>
-  </si>
-  <si>
-    <t>20:50:50</t>
-  </si>
-  <si>
-    <t>22:28:34</t>
-  </si>
-  <si>
-    <t>03:24:39</t>
-  </si>
-  <si>
-    <t>05:02:12</t>
-  </si>
-  <si>
-    <t>21:42:00</t>
-  </si>
-  <si>
-    <t>02:38:04</t>
-  </si>
-  <si>
-    <t>04:15:48</t>
-  </si>
-  <si>
-    <t>20:55:25</t>
-  </si>
-  <si>
-    <t>00:44:07</t>
-  </si>
-  <si>
-    <t>05:41:04</t>
-  </si>
-  <si>
-    <t>22:21:37</t>
-  </si>
-  <si>
-    <t>23:58:30</t>
+    <t>21:32:22</t>
+  </si>
+  <si>
+    <t>23:09:46</t>
+  </si>
+  <si>
+    <t>04:05:51</t>
+  </si>
+  <si>
+    <t>20:46:17</t>
+  </si>
+  <si>
+    <t>22:23:32</t>
+  </si>
+  <si>
+    <t>04:57:32</t>
+  </si>
+  <si>
+    <t>21:37:16</t>
+  </si>
+  <si>
+    <t>23:15:12</t>
+  </si>
+  <si>
+    <t>04:11:13</t>
+  </si>
+  <si>
+    <t>20:50:59</t>
+  </si>
+  <si>
+    <t>22:28:43</t>
+  </si>
+  <si>
+    <t>03:24:49</t>
+  </si>
+  <si>
+    <t>05:02:22</t>
+  </si>
+  <si>
+    <t>21:42:13</t>
+  </si>
+  <si>
+    <t>02:38:18</t>
+  </si>
+  <si>
+    <t>04:16:02</t>
+  </si>
+  <si>
+    <t>20:55:42</t>
+  </si>
+  <si>
+    <t>01:51:41</t>
+  </si>
+  <si>
+    <t>03:29:37</t>
   </si>
   <si>
     <t>04:54:18</t>
   </si>
   <si>
-    <t>21:35:11</t>
-  </si>
-  <si>
-    <t>23:12:41</t>
-  </si>
-  <si>
-    <t>04:07:07</t>
-  </si>
-  <si>
-    <t>20:48:21</t>
-  </si>
-  <si>
-    <t>22:26:41</t>
-  </si>
-  <si>
-    <t>05:00:44</t>
-  </si>
-  <si>
-    <t>21:40:32</t>
-  </si>
-  <si>
-    <t>23:16:10</t>
-  </si>
-  <si>
-    <t>04:14:07</t>
-  </si>
-  <si>
-    <t>20:54:11</t>
-  </si>
-  <si>
-    <t>22:30:35</t>
-  </si>
-  <si>
-    <t>03:27:14</t>
-  </si>
-  <si>
-    <t>05:05:24</t>
-  </si>
-  <si>
-    <t>21:44:36</t>
-  </si>
-  <si>
-    <t>02:40:03</t>
-  </si>
-  <si>
-    <t>04:19:10</t>
-  </si>
-  <si>
-    <t>20:58:25</t>
-  </si>
-  <si>
-    <t>00:47:00</t>
-  </si>
-  <si>
-    <t>05:43:31</t>
-  </si>
-  <si>
-    <t>22:23:47</t>
-  </si>
-  <si>
-    <t>00:01:03</t>
-  </si>
-  <si>
-    <t>04:57:02</t>
-  </si>
-  <si>
-    <t>21:37:30</t>
-  </si>
-  <si>
-    <t>23:15:00</t>
-  </si>
-  <si>
-    <t>04:10:25</t>
-  </si>
-  <si>
-    <t>20:51:02</t>
-  </si>
-  <si>
-    <t>22:28:53</t>
-  </si>
-  <si>
-    <t>05:02:54</t>
-  </si>
-  <si>
-    <t>21:42:39</t>
-  </si>
-  <si>
-    <t>23:19:38</t>
-  </si>
-  <si>
-    <t>04:16:24</t>
-  </si>
-  <si>
-    <t>20:56:18</t>
-  </si>
-  <si>
-    <t>22:33:23</t>
-  </si>
-  <si>
-    <t>03:29:43</t>
-  </si>
-  <si>
-    <t>05:07:34</t>
-  </si>
-  <si>
-    <t>21:47:05</t>
-  </si>
-  <si>
-    <t>02:42:52</t>
-  </si>
-  <si>
-    <t>04:21:16</t>
-  </si>
-  <si>
-    <t>21:00:42</t>
+    <t>21:35:13</t>
+  </si>
+  <si>
+    <t>23:12:43</t>
+  </si>
+  <si>
+    <t>04:07:09</t>
+  </si>
+  <si>
+    <t>20:48:24</t>
+  </si>
+  <si>
+    <t>22:26:45</t>
+  </si>
+  <si>
+    <t>05:00:48</t>
+  </si>
+  <si>
+    <t>21:40:37</t>
+  </si>
+  <si>
+    <t>23:16:16</t>
+  </si>
+  <si>
+    <t>04:14:13</t>
+  </si>
+  <si>
+    <t>20:54:20</t>
+  </si>
+  <si>
+    <t>22:30:44</t>
+  </si>
+  <si>
+    <t>03:27:24</t>
+  </si>
+  <si>
+    <t>05:05:34</t>
+  </si>
+  <si>
+    <t>21:44:49</t>
+  </si>
+  <si>
+    <t>02:40:17</t>
+  </si>
+  <si>
+    <t>04:19:24</t>
+  </si>
+  <si>
+    <t>20:58:42</t>
+  </si>
+  <si>
+    <t>01:52:41</t>
+  </si>
+  <si>
+    <t>03:32:58</t>
+  </si>
+  <si>
+    <t>04:57:03</t>
+  </si>
+  <si>
+    <t>21:37:32</t>
+  </si>
+  <si>
+    <t>23:15:02</t>
+  </si>
+  <si>
+    <t>04:10:26</t>
+  </si>
+  <si>
+    <t>20:51:05</t>
+  </si>
+  <si>
+    <t>22:28:56</t>
+  </si>
+  <si>
+    <t>05:02:58</t>
+  </si>
+  <si>
+    <t>21:42:45</t>
+  </si>
+  <si>
+    <t>23:19:44</t>
+  </si>
+  <si>
+    <t>04:16:30</t>
+  </si>
+  <si>
+    <t>20:56:27</t>
+  </si>
+  <si>
+    <t>22:33:32</t>
+  </si>
+  <si>
+    <t>03:29:53</t>
+  </si>
+  <si>
+    <t>05:07:44</t>
+  </si>
+  <si>
+    <t>21:47:18</t>
+  </si>
+  <si>
+    <t>02:43:06</t>
+  </si>
+  <si>
+    <t>04:21:31</t>
+  </si>
+  <si>
+    <t>21:00:59</t>
+  </si>
+  <si>
+    <t>01:56:11</t>
+  </si>
+  <si>
+    <t>03:35:05</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>6°</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>6°</t>
-  </si>
-  <si>
     <t>8°</t>
   </si>
   <si>
-    <t>29°</t>
+    <t>28°</t>
   </si>
   <si>
     <t>2°</t>
@@ -568,52 +526,49 @@
     <t>14°</t>
   </si>
   <si>
-    <t>21:28:44</t>
-  </si>
-  <si>
-    <t>20:48:55</t>
-  </si>
-  <si>
-    <t>22:22:16</t>
-  </si>
-  <si>
-    <t>21:42:06</t>
-  </si>
-  <si>
-    <t>23:15:22</t>
-  </si>
-  <si>
-    <t>04:06:42</t>
-  </si>
-  <si>
-    <t>22:33:24</t>
-  </si>
-  <si>
-    <t>03:26:12</t>
-  </si>
-  <si>
-    <t>04:59:33</t>
-  </si>
-  <si>
-    <t>04:19:34</t>
+    <t>21:28:45</t>
+  </si>
+  <si>
+    <t>20:48:58</t>
+  </si>
+  <si>
+    <t>22:22:19</t>
+  </si>
+  <si>
+    <t>21:42:11</t>
+  </si>
+  <si>
+    <t>23:15:27</t>
+  </si>
+  <si>
+    <t>04:06:49</t>
+  </si>
+  <si>
+    <t>03:26:22</t>
+  </si>
+  <si>
+    <t>04:59:42</t>
+  </si>
+  <si>
+    <t>04:19:47</t>
+  </si>
+  <si>
+    <t>A+B</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>A+B</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>1</t>
@@ -650,7 +605,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -671,7 +626,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -683,7 +638,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -695,67 +674,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -796,7 +733,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -850,15 +787,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1262,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1340,55 +1268,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="F2" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>64</v>
+        <v>160</v>
       </c>
       <c r="L2" s="4">
-        <v>-37.9</v>
+        <v>-15.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="O2" s="6">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="P2" s="7">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
       </c>
-      <c r="R2" s="9">
-        <v>3</v>
+      <c r="R2" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1396,49 +1324,49 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-16.5</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="O3" s="9">
+        <v>62</v>
+      </c>
+      <c r="P3" s="10">
         <v>60</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-7.1</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O3" s="6">
-        <v>45</v>
-      </c>
-      <c r="P3" s="10">
-        <v>41</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1452,55 +1380,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L4" s="4">
-        <v>-24</v>
+        <v>-30.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="O4" s="11">
-        <v>100</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="12">
-        <v>13</v>
-      </c>
-      <c r="R4" s="13">
-        <v>100</v>
+        <v>183</v>
+      </c>
+      <c r="O4" s="9">
+        <v>62</v>
+      </c>
+      <c r="P4" s="10">
+        <v>62</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1508,55 +1436,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>67</v>
+        <v>160</v>
       </c>
       <c r="L5" s="4">
-        <v>-35.4</v>
+        <v>-23.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="O5" s="11">
-        <v>100</v>
-      </c>
-      <c r="P5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="14">
-        <v>88</v>
-      </c>
-      <c r="R5" s="15">
-        <v>97</v>
+        <v>184</v>
+      </c>
+      <c r="O5" s="6">
+        <v>31</v>
+      </c>
+      <c r="P5" s="7">
+        <v>31</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="R5" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1567,46 +1495,46 @@
         <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="L6" s="4">
-        <v>-15.5</v>
+        <v>-8.4</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O6" s="16">
-        <v>0</v>
+        <v>182</v>
+      </c>
+      <c r="O6" s="11">
+        <v>15</v>
       </c>
       <c r="P6" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="8">
         <v>0</v>
@@ -1620,49 +1548,49 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="L7" s="4">
-        <v>-16.5</v>
+        <v>-24.8</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="O7" s="11">
-        <v>60</v>
-      </c>
-      <c r="P7" s="17">
-        <v>55</v>
+        <v>2</v>
+      </c>
+      <c r="P7" s="8">
+        <v>2</v>
       </c>
       <c r="Q7" s="8">
         <v>0</v>
@@ -1676,49 +1604,49 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="L8" s="4">
-        <v>-30.9</v>
+        <v>-14.7</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="O8" s="11">
-        <v>51</v>
-      </c>
-      <c r="P8" s="18">
-        <v>51</v>
+        <v>182</v>
+      </c>
+      <c r="O8" s="6">
+        <v>5</v>
+      </c>
+      <c r="P8" s="12">
+        <v>5</v>
       </c>
       <c r="Q8" s="8">
         <v>0</v>
@@ -1732,52 +1660,52 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L9" s="4">
-        <v>-23.2</v>
+        <v>-17.5</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O9" s="6">
-        <v>26</v>
-      </c>
-      <c r="P9" s="19">
-        <v>26</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0</v>
+        <v>185</v>
+      </c>
+      <c r="O9" s="9">
+        <v>73</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>58</v>
       </c>
       <c r="R9" s="8">
         <v>0</v>
@@ -1788,52 +1716,52 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="L10" s="4">
-        <v>-8.4</v>
+        <v>-31.6</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O10" s="16">
-        <v>11</v>
-      </c>
-      <c r="P10" s="9">
-        <v>5</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>0</v>
+        <v>184</v>
+      </c>
+      <c r="O10" s="6">
+        <v>28</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="13">
+        <v>20</v>
       </c>
       <c r="R10" s="8">
         <v>0</v>
@@ -1844,55 +1772,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>29</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-22.6</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="O11" s="6">
+        <v>48</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="14">
         <v>41</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="L11" s="4">
-        <v>-24.8</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O11" s="16">
-        <v>0</v>
-      </c>
-      <c r="P11" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>0</v>
-      </c>
       <c r="R11" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1900,55 +1828,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="L12" s="4">
-        <v>-14.7</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O12" s="16">
-        <v>0</v>
+        <v>182</v>
+      </c>
+      <c r="O12" s="9">
+        <v>82</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
       </c>
-      <c r="Q12" s="8">
-        <v>0</v>
-      </c>
-      <c r="R12" s="8">
-        <v>0</v>
+      <c r="Q12" s="10">
+        <v>62</v>
+      </c>
+      <c r="R12" s="15">
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1956,55 +1884,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>187</v>
+        <v>151</v>
       </c>
       <c r="L13" s="4">
-        <v>-17.5</v>
+        <v>-25.7</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O13" s="6">
-        <v>38</v>
+        <v>182</v>
+      </c>
+      <c r="O13" s="9">
+        <v>94</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
       </c>
-      <c r="Q13" s="10">
-        <v>38</v>
-      </c>
-      <c r="R13" s="8">
-        <v>0</v>
+      <c r="Q13" s="16">
+        <v>82</v>
+      </c>
+      <c r="R13" s="15">
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2012,55 +1940,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="L14" s="4">
-        <v>-31.6</v>
+        <v>-29.1</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O14" s="16">
-        <v>0</v>
+        <v>182</v>
+      </c>
+      <c r="O14" s="9">
+        <v>93</v>
       </c>
       <c r="P14" s="8">
         <v>0</v>
       </c>
-      <c r="Q14" s="8">
-        <v>0</v>
-      </c>
-      <c r="R14" s="8">
-        <v>0</v>
+      <c r="Q14" s="17">
+        <v>87</v>
+      </c>
+      <c r="R14" s="18">
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2068,55 +1996,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="L15" s="4">
-        <v>-22.6</v>
+        <v>-14.1</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O15" s="11">
-        <v>75</v>
+        <v>182</v>
+      </c>
+      <c r="O15" s="6">
+        <v>39</v>
       </c>
       <c r="P15" s="8">
         <v>0</v>
       </c>
-      <c r="Q15" s="9">
-        <v>3</v>
-      </c>
-      <c r="R15" s="8">
-        <v>0</v>
+      <c r="Q15" s="13">
+        <v>18</v>
+      </c>
+      <c r="R15" s="14">
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2124,55 +2052,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="L16" s="4">
-        <v>-9.199999999999999</v>
+        <v>-18.3</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O16" s="11">
-        <v>72</v>
+        <v>182</v>
+      </c>
+      <c r="O16" s="6">
+        <v>26</v>
       </c>
       <c r="P16" s="8">
         <v>0</v>
       </c>
-      <c r="Q16" s="17">
-        <v>54</v>
+      <c r="Q16" s="8">
+        <v>2</v>
       </c>
       <c r="R16" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2183,52 +2111,52 @@
         <v>15</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>190</v>
+        <v>75</v>
       </c>
       <c r="L17" s="4">
-        <v>-25.6</v>
+        <v>-34.4</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="O17" s="11">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="P17" s="8">
         <v>0</v>
       </c>
-      <c r="Q17" s="20">
-        <v>46</v>
-      </c>
-      <c r="R17" s="9">
-        <v>3</v>
+      <c r="Q17" s="8">
+        <v>0</v>
+      </c>
+      <c r="R17" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2236,52 +2164,52 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="L18" s="4">
-        <v>-29.2</v>
+        <v>-21.8</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="O18" s="11">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="P18" s="8">
         <v>0</v>
       </c>
-      <c r="Q18" s="20">
-        <v>44</v>
+      <c r="Q18" s="8">
+        <v>0</v>
       </c>
       <c r="R18" s="8">
         <v>0</v>
@@ -2292,52 +2220,52 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="L19" s="4">
-        <v>-14.1</v>
+        <v>-10.1</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="O19" s="11">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="P19" s="8">
         <v>0</v>
       </c>
-      <c r="Q19" s="21">
-        <v>20</v>
+      <c r="Q19" s="8">
+        <v>0</v>
       </c>
       <c r="R19" s="8">
         <v>0</v>
@@ -2348,46 +2276,46 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="L20" s="4">
-        <v>-18.2</v>
+        <v>-37.8</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O20" s="16">
-        <v>1</v>
+        <v>184</v>
+      </c>
+      <c r="O20" s="11">
+        <v>9</v>
       </c>
       <c r="P20" s="8">
         <v>0</v>
@@ -2404,46 +2332,46 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L21" s="4">
-        <v>-34.5</v>
+        <v>-28.7</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="O21" s="16">
-        <v>0</v>
+        <v>183</v>
+      </c>
+      <c r="O21" s="6">
+        <v>31</v>
       </c>
       <c r="P21" s="8">
         <v>0</v>
@@ -2452,178 +2380,66 @@
         <v>0</v>
       </c>
       <c r="R21" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
-      <c r="A22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="2">
-        <v>72</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="L22" s="4">
-        <v>-21.8</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="O22" s="16">
-        <v>0</v>
-      </c>
-      <c r="P22" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="8">
-        <v>0</v>
-      </c>
-      <c r="R22" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="A23" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="2">
-        <v>29</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="L23" s="4">
-        <v>-10</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O23" s="16">
-        <v>0</v>
-      </c>
-      <c r="P23" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>0</v>
-      </c>
-      <c r="R23" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A23">
+  <conditionalFormatting sqref="A2:A21">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B23">
+  <conditionalFormatting sqref="B2:B21">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C23">
+  <conditionalFormatting sqref="C2:C21">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D23">
+  <conditionalFormatting sqref="D2:D21">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E23">
+  <conditionalFormatting sqref="E2:E21">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F23">
+  <conditionalFormatting sqref="F2:F21">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G23">
+  <conditionalFormatting sqref="G2:G21">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H23">
+  <conditionalFormatting sqref="H2:H21">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I23">
+  <conditionalFormatting sqref="I2:I21">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J23">
+  <conditionalFormatting sqref="J2:J21">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K23">
+  <conditionalFormatting sqref="K2:K21">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L23">
+  <conditionalFormatting sqref="L2:L21">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2642,12 +2458,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M23">
+  <conditionalFormatting sqref="M2:M21">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N23">
+  <conditionalFormatting sqref="N2:N21">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2664,22 +2480,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O23">
+  <conditionalFormatting sqref="O2:O21">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P23">
+  <conditionalFormatting sqref="P2:P21">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q23">
+  <conditionalFormatting sqref="Q2:Q21">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R23">
+  <conditionalFormatting sqref="R2:R21">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="184">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260627--01</t>
-  </si>
-  <si>
-    <t>20260627--02</t>
-  </si>
-  <si>
-    <t>20260627--03</t>
-  </si>
-  <si>
     <t>20260628--01</t>
   </si>
   <si>
@@ -130,13 +121,13 @@
     <t>20260703--02</t>
   </si>
   <si>
-    <t>04:17</t>
-  </si>
-  <si>
-    <t>05:41</t>
-  </si>
-  <si>
-    <t>05:51</t>
+    <t>20260704--01</t>
+  </si>
+  <si>
+    <t>20260704--02</t>
+  </si>
+  <si>
+    <t>20260704--03</t>
   </si>
   <si>
     <t>02:36</t>
@@ -145,7 +136,7 @@
     <t>04:13</t>
   </si>
   <si>
-    <t>06:25</t>
+    <t>06:24</t>
   </si>
   <si>
     <t>06:31</t>
@@ -160,16 +151,16 @@
     <t>05:59</t>
   </si>
   <si>
-    <t>04:01</t>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>04:00</t>
   </si>
   <si>
     <t>05:11</t>
   </si>
   <si>
-    <t>06:24</t>
-  </si>
-  <si>
-    <t>03:58</t>
+    <t>03:59</t>
   </si>
   <si>
     <t>06:44</t>
@@ -178,33 +169,33 @@
     <t>02:00</t>
   </si>
   <si>
-    <t>06:43</t>
+    <t>06:42</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>04:24</t>
+  </si>
+  <si>
+    <t>02:40</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:59</t>
+    <t>01:58</t>
   </si>
   <si>
     <t>01:18</t>
   </si>
   <si>
-    <t>01:02</t>
+    <t>01:03</t>
   </si>
   <si>
     <t>05:52</t>
   </si>
   <si>
-    <t>04:47:16</t>
-  </si>
-  <si>
-    <t>21:27:13</t>
-  </si>
-  <si>
-    <t>23:04:34</t>
-  </si>
-  <si>
     <t>04:01:15</t>
   </si>
   <si>
@@ -214,55 +205,55 @@
     <t>22:18:10</t>
   </si>
   <si>
-    <t>04:52:06</t>
-  </si>
-  <si>
-    <t>21:31:49</t>
-  </si>
-  <si>
-    <t>23:10:42</t>
-  </si>
-  <si>
-    <t>04:05:56</t>
-  </si>
-  <si>
-    <t>20:45:33</t>
-  </si>
-  <si>
-    <t>22:23:55</t>
-  </si>
-  <si>
-    <t>03:19:44</t>
-  </si>
-  <si>
-    <t>04:57:00</t>
-  </si>
-  <si>
-    <t>21:37:10</t>
-  </si>
-  <si>
-    <t>02:33:29</t>
-  </si>
-  <si>
-    <t>04:10:34</t>
-  </si>
-  <si>
-    <t>20:50:27</t>
-  </si>
-  <si>
-    <t>01:47:10</t>
-  </si>
-  <si>
-    <t>03:24:08</t>
-  </si>
-  <si>
-    <t>04:50:01</t>
-  </si>
-  <si>
-    <t>21:29:32</t>
-  </si>
-  <si>
-    <t>23:06:52</t>
+    <t>04:52:07</t>
+  </si>
+  <si>
+    <t>21:31:50</t>
+  </si>
+  <si>
+    <t>23:10:43</t>
+  </si>
+  <si>
+    <t>04:05:57</t>
+  </si>
+  <si>
+    <t>20:45:35</t>
+  </si>
+  <si>
+    <t>22:23:57</t>
+  </si>
+  <si>
+    <t>03:19:46</t>
+  </si>
+  <si>
+    <t>04:57:02</t>
+  </si>
+  <si>
+    <t>21:37:13</t>
+  </si>
+  <si>
+    <t>02:33:32</t>
+  </si>
+  <si>
+    <t>04:10:37</t>
+  </si>
+  <si>
+    <t>20:50:31</t>
+  </si>
+  <si>
+    <t>01:47:15</t>
+  </si>
+  <si>
+    <t>03:24:13</t>
+  </si>
+  <si>
+    <t>02:37:48</t>
+  </si>
+  <si>
+    <t>04:15:35</t>
+  </si>
+  <si>
+    <t>20:56:02</t>
   </si>
   <si>
     <t>04:04:33</t>
@@ -271,118 +262,118 @@
     <t>20:44:11</t>
   </si>
   <si>
-    <t>22:20:20</t>
+    <t>22:20:21</t>
   </si>
   <si>
     <t>04:54:17</t>
   </si>
   <si>
-    <t>21:33:56</t>
-  </si>
-  <si>
-    <t>23:14:09</t>
-  </si>
-  <si>
-    <t>04:08:14</t>
-  </si>
-  <si>
-    <t>20:47:39</t>
-  </si>
-  <si>
-    <t>22:26:43</t>
-  </si>
-  <si>
-    <t>03:22:13</t>
-  </si>
-  <si>
-    <t>04:59:10</t>
-  </si>
-  <si>
-    <t>21:39:38</t>
-  </si>
-  <si>
-    <t>02:36:19</t>
-  </si>
-  <si>
-    <t>04:12:40</t>
-  </si>
-  <si>
-    <t>20:52:43</t>
-  </si>
-  <si>
-    <t>01:50:41</t>
-  </si>
-  <si>
-    <t>03:26:15</t>
-  </si>
-  <si>
-    <t>04:52:09</t>
-  </si>
-  <si>
-    <t>21:32:22</t>
-  </si>
-  <si>
-    <t>23:09:46</t>
+    <t>21:33:57</t>
+  </si>
+  <si>
+    <t>23:14:10</t>
+  </si>
+  <si>
+    <t>04:08:15</t>
+  </si>
+  <si>
+    <t>20:47:41</t>
+  </si>
+  <si>
+    <t>22:26:45</t>
+  </si>
+  <si>
+    <t>03:22:15</t>
+  </si>
+  <si>
+    <t>04:59:12</t>
+  </si>
+  <si>
+    <t>21:39:41</t>
+  </si>
+  <si>
+    <t>02:36:21</t>
+  </si>
+  <si>
+    <t>04:12:43</t>
+  </si>
+  <si>
+    <t>20:52:47</t>
+  </si>
+  <si>
+    <t>01:50:45</t>
+  </si>
+  <si>
+    <t>03:26:20</t>
+  </si>
+  <si>
+    <t>02:40:00</t>
+  </si>
+  <si>
+    <t>04:18:14</t>
+  </si>
+  <si>
+    <t>20:59:17</t>
   </si>
   <si>
     <t>04:05:51</t>
   </si>
   <si>
-    <t>20:46:17</t>
-  </si>
-  <si>
-    <t>22:23:32</t>
-  </si>
-  <si>
-    <t>04:57:32</t>
-  </si>
-  <si>
-    <t>21:37:16</t>
-  </si>
-  <si>
-    <t>23:15:12</t>
-  </si>
-  <si>
-    <t>04:11:13</t>
-  </si>
-  <si>
-    <t>20:50:59</t>
-  </si>
-  <si>
-    <t>22:28:43</t>
-  </si>
-  <si>
-    <t>03:24:49</t>
-  </si>
-  <si>
-    <t>05:02:22</t>
-  </si>
-  <si>
-    <t>21:42:13</t>
-  </si>
-  <si>
-    <t>02:38:18</t>
-  </si>
-  <si>
-    <t>04:16:02</t>
-  </si>
-  <si>
-    <t>20:55:42</t>
-  </si>
-  <si>
-    <t>01:51:41</t>
-  </si>
-  <si>
-    <t>03:29:37</t>
-  </si>
-  <si>
-    <t>04:54:18</t>
-  </si>
-  <si>
-    <t>21:35:13</t>
-  </si>
-  <si>
-    <t>23:12:43</t>
+    <t>20:46:18</t>
+  </si>
+  <si>
+    <t>22:23:33</t>
+  </si>
+  <si>
+    <t>04:57:33</t>
+  </si>
+  <si>
+    <t>21:37:17</t>
+  </si>
+  <si>
+    <t>23:15:13</t>
+  </si>
+  <si>
+    <t>04:11:14</t>
+  </si>
+  <si>
+    <t>20:51:01</t>
+  </si>
+  <si>
+    <t>22:28:45</t>
+  </si>
+  <si>
+    <t>03:24:50</t>
+  </si>
+  <si>
+    <t>05:02:24</t>
+  </si>
+  <si>
+    <t>21:42:16</t>
+  </si>
+  <si>
+    <t>02:38:21</t>
+  </si>
+  <si>
+    <t>04:16:05</t>
+  </si>
+  <si>
+    <t>20:55:46</t>
+  </si>
+  <si>
+    <t>01:51:45</t>
+  </si>
+  <si>
+    <t>03:29:41</t>
+  </si>
+  <si>
+    <t>02:43:11</t>
+  </si>
+  <si>
+    <t>04:20:26</t>
+  </si>
+  <si>
+    <t>21:00:37</t>
   </si>
   <si>
     <t>04:07:09</t>
@@ -391,70 +382,67 @@
     <t>20:48:24</t>
   </si>
   <si>
-    <t>22:26:45</t>
-  </si>
-  <si>
     <t>05:00:48</t>
   </si>
   <si>
-    <t>21:40:37</t>
-  </si>
-  <si>
-    <t>23:16:16</t>
-  </si>
-  <si>
-    <t>04:14:13</t>
-  </si>
-  <si>
-    <t>20:54:20</t>
-  </si>
-  <si>
-    <t>22:30:44</t>
-  </si>
-  <si>
-    <t>03:27:24</t>
-  </si>
-  <si>
-    <t>05:05:34</t>
-  </si>
-  <si>
-    <t>21:44:49</t>
-  </si>
-  <si>
-    <t>02:40:17</t>
-  </si>
-  <si>
-    <t>04:19:24</t>
-  </si>
-  <si>
-    <t>20:58:42</t>
-  </si>
-  <si>
-    <t>01:52:41</t>
-  </si>
-  <si>
-    <t>03:32:58</t>
-  </si>
-  <si>
-    <t>04:57:03</t>
-  </si>
-  <si>
-    <t>21:37:32</t>
-  </si>
-  <si>
-    <t>23:15:02</t>
+    <t>21:40:38</t>
+  </si>
+  <si>
+    <t>23:16:17</t>
+  </si>
+  <si>
+    <t>04:14:14</t>
+  </si>
+  <si>
+    <t>20:54:21</t>
+  </si>
+  <si>
+    <t>22:30:45</t>
+  </si>
+  <si>
+    <t>03:27:26</t>
+  </si>
+  <si>
+    <t>05:05:36</t>
+  </si>
+  <si>
+    <t>21:44:52</t>
+  </si>
+  <si>
+    <t>02:40:20</t>
+  </si>
+  <si>
+    <t>04:19:27</t>
+  </si>
+  <si>
+    <t>20:58:46</t>
+  </si>
+  <si>
+    <t>01:52:45</t>
+  </si>
+  <si>
+    <t>03:33:02</t>
+  </si>
+  <si>
+    <t>02:46:23</t>
+  </si>
+  <si>
+    <t>04:22:38</t>
+  </si>
+  <si>
+    <t>21:01:57</t>
   </si>
   <si>
     <t>04:10:26</t>
   </si>
   <si>
-    <t>20:51:05</t>
+    <t>20:51:06</t>
   </si>
   <si>
     <t>22:28:56</t>
   </si>
   <si>
-    <t>05:02:58</t>
+    <t>05:02:59</t>
   </si>
   <si>
     <t>21:42:45</t>
@@ -463,72 +451,75 @@
     <t>23:19:44</t>
   </si>
   <si>
-    <t>04:16:30</t>
-  </si>
-  <si>
-    <t>20:56:27</t>
-  </si>
-  <si>
-    <t>22:33:32</t>
-  </si>
-  <si>
-    <t>03:29:53</t>
-  </si>
-  <si>
-    <t>05:07:44</t>
-  </si>
-  <si>
-    <t>21:47:18</t>
-  </si>
-  <si>
-    <t>02:43:06</t>
-  </si>
-  <si>
-    <t>04:21:31</t>
-  </si>
-  <si>
-    <t>21:00:59</t>
-  </si>
-  <si>
-    <t>01:56:11</t>
-  </si>
-  <si>
-    <t>03:35:05</t>
+    <t>04:16:31</t>
+  </si>
+  <si>
+    <t>20:56:28</t>
+  </si>
+  <si>
+    <t>22:33:34</t>
+  </si>
+  <si>
+    <t>03:29:55</t>
+  </si>
+  <si>
+    <t>05:07:46</t>
+  </si>
+  <si>
+    <t>21:47:21</t>
+  </si>
+  <si>
+    <t>02:43:09</t>
+  </si>
+  <si>
+    <t>04:21:34</t>
+  </si>
+  <si>
+    <t>21:01:03</t>
+  </si>
+  <si>
+    <t>01:56:16</t>
+  </si>
+  <si>
+    <t>03:35:09</t>
+  </si>
+  <si>
+    <t>02:48:35</t>
+  </si>
+  <si>
+    <t>04:25:17</t>
+  </si>
+  <si>
+    <t>21:05:13</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>6°</t>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>28°</t>
+  </si>
+  <si>
+    <t>2°</t>
+  </si>
+  <si>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>3°</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>28°</t>
-  </si>
-  <si>
-    <t>2°</t>
-  </si>
-  <si>
-    <t>11°</t>
-  </si>
-  <si>
-    <t>3°</t>
-  </si>
-  <si>
     <t>15°</t>
   </si>
   <si>
     <t>14°</t>
   </si>
   <si>
-    <t>21:28:45</t>
-  </si>
-  <si>
     <t>20:48:58</t>
   </si>
   <si>
@@ -538,40 +529,43 @@
     <t>21:42:11</t>
   </si>
   <si>
-    <t>23:15:27</t>
-  </si>
-  <si>
-    <t>04:06:49</t>
-  </si>
-  <si>
-    <t>03:26:22</t>
-  </si>
-  <si>
-    <t>04:59:42</t>
-  </si>
-  <si>
-    <t>04:19:47</t>
+    <t>23:15:28</t>
+  </si>
+  <si>
+    <t>04:06:50</t>
+  </si>
+  <si>
+    <t>22:33:33</t>
+  </si>
+  <si>
+    <t>03:26:23</t>
+  </si>
+  <si>
+    <t>04:59:44</t>
+  </si>
+  <si>
+    <t>04:19:50</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
-    <t>A</t>
+    <t>4</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
 </sst>
 </file>
@@ -605,7 +599,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -620,31 +614,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -662,37 +644,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -733,7 +709,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -778,15 +754,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1268,7 +1235,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>38</v>
@@ -1289,28 +1256,28 @@
         <v>120</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L2" s="4">
-        <v>-15.5</v>
+        <v>-23.1</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="O2" s="6">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="P2" s="7">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1324,13 +1291,13 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>61</v>
@@ -1345,28 +1312,28 @@
         <v>121</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="L3" s="4">
-        <v>-16.5</v>
+        <v>-8.4</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="O3" s="9">
-        <v>62</v>
-      </c>
-      <c r="P3" s="10">
-        <v>60</v>
+        <v>2</v>
+      </c>
+      <c r="P3" s="8">
+        <v>0</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1380,13 +1347,13 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>62</v>
@@ -1398,31 +1365,31 @@
         <v>102</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>62</v>
+        <v>169</v>
       </c>
       <c r="L4" s="4">
-        <v>-30.9</v>
+        <v>-24.8</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="O4" s="9">
-        <v>62</v>
-      </c>
-      <c r="P4" s="10">
-        <v>62</v>
+        <v>2</v>
+      </c>
+      <c r="P4" s="8">
+        <v>2</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
@@ -1436,7 +1403,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>41</v>
@@ -1454,31 +1421,31 @@
         <v>103</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L5" s="4">
-        <v>-23.1</v>
+        <v>-14.7</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O5" s="6">
-        <v>31</v>
-      </c>
-      <c r="P5" s="7">
-        <v>31</v>
+        <v>181</v>
+      </c>
+      <c r="O5" s="9">
+        <v>4</v>
+      </c>
+      <c r="P5" s="10">
+        <v>4</v>
       </c>
       <c r="Q5" s="8">
         <v>0</v>
@@ -1492,7 +1459,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>42</v>
@@ -1510,34 +1477,34 @@
         <v>104</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L6" s="4">
-        <v>-8.4</v>
+        <v>-17.6</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="O6" s="11">
-        <v>15</v>
+      <c r="O6" s="9">
+        <v>5</v>
       </c>
       <c r="P6" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>4</v>
       </c>
       <c r="R6" s="8">
         <v>0</v>
@@ -1548,13 +1515,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>65</v>
@@ -1566,34 +1533,34 @@
         <v>105</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L7" s="4">
-        <v>-24.8</v>
+        <v>-31.6</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="O7" s="11">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="P7" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="12">
+        <v>22</v>
       </c>
       <c r="R7" s="8">
         <v>0</v>
@@ -1604,13 +1571,13 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>66</v>
@@ -1622,34 +1589,34 @@
         <v>106</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="L8" s="4">
-        <v>-14.7</v>
+        <v>-22.6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>182</v>
       </c>
       <c r="O8" s="6">
-        <v>5</v>
-      </c>
-      <c r="P8" s="12">
-        <v>5</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>0</v>
+        <v>52</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>52</v>
       </c>
       <c r="R8" s="8">
         <v>0</v>
@@ -1666,7 +1633,7 @@
         <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>67</v>
@@ -1678,37 +1645,37 @@
         <v>107</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="L9" s="4">
-        <v>-17.5</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="M9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="N9" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="O9" s="9">
-        <v>73</v>
+      <c r="O9" s="6">
+        <v>57</v>
       </c>
       <c r="P9" s="8">
         <v>0</v>
       </c>
-      <c r="Q9" s="10">
-        <v>58</v>
-      </c>
-      <c r="R9" s="8">
-        <v>0</v>
+      <c r="Q9" s="14">
+        <v>36</v>
+      </c>
+      <c r="R9" s="10">
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1716,13 +1683,13 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>68</v>
@@ -1734,34 +1701,34 @@
         <v>108</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L10" s="4">
-        <v>-31.6</v>
+        <v>-25.7</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O10" s="6">
-        <v>28</v>
+        <v>181</v>
+      </c>
+      <c r="O10" s="11">
+        <v>19</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
       </c>
-      <c r="Q10" s="13">
-        <v>20</v>
+      <c r="Q10" s="15">
+        <v>14</v>
       </c>
       <c r="R10" s="8">
         <v>0</v>
@@ -1772,13 +1739,13 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>69</v>
@@ -1790,37 +1757,37 @@
         <v>109</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L11" s="4">
-        <v>-22.6</v>
+        <v>-29.1</v>
       </c>
       <c r="M11" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="N11" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="N11" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="O11" s="6">
-        <v>48</v>
+      <c r="O11" s="9">
+        <v>2</v>
       </c>
       <c r="P11" s="8">
         <v>0</v>
       </c>
-      <c r="Q11" s="14">
-        <v>41</v>
+      <c r="Q11" s="8">
+        <v>2</v>
       </c>
       <c r="R11" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1828,13 +1795,13 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>70</v>
@@ -1846,37 +1813,37 @@
         <v>110</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="L12" s="4">
-        <v>-9.199999999999999</v>
+        <v>-14</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O12" s="9">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
       </c>
-      <c r="Q12" s="10">
-        <v>62</v>
-      </c>
-      <c r="R12" s="15">
-        <v>72</v>
+      <c r="Q12" s="8">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1884,13 +1851,13 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>71</v>
@@ -1902,37 +1869,37 @@
         <v>111</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="L13" s="4">
-        <v>-25.7</v>
+        <v>-18.3</v>
       </c>
       <c r="M13" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="N13" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="N13" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="O13" s="9">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
       </c>
-      <c r="Q13" s="16">
-        <v>82</v>
-      </c>
-      <c r="R13" s="15">
-        <v>70</v>
+      <c r="Q13" s="8">
+        <v>1</v>
+      </c>
+      <c r="R13" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1940,13 +1907,13 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>72</v>
@@ -1958,37 +1925,37 @@
         <v>112</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>176</v>
+        <v>72</v>
       </c>
       <c r="L14" s="4">
-        <v>-29.1</v>
+        <v>-34.4</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>179</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O14" s="9">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="P14" s="8">
         <v>0</v>
       </c>
-      <c r="Q14" s="17">
-        <v>87</v>
-      </c>
-      <c r="R14" s="18">
-        <v>93</v>
+      <c r="Q14" s="8">
+        <v>0</v>
+      </c>
+      <c r="R14" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1996,13 +1963,13 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>73</v>
@@ -2014,37 +1981,37 @@
         <v>113</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L15" s="4">
-        <v>-14.1</v>
+        <v>-21.8</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>179</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O15" s="6">
-        <v>39</v>
+        <v>183</v>
+      </c>
+      <c r="O15" s="9">
+        <v>0</v>
       </c>
       <c r="P15" s="8">
         <v>0</v>
       </c>
-      <c r="Q15" s="13">
-        <v>18</v>
-      </c>
-      <c r="R15" s="14">
-        <v>38</v>
+      <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+      <c r="R15" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2052,10 +2019,10 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>55</v>
@@ -2070,37 +2037,37 @@
         <v>114</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L16" s="4">
-        <v>-18.3</v>
+        <v>-10.1</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O16" s="6">
-        <v>26</v>
+        <v>181</v>
+      </c>
+      <c r="O16" s="9">
+        <v>0</v>
       </c>
       <c r="P16" s="8">
         <v>0</v>
       </c>
       <c r="Q16" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R16" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2108,10 +2075,10 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>55</v>
@@ -2126,28 +2093,28 @@
         <v>115</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>75</v>
       </c>
       <c r="L17" s="4">
-        <v>-34.4</v>
+        <v>-37.8</v>
       </c>
       <c r="M17" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="N17" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="N17" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="O17" s="11">
-        <v>1</v>
+      <c r="O17" s="9">
+        <v>0</v>
       </c>
       <c r="P17" s="8">
         <v>0</v>
@@ -2164,10 +2131,10 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>55</v>
@@ -2182,28 +2149,28 @@
         <v>116</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>178</v>
+        <v>76</v>
       </c>
       <c r="L18" s="4">
-        <v>-21.8</v>
+        <v>-28.7</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="O18" s="11">
-        <v>1</v>
+      <c r="O18" s="9">
+        <v>0</v>
       </c>
       <c r="P18" s="8">
         <v>0</v>
@@ -2220,10 +2187,10 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>55</v>
@@ -2238,27 +2205,27 @@
         <v>117</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>160</v>
+        <v>77</v>
       </c>
       <c r="L19" s="4">
-        <v>-10.1</v>
+        <v>-34.2</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>179</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O19" s="11">
+        <v>183</v>
+      </c>
+      <c r="O19" s="9">
         <v>0</v>
       </c>
       <c r="P19" s="8">
@@ -2276,7 +2243,7 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>53</v>
@@ -2294,28 +2261,28 @@
         <v>118</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>78</v>
       </c>
       <c r="L20" s="4">
-        <v>-37.8</v>
+        <v>-21.3</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O20" s="11">
-        <v>9</v>
+        <v>183</v>
+      </c>
+      <c r="O20" s="9">
+        <v>0</v>
       </c>
       <c r="P20" s="8">
         <v>0</v>
@@ -2332,7 +2299,7 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>54</v>
@@ -2350,28 +2317,28 @@
         <v>119</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I21" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="K21" s="1" t="s">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="L21" s="4">
-        <v>-28.7</v>
+        <v>-11</v>
       </c>
       <c r="M21" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="N21" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="N21" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="O21" s="6">
-        <v>31</v>
+      <c r="O21" s="9">
+        <v>15</v>
       </c>
       <c r="P21" s="8">
         <v>0</v>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="175">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260628--01</t>
-  </si>
-  <si>
-    <t>20260628--02</t>
-  </si>
-  <si>
-    <t>20260628--03</t>
-  </si>
-  <si>
     <t>20260629--01</t>
   </si>
   <si>
@@ -130,13 +121,10 @@
     <t>20260704--03</t>
   </si>
   <si>
-    <t>02:36</t>
-  </si>
-  <si>
-    <t>04:13</t>
-  </si>
-  <si>
-    <t>06:24</t>
+    <t>20260705--01</t>
+  </si>
+  <si>
+    <t>20260705--02</t>
   </si>
   <si>
     <t>06:31</t>
@@ -148,61 +136,58 @@
     <t>02:07</t>
   </si>
   <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>04:01</t>
+  </si>
+  <si>
+    <t>05:10</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>05:11</t>
+  </si>
+  <si>
+    <t>03:58</t>
+  </si>
+  <si>
+    <t>06:43</t>
+  </si>
+  <si>
     <t>05:59</t>
   </si>
   <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>04:00</t>
-  </si>
-  <si>
-    <t>05:11</t>
-  </si>
-  <si>
-    <t>03:59</t>
-  </si>
-  <si>
-    <t>06:44</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:42</t>
-  </si>
-  <si>
-    <t>06:23</t>
+    <t>01:59</t>
   </si>
   <si>
     <t>04:24</t>
   </si>
   <si>
-    <t>02:40</t>
+    <t>02:41</t>
+  </si>
+  <si>
+    <t>05:48</t>
+  </si>
+  <si>
+    <t>05:47</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:58</t>
-  </si>
-  <si>
     <t>01:18</t>
   </si>
   <si>
-    <t>01:03</t>
-  </si>
-  <si>
-    <t>05:52</t>
-  </si>
-  <si>
-    <t>04:01:15</t>
-  </si>
-  <si>
-    <t>20:41:30</t>
-  </si>
-  <si>
-    <t>22:18:10</t>
+    <t>01:02</t>
+  </si>
+  <si>
+    <t>05:51</t>
   </si>
   <si>
     <t>04:52:07</t>
@@ -217,7 +202,7 @@
     <t>04:05:57</t>
   </si>
   <si>
-    <t>20:45:35</t>
+    <t>20:45:34</t>
   </si>
   <si>
     <t>22:23:57</t>
@@ -226,43 +211,40 @@
     <t>03:19:46</t>
   </si>
   <si>
-    <t>04:57:02</t>
-  </si>
-  <si>
-    <t>21:37:13</t>
+    <t>04:57:01</t>
+  </si>
+  <si>
+    <t>21:37:12</t>
   </si>
   <si>
     <t>02:33:32</t>
   </si>
   <si>
-    <t>04:10:37</t>
-  </si>
-  <si>
-    <t>20:50:31</t>
-  </si>
-  <si>
-    <t>01:47:15</t>
-  </si>
-  <si>
-    <t>03:24:13</t>
-  </si>
-  <si>
-    <t>02:37:48</t>
-  </si>
-  <si>
-    <t>04:15:35</t>
-  </si>
-  <si>
-    <t>20:56:02</t>
-  </si>
-  <si>
-    <t>04:04:33</t>
-  </si>
-  <si>
-    <t>20:44:11</t>
-  </si>
-  <si>
-    <t>22:20:21</t>
+    <t>04:10:36</t>
+  </si>
+  <si>
+    <t>20:50:30</t>
+  </si>
+  <si>
+    <t>01:47:14</t>
+  </si>
+  <si>
+    <t>03:24:12</t>
+  </si>
+  <si>
+    <t>02:37:47</t>
+  </si>
+  <si>
+    <t>04:15:34</t>
+  </si>
+  <si>
+    <t>20:56:01</t>
+  </si>
+  <si>
+    <t>01:51:21</t>
+  </si>
+  <si>
+    <t>03:28:48</t>
   </si>
   <si>
     <t>04:54:17</t>
@@ -271,16 +253,16 @@
     <t>21:33:57</t>
   </si>
   <si>
-    <t>23:14:10</t>
-  </si>
-  <si>
-    <t>04:08:15</t>
+    <t>23:14:09</t>
+  </si>
+  <si>
+    <t>04:08:14</t>
   </si>
   <si>
     <t>20:47:41</t>
   </si>
   <si>
-    <t>22:26:45</t>
+    <t>22:26:44</t>
   </si>
   <si>
     <t>03:22:15</t>
@@ -289,7 +271,7 @@
     <t>04:59:12</t>
   </si>
   <si>
-    <t>21:39:41</t>
+    <t>21:39:40</t>
   </si>
   <si>
     <t>02:36:21</t>
@@ -304,25 +286,22 @@
     <t>01:50:45</t>
   </si>
   <si>
-    <t>03:26:20</t>
-  </si>
-  <si>
-    <t>02:40:00</t>
-  </si>
-  <si>
-    <t>04:18:14</t>
-  </si>
-  <si>
-    <t>20:59:17</t>
-  </si>
-  <si>
-    <t>04:05:51</t>
-  </si>
-  <si>
-    <t>20:46:18</t>
-  </si>
-  <si>
-    <t>22:23:33</t>
+    <t>03:26:19</t>
+  </si>
+  <si>
+    <t>02:39:59</t>
+  </si>
+  <si>
+    <t>04:18:13</t>
+  </si>
+  <si>
+    <t>20:59:15</t>
+  </si>
+  <si>
+    <t>01:53:41</t>
+  </si>
+  <si>
+    <t>03:31:06</t>
   </si>
   <si>
     <t>04:57:33</t>
@@ -337,7 +316,7 @@
     <t>04:11:14</t>
   </si>
   <si>
-    <t>20:51:01</t>
+    <t>20:51:00</t>
   </si>
   <si>
     <t>22:28:45</t>
@@ -349,10 +328,10 @@
     <t>05:02:24</t>
   </si>
   <si>
-    <t>21:42:16</t>
-  </si>
-  <si>
-    <t>02:38:21</t>
+    <t>21:42:15</t>
+  </si>
+  <si>
+    <t>02:38:20</t>
   </si>
   <si>
     <t>04:16:05</t>
@@ -364,22 +343,22 @@
     <t>01:51:45</t>
   </si>
   <si>
-    <t>03:29:41</t>
-  </si>
-  <si>
-    <t>02:43:11</t>
-  </si>
-  <si>
-    <t>04:20:26</t>
-  </si>
-  <si>
-    <t>21:00:37</t>
-  </si>
-  <si>
-    <t>04:07:09</t>
-  </si>
-  <si>
-    <t>20:48:24</t>
+    <t>03:29:40</t>
+  </si>
+  <si>
+    <t>02:43:10</t>
+  </si>
+  <si>
+    <t>04:20:25</t>
+  </si>
+  <si>
+    <t>21:00:36</t>
+  </si>
+  <si>
+    <t>01:56:35</t>
+  </si>
+  <si>
+    <t>03:33:59</t>
   </si>
   <si>
     <t>05:00:48</t>
@@ -388,7 +367,7 @@
     <t>21:40:38</t>
   </si>
   <si>
-    <t>23:16:17</t>
+    <t>23:16:16</t>
   </si>
   <si>
     <t>04:14:14</t>
@@ -400,49 +379,46 @@
     <t>22:30:45</t>
   </si>
   <si>
-    <t>03:27:26</t>
-  </si>
-  <si>
-    <t>05:05:36</t>
-  </si>
-  <si>
-    <t>21:44:52</t>
-  </si>
-  <si>
-    <t>02:40:20</t>
-  </si>
-  <si>
-    <t>04:19:27</t>
+    <t>03:27:25</t>
+  </si>
+  <si>
+    <t>05:05:35</t>
+  </si>
+  <si>
+    <t>21:44:51</t>
+  </si>
+  <si>
+    <t>02:40:19</t>
+  </si>
+  <si>
+    <t>04:19:26</t>
   </si>
   <si>
     <t>20:58:46</t>
   </si>
   <si>
-    <t>01:52:45</t>
+    <t>01:52:44</t>
   </si>
   <si>
     <t>03:33:02</t>
   </si>
   <si>
-    <t>02:46:23</t>
-  </si>
-  <si>
-    <t>04:22:38</t>
-  </si>
-  <si>
-    <t>21:01:57</t>
-  </si>
-  <si>
-    <t>04:10:26</t>
-  </si>
-  <si>
-    <t>20:51:06</t>
-  </si>
-  <si>
-    <t>22:28:56</t>
-  </si>
-  <si>
-    <t>05:02:59</t>
+    <t>02:46:22</t>
+  </si>
+  <si>
+    <t>04:22:37</t>
+  </si>
+  <si>
+    <t>21:01:56</t>
+  </si>
+  <si>
+    <t>01:59:29</t>
+  </si>
+  <si>
+    <t>03:36:53</t>
+  </si>
+  <si>
+    <t>05:02:58</t>
   </si>
   <si>
     <t>21:42:45</t>
@@ -460,76 +436,73 @@
     <t>22:33:34</t>
   </si>
   <si>
-    <t>03:29:55</t>
+    <t>03:29:54</t>
   </si>
   <si>
     <t>05:07:46</t>
   </si>
   <si>
-    <t>21:47:21</t>
+    <t>21:47:20</t>
   </si>
   <si>
     <t>02:43:09</t>
   </si>
   <si>
-    <t>04:21:34</t>
-  </si>
-  <si>
-    <t>21:01:03</t>
-  </si>
-  <si>
-    <t>01:56:16</t>
+    <t>04:21:33</t>
+  </si>
+  <si>
+    <t>21:01:02</t>
+  </si>
+  <si>
+    <t>01:56:15</t>
   </si>
   <si>
     <t>03:35:09</t>
   </si>
   <si>
-    <t>02:48:35</t>
-  </si>
-  <si>
-    <t>04:25:17</t>
-  </si>
-  <si>
-    <t>21:05:13</t>
+    <t>02:48:33</t>
+  </si>
+  <si>
+    <t>04:25:16</t>
+  </si>
+  <si>
+    <t>21:05:11</t>
+  </si>
+  <si>
+    <t>02:01:48</t>
+  </si>
+  <si>
+    <t>03:39:11</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>2°</t>
+  </si>
+  <si>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>3°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>15°</t>
+  </si>
+  <si>
+    <t>14°</t>
+  </si>
+  <si>
     <t>8°</t>
   </si>
   <si>
-    <t>28°</t>
-  </si>
-  <si>
-    <t>2°</t>
-  </si>
-  <si>
-    <t>11°</t>
-  </si>
-  <si>
-    <t>3°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>15°</t>
-  </si>
-  <si>
-    <t>14°</t>
-  </si>
-  <si>
-    <t>20:48:58</t>
-  </si>
-  <si>
-    <t>22:22:19</t>
-  </si>
-  <si>
     <t>21:42:11</t>
   </si>
   <si>
-    <t>23:15:28</t>
+    <t>23:15:27</t>
   </si>
   <si>
     <t>04:06:50</t>
@@ -556,13 +529,13 @@
     <t>B</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>3</t>
@@ -614,13 +587,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -638,37 +611,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1157,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1235,49 +1208,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="L2" s="4">
-        <v>-23.1</v>
+        <v>-14.7</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="O2" s="6">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="P2" s="7">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1291,52 +1264,52 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="L3" s="4">
-        <v>-8.4</v>
+        <v>-17.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="O3" s="9">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="P3" s="8">
         <v>0</v>
       </c>
-      <c r="Q3" s="8">
-        <v>0</v>
+      <c r="Q3" s="10">
+        <v>13</v>
       </c>
       <c r="R3" s="8">
         <v>0</v>
@@ -1347,52 +1320,52 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="L4" s="4">
-        <v>-24.8</v>
+        <v>-31.6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="O4" s="9">
-        <v>2</v>
+        <v>173</v>
+      </c>
+      <c r="O4" s="6">
+        <v>48</v>
       </c>
       <c r="P4" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="11">
+        <v>47</v>
       </c>
       <c r="R4" s="8">
         <v>0</v>
@@ -1403,52 +1376,52 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="L5" s="4">
-        <v>-14.7</v>
+        <v>-22.6</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="O5" s="9">
-        <v>4</v>
-      </c>
-      <c r="P5" s="10">
-        <v>4</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>0</v>
+        <v>172</v>
+      </c>
+      <c r="O5" s="6">
+        <v>21</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>15</v>
       </c>
       <c r="R5" s="8">
         <v>0</v>
@@ -1462,52 +1435,52 @@
         <v>69</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="L6" s="4">
-        <v>-17.6</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O6" s="9">
-        <v>5</v>
+        <v>171</v>
+      </c>
+      <c r="O6" s="12">
+        <v>63</v>
       </c>
       <c r="P6" s="8">
         <v>0</v>
       </c>
-      <c r="Q6" s="10">
-        <v>4</v>
-      </c>
-      <c r="R6" s="8">
-        <v>0</v>
+      <c r="Q6" s="13">
+        <v>63</v>
+      </c>
+      <c r="R6" s="14">
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1515,55 +1488,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="K7" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-25.7</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="L7" s="4">
-        <v>-31.6</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="O7" s="11">
-        <v>22</v>
+      <c r="O7" s="12">
+        <v>61</v>
       </c>
       <c r="P7" s="8">
         <v>0</v>
       </c>
-      <c r="Q7" s="12">
-        <v>22</v>
-      </c>
-      <c r="R7" s="8">
-        <v>0</v>
+      <c r="Q7" s="15">
+        <v>61</v>
+      </c>
+      <c r="R7" s="10">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1571,52 +1544,52 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="L8" s="4">
-        <v>-22.6</v>
+        <v>-29.1</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O8" s="6">
-        <v>52</v>
+        <v>171</v>
+      </c>
+      <c r="O8" s="9">
+        <v>3</v>
       </c>
       <c r="P8" s="8">
         <v>0</v>
       </c>
-      <c r="Q8" s="13">
-        <v>52</v>
+      <c r="Q8" s="14">
+        <v>3</v>
       </c>
       <c r="R8" s="8">
         <v>0</v>
@@ -1627,55 +1600,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>159</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="L9" s="4">
-        <v>-9.199999999999999</v>
+        <v>-14.1</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="O9" s="6">
-        <v>57</v>
+        <v>171</v>
+      </c>
+      <c r="O9" s="9">
+        <v>0</v>
       </c>
       <c r="P9" s="8">
         <v>0</v>
       </c>
-      <c r="Q9" s="14">
-        <v>36</v>
-      </c>
-      <c r="R9" s="10">
-        <v>4</v>
+      <c r="Q9" s="8">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1683,52 +1656,52 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="L10" s="4">
-        <v>-25.7</v>
+        <v>-18.3</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="O10" s="11">
-        <v>19</v>
+        <v>171</v>
+      </c>
+      <c r="O10" s="9">
+        <v>0</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
       </c>
-      <c r="Q10" s="15">
-        <v>14</v>
+      <c r="Q10" s="8">
+        <v>0</v>
       </c>
       <c r="R10" s="8">
         <v>0</v>
@@ -1739,52 +1712,52 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="K11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-34.4</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="N11" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L11" s="4">
-        <v>-29.1</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="O11" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P11" s="8">
         <v>0</v>
       </c>
       <c r="Q11" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" s="8">
         <v>0</v>
@@ -1795,46 +1768,46 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J12" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="L12" s="4">
-        <v>-14</v>
+        <v>-21.8</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="O12" s="9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
@@ -1843,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="R12" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1851,52 +1824,52 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="L13" s="4">
-        <v>-18.3</v>
+        <v>-10.1</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="O13" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
       </c>
       <c r="Q13" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" s="8">
         <v>0</v>
@@ -1907,43 +1880,43 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L14" s="4">
-        <v>-34.4</v>
+        <v>-37.8</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="O14" s="9">
         <v>0</v>
@@ -1963,43 +1936,43 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
+        <v>67</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="F15" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>176</v>
+        <v>71</v>
       </c>
       <c r="L15" s="4">
-        <v>-21.8</v>
+        <v>-28.7</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="O15" s="9">
         <v>0</v>
@@ -2019,43 +1992,43 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="L16" s="4">
-        <v>-10.1</v>
+        <v>-34.2</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="O16" s="9">
         <v>0</v>
@@ -2075,43 +2048,43 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L17" s="4">
-        <v>-37.8</v>
+        <v>-21.3</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="O17" s="9">
         <v>0</v>
@@ -2131,43 +2104,43 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="L18" s="4">
-        <v>-28.7</v>
+        <v>-11</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="O18" s="9">
         <v>0</v>
@@ -2187,43 +2160,43 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L19" s="4">
-        <v>-34.2</v>
+        <v>-37.7</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="O19" s="9">
         <v>0</v>
@@ -2243,43 +2216,43 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="K20" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L20" s="4">
-        <v>-21.3</v>
+        <v>-28.3</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="O20" s="9">
         <v>0</v>
@@ -2291,122 +2264,66 @@
         <v>0</v>
       </c>
       <c r="R20" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
-      <c r="A21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="2">
-        <v>12</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="L21" s="4">
-        <v>-11</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="O21" s="9">
-        <v>15</v>
-      </c>
-      <c r="P21" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="8">
-        <v>0</v>
-      </c>
-      <c r="R21" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A21">
+  <conditionalFormatting sqref="A2:A20">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B21">
+  <conditionalFormatting sqref="B2:B20">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C21">
+  <conditionalFormatting sqref="C2:C20">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D21">
+  <conditionalFormatting sqref="D2:D20">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E21">
+  <conditionalFormatting sqref="E2:E20">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F21">
+  <conditionalFormatting sqref="F2:F20">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G21">
+  <conditionalFormatting sqref="G2:G20">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H21">
+  <conditionalFormatting sqref="H2:H20">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I21">
+  <conditionalFormatting sqref="I2:I20">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J21">
+  <conditionalFormatting sqref="J2:J20">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K21">
+  <conditionalFormatting sqref="K2:K20">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L21">
+  <conditionalFormatting sqref="L2:L20">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2425,12 +2342,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M21">
+  <conditionalFormatting sqref="M2:M20">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N21">
+  <conditionalFormatting sqref="N2:N20">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2447,22 +2364,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O21">
+  <conditionalFormatting sqref="O2:O20">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P21">
+  <conditionalFormatting sqref="P2:P20">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q21">
+  <conditionalFormatting sqref="Q2:Q20">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R21">
+  <conditionalFormatting sqref="R2:R20">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="165">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260629--01</t>
-  </si>
-  <si>
-    <t>20260629--02</t>
-  </si>
-  <si>
-    <t>20260629--03</t>
-  </si>
-  <si>
     <t>20260630--01</t>
   </si>
   <si>
@@ -127,13 +118,10 @@
     <t>20260705--02</t>
   </si>
   <si>
-    <t>06:31</t>
-  </si>
-  <si>
-    <t>06:41</t>
-  </si>
-  <si>
-    <t>02:07</t>
+    <t>20260706--01</t>
+  </si>
+  <si>
+    <t>20260706--02</t>
   </si>
   <si>
     <t>06:00</t>
@@ -166,39 +154,39 @@
     <t>01:59</t>
   </si>
   <si>
+    <t>06:42</t>
+  </si>
+  <si>
+    <t>06:24</t>
+  </si>
+  <si>
     <t>04:24</t>
   </si>
   <si>
     <t>02:41</t>
   </si>
   <si>
+    <t>05:47</t>
+  </si>
+  <si>
     <t>05:48</t>
   </si>
   <si>
-    <t>05:47</t>
+    <t>04:53</t>
+  </si>
+  <si>
+    <t>06:28</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:18</t>
-  </si>
-  <si>
     <t>01:02</t>
   </si>
   <si>
     <t>05:51</t>
   </si>
   <si>
-    <t>04:52:07</t>
-  </si>
-  <si>
-    <t>21:31:50</t>
-  </si>
-  <si>
-    <t>23:10:43</t>
-  </si>
-  <si>
     <t>04:05:57</t>
   </si>
   <si>
@@ -208,7 +196,7 @@
     <t>22:23:57</t>
   </si>
   <si>
-    <t>03:19:46</t>
+    <t>03:19:45</t>
   </si>
   <si>
     <t>04:57:01</t>
@@ -217,7 +205,7 @@
     <t>21:37:12</t>
   </si>
   <si>
-    <t>02:33:32</t>
+    <t>02:33:31</t>
   </si>
   <si>
     <t>04:10:36</t>
@@ -244,16 +232,13 @@
     <t>01:51:21</t>
   </si>
   <si>
-    <t>03:28:48</t>
-  </si>
-  <si>
-    <t>04:54:17</t>
-  </si>
-  <si>
-    <t>21:33:57</t>
-  </si>
-  <si>
-    <t>23:14:09</t>
+    <t>03:28:47</t>
+  </si>
+  <si>
+    <t>01:04:53</t>
+  </si>
+  <si>
+    <t>02:42:05</t>
   </si>
   <si>
     <t>04:08:14</t>
@@ -280,7 +265,7 @@
     <t>04:12:43</t>
   </si>
   <si>
-    <t>20:52:47</t>
+    <t>20:52:46</t>
   </si>
   <si>
     <t>01:50:45</t>
@@ -289,7 +274,7 @@
     <t>03:26:19</t>
   </si>
   <si>
-    <t>02:39:59</t>
+    <t>02:39:58</t>
   </si>
   <si>
     <t>04:18:13</t>
@@ -301,16 +286,13 @@
     <t>01:53:41</t>
   </si>
   <si>
-    <t>03:31:06</t>
-  </si>
-  <si>
-    <t>04:57:33</t>
-  </si>
-  <si>
-    <t>21:37:17</t>
-  </si>
-  <si>
-    <t>23:15:13</t>
+    <t>03:31:05</t>
+  </si>
+  <si>
+    <t>01:07:27</t>
+  </si>
+  <si>
+    <t>02:44:14</t>
   </si>
   <si>
     <t>04:11:14</t>
@@ -319,7 +301,7 @@
     <t>20:51:00</t>
   </si>
   <si>
-    <t>22:28:45</t>
+    <t>22:28:44</t>
   </si>
   <si>
     <t>03:24:50</t>
@@ -334,13 +316,13 @@
     <t>02:38:20</t>
   </si>
   <si>
-    <t>04:16:05</t>
-  </si>
-  <si>
-    <t>20:55:46</t>
-  </si>
-  <si>
-    <t>01:51:45</t>
+    <t>04:16:04</t>
+  </si>
+  <si>
+    <t>20:55:45</t>
+  </si>
+  <si>
+    <t>01:51:44</t>
   </si>
   <si>
     <t>03:29:40</t>
@@ -355,19 +337,16 @@
     <t>21:00:36</t>
   </si>
   <si>
-    <t>01:56:35</t>
+    <t>01:56:34</t>
   </si>
   <si>
     <t>03:33:59</t>
   </si>
   <si>
-    <t>05:00:48</t>
-  </si>
-  <si>
-    <t>21:40:38</t>
-  </si>
-  <si>
-    <t>23:16:16</t>
+    <t>01:09:53</t>
+  </si>
+  <si>
+    <t>02:47:28</t>
   </si>
   <si>
     <t>04:14:14</t>
@@ -394,13 +373,13 @@
     <t>04:19:26</t>
   </si>
   <si>
-    <t>20:58:46</t>
+    <t>20:58:45</t>
   </si>
   <si>
     <t>01:52:44</t>
   </si>
   <si>
-    <t>03:33:02</t>
+    <t>03:33:01</t>
   </si>
   <si>
     <t>02:46:22</t>
@@ -412,19 +391,16 @@
     <t>21:01:56</t>
   </si>
   <si>
-    <t>01:59:29</t>
+    <t>01:59:28</t>
   </si>
   <si>
     <t>03:36:53</t>
   </si>
   <si>
-    <t>05:02:58</t>
-  </si>
-  <si>
-    <t>21:42:45</t>
-  </si>
-  <si>
-    <t>23:19:44</t>
+    <t>01:12:20</t>
+  </si>
+  <si>
+    <t>02:50:42</t>
   </si>
   <si>
     <t>04:16:31</t>
@@ -445,7 +421,7 @@
     <t>21:47:20</t>
   </si>
   <si>
-    <t>02:43:09</t>
+    <t>02:43:08</t>
   </si>
   <si>
     <t>04:21:33</t>
@@ -457,7 +433,7 @@
     <t>01:56:15</t>
   </si>
   <si>
-    <t>03:35:09</t>
+    <t>03:35:08</t>
   </si>
   <si>
     <t>02:48:33</t>
@@ -475,18 +451,18 @@
     <t>03:39:11</t>
   </si>
   <si>
+    <t>01:14:53</t>
+  </si>
+  <si>
+    <t>02:52:51</t>
+  </si>
+  <si>
+    <t>3°</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
-    <t>2°</t>
-  </si>
-  <si>
-    <t>11°</t>
-  </si>
-  <si>
-    <t>3°</t>
-  </si>
-  <si>
     <t>0°</t>
   </si>
   <si>
@@ -499,12 +475,6 @@
     <t>8°</t>
   </si>
   <si>
-    <t>21:42:11</t>
-  </si>
-  <si>
-    <t>23:15:27</t>
-  </si>
-  <si>
     <t>04:06:50</t>
   </si>
   <si>
@@ -517,28 +487,28 @@
     <t>04:59:44</t>
   </si>
   <si>
-    <t>04:19:50</t>
+    <t>04:19:49</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>B</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>1</t>
+    <t>3</t>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -572,7 +542,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -587,13 +557,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -605,31 +581,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -641,7 +593,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -682,7 +646,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -724,9 +688,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1130,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1208,54 +1169,54 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>153</v>
       </c>
       <c r="L2" s="4">
-        <v>-14.7</v>
+        <v>-22.6</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="O2" s="6">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="P2" s="7">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="Q2" s="8">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
+        <v>29</v>
+      </c>
+      <c r="R2" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1267,52 +1228,52 @@
         <v>69</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="L3" s="4">
-        <v>-17.5</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O3" s="9">
-        <v>13</v>
-      </c>
-      <c r="P3" s="8">
+        <v>162</v>
+      </c>
+      <c r="O3" s="6">
+        <v>83</v>
+      </c>
+      <c r="P3" s="9">
         <v>0</v>
       </c>
       <c r="Q3" s="10">
-        <v>13</v>
-      </c>
-      <c r="R3" s="8">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="R3" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1320,54 +1281,54 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="K4" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-25.7</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="L4" s="4">
-        <v>-31.6</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="O4" s="6">
-        <v>48</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>47</v>
-      </c>
-      <c r="R4" s="8">
+        <v>81</v>
+      </c>
+      <c r="P4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>80</v>
+      </c>
+      <c r="R4" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1376,54 +1337,54 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="L5" s="4">
-        <v>-22.6</v>
+        <v>-29.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O5" s="6">
-        <v>21</v>
-      </c>
-      <c r="P5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="10">
-        <v>15</v>
-      </c>
-      <c r="R5" s="8">
+        <v>162</v>
+      </c>
+      <c r="O5" s="13">
+        <v>3</v>
+      </c>
+      <c r="P5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>2</v>
+      </c>
+      <c r="R5" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1432,55 +1393,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="L6" s="4">
-        <v>-9.199999999999999</v>
+        <v>-14.1</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="O6" s="12">
-        <v>63</v>
-      </c>
-      <c r="P6" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="13">
-        <v>63</v>
-      </c>
-      <c r="R6" s="14">
-        <v>7</v>
+        <v>162</v>
+      </c>
+      <c r="O6" s="13">
+        <v>0</v>
+      </c>
+      <c r="P6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>0</v>
+      </c>
+      <c r="R6" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1488,55 +1449,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="L7" s="4">
-        <v>-25.7</v>
+        <v>-18.3</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="O7" s="12">
-        <v>61</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="15">
-        <v>61</v>
-      </c>
-      <c r="R7" s="10">
-        <v>15</v>
+        <v>162</v>
+      </c>
+      <c r="O7" s="13">
+        <v>0</v>
+      </c>
+      <c r="P7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>0</v>
+      </c>
+      <c r="R7" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1544,54 +1505,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>165</v>
+        <v>63</v>
       </c>
       <c r="L8" s="4">
-        <v>-29.1</v>
+        <v>-34.4</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="O8" s="9">
+        <v>163</v>
+      </c>
+      <c r="O8" s="13">
         <v>3</v>
       </c>
-      <c r="P8" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="14">
-        <v>3</v>
-      </c>
-      <c r="R8" s="8">
+      <c r="P8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>0</v>
+      </c>
+      <c r="R8" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1600,54 +1561,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>71</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-21.8</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="O9" s="14">
         <v>40</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-14.1</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="O9" s="9">
-        <v>0</v>
-      </c>
-      <c r="P9" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8">
+      <c r="P9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>0</v>
+      </c>
+      <c r="R9" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1656,54 +1617,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="L10" s="4">
-        <v>-18.3</v>
+        <v>-10.1</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="O10" s="9">
-        <v>0</v>
-      </c>
-      <c r="P10" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>0</v>
-      </c>
-      <c r="R10" s="8">
+        <v>162</v>
+      </c>
+      <c r="O10" s="13">
+        <v>0</v>
+      </c>
+      <c r="P10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0</v>
+      </c>
+      <c r="R10" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1712,54 +1673,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L11" s="4">
-        <v>-34.4</v>
+        <v>-37.8</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="O11" s="9">
-        <v>1</v>
-      </c>
-      <c r="P11" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>0</v>
-      </c>
-      <c r="R11" s="8">
+        <v>164</v>
+      </c>
+      <c r="O11" s="13">
+        <v>0</v>
+      </c>
+      <c r="P11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>0</v>
+      </c>
+      <c r="R11" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1768,55 +1729,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="J12" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L12" s="4">
+        <v>-28.7</v>
+      </c>
+      <c r="M12" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="L12" s="4">
-        <v>-21.8</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="N12" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="O12" s="9">
-        <v>4</v>
-      </c>
-      <c r="P12" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>0</v>
-      </c>
-      <c r="R12" s="8">
-        <v>1</v>
+        <v>163</v>
+      </c>
+      <c r="O12" s="13">
+        <v>0</v>
+      </c>
+      <c r="P12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>0</v>
+      </c>
+      <c r="R12" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1824,54 +1785,54 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>153</v>
+        <v>68</v>
       </c>
       <c r="L13" s="4">
-        <v>-10.1</v>
+        <v>-34.2</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="O13" s="9">
-        <v>0</v>
-      </c>
-      <c r="P13" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>0</v>
-      </c>
-      <c r="R13" s="8">
+        <v>163</v>
+      </c>
+      <c r="O13" s="13">
+        <v>0</v>
+      </c>
+      <c r="P13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>0</v>
+      </c>
+      <c r="R13" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1880,54 +1841,54 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L14" s="4">
-        <v>-37.8</v>
+        <v>-21.3</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="O14" s="9">
-        <v>0</v>
-      </c>
-      <c r="P14" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>0</v>
-      </c>
-      <c r="R14" s="8">
+        <v>163</v>
+      </c>
+      <c r="O14" s="13">
+        <v>0</v>
+      </c>
+      <c r="P14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>0</v>
+      </c>
+      <c r="R14" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1936,54 +1897,54 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>71</v>
+        <v>148</v>
       </c>
       <c r="L15" s="4">
-        <v>-28.7</v>
+        <v>-11</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="O15" s="9">
-        <v>0</v>
-      </c>
-      <c r="P15" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>0</v>
-      </c>
-      <c r="R15" s="8">
+        <v>164</v>
+      </c>
+      <c r="O15" s="13">
+        <v>0</v>
+      </c>
+      <c r="P15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>0</v>
+      </c>
+      <c r="R15" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1992,54 +1953,54 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L16" s="4">
-        <v>-34.2</v>
+        <v>-37.7</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="O16" s="9">
-        <v>0</v>
-      </c>
-      <c r="P16" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>0</v>
-      </c>
-      <c r="R16" s="8">
+        <v>163</v>
+      </c>
+      <c r="O16" s="13">
+        <v>0</v>
+      </c>
+      <c r="P16" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="9">
+        <v>0</v>
+      </c>
+      <c r="R16" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2048,54 +2009,54 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I17" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="K17" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L17" s="4">
-        <v>-21.3</v>
+        <v>-28.3</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="O17" s="9">
-        <v>0</v>
-      </c>
-      <c r="P17" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>0</v>
-      </c>
-      <c r="R17" s="8">
+        <v>163</v>
+      </c>
+      <c r="O17" s="13">
+        <v>0</v>
+      </c>
+      <c r="P17" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>0</v>
+      </c>
+      <c r="R17" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2104,54 +2065,54 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>153</v>
+        <v>73</v>
       </c>
       <c r="L18" s="4">
-        <v>-11</v>
+        <v>-39</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="O18" s="9">
-        <v>0</v>
-      </c>
-      <c r="P18" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>0</v>
-      </c>
-      <c r="R18" s="8">
+        <v>163</v>
+      </c>
+      <c r="O18" s="13">
+        <v>12</v>
+      </c>
+      <c r="P18" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="9">
+        <v>0</v>
+      </c>
+      <c r="R18" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2160,170 +2121,114 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L19" s="4">
-        <v>-37.7</v>
+        <v>-33.9</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="O19" s="9">
-        <v>0</v>
-      </c>
-      <c r="P19" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="8">
-        <v>0</v>
-      </c>
-      <c r="R19" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
-      <c r="A20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="2">
-        <v>27</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L20" s="4">
-        <v>-28.3</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="O20" s="9">
-        <v>0</v>
-      </c>
-      <c r="P20" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="8">
-        <v>0</v>
-      </c>
-      <c r="R20" s="8">
+        <v>163</v>
+      </c>
+      <c r="O19" s="14">
+        <v>15</v>
+      </c>
+      <c r="P19" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="9">
+        <v>0</v>
+      </c>
+      <c r="R19" s="9">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A20">
+  <conditionalFormatting sqref="A2:A19">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B20">
+  <conditionalFormatting sqref="B2:B19">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C20">
+  <conditionalFormatting sqref="C2:C19">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D20">
+  <conditionalFormatting sqref="D2:D19">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E20">
+  <conditionalFormatting sqref="E2:E19">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F20">
+  <conditionalFormatting sqref="F2:F19">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G20">
+  <conditionalFormatting sqref="G2:G19">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H20">
+  <conditionalFormatting sqref="H2:H19">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I20">
+  <conditionalFormatting sqref="I2:I19">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J20">
+  <conditionalFormatting sqref="J2:J19">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K20">
+  <conditionalFormatting sqref="K2:K19">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L20">
+  <conditionalFormatting sqref="L2:L19">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2342,12 +2247,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M20">
+  <conditionalFormatting sqref="M2:M19">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N20">
+  <conditionalFormatting sqref="N2:N19">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2364,22 +2269,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O20">
+  <conditionalFormatting sqref="O2:O19">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P20">
+  <conditionalFormatting sqref="P2:P19">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q20">
+  <conditionalFormatting sqref="Q2:Q19">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R20">
+  <conditionalFormatting sqref="R2:R19">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="161">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260630--01</t>
-  </si>
-  <si>
-    <t>20260630--02</t>
-  </si>
-  <si>
-    <t>20260630--03</t>
-  </si>
-  <si>
     <t>20260701--01</t>
   </si>
   <si>
@@ -124,13 +115,13 @@
     <t>20260706--02</t>
   </si>
   <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>04:01</t>
+    <t>20260707--01</t>
+  </si>
+  <si>
+    <t>20260707--02</t>
+  </si>
+  <si>
+    <t>20260707--03</t>
   </si>
   <si>
     <t>05:10</t>
@@ -151,19 +142,16 @@
     <t>05:59</t>
   </si>
   <si>
-    <t>01:59</t>
+    <t>01:57</t>
   </si>
   <si>
     <t>06:42</t>
   </si>
   <si>
-    <t>06:24</t>
-  </si>
-  <si>
-    <t>04:24</t>
-  </si>
-  <si>
-    <t>02:41</t>
+    <t>04:25</t>
+  </si>
+  <si>
+    <t>02:42</t>
   </si>
   <si>
     <t>05:47</t>
@@ -172,82 +160,79 @@
     <t>05:48</t>
   </si>
   <si>
-    <t>04:53</t>
+    <t>04:52</t>
   </si>
   <si>
     <t>06:28</t>
   </si>
   <si>
+    <t>03:30</t>
+  </si>
+  <si>
+    <t>00:12</t>
+  </si>
+  <si>
+    <t>01:02</t>
+  </si>
+  <si>
+    <t>05:51</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:02</t>
-  </si>
-  <si>
-    <t>05:51</t>
-  </si>
-  <si>
-    <t>04:05:57</t>
-  </si>
-  <si>
-    <t>20:45:34</t>
-  </si>
-  <si>
-    <t>22:23:57</t>
-  </si>
-  <si>
     <t>03:19:45</t>
   </si>
   <si>
     <t>04:57:01</t>
   </si>
   <si>
-    <t>21:37:12</t>
-  </si>
-  <si>
-    <t>02:33:31</t>
-  </si>
-  <si>
-    <t>04:10:36</t>
-  </si>
-  <si>
-    <t>20:50:30</t>
-  </si>
-  <si>
-    <t>01:47:14</t>
-  </si>
-  <si>
-    <t>03:24:12</t>
-  </si>
-  <si>
-    <t>02:37:47</t>
-  </si>
-  <si>
-    <t>04:15:34</t>
-  </si>
-  <si>
-    <t>20:56:01</t>
-  </si>
-  <si>
-    <t>01:51:21</t>
-  </si>
-  <si>
-    <t>03:28:47</t>
-  </si>
-  <si>
-    <t>01:04:53</t>
-  </si>
-  <si>
-    <t>02:42:05</t>
-  </si>
-  <si>
-    <t>04:08:14</t>
-  </si>
-  <si>
-    <t>20:47:41</t>
-  </si>
-  <si>
-    <t>22:26:44</t>
+    <t>21:37:11</t>
+  </si>
+  <si>
+    <t>02:33:30</t>
+  </si>
+  <si>
+    <t>04:10:35</t>
+  </si>
+  <si>
+    <t>20:50:27</t>
+  </si>
+  <si>
+    <t>01:47:10</t>
+  </si>
+  <si>
+    <t>03:24:08</t>
+  </si>
+  <si>
+    <t>02:37:39</t>
+  </si>
+  <si>
+    <t>04:15:26</t>
+  </si>
+  <si>
+    <t>20:55:49</t>
+  </si>
+  <si>
+    <t>01:51:08</t>
+  </si>
+  <si>
+    <t>03:28:34</t>
+  </si>
+  <si>
+    <t>01:04:35</t>
+  </si>
+  <si>
+    <t>02:41:45</t>
+  </si>
+  <si>
+    <t>00:17:57</t>
+  </si>
+  <si>
+    <t>01:54:57</t>
+  </si>
+  <si>
+    <t>23:31:14</t>
   </si>
   <si>
     <t>03:22:15</t>
@@ -256,106 +241,103 @@
     <t>04:59:12</t>
   </si>
   <si>
-    <t>21:39:40</t>
-  </si>
-  <si>
-    <t>02:36:21</t>
-  </si>
-  <si>
-    <t>04:12:43</t>
-  </si>
-  <si>
-    <t>20:52:46</t>
-  </si>
-  <si>
-    <t>01:50:45</t>
-  </si>
-  <si>
-    <t>03:26:19</t>
-  </si>
-  <si>
-    <t>02:39:58</t>
-  </si>
-  <si>
-    <t>04:18:13</t>
-  </si>
-  <si>
-    <t>20:59:15</t>
-  </si>
-  <si>
-    <t>01:53:41</t>
-  </si>
-  <si>
-    <t>03:31:05</t>
-  </si>
-  <si>
-    <t>01:07:27</t>
-  </si>
-  <si>
-    <t>02:44:14</t>
-  </si>
-  <si>
-    <t>04:11:14</t>
-  </si>
-  <si>
-    <t>20:51:00</t>
-  </si>
-  <si>
-    <t>22:28:44</t>
+    <t>21:39:39</t>
+  </si>
+  <si>
+    <t>02:36:20</t>
+  </si>
+  <si>
+    <t>04:12:41</t>
+  </si>
+  <si>
+    <t>20:52:43</t>
+  </si>
+  <si>
+    <t>01:50:42</t>
+  </si>
+  <si>
+    <t>03:26:15</t>
+  </si>
+  <si>
+    <t>02:39:51</t>
+  </si>
+  <si>
+    <t>04:18:04</t>
+  </si>
+  <si>
+    <t>20:59:03</t>
+  </si>
+  <si>
+    <t>01:53:28</t>
+  </si>
+  <si>
+    <t>03:30:52</t>
+  </si>
+  <si>
+    <t>01:07:08</t>
+  </si>
+  <si>
+    <t>02:43:55</t>
+  </si>
+  <si>
+    <t>00:20:55</t>
+  </si>
+  <si>
+    <t>01:57:04</t>
+  </si>
+  <si>
+    <t>23:35:38</t>
   </si>
   <si>
     <t>03:24:50</t>
   </si>
   <si>
-    <t>05:02:24</t>
-  </si>
-  <si>
-    <t>21:42:15</t>
-  </si>
-  <si>
-    <t>02:38:20</t>
-  </si>
-  <si>
-    <t>04:16:04</t>
-  </si>
-  <si>
-    <t>20:55:45</t>
-  </si>
-  <si>
-    <t>01:51:44</t>
-  </si>
-  <si>
-    <t>03:29:40</t>
-  </si>
-  <si>
-    <t>02:43:10</t>
-  </si>
-  <si>
-    <t>04:20:25</t>
-  </si>
-  <si>
-    <t>21:00:36</t>
-  </si>
-  <si>
-    <t>01:56:34</t>
-  </si>
-  <si>
-    <t>03:33:59</t>
-  </si>
-  <si>
-    <t>01:09:53</t>
-  </si>
-  <si>
-    <t>02:47:28</t>
-  </si>
-  <si>
-    <t>04:14:14</t>
-  </si>
-  <si>
-    <t>20:54:21</t>
-  </si>
-  <si>
-    <t>22:30:45</t>
+    <t>05:02:23</t>
+  </si>
+  <si>
+    <t>21:42:14</t>
+  </si>
+  <si>
+    <t>02:38:19</t>
+  </si>
+  <si>
+    <t>04:16:03</t>
+  </si>
+  <si>
+    <t>20:55:42</t>
+  </si>
+  <si>
+    <t>01:51:40</t>
+  </si>
+  <si>
+    <t>03:29:36</t>
+  </si>
+  <si>
+    <t>02:43:02</t>
+  </si>
+  <si>
+    <t>04:20:17</t>
+  </si>
+  <si>
+    <t>21:00:24</t>
+  </si>
+  <si>
+    <t>01:56:22</t>
+  </si>
+  <si>
+    <t>03:33:46</t>
+  </si>
+  <si>
+    <t>01:09:35</t>
+  </si>
+  <si>
+    <t>02:47:09</t>
+  </si>
+  <si>
+    <t>00:22:40</t>
+  </si>
+  <si>
+    <t>02:00:26</t>
   </si>
   <si>
     <t>03:27:25</t>
@@ -364,100 +346,112 @@
     <t>05:05:35</t>
   </si>
   <si>
-    <t>21:44:51</t>
-  </si>
-  <si>
-    <t>02:40:19</t>
-  </si>
-  <si>
-    <t>04:19:26</t>
-  </si>
-  <si>
-    <t>20:58:45</t>
-  </si>
-  <si>
-    <t>01:52:44</t>
-  </si>
-  <si>
-    <t>03:33:01</t>
-  </si>
-  <si>
-    <t>02:46:22</t>
-  </si>
-  <si>
-    <t>04:22:37</t>
-  </si>
-  <si>
-    <t>21:01:56</t>
-  </si>
-  <si>
-    <t>01:59:28</t>
-  </si>
-  <si>
-    <t>03:36:53</t>
-  </si>
-  <si>
-    <t>01:12:20</t>
-  </si>
-  <si>
-    <t>02:50:42</t>
-  </si>
-  <si>
-    <t>04:16:31</t>
-  </si>
-  <si>
-    <t>20:56:28</t>
-  </si>
-  <si>
-    <t>22:33:34</t>
+    <t>21:44:50</t>
+  </si>
+  <si>
+    <t>02:40:18</t>
+  </si>
+  <si>
+    <t>04:19:24</t>
+  </si>
+  <si>
+    <t>20:58:42</t>
+  </si>
+  <si>
+    <t>01:52:39</t>
+  </si>
+  <si>
+    <t>03:32:57</t>
+  </si>
+  <si>
+    <t>02:46:14</t>
+  </si>
+  <si>
+    <t>04:22:29</t>
+  </si>
+  <si>
+    <t>21:01:45</t>
+  </si>
+  <si>
+    <t>01:59:15</t>
+  </si>
+  <si>
+    <t>03:36:40</t>
+  </si>
+  <si>
+    <t>01:12:00</t>
+  </si>
+  <si>
+    <t>02:50:23</t>
+  </si>
+  <si>
+    <t>00:24:25</t>
+  </si>
+  <si>
+    <t>02:03:47</t>
+  </si>
+  <si>
+    <t>23:35:50</t>
   </si>
   <si>
     <t>03:29:54</t>
   </si>
   <si>
-    <t>05:07:46</t>
-  </si>
-  <si>
-    <t>21:47:20</t>
-  </si>
-  <si>
-    <t>02:43:08</t>
-  </si>
-  <si>
-    <t>04:21:33</t>
-  </si>
-  <si>
-    <t>21:01:02</t>
-  </si>
-  <si>
-    <t>01:56:15</t>
-  </si>
-  <si>
-    <t>03:35:08</t>
-  </si>
-  <si>
-    <t>02:48:33</t>
-  </si>
-  <si>
-    <t>04:25:16</t>
-  </si>
-  <si>
-    <t>21:05:11</t>
-  </si>
-  <si>
-    <t>02:01:48</t>
-  </si>
-  <si>
-    <t>03:39:11</t>
-  </si>
-  <si>
-    <t>01:14:53</t>
-  </si>
-  <si>
-    <t>02:52:51</t>
-  </si>
-  <si>
-    <t>3°</t>
+    <t>05:07:45</t>
+  </si>
+  <si>
+    <t>21:47:19</t>
+  </si>
+  <si>
+    <t>02:43:07</t>
+  </si>
+  <si>
+    <t>04:21:31</t>
+  </si>
+  <si>
+    <t>21:00:59</t>
+  </si>
+  <si>
+    <t>01:56:10</t>
+  </si>
+  <si>
+    <t>03:35:04</t>
+  </si>
+  <si>
+    <t>02:48:25</t>
+  </si>
+  <si>
+    <t>04:25:08</t>
+  </si>
+  <si>
+    <t>21:04:59</t>
+  </si>
+  <si>
+    <t>02:01:35</t>
+  </si>
+  <si>
+    <t>03:38:58</t>
+  </si>
+  <si>
+    <t>01:14:34</t>
+  </si>
+  <si>
+    <t>02:52:32</t>
+  </si>
+  <si>
+    <t>00:27:22</t>
+  </si>
+  <si>
+    <t>02:05:53</t>
+  </si>
+  <si>
+    <t>23:40:02</t>
+  </si>
+  <si>
+    <t>15°</t>
+  </si>
+  <si>
+    <t>14°</t>
   </si>
   <si>
     <t>-</t>
@@ -466,19 +460,13 @@
     <t>0°</t>
   </si>
   <si>
-    <t>15°</t>
-  </si>
-  <si>
-    <t>14°</t>
-  </si>
-  <si>
     <t>8°</t>
   </si>
   <si>
-    <t>04:06:50</t>
-  </si>
-  <si>
-    <t>22:33:33</t>
+    <t>2°</t>
+  </si>
+  <si>
+    <t>7°</t>
   </si>
   <si>
     <t>03:26:23</t>
@@ -487,19 +475,19 @@
     <t>04:59:44</t>
   </si>
   <si>
-    <t>04:19:49</t>
-  </si>
-  <si>
-    <t>A</t>
+    <t>04:19:48</t>
+  </si>
+  <si>
+    <t>00:18:39</t>
+  </si>
+  <si>
+    <t>23:33:34</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
     <t>B</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>2</t>
@@ -542,7 +530,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -557,19 +545,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -581,31 +569,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -646,7 +616,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -679,15 +649,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1169,52 +1130,52 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L2" s="4">
-        <v>-22.6</v>
+        <v>-29.1</v>
       </c>
       <c r="M2" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="O2" s="6">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="P2" s="7">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="Q2" s="8">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="R2" s="9">
         <v>0</v>
@@ -1225,55 +1186,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L3" s="4">
-        <v>-9.199999999999999</v>
+        <v>-14.1</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="O3" s="6">
-        <v>83</v>
-      </c>
-      <c r="P3" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>75</v>
-      </c>
-      <c r="R3" s="11">
-        <v>3</v>
+        <v>17</v>
+      </c>
+      <c r="P3" s="10">
+        <v>16</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>0</v>
+      </c>
+      <c r="R3" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1281,52 +1242,52 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="L4" s="4">
-        <v>-25.7</v>
+        <v>-18.3</v>
       </c>
       <c r="M4" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="N4" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="O4" s="6">
-        <v>81</v>
+      <c r="O4" s="11">
+        <v>0</v>
       </c>
       <c r="P4" s="9">
         <v>0</v>
       </c>
-      <c r="Q4" s="12">
-        <v>80</v>
+      <c r="Q4" s="9">
+        <v>0</v>
       </c>
       <c r="R4" s="9">
         <v>0</v>
@@ -1337,55 +1298,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>39</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>155</v>
+        <v>58</v>
       </c>
       <c r="L5" s="4">
-        <v>-29.1</v>
+        <v>-34.4</v>
       </c>
       <c r="M5" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="N5" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="O5" s="13">
+      <c r="O5" s="11">
         <v>3</v>
       </c>
       <c r="P5" s="9">
         <v>0</v>
       </c>
       <c r="Q5" s="9">
-        <v>2</v>
-      </c>
-      <c r="R5" s="9">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="R5" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1393,46 +1354,46 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="L6" s="4">
-        <v>-14.1</v>
+        <v>-21.8</v>
       </c>
       <c r="M6" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="N6" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="O6" s="13">
-        <v>0</v>
+      <c r="O6" s="11">
+        <v>1</v>
       </c>
       <c r="P6" s="9">
         <v>0</v>
@@ -1449,7 +1410,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>41</v>
@@ -1458,36 +1419,36 @@
         <v>54</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L7" s="4">
-        <v>-18.3</v>
+        <v>-10.1</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="O7" s="13">
+        <v>158</v>
+      </c>
+      <c r="O7" s="11">
         <v>0</v>
       </c>
       <c r="P7" s="9">
@@ -1505,7 +1466,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>42</v>
@@ -1514,37 +1475,37 @@
         <v>54</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L8" s="4">
-        <v>-34.4</v>
+        <v>-37.8</v>
       </c>
       <c r="M8" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="N8" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O8" s="13">
-        <v>3</v>
+      <c r="O8" s="11">
+        <v>0</v>
       </c>
       <c r="P8" s="9">
         <v>0</v>
@@ -1561,7 +1522,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>43</v>
@@ -1570,37 +1531,37 @@
         <v>54</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="K9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-28.7</v>
+      </c>
+      <c r="M9" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="L9" s="4">
-        <v>-21.8</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="N9" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O9" s="14">
-        <v>40</v>
+        <v>159</v>
+      </c>
+      <c r="O9" s="11">
+        <v>0</v>
       </c>
       <c r="P9" s="9">
         <v>0</v>
@@ -1617,45 +1578,45 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>148</v>
+        <v>63</v>
       </c>
       <c r="L10" s="4">
-        <v>-10.1</v>
+        <v>-34.2</v>
       </c>
       <c r="M10" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="N10" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="N10" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="O10" s="13">
+      <c r="O10" s="11">
         <v>0</v>
       </c>
       <c r="P10" s="9">
@@ -1673,49 +1634,49 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L11" s="4">
-        <v>-37.8</v>
+        <v>-21.4</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O11" s="13">
-        <v>0</v>
-      </c>
-      <c r="P11" s="9">
-        <v>0</v>
+        <v>159</v>
+      </c>
+      <c r="O11" s="11">
+        <v>5</v>
+      </c>
+      <c r="P11" s="8">
+        <v>5</v>
       </c>
       <c r="Q11" s="9">
         <v>0</v>
@@ -1729,45 +1690,45 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>67</v>
+        <v>146</v>
       </c>
       <c r="L12" s="4">
-        <v>-28.7</v>
+        <v>-11</v>
       </c>
       <c r="M12" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="N12" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="N12" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O12" s="13">
+      <c r="O12" s="11">
         <v>0</v>
       </c>
       <c r="P12" s="9">
@@ -1785,45 +1746,45 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L13" s="4">
-        <v>-34.2</v>
+        <v>-37.7</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O13" s="13">
+        <v>159</v>
+      </c>
+      <c r="O13" s="11">
         <v>0</v>
       </c>
       <c r="P13" s="9">
@@ -1841,45 +1802,45 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L14" s="4">
-        <v>-21.3</v>
+        <v>-28.3</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O14" s="13">
+        <v>159</v>
+      </c>
+      <c r="O14" s="11">
         <v>0</v>
       </c>
       <c r="P14" s="9">
@@ -1897,46 +1858,46 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>148</v>
+        <v>68</v>
       </c>
       <c r="L15" s="4">
-        <v>-11</v>
+        <v>-39</v>
       </c>
       <c r="M15" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="N15" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O15" s="13">
-        <v>0</v>
+      <c r="O15" s="6">
+        <v>15</v>
       </c>
       <c r="P15" s="9">
         <v>0</v>
@@ -1945,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="R15" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1953,46 +1914,46 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L16" s="4">
-        <v>-37.7</v>
+        <v>-34</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O16" s="13">
-        <v>0</v>
+        <v>159</v>
+      </c>
+      <c r="O16" s="11">
+        <v>11</v>
       </c>
       <c r="P16" s="9">
         <v>0</v>
@@ -2001,7 +1962,7 @@
         <v>0</v>
       </c>
       <c r="R16" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2009,46 +1970,46 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>149</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>72</v>
+        <v>154</v>
       </c>
       <c r="L17" s="4">
-        <v>-28.3</v>
+        <v>-37.8</v>
       </c>
       <c r="M17" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="N17" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="N17" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O17" s="13">
-        <v>0</v>
+      <c r="O17" s="11">
+        <v>1</v>
       </c>
       <c r="P17" s="9">
         <v>0</v>
@@ -2065,46 +2026,46 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L18" s="4">
-        <v>-39</v>
+        <v>-37.7</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O18" s="13">
-        <v>12</v>
+        <v>159</v>
+      </c>
+      <c r="O18" s="11">
+        <v>0</v>
       </c>
       <c r="P18" s="9">
         <v>0</v>
@@ -2121,52 +2082,52 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>74</v>
+        <v>155</v>
       </c>
       <c r="L19" s="4">
-        <v>-33.9</v>
+        <v>-34.2</v>
       </c>
       <c r="M19" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="N19" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="N19" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O19" s="14">
-        <v>15</v>
+      <c r="O19" s="11">
+        <v>1</v>
       </c>
       <c r="P19" s="9">
         <v>0</v>
       </c>
       <c r="Q19" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" s="9">
         <v>0</v>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="150">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260701--01</t>
-  </si>
-  <si>
-    <t>20260701--02</t>
-  </si>
-  <si>
-    <t>20260701--03</t>
-  </si>
-  <si>
     <t>20260702--01</t>
   </si>
   <si>
@@ -124,13 +115,10 @@
     <t>20260707--03</t>
   </si>
   <si>
-    <t>05:10</t>
-  </si>
-  <si>
-    <t>06:23</t>
-  </si>
-  <si>
-    <t>05:11</t>
+    <t>20260708--01</t>
+  </si>
+  <si>
+    <t>20260708--02</t>
   </si>
   <si>
     <t>03:58</t>
@@ -142,12 +130,15 @@
     <t>05:59</t>
   </si>
   <si>
-    <t>01:57</t>
+    <t>01:58</t>
   </si>
   <si>
     <t>06:42</t>
   </si>
   <si>
+    <t>06:24</t>
+  </si>
+  <si>
     <t>04:25</t>
   </si>
   <si>
@@ -169,27 +160,21 @@
     <t>03:30</t>
   </si>
   <si>
-    <t>00:12</t>
-  </si>
-  <si>
-    <t>01:02</t>
-  </si>
-  <si>
-    <t>05:51</t>
+    <t>06:44</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>06:37</t>
+  </si>
+  <si>
+    <t>02:17</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:19:45</t>
-  </si>
-  <si>
-    <t>04:57:01</t>
-  </si>
-  <si>
-    <t>21:37:11</t>
-  </si>
-  <si>
     <t>02:33:30</t>
   </si>
   <si>
@@ -199,103 +184,97 @@
     <t>20:50:27</t>
   </si>
   <si>
-    <t>01:47:10</t>
-  </si>
-  <si>
-    <t>03:24:08</t>
-  </si>
-  <si>
-    <t>02:37:39</t>
-  </si>
-  <si>
-    <t>04:15:26</t>
-  </si>
-  <si>
-    <t>20:55:49</t>
-  </si>
-  <si>
-    <t>01:51:08</t>
-  </si>
-  <si>
-    <t>03:28:34</t>
-  </si>
-  <si>
-    <t>01:04:35</t>
-  </si>
-  <si>
-    <t>02:41:45</t>
-  </si>
-  <si>
-    <t>00:17:57</t>
-  </si>
-  <si>
-    <t>01:54:57</t>
-  </si>
-  <si>
-    <t>23:31:14</t>
-  </si>
-  <si>
-    <t>03:22:15</t>
-  </si>
-  <si>
-    <t>04:59:12</t>
-  </si>
-  <si>
-    <t>21:39:39</t>
+    <t>01:47:11</t>
+  </si>
+  <si>
+    <t>03:24:09</t>
+  </si>
+  <si>
+    <t>02:37:41</t>
+  </si>
+  <si>
+    <t>04:15:28</t>
+  </si>
+  <si>
+    <t>20:55:51</t>
+  </si>
+  <si>
+    <t>01:51:11</t>
+  </si>
+  <si>
+    <t>03:28:37</t>
+  </si>
+  <si>
+    <t>01:04:38</t>
+  </si>
+  <si>
+    <t>02:41:49</t>
+  </si>
+  <si>
+    <t>00:18:02</t>
+  </si>
+  <si>
+    <t>01:55:03</t>
+  </si>
+  <si>
+    <t>23:31:21</t>
+  </si>
+  <si>
+    <t>01:08:16</t>
+  </si>
+  <si>
+    <t>02:46:22</t>
   </si>
   <si>
     <t>02:36:20</t>
   </si>
   <si>
-    <t>04:12:41</t>
-  </si>
-  <si>
-    <t>20:52:43</t>
+    <t>04:12:42</t>
+  </si>
+  <si>
+    <t>20:52:44</t>
   </si>
   <si>
     <t>01:50:42</t>
   </si>
   <si>
-    <t>03:26:15</t>
-  </si>
-  <si>
-    <t>02:39:51</t>
-  </si>
-  <si>
-    <t>04:18:04</t>
-  </si>
-  <si>
-    <t>20:59:03</t>
-  </si>
-  <si>
-    <t>01:53:28</t>
-  </si>
-  <si>
-    <t>03:30:52</t>
-  </si>
-  <si>
-    <t>01:07:08</t>
-  </si>
-  <si>
-    <t>02:43:55</t>
-  </si>
-  <si>
-    <t>00:20:55</t>
-  </si>
-  <si>
-    <t>01:57:04</t>
-  </si>
-  <si>
-    <t>23:35:38</t>
-  </si>
-  <si>
-    <t>03:24:50</t>
-  </si>
-  <si>
-    <t>05:02:23</t>
-  </si>
-  <si>
-    <t>21:42:14</t>
+    <t>03:26:16</t>
+  </si>
+  <si>
+    <t>02:39:52</t>
+  </si>
+  <si>
+    <t>04:18:06</t>
+  </si>
+  <si>
+    <t>20:59:05</t>
+  </si>
+  <si>
+    <t>01:53:31</t>
+  </si>
+  <si>
+    <t>03:30:55</t>
+  </si>
+  <si>
+    <t>01:07:12</t>
+  </si>
+  <si>
+    <t>02:43:59</t>
+  </si>
+  <si>
+    <t>00:21:00</t>
+  </si>
+  <si>
+    <t>01:57:09</t>
+  </si>
+  <si>
+    <t>23:35:45</t>
+  </si>
+  <si>
+    <t>01:10:24</t>
+  </si>
+  <si>
+    <t>02:49:41</t>
   </si>
   <si>
     <t>02:38:19</t>
@@ -304,103 +283,97 @@
     <t>04:16:03</t>
   </si>
   <si>
-    <t>20:55:42</t>
-  </si>
-  <si>
-    <t>01:51:40</t>
-  </si>
-  <si>
-    <t>03:29:36</t>
-  </si>
-  <si>
-    <t>02:43:02</t>
-  </si>
-  <si>
-    <t>04:20:17</t>
-  </si>
-  <si>
-    <t>21:00:24</t>
-  </si>
-  <si>
-    <t>01:56:22</t>
-  </si>
-  <si>
-    <t>03:33:46</t>
-  </si>
-  <si>
-    <t>01:09:35</t>
-  </si>
-  <si>
-    <t>02:47:09</t>
-  </si>
-  <si>
-    <t>00:22:40</t>
-  </si>
-  <si>
-    <t>02:00:26</t>
-  </si>
-  <si>
-    <t>03:27:25</t>
-  </si>
-  <si>
-    <t>05:05:35</t>
-  </si>
-  <si>
-    <t>21:44:50</t>
+    <t>20:55:43</t>
+  </si>
+  <si>
+    <t>01:51:41</t>
+  </si>
+  <si>
+    <t>03:29:37</t>
+  </si>
+  <si>
+    <t>02:43:04</t>
+  </si>
+  <si>
+    <t>04:20:19</t>
+  </si>
+  <si>
+    <t>21:00:26</t>
+  </si>
+  <si>
+    <t>01:56:24</t>
+  </si>
+  <si>
+    <t>03:33:49</t>
+  </si>
+  <si>
+    <t>01:09:38</t>
+  </si>
+  <si>
+    <t>02:47:13</t>
+  </si>
+  <si>
+    <t>00:22:45</t>
+  </si>
+  <si>
+    <t>02:00:31</t>
+  </si>
+  <si>
+    <t>01:13:43</t>
+  </si>
+  <si>
+    <t>02:50:49</t>
   </si>
   <si>
     <t>02:40:18</t>
   </si>
   <si>
-    <t>04:19:24</t>
-  </si>
-  <si>
-    <t>20:58:42</t>
-  </si>
-  <si>
-    <t>01:52:39</t>
-  </si>
-  <si>
-    <t>03:32:57</t>
-  </si>
-  <si>
-    <t>02:46:14</t>
-  </si>
-  <si>
-    <t>04:22:29</t>
-  </si>
-  <si>
-    <t>21:01:45</t>
-  </si>
-  <si>
-    <t>01:59:15</t>
-  </si>
-  <si>
-    <t>03:36:40</t>
-  </si>
-  <si>
-    <t>01:12:00</t>
-  </si>
-  <si>
-    <t>02:50:23</t>
-  </si>
-  <si>
-    <t>00:24:25</t>
-  </si>
-  <si>
-    <t>02:03:47</t>
-  </si>
-  <si>
-    <t>23:35:50</t>
-  </si>
-  <si>
-    <t>03:29:54</t>
-  </si>
-  <si>
-    <t>05:07:45</t>
-  </si>
-  <si>
-    <t>21:47:19</t>
+    <t>04:19:25</t>
+  </si>
+  <si>
+    <t>20:58:43</t>
+  </si>
+  <si>
+    <t>01:52:40</t>
+  </si>
+  <si>
+    <t>03:32:58</t>
+  </si>
+  <si>
+    <t>02:46:16</t>
+  </si>
+  <si>
+    <t>04:22:31</t>
+  </si>
+  <si>
+    <t>21:01:47</t>
+  </si>
+  <si>
+    <t>01:59:18</t>
+  </si>
+  <si>
+    <t>03:36:43</t>
+  </si>
+  <si>
+    <t>01:12:04</t>
+  </si>
+  <si>
+    <t>02:50:27</t>
+  </si>
+  <si>
+    <t>00:24:30</t>
+  </si>
+  <si>
+    <t>02:03:53</t>
+  </si>
+  <si>
+    <t>23:36:00</t>
+  </si>
+  <si>
+    <t>01:17:01</t>
+  </si>
+  <si>
+    <t>02:51:58</t>
   </si>
   <si>
     <t>02:43:07</t>
@@ -409,91 +382,85 @@
     <t>04:21:31</t>
   </si>
   <si>
-    <t>21:00:59</t>
-  </si>
-  <si>
-    <t>01:56:10</t>
-  </si>
-  <si>
-    <t>03:35:04</t>
-  </si>
-  <si>
-    <t>02:48:25</t>
-  </si>
-  <si>
-    <t>04:25:08</t>
-  </si>
-  <si>
-    <t>21:04:59</t>
-  </si>
-  <si>
-    <t>02:01:35</t>
-  </si>
-  <si>
-    <t>03:38:58</t>
-  </si>
-  <si>
-    <t>01:14:34</t>
-  </si>
-  <si>
-    <t>02:52:32</t>
-  </si>
-  <si>
-    <t>00:27:22</t>
-  </si>
-  <si>
-    <t>02:05:53</t>
-  </si>
-  <si>
-    <t>23:40:02</t>
-  </si>
-  <si>
-    <t>15°</t>
-  </si>
-  <si>
-    <t>14°</t>
+    <t>21:01:00</t>
+  </si>
+  <si>
+    <t>01:56:11</t>
+  </si>
+  <si>
+    <t>03:35:05</t>
+  </si>
+  <si>
+    <t>02:48:27</t>
+  </si>
+  <si>
+    <t>04:25:09</t>
+  </si>
+  <si>
+    <t>21:05:02</t>
+  </si>
+  <si>
+    <t>02:01:37</t>
+  </si>
+  <si>
+    <t>03:39:00</t>
+  </si>
+  <si>
+    <t>01:14:38</t>
+  </si>
+  <si>
+    <t>02:52:36</t>
+  </si>
+  <si>
+    <t>00:27:28</t>
+  </si>
+  <si>
+    <t>02:05:59</t>
+  </si>
+  <si>
+    <t>23:40:09</t>
+  </si>
+  <si>
+    <t>01:19:09</t>
+  </si>
+  <si>
+    <t>02:55:17</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>8°</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
     <t>2°</t>
   </si>
   <si>
     <t>7°</t>
   </si>
   <si>
-    <t>03:26:23</t>
-  </si>
-  <si>
-    <t>04:59:44</t>
-  </si>
-  <si>
     <t>04:19:48</t>
   </si>
   <si>
-    <t>00:18:39</t>
-  </si>
-  <si>
-    <t>23:33:34</t>
+    <t>00:18:44</t>
+  </si>
+  <si>
+    <t>23:33:40</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>B</t>
+    <t>3</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>4</t>
@@ -545,19 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -569,13 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1052,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1130,54 +1097,54 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>52</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>151</v>
+        <v>53</v>
       </c>
       <c r="L2" s="4">
-        <v>-29.1</v>
+        <v>-34.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="O2" s="6">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="P2" s="7">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="Q2" s="8">
-        <v>3</v>
-      </c>
-      <c r="R2" s="9">
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1186,54 +1153,54 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-21.8</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-14.1</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="N3" s="1" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="O3" s="6">
-        <v>17</v>
-      </c>
-      <c r="P3" s="10">
-        <v>16</v>
-      </c>
-      <c r="Q3" s="9">
-        <v>0</v>
-      </c>
-      <c r="R3" s="9">
+        <v>71</v>
+      </c>
+      <c r="P3" s="9">
+        <v>72</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>0</v>
+      </c>
+      <c r="R3" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1242,54 +1209,54 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-10.1</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-18.3</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="N4" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="O4" s="11">
-        <v>0</v>
-      </c>
-      <c r="P4" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="9">
-        <v>0</v>
-      </c>
-      <c r="R4" s="9">
+        <v>148</v>
+      </c>
+      <c r="O4" s="10">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1298,55 +1265,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L5" s="4">
-        <v>-34.4</v>
+        <v>-37.8</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O5" s="11">
-        <v>3</v>
-      </c>
-      <c r="P5" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="9">
+        <v>149</v>
+      </c>
+      <c r="O5" s="10">
+        <v>0</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="8">
         <v>0</v>
       </c>
       <c r="R5" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1354,54 +1321,54 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>153</v>
+        <v>57</v>
       </c>
       <c r="L6" s="4">
-        <v>-21.8</v>
+        <v>-28.7</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O6" s="11">
-        <v>1</v>
-      </c>
-      <c r="P6" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="9">
-        <v>0</v>
-      </c>
-      <c r="R6" s="9">
+        <v>147</v>
+      </c>
+      <c r="O6" s="10">
+        <v>0</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1410,54 +1377,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>146</v>
+        <v>58</v>
       </c>
       <c r="L7" s="4">
-        <v>-10.1</v>
+        <v>-34.2</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="O7" s="11">
-        <v>0</v>
-      </c>
-      <c r="P7" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="9">
-        <v>0</v>
-      </c>
-      <c r="R7" s="9">
+        <v>147</v>
+      </c>
+      <c r="O7" s="10">
+        <v>0</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
+      <c r="R7" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1466,54 +1433,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="J8" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-21.4</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L8" s="4">
-        <v>-37.8</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="O8" s="11">
-        <v>0</v>
-      </c>
-      <c r="P8" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="9">
-        <v>0</v>
-      </c>
-      <c r="R8" s="9">
+      <c r="O8" s="10">
+        <v>0</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1522,54 +1489,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="L9" s="4">
-        <v>-28.7</v>
+        <v>-11</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O9" s="11">
-        <v>0</v>
-      </c>
-      <c r="P9" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="9">
-        <v>0</v>
-      </c>
-      <c r="R9" s="9">
+        <v>149</v>
+      </c>
+      <c r="O9" s="10">
+        <v>0</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1578,54 +1545,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="J10" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-37.7</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="N10" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="L10" s="4">
-        <v>-34.2</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O10" s="11">
-        <v>0</v>
-      </c>
-      <c r="P10" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="9">
-        <v>0</v>
-      </c>
-      <c r="R10" s="9">
+      <c r="O10" s="10">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1634,54 +1601,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="J11" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-28.3</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="N11" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="L11" s="4">
-        <v>-21.4</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O11" s="11">
-        <v>5</v>
+      <c r="O11" s="10">
+        <v>0</v>
       </c>
       <c r="P11" s="8">
-        <v>5</v>
-      </c>
-      <c r="Q11" s="9">
-        <v>0</v>
-      </c>
-      <c r="R11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>0</v>
+      </c>
+      <c r="R11" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1690,54 +1657,54 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="L12" s="4">
-        <v>-11</v>
+        <v>-39</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="O12" s="11">
-        <v>0</v>
-      </c>
-      <c r="P12" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="9">
-        <v>0</v>
-      </c>
-      <c r="R12" s="9">
+        <v>147</v>
+      </c>
+      <c r="O12" s="10">
+        <v>1</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1746,54 +1713,54 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="I13" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="K13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-34</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="N13" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-37.7</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O13" s="11">
-        <v>0</v>
-      </c>
-      <c r="P13" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="9">
-        <v>0</v>
-      </c>
-      <c r="R13" s="9">
+      <c r="O13" s="10">
+        <v>0</v>
+      </c>
+      <c r="P13" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>0</v>
+      </c>
+      <c r="R13" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1802,54 +1769,54 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>67</v>
+        <v>143</v>
       </c>
       <c r="L14" s="4">
-        <v>-28.3</v>
+        <v>-37.8</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O14" s="11">
-        <v>0</v>
-      </c>
-      <c r="P14" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="9">
-        <v>0</v>
-      </c>
-      <c r="R14" s="9">
+        <v>149</v>
+      </c>
+      <c r="O14" s="10">
+        <v>3</v>
+      </c>
+      <c r="P14" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>3</v>
+      </c>
+      <c r="R14" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1858,55 +1825,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="J15" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L15" s="4">
+        <v>-37.7</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="L15" s="4">
-        <v>-39</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O15" s="6">
-        <v>15</v>
-      </c>
-      <c r="P15" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="9">
-        <v>0</v>
-      </c>
-      <c r="R15" s="9">
+      <c r="O15" s="10">
+        <v>4</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8">
         <v>1</v>
+      </c>
+      <c r="R15" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1914,55 +1881,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>69</v>
+        <v>144</v>
       </c>
       <c r="L16" s="4">
-        <v>-34</v>
+        <v>-34.2</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O16" s="11">
-        <v>11</v>
-      </c>
-      <c r="P16" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="9">
-        <v>0</v>
-      </c>
-      <c r="R16" s="9">
+        <v>149</v>
+      </c>
+      <c r="O16" s="10">
         <v>1</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>1</v>
+      </c>
+      <c r="R16" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -1970,54 +1937,54 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>154</v>
+        <v>68</v>
       </c>
       <c r="L17" s="4">
-        <v>-37.8</v>
+        <v>-39.2</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="O17" s="11">
-        <v>1</v>
-      </c>
-      <c r="P17" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="9">
-        <v>0</v>
-      </c>
-      <c r="R17" s="9">
+        <v>147</v>
+      </c>
+      <c r="O17" s="10">
+        <v>2</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0</v>
+      </c>
+      <c r="R17" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2026,170 +1993,114 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L18" s="4">
-        <v>-37.7</v>
+        <v>-33.8</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O18" s="11">
-        <v>0</v>
-      </c>
-      <c r="P18" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="9">
-        <v>0</v>
-      </c>
-      <c r="R18" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="2">
-        <v>10</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="L19" s="4">
-        <v>-34.2</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="O19" s="11">
-        <v>1</v>
-      </c>
-      <c r="P19" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="9">
-        <v>1</v>
-      </c>
-      <c r="R19" s="9">
+        <v>149</v>
+      </c>
+      <c r="O18" s="10">
+        <v>2</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>0</v>
+      </c>
+      <c r="R18" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A19">
+  <conditionalFormatting sqref="A2:A18">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B19">
+  <conditionalFormatting sqref="B2:B18">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C19">
+  <conditionalFormatting sqref="C2:C18">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D19">
+  <conditionalFormatting sqref="D2:D18">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E19">
+  <conditionalFormatting sqref="E2:E18">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F19">
+  <conditionalFormatting sqref="F2:F18">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G19">
+  <conditionalFormatting sqref="G2:G18">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H19">
+  <conditionalFormatting sqref="H2:H18">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I19">
+  <conditionalFormatting sqref="I2:I18">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J19">
+  <conditionalFormatting sqref="J2:J18">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K19">
+  <conditionalFormatting sqref="K2:K18">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L19">
+  <conditionalFormatting sqref="L2:L18">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2208,12 +2119,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M19">
+  <conditionalFormatting sqref="M2:M18">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N19">
+  <conditionalFormatting sqref="N2:N18">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2230,22 +2141,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O19">
+  <conditionalFormatting sqref="O2:O18">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P19">
+  <conditionalFormatting sqref="P2:P18">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q19">
+  <conditionalFormatting sqref="Q2:Q18">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R19">
+  <conditionalFormatting sqref="R2:R18">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="148">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260702--01</t>
-  </si>
-  <si>
-    <t>20260702--02</t>
-  </si>
-  <si>
-    <t>20260702--03</t>
-  </si>
-  <si>
     <t>20260703--01</t>
   </si>
   <si>
@@ -121,169 +112,169 @@
     <t>20260708--02</t>
   </si>
   <si>
-    <t>03:58</t>
+    <t>20260709--01</t>
+  </si>
+  <si>
+    <t>20260709--02</t>
+  </si>
+  <si>
+    <t>20260709--03</t>
+  </si>
+  <si>
+    <t>01:57</t>
+  </si>
+  <si>
+    <t>06:42</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>04:25</t>
+  </si>
+  <si>
+    <t>02:41</t>
+  </si>
+  <si>
+    <t>05:47</t>
+  </si>
+  <si>
+    <t>05:48</t>
+  </si>
+  <si>
+    <t>04:52</t>
+  </si>
+  <si>
+    <t>06:29</t>
+  </si>
+  <si>
+    <t>03:31</t>
   </si>
   <si>
     <t>06:43</t>
   </si>
   <si>
-    <t>05:59</t>
-  </si>
-  <si>
-    <t>01:58</t>
-  </si>
-  <si>
-    <t>06:42</t>
-  </si>
-  <si>
-    <t>06:24</t>
-  </si>
-  <si>
-    <t>04:25</t>
-  </si>
-  <si>
-    <t>02:42</t>
-  </si>
-  <si>
-    <t>05:47</t>
-  </si>
-  <si>
-    <t>05:48</t>
-  </si>
-  <si>
-    <t>04:52</t>
-  </si>
-  <si>
-    <t>06:28</t>
-  </si>
-  <si>
-    <t>03:30</t>
-  </si>
-  <si>
-    <t>06:44</t>
-  </si>
-  <si>
-    <t>00:15</t>
+    <t>00:17</t>
   </si>
   <si>
     <t>06:37</t>
   </si>
   <si>
-    <t>02:17</t>
+    <t>02:14</t>
+  </si>
+  <si>
+    <t>06:14</t>
+  </si>
+  <si>
+    <t>04:54</t>
+  </si>
+  <si>
+    <t>05:31</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:33:30</t>
-  </si>
-  <si>
-    <t>04:10:35</t>
-  </si>
-  <si>
-    <t>20:50:27</t>
-  </si>
-  <si>
     <t>01:47:11</t>
   </si>
   <si>
     <t>03:24:09</t>
   </si>
   <si>
-    <t>02:37:41</t>
-  </si>
-  <si>
-    <t>04:15:28</t>
-  </si>
-  <si>
-    <t>20:55:51</t>
-  </si>
-  <si>
-    <t>01:51:11</t>
-  </si>
-  <si>
-    <t>03:28:37</t>
-  </si>
-  <si>
-    <t>01:04:38</t>
-  </si>
-  <si>
-    <t>02:41:49</t>
-  </si>
-  <si>
-    <t>00:18:02</t>
-  </si>
-  <si>
-    <t>01:55:03</t>
-  </si>
-  <si>
-    <t>23:31:21</t>
-  </si>
-  <si>
-    <t>01:08:16</t>
-  </si>
-  <si>
-    <t>02:46:22</t>
-  </si>
-  <si>
-    <t>02:36:20</t>
-  </si>
-  <si>
-    <t>04:12:42</t>
-  </si>
-  <si>
-    <t>20:52:44</t>
-  </si>
-  <si>
-    <t>01:50:42</t>
+    <t>02:37:42</t>
+  </si>
+  <si>
+    <t>04:15:29</t>
+  </si>
+  <si>
+    <t>20:55:54</t>
+  </si>
+  <si>
+    <t>01:51:14</t>
+  </si>
+  <si>
+    <t>03:28:40</t>
+  </si>
+  <si>
+    <t>01:04:43</t>
+  </si>
+  <si>
+    <t>02:41:54</t>
+  </si>
+  <si>
+    <t>00:18:09</t>
+  </si>
+  <si>
+    <t>01:55:10</t>
+  </si>
+  <si>
+    <t>23:31:31</t>
+  </si>
+  <si>
+    <t>01:08:26</t>
+  </si>
+  <si>
+    <t>02:46:32</t>
+  </si>
+  <si>
+    <t>00:21:42</t>
+  </si>
+  <si>
+    <t>01:59:21</t>
+  </si>
+  <si>
+    <t>23:34:55</t>
+  </si>
+  <si>
+    <t>01:50:43</t>
   </si>
   <si>
     <t>03:26:16</t>
   </si>
   <si>
-    <t>02:39:52</t>
-  </si>
-  <si>
-    <t>04:18:06</t>
-  </si>
-  <si>
-    <t>20:59:05</t>
-  </si>
-  <si>
-    <t>01:53:31</t>
-  </si>
-  <si>
-    <t>03:30:55</t>
-  </si>
-  <si>
-    <t>01:07:12</t>
-  </si>
-  <si>
-    <t>02:43:59</t>
-  </si>
-  <si>
-    <t>00:21:00</t>
-  </si>
-  <si>
-    <t>01:57:09</t>
-  </si>
-  <si>
-    <t>23:35:45</t>
-  </si>
-  <si>
-    <t>01:10:24</t>
-  </si>
-  <si>
-    <t>02:49:41</t>
-  </si>
-  <si>
-    <t>02:38:19</t>
-  </si>
-  <si>
-    <t>04:16:03</t>
-  </si>
-  <si>
-    <t>20:55:43</t>
+    <t>02:39:54</t>
+  </si>
+  <si>
+    <t>04:18:07</t>
+  </si>
+  <si>
+    <t>20:59:08</t>
+  </si>
+  <si>
+    <t>01:53:34</t>
+  </si>
+  <si>
+    <t>03:30:57</t>
+  </si>
+  <si>
+    <t>01:07:17</t>
+  </si>
+  <si>
+    <t>02:44:03</t>
+  </si>
+  <si>
+    <t>00:21:07</t>
+  </si>
+  <si>
+    <t>01:57:17</t>
+  </si>
+  <si>
+    <t>23:35:55</t>
+  </si>
+  <si>
+    <t>01:10:35</t>
+  </si>
+  <si>
+    <t>02:49:53</t>
+  </si>
+  <si>
+    <t>00:23:55</t>
+  </si>
+  <si>
+    <t>02:01:51</t>
+  </si>
+  <si>
+    <t>23:37:19</t>
   </si>
   <si>
     <t>01:51:41</t>
@@ -292,46 +283,46 @@
     <t>03:29:37</t>
   </si>
   <si>
-    <t>02:43:04</t>
-  </si>
-  <si>
-    <t>04:20:19</t>
-  </si>
-  <si>
-    <t>21:00:26</t>
-  </si>
-  <si>
-    <t>01:56:24</t>
-  </si>
-  <si>
-    <t>03:33:49</t>
-  </si>
-  <si>
-    <t>01:09:38</t>
-  </si>
-  <si>
-    <t>02:47:13</t>
-  </si>
-  <si>
-    <t>00:22:45</t>
-  </si>
-  <si>
-    <t>02:00:31</t>
-  </si>
-  <si>
-    <t>01:13:43</t>
-  </si>
-  <si>
-    <t>02:50:49</t>
-  </si>
-  <si>
-    <t>02:40:18</t>
-  </si>
-  <si>
-    <t>04:19:25</t>
-  </si>
-  <si>
-    <t>20:58:43</t>
+    <t>02:43:05</t>
+  </si>
+  <si>
+    <t>04:20:20</t>
+  </si>
+  <si>
+    <t>21:00:29</t>
+  </si>
+  <si>
+    <t>01:56:27</t>
+  </si>
+  <si>
+    <t>03:33:51</t>
+  </si>
+  <si>
+    <t>01:09:43</t>
+  </si>
+  <si>
+    <t>02:47:18</t>
+  </si>
+  <si>
+    <t>00:22:52</t>
+  </si>
+  <si>
+    <t>02:00:39</t>
+  </si>
+  <si>
+    <t>01:13:53</t>
+  </si>
+  <si>
+    <t>02:51:00</t>
+  </si>
+  <si>
+    <t>00:27:02</t>
+  </si>
+  <si>
+    <t>02:04:18</t>
+  </si>
+  <si>
+    <t>23:40:05</t>
   </si>
   <si>
     <t>01:52:40</t>
@@ -340,49 +331,46 @@
     <t>03:32:58</t>
   </si>
   <si>
-    <t>02:46:16</t>
-  </si>
-  <si>
-    <t>04:22:31</t>
-  </si>
-  <si>
-    <t>21:01:47</t>
-  </si>
-  <si>
-    <t>01:59:18</t>
-  </si>
-  <si>
-    <t>03:36:43</t>
-  </si>
-  <si>
-    <t>01:12:04</t>
-  </si>
-  <si>
-    <t>02:50:27</t>
-  </si>
-  <si>
-    <t>00:24:30</t>
-  </si>
-  <si>
-    <t>02:03:53</t>
-  </si>
-  <si>
-    <t>23:36:00</t>
-  </si>
-  <si>
-    <t>01:17:01</t>
-  </si>
-  <si>
-    <t>02:51:58</t>
-  </si>
-  <si>
-    <t>02:43:07</t>
-  </si>
-  <si>
-    <t>04:21:31</t>
-  </si>
-  <si>
-    <t>21:01:00</t>
+    <t>02:46:17</t>
+  </si>
+  <si>
+    <t>04:22:32</t>
+  </si>
+  <si>
+    <t>21:01:49</t>
+  </si>
+  <si>
+    <t>03:36:45</t>
+  </si>
+  <si>
+    <t>01:12:09</t>
+  </si>
+  <si>
+    <t>02:50:32</t>
+  </si>
+  <si>
+    <t>00:24:38</t>
+  </si>
+  <si>
+    <t>02:04:00</t>
+  </si>
+  <si>
+    <t>23:36:12</t>
+  </si>
+  <si>
+    <t>01:17:12</t>
+  </si>
+  <si>
+    <t>02:52:07</t>
+  </si>
+  <si>
+    <t>00:30:09</t>
+  </si>
+  <si>
+    <t>02:06:45</t>
+  </si>
+  <si>
+    <t>23:42:50</t>
   </si>
   <si>
     <t>01:56:11</t>
@@ -391,48 +379,54 @@
     <t>03:35:05</t>
   </si>
   <si>
-    <t>02:48:27</t>
-  </si>
-  <si>
-    <t>04:25:09</t>
-  </si>
-  <si>
-    <t>21:05:02</t>
-  </si>
-  <si>
-    <t>02:01:37</t>
-  </si>
-  <si>
-    <t>03:39:00</t>
-  </si>
-  <si>
-    <t>01:14:38</t>
-  </si>
-  <si>
-    <t>02:52:36</t>
-  </si>
-  <si>
-    <t>00:27:28</t>
-  </si>
-  <si>
-    <t>02:05:59</t>
-  </si>
-  <si>
-    <t>23:40:09</t>
-  </si>
-  <si>
-    <t>01:19:09</t>
-  </si>
-  <si>
-    <t>02:55:17</t>
+    <t>02:48:28</t>
+  </si>
+  <si>
+    <t>04:25:10</t>
+  </si>
+  <si>
+    <t>21:05:04</t>
+  </si>
+  <si>
+    <t>02:01:40</t>
+  </si>
+  <si>
+    <t>03:39:03</t>
+  </si>
+  <si>
+    <t>01:14:42</t>
+  </si>
+  <si>
+    <t>02:52:41</t>
+  </si>
+  <si>
+    <t>00:27:35</t>
+  </si>
+  <si>
+    <t>02:06:06</t>
+  </si>
+  <si>
+    <t>23:40:19</t>
+  </si>
+  <si>
+    <t>01:19:19</t>
+  </si>
+  <si>
+    <t>02:55:27</t>
+  </si>
+  <si>
+    <t>00:32:21</t>
+  </si>
+  <si>
+    <t>02:09:15</t>
+  </si>
+  <si>
+    <t>23:45:13</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>8°</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -442,13 +436,16 @@
     <t>7°</t>
   </si>
   <si>
-    <t>04:19:48</t>
-  </si>
-  <si>
-    <t>00:18:44</t>
-  </si>
-  <si>
-    <t>23:33:40</t>
+    <t>00:18:51</t>
+  </si>
+  <si>
+    <t>23:33:50</t>
+  </si>
+  <si>
+    <t>00:21:45</t>
+  </si>
+  <si>
+    <t>23:36:38</t>
   </si>
   <si>
     <t>B</t>
@@ -457,13 +454,10 @@
     <t>A+B</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -497,7 +491,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -518,7 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,7 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -543,6 +537,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,7 +583,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -616,6 +616,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1097,7 +1100,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>35</v>
@@ -1118,28 +1121,28 @@
         <v>103</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>53</v>
       </c>
       <c r="L2" s="4">
-        <v>-34.4</v>
+        <v>-37.8</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O2" s="6">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="P2" s="7">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1153,7 +1156,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>36</v>
@@ -1174,28 +1177,28 @@
         <v>104</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>142</v>
+        <v>54</v>
       </c>
       <c r="L3" s="4">
-        <v>-21.8</v>
+        <v>-28.7</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>147</v>
       </c>
       <c r="O3" s="6">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="P3" s="9">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1209,7 +1212,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>37</v>
@@ -1230,28 +1233,28 @@
         <v>105</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>139</v>
+        <v>55</v>
       </c>
       <c r="L4" s="4">
-        <v>-10.1</v>
+        <v>-34.2</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O4" s="10">
-        <v>0</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="P4" s="11">
+        <v>5</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
@@ -1265,7 +1268,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>38</v>
@@ -1286,22 +1289,22 @@
         <v>106</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>56</v>
       </c>
       <c r="L5" s="4">
-        <v>-37.8</v>
+        <v>-21.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="O5" s="10">
         <v>0</v>
@@ -1321,7 +1324,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>39</v>
@@ -1342,22 +1345,22 @@
         <v>107</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>137</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="L6" s="4">
-        <v>-28.7</v>
+        <v>-11</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>145</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O6" s="10">
         <v>0</v>
@@ -1377,7 +1380,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>40</v>
@@ -1395,22 +1398,22 @@
         <v>92</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>58</v>
       </c>
       <c r="L7" s="4">
-        <v>-34.2</v>
+        <v>-37.7</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>147</v>
@@ -1433,7 +1436,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>41</v>
@@ -1451,31 +1454,31 @@
         <v>93</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>59</v>
       </c>
       <c r="L8" s="4">
-        <v>-21.4</v>
+        <v>-28.3</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="O8" s="10">
-        <v>0</v>
+      <c r="O8" s="12">
+        <v>2</v>
       </c>
       <c r="P8" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="8">
         <v>0</v>
@@ -1489,7 +1492,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>42</v>
@@ -1507,28 +1510,28 @@
         <v>94</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="L9" s="4">
-        <v>-11</v>
+        <v>-39</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="O9" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P9" s="8">
         <v>0</v>
@@ -1545,7 +1548,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>43</v>
@@ -1563,28 +1566,28 @@
         <v>95</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>61</v>
       </c>
       <c r="L10" s="4">
-        <v>-37.7</v>
+        <v>-34</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>147</v>
       </c>
       <c r="O10" s="10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
@@ -1601,7 +1604,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>44</v>
@@ -1619,25 +1622,25 @@
         <v>96</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>62</v>
+        <v>140</v>
       </c>
       <c r="L11" s="4">
-        <v>-28.3</v>
+        <v>-37.8</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O11" s="10">
         <v>0</v>
@@ -1657,7 +1660,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>45</v>
@@ -1675,28 +1678,28 @@
         <v>97</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>63</v>
       </c>
       <c r="L12" s="4">
-        <v>-39</v>
+        <v>-37.7</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>147</v>
       </c>
       <c r="O12" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
@@ -1713,7 +1716,7 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>46</v>
@@ -1728,37 +1731,37 @@
         <v>81</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="L13" s="4">
-        <v>-34</v>
+        <v>-34.2</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O13" s="10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
       </c>
-      <c r="Q13" s="8">
-        <v>0</v>
+      <c r="Q13" s="11">
+        <v>6</v>
       </c>
       <c r="R13" s="8">
         <v>0</v>
@@ -1769,7 +1772,7 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>47</v>
@@ -1784,37 +1787,37 @@
         <v>82</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="L14" s="4">
-        <v>-37.8</v>
+        <v>-39.2</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="O14" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P14" s="8">
         <v>0</v>
       </c>
-      <c r="Q14" s="11">
-        <v>3</v>
+      <c r="Q14" s="8">
+        <v>1</v>
       </c>
       <c r="R14" s="8">
         <v>0</v>
@@ -1825,7 +1828,7 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>48</v>
@@ -1840,31 +1843,31 @@
         <v>83</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>66</v>
       </c>
       <c r="L15" s="4">
-        <v>-37.7</v>
+        <v>-33.8</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O15" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P15" s="8">
         <v>0</v>
@@ -1881,7 +1884,7 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>49</v>
@@ -1896,37 +1899,37 @@
         <v>84</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="K16" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="L16" s="4">
+        <v>-38.2</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="L16" s="4">
-        <v>-34.2</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="N16" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="O16" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" s="8">
         <v>0</v>
       </c>
       <c r="Q16" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" s="8">
         <v>0</v>
@@ -1937,7 +1940,7 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>50</v>
@@ -1955,28 +1958,28 @@
         <v>101</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>68</v>
       </c>
       <c r="L17" s="4">
-        <v>-39.2</v>
+        <v>-37.7</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>147</v>
       </c>
       <c r="O17" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P17" s="8">
         <v>0</v>
@@ -1993,7 +1996,7 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>51</v>
@@ -2011,28 +2014,28 @@
         <v>102</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="L18" s="4">
-        <v>-33.8</v>
+        <v>-34.8</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="O18" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P18" s="8">
         <v>0</v>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="152">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260703--01</t>
-  </si>
-  <si>
-    <t>20260703--02</t>
-  </si>
-  <si>
     <t>20260704--01</t>
   </si>
   <si>
@@ -121,10 +115,10 @@
     <t>20260709--03</t>
   </si>
   <si>
-    <t>01:57</t>
-  </si>
-  <si>
-    <t>06:42</t>
+    <t>20260710--01</t>
+  </si>
+  <si>
+    <t>20260710--02</t>
   </si>
   <si>
     <t>06:23</t>
@@ -172,13 +166,16 @@
     <t>05:31</t>
   </si>
   <si>
+    <t>06:03</t>
+  </si>
+  <si>
+    <t>04:29</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:47:11</t>
-  </si>
-  <si>
-    <t>03:24:09</t>
+    <t>00:43</t>
   </si>
   <si>
     <t>02:37:42</t>
@@ -226,10 +223,10 @@
     <t>23:34:55</t>
   </si>
   <si>
-    <t>01:50:43</t>
-  </si>
-  <si>
-    <t>03:26:16</t>
+    <t>01:12:15</t>
+  </si>
+  <si>
+    <t>22:48:06</t>
   </si>
   <si>
     <t>02:39:54</t>
@@ -277,10 +274,10 @@
     <t>23:37:19</t>
   </si>
   <si>
-    <t>01:51:41</t>
-  </si>
-  <si>
-    <t>03:29:37</t>
+    <t>01:14:29</t>
+  </si>
+  <si>
+    <t>22:50:46</t>
   </si>
   <si>
     <t>02:43:05</t>
@@ -325,10 +322,10 @@
     <t>23:40:05</t>
   </si>
   <si>
-    <t>01:52:40</t>
-  </si>
-  <si>
-    <t>03:32:58</t>
+    <t>01:17:31</t>
+  </si>
+  <si>
+    <t>22:53:01</t>
   </si>
   <si>
     <t>02:46:17</t>
@@ -373,10 +370,10 @@
     <t>23:42:50</t>
   </si>
   <si>
-    <t>01:56:11</t>
-  </si>
-  <si>
-    <t>03:35:05</t>
+    <t>01:20:32</t>
+  </si>
+  <si>
+    <t>22:55:15</t>
   </si>
   <si>
     <t>02:48:28</t>
@@ -424,6 +421,12 @@
     <t>23:45:13</t>
   </si>
   <si>
+    <t>01:22:46</t>
+  </si>
+  <si>
+    <t>22:57:55</t>
+  </si>
+  <si>
     <t>0°</t>
   </si>
   <si>
@@ -436,6 +439,9 @@
     <t>7°</t>
   </si>
   <si>
+    <t>13°</t>
+  </si>
+  <si>
     <t>00:18:51</t>
   </si>
   <si>
@@ -448,16 +454,22 @@
     <t>23:36:38</t>
   </si>
   <si>
+    <t>22:51:29</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
-    <t>3</t>
+    <t>2</t>
   </si>
 </sst>
 </file>
@@ -491,7 +503,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -506,13 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,7 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +554,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,7 +601,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -619,6 +637,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1100,7 +1121,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>35</v>
@@ -1109,40 +1130,40 @@
         <v>52</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L2" s="4">
-        <v>-37.8</v>
+        <v>-34.2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O2" s="6">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="P2" s="7">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1156,7 +1177,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>36</v>
@@ -1165,40 +1186,40 @@
         <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L3" s="4">
-        <v>-28.7</v>
+        <v>-21.4</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O3" s="6">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="P3" s="9">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1212,7 +1233,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>37</v>
@@ -1221,40 +1242,40 @@
         <v>52</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>55</v>
+        <v>138</v>
       </c>
       <c r="L4" s="4">
-        <v>-34.2</v>
+        <v>-11</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="O4" s="10">
-        <v>5</v>
-      </c>
-      <c r="P4" s="11">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
@@ -1268,7 +1289,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>38</v>
@@ -1277,34 +1298,34 @@
         <v>52</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L5" s="4">
-        <v>-21.4</v>
+        <v>-37.7</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O5" s="10">
         <v>0</v>
@@ -1324,7 +1345,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>39</v>
@@ -1333,34 +1354,34 @@
         <v>52</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>107</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>137</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>137</v>
+        <v>58</v>
       </c>
       <c r="L6" s="4">
-        <v>-11</v>
+        <v>-28.3</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O6" s="10">
         <v>0</v>
@@ -1380,7 +1401,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>40</v>
@@ -1389,43 +1410,43 @@
         <v>52</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L7" s="4">
-        <v>-37.7</v>
+        <v>-39</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O7" s="10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P7" s="8">
         <v>0</v>
       </c>
       <c r="Q7" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R7" s="8">
         <v>0</v>
@@ -1436,7 +1457,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>41</v>
@@ -1445,43 +1466,43 @@
         <v>52</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L8" s="4">
-        <v>-28.3</v>
+        <v>-34</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="O8" s="12">
-        <v>2</v>
+        <v>149</v>
+      </c>
+      <c r="O8" s="10">
+        <v>5</v>
       </c>
       <c r="P8" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>4</v>
       </c>
       <c r="R8" s="8">
         <v>0</v>
@@ -1492,7 +1513,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>42</v>
@@ -1501,46 +1522,46 @@
         <v>52</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="L9" s="4">
-        <v>-39</v>
+        <v>-37.8</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="O9" s="10">
-        <v>2</v>
+        <v>150</v>
+      </c>
+      <c r="O9" s="12">
+        <v>52</v>
       </c>
       <c r="P9" s="8">
         <v>0</v>
       </c>
       <c r="Q9" s="8">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R9" s="11">
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1548,7 +1569,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>43</v>
@@ -1557,43 +1578,43 @@
         <v>52</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L10" s="4">
-        <v>-34</v>
+        <v>-37.7</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O10" s="10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
       </c>
-      <c r="Q10" s="8">
-        <v>0</v>
+      <c r="Q10" s="11">
+        <v>7</v>
       </c>
       <c r="R10" s="8">
         <v>0</v>
@@ -1604,7 +1625,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>44</v>
@@ -1613,43 +1634,43 @@
         <v>52</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L11" s="4">
-        <v>-37.8</v>
+        <v>-34.2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="O11" s="10">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P11" s="8">
         <v>0</v>
       </c>
-      <c r="Q11" s="8">
-        <v>0</v>
+      <c r="Q11" s="13">
+        <v>12</v>
       </c>
       <c r="R11" s="8">
         <v>0</v>
@@ -1660,7 +1681,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>45</v>
@@ -1669,43 +1690,43 @@
         <v>52</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>97</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L12" s="4">
-        <v>-37.7</v>
+        <v>-39.2</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O12" s="10">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
       </c>
-      <c r="Q12" s="8">
-        <v>0</v>
+      <c r="Q12" s="11">
+        <v>7</v>
       </c>
       <c r="R12" s="8">
         <v>0</v>
@@ -1716,7 +1737,7 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>46</v>
@@ -1725,43 +1746,43 @@
         <v>52</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>141</v>
+        <v>65</v>
       </c>
       <c r="L13" s="4">
-        <v>-34.2</v>
+        <v>-33.8</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="O13" s="10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
       </c>
       <c r="Q13" s="11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R13" s="8">
         <v>0</v>
@@ -1772,7 +1793,7 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>47</v>
@@ -1781,43 +1802,43 @@
         <v>52</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>65</v>
+        <v>144</v>
       </c>
       <c r="L14" s="4">
-        <v>-39.2</v>
+        <v>-38.2</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O14" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P14" s="8">
         <v>0</v>
       </c>
       <c r="Q14" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" s="8">
         <v>0</v>
@@ -1828,7 +1849,7 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>48</v>
@@ -1837,46 +1858,46 @@
         <v>52</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L15" s="4">
-        <v>-33.8</v>
+        <v>-37.7</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O15" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P15" s="8">
         <v>0</v>
       </c>
       <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+      <c r="R15" s="8">
         <v>1</v>
-      </c>
-      <c r="R15" s="8">
-        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1884,7 +1905,7 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>49</v>
@@ -1893,43 +1914,43 @@
         <v>52</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="L16" s="4">
-        <v>-38.2</v>
+        <v>-34.8</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O16" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P16" s="8">
         <v>0</v>
       </c>
-      <c r="Q16" s="8">
-        <v>0</v>
+      <c r="Q16" s="11">
+        <v>3</v>
       </c>
       <c r="R16" s="8">
         <v>0</v>
@@ -1940,7 +1961,7 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>50</v>
@@ -1949,43 +1970,43 @@
         <v>52</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L17" s="4">
-        <v>-37.7</v>
+        <v>-39.4</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O17" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" s="8">
         <v>0</v>
       </c>
       <c r="Q17" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="8">
         <v>0</v>
@@ -1996,46 +2017,46 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="L18" s="4">
-        <v>-34.8</v>
+        <v>-29.4</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="O18" s="10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P18" s="8">
         <v>0</v>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="155">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260704--01</t>
-  </si>
-  <si>
-    <t>20260704--02</t>
-  </si>
-  <si>
-    <t>20260704--03</t>
-  </si>
-  <si>
     <t>20260705--01</t>
   </si>
   <si>
@@ -121,25 +112,22 @@
     <t>20260710--02</t>
   </si>
   <si>
-    <t>06:23</t>
-  </si>
-  <si>
-    <t>04:25</t>
-  </si>
-  <si>
-    <t>02:41</t>
+    <t>20260711--01</t>
+  </si>
+  <si>
+    <t>20260711--02</t>
+  </si>
+  <si>
+    <t>20260711--03</t>
   </si>
   <si>
     <t>05:47</t>
   </si>
   <si>
-    <t>05:48</t>
-  </si>
-  <si>
     <t>04:52</t>
   </si>
   <si>
-    <t>06:29</t>
+    <t>06:28</t>
   </si>
   <si>
     <t>03:31</t>
@@ -148,7 +136,7 @@
     <t>06:43</t>
   </si>
   <si>
-    <t>00:17</t>
+    <t>00:16</t>
   </si>
   <si>
     <t>06:37</t>
@@ -157,19 +145,25 @@
     <t>02:14</t>
   </si>
   <si>
-    <t>06:14</t>
+    <t>06:13</t>
   </si>
   <si>
     <t>04:54</t>
   </si>
   <si>
-    <t>05:31</t>
+    <t>05:32</t>
   </si>
   <si>
     <t>06:03</t>
   </si>
   <si>
-    <t>04:29</t>
+    <t>04:30</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>02:53</t>
   </si>
   <si>
     <t>00:00</t>
@@ -178,13 +172,7 @@
     <t>00:43</t>
   </si>
   <si>
-    <t>02:37:42</t>
-  </si>
-  <si>
-    <t>04:15:29</t>
-  </si>
-  <si>
-    <t>20:55:54</t>
+    <t>01:53</t>
   </si>
   <si>
     <t>01:51:14</t>
@@ -193,150 +181,153 @@
     <t>03:28:40</t>
   </si>
   <si>
-    <t>01:04:43</t>
-  </si>
-  <si>
-    <t>02:41:54</t>
-  </si>
-  <si>
-    <t>00:18:09</t>
-  </si>
-  <si>
-    <t>01:55:10</t>
-  </si>
-  <si>
-    <t>23:31:31</t>
-  </si>
-  <si>
-    <t>01:08:26</t>
-  </si>
-  <si>
-    <t>02:46:32</t>
-  </si>
-  <si>
-    <t>00:21:42</t>
+    <t>01:04:44</t>
+  </si>
+  <si>
+    <t>02:41:55</t>
+  </si>
+  <si>
+    <t>00:18:10</t>
+  </si>
+  <si>
+    <t>01:55:11</t>
+  </si>
+  <si>
+    <t>23:31:33</t>
+  </si>
+  <si>
+    <t>01:08:28</t>
+  </si>
+  <si>
+    <t>02:46:34</t>
+  </si>
+  <si>
+    <t>00:21:44</t>
+  </si>
+  <si>
+    <t>01:59:23</t>
+  </si>
+  <si>
+    <t>23:34:58</t>
+  </si>
+  <si>
+    <t>01:12:18</t>
+  </si>
+  <si>
+    <t>22:48:09</t>
+  </si>
+  <si>
+    <t>00:25:16</t>
+  </si>
+  <si>
+    <t>22:01:18</t>
+  </si>
+  <si>
+    <t>23:38:15</t>
+  </si>
+  <si>
+    <t>01:53:34</t>
+  </si>
+  <si>
+    <t>03:30:58</t>
+  </si>
+  <si>
+    <t>01:07:17</t>
+  </si>
+  <si>
+    <t>02:44:04</t>
+  </si>
+  <si>
+    <t>00:21:08</t>
+  </si>
+  <si>
+    <t>01:57:18</t>
+  </si>
+  <si>
+    <t>23:35:57</t>
+  </si>
+  <si>
+    <t>01:10:36</t>
+  </si>
+  <si>
+    <t>02:49:54</t>
+  </si>
+  <si>
+    <t>00:23:57</t>
+  </si>
+  <si>
+    <t>02:01:53</t>
+  </si>
+  <si>
+    <t>23:37:21</t>
+  </si>
+  <si>
+    <t>01:14:32</t>
+  </si>
+  <si>
+    <t>22:50:49</t>
+  </si>
+  <si>
+    <t>00:27:24</t>
+  </si>
+  <si>
+    <t>22:04:28</t>
+  </si>
+  <si>
+    <t>23:40:22</t>
+  </si>
+  <si>
+    <t>01:56:27</t>
+  </si>
+  <si>
+    <t>03:33:52</t>
+  </si>
+  <si>
+    <t>01:09:43</t>
+  </si>
+  <si>
+    <t>02:47:18</t>
+  </si>
+  <si>
+    <t>00:22:53</t>
+  </si>
+  <si>
+    <t>02:00:40</t>
+  </si>
+  <si>
+    <t>01:13:55</t>
+  </si>
+  <si>
+    <t>02:51:01</t>
+  </si>
+  <si>
+    <t>00:27:04</t>
+  </si>
+  <si>
+    <t>02:04:20</t>
+  </si>
+  <si>
+    <t>23:40:07</t>
+  </si>
+  <si>
+    <t>01:17:34</t>
+  </si>
+  <si>
+    <t>22:53:04</t>
+  </si>
+  <si>
+    <t>00:30:41</t>
+  </si>
+  <si>
+    <t>22:05:55</t>
+  </si>
+  <si>
+    <t>23:43:44</t>
   </si>
   <si>
     <t>01:59:21</t>
   </si>
   <si>
-    <t>23:34:55</t>
-  </si>
-  <si>
-    <t>01:12:15</t>
-  </si>
-  <si>
-    <t>22:48:06</t>
-  </si>
-  <si>
-    <t>02:39:54</t>
-  </si>
-  <si>
-    <t>04:18:07</t>
-  </si>
-  <si>
-    <t>20:59:08</t>
-  </si>
-  <si>
-    <t>01:53:34</t>
-  </si>
-  <si>
-    <t>03:30:57</t>
-  </si>
-  <si>
-    <t>01:07:17</t>
-  </si>
-  <si>
-    <t>02:44:03</t>
-  </si>
-  <si>
-    <t>00:21:07</t>
-  </si>
-  <si>
-    <t>01:57:17</t>
-  </si>
-  <si>
-    <t>23:35:55</t>
-  </si>
-  <si>
-    <t>01:10:35</t>
-  </si>
-  <si>
-    <t>02:49:53</t>
-  </si>
-  <si>
-    <t>00:23:55</t>
-  </si>
-  <si>
-    <t>02:01:51</t>
-  </si>
-  <si>
-    <t>23:37:19</t>
-  </si>
-  <si>
-    <t>01:14:29</t>
-  </si>
-  <si>
-    <t>22:50:46</t>
-  </si>
-  <si>
-    <t>02:43:05</t>
-  </si>
-  <si>
-    <t>04:20:20</t>
-  </si>
-  <si>
-    <t>21:00:29</t>
-  </si>
-  <si>
-    <t>01:56:27</t>
-  </si>
-  <si>
-    <t>03:33:51</t>
-  </si>
-  <si>
-    <t>01:09:43</t>
-  </si>
-  <si>
-    <t>02:47:18</t>
-  </si>
-  <si>
-    <t>00:22:52</t>
-  </si>
-  <si>
-    <t>02:00:39</t>
-  </si>
-  <si>
-    <t>01:13:53</t>
-  </si>
-  <si>
-    <t>02:51:00</t>
-  </si>
-  <si>
-    <t>00:27:02</t>
-  </si>
-  <si>
-    <t>02:04:18</t>
-  </si>
-  <si>
-    <t>23:40:05</t>
-  </si>
-  <si>
-    <t>01:17:31</t>
-  </si>
-  <si>
-    <t>22:53:01</t>
-  </si>
-  <si>
-    <t>02:46:17</t>
-  </si>
-  <si>
-    <t>04:22:32</t>
-  </si>
-  <si>
-    <t>21:01:49</t>
-  </si>
-  <si>
     <t>03:36:45</t>
   </si>
   <si>
@@ -346,43 +337,43 @@
     <t>02:50:32</t>
   </si>
   <si>
-    <t>00:24:38</t>
-  </si>
-  <si>
-    <t>02:04:00</t>
-  </si>
-  <si>
-    <t>23:36:12</t>
-  </si>
-  <si>
-    <t>01:17:12</t>
-  </si>
-  <si>
-    <t>02:52:07</t>
-  </si>
-  <si>
-    <t>00:30:09</t>
-  </si>
-  <si>
-    <t>02:06:45</t>
-  </si>
-  <si>
-    <t>23:42:50</t>
-  </si>
-  <si>
-    <t>01:20:32</t>
-  </si>
-  <si>
-    <t>22:55:15</t>
-  </si>
-  <si>
-    <t>02:48:28</t>
-  </si>
-  <si>
-    <t>04:25:10</t>
-  </si>
-  <si>
-    <t>21:05:04</t>
+    <t>00:24:39</t>
+  </si>
+  <si>
+    <t>02:04:01</t>
+  </si>
+  <si>
+    <t>23:36:13</t>
+  </si>
+  <si>
+    <t>01:17:13</t>
+  </si>
+  <si>
+    <t>02:52:08</t>
+  </si>
+  <si>
+    <t>00:30:10</t>
+  </si>
+  <si>
+    <t>02:06:47</t>
+  </si>
+  <si>
+    <t>23:42:53</t>
+  </si>
+  <si>
+    <t>01:20:35</t>
+  </si>
+  <si>
+    <t>22:55:19</t>
+  </si>
+  <si>
+    <t>00:33:59</t>
+  </si>
+  <si>
+    <t>22:07:21</t>
+  </si>
+  <si>
+    <t>23:47:05</t>
   </si>
   <si>
     <t>02:01:40</t>
@@ -391,48 +382,54 @@
     <t>03:39:03</t>
   </si>
   <si>
-    <t>01:14:42</t>
+    <t>01:14:43</t>
   </si>
   <si>
     <t>02:52:41</t>
   </si>
   <si>
-    <t>00:27:35</t>
-  </si>
-  <si>
-    <t>02:06:06</t>
-  </si>
-  <si>
-    <t>23:40:19</t>
-  </si>
-  <si>
-    <t>01:19:19</t>
-  </si>
-  <si>
-    <t>02:55:27</t>
-  </si>
-  <si>
-    <t>00:32:21</t>
-  </si>
-  <si>
-    <t>02:09:15</t>
-  </si>
-  <si>
-    <t>23:45:13</t>
-  </si>
-  <si>
-    <t>01:22:46</t>
-  </si>
-  <si>
-    <t>22:57:55</t>
+    <t>00:27:36</t>
+  </si>
+  <si>
+    <t>02:06:07</t>
+  </si>
+  <si>
+    <t>23:40:21</t>
+  </si>
+  <si>
+    <t>01:19:21</t>
+  </si>
+  <si>
+    <t>02:55:29</t>
+  </si>
+  <si>
+    <t>00:32:23</t>
+  </si>
+  <si>
+    <t>02:09:17</t>
+  </si>
+  <si>
+    <t>23:45:16</t>
+  </si>
+  <si>
+    <t>01:22:48</t>
+  </si>
+  <si>
+    <t>22:57:58</t>
+  </si>
+  <si>
+    <t>00:36:06</t>
+  </si>
+  <si>
+    <t>22:10:31</t>
+  </si>
+  <si>
+    <t>23:49:11</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>2°</t>
   </si>
   <si>
@@ -442,19 +439,31 @@
     <t>13°</t>
   </si>
   <si>
-    <t>00:18:51</t>
-  </si>
-  <si>
-    <t>23:33:50</t>
-  </si>
-  <si>
-    <t>00:21:45</t>
-  </si>
-  <si>
-    <t>23:36:38</t>
-  </si>
-  <si>
-    <t>22:51:29</t>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>4°</t>
+  </si>
+  <si>
+    <t>00:18:52</t>
+  </si>
+  <si>
+    <t>23:33:51</t>
+  </si>
+  <si>
+    <t>00:21:47</t>
+  </si>
+  <si>
+    <t>23:36:40</t>
+  </si>
+  <si>
+    <t>22:51:32</t>
+  </si>
+  <si>
+    <t>22:06:21</t>
+  </si>
+  <si>
+    <t>23:39:21</t>
   </si>
   <si>
     <t>B</t>
@@ -518,30 +527,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -554,13 +539,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1121,25 +1130,25 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>120</v>
@@ -1148,22 +1157,22 @@
         <v>137</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L2" s="4">
-        <v>-34.2</v>
+        <v>-37.7</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="O2" s="6">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="P2" s="7">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1177,25 +1186,25 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>121</v>
@@ -1204,22 +1213,22 @@
         <v>137</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L3" s="4">
-        <v>-21.4</v>
+        <v>-28.3</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="O3" s="6">
-        <v>22</v>
-      </c>
-      <c r="P3" s="9">
-        <v>20</v>
+        <v>5</v>
+      </c>
+      <c r="P3" s="7">
+        <v>5</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1233,45 +1242,45 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>122</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>138</v>
+        <v>55</v>
       </c>
       <c r="L4" s="4">
-        <v>-11</v>
+        <v>-39</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="O4" s="10">
+        <v>152</v>
+      </c>
+      <c r="O4" s="6">
         <v>0</v>
       </c>
       <c r="P4" s="8">
@@ -1289,25 +1298,25 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>123</v>
@@ -1316,18 +1325,18 @@
         <v>137</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L5" s="4">
-        <v>-37.7</v>
+        <v>-33.9</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="O5" s="10">
+        <v>152</v>
+      </c>
+      <c r="O5" s="6">
         <v>0</v>
       </c>
       <c r="P5" s="8">
@@ -1345,22 +1354,22 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>107</v>
@@ -1369,21 +1378,21 @@
         <v>124</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>58</v>
+        <v>143</v>
       </c>
       <c r="L6" s="4">
-        <v>-28.3</v>
+        <v>-37.8</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="O6" s="10">
+        <v>153</v>
+      </c>
+      <c r="O6" s="6">
         <v>0</v>
       </c>
       <c r="P6" s="8">
@@ -1401,22 +1410,22 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>108</v>
@@ -1428,25 +1437,25 @@
         <v>137</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L7" s="4">
-        <v>-39</v>
+        <v>-37.7</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="O7" s="10">
-        <v>4</v>
+        <v>152</v>
+      </c>
+      <c r="O7" s="6">
+        <v>0</v>
       </c>
       <c r="P7" s="8">
         <v>0</v>
       </c>
       <c r="Q7" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R7" s="8">
         <v>0</v>
@@ -1457,22 +1466,22 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>109</v>
@@ -1481,28 +1490,28 @@
         <v>126</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="L8" s="4">
-        <v>-34</v>
+        <v>-34.2</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="O8" s="10">
-        <v>5</v>
+        <v>153</v>
+      </c>
+      <c r="O8" s="9">
+        <v>22</v>
       </c>
       <c r="P8" s="8">
         <v>0</v>
       </c>
-      <c r="Q8" s="11">
-        <v>4</v>
+      <c r="Q8" s="10">
+        <v>17</v>
       </c>
       <c r="R8" s="8">
         <v>0</v>
@@ -1513,22 +1522,22 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>110</v>
@@ -1537,31 +1546,31 @@
         <v>127</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>142</v>
+        <v>60</v>
       </c>
       <c r="L9" s="4">
-        <v>-37.8</v>
+        <v>-39.2</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="O9" s="12">
-        <v>52</v>
+        <v>152</v>
+      </c>
+      <c r="O9" s="6">
+        <v>3</v>
       </c>
       <c r="P9" s="8">
         <v>0</v>
       </c>
       <c r="Q9" s="8">
-        <v>1</v>
-      </c>
-      <c r="R9" s="11">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="R9" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1569,22 +1578,22 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>111</v>
@@ -1596,25 +1605,25 @@
         <v>137</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L10" s="4">
-        <v>-37.7</v>
+        <v>-33.8</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="O10" s="10">
-        <v>9</v>
+        <v>153</v>
+      </c>
+      <c r="O10" s="6">
+        <v>2</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
       </c>
-      <c r="Q10" s="11">
-        <v>7</v>
+      <c r="Q10" s="8">
+        <v>2</v>
       </c>
       <c r="R10" s="8">
         <v>0</v>
@@ -1625,22 +1634,22 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>112</v>
@@ -1649,28 +1658,28 @@
         <v>129</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L11" s="4">
-        <v>-34.2</v>
+        <v>-38.2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="O11" s="10">
-        <v>12</v>
+        <v>152</v>
+      </c>
+      <c r="O11" s="6">
+        <v>0</v>
       </c>
       <c r="P11" s="8">
         <v>0</v>
       </c>
-      <c r="Q11" s="13">
-        <v>12</v>
+      <c r="Q11" s="8">
+        <v>0</v>
       </c>
       <c r="R11" s="8">
         <v>0</v>
@@ -1681,22 +1690,22 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>113</v>
@@ -1708,25 +1717,25 @@
         <v>137</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L12" s="4">
-        <v>-39.2</v>
+        <v>-37.7</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="O12" s="10">
-        <v>11</v>
+        <v>152</v>
+      </c>
+      <c r="O12" s="6">
+        <v>2</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
       </c>
-      <c r="Q12" s="11">
-        <v>7</v>
+      <c r="Q12" s="8">
+        <v>1</v>
       </c>
       <c r="R12" s="8">
         <v>0</v>
@@ -1737,22 +1746,22 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>114</v>
@@ -1761,28 +1770,28 @@
         <v>131</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>65</v>
+        <v>146</v>
       </c>
       <c r="L13" s="4">
-        <v>-33.8</v>
+        <v>-34.8</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="O13" s="10">
-        <v>10</v>
+        <v>152</v>
+      </c>
+      <c r="O13" s="6">
+        <v>3</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
       </c>
-      <c r="Q13" s="11">
-        <v>5</v>
+      <c r="Q13" s="8">
+        <v>0</v>
       </c>
       <c r="R13" s="8">
         <v>0</v>
@@ -1793,22 +1802,22 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>115</v>
@@ -1820,19 +1829,19 @@
         <v>137</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>144</v>
+        <v>65</v>
       </c>
       <c r="L14" s="4">
-        <v>-38.2</v>
+        <v>-39.4</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="O14" s="10">
-        <v>2</v>
+        <v>152</v>
+      </c>
+      <c r="O14" s="6">
+        <v>3</v>
       </c>
       <c r="P14" s="8">
         <v>0</v>
@@ -1849,22 +1858,22 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>116</v>
@@ -1873,22 +1882,22 @@
         <v>133</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>67</v>
+        <v>147</v>
       </c>
       <c r="L15" s="4">
-        <v>-37.7</v>
+        <v>-29.5</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="O15" s="10">
-        <v>1</v>
+        <v>154</v>
+      </c>
+      <c r="O15" s="6">
+        <v>0</v>
       </c>
       <c r="P15" s="8">
         <v>0</v>
@@ -1897,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="R15" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1905,22 +1914,22 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>117</v>
@@ -1929,28 +1938,28 @@
         <v>134</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>145</v>
+        <v>67</v>
       </c>
       <c r="L16" s="4">
-        <v>-34.8</v>
+        <v>-38.6</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="O16" s="10">
-        <v>3</v>
+        <v>152</v>
+      </c>
+      <c r="O16" s="6">
+        <v>0</v>
       </c>
       <c r="P16" s="8">
         <v>0</v>
       </c>
-      <c r="Q16" s="11">
-        <v>3</v>
+      <c r="Q16" s="8">
+        <v>0</v>
       </c>
       <c r="R16" s="8">
         <v>0</v>
@@ -1961,22 +1970,22 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>52</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>118</v>
@@ -1985,28 +1994,28 @@
         <v>135</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>69</v>
+        <v>148</v>
       </c>
       <c r="L17" s="4">
-        <v>-39.4</v>
+        <v>-22.7</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="O17" s="10">
-        <v>1</v>
-      </c>
-      <c r="P17" s="8">
-        <v>0</v>
+        <v>153</v>
+      </c>
+      <c r="O17" s="11">
+        <v>60</v>
+      </c>
+      <c r="P17" s="12">
+        <v>34</v>
       </c>
       <c r="Q17" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" s="8">
         <v>0</v>
@@ -2017,22 +2026,22 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>119</v>
@@ -2041,25 +2050,25 @@
         <v>136</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L18" s="4">
-        <v>-29.4</v>
+        <v>-35.3</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O18" s="10">
-        <v>6</v>
-      </c>
-      <c r="P18" s="8">
-        <v>0</v>
+        <v>152</v>
+      </c>
+      <c r="O18" s="11">
+        <v>65</v>
+      </c>
+      <c r="P18" s="13">
+        <v>50</v>
       </c>
       <c r="Q18" s="8">
         <v>0</v>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="152">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260705--01</t>
-  </si>
-  <si>
-    <t>20260705--02</t>
-  </si>
-  <si>
     <t>20260706--01</t>
   </si>
   <si>
@@ -121,49 +115,52 @@
     <t>20260711--03</t>
   </si>
   <si>
-    <t>05:47</t>
-  </si>
-  <si>
-    <t>04:52</t>
+    <t>20260712--01</t>
+  </si>
+  <si>
+    <t>04:51</t>
   </si>
   <si>
     <t>06:28</t>
   </si>
   <si>
-    <t>03:31</t>
+    <t>03:28</t>
   </si>
   <si>
     <t>06:43</t>
   </si>
   <si>
-    <t>00:16</t>
-  </si>
-  <si>
-    <t>06:37</t>
-  </si>
-  <si>
-    <t>02:14</t>
-  </si>
-  <si>
-    <t>06:13</t>
-  </si>
-  <si>
-    <t>04:54</t>
-  </si>
-  <si>
-    <t>05:32</t>
-  </si>
-  <si>
-    <t>06:03</t>
-  </si>
-  <si>
-    <t>04:30</t>
+    <t>00:04</t>
+  </si>
+  <si>
+    <t>06:36</t>
+  </si>
+  <si>
+    <t>02:19</t>
+  </si>
+  <si>
+    <t>06:12</t>
+  </si>
+  <si>
+    <t>04:56</t>
+  </si>
+  <si>
+    <t>05:29</t>
+  </si>
+  <si>
+    <t>06:04</t>
+  </si>
+  <si>
+    <t>04:24</t>
   </si>
   <si>
     <t>06:35</t>
   </si>
   <si>
-    <t>02:53</t>
+    <t>02:43</t>
+  </si>
+  <si>
+    <t>06:42</t>
   </si>
   <si>
     <t>00:00</t>
@@ -175,256 +172,244 @@
     <t>01:53</t>
   </si>
   <si>
-    <t>01:51:14</t>
-  </si>
-  <si>
-    <t>03:28:40</t>
-  </si>
-  <si>
-    <t>01:04:44</t>
-  </si>
-  <si>
-    <t>02:41:55</t>
-  </si>
-  <si>
-    <t>00:18:10</t>
-  </si>
-  <si>
-    <t>01:55:11</t>
-  </si>
-  <si>
-    <t>23:31:33</t>
-  </si>
-  <si>
-    <t>01:08:28</t>
-  </si>
-  <si>
-    <t>02:46:34</t>
-  </si>
-  <si>
-    <t>00:21:44</t>
-  </si>
-  <si>
-    <t>01:59:23</t>
-  </si>
-  <si>
-    <t>23:34:58</t>
-  </si>
-  <si>
-    <t>01:12:18</t>
-  </si>
-  <si>
-    <t>22:48:09</t>
-  </si>
-  <si>
-    <t>00:25:16</t>
-  </si>
-  <si>
-    <t>22:01:18</t>
-  </si>
-  <si>
-    <t>23:38:15</t>
-  </si>
-  <si>
-    <t>01:53:34</t>
-  </si>
-  <si>
-    <t>03:30:58</t>
-  </si>
-  <si>
-    <t>01:07:17</t>
-  </si>
-  <si>
-    <t>02:44:04</t>
-  </si>
-  <si>
-    <t>00:21:08</t>
-  </si>
-  <si>
-    <t>01:57:18</t>
-  </si>
-  <si>
-    <t>23:35:57</t>
-  </si>
-  <si>
-    <t>01:10:36</t>
-  </si>
-  <si>
-    <t>02:49:54</t>
-  </si>
-  <si>
-    <t>00:23:57</t>
-  </si>
-  <si>
-    <t>02:01:53</t>
-  </si>
-  <si>
-    <t>23:37:21</t>
-  </si>
-  <si>
-    <t>01:14:32</t>
-  </si>
-  <si>
-    <t>22:50:49</t>
-  </si>
-  <si>
-    <t>00:27:24</t>
-  </si>
-  <si>
-    <t>22:04:28</t>
-  </si>
-  <si>
-    <t>23:40:22</t>
-  </si>
-  <si>
-    <t>01:56:27</t>
-  </si>
-  <si>
-    <t>03:33:52</t>
-  </si>
-  <si>
-    <t>01:09:43</t>
-  </si>
-  <si>
-    <t>02:47:18</t>
-  </si>
-  <si>
-    <t>00:22:53</t>
-  </si>
-  <si>
-    <t>02:00:40</t>
-  </si>
-  <si>
-    <t>01:13:55</t>
-  </si>
-  <si>
-    <t>02:51:01</t>
-  </si>
-  <si>
-    <t>00:27:04</t>
-  </si>
-  <si>
-    <t>02:04:20</t>
-  </si>
-  <si>
-    <t>23:40:07</t>
-  </si>
-  <si>
-    <t>01:17:34</t>
-  </si>
-  <si>
-    <t>22:53:04</t>
-  </si>
-  <si>
-    <t>00:30:41</t>
-  </si>
-  <si>
-    <t>22:05:55</t>
-  </si>
-  <si>
-    <t>23:43:44</t>
-  </si>
-  <si>
-    <t>01:59:21</t>
-  </si>
-  <si>
-    <t>03:36:45</t>
-  </si>
-  <si>
-    <t>01:12:09</t>
-  </si>
-  <si>
-    <t>02:50:32</t>
-  </si>
-  <si>
-    <t>00:24:39</t>
-  </si>
-  <si>
-    <t>02:04:01</t>
-  </si>
-  <si>
-    <t>23:36:13</t>
-  </si>
-  <si>
-    <t>01:17:13</t>
-  </si>
-  <si>
-    <t>02:52:08</t>
-  </si>
-  <si>
-    <t>00:30:10</t>
-  </si>
-  <si>
-    <t>02:06:47</t>
-  </si>
-  <si>
-    <t>23:42:53</t>
-  </si>
-  <si>
-    <t>01:20:35</t>
-  </si>
-  <si>
-    <t>22:55:19</t>
-  </si>
-  <si>
-    <t>00:33:59</t>
-  </si>
-  <si>
-    <t>22:07:21</t>
-  </si>
-  <si>
-    <t>23:47:05</t>
-  </si>
-  <si>
-    <t>02:01:40</t>
-  </si>
-  <si>
-    <t>03:39:03</t>
-  </si>
-  <si>
-    <t>01:14:43</t>
-  </si>
-  <si>
-    <t>02:52:41</t>
-  </si>
-  <si>
-    <t>00:27:36</t>
-  </si>
-  <si>
-    <t>02:06:07</t>
-  </si>
-  <si>
-    <t>23:40:21</t>
-  </si>
-  <si>
-    <t>01:19:21</t>
-  </si>
-  <si>
-    <t>02:55:29</t>
-  </si>
-  <si>
-    <t>00:32:23</t>
-  </si>
-  <si>
-    <t>02:09:17</t>
-  </si>
-  <si>
-    <t>23:45:16</t>
-  </si>
-  <si>
-    <t>01:22:48</t>
-  </si>
-  <si>
-    <t>22:57:58</t>
-  </si>
-  <si>
-    <t>00:36:06</t>
-  </si>
-  <si>
-    <t>22:10:31</t>
-  </si>
-  <si>
-    <t>23:49:11</t>
+    <t>00:48</t>
+  </si>
+  <si>
+    <t>01:04:37</t>
+  </si>
+  <si>
+    <t>02:41:48</t>
+  </si>
+  <si>
+    <t>00:17:56</t>
+  </si>
+  <si>
+    <t>01:54:57</t>
+  </si>
+  <si>
+    <t>23:31:09</t>
+  </si>
+  <si>
+    <t>01:08:04</t>
+  </si>
+  <si>
+    <t>02:46:08</t>
+  </si>
+  <si>
+    <t>00:21:07</t>
+  </si>
+  <si>
+    <t>01:58:45</t>
+  </si>
+  <si>
+    <t>23:34:07</t>
+  </si>
+  <si>
+    <t>01:11:25</t>
+  </si>
+  <si>
+    <t>22:47:01</t>
+  </si>
+  <si>
+    <t>00:24:06</t>
+  </si>
+  <si>
+    <t>21:59:50</t>
+  </si>
+  <si>
+    <t>23:36:46</t>
+  </si>
+  <si>
+    <t>22:49:24</t>
+  </si>
+  <si>
+    <t>01:07:11</t>
+  </si>
+  <si>
+    <t>02:43:57</t>
+  </si>
+  <si>
+    <t>00:20:55</t>
+  </si>
+  <si>
+    <t>01:57:03</t>
+  </si>
+  <si>
+    <t>23:35:33</t>
+  </si>
+  <si>
+    <t>01:10:12</t>
+  </si>
+  <si>
+    <t>02:49:27</t>
+  </si>
+  <si>
+    <t>00:23:21</t>
+  </si>
+  <si>
+    <t>02:01:14</t>
+  </si>
+  <si>
+    <t>23:36:31</t>
+  </si>
+  <si>
+    <t>01:13:39</t>
+  </si>
+  <si>
+    <t>22:49:43</t>
+  </si>
+  <si>
+    <t>00:26:14</t>
+  </si>
+  <si>
+    <t>22:03:04</t>
+  </si>
+  <si>
+    <t>23:38:53</t>
+  </si>
+  <si>
+    <t>22:51:34</t>
+  </si>
+  <si>
+    <t>01:09:37</t>
+  </si>
+  <si>
+    <t>02:47:11</t>
+  </si>
+  <si>
+    <t>00:22:39</t>
+  </si>
+  <si>
+    <t>02:00:25</t>
+  </si>
+  <si>
+    <t>01:13:30</t>
+  </si>
+  <si>
+    <t>02:50:36</t>
+  </si>
+  <si>
+    <t>00:26:27</t>
+  </si>
+  <si>
+    <t>02:03:42</t>
+  </si>
+  <si>
+    <t>23:39:15</t>
+  </si>
+  <si>
+    <t>01:16:41</t>
+  </si>
+  <si>
+    <t>22:51:55</t>
+  </si>
+  <si>
+    <t>00:29:32</t>
+  </si>
+  <si>
+    <t>22:04:26</t>
+  </si>
+  <si>
+    <t>23:42:14</t>
+  </si>
+  <si>
+    <t>22:54:48</t>
+  </si>
+  <si>
+    <t>01:12:02</t>
+  </si>
+  <si>
+    <t>02:50:25</t>
+  </si>
+  <si>
+    <t>00:24:23</t>
+  </si>
+  <si>
+    <t>02:03:46</t>
+  </si>
+  <si>
+    <t>23:35:37</t>
+  </si>
+  <si>
+    <t>01:16:48</t>
+  </si>
+  <si>
+    <t>02:51:46</t>
+  </si>
+  <si>
+    <t>00:29:33</t>
+  </si>
+  <si>
+    <t>02:06:10</t>
+  </si>
+  <si>
+    <t>23:42:00</t>
+  </si>
+  <si>
+    <t>01:19:43</t>
+  </si>
+  <si>
+    <t>22:54:07</t>
+  </si>
+  <si>
+    <t>00:32:49</t>
+  </si>
+  <si>
+    <t>22:05:47</t>
+  </si>
+  <si>
+    <t>23:45:35</t>
+  </si>
+  <si>
+    <t>22:58:02</t>
+  </si>
+  <si>
+    <t>01:14:35</t>
+  </si>
+  <si>
+    <t>02:52:34</t>
+  </si>
+  <si>
+    <t>00:27:21</t>
+  </si>
+  <si>
+    <t>02:05:52</t>
+  </si>
+  <si>
+    <t>23:39:56</t>
+  </si>
+  <si>
+    <t>01:18:56</t>
+  </si>
+  <si>
+    <t>02:55:04</t>
+  </si>
+  <si>
+    <t>00:31:46</t>
+  </si>
+  <si>
+    <t>02:08:40</t>
+  </si>
+  <si>
+    <t>23:44:23</t>
+  </si>
+  <si>
+    <t>01:21:56</t>
+  </si>
+  <si>
+    <t>22:56:48</t>
+  </si>
+  <si>
+    <t>00:34:56</t>
+  </si>
+  <si>
+    <t>22:09:00</t>
+  </si>
+  <si>
+    <t>23:47:41</t>
+  </si>
+  <si>
+    <t>23:00:11</t>
   </si>
   <si>
     <t>0°</t>
@@ -442,28 +427,34 @@
     <t>12°</t>
   </si>
   <si>
-    <t>4°</t>
-  </si>
-  <si>
-    <t>00:18:52</t>
-  </si>
-  <si>
-    <t>23:33:51</t>
-  </si>
-  <si>
-    <t>00:21:47</t>
-  </si>
-  <si>
-    <t>23:36:40</t>
-  </si>
-  <si>
-    <t>22:51:32</t>
-  </si>
-  <si>
-    <t>22:06:21</t>
-  </si>
-  <si>
-    <t>23:39:21</t>
+    <t>5°</t>
+  </si>
+  <si>
+    <t>16°</t>
+  </si>
+  <si>
+    <t>00:18:38</t>
+  </si>
+  <si>
+    <t>23:33:28</t>
+  </si>
+  <si>
+    <t>00:21:12</t>
+  </si>
+  <si>
+    <t>23:35:51</t>
+  </si>
+  <si>
+    <t>22:50:26</t>
+  </si>
+  <si>
+    <t>22:04:57</t>
+  </si>
+  <si>
+    <t>23:37:55</t>
+  </si>
+  <si>
+    <t>22:52:22</t>
   </si>
   <si>
     <t>B</t>
@@ -512,7 +503,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -533,7 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -551,25 +542,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -610,7 +589,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -643,12 +622,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1052,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1130,49 +1103,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>53</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>53</v>
       </c>
       <c r="L2" s="4">
-        <v>-37.7</v>
+        <v>-39</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O2" s="6">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="P2" s="7">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1186,49 +1159,49 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>54</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>54</v>
       </c>
       <c r="L3" s="4">
-        <v>-28.3</v>
+        <v>-34</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O3" s="6">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="P3" s="7">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1242,52 +1215,52 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="L4" s="4">
-        <v>-39</v>
+        <v>-37.8</v>
       </c>
       <c r="M4" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="N4" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="O4" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P4" s="8">
         <v>0</v>
       </c>
       <c r="Q4" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R4" s="8">
         <v>0</v>
@@ -1298,52 +1271,52 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>56</v>
       </c>
       <c r="L5" s="4">
-        <v>-33.9</v>
+        <v>-37.7</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O5" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P5" s="8">
         <v>0</v>
       </c>
       <c r="Q5" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R5" s="8">
         <v>0</v>
@@ -1354,43 +1327,43 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>57</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="L6" s="4">
-        <v>-37.8</v>
+        <v>-34.2</v>
       </c>
       <c r="M6" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="O6" s="6">
         <v>0</v>
@@ -1410,43 +1383,43 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>39</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>58</v>
       </c>
       <c r="L7" s="4">
-        <v>-37.7</v>
+        <v>-39.2</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O7" s="6">
         <v>0</v>
@@ -1466,52 +1439,52 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>59</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>144</v>
+        <v>59</v>
       </c>
       <c r="L8" s="4">
-        <v>-34.2</v>
+        <v>-33.8</v>
       </c>
       <c r="M8" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="N8" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="O8" s="9">
-        <v>22</v>
+      <c r="O8" s="6">
+        <v>0</v>
       </c>
       <c r="P8" s="8">
         <v>0</v>
       </c>
-      <c r="Q8" s="10">
-        <v>17</v>
+      <c r="Q8" s="8">
+        <v>0</v>
       </c>
       <c r="R8" s="8">
         <v>0</v>
@@ -1522,52 +1495,52 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>60</v>
+        <v>141</v>
       </c>
       <c r="L9" s="4">
-        <v>-39.2</v>
+        <v>-38.1</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O9" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P9" s="8">
         <v>0</v>
       </c>
       <c r="Q9" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R9" s="8">
         <v>0</v>
@@ -1578,52 +1551,52 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>61</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>61</v>
       </c>
       <c r="L10" s="4">
-        <v>-33.8</v>
+        <v>-37.8</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="O10" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
       </c>
       <c r="Q10" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R10" s="8">
         <v>0</v>
@@ -1634,43 +1607,43 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>62</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="L11" s="4">
-        <v>-38.2</v>
+        <v>-34.7</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O11" s="6">
         <v>0</v>
@@ -1690,52 +1663,52 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>63</v>
       </c>
       <c r="L12" s="4">
-        <v>-37.7</v>
+        <v>-39.4</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O12" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
       </c>
       <c r="Q12" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" s="8">
         <v>0</v>
@@ -1746,7 +1719,7 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>45</v>
@@ -1758,34 +1731,34 @@
         <v>64</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="L13" s="4">
-        <v>-34.8</v>
+        <v>-29.3</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O13" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
@@ -1802,46 +1775,46 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>65</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I14" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>65</v>
       </c>
       <c r="L14" s="4">
-        <v>-39.4</v>
+        <v>-38.6</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O14" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P14" s="8">
         <v>0</v>
@@ -1858,7 +1831,7 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>47</v>
@@ -1870,37 +1843,37 @@
         <v>66</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="L15" s="4">
-        <v>-29.5</v>
+        <v>-22.4</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="O15" s="6">
-        <v>0</v>
-      </c>
-      <c r="P15" s="8">
-        <v>0</v>
+        <v>150</v>
+      </c>
+      <c r="O15" s="9">
+        <v>34</v>
+      </c>
+      <c r="P15" s="10">
+        <v>34</v>
       </c>
       <c r="Q15" s="8">
         <v>0</v>
@@ -1914,49 +1887,49 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>67</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>137</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>67</v>
+        <v>145</v>
       </c>
       <c r="L16" s="4">
-        <v>-38.6</v>
+        <v>-35.2</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="O16" s="6">
-        <v>0</v>
-      </c>
-      <c r="P16" s="8">
-        <v>0</v>
+        <v>149</v>
+      </c>
+      <c r="O16" s="9">
+        <v>25</v>
+      </c>
+      <c r="P16" s="11">
+        <v>25</v>
       </c>
       <c r="Q16" s="8">
         <v>0</v>
@@ -1970,10 +1943,10 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>52</v>
@@ -1982,158 +1955,102 @@
         <v>68</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="K17" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-29.9</v>
+      </c>
+      <c r="M17" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L17" s="4">
-        <v>-22.7</v>
-      </c>
-      <c r="M17" s="3" t="s">
+      <c r="N17" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="N17" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="O17" s="11">
-        <v>60</v>
-      </c>
-      <c r="P17" s="12">
-        <v>34</v>
+      <c r="O17" s="6">
+        <v>1</v>
+      </c>
+      <c r="P17" s="8">
+        <v>1</v>
       </c>
       <c r="Q17" s="8">
         <v>0</v>
       </c>
       <c r="R17" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="2">
-        <v>82</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="L18" s="4">
-        <v>-35.3</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="O18" s="11">
-        <v>65</v>
-      </c>
-      <c r="P18" s="13">
-        <v>50</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>0</v>
-      </c>
-      <c r="R18" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A18">
+  <conditionalFormatting sqref="A2:A17">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B18">
+  <conditionalFormatting sqref="B2:B17">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C18">
+  <conditionalFormatting sqref="C2:C17">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D18">
+  <conditionalFormatting sqref="D2:D17">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E18">
+  <conditionalFormatting sqref="E2:E17">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F18">
+  <conditionalFormatting sqref="F2:F17">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G18">
+  <conditionalFormatting sqref="G2:G17">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H18">
+  <conditionalFormatting sqref="H2:H17">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I18">
+  <conditionalFormatting sqref="I2:I17">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J18">
+  <conditionalFormatting sqref="J2:J17">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K18">
+  <conditionalFormatting sqref="K2:K17">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L18">
+  <conditionalFormatting sqref="L2:L17">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2152,12 +2069,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M18">
+  <conditionalFormatting sqref="M2:M17">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N18">
+  <conditionalFormatting sqref="N2:N17">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2174,22 +2091,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O18">
+  <conditionalFormatting sqref="O2:O17">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P18">
+  <conditionalFormatting sqref="P2:P17">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q18">
+  <conditionalFormatting sqref="Q2:Q17">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R18">
+  <conditionalFormatting sqref="R2:R17">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="165">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260706--01</t>
-  </si>
-  <si>
-    <t>20260706--02</t>
-  </si>
-  <si>
     <t>20260707--01</t>
   </si>
   <si>
@@ -118,306 +112,339 @@
     <t>20260712--01</t>
   </si>
   <si>
-    <t>04:51</t>
-  </si>
-  <si>
-    <t>06:28</t>
-  </si>
-  <si>
-    <t>03:28</t>
+    <t>20260713--01</t>
+  </si>
+  <si>
+    <t>20260713--02</t>
+  </si>
+  <si>
+    <t>20260713--03</t>
+  </si>
+  <si>
+    <t>03:29</t>
   </si>
   <si>
     <t>06:43</t>
   </si>
   <si>
-    <t>00:04</t>
+    <t>00:05</t>
   </si>
   <si>
     <t>06:36</t>
   </si>
   <si>
-    <t>02:19</t>
+    <t>02:17</t>
   </si>
   <si>
     <t>06:12</t>
   </si>
   <si>
-    <t>04:56</t>
+    <t>04:55</t>
   </si>
   <si>
     <t>05:29</t>
   </si>
   <si>
-    <t>06:04</t>
-  </si>
-  <si>
-    <t>04:24</t>
+    <t>06:03</t>
+  </si>
+  <si>
+    <t>04:26</t>
   </si>
   <si>
     <t>06:35</t>
   </si>
   <si>
-    <t>02:43</t>
+    <t>02:47</t>
   </si>
   <si>
     <t>06:42</t>
   </si>
   <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>03:36</t>
+  </si>
+  <si>
+    <t>05:58</t>
+  </si>
+  <si>
+    <t>05:27</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
     <t>00:43</t>
   </si>
   <si>
-    <t>01:53</t>
-  </si>
-  <si>
-    <t>00:48</t>
-  </si>
-  <si>
-    <t>01:04:37</t>
-  </si>
-  <si>
-    <t>02:41:48</t>
-  </si>
-  <si>
-    <t>00:17:56</t>
-  </si>
-  <si>
-    <t>01:54:57</t>
-  </si>
-  <si>
-    <t>23:31:09</t>
-  </si>
-  <si>
-    <t>01:08:04</t>
-  </si>
-  <si>
-    <t>02:46:08</t>
-  </si>
-  <si>
-    <t>00:21:07</t>
-  </si>
-  <si>
-    <t>01:58:45</t>
-  </si>
-  <si>
-    <t>23:34:07</t>
-  </si>
-  <si>
-    <t>01:11:25</t>
-  </si>
-  <si>
-    <t>22:47:01</t>
-  </si>
-  <si>
-    <t>00:24:06</t>
-  </si>
-  <si>
-    <t>21:59:50</t>
-  </si>
-  <si>
-    <t>23:36:46</t>
-  </si>
-  <si>
-    <t>22:49:24</t>
-  </si>
-  <si>
-    <t>01:07:11</t>
-  </si>
-  <si>
-    <t>02:43:57</t>
-  </si>
-  <si>
-    <t>00:20:55</t>
-  </si>
-  <si>
-    <t>01:57:03</t>
-  </si>
-  <si>
-    <t>23:35:33</t>
-  </si>
-  <si>
-    <t>01:10:12</t>
-  </si>
-  <si>
-    <t>02:49:27</t>
-  </si>
-  <si>
-    <t>00:23:21</t>
-  </si>
-  <si>
-    <t>02:01:14</t>
-  </si>
-  <si>
-    <t>23:36:31</t>
+    <t>01:52</t>
+  </si>
+  <si>
+    <t>00:46</t>
+  </si>
+  <si>
+    <t>02:28</t>
+  </si>
+  <si>
+    <t>00:18:00</t>
+  </si>
+  <si>
+    <t>01:55:01</t>
+  </si>
+  <si>
+    <t>23:31:18</t>
+  </si>
+  <si>
+    <t>01:08:13</t>
+  </si>
+  <si>
+    <t>02:46:18</t>
+  </si>
+  <si>
+    <t>00:21:23</t>
+  </si>
+  <si>
+    <t>01:59:01</t>
+  </si>
+  <si>
+    <t>23:34:31</t>
+  </si>
+  <si>
+    <t>01:11:50</t>
+  </si>
+  <si>
+    <t>22:47:36</t>
+  </si>
+  <si>
+    <t>00:24:41</t>
+  </si>
+  <si>
+    <t>22:00:36</t>
+  </si>
+  <si>
+    <t>23:37:33</t>
+  </si>
+  <si>
+    <t>22:50:25</t>
+  </si>
+  <si>
+    <t>00:28:18</t>
+  </si>
+  <si>
+    <t>22:03:14</t>
+  </si>
+  <si>
+    <t>23:40:43</t>
+  </si>
+  <si>
+    <t>00:20:58</t>
+  </si>
+  <si>
+    <t>01:57:07</t>
+  </si>
+  <si>
+    <t>23:35:42</t>
+  </si>
+  <si>
+    <t>01:10:21</t>
+  </si>
+  <si>
+    <t>02:49:37</t>
+  </si>
+  <si>
+    <t>00:23:36</t>
+  </si>
+  <si>
+    <t>02:01:31</t>
+  </si>
+  <si>
+    <t>23:36:55</t>
+  </si>
+  <si>
+    <t>01:14:04</t>
+  </si>
+  <si>
+    <t>22:50:16</t>
+  </si>
+  <si>
+    <t>00:26:49</t>
+  </si>
+  <si>
+    <t>22:03:49</t>
+  </si>
+  <si>
+    <t>23:39:40</t>
+  </si>
+  <si>
+    <t>22:52:34</t>
+  </si>
+  <si>
+    <t>00:31:10</t>
+  </si>
+  <si>
+    <t>22:05:31</t>
+  </si>
+  <si>
+    <t>23:43:05</t>
+  </si>
+  <si>
+    <t>00:22:43</t>
+  </si>
+  <si>
+    <t>02:00:29</t>
   </si>
   <si>
     <t>01:13:39</t>
   </si>
   <si>
-    <t>22:49:43</t>
-  </si>
-  <si>
-    <t>00:26:14</t>
-  </si>
-  <si>
-    <t>22:03:04</t>
-  </si>
-  <si>
-    <t>23:38:53</t>
-  </si>
-  <si>
-    <t>22:51:34</t>
-  </si>
-  <si>
-    <t>01:09:37</t>
-  </si>
-  <si>
-    <t>02:47:11</t>
-  </si>
-  <si>
-    <t>00:22:39</t>
-  </si>
-  <si>
-    <t>02:00:25</t>
-  </si>
-  <si>
-    <t>01:13:30</t>
-  </si>
-  <si>
-    <t>02:50:36</t>
-  </si>
-  <si>
-    <t>00:26:27</t>
-  </si>
-  <si>
-    <t>02:03:42</t>
-  </si>
-  <si>
-    <t>23:39:15</t>
-  </si>
-  <si>
-    <t>01:16:41</t>
-  </si>
-  <si>
-    <t>22:51:55</t>
-  </si>
-  <si>
-    <t>00:29:32</t>
-  </si>
-  <si>
-    <t>22:04:26</t>
-  </si>
-  <si>
-    <t>23:42:14</t>
-  </si>
-  <si>
-    <t>22:54:48</t>
-  </si>
-  <si>
-    <t>01:12:02</t>
-  </si>
-  <si>
-    <t>02:50:25</t>
-  </si>
-  <si>
-    <t>00:24:23</t>
-  </si>
-  <si>
-    <t>02:03:46</t>
-  </si>
-  <si>
-    <t>23:35:37</t>
-  </si>
-  <si>
-    <t>01:16:48</t>
-  </si>
-  <si>
-    <t>02:51:46</t>
-  </si>
-  <si>
-    <t>00:29:33</t>
-  </si>
-  <si>
-    <t>02:06:10</t>
-  </si>
-  <si>
-    <t>23:42:00</t>
-  </si>
-  <si>
-    <t>01:19:43</t>
-  </si>
-  <si>
-    <t>22:54:07</t>
-  </si>
-  <si>
-    <t>00:32:49</t>
-  </si>
-  <si>
-    <t>22:05:47</t>
-  </si>
-  <si>
-    <t>23:45:35</t>
-  </si>
-  <si>
-    <t>22:58:02</t>
-  </si>
-  <si>
-    <t>01:14:35</t>
-  </si>
-  <si>
-    <t>02:52:34</t>
-  </si>
-  <si>
-    <t>00:27:21</t>
-  </si>
-  <si>
-    <t>02:05:52</t>
-  </si>
-  <si>
-    <t>23:39:56</t>
-  </si>
-  <si>
-    <t>01:18:56</t>
-  </si>
-  <si>
-    <t>02:55:04</t>
-  </si>
-  <si>
-    <t>00:31:46</t>
-  </si>
-  <si>
-    <t>02:08:40</t>
-  </si>
-  <si>
-    <t>23:44:23</t>
-  </si>
-  <si>
-    <t>01:21:56</t>
-  </si>
-  <si>
-    <t>22:56:48</t>
-  </si>
-  <si>
-    <t>00:34:56</t>
-  </si>
-  <si>
-    <t>22:09:00</t>
-  </si>
-  <si>
-    <t>23:47:41</t>
-  </si>
-  <si>
-    <t>23:00:11</t>
+    <t>02:50:45</t>
+  </si>
+  <si>
+    <t>00:26:43</t>
+  </si>
+  <si>
+    <t>02:03:58</t>
+  </si>
+  <si>
+    <t>23:39:39</t>
+  </si>
+  <si>
+    <t>01:17:06</t>
+  </si>
+  <si>
+    <t>22:52:29</t>
+  </si>
+  <si>
+    <t>00:30:07</t>
+  </si>
+  <si>
+    <t>22:05:12</t>
+  </si>
+  <si>
+    <t>23:43:01</t>
+  </si>
+  <si>
+    <t>22:55:49</t>
+  </si>
+  <si>
+    <t>00:32:57</t>
+  </si>
+  <si>
+    <t>22:08:30</t>
+  </si>
+  <si>
+    <t>23:45:49</t>
+  </si>
+  <si>
+    <t>00:24:27</t>
+  </si>
+  <si>
+    <t>02:03:50</t>
+  </si>
+  <si>
+    <t>23:35:47</t>
+  </si>
+  <si>
+    <t>01:16:57</t>
+  </si>
+  <si>
+    <t>02:51:54</t>
+  </si>
+  <si>
+    <t>00:29:48</t>
+  </si>
+  <si>
+    <t>02:06:26</t>
+  </si>
+  <si>
+    <t>23:42:24</t>
+  </si>
+  <si>
+    <t>01:20:07</t>
+  </si>
+  <si>
+    <t>22:54:42</t>
+  </si>
+  <si>
+    <t>00:33:24</t>
+  </si>
+  <si>
+    <t>22:06:36</t>
+  </si>
+  <si>
+    <t>23:46:22</t>
+  </si>
+  <si>
+    <t>22:59:04</t>
+  </si>
+  <si>
+    <t>00:34:46</t>
+  </si>
+  <si>
+    <t>22:11:29</t>
+  </si>
+  <si>
+    <t>23:48:32</t>
+  </si>
+  <si>
+    <t>00:27:25</t>
+  </si>
+  <si>
+    <t>02:05:56</t>
+  </si>
+  <si>
+    <t>23:40:04</t>
+  </si>
+  <si>
+    <t>01:19:04</t>
+  </si>
+  <si>
+    <t>02:55:13</t>
+  </si>
+  <si>
+    <t>00:32:01</t>
+  </si>
+  <si>
+    <t>02:08:55</t>
+  </si>
+  <si>
+    <t>23:44:47</t>
+  </si>
+  <si>
+    <t>01:22:20</t>
+  </si>
+  <si>
+    <t>22:57:22</t>
+  </si>
+  <si>
+    <t>00:35:31</t>
+  </si>
+  <si>
+    <t>22:09:48</t>
+  </si>
+  <si>
+    <t>23:48:28</t>
+  </si>
+  <si>
+    <t>23:01:12</t>
+  </si>
+  <si>
+    <t>00:37:37</t>
+  </si>
+  <si>
+    <t>22:13:45</t>
+  </si>
+  <si>
+    <t>23:50:54</t>
+  </si>
+  <si>
+    <t>2°</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>2°</t>
-  </si>
-  <si>
     <t>7°</t>
   </si>
   <si>
@@ -433,28 +460,40 @@
     <t>16°</t>
   </si>
   <si>
-    <t>00:18:38</t>
-  </si>
-  <si>
-    <t>23:33:28</t>
-  </si>
-  <si>
-    <t>00:21:12</t>
-  </si>
-  <si>
-    <t>23:35:51</t>
-  </si>
-  <si>
-    <t>22:50:26</t>
-  </si>
-  <si>
-    <t>22:04:57</t>
-  </si>
-  <si>
-    <t>23:37:55</t>
-  </si>
-  <si>
-    <t>22:52:22</t>
+    <t>28°</t>
+  </si>
+  <si>
+    <t>1°</t>
+  </si>
+  <si>
+    <t>00:18:42</t>
+  </si>
+  <si>
+    <t>23:33:36</t>
+  </si>
+  <si>
+    <t>00:21:26</t>
+  </si>
+  <si>
+    <t>23:36:14</t>
+  </si>
+  <si>
+    <t>22:50:59</t>
+  </si>
+  <si>
+    <t>22:05:41</t>
+  </si>
+  <si>
+    <t>23:38:40</t>
+  </si>
+  <si>
+    <t>22:53:20</t>
+  </si>
+  <si>
+    <t>22:07:59</t>
+  </si>
+  <si>
+    <t>23:40:58</t>
   </si>
   <si>
     <t>B</t>
@@ -463,10 +502,10 @@
     <t>A+B</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>2</t>
@@ -503,7 +542,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -536,19 +575,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -589,7 +652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -622,6 +685,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1025,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1103,49 +1178,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="L2" s="4">
-        <v>-39</v>
+        <v>-37.8</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="O2" s="6">
+        <v>12</v>
+      </c>
+      <c r="P2" s="7">
         <v>13</v>
-      </c>
-      <c r="P2" s="7">
-        <v>14</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1159,49 +1234,49 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L3" s="4">
-        <v>-34</v>
+        <v>-37.7</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="O3" s="6">
-        <v>13</v>
-      </c>
-      <c r="P3" s="7">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="P3" s="8">
+        <v>0</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1215,43 +1290,43 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="L4" s="4">
-        <v>-37.8</v>
+        <v>-34.2</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="O4" s="6">
         <v>2</v>
@@ -1271,46 +1346,46 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L5" s="4">
-        <v>-37.7</v>
+        <v>-39.2</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="O5" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P5" s="8">
         <v>0</v>
@@ -1327,52 +1402,52 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="L6" s="4">
-        <v>-34.2</v>
+        <v>-33.8</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="O6" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P6" s="8">
         <v>0</v>
       </c>
       <c r="Q6" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R6" s="8">
         <v>0</v>
@@ -1383,43 +1458,43 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>58</v>
+        <v>152</v>
       </c>
       <c r="L7" s="4">
-        <v>-39.2</v>
+        <v>-38.1</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="O7" s="6">
         <v>0</v>
@@ -1439,43 +1514,43 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="L8" s="4">
-        <v>-33.8</v>
+        <v>-37.8</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="O8" s="6">
         <v>0</v>
@@ -1495,43 +1570,43 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="L9" s="4">
-        <v>-38.1</v>
+        <v>-34.8</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="O9" s="6">
         <v>0</v>
@@ -1551,43 +1626,43 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="L10" s="4">
-        <v>-37.8</v>
+        <v>-39.4</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="O10" s="6">
         <v>0</v>
@@ -1607,43 +1682,43 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="L11" s="4">
-        <v>-34.7</v>
+        <v>-29.4</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="O11" s="6">
         <v>0</v>
@@ -1663,43 +1738,43 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="L12" s="4">
-        <v>-39.4</v>
+        <v>-38.6</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="O12" s="6">
         <v>0</v>
@@ -1719,49 +1794,49 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="L13" s="4">
-        <v>-29.3</v>
+        <v>-22.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O13" s="6">
-        <v>0</v>
-      </c>
-      <c r="P13" s="8">
-        <v>0</v>
+        <v>162</v>
+      </c>
+      <c r="O13" s="9">
+        <v>62</v>
+      </c>
+      <c r="P13" s="10">
+        <v>60</v>
       </c>
       <c r="Q13" s="8">
         <v>0</v>
@@ -1775,49 +1850,49 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>65</v>
+        <v>156</v>
       </c>
       <c r="L14" s="4">
-        <v>-38.6</v>
+        <v>-35.2</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="O14" s="6">
-        <v>0</v>
-      </c>
-      <c r="P14" s="8">
-        <v>0</v>
+        <v>163</v>
+      </c>
+      <c r="O14" s="9">
+        <v>59</v>
+      </c>
+      <c r="P14" s="11">
+        <v>57</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
@@ -1831,49 +1906,49 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="L15" s="4">
-        <v>-22.4</v>
+        <v>-30</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="O15" s="9">
-        <v>34</v>
-      </c>
-      <c r="P15" s="10">
-        <v>34</v>
+        <v>164</v>
+      </c>
+      <c r="O15" s="12">
+        <v>39</v>
+      </c>
+      <c r="P15" s="13">
+        <v>28</v>
       </c>
       <c r="Q15" s="8">
         <v>0</v>
@@ -1887,49 +1962,49 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="L16" s="4">
-        <v>-35.2</v>
+        <v>-39</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="O16" s="9">
-        <v>25</v>
-      </c>
-      <c r="P16" s="11">
-        <v>25</v>
+        <v>162</v>
+      </c>
+      <c r="O16" s="12">
+        <v>38</v>
+      </c>
+      <c r="P16" s="14">
+        <v>26</v>
       </c>
       <c r="Q16" s="8">
         <v>0</v>
@@ -1943,114 +2018,170 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-23.2</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="O17" s="12">
+        <v>14</v>
+      </c>
+      <c r="P17" s="15">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0</v>
+      </c>
+      <c r="R17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="2">
+        <v>23</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="L17" s="4">
-        <v>-29.9</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O17" s="6">
-        <v>1</v>
-      </c>
-      <c r="P17" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>0</v>
-      </c>
-      <c r="R17" s="8">
+      <c r="E18" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="L18" s="4">
+        <v>-35.8</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="O18" s="6">
+        <v>7</v>
+      </c>
+      <c r="P18" s="8">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>0</v>
+      </c>
+      <c r="R18" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A17">
+  <conditionalFormatting sqref="A2:A18">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B17">
+  <conditionalFormatting sqref="B2:B18">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C17">
+  <conditionalFormatting sqref="C2:C18">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D17">
+  <conditionalFormatting sqref="D2:D18">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E17">
+  <conditionalFormatting sqref="E2:E18">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F17">
+  <conditionalFormatting sqref="F2:F18">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G17">
+  <conditionalFormatting sqref="G2:G18">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H17">
+  <conditionalFormatting sqref="H2:H18">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I17">
+  <conditionalFormatting sqref="I2:I18">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J17">
+  <conditionalFormatting sqref="J2:J18">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K17">
+  <conditionalFormatting sqref="K2:K18">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L17">
+  <conditionalFormatting sqref="L2:L18">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2069,12 +2200,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M17">
+  <conditionalFormatting sqref="M2:M18">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N17">
+  <conditionalFormatting sqref="N2:N18">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2091,22 +2222,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O17">
+  <conditionalFormatting sqref="O2:O18">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P17">
+  <conditionalFormatting sqref="P2:P18">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q17">
+  <conditionalFormatting sqref="Q2:Q18">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R17">
+  <conditionalFormatting sqref="R2:R18">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="162">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260707--01</t>
-  </si>
-  <si>
-    <t>20260707--02</t>
-  </si>
-  <si>
-    <t>20260707--03</t>
-  </si>
-  <si>
     <t>20260708--01</t>
   </si>
   <si>
@@ -121,325 +112,319 @@
     <t>20260713--03</t>
   </si>
   <si>
-    <t>03:29</t>
-  </si>
-  <si>
-    <t>06:43</t>
-  </si>
-  <si>
-    <t>00:05</t>
+    <t>20260714--01</t>
+  </si>
+  <si>
+    <t>20260714--02</t>
   </si>
   <si>
     <t>06:36</t>
   </si>
   <si>
-    <t>02:17</t>
+    <t>02:15</t>
   </si>
   <si>
     <t>06:12</t>
   </si>
   <si>
-    <t>04:55</t>
+    <t>04:54</t>
   </si>
   <si>
     <t>05:29</t>
   </si>
   <si>
-    <t>06:03</t>
-  </si>
-  <si>
-    <t>04:26</t>
+    <t>06:02</t>
+  </si>
+  <si>
+    <t>04:27</t>
   </si>
   <si>
     <t>06:35</t>
   </si>
   <si>
-    <t>02:47</t>
+    <t>02:50</t>
   </si>
   <si>
     <t>06:42</t>
   </si>
   <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>03:36</t>
-  </si>
-  <si>
-    <t>05:58</t>
-  </si>
-  <si>
-    <t>05:27</t>
+    <t>06:29</t>
+  </si>
+  <si>
+    <t>03:31</t>
+  </si>
+  <si>
+    <t>05:59</t>
+  </si>
+  <si>
+    <t>05:24</t>
+  </si>
+  <si>
+    <t>05:09</t>
+  </si>
+  <si>
+    <t>06:18</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:43</t>
-  </si>
-  <si>
-    <t>01:52</t>
-  </si>
-  <si>
-    <t>00:46</t>
-  </si>
-  <si>
-    <t>02:28</t>
-  </si>
-  <si>
-    <t>00:18:00</t>
-  </si>
-  <si>
-    <t>01:55:01</t>
-  </si>
-  <si>
-    <t>23:31:18</t>
-  </si>
-  <si>
-    <t>01:08:13</t>
-  </si>
-  <si>
-    <t>02:46:18</t>
-  </si>
-  <si>
-    <t>00:21:23</t>
-  </si>
-  <si>
-    <t>01:59:01</t>
-  </si>
-  <si>
-    <t>23:34:31</t>
-  </si>
-  <si>
-    <t>01:11:50</t>
-  </si>
-  <si>
-    <t>22:47:36</t>
-  </si>
-  <si>
-    <t>00:24:41</t>
-  </si>
-  <si>
-    <t>22:00:36</t>
-  </si>
-  <si>
-    <t>23:37:33</t>
-  </si>
-  <si>
-    <t>22:50:25</t>
-  </si>
-  <si>
-    <t>00:28:18</t>
-  </si>
-  <si>
-    <t>22:03:14</t>
-  </si>
-  <si>
-    <t>23:40:43</t>
-  </si>
-  <si>
-    <t>00:20:58</t>
-  </si>
-  <si>
-    <t>01:57:07</t>
-  </si>
-  <si>
-    <t>23:35:42</t>
-  </si>
-  <si>
-    <t>01:10:21</t>
-  </si>
-  <si>
-    <t>02:49:37</t>
-  </si>
-  <si>
-    <t>00:23:36</t>
-  </si>
-  <si>
-    <t>02:01:31</t>
-  </si>
-  <si>
-    <t>23:36:55</t>
-  </si>
-  <si>
-    <t>01:14:04</t>
-  </si>
-  <si>
-    <t>22:50:16</t>
-  </si>
-  <si>
-    <t>00:26:49</t>
-  </si>
-  <si>
-    <t>22:03:49</t>
-  </si>
-  <si>
-    <t>23:39:40</t>
-  </si>
-  <si>
-    <t>22:52:34</t>
-  </si>
-  <si>
-    <t>00:31:10</t>
-  </si>
-  <si>
-    <t>22:05:31</t>
-  </si>
-  <si>
-    <t>23:43:05</t>
-  </si>
-  <si>
-    <t>00:22:43</t>
-  </si>
-  <si>
-    <t>02:00:29</t>
-  </si>
-  <si>
-    <t>01:13:39</t>
-  </si>
-  <si>
-    <t>02:50:45</t>
-  </si>
-  <si>
-    <t>00:26:43</t>
-  </si>
-  <si>
-    <t>02:03:58</t>
-  </si>
-  <si>
-    <t>23:39:39</t>
-  </si>
-  <si>
-    <t>01:17:06</t>
-  </si>
-  <si>
-    <t>22:52:29</t>
-  </si>
-  <si>
-    <t>00:30:07</t>
-  </si>
-  <si>
-    <t>22:05:12</t>
-  </si>
-  <si>
-    <t>23:43:01</t>
-  </si>
-  <si>
-    <t>22:55:49</t>
-  </si>
-  <si>
-    <t>00:32:57</t>
-  </si>
-  <si>
-    <t>22:08:30</t>
-  </si>
-  <si>
-    <t>23:45:49</t>
-  </si>
-  <si>
-    <t>00:24:27</t>
-  </si>
-  <si>
-    <t>02:03:50</t>
-  </si>
-  <si>
-    <t>23:35:47</t>
-  </si>
-  <si>
-    <t>01:16:57</t>
-  </si>
-  <si>
-    <t>02:51:54</t>
-  </si>
-  <si>
-    <t>00:29:48</t>
-  </si>
-  <si>
-    <t>02:06:26</t>
-  </si>
-  <si>
-    <t>23:42:24</t>
-  </si>
-  <si>
-    <t>01:20:07</t>
-  </si>
-  <si>
-    <t>22:54:42</t>
-  </si>
-  <si>
-    <t>00:33:24</t>
-  </si>
-  <si>
-    <t>22:06:36</t>
-  </si>
-  <si>
-    <t>23:46:22</t>
-  </si>
-  <si>
-    <t>22:59:04</t>
-  </si>
-  <si>
-    <t>00:34:46</t>
-  </si>
-  <si>
-    <t>22:11:29</t>
-  </si>
-  <si>
-    <t>23:48:32</t>
-  </si>
-  <si>
-    <t>00:27:25</t>
-  </si>
-  <si>
-    <t>02:05:56</t>
-  </si>
-  <si>
-    <t>23:40:04</t>
-  </si>
-  <si>
-    <t>01:19:04</t>
-  </si>
-  <si>
-    <t>02:55:13</t>
-  </si>
-  <si>
-    <t>00:32:01</t>
-  </si>
-  <si>
-    <t>02:08:55</t>
-  </si>
-  <si>
-    <t>23:44:47</t>
-  </si>
-  <si>
-    <t>01:22:20</t>
-  </si>
-  <si>
-    <t>22:57:22</t>
-  </si>
-  <si>
-    <t>00:35:31</t>
-  </si>
-  <si>
-    <t>22:09:48</t>
-  </si>
-  <si>
-    <t>23:48:28</t>
-  </si>
-  <si>
-    <t>23:01:12</t>
-  </si>
-  <si>
-    <t>00:37:37</t>
-  </si>
-  <si>
-    <t>22:13:45</t>
-  </si>
-  <si>
-    <t>23:50:54</t>
-  </si>
-  <si>
-    <t>2°</t>
+    <t>00:42</t>
+  </si>
+  <si>
+    <t>01:53</t>
+  </si>
+  <si>
+    <t>00:44</t>
+  </si>
+  <si>
+    <t>02:26</t>
+  </si>
+  <si>
+    <t>04:04</t>
+  </si>
+  <si>
+    <t>00:09</t>
+  </si>
+  <si>
+    <t>01:08:15</t>
+  </si>
+  <si>
+    <t>02:46:21</t>
+  </si>
+  <si>
+    <t>00:21:29</t>
+  </si>
+  <si>
+    <t>01:59:07</t>
+  </si>
+  <si>
+    <t>23:34:41</t>
+  </si>
+  <si>
+    <t>01:12:01</t>
+  </si>
+  <si>
+    <t>22:47:51</t>
+  </si>
+  <si>
+    <t>00:24:58</t>
+  </si>
+  <si>
+    <t>22:00:59</t>
+  </si>
+  <si>
+    <t>23:37:57</t>
+  </si>
+  <si>
+    <t>22:50:56</t>
+  </si>
+  <si>
+    <t>00:28:50</t>
+  </si>
+  <si>
+    <t>22:03:55</t>
+  </si>
+  <si>
+    <t>23:41:25</t>
+  </si>
+  <si>
+    <t>21:16:53</t>
+  </si>
+  <si>
+    <t>22:54:06</t>
+  </si>
+  <si>
+    <t>01:10:23</t>
+  </si>
+  <si>
+    <t>02:49:41</t>
+  </si>
+  <si>
+    <t>00:23:42</t>
+  </si>
+  <si>
+    <t>02:01:37</t>
+  </si>
+  <si>
+    <t>23:37:05</t>
+  </si>
+  <si>
+    <t>01:14:15</t>
+  </si>
+  <si>
+    <t>22:50:32</t>
+  </si>
+  <si>
+    <t>00:27:05</t>
+  </si>
+  <si>
+    <t>22:04:10</t>
+  </si>
+  <si>
+    <t>23:40:03</t>
+  </si>
+  <si>
+    <t>22:53:06</t>
+  </si>
+  <si>
+    <t>00:31:44</t>
+  </si>
+  <si>
+    <t>22:06:12</t>
+  </si>
+  <si>
+    <t>23:43:48</t>
+  </si>
+  <si>
+    <t>21:19:22</t>
+  </si>
+  <si>
+    <t>22:56:17</t>
+  </si>
+  <si>
+    <t>01:13:42</t>
+  </si>
+  <si>
+    <t>02:50:48</t>
+  </si>
+  <si>
+    <t>00:26:48</t>
+  </si>
+  <si>
+    <t>02:04:04</t>
+  </si>
+  <si>
+    <t>23:39:50</t>
+  </si>
+  <si>
+    <t>01:17:16</t>
+  </si>
+  <si>
+    <t>22:52:45</t>
+  </si>
+  <si>
+    <t>00:30:23</t>
+  </si>
+  <si>
+    <t>22:05:35</t>
+  </si>
+  <si>
+    <t>23:43:24</t>
+  </si>
+  <si>
+    <t>22:56:21</t>
+  </si>
+  <si>
+    <t>00:33:29</t>
+  </si>
+  <si>
+    <t>22:09:12</t>
+  </si>
+  <si>
+    <t>23:46:30</t>
+  </si>
+  <si>
+    <t>21:21:57</t>
+  </si>
+  <si>
+    <t>22:59:26</t>
+  </si>
+  <si>
+    <t>01:16:59</t>
+  </si>
+  <si>
+    <t>02:51:56</t>
+  </si>
+  <si>
+    <t>00:29:54</t>
+  </si>
+  <si>
+    <t>02:06:31</t>
+  </si>
+  <si>
+    <t>23:42:34</t>
+  </si>
+  <si>
+    <t>01:20:17</t>
+  </si>
+  <si>
+    <t>22:54:59</t>
+  </si>
+  <si>
+    <t>00:33:40</t>
+  </si>
+  <si>
+    <t>22:07:00</t>
+  </si>
+  <si>
+    <t>23:46:45</t>
+  </si>
+  <si>
+    <t>22:59:35</t>
+  </si>
+  <si>
+    <t>00:35:15</t>
+  </si>
+  <si>
+    <t>22:12:11</t>
+  </si>
+  <si>
+    <t>23:49:12</t>
+  </si>
+  <si>
+    <t>21:24:31</t>
+  </si>
+  <si>
+    <t>23:02:35</t>
+  </si>
+  <si>
+    <t>01:19:07</t>
+  </si>
+  <si>
+    <t>02:55:16</t>
+  </si>
+  <si>
+    <t>00:32:07</t>
+  </si>
+  <si>
+    <t>02:09:01</t>
+  </si>
+  <si>
+    <t>23:44:57</t>
+  </si>
+  <si>
+    <t>01:22:31</t>
+  </si>
+  <si>
+    <t>22:57:38</t>
+  </si>
+  <si>
+    <t>00:35:47</t>
+  </si>
+  <si>
+    <t>22:10:11</t>
+  </si>
+  <si>
+    <t>23:48:51</t>
+  </si>
+  <si>
+    <t>23:01:44</t>
+  </si>
+  <si>
+    <t>00:38:08</t>
+  </si>
+  <si>
+    <t>22:14:27</t>
+  </si>
+  <si>
+    <t>23:51:34</t>
+  </si>
+  <si>
+    <t>21:26:59</t>
+  </si>
+  <si>
+    <t>23:04:45</t>
   </si>
   <si>
     <t>0°</t>
@@ -454,46 +439,52 @@
     <t>12°</t>
   </si>
   <si>
-    <t>5°</t>
+    <t>4°</t>
+  </si>
+  <si>
+    <t>15°</t>
+  </si>
+  <si>
+    <t>28°</t>
+  </si>
+  <si>
+    <t>1°</t>
   </si>
   <si>
     <t>16°</t>
   </si>
   <si>
-    <t>28°</t>
-  </si>
-  <si>
-    <t>1°</t>
-  </si>
-  <si>
-    <t>00:18:42</t>
-  </si>
-  <si>
-    <t>23:33:36</t>
-  </si>
-  <si>
-    <t>00:21:26</t>
-  </si>
-  <si>
-    <t>23:36:14</t>
-  </si>
-  <si>
-    <t>22:50:59</t>
-  </si>
-  <si>
-    <t>22:05:41</t>
-  </si>
-  <si>
-    <t>23:38:40</t>
-  </si>
-  <si>
-    <t>22:53:20</t>
-  </si>
-  <si>
-    <t>22:07:59</t>
-  </si>
-  <si>
-    <t>23:40:58</t>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>00:21:32</t>
+  </si>
+  <si>
+    <t>23:36:24</t>
+  </si>
+  <si>
+    <t>22:51:14</t>
+  </si>
+  <si>
+    <t>22:06:03</t>
+  </si>
+  <si>
+    <t>23:39:02</t>
+  </si>
+  <si>
+    <t>22:53:50</t>
+  </si>
+  <si>
+    <t>22:08:38</t>
+  </si>
+  <si>
+    <t>23:41:38</t>
+  </si>
+  <si>
+    <t>21:23:26</t>
+  </si>
+  <si>
+    <t>22:56:26</t>
   </si>
   <si>
     <t>B</t>
@@ -502,10 +493,10 @@
     <t>A+B</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>2</t>
@@ -542,7 +533,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -557,7 +548,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -569,7 +578,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -581,7 +590,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -593,7 +602,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -605,13 +614,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -652,7 +655,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -697,6 +700,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1100,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1178,54 +1187,54 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>57</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>150</v>
+        <v>57</v>
       </c>
       <c r="L2" s="4">
-        <v>-37.8</v>
+        <v>-39.2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="O2" s="6">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="P2" s="7">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Q2" s="8">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
+        <v>6</v>
+      </c>
+      <c r="R2" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1234,54 +1243,54 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>58</v>
       </c>
       <c r="L3" s="4">
-        <v>-37.7</v>
+        <v>-33.8</v>
       </c>
       <c r="M3" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="O3" s="6">
-        <v>0</v>
-      </c>
-      <c r="P3" s="8">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="P3" s="10">
+        <v>15</v>
       </c>
       <c r="Q3" s="8">
-        <v>0</v>
-      </c>
-      <c r="R3" s="8">
+        <v>4</v>
+      </c>
+      <c r="R3" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1290,54 +1299,54 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>59</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="L4" s="4">
-        <v>-34.2</v>
+        <v>-38.1</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="O4" s="6">
-        <v>2</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>2</v>
-      </c>
-      <c r="R4" s="8">
+        <v>159</v>
+      </c>
+      <c r="O4" s="11">
+        <v>0</v>
+      </c>
+      <c r="P4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>0</v>
+      </c>
+      <c r="R4" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1346,54 +1355,54 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>60</v>
       </c>
       <c r="L5" s="4">
-        <v>-39.2</v>
+        <v>-37.8</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O5" s="6">
-        <v>3</v>
-      </c>
-      <c r="P5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>2</v>
-      </c>
-      <c r="R5" s="8">
+        <v>159</v>
+      </c>
+      <c r="O5" s="11">
+        <v>0</v>
+      </c>
+      <c r="P5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>0</v>
+      </c>
+      <c r="R5" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1402,54 +1411,54 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>61</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="L6" s="4">
-        <v>-33.8</v>
+        <v>-34.8</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="O6" s="6">
-        <v>2</v>
-      </c>
-      <c r="P6" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>2</v>
-      </c>
-      <c r="R6" s="8">
+        <v>159</v>
+      </c>
+      <c r="O6" s="11">
+        <v>0</v>
+      </c>
+      <c r="P6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>0</v>
+      </c>
+      <c r="R6" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1458,54 +1467,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>62</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>152</v>
+        <v>62</v>
       </c>
       <c r="L7" s="4">
-        <v>-38.1</v>
+        <v>-39.4</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O7" s="6">
-        <v>0</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>0</v>
-      </c>
-      <c r="R7" s="8">
+        <v>159</v>
+      </c>
+      <c r="O7" s="11">
+        <v>0</v>
+      </c>
+      <c r="P7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>0</v>
+      </c>
+      <c r="R7" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1514,54 +1523,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>63</v>
+        <v>149</v>
       </c>
       <c r="L8" s="4">
-        <v>-37.8</v>
+        <v>-29.4</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>0</v>
-      </c>
-      <c r="R8" s="8">
+        <v>161</v>
+      </c>
+      <c r="O8" s="11">
+        <v>0</v>
+      </c>
+      <c r="P8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>0</v>
+      </c>
+      <c r="R8" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1570,54 +1579,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>153</v>
+        <v>64</v>
       </c>
       <c r="L9" s="4">
-        <v>-34.8</v>
+        <v>-38.6</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O9" s="6">
-        <v>0</v>
-      </c>
-      <c r="P9" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8">
+        <v>159</v>
+      </c>
+      <c r="O9" s="11">
+        <v>0</v>
+      </c>
+      <c r="P9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>0</v>
+      </c>
+      <c r="R9" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1626,10 +1635,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>52</v>
@@ -1638,42 +1647,42 @@
         <v>65</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="L10" s="4">
-        <v>-39.4</v>
+        <v>-22.6</v>
       </c>
       <c r="M10" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="N10" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="N10" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O10" s="6">
-        <v>0</v>
-      </c>
-      <c r="P10" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>0</v>
-      </c>
-      <c r="R10" s="8">
+      <c r="O10" s="12">
+        <v>53</v>
+      </c>
+      <c r="P10" s="13">
+        <v>52</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0</v>
+      </c>
+      <c r="R10" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1682,54 +1691,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="L11" s="4">
-        <v>-29.4</v>
+        <v>-35.3</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O11" s="6">
-        <v>0</v>
-      </c>
-      <c r="P11" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>0</v>
-      </c>
-      <c r="R11" s="8">
+        <v>159</v>
+      </c>
+      <c r="O11" s="12">
+        <v>56</v>
+      </c>
+      <c r="P11" s="14">
+        <v>56</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>0</v>
+      </c>
+      <c r="R11" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1738,54 +1747,54 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>67</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>142</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>67</v>
+        <v>152</v>
       </c>
       <c r="L12" s="4">
-        <v>-38.6</v>
+        <v>-30.1</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O12" s="6">
-        <v>0</v>
-      </c>
-      <c r="P12" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>0</v>
-      </c>
-      <c r="R12" s="8">
+        <v>161</v>
+      </c>
+      <c r="O12" s="12">
+        <v>46</v>
+      </c>
+      <c r="P12" s="15">
+        <v>46</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>0</v>
+      </c>
+      <c r="R12" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1794,54 +1803,54 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>155</v>
+        <v>68</v>
       </c>
       <c r="L13" s="4">
-        <v>-22.5</v>
+        <v>-39</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="O13" s="9">
-        <v>62</v>
-      </c>
-      <c r="P13" s="10">
-        <v>60</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>0</v>
-      </c>
-      <c r="R13" s="8">
+        <v>160</v>
+      </c>
+      <c r="O13" s="6">
+        <v>28</v>
+      </c>
+      <c r="P13" s="16">
+        <v>28</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>0</v>
+      </c>
+      <c r="R13" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1850,54 +1859,54 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>69</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="L14" s="4">
-        <v>-35.2</v>
+        <v>-23.3</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O14" s="9">
-        <v>59</v>
-      </c>
-      <c r="P14" s="11">
-        <v>57</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>0</v>
-      </c>
-      <c r="R14" s="8">
+        <v>161</v>
+      </c>
+      <c r="O14" s="6">
+        <v>21</v>
+      </c>
+      <c r="P14" s="10">
+        <v>16</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>0</v>
+      </c>
+      <c r="R14" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1906,54 +1915,54 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>70</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="K15" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="L15" s="4">
+        <v>-35.9</v>
+      </c>
+      <c r="M15" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="L15" s="4">
-        <v>-30</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="N15" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O15" s="12">
-        <v>39</v>
-      </c>
-      <c r="P15" s="13">
-        <v>28</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>0</v>
-      </c>
-      <c r="R15" s="8">
+        <v>159</v>
+      </c>
+      <c r="O15" s="11">
+        <v>10</v>
+      </c>
+      <c r="P15" s="17">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>0</v>
+      </c>
+      <c r="R15" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1962,54 +1971,54 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>71</v>
+        <v>155</v>
       </c>
       <c r="L16" s="4">
-        <v>-39</v>
+        <v>-15.5</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="O16" s="12">
-        <v>38</v>
-      </c>
-      <c r="P16" s="14">
-        <v>26</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>0</v>
-      </c>
-      <c r="R16" s="8">
+        <v>161</v>
+      </c>
+      <c r="O16" s="11">
+        <v>0</v>
+      </c>
+      <c r="P16" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="9">
+        <v>0</v>
+      </c>
+      <c r="R16" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2018,10 +2027,10 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>56</v>
@@ -2030,158 +2039,102 @@
         <v>72</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K17" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-30.7</v>
+      </c>
+      <c r="M17" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="L17" s="4">
-        <v>-23.2</v>
-      </c>
-      <c r="M17" s="3" t="s">
+      <c r="N17" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="N17" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O17" s="12">
-        <v>14</v>
-      </c>
-      <c r="P17" s="15">
-        <v>4</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>0</v>
-      </c>
-      <c r="R17" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="2">
-        <v>23</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="L18" s="4">
-        <v>-35.8</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O18" s="6">
-        <v>7</v>
-      </c>
-      <c r="P18" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>0</v>
-      </c>
-      <c r="R18" s="8">
+      <c r="O17" s="11">
+        <v>0</v>
+      </c>
+      <c r="P17" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>0</v>
+      </c>
+      <c r="R17" s="9">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A18">
+  <conditionalFormatting sqref="A2:A17">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B18">
+  <conditionalFormatting sqref="B2:B17">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C18">
+  <conditionalFormatting sqref="C2:C17">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D18">
+  <conditionalFormatting sqref="D2:D17">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E18">
+  <conditionalFormatting sqref="E2:E17">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F18">
+  <conditionalFormatting sqref="F2:F17">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G18">
+  <conditionalFormatting sqref="G2:G17">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H18">
+  <conditionalFormatting sqref="H2:H17">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I18">
+  <conditionalFormatting sqref="I2:I17">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J18">
+  <conditionalFormatting sqref="J2:J17">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K18">
+  <conditionalFormatting sqref="K2:K17">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L18">
+  <conditionalFormatting sqref="L2:L17">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2200,12 +2153,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M18">
+  <conditionalFormatting sqref="M2:M17">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N18">
+  <conditionalFormatting sqref="N2:N17">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2222,22 +2175,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O18">
+  <conditionalFormatting sqref="O2:O17">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P18">
+  <conditionalFormatting sqref="P2:P17">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q18">
+  <conditionalFormatting sqref="Q2:Q17">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R18">
+  <conditionalFormatting sqref="R2:R17">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="158">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260708--01</t>
-  </si>
-  <si>
-    <t>20260708--02</t>
-  </si>
-  <si>
     <t>20260709--01</t>
   </si>
   <si>
@@ -118,28 +112,25 @@
     <t>20260714--02</t>
   </si>
   <si>
-    <t>06:36</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>06:12</t>
+    <t>20260715--01</t>
+  </si>
+  <si>
+    <t>06:11</t>
   </si>
   <si>
     <t>04:54</t>
   </si>
   <si>
-    <t>05:29</t>
+    <t>05:30</t>
   </si>
   <si>
     <t>06:02</t>
   </si>
   <si>
-    <t>04:27</t>
-  </si>
-  <si>
-    <t>06:35</t>
+    <t>04:26</t>
+  </si>
+  <si>
+    <t>06:34</t>
   </si>
   <si>
     <t>02:50</t>
@@ -148,103 +139,100 @@
     <t>06:42</t>
   </si>
   <si>
-    <t>06:29</t>
-  </si>
-  <si>
-    <t>03:31</t>
-  </si>
-  <si>
-    <t>05:59</t>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>03:32</t>
+  </si>
+  <si>
+    <t>05:58</t>
   </si>
   <si>
     <t>05:24</t>
   </si>
   <si>
-    <t>05:09</t>
-  </si>
-  <si>
-    <t>06:18</t>
+    <t>05:10</t>
+  </si>
+  <si>
+    <t>06:17</t>
+  </si>
+  <si>
+    <t>06:40</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:42</t>
-  </si>
-  <si>
-    <t>01:53</t>
-  </si>
-  <si>
-    <t>00:44</t>
+    <t>00:41</t>
+  </si>
+  <si>
+    <t>01:52</t>
+  </si>
+  <si>
+    <t>00:45</t>
   </si>
   <si>
     <t>02:26</t>
   </si>
   <si>
-    <t>04:04</t>
-  </si>
-  <si>
-    <t>00:09</t>
-  </si>
-  <si>
-    <t>01:08:15</t>
-  </si>
-  <si>
-    <t>02:46:21</t>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>00:08</t>
+  </si>
+  <si>
+    <t>02:17</t>
   </si>
   <si>
     <t>00:21:29</t>
   </si>
   <si>
-    <t>01:59:07</t>
-  </si>
-  <si>
-    <t>23:34:41</t>
+    <t>01:59:08</t>
+  </si>
+  <si>
+    <t>23:34:42</t>
   </si>
   <si>
     <t>01:12:01</t>
   </si>
   <si>
-    <t>22:47:51</t>
+    <t>22:47:52</t>
   </si>
   <si>
     <t>00:24:58</t>
   </si>
   <si>
-    <t>22:00:59</t>
+    <t>22:01:00</t>
   </si>
   <si>
     <t>23:37:57</t>
   </si>
   <si>
-    <t>22:50:56</t>
-  </si>
-  <si>
-    <t>00:28:50</t>
-  </si>
-  <si>
-    <t>22:03:55</t>
-  </si>
-  <si>
-    <t>23:41:25</t>
+    <t>22:50:57</t>
+  </si>
+  <si>
+    <t>00:28:51</t>
+  </si>
+  <si>
+    <t>22:03:56</t>
+  </si>
+  <si>
+    <t>23:41:26</t>
   </si>
   <si>
     <t>21:16:53</t>
   </si>
   <si>
-    <t>22:54:06</t>
-  </si>
-  <si>
-    <t>01:10:23</t>
-  </si>
-  <si>
-    <t>02:49:41</t>
-  </si>
-  <si>
-    <t>00:23:42</t>
-  </si>
-  <si>
-    <t>02:01:37</t>
+    <t>22:54:07</t>
+  </si>
+  <si>
+    <t>22:06:50</t>
+  </si>
+  <si>
+    <t>00:23:43</t>
+  </si>
+  <si>
+    <t>02:01:38</t>
   </si>
   <si>
     <t>23:37:05</t>
@@ -253,16 +241,16 @@
     <t>01:14:15</t>
   </si>
   <si>
-    <t>22:50:32</t>
-  </si>
-  <si>
-    <t>00:27:05</t>
-  </si>
-  <si>
-    <t>22:04:10</t>
-  </si>
-  <si>
-    <t>23:40:03</t>
+    <t>22:50:33</t>
+  </si>
+  <si>
+    <t>00:27:06</t>
+  </si>
+  <si>
+    <t>22:04:11</t>
+  </si>
+  <si>
+    <t>23:40:04</t>
   </si>
   <si>
     <t>22:53:06</t>
@@ -271,79 +259,73 @@
     <t>00:31:44</t>
   </si>
   <si>
-    <t>22:06:12</t>
-  </si>
-  <si>
-    <t>23:43:48</t>
+    <t>22:06:13</t>
+  </si>
+  <si>
+    <t>23:43:49</t>
   </si>
   <si>
     <t>21:19:22</t>
   </si>
   <si>
-    <t>22:56:17</t>
-  </si>
-  <si>
-    <t>01:13:42</t>
-  </si>
-  <si>
-    <t>02:50:48</t>
-  </si>
-  <si>
-    <t>00:26:48</t>
-  </si>
-  <si>
-    <t>02:04:04</t>
+    <t>22:56:18</t>
+  </si>
+  <si>
+    <t>22:08:57</t>
+  </si>
+  <si>
+    <t>00:26:49</t>
+  </si>
+  <si>
+    <t>02:04:05</t>
   </si>
   <si>
     <t>23:39:50</t>
   </si>
   <si>
-    <t>01:17:16</t>
-  </si>
-  <si>
-    <t>22:52:45</t>
+    <t>01:17:17</t>
+  </si>
+  <si>
+    <t>22:52:46</t>
   </si>
   <si>
     <t>00:30:23</t>
   </si>
   <si>
-    <t>22:05:35</t>
-  </si>
-  <si>
-    <t>23:43:24</t>
-  </si>
-  <si>
-    <t>22:56:21</t>
-  </si>
-  <si>
-    <t>00:33:29</t>
+    <t>22:05:36</t>
+  </si>
+  <si>
+    <t>23:43:25</t>
+  </si>
+  <si>
+    <t>22:56:22</t>
+  </si>
+  <si>
+    <t>00:33:30</t>
   </si>
   <si>
     <t>22:09:12</t>
   </si>
   <si>
-    <t>23:46:30</t>
+    <t>23:46:31</t>
   </si>
   <si>
     <t>21:21:57</t>
   </si>
   <si>
-    <t>22:59:26</t>
-  </si>
-  <si>
-    <t>01:16:59</t>
-  </si>
-  <si>
-    <t>02:51:56</t>
+    <t>22:59:27</t>
+  </si>
+  <si>
+    <t>22:12:18</t>
   </si>
   <si>
     <t>00:29:54</t>
   </si>
   <si>
-    <t>02:06:31</t>
-  </si>
-  <si>
-    <t>23:42:34</t>
+    <t>02:06:32</t>
+  </si>
+  <si>
+    <t>23:42:35</t>
   </si>
   <si>
     <t>01:20:17</t>
@@ -355,34 +337,31 @@
     <t>00:33:40</t>
   </si>
   <si>
-    <t>22:07:00</t>
-  </si>
-  <si>
-    <t>23:46:45</t>
-  </si>
-  <si>
-    <t>22:59:35</t>
-  </si>
-  <si>
-    <t>00:35:15</t>
+    <t>22:07:01</t>
+  </si>
+  <si>
+    <t>23:46:46</t>
+  </si>
+  <si>
+    <t>22:59:36</t>
+  </si>
+  <si>
+    <t>00:35:16</t>
   </si>
   <si>
     <t>22:12:11</t>
   </si>
   <si>
-    <t>23:49:12</t>
-  </si>
-  <si>
-    <t>21:24:31</t>
+    <t>23:49:13</t>
+  </si>
+  <si>
+    <t>21:24:32</t>
   </si>
   <si>
     <t>23:02:35</t>
   </si>
   <si>
-    <t>01:19:07</t>
-  </si>
-  <si>
-    <t>02:55:16</t>
+    <t>22:15:37</t>
   </si>
   <si>
     <t>00:32:07</t>
@@ -391,13 +370,13 @@
     <t>02:09:01</t>
   </si>
   <si>
-    <t>23:44:57</t>
+    <t>23:44:58</t>
   </si>
   <si>
     <t>01:22:31</t>
   </si>
   <si>
-    <t>22:57:38</t>
+    <t>22:57:39</t>
   </si>
   <si>
     <t>00:35:47</t>
@@ -412,21 +391,24 @@
     <t>23:01:44</t>
   </si>
   <si>
-    <t>00:38:08</t>
+    <t>00:38:09</t>
   </si>
   <si>
     <t>22:14:27</t>
   </si>
   <si>
-    <t>23:51:34</t>
-  </si>
-  <si>
-    <t>21:26:59</t>
+    <t>23:51:35</t>
+  </si>
+  <si>
+    <t>21:27:00</t>
   </si>
   <si>
     <t>23:04:45</t>
   </si>
   <si>
+    <t>22:17:43</t>
+  </si>
+  <si>
     <t>0°</t>
   </si>
   <si>
@@ -457,6 +439,9 @@
     <t>11°</t>
   </si>
   <si>
+    <t>40°</t>
+  </si>
+  <si>
     <t>00:21:32</t>
   </si>
   <si>
@@ -469,24 +454,27 @@
     <t>22:06:03</t>
   </si>
   <si>
-    <t>23:39:02</t>
-  </si>
-  <si>
-    <t>22:53:50</t>
-  </si>
-  <si>
-    <t>22:08:38</t>
+    <t>23:39:03</t>
+  </si>
+  <si>
+    <t>22:53:51</t>
+  </si>
+  <si>
+    <t>22:08:39</t>
   </si>
   <si>
     <t>23:41:38</t>
   </si>
   <si>
-    <t>21:23:26</t>
+    <t>21:23:27</t>
   </si>
   <si>
     <t>22:56:26</t>
   </si>
   <si>
+    <t>22:11:14</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
@@ -496,10 +484,10 @@
     <t>3</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
 </sst>
 </file>
@@ -533,7 +521,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -548,13 +536,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -566,25 +560,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -596,25 +596,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -655,7 +637,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -703,9 +685,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1109,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1187,54 +1166,54 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>34</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="F2" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>57</v>
+        <v>142</v>
       </c>
       <c r="L2" s="4">
-        <v>-39.2</v>
+        <v>-38.1</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="O2" s="6">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="P2" s="7">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="Q2" s="8">
-        <v>6</v>
-      </c>
-      <c r="R2" s="9">
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1243,54 +1222,54 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L3" s="4">
-        <v>-33.8</v>
+        <v>-37.8</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="O3" s="6">
-        <v>25</v>
-      </c>
-      <c r="P3" s="10">
-        <v>15</v>
+        <v>3</v>
+      </c>
+      <c r="P3" s="9">
+        <v>4</v>
       </c>
       <c r="Q3" s="8">
-        <v>4</v>
-      </c>
-      <c r="R3" s="9">
+        <v>0</v>
+      </c>
+      <c r="R3" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1299,54 +1278,54 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="L4" s="4">
-        <v>-38.1</v>
+        <v>-34.8</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O4" s="11">
-        <v>0</v>
-      </c>
-      <c r="P4" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="9">
-        <v>0</v>
-      </c>
-      <c r="R4" s="9">
+        <v>155</v>
+      </c>
+      <c r="O4" s="6">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1355,54 +1334,54 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L5" s="4">
-        <v>-37.8</v>
+        <v>-39.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O5" s="11">
-        <v>0</v>
-      </c>
-      <c r="P5" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>0</v>
-      </c>
-      <c r="R5" s="9">
+        <v>155</v>
+      </c>
+      <c r="O5" s="6">
+        <v>0</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="R5" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1411,54 +1390,54 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="L6" s="4">
-        <v>-34.8</v>
+        <v>-29.4</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O6" s="11">
-        <v>0</v>
-      </c>
-      <c r="P6" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="9">
-        <v>0</v>
-      </c>
-      <c r="R6" s="9">
+        <v>156</v>
+      </c>
+      <c r="O6" s="6">
+        <v>0</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1467,54 +1446,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L7" s="4">
-        <v>-39.4</v>
+        <v>-38.6</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O7" s="11">
-        <v>0</v>
-      </c>
-      <c r="P7" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="9">
-        <v>0</v>
-      </c>
-      <c r="R7" s="9">
+        <v>155</v>
+      </c>
+      <c r="O7" s="6">
+        <v>0</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
+      <c r="R7" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1523,54 +1502,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L8" s="4">
-        <v>-29.4</v>
+        <v>-22.6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="O8" s="11">
-        <v>0</v>
-      </c>
-      <c r="P8" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="9">
-        <v>0</v>
-      </c>
-      <c r="R8" s="9">
+        <v>157</v>
+      </c>
+      <c r="O8" s="10">
+        <v>84</v>
+      </c>
+      <c r="P8" s="11">
+        <v>84</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1579,54 +1558,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>64</v>
+        <v>146</v>
       </c>
       <c r="L9" s="4">
-        <v>-38.6</v>
+        <v>-35.3</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O9" s="11">
-        <v>0</v>
-      </c>
-      <c r="P9" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="9">
-        <v>0</v>
-      </c>
-      <c r="R9" s="9">
+        <v>155</v>
+      </c>
+      <c r="O9" s="10">
+        <v>82</v>
+      </c>
+      <c r="P9" s="12">
+        <v>82</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1635,54 +1614,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="L10" s="4">
-        <v>-22.6</v>
+        <v>-30.1</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="O10" s="12">
-        <v>53</v>
-      </c>
-      <c r="P10" s="13">
-        <v>52</v>
-      </c>
-      <c r="Q10" s="9">
-        <v>0</v>
-      </c>
-      <c r="R10" s="9">
+        <v>156</v>
+      </c>
+      <c r="O10" s="13">
+        <v>35</v>
+      </c>
+      <c r="P10" s="14">
+        <v>30</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1691,54 +1670,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>151</v>
+        <v>65</v>
       </c>
       <c r="L11" s="4">
-        <v>-35.3</v>
+        <v>-39</v>
       </c>
       <c r="M11" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="N11" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="N11" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O11" s="12">
-        <v>56</v>
-      </c>
-      <c r="P11" s="14">
-        <v>56</v>
-      </c>
-      <c r="Q11" s="9">
-        <v>0</v>
-      </c>
-      <c r="R11" s="9">
+      <c r="O11" s="10">
+        <v>49</v>
+      </c>
+      <c r="P11" s="15">
+        <v>48</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>0</v>
+      </c>
+      <c r="R11" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1747,54 +1726,54 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L12" s="4">
-        <v>-30.1</v>
+        <v>-23.3</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="O12" s="12">
-        <v>46</v>
-      </c>
-      <c r="P12" s="15">
-        <v>46</v>
-      </c>
-      <c r="Q12" s="9">
-        <v>0</v>
-      </c>
-      <c r="R12" s="9">
+        <v>156</v>
+      </c>
+      <c r="O12" s="13">
+        <v>23</v>
+      </c>
+      <c r="P12" s="16">
+        <v>15</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1803,54 +1782,54 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
+        <v>23</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-35.9</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="O13" s="13">
+        <v>17</v>
+      </c>
+      <c r="P13" s="16">
         <v>14</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-39</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="O13" s="6">
-        <v>28</v>
-      </c>
-      <c r="P13" s="16">
-        <v>28</v>
-      </c>
-      <c r="Q13" s="9">
-        <v>0</v>
-      </c>
-      <c r="R13" s="9">
+      <c r="Q13" s="8">
+        <v>0</v>
+      </c>
+      <c r="R13" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1859,54 +1838,54 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="L14" s="4">
-        <v>-23.3</v>
+        <v>-15.5</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="O14" s="6">
-        <v>21</v>
-      </c>
-      <c r="P14" s="10">
-        <v>16</v>
-      </c>
-      <c r="Q14" s="9">
-        <v>0</v>
-      </c>
-      <c r="R14" s="9">
+        <v>0</v>
+      </c>
+      <c r="P14" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>0</v>
+      </c>
+      <c r="R14" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1915,54 +1894,54 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="K15" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="L15" s="4">
+        <v>-30.7</v>
+      </c>
+      <c r="M15" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="L15" s="4">
-        <v>-35.9</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="N15" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O15" s="11">
-        <v>10</v>
-      </c>
-      <c r="P15" s="17">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="9">
-        <v>0</v>
-      </c>
-      <c r="R15" s="9">
+        <v>156</v>
+      </c>
+      <c r="O15" s="6">
+        <v>0</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+      <c r="R15" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1971,170 +1950,114 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="L16" s="4">
-        <v>-15.5</v>
+        <v>-24</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="O16" s="11">
-        <v>0</v>
-      </c>
-      <c r="P16" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="9">
-        <v>0</v>
-      </c>
-      <c r="R16" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="A17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="2">
-        <v>39</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="K17" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="L17" s="4">
-        <v>-30.7</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="O17" s="11">
-        <v>0</v>
-      </c>
-      <c r="P17" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="9">
-        <v>0</v>
-      </c>
-      <c r="R17" s="9">
+      <c r="O16" s="6">
+        <v>0</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>0</v>
+      </c>
+      <c r="R16" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A17">
+  <conditionalFormatting sqref="A2:A16">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B17">
+  <conditionalFormatting sqref="B2:B16">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C17">
+  <conditionalFormatting sqref="C2:C16">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D17">
+  <conditionalFormatting sqref="D2:D16">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E17">
+  <conditionalFormatting sqref="E2:E16">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F17">
+  <conditionalFormatting sqref="F2:F16">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G17">
+  <conditionalFormatting sqref="G2:G16">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H17">
+  <conditionalFormatting sqref="H2:H16">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I17">
+  <conditionalFormatting sqref="I2:I16">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J17">
+  <conditionalFormatting sqref="J2:J16">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K17">
+  <conditionalFormatting sqref="K2:K16">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L17">
+  <conditionalFormatting sqref="L2:L16">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2153,12 +2076,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M17">
+  <conditionalFormatting sqref="M2:M16">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N17">
+  <conditionalFormatting sqref="N2:N16">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2175,22 +2098,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O17">
+  <conditionalFormatting sqref="O2:O16">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P17">
+  <conditionalFormatting sqref="P2:P16">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q17">
+  <conditionalFormatting sqref="Q2:Q16">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R17">
+  <conditionalFormatting sqref="R2:R16">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="146">
   <si>
     <t>Datum</t>
   </si>
@@ -70,21 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260709--01</t>
-  </si>
-  <si>
-    <t>20260709--02</t>
-  </si>
-  <si>
-    <t>20260709--03</t>
-  </si>
-  <si>
-    <t>20260710--01</t>
-  </si>
-  <si>
-    <t>20260710--02</t>
-  </si>
-  <si>
     <t>20260711--01</t>
   </si>
   <si>
@@ -115,309 +100,279 @@
     <t>20260715--01</t>
   </si>
   <si>
-    <t>06:11</t>
-  </si>
-  <si>
-    <t>04:54</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>06:02</t>
-  </si>
-  <si>
-    <t>04:26</t>
+    <t>20260716--01</t>
+  </si>
+  <si>
+    <t>20260717--01</t>
+  </si>
+  <si>
+    <t>20260717--02</t>
   </si>
   <si>
     <t>06:34</t>
   </si>
   <si>
-    <t>02:50</t>
+    <t>02:49</t>
   </si>
   <si>
     <t>06:42</t>
   </si>
   <si>
-    <t>06:30</t>
+    <t>06:29</t>
   </si>
   <si>
     <t>03:32</t>
   </si>
   <si>
-    <t>05:58</t>
+    <t>05:59</t>
   </si>
   <si>
     <t>05:24</t>
   </si>
   <si>
-    <t>05:10</t>
-  </si>
-  <si>
-    <t>06:17</t>
+    <t>05:08</t>
+  </si>
+  <si>
+    <t>06:18</t>
   </si>
   <si>
     <t>06:40</t>
   </si>
   <si>
+    <t>06:39</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>04:30</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:41</t>
-  </si>
-  <si>
     <t>01:52</t>
   </si>
   <si>
-    <t>00:45</t>
-  </si>
-  <si>
-    <t>02:26</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>00:08</t>
-  </si>
-  <si>
-    <t>02:17</t>
-  </si>
-  <si>
-    <t>00:21:29</t>
-  </si>
-  <si>
-    <t>01:59:08</t>
-  </si>
-  <si>
-    <t>23:34:42</t>
-  </si>
-  <si>
-    <t>01:12:01</t>
-  </si>
-  <si>
-    <t>22:47:52</t>
-  </si>
-  <si>
-    <t>00:24:58</t>
-  </si>
-  <si>
-    <t>22:01:00</t>
-  </si>
-  <si>
-    <t>23:37:57</t>
-  </si>
-  <si>
-    <t>22:50:57</t>
-  </si>
-  <si>
-    <t>00:28:51</t>
-  </si>
-  <si>
-    <t>22:03:56</t>
-  </si>
-  <si>
-    <t>23:41:26</t>
-  </si>
-  <si>
-    <t>21:16:53</t>
-  </si>
-  <si>
-    <t>22:54:07</t>
-  </si>
-  <si>
-    <t>22:06:50</t>
-  </si>
-  <si>
-    <t>00:23:43</t>
-  </si>
-  <si>
-    <t>02:01:38</t>
-  </si>
-  <si>
-    <t>23:37:05</t>
-  </si>
-  <si>
-    <t>01:14:15</t>
-  </si>
-  <si>
-    <t>22:50:33</t>
-  </si>
-  <si>
-    <t>00:27:06</t>
-  </si>
-  <si>
-    <t>22:04:11</t>
-  </si>
-  <si>
-    <t>23:40:04</t>
-  </si>
-  <si>
-    <t>22:53:06</t>
-  </si>
-  <si>
-    <t>00:31:44</t>
-  </si>
-  <si>
-    <t>22:06:13</t>
-  </si>
-  <si>
-    <t>23:43:49</t>
-  </si>
-  <si>
-    <t>21:19:22</t>
-  </si>
-  <si>
-    <t>22:56:18</t>
-  </si>
-  <si>
-    <t>22:08:57</t>
-  </si>
-  <si>
-    <t>00:26:49</t>
-  </si>
-  <si>
-    <t>02:04:05</t>
-  </si>
-  <si>
-    <t>23:39:50</t>
-  </si>
-  <si>
-    <t>01:17:17</t>
-  </si>
-  <si>
-    <t>22:52:46</t>
-  </si>
-  <si>
-    <t>00:30:23</t>
-  </si>
-  <si>
-    <t>22:05:36</t>
-  </si>
-  <si>
-    <t>23:43:25</t>
-  </si>
-  <si>
-    <t>22:56:22</t>
-  </si>
-  <si>
-    <t>00:33:30</t>
-  </si>
-  <si>
-    <t>22:09:12</t>
-  </si>
-  <si>
-    <t>23:46:31</t>
-  </si>
-  <si>
-    <t>21:21:57</t>
-  </si>
-  <si>
-    <t>22:59:27</t>
-  </si>
-  <si>
-    <t>22:12:18</t>
-  </si>
-  <si>
-    <t>00:29:54</t>
-  </si>
-  <si>
-    <t>02:06:32</t>
-  </si>
-  <si>
-    <t>23:42:35</t>
-  </si>
-  <si>
-    <t>01:20:17</t>
-  </si>
-  <si>
-    <t>22:54:59</t>
-  </si>
-  <si>
-    <t>00:33:40</t>
-  </si>
-  <si>
-    <t>22:07:01</t>
-  </si>
-  <si>
-    <t>23:46:46</t>
-  </si>
-  <si>
-    <t>22:59:36</t>
-  </si>
-  <si>
-    <t>00:35:16</t>
-  </si>
-  <si>
-    <t>22:12:11</t>
-  </si>
-  <si>
-    <t>23:49:13</t>
-  </si>
-  <si>
-    <t>21:24:32</t>
-  </si>
-  <si>
-    <t>23:02:35</t>
-  </si>
-  <si>
-    <t>22:15:37</t>
-  </si>
-  <si>
-    <t>00:32:07</t>
-  </si>
-  <si>
-    <t>02:09:01</t>
-  </si>
-  <si>
-    <t>23:44:58</t>
-  </si>
-  <si>
-    <t>01:22:31</t>
-  </si>
-  <si>
-    <t>22:57:39</t>
-  </si>
-  <si>
-    <t>00:35:47</t>
-  </si>
-  <si>
-    <t>22:10:11</t>
-  </si>
-  <si>
-    <t>23:48:51</t>
-  </si>
-  <si>
-    <t>23:01:44</t>
-  </si>
-  <si>
-    <t>00:38:09</t>
-  </si>
-  <si>
-    <t>22:14:27</t>
-  </si>
-  <si>
-    <t>23:51:35</t>
-  </si>
-  <si>
-    <t>21:27:00</t>
-  </si>
-  <si>
-    <t>23:04:45</t>
-  </si>
-  <si>
-    <t>22:17:43</t>
+    <t>00:44</t>
+  </si>
+  <si>
+    <t>02:27</t>
+  </si>
+  <si>
+    <t>04:04</t>
+  </si>
+  <si>
+    <t>00:09</t>
+  </si>
+  <si>
+    <t>02:18</t>
+  </si>
+  <si>
+    <t>04:21</t>
+  </si>
+  <si>
+    <t>01:14</t>
+  </si>
+  <si>
+    <t>00:24:57</t>
+  </si>
+  <si>
+    <t>22:00:58</t>
+  </si>
+  <si>
+    <t>23:37:55</t>
+  </si>
+  <si>
+    <t>22:50:54</t>
+  </si>
+  <si>
+    <t>00:28:48</t>
+  </si>
+  <si>
+    <t>22:03:51</t>
+  </si>
+  <si>
+    <t>23:41:21</t>
+  </si>
+  <si>
+    <t>21:16:47</t>
+  </si>
+  <si>
+    <t>22:54:00</t>
+  </si>
+  <si>
+    <t>22:06:42</t>
+  </si>
+  <si>
+    <t>21:19:25</t>
+  </si>
+  <si>
+    <t>20:32:08</t>
+  </si>
+  <si>
+    <t>22:09:50</t>
+  </si>
+  <si>
+    <t>00:27:05</t>
+  </si>
+  <si>
+    <t>22:04:10</t>
+  </si>
+  <si>
+    <t>23:40:02</t>
+  </si>
+  <si>
+    <t>22:53:04</t>
+  </si>
+  <si>
+    <t>00:31:41</t>
+  </si>
+  <si>
+    <t>22:06:08</t>
+  </si>
+  <si>
+    <t>23:43:44</t>
+  </si>
+  <si>
+    <t>21:19:17</t>
+  </si>
+  <si>
+    <t>22:56:11</t>
+  </si>
+  <si>
+    <t>22:08:49</t>
+  </si>
+  <si>
+    <t>21:21:33</t>
+  </si>
+  <si>
+    <t>20:34:20</t>
+  </si>
+  <si>
+    <t>22:12:27</t>
+  </si>
+  <si>
+    <t>00:30:22</t>
+  </si>
+  <si>
+    <t>22:05:34</t>
+  </si>
+  <si>
+    <t>23:43:23</t>
+  </si>
+  <si>
+    <t>22:56:19</t>
+  </si>
+  <si>
+    <t>00:33:27</t>
+  </si>
+  <si>
+    <t>22:09:08</t>
+  </si>
+  <si>
+    <t>23:46:26</t>
+  </si>
+  <si>
+    <t>21:21:51</t>
+  </si>
+  <si>
+    <t>22:59:20</t>
+  </si>
+  <si>
+    <t>22:12:10</t>
+  </si>
+  <si>
+    <t>21:24:53</t>
+  </si>
+  <si>
+    <t>20:37:30</t>
+  </si>
+  <si>
+    <t>22:14:42</t>
+  </si>
+  <si>
+    <t>00:33:39</t>
+  </si>
+  <si>
+    <t>22:06:59</t>
+  </si>
+  <si>
+    <t>23:46:44</t>
+  </si>
+  <si>
+    <t>22:59:33</t>
+  </si>
+  <si>
+    <t>00:35:13</t>
+  </si>
+  <si>
+    <t>22:12:07</t>
+  </si>
+  <si>
+    <t>23:49:08</t>
+  </si>
+  <si>
+    <t>21:24:25</t>
+  </si>
+  <si>
+    <t>23:02:29</t>
+  </si>
+  <si>
+    <t>22:15:29</t>
+  </si>
+  <si>
+    <t>21:28:12</t>
+  </si>
+  <si>
+    <t>20:40:40</t>
+  </si>
+  <si>
+    <t>22:16:57</t>
+  </si>
+  <si>
+    <t>00:35:46</t>
+  </si>
+  <si>
+    <t>22:10:09</t>
+  </si>
+  <si>
+    <t>23:48:49</t>
+  </si>
+  <si>
+    <t>23:01:41</t>
+  </si>
+  <si>
+    <t>00:38:06</t>
+  </si>
+  <si>
+    <t>22:14:23</t>
+  </si>
+  <si>
+    <t>23:51:30</t>
+  </si>
+  <si>
+    <t>21:26:54</t>
+  </si>
+  <si>
+    <t>23:04:39</t>
+  </si>
+  <si>
+    <t>22:17:35</t>
+  </si>
+  <si>
+    <t>21:30:18</t>
+  </si>
+  <si>
+    <t>20:42:51</t>
+  </si>
+  <si>
+    <t>22:19:33</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>7°</t>
-  </si>
-  <si>
-    <t>13°</t>
-  </si>
-  <si>
     <t>12°</t>
   </si>
   <si>
@@ -442,37 +397,40 @@
     <t>40°</t>
   </si>
   <si>
-    <t>00:21:32</t>
-  </si>
-  <si>
-    <t>23:36:24</t>
-  </si>
-  <si>
-    <t>22:51:14</t>
-  </si>
-  <si>
-    <t>22:06:03</t>
-  </si>
-  <si>
-    <t>23:39:03</t>
-  </si>
-  <si>
-    <t>22:53:51</t>
-  </si>
-  <si>
-    <t>22:08:39</t>
-  </si>
-  <si>
-    <t>23:41:38</t>
-  </si>
-  <si>
-    <t>21:23:27</t>
-  </si>
-  <si>
-    <t>22:56:26</t>
-  </si>
-  <si>
-    <t>22:11:14</t>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>22:06:02</t>
+  </si>
+  <si>
+    <t>23:39:01</t>
+  </si>
+  <si>
+    <t>22:53:48</t>
+  </si>
+  <si>
+    <t>22:08:35</t>
+  </si>
+  <si>
+    <t>23:41:34</t>
+  </si>
+  <si>
+    <t>21:23:21</t>
+  </si>
+  <si>
+    <t>22:56:20</t>
+  </si>
+  <si>
+    <t>22:11:07</t>
+  </si>
+  <si>
+    <t>21:25:54</t>
+  </si>
+  <si>
+    <t>20:40:42</t>
+  </si>
+  <si>
+    <t>22:13:41</t>
   </si>
   <si>
     <t>B</t>
@@ -481,13 +439,19 @@
     <t>A+B</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>4</t>
+    <t>1</t>
   </si>
 </sst>
 </file>
@@ -521,7 +485,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -542,7 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -554,25 +518,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -584,13 +542,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -637,7 +595,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -682,9 +640,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1088,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1166,49 +1121,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-38.6</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="L2" s="4">
-        <v>-38.1</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="O2" s="6">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="P2" s="7">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1222,49 +1177,49 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>57</v>
+        <v>128</v>
       </c>
       <c r="L3" s="4">
-        <v>-37.8</v>
+        <v>-22.6</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="O3" s="6">
-        <v>3</v>
-      </c>
-      <c r="P3" s="9">
-        <v>4</v>
+        <v>143</v>
+      </c>
+      <c r="O3" s="9">
+        <v>66</v>
+      </c>
+      <c r="P3" s="10">
+        <v>62</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1278,49 +1233,49 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="L4" s="4">
-        <v>-34.8</v>
+        <v>-35.3</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="O4" s="6">
-        <v>0</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
+        <v>142</v>
+      </c>
+      <c r="O4" s="9">
+        <v>63</v>
+      </c>
+      <c r="P4" s="10">
+        <v>61</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
@@ -1334,49 +1289,49 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>59</v>
+        <v>130</v>
       </c>
       <c r="L5" s="4">
-        <v>-39.4</v>
+        <v>-30.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="O5" s="6">
-        <v>0</v>
-      </c>
-      <c r="P5" s="8">
-        <v>0</v>
+        <v>144</v>
+      </c>
+      <c r="O5" s="9">
+        <v>61</v>
+      </c>
+      <c r="P5" s="11">
+        <v>37</v>
       </c>
       <c r="Q5" s="8">
         <v>0</v>
@@ -1390,49 +1345,49 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="L6" s="4">
-        <v>-29.4</v>
+        <v>-39</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="8">
-        <v>0</v>
+        <v>143</v>
+      </c>
+      <c r="O6" s="12">
+        <v>48</v>
+      </c>
+      <c r="P6" s="11">
+        <v>35</v>
       </c>
       <c r="Q6" s="8">
         <v>0</v>
@@ -1446,49 +1401,49 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="J7" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="L7" s="4">
-        <v>-38.6</v>
+        <v>-23.3</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="O7" s="6">
-        <v>0</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
+        <v>144</v>
+      </c>
+      <c r="O7" s="12">
+        <v>25</v>
+      </c>
+      <c r="P7" s="13">
+        <v>10</v>
       </c>
       <c r="Q7" s="8">
         <v>0</v>
@@ -1502,49 +1457,49 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="L8" s="4">
-        <v>-22.6</v>
+        <v>-35.8</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="O8" s="10">
-        <v>84</v>
-      </c>
-      <c r="P8" s="11">
-        <v>84</v>
+        <v>142</v>
+      </c>
+      <c r="O8" s="12">
+        <v>23</v>
+      </c>
+      <c r="P8" s="13">
+        <v>11</v>
       </c>
       <c r="Q8" s="8">
         <v>0</v>
@@ -1558,49 +1513,49 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>48</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="L9" s="4">
-        <v>-35.3</v>
+        <v>-15.4</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="O9" s="10">
-        <v>82</v>
-      </c>
-      <c r="P9" s="12">
-        <v>82</v>
+        <v>144</v>
+      </c>
+      <c r="O9" s="6">
+        <v>11</v>
+      </c>
+      <c r="P9" s="14">
+        <v>7</v>
       </c>
       <c r="Q9" s="8">
         <v>0</v>
@@ -1614,49 +1569,49 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="L10" s="4">
-        <v>-30.1</v>
+        <v>-30.7</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="O10" s="13">
-        <v>35</v>
+        <v>144</v>
+      </c>
+      <c r="O10" s="6">
+        <v>9</v>
       </c>
       <c r="P10" s="14">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="Q10" s="8">
         <v>0</v>
@@ -1670,49 +1625,49 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>65</v>
+        <v>135</v>
       </c>
       <c r="L11" s="4">
-        <v>-39</v>
+        <v>-24</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="O11" s="10">
-        <v>49</v>
-      </c>
-      <c r="P11" s="15">
-        <v>48</v>
+        <v>144</v>
+      </c>
+      <c r="O11" s="6">
+        <v>0</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0</v>
       </c>
       <c r="Q11" s="8">
         <v>0</v>
@@ -1726,49 +1681,49 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="K12" s="1" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="L12" s="4">
-        <v>-23.3</v>
+        <v>-16.1</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="O12" s="13">
-        <v>23</v>
-      </c>
-      <c r="P12" s="16">
-        <v>15</v>
+        <v>144</v>
+      </c>
+      <c r="O12" s="6">
+        <v>0</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0</v>
       </c>
       <c r="Q12" s="8">
         <v>0</v>
@@ -1782,52 +1737,52 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="I13" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="K13" s="1" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="L13" s="4">
-        <v>-35.9</v>
+        <v>-7.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="O13" s="13">
+        <v>145</v>
+      </c>
+      <c r="O13" s="12">
+        <v>30</v>
+      </c>
+      <c r="P13" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="15">
         <v>17</v>
-      </c>
-      <c r="P13" s="16">
-        <v>14</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>0</v>
       </c>
       <c r="R13" s="8">
         <v>0</v>
@@ -1838,226 +1793,114 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="L14" s="4">
-        <v>-15.5</v>
+        <v>-24.6</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="O14" s="6">
-        <v>0</v>
+        <v>144</v>
+      </c>
+      <c r="O14" s="12">
+        <v>40</v>
       </c>
       <c r="P14" s="8">
         <v>0</v>
       </c>
-      <c r="Q14" s="8">
-        <v>0</v>
+      <c r="Q14" s="14">
+        <v>3</v>
       </c>
       <c r="R14" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="2">
-        <v>39</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="L15" s="4">
-        <v>-30.7</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="O15" s="6">
-        <v>0</v>
-      </c>
-      <c r="P15" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>0</v>
-      </c>
-      <c r="R15" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="2">
-        <v>71</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="L16" s="4">
-        <v>-24</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="O16" s="6">
-        <v>0</v>
-      </c>
-      <c r="P16" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>0</v>
-      </c>
-      <c r="R16" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A16">
+  <conditionalFormatting sqref="A2:A14">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B16">
+  <conditionalFormatting sqref="B2:B14">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C16">
+  <conditionalFormatting sqref="C2:C14">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D16">
+  <conditionalFormatting sqref="D2:D14">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E16">
+  <conditionalFormatting sqref="E2:E14">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F16">
+  <conditionalFormatting sqref="F2:F14">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G16">
+  <conditionalFormatting sqref="G2:G14">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H16">
+  <conditionalFormatting sqref="H2:H14">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I16">
+  <conditionalFormatting sqref="I2:I14">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J16">
+  <conditionalFormatting sqref="J2:J14">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K16">
+  <conditionalFormatting sqref="K2:K14">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L16">
+  <conditionalFormatting sqref="L2:L14">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2076,12 +1919,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M16">
+  <conditionalFormatting sqref="M2:M14">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N16">
+  <conditionalFormatting sqref="N2:N14">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2098,22 +1941,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O16">
+  <conditionalFormatting sqref="O2:O14">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P16">
+  <conditionalFormatting sqref="P2:P14">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q16">
+  <conditionalFormatting sqref="Q2:Q14">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R16">
+  <conditionalFormatting sqref="R2:R14">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="127">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260711--01</t>
-  </si>
-  <si>
-    <t>20260711--02</t>
-  </si>
-  <si>
-    <t>20260711--03</t>
-  </si>
-  <si>
     <t>20260712--01</t>
   </si>
   <si>
@@ -109,34 +100,25 @@
     <t>20260717--02</t>
   </si>
   <si>
-    <t>06:34</t>
-  </si>
-  <si>
-    <t>02:49</t>
-  </si>
-  <si>
-    <t>06:42</t>
+    <t>20260718--01</t>
   </si>
   <si>
     <t>06:29</t>
   </si>
   <si>
-    <t>03:32</t>
+    <t>03:31</t>
   </si>
   <si>
     <t>05:59</t>
   </si>
   <si>
-    <t>05:24</t>
-  </si>
-  <si>
-    <t>05:08</t>
-  </si>
-  <si>
-    <t>06:18</t>
-  </si>
-  <si>
-    <t>06:40</t>
+    <t>05:23</t>
+  </si>
+  <si>
+    <t>05:09</t>
+  </si>
+  <si>
+    <t>06:17</t>
   </si>
   <si>
     <t>06:39</t>
@@ -145,243 +127,210 @@
     <t>06:20</t>
   </si>
   <si>
-    <t>04:30</t>
+    <t>04:28</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>00:44</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:52</t>
-  </si>
-  <si>
-    <t>00:44</t>
-  </si>
-  <si>
-    <t>02:27</t>
+    <t>02:26</t>
   </si>
   <si>
     <t>04:04</t>
   </si>
   <si>
-    <t>00:09</t>
-  </si>
-  <si>
-    <t>02:18</t>
-  </si>
-  <si>
-    <t>04:21</t>
-  </si>
-  <si>
-    <t>01:14</t>
-  </si>
-  <si>
-    <t>00:24:57</t>
-  </si>
-  <si>
-    <t>22:00:58</t>
-  </si>
-  <si>
-    <t>23:37:55</t>
-  </si>
-  <si>
-    <t>22:50:54</t>
-  </si>
-  <si>
-    <t>00:28:48</t>
-  </si>
-  <si>
-    <t>22:03:51</t>
-  </si>
-  <si>
-    <t>23:41:21</t>
-  </si>
-  <si>
-    <t>21:16:47</t>
-  </si>
-  <si>
-    <t>22:54:00</t>
-  </si>
-  <si>
-    <t>22:06:42</t>
-  </si>
-  <si>
-    <t>21:19:25</t>
-  </si>
-  <si>
-    <t>20:32:08</t>
-  </si>
-  <si>
-    <t>22:09:50</t>
-  </si>
-  <si>
-    <t>00:27:05</t>
-  </si>
-  <si>
-    <t>22:04:10</t>
-  </si>
-  <si>
-    <t>23:40:02</t>
-  </si>
-  <si>
-    <t>22:53:04</t>
-  </si>
-  <si>
-    <t>00:31:41</t>
-  </si>
-  <si>
-    <t>22:06:08</t>
-  </si>
-  <si>
-    <t>23:43:44</t>
-  </si>
-  <si>
-    <t>21:19:17</t>
-  </si>
-  <si>
-    <t>22:56:11</t>
-  </si>
-  <si>
-    <t>22:08:49</t>
-  </si>
-  <si>
-    <t>21:21:33</t>
-  </si>
-  <si>
-    <t>20:34:20</t>
-  </si>
-  <si>
-    <t>22:12:27</t>
-  </si>
-  <si>
-    <t>00:30:22</t>
-  </si>
-  <si>
-    <t>22:05:34</t>
-  </si>
-  <si>
-    <t>23:43:23</t>
-  </si>
-  <si>
-    <t>22:56:19</t>
-  </si>
-  <si>
-    <t>00:33:27</t>
-  </si>
-  <si>
-    <t>22:09:08</t>
-  </si>
-  <si>
-    <t>23:46:26</t>
+    <t>00:08</t>
+  </si>
+  <si>
+    <t>02:16</t>
+  </si>
+  <si>
+    <t>04:20</t>
+  </si>
+  <si>
+    <t>01:12</t>
+  </si>
+  <si>
+    <t>04:00</t>
+  </si>
+  <si>
+    <t>22:50:57</t>
+  </si>
+  <si>
+    <t>00:28:52</t>
+  </si>
+  <si>
+    <t>22:03:58</t>
+  </si>
+  <si>
+    <t>23:41:28</t>
+  </si>
+  <si>
+    <t>21:16:57</t>
+  </si>
+  <si>
+    <t>22:54:10</t>
+  </si>
+  <si>
+    <t>22:06:56</t>
+  </si>
+  <si>
+    <t>21:19:44</t>
+  </si>
+  <si>
+    <t>20:32:32</t>
+  </si>
+  <si>
+    <t>22:10:15</t>
+  </si>
+  <si>
+    <t>21:22:42</t>
+  </si>
+  <si>
+    <t>22:53:07</t>
+  </si>
+  <si>
+    <t>00:31:45</t>
+  </si>
+  <si>
+    <t>22:06:14</t>
+  </si>
+  <si>
+    <t>23:43:51</t>
+  </si>
+  <si>
+    <t>21:19:26</t>
+  </si>
+  <si>
+    <t>22:56:21</t>
+  </si>
+  <si>
+    <t>22:09:03</t>
   </si>
   <si>
     <t>21:21:51</t>
   </si>
   <si>
-    <t>22:59:20</t>
-  </si>
-  <si>
-    <t>22:12:10</t>
-  </si>
-  <si>
-    <t>21:24:53</t>
-  </si>
-  <si>
-    <t>20:37:30</t>
-  </si>
-  <si>
-    <t>22:14:42</t>
-  </si>
-  <si>
-    <t>00:33:39</t>
-  </si>
-  <si>
-    <t>22:06:59</t>
-  </si>
-  <si>
-    <t>23:46:44</t>
-  </si>
-  <si>
-    <t>22:59:33</t>
-  </si>
-  <si>
-    <t>00:35:13</t>
-  </si>
-  <si>
-    <t>22:12:07</t>
-  </si>
-  <si>
-    <t>23:49:08</t>
-  </si>
-  <si>
-    <t>21:24:25</t>
-  </si>
-  <si>
-    <t>23:02:29</t>
-  </si>
-  <si>
-    <t>22:15:29</t>
-  </si>
-  <si>
-    <t>21:28:12</t>
-  </si>
-  <si>
-    <t>20:40:40</t>
-  </si>
-  <si>
-    <t>22:16:57</t>
-  </si>
-  <si>
-    <t>00:35:46</t>
-  </si>
-  <si>
-    <t>22:10:09</t>
-  </si>
-  <si>
-    <t>23:48:49</t>
-  </si>
-  <si>
-    <t>23:01:41</t>
-  </si>
-  <si>
-    <t>00:38:06</t>
-  </si>
-  <si>
-    <t>22:14:23</t>
-  </si>
-  <si>
-    <t>23:51:30</t>
-  </si>
-  <si>
-    <t>21:26:54</t>
-  </si>
-  <si>
-    <t>23:04:39</t>
-  </si>
-  <si>
-    <t>22:17:35</t>
-  </si>
-  <si>
-    <t>21:30:18</t>
-  </si>
-  <si>
-    <t>20:42:51</t>
-  </si>
-  <si>
-    <t>22:19:33</t>
+    <t>20:34:44</t>
+  </si>
+  <si>
+    <t>22:12:52</t>
+  </si>
+  <si>
+    <t>21:24:59</t>
+  </si>
+  <si>
+    <t>22:56:22</t>
+  </si>
+  <si>
+    <t>00:33:30</t>
+  </si>
+  <si>
+    <t>22:09:14</t>
+  </si>
+  <si>
+    <t>23:46:32</t>
+  </si>
+  <si>
+    <t>21:22:01</t>
+  </si>
+  <si>
+    <t>22:59:30</t>
+  </si>
+  <si>
+    <t>22:12:23</t>
+  </si>
+  <si>
+    <t>21:25:11</t>
+  </si>
+  <si>
+    <t>20:37:54</t>
+  </si>
+  <si>
+    <t>22:15:06</t>
+  </si>
+  <si>
+    <t>21:27:55</t>
+  </si>
+  <si>
+    <t>22:59:36</t>
+  </si>
+  <si>
+    <t>00:35:16</t>
+  </si>
+  <si>
+    <t>22:12:13</t>
+  </si>
+  <si>
+    <t>23:49:14</t>
+  </si>
+  <si>
+    <t>21:24:35</t>
+  </si>
+  <si>
+    <t>23:02:38</t>
+  </si>
+  <si>
+    <t>22:15:42</t>
+  </si>
+  <si>
+    <t>21:28:30</t>
+  </si>
+  <si>
+    <t>20:41:04</t>
+  </si>
+  <si>
+    <t>22:17:20</t>
+  </si>
+  <si>
+    <t>21:30:49</t>
+  </si>
+  <si>
+    <t>23:01:45</t>
+  </si>
+  <si>
+    <t>00:38:09</t>
+  </si>
+  <si>
+    <t>22:14:28</t>
+  </si>
+  <si>
+    <t>23:51:36</t>
+  </si>
+  <si>
+    <t>21:27:03</t>
+  </si>
+  <si>
+    <t>23:04:48</t>
+  </si>
+  <si>
+    <t>22:17:48</t>
+  </si>
+  <si>
+    <t>21:30:37</t>
+  </si>
+  <si>
+    <t>20:43:14</t>
+  </si>
+  <si>
+    <t>22:19:56</t>
+  </si>
+  <si>
+    <t>21:33:05</t>
+  </si>
+  <si>
+    <t>15°</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>4°</t>
-  </si>
-  <si>
-    <t>15°</t>
-  </si>
-  <si>
     <t>28°</t>
   </si>
   <si>
@@ -394,64 +343,58 @@
     <t>11°</t>
   </si>
   <si>
+    <t>39°</t>
+  </si>
+  <si>
     <t>40°</t>
   </si>
   <si>
     <t>10°</t>
   </si>
   <si>
-    <t>22:06:02</t>
-  </si>
-  <si>
-    <t>23:39:01</t>
-  </si>
-  <si>
-    <t>22:53:48</t>
-  </si>
-  <si>
-    <t>22:08:35</t>
-  </si>
-  <si>
-    <t>23:41:34</t>
-  </si>
-  <si>
-    <t>21:23:21</t>
-  </si>
-  <si>
-    <t>22:56:20</t>
-  </si>
-  <si>
-    <t>22:11:07</t>
-  </si>
-  <si>
-    <t>21:25:54</t>
-  </si>
-  <si>
-    <t>20:40:42</t>
-  </si>
-  <si>
-    <t>22:13:41</t>
+    <t>23°</t>
+  </si>
+  <si>
+    <t>22:53:51</t>
+  </si>
+  <si>
+    <t>22:08:40</t>
+  </si>
+  <si>
+    <t>23:41:39</t>
+  </si>
+  <si>
+    <t>21:23:30</t>
+  </si>
+  <si>
+    <t>22:56:29</t>
+  </si>
+  <si>
+    <t>22:11:19</t>
+  </si>
+  <si>
+    <t>21:26:11</t>
+  </si>
+  <si>
+    <t>22:14:04</t>
+  </si>
+  <si>
+    <t>21:28:59</t>
+  </si>
+  <si>
+    <t>A+B</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>A+B</t>
-  </si>
-  <si>
-    <t>A</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
 </sst>
 </file>
@@ -485,7 +428,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -506,31 +449,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,13 +461,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -595,7 +514,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -628,18 +547,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1043,7 +950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1121,54 +1028,54 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="J2" s="3" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="L2" s="4">
-        <v>-38.6</v>
+        <v>-30.1</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="O2" s="6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P2" s="7">
-        <v>20</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1177,54 +1084,54 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="J3" s="3" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="L3" s="4">
-        <v>-22.6</v>
+        <v>-39</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O3" s="9">
-        <v>66</v>
-      </c>
-      <c r="P3" s="10">
-        <v>62</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>0</v>
-      </c>
-      <c r="R3" s="8">
+        <v>125</v>
+      </c>
+      <c r="O3" s="8">
+        <v>21</v>
+      </c>
+      <c r="P3" s="9">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1233,54 +1140,54 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="J4" s="3" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="L4" s="4">
-        <v>-35.3</v>
+        <v>-23.3</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O4" s="9">
-        <v>63</v>
-      </c>
-      <c r="P4" s="10">
-        <v>61</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="8">
+        <v>124</v>
+      </c>
+      <c r="O4" s="8">
+        <v>30</v>
+      </c>
+      <c r="P4" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>0</v>
+      </c>
+      <c r="R4" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1289,54 +1196,54 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="L5" s="4">
-        <v>-30.1</v>
+        <v>-35.9</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O5" s="9">
-        <v>61</v>
-      </c>
-      <c r="P5" s="11">
-        <v>37</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>0</v>
-      </c>
-      <c r="R5" s="8">
+        <v>126</v>
+      </c>
+      <c r="O5" s="8">
+        <v>39</v>
+      </c>
+      <c r="P5" s="9">
+        <v>5</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>0</v>
+      </c>
+      <c r="R5" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1345,54 +1252,54 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="L6" s="4">
-        <v>-39</v>
+        <v>-15.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O6" s="12">
-        <v>48</v>
-      </c>
-      <c r="P6" s="11">
-        <v>35</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>0</v>
-      </c>
-      <c r="R6" s="8">
+        <v>124</v>
+      </c>
+      <c r="O6" s="6">
+        <v>10</v>
+      </c>
+      <c r="P6" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>0</v>
+      </c>
+      <c r="R6" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1401,54 +1308,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="J7" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-30.7</v>
+      </c>
+      <c r="M7" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-23.3</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="N7" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O7" s="12">
-        <v>25</v>
-      </c>
-      <c r="P7" s="13">
-        <v>10</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>0</v>
-      </c>
-      <c r="R7" s="8">
+        <v>124</v>
+      </c>
+      <c r="O7" s="6">
+        <v>9</v>
+      </c>
+      <c r="P7" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1457,54 +1364,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="L8" s="4">
-        <v>-35.8</v>
+        <v>-24</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O8" s="12">
-        <v>23</v>
-      </c>
-      <c r="P8" s="13">
-        <v>11</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>0</v>
-      </c>
-      <c r="R8" s="8">
+        <v>124</v>
+      </c>
+      <c r="O8" s="6">
+        <v>0</v>
+      </c>
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1513,54 +1420,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H9" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="J9" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-16.2</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-15.4</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="O9" s="6">
-        <v>11</v>
-      </c>
-      <c r="P9" s="14">
-        <v>7</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8">
+        <v>10</v>
+      </c>
+      <c r="P9" s="10">
+        <v>8</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1569,54 +1476,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="L10" s="4">
-        <v>-30.7</v>
+        <v>-7.5</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O10" s="6">
-        <v>9</v>
-      </c>
-      <c r="P10" s="14">
-        <v>7</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>0</v>
-      </c>
-      <c r="R10" s="8">
+        <v>124</v>
+      </c>
+      <c r="O10" s="8">
+        <v>30</v>
+      </c>
+      <c r="P10" s="11">
+        <v>15</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>0</v>
+      </c>
+      <c r="R10" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1625,54 +1532,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="L11" s="4">
-        <v>-24</v>
+        <v>-24.6</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O11" s="6">
-        <v>0</v>
-      </c>
-      <c r="P11" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>0</v>
-      </c>
-      <c r="R11" s="8">
+        <v>124</v>
+      </c>
+      <c r="O11" s="8">
+        <v>19</v>
+      </c>
+      <c r="P11" s="11">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>0</v>
+      </c>
+      <c r="R11" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1681,226 +1588,114 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="L12" s="4">
-        <v>-16.1</v>
+        <v>-16.8</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O12" s="6">
-        <v>0</v>
-      </c>
-      <c r="P12" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>0</v>
-      </c>
-      <c r="R12" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="2">
-        <v>38</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-7.5</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O13" s="12">
-        <v>30</v>
-      </c>
-      <c r="P13" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="15">
-        <v>17</v>
-      </c>
-      <c r="R13" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="2">
-        <v>17</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="L14" s="4">
-        <v>-24.6</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O14" s="12">
-        <v>40</v>
-      </c>
-      <c r="P14" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="14">
-        <v>3</v>
-      </c>
-      <c r="R14" s="8">
+        <v>124</v>
+      </c>
+      <c r="O12" s="8">
+        <v>23</v>
+      </c>
+      <c r="P12" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>0</v>
+      </c>
+      <c r="R12" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A14">
+  <conditionalFormatting sqref="A2:A12">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B14">
+  <conditionalFormatting sqref="B2:B12">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C14">
+  <conditionalFormatting sqref="C2:C12">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D14">
+  <conditionalFormatting sqref="D2:D12">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E14">
+  <conditionalFormatting sqref="E2:E12">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F14">
+  <conditionalFormatting sqref="F2:F12">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G14">
+  <conditionalFormatting sqref="G2:G12">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H14">
+  <conditionalFormatting sqref="H2:H12">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I14">
+  <conditionalFormatting sqref="I2:I12">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J14">
+  <conditionalFormatting sqref="J2:J12">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K14">
+  <conditionalFormatting sqref="K2:K12">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L14">
+  <conditionalFormatting sqref="L2:L12">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1919,12 +1714,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M14">
+  <conditionalFormatting sqref="M2:M12">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N14">
+  <conditionalFormatting sqref="N2:N12">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1941,22 +1736,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O14">
+  <conditionalFormatting sqref="O2:O12">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P14">
+  <conditionalFormatting sqref="P2:P12">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q14">
+  <conditionalFormatting sqref="Q2:Q12">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R14">
+  <conditionalFormatting sqref="R2:R12">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="130">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260712--01</t>
-  </si>
-  <si>
     <t>20260713--01</t>
   </si>
   <si>
@@ -103,13 +100,13 @@
     <t>20260718--01</t>
   </si>
   <si>
-    <t>06:29</t>
+    <t>20260719--01</t>
   </si>
   <si>
     <t>03:31</t>
   </si>
   <si>
-    <t>05:59</t>
+    <t>05:58</t>
   </si>
   <si>
     <t>05:23</t>
@@ -121,19 +118,22 @@
     <t>06:17</t>
   </si>
   <si>
+    <t>06:40</t>
+  </si>
+  <si>
     <t>06:39</t>
   </si>
   <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>04:28</t>
+    <t>06:19</t>
+  </si>
+  <si>
+    <t>04:27</t>
   </si>
   <si>
     <t>05:50</t>
   </si>
   <si>
-    <t>00:44</t>
+    <t>06:30</t>
   </si>
   <si>
     <t>00:00</t>
@@ -145,10 +145,10 @@
     <t>04:04</t>
   </si>
   <si>
-    <t>00:08</t>
-  </si>
-  <si>
-    <t>02:16</t>
+    <t>00:07</t>
+  </si>
+  <si>
+    <t>02:17</t>
   </si>
   <si>
     <t>04:20</t>
@@ -160,9 +160,6 @@
     <t>04:00</t>
   </si>
   <si>
-    <t>22:50:57</t>
-  </si>
-  <si>
     <t>00:28:52</t>
   </si>
   <si>
@@ -175,31 +172,31 @@
     <t>21:16:57</t>
   </si>
   <si>
-    <t>22:54:10</t>
-  </si>
-  <si>
-    <t>22:06:56</t>
+    <t>22:54:11</t>
+  </si>
+  <si>
+    <t>22:06:57</t>
   </si>
   <si>
     <t>21:19:44</t>
   </si>
   <si>
-    <t>20:32:32</t>
-  </si>
-  <si>
-    <t>22:10:15</t>
-  </si>
-  <si>
-    <t>21:22:42</t>
-  </si>
-  <si>
-    <t>22:53:07</t>
+    <t>20:32:33</t>
+  </si>
+  <si>
+    <t>22:10:16</t>
+  </si>
+  <si>
+    <t>21:22:43</t>
+  </si>
+  <si>
+    <t>20:35:15</t>
   </si>
   <si>
     <t>00:31:45</t>
   </si>
   <si>
-    <t>22:06:14</t>
+    <t>22:06:15</t>
   </si>
   <si>
     <t>23:43:51</t>
@@ -208,58 +205,58 @@
     <t>21:19:26</t>
   </si>
   <si>
-    <t>22:56:21</t>
+    <t>22:56:22</t>
   </si>
   <si>
     <t>22:09:03</t>
   </si>
   <si>
-    <t>21:21:51</t>
-  </si>
-  <si>
-    <t>20:34:44</t>
-  </si>
-  <si>
-    <t>22:12:52</t>
-  </si>
-  <si>
-    <t>21:24:59</t>
-  </si>
-  <si>
-    <t>22:56:22</t>
-  </si>
-  <si>
-    <t>00:33:30</t>
+    <t>21:21:52</t>
+  </si>
+  <si>
+    <t>20:34:45</t>
+  </si>
+  <si>
+    <t>22:12:53</t>
+  </si>
+  <si>
+    <t>21:25:00</t>
+  </si>
+  <si>
+    <t>20:37:24</t>
+  </si>
+  <si>
+    <t>00:33:31</t>
   </si>
   <si>
     <t>22:09:14</t>
   </si>
   <si>
-    <t>23:46:32</t>
+    <t>23:46:33</t>
   </si>
   <si>
     <t>21:22:01</t>
   </si>
   <si>
-    <t>22:59:30</t>
-  </si>
-  <si>
-    <t>22:12:23</t>
-  </si>
-  <si>
-    <t>21:25:11</t>
-  </si>
-  <si>
-    <t>20:37:54</t>
-  </si>
-  <si>
-    <t>22:15:06</t>
+    <t>22:59:31</t>
+  </si>
+  <si>
+    <t>22:12:24</t>
+  </si>
+  <si>
+    <t>21:25:12</t>
+  </si>
+  <si>
+    <t>20:37:55</t>
+  </si>
+  <si>
+    <t>22:15:07</t>
   </si>
   <si>
     <t>21:27:55</t>
   </si>
   <si>
-    <t>22:59:36</t>
+    <t>20:40:39</t>
   </si>
   <si>
     <t>00:35:16</t>
@@ -274,13 +271,13 @@
     <t>21:24:35</t>
   </si>
   <si>
-    <t>23:02:38</t>
-  </si>
-  <si>
-    <t>22:15:42</t>
-  </si>
-  <si>
-    <t>21:28:30</t>
+    <t>23:02:39</t>
+  </si>
+  <si>
+    <t>22:15:43</t>
+  </si>
+  <si>
+    <t>21:28:31</t>
   </si>
   <si>
     <t>20:41:04</t>
@@ -289,16 +286,16 @@
     <t>22:17:20</t>
   </si>
   <si>
-    <t>21:30:49</t>
-  </si>
-  <si>
-    <t>23:01:45</t>
+    <t>21:30:50</t>
+  </si>
+  <si>
+    <t>20:43:54</t>
   </si>
   <si>
     <t>00:38:09</t>
   </si>
   <si>
-    <t>22:14:28</t>
+    <t>22:14:29</t>
   </si>
   <si>
     <t>23:51:36</t>
@@ -307,61 +304,61 @@
     <t>21:27:03</t>
   </si>
   <si>
-    <t>23:04:48</t>
-  </si>
-  <si>
-    <t>22:17:48</t>
+    <t>23:04:49</t>
+  </si>
+  <si>
+    <t>22:17:49</t>
   </si>
   <si>
     <t>21:30:37</t>
   </si>
   <si>
-    <t>20:43:14</t>
-  </si>
-  <si>
-    <t>22:19:56</t>
-  </si>
-  <si>
-    <t>21:33:05</t>
+    <t>20:43:15</t>
+  </si>
+  <si>
+    <t>22:19:57</t>
+  </si>
+  <si>
+    <t>21:33:06</t>
+  </si>
+  <si>
+    <t>20:46:01</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>28°</t>
+  </si>
+  <si>
+    <t>1°</t>
+  </si>
+  <si>
+    <t>16°</t>
+  </si>
+  <si>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>39°</t>
+  </si>
+  <si>
+    <t>40°</t>
+  </si>
+  <si>
+    <t>10°</t>
   </si>
   <si>
     <t>15°</t>
   </si>
   <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>28°</t>
-  </si>
-  <si>
-    <t>1°</t>
-  </si>
-  <si>
-    <t>16°</t>
-  </si>
-  <si>
-    <t>11°</t>
-  </si>
-  <si>
-    <t>39°</t>
-  </si>
-  <si>
-    <t>40°</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
     <t>23°</t>
   </si>
   <si>
-    <t>22:53:51</t>
-  </si>
-  <si>
-    <t>22:08:40</t>
-  </si>
-  <si>
-    <t>23:41:39</t>
+    <t>22:08:41</t>
+  </si>
+  <si>
+    <t>23:41:40</t>
   </si>
   <si>
     <t>21:23:30</t>
@@ -370,31 +367,43 @@
     <t>22:56:29</t>
   </si>
   <si>
-    <t>22:11:19</t>
-  </si>
-  <si>
-    <t>21:26:11</t>
-  </si>
-  <si>
-    <t>22:14:04</t>
-  </si>
-  <si>
-    <t>21:28:59</t>
+    <t>22:11:20</t>
+  </si>
+  <si>
+    <t>21:26:12</t>
+  </si>
+  <si>
+    <t>20:41:05</t>
+  </si>
+  <si>
+    <t>22:14:05</t>
+  </si>
+  <si>
+    <t>21:29:00</t>
+  </si>
+  <si>
+    <t>20:43:58</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>B</t>
+    <t>A</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
@@ -428,7 +437,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -449,6 +458,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -462,18 +477,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -514,7 +517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -544,9 +547,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1028,13 +1028,13 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>48</v>
@@ -1055,27 +1055,27 @@
         <v>103</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="L2" s="4">
-        <v>-30.1</v>
+        <v>-39</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O2" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="7">
+        <v>19</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1084,13 +1084,13 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>49</v>
@@ -1111,27 +1111,27 @@
         <v>104</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="L3" s="4">
-        <v>-39</v>
+        <v>-23.3</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="O3" s="8">
-        <v>21</v>
-      </c>
-      <c r="P3" s="9">
-        <v>3</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="7">
+        <v>127</v>
+      </c>
+      <c r="O3" s="9">
+        <v>20</v>
+      </c>
+      <c r="P3" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>0</v>
+      </c>
+      <c r="R3" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1140,13 +1140,13 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>50</v>
@@ -1170,24 +1170,24 @@
         <v>114</v>
       </c>
       <c r="L4" s="4">
-        <v>-23.3</v>
+        <v>-35.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="O4" s="8">
-        <v>30</v>
-      </c>
-      <c r="P4" s="9">
-        <v>4</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>0</v>
-      </c>
-      <c r="R4" s="7">
+        <v>128</v>
+      </c>
+      <c r="O4" s="9">
+        <v>22</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1196,13 +1196,13 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>51</v>
@@ -1226,24 +1226,24 @@
         <v>115</v>
       </c>
       <c r="L5" s="4">
-        <v>-35.9</v>
+        <v>-15.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="O5" s="8">
-        <v>39</v>
-      </c>
-      <c r="P5" s="9">
-        <v>5</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="7">
+        <v>127</v>
+      </c>
+      <c r="O5" s="6">
+        <v>0</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="R5" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1252,13 +1252,13 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>52</v>
@@ -1282,24 +1282,24 @@
         <v>116</v>
       </c>
       <c r="L6" s="4">
-        <v>-15.5</v>
+        <v>-30.7</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="O6" s="6">
-        <v>10</v>
-      </c>
-      <c r="P6" s="9">
-        <v>4</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="7">
+        <v>0</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1308,13 +1308,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>53</v>
@@ -1338,24 +1338,24 @@
         <v>117</v>
       </c>
       <c r="L7" s="4">
-        <v>-30.7</v>
+        <v>-24</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="O7" s="6">
-        <v>9</v>
-      </c>
-      <c r="P7" s="9">
-        <v>4</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-      <c r="R7" s="7">
+        <v>0</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
+      <c r="R7" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1364,13 +1364,13 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>54</v>
@@ -1394,24 +1394,24 @@
         <v>118</v>
       </c>
       <c r="L8" s="4">
-        <v>-24</v>
+        <v>-16.2</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-      <c r="R8" s="7">
+        <v>14</v>
+      </c>
+      <c r="P8" s="10">
+        <v>7</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>4</v>
+      </c>
+      <c r="R8" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1420,13 +1420,13 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>55</v>
@@ -1450,24 +1450,24 @@
         <v>119</v>
       </c>
       <c r="L9" s="4">
-        <v>-16.2</v>
+        <v>-7.5</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="O9" s="6">
-        <v>10</v>
-      </c>
-      <c r="P9" s="10">
-        <v>8</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>0</v>
-      </c>
-      <c r="R9" s="7">
+        <v>3</v>
+      </c>
+      <c r="P9" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1476,13 +1476,13 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>56</v>
@@ -1503,27 +1503,27 @@
         <v>111</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="L10" s="4">
-        <v>-7.5</v>
+        <v>-24.6</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="O10" s="8">
-        <v>30</v>
-      </c>
-      <c r="P10" s="11">
-        <v>15</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>0</v>
-      </c>
-      <c r="R10" s="7">
+        <v>127</v>
+      </c>
+      <c r="O10" s="6">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1532,13 +1532,13 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>57</v>
@@ -1556,30 +1556,30 @@
         <v>101</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L11" s="4">
-        <v>-24.6</v>
+        <v>-16.8</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="O11" s="8">
-        <v>19</v>
-      </c>
-      <c r="P11" s="11">
-        <v>13</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>0</v>
-      </c>
-      <c r="R11" s="7">
+        <v>127</v>
+      </c>
+      <c r="O11" s="6">
+        <v>8</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>2</v>
+      </c>
+      <c r="R11" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1588,13 +1588,13 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>58</v>
@@ -1612,30 +1612,30 @@
         <v>102</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L12" s="4">
-        <v>-16.8</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="O12" s="8">
-        <v>23</v>
-      </c>
-      <c r="P12" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>0</v>
-      </c>
-      <c r="R12" s="7">
+        <v>129</v>
+      </c>
+      <c r="O12" s="6">
+        <v>0</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8">
         <v>0</v>
       </c>
     </row>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="98">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260713--01</t>
-  </si>
-  <si>
-    <t>20260713--02</t>
-  </si>
-  <si>
-    <t>20260713--03</t>
-  </si>
-  <si>
     <t>20260714--01</t>
   </si>
   <si>
@@ -103,235 +94,163 @@
     <t>20260719--01</t>
   </si>
   <si>
-    <t>03:31</t>
-  </si>
-  <si>
-    <t>05:58</t>
-  </si>
-  <si>
-    <t>05:23</t>
-  </si>
-  <si>
-    <t>05:09</t>
+    <t>05:08</t>
   </si>
   <si>
     <t>06:17</t>
   </si>
   <si>
-    <t>06:40</t>
-  </si>
-  <si>
     <t>06:39</t>
   </si>
   <si>
     <t>06:19</t>
   </si>
   <si>
-    <t>04:27</t>
-  </si>
-  <si>
-    <t>05:50</t>
+    <t>04:29</t>
+  </si>
+  <si>
+    <t>05:51</t>
   </si>
   <si>
     <t>06:30</t>
   </si>
   <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>02:26</t>
-  </si>
-  <si>
-    <t>04:04</t>
-  </si>
-  <si>
-    <t>00:07</t>
-  </si>
-  <si>
-    <t>02:17</t>
+    <t>04:03</t>
+  </si>
+  <si>
+    <t>00:08</t>
+  </si>
+  <si>
+    <t>02:16</t>
   </si>
   <si>
     <t>04:20</t>
   </si>
   <si>
-    <t>01:12</t>
-  </si>
-  <si>
-    <t>04:00</t>
-  </si>
-  <si>
-    <t>00:28:52</t>
-  </si>
-  <si>
-    <t>22:03:58</t>
-  </si>
-  <si>
-    <t>23:41:28</t>
-  </si>
-  <si>
-    <t>21:16:57</t>
-  </si>
-  <si>
-    <t>22:54:11</t>
-  </si>
-  <si>
-    <t>22:06:57</t>
-  </si>
-  <si>
-    <t>21:19:44</t>
-  </si>
-  <si>
-    <t>20:32:33</t>
-  </si>
-  <si>
-    <t>22:10:16</t>
-  </si>
-  <si>
-    <t>21:22:43</t>
-  </si>
-  <si>
-    <t>20:35:15</t>
-  </si>
-  <si>
-    <t>00:31:45</t>
-  </si>
-  <si>
-    <t>22:06:15</t>
-  </si>
-  <si>
-    <t>23:43:51</t>
-  </si>
-  <si>
-    <t>21:19:26</t>
-  </si>
-  <si>
-    <t>22:56:22</t>
-  </si>
-  <si>
-    <t>22:09:03</t>
-  </si>
-  <si>
-    <t>21:21:52</t>
-  </si>
-  <si>
-    <t>20:34:45</t>
-  </si>
-  <si>
-    <t>22:12:53</t>
-  </si>
-  <si>
-    <t>21:25:00</t>
-  </si>
-  <si>
-    <t>20:37:24</t>
-  </si>
-  <si>
-    <t>00:33:31</t>
-  </si>
-  <si>
-    <t>22:09:14</t>
-  </si>
-  <si>
-    <t>23:46:33</t>
-  </si>
-  <si>
-    <t>21:22:01</t>
-  </si>
-  <si>
-    <t>22:59:31</t>
-  </si>
-  <si>
-    <t>22:12:24</t>
-  </si>
-  <si>
-    <t>21:25:12</t>
-  </si>
-  <si>
-    <t>20:37:55</t>
-  </si>
-  <si>
-    <t>22:15:07</t>
-  </si>
-  <si>
-    <t>21:27:55</t>
-  </si>
-  <si>
-    <t>20:40:39</t>
-  </si>
-  <si>
-    <t>00:35:16</t>
-  </si>
-  <si>
-    <t>22:12:13</t>
-  </si>
-  <si>
-    <t>23:49:14</t>
-  </si>
-  <si>
-    <t>21:24:35</t>
-  </si>
-  <si>
-    <t>23:02:39</t>
-  </si>
-  <si>
-    <t>22:15:43</t>
-  </si>
-  <si>
-    <t>21:28:31</t>
-  </si>
-  <si>
-    <t>20:41:04</t>
-  </si>
-  <si>
-    <t>22:17:20</t>
-  </si>
-  <si>
-    <t>21:30:50</t>
-  </si>
-  <si>
-    <t>20:43:54</t>
-  </si>
-  <si>
-    <t>00:38:09</t>
-  </si>
-  <si>
-    <t>22:14:29</t>
-  </si>
-  <si>
-    <t>23:51:36</t>
-  </si>
-  <si>
-    <t>21:27:03</t>
-  </si>
-  <si>
-    <t>23:04:49</t>
-  </si>
-  <si>
-    <t>22:17:49</t>
-  </si>
-  <si>
-    <t>21:30:37</t>
-  </si>
-  <si>
-    <t>20:43:15</t>
-  </si>
-  <si>
-    <t>22:19:57</t>
-  </si>
-  <si>
-    <t>21:33:06</t>
-  </si>
-  <si>
-    <t>20:46:01</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>28°</t>
-  </si>
-  <si>
-    <t>1°</t>
+    <t>01:13</t>
+  </si>
+  <si>
+    <t>04:01</t>
+  </si>
+  <si>
+    <t>21:16:55</t>
+  </si>
+  <si>
+    <t>22:54:09</t>
+  </si>
+  <si>
+    <t>22:06:53</t>
+  </si>
+  <si>
+    <t>21:19:38</t>
+  </si>
+  <si>
+    <t>20:32:24</t>
+  </si>
+  <si>
+    <t>22:10:07</t>
+  </si>
+  <si>
+    <t>21:22:30</t>
+  </si>
+  <si>
+    <t>20:34:58</t>
+  </si>
+  <si>
+    <t>21:19:25</t>
+  </si>
+  <si>
+    <t>22:56:20</t>
+  </si>
+  <si>
+    <t>22:09:00</t>
+  </si>
+  <si>
+    <t>21:21:46</t>
+  </si>
+  <si>
+    <t>20:34:36</t>
+  </si>
+  <si>
+    <t>22:12:43</t>
+  </si>
+  <si>
+    <t>21:24:47</t>
+  </si>
+  <si>
+    <t>20:37:07</t>
+  </si>
+  <si>
+    <t>21:21:59</t>
+  </si>
+  <si>
+    <t>22:59:29</t>
+  </si>
+  <si>
+    <t>22:12:20</t>
+  </si>
+  <si>
+    <t>21:25:06</t>
+  </si>
+  <si>
+    <t>20:37:46</t>
+  </si>
+  <si>
+    <t>22:14:58</t>
+  </si>
+  <si>
+    <t>21:27:43</t>
+  </si>
+  <si>
+    <t>20:40:22</t>
+  </si>
+  <si>
+    <t>21:24:33</t>
+  </si>
+  <si>
+    <t>23:02:37</t>
+  </si>
+  <si>
+    <t>22:15:39</t>
+  </si>
+  <si>
+    <t>21:28:25</t>
+  </si>
+  <si>
+    <t>20:40:55</t>
+  </si>
+  <si>
+    <t>22:17:12</t>
+  </si>
+  <si>
+    <t>21:30:38</t>
+  </si>
+  <si>
+    <t>20:43:37</t>
+  </si>
+  <si>
+    <t>21:27:01</t>
+  </si>
+  <si>
+    <t>23:04:47</t>
+  </si>
+  <si>
+    <t>22:17:45</t>
+  </si>
+  <si>
+    <t>21:30:31</t>
+  </si>
+  <si>
+    <t>20:43:06</t>
+  </si>
+  <si>
+    <t>22:19:48</t>
+  </si>
+  <si>
+    <t>21:32:53</t>
+  </si>
+  <si>
+    <t>20:45:45</t>
   </si>
   <si>
     <t>16°</t>
@@ -355,37 +274,28 @@
     <t>23°</t>
   </si>
   <si>
-    <t>22:08:41</t>
-  </si>
-  <si>
-    <t>23:41:40</t>
-  </si>
-  <si>
-    <t>21:23:30</t>
-  </si>
-  <si>
-    <t>22:56:29</t>
-  </si>
-  <si>
-    <t>22:11:20</t>
-  </si>
-  <si>
-    <t>21:26:12</t>
-  </si>
-  <si>
-    <t>20:41:05</t>
-  </si>
-  <si>
-    <t>22:14:05</t>
-  </si>
-  <si>
-    <t>21:29:00</t>
-  </si>
-  <si>
-    <t>20:43:58</t>
-  </si>
-  <si>
-    <t>B</t>
+    <t>21:23:28</t>
+  </si>
+  <si>
+    <t>22:56:28</t>
+  </si>
+  <si>
+    <t>22:11:16</t>
+  </si>
+  <si>
+    <t>21:26:06</t>
+  </si>
+  <si>
+    <t>20:40:56</t>
+  </si>
+  <si>
+    <t>22:13:56</t>
+  </si>
+  <si>
+    <t>21:28:48</t>
+  </si>
+  <si>
+    <t>20:43:42</t>
   </si>
   <si>
     <t>A+B</t>
@@ -394,13 +304,7 @@
     <t>A</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>1</t>
@@ -437,7 +341,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -458,12 +362,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -476,7 +374,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -517,7 +415,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -544,9 +442,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -950,7 +845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1028,54 +923,54 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="L2" s="4">
-        <v>-39</v>
+        <v>-15.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="O2" s="6">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="P2" s="7">
-        <v>19</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1084,54 +979,54 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="L3" s="4">
-        <v>-23.3</v>
+        <v>-30.7</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="O3" s="9">
-        <v>20</v>
-      </c>
-      <c r="P3" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>0</v>
-      </c>
-      <c r="R3" s="8">
+        <v>96</v>
+      </c>
+      <c r="O3" s="6">
+        <v>0</v>
+      </c>
+      <c r="P3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1140,54 +1035,54 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-24</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-35.9</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="N4" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="O4" s="9">
-        <v>22</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="8">
+        <v>96</v>
+      </c>
+      <c r="O4" s="8">
+        <v>39</v>
+      </c>
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>39</v>
+      </c>
+      <c r="R4" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1196,54 +1091,54 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="L5" s="4">
-        <v>-15.5</v>
+        <v>-16.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="O5" s="6">
-        <v>0</v>
-      </c>
-      <c r="P5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>0</v>
-      </c>
-      <c r="R5" s="8">
+        <v>2</v>
+      </c>
+      <c r="P5" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>0</v>
+      </c>
+      <c r="R5" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1252,54 +1147,54 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="L6" s="4">
-        <v>-30.7</v>
+        <v>-7.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="O6" s="6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>0</v>
-      </c>
-      <c r="R6" s="8">
+        <v>4</v>
+      </c>
+      <c r="P6" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>2</v>
+      </c>
+      <c r="R6" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1308,54 +1203,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="F7" s="3" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="L7" s="4">
-        <v>-24</v>
+        <v>-24.6</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="O7" s="6">
-        <v>0</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>0</v>
-      </c>
-      <c r="R7" s="8">
+        <v>2</v>
+      </c>
+      <c r="P7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>2</v>
+      </c>
+      <c r="R7" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1364,54 +1259,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="F8" s="3" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="L8" s="4">
-        <v>-16.2</v>
+        <v>-16.8</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="O8" s="6">
-        <v>14</v>
-      </c>
-      <c r="P8" s="10">
-        <v>7</v>
-      </c>
-      <c r="Q8" s="10">
-        <v>4</v>
-      </c>
-      <c r="R8" s="8">
+        <v>0</v>
+      </c>
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1420,282 +1315,114 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="L9" s="4">
-        <v>-7.5</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O9" s="6">
-        <v>3</v>
-      </c>
-      <c r="P9" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="2">
-        <v>17</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="L10" s="4">
-        <v>-24.6</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="O10" s="6">
-        <v>0</v>
-      </c>
-      <c r="P10" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>0</v>
-      </c>
-      <c r="R10" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="O9" s="8">
         <v>27</v>
       </c>
-      <c r="B11" s="2">
-        <v>28</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="L11" s="4">
-        <v>-16.8</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="O11" s="6">
-        <v>8</v>
-      </c>
-      <c r="P11" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>2</v>
-      </c>
-      <c r="R11" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="2">
-        <v>50</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="L12" s="4">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O12" s="6">
-        <v>0</v>
-      </c>
-      <c r="P12" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>0</v>
-      </c>
-      <c r="R12" s="8">
+      <c r="P9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A12">
+  <conditionalFormatting sqref="A2:A9">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B12">
+  <conditionalFormatting sqref="B2:B9">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C12">
+  <conditionalFormatting sqref="C2:C9">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D12">
+  <conditionalFormatting sqref="D2:D9">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E12">
+  <conditionalFormatting sqref="E2:E9">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F12">
+  <conditionalFormatting sqref="F2:F9">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G12">
+  <conditionalFormatting sqref="G2:G9">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H12">
+  <conditionalFormatting sqref="H2:H9">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I12">
+  <conditionalFormatting sqref="I2:I9">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J12">
+  <conditionalFormatting sqref="J2:J9">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K12">
+  <conditionalFormatting sqref="K2:K9">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L12">
+  <conditionalFormatting sqref="L2:L9">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1714,12 +1441,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M12">
+  <conditionalFormatting sqref="M2:M9">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N12">
+  <conditionalFormatting sqref="N2:N9">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1736,22 +1463,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O12">
+  <conditionalFormatting sqref="O2:O9">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P12">
+  <conditionalFormatting sqref="P2:P9">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q12">
+  <conditionalFormatting sqref="Q2:Q9">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R12">
+  <conditionalFormatting sqref="R2:R9">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="88">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260714--01</t>
-  </si>
-  <si>
-    <t>20260714--02</t>
-  </si>
-  <si>
     <t>20260715--01</t>
   </si>
   <si>
@@ -94,10 +88,7 @@
     <t>20260719--01</t>
   </si>
   <si>
-    <t>05:08</t>
-  </si>
-  <si>
-    <t>06:17</t>
+    <t>20260721--01</t>
   </si>
   <si>
     <t>06:39</t>
@@ -106,7 +97,7 @@
     <t>06:19</t>
   </si>
   <si>
-    <t>04:29</t>
+    <t>04:27</t>
   </si>
   <si>
     <t>05:51</t>
@@ -115,148 +106,124 @@
     <t>06:30</t>
   </si>
   <si>
-    <t>04:03</t>
-  </si>
-  <si>
-    <t>00:08</t>
-  </si>
-  <si>
-    <t>02:16</t>
-  </si>
-  <si>
-    <t>04:20</t>
-  </si>
-  <si>
-    <t>01:13</t>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>02:17</t>
+  </si>
+  <si>
+    <t>04:19</t>
+  </si>
+  <si>
+    <t>01:12</t>
   </si>
   <si>
     <t>04:01</t>
   </si>
   <si>
-    <t>21:16:55</t>
-  </si>
-  <si>
-    <t>22:54:09</t>
-  </si>
-  <si>
-    <t>22:06:53</t>
-  </si>
-  <si>
-    <t>21:19:38</t>
-  </si>
-  <si>
-    <t>20:32:24</t>
-  </si>
-  <si>
-    <t>22:10:07</t>
-  </si>
-  <si>
-    <t>21:22:30</t>
-  </si>
-  <si>
-    <t>20:34:58</t>
-  </si>
-  <si>
-    <t>21:19:25</t>
-  </si>
-  <si>
-    <t>22:56:20</t>
-  </si>
-  <si>
-    <t>22:09:00</t>
-  </si>
-  <si>
-    <t>21:21:46</t>
-  </si>
-  <si>
-    <t>20:34:36</t>
-  </si>
-  <si>
-    <t>22:12:43</t>
-  </si>
-  <si>
-    <t>21:24:47</t>
-  </si>
-  <si>
-    <t>20:37:07</t>
-  </si>
-  <si>
-    <t>21:21:59</t>
-  </si>
-  <si>
-    <t>22:59:29</t>
-  </si>
-  <si>
-    <t>22:12:20</t>
-  </si>
-  <si>
-    <t>21:25:06</t>
-  </si>
-  <si>
-    <t>20:37:46</t>
-  </si>
-  <si>
-    <t>22:14:58</t>
-  </si>
-  <si>
-    <t>21:27:43</t>
-  </si>
-  <si>
-    <t>20:40:22</t>
-  </si>
-  <si>
-    <t>21:24:33</t>
-  </si>
-  <si>
-    <t>23:02:37</t>
-  </si>
-  <si>
-    <t>22:15:39</t>
-  </si>
-  <si>
-    <t>21:28:25</t>
-  </si>
-  <si>
-    <t>20:40:55</t>
-  </si>
-  <si>
-    <t>22:17:12</t>
-  </si>
-  <si>
-    <t>21:30:38</t>
-  </si>
-  <si>
-    <t>20:43:37</t>
-  </si>
-  <si>
-    <t>21:27:01</t>
-  </si>
-  <si>
-    <t>23:04:47</t>
-  </si>
-  <si>
-    <t>22:17:45</t>
-  </si>
-  <si>
-    <t>21:30:31</t>
-  </si>
-  <si>
-    <t>20:43:06</t>
-  </si>
-  <si>
-    <t>22:19:48</t>
-  </si>
-  <si>
-    <t>21:32:53</t>
-  </si>
-  <si>
-    <t>20:45:45</t>
-  </si>
-  <si>
-    <t>16°</t>
-  </si>
-  <si>
-    <t>11°</t>
+    <t>22:06:56</t>
+  </si>
+  <si>
+    <t>21:19:44</t>
+  </si>
+  <si>
+    <t>20:32:33</t>
+  </si>
+  <si>
+    <t>22:10:16</t>
+  </si>
+  <si>
+    <t>21:22:44</t>
+  </si>
+  <si>
+    <t>20:35:16</t>
+  </si>
+  <si>
+    <t>20:38:27</t>
+  </si>
+  <si>
+    <t>22:09:03</t>
+  </si>
+  <si>
+    <t>21:21:52</t>
+  </si>
+  <si>
+    <t>20:34:45</t>
+  </si>
+  <si>
+    <t>22:12:53</t>
+  </si>
+  <si>
+    <t>21:25:00</t>
+  </si>
+  <si>
+    <t>20:37:25</t>
+  </si>
+  <si>
+    <t>20:41:31</t>
+  </si>
+  <si>
+    <t>22:12:23</t>
+  </si>
+  <si>
+    <t>21:25:12</t>
+  </si>
+  <si>
+    <t>20:37:55</t>
+  </si>
+  <si>
+    <t>22:15:07</t>
+  </si>
+  <si>
+    <t>21:27:56</t>
+  </si>
+  <si>
+    <t>20:40:41</t>
+  </si>
+  <si>
+    <t>20:43:01</t>
+  </si>
+  <si>
+    <t>22:15:42</t>
+  </si>
+  <si>
+    <t>21:28:31</t>
+  </si>
+  <si>
+    <t>20:41:04</t>
+  </si>
+  <si>
+    <t>22:17:20</t>
+  </si>
+  <si>
+    <t>21:30:51</t>
+  </si>
+  <si>
+    <t>20:43:55</t>
+  </si>
+  <si>
+    <t>20:44:31</t>
+  </si>
+  <si>
+    <t>22:17:48</t>
+  </si>
+  <si>
+    <t>21:30:37</t>
+  </si>
+  <si>
+    <t>20:43:15</t>
+  </si>
+  <si>
+    <t>22:19:57</t>
+  </si>
+  <si>
+    <t>21:33:07</t>
+  </si>
+  <si>
+    <t>20:46:03</t>
+  </si>
+  <si>
+    <t>20:47:34</t>
   </si>
   <si>
     <t>39°</t>
@@ -274,28 +241,28 @@
     <t>23°</t>
   </si>
   <si>
-    <t>21:23:28</t>
-  </si>
-  <si>
-    <t>22:56:28</t>
-  </si>
-  <si>
-    <t>22:11:16</t>
-  </si>
-  <si>
-    <t>21:26:06</t>
-  </si>
-  <si>
-    <t>20:40:56</t>
-  </si>
-  <si>
-    <t>22:13:56</t>
-  </si>
-  <si>
-    <t>21:28:48</t>
-  </si>
-  <si>
-    <t>20:43:42</t>
+    <t>2°</t>
+  </si>
+  <si>
+    <t>22:11:20</t>
+  </si>
+  <si>
+    <t>21:26:11</t>
+  </si>
+  <si>
+    <t>20:41:05</t>
+  </si>
+  <si>
+    <t>22:14:05</t>
+  </si>
+  <si>
+    <t>21:29:01</t>
+  </si>
+  <si>
+    <t>20:43:59</t>
+  </si>
+  <si>
+    <t>20:47:03</t>
   </si>
   <si>
     <t>A+B</t>
@@ -308,6 +275,9 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
 </sst>
 </file>
@@ -368,13 +338,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -845,7 +815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -923,52 +893,52 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="J2" s="3" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="L2" s="4">
-        <v>-15.5</v>
+        <v>-24</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="O2" s="6">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="7">
-        <v>0</v>
+      <c r="Q2" s="8">
+        <v>11</v>
       </c>
       <c r="R2" s="7">
         <v>0</v>
@@ -979,52 +949,52 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="J3" s="3" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="L3" s="4">
-        <v>-30.7</v>
+        <v>-16.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="O3" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
       <c r="Q3" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R3" s="7">
         <v>0</v>
@@ -1035,52 +1005,52 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="J4" s="3" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="L4" s="4">
-        <v>-24</v>
+        <v>-7.5</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="O4" s="8">
-        <v>39</v>
+        <v>86</v>
+      </c>
+      <c r="O4" s="6">
+        <v>1</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
       </c>
-      <c r="Q4" s="9">
-        <v>39</v>
+      <c r="Q4" s="7">
+        <v>1</v>
       </c>
       <c r="R4" s="7">
         <v>0</v>
@@ -1091,52 +1061,52 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="L5" s="4">
-        <v>-16.1</v>
+        <v>-24.6</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="O5" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P5" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>4</v>
       </c>
       <c r="R5" s="7">
         <v>0</v>
@@ -1147,52 +1117,52 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="J6" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-16.9</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-7.5</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="N6" s="1" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="O6" s="6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P6" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R6" s="7">
         <v>0</v>
@@ -1203,43 +1173,43 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="J7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="M7" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-24.6</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="N7" s="1" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="O7" s="6">
         <v>2</v>
@@ -1248,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R7" s="7">
         <v>0</v>
@@ -1259,43 +1229,43 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="L8" s="4">
-        <v>-16.8</v>
+        <v>-8.9</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="O8" s="6">
         <v>0</v>
@@ -1307,122 +1277,66 @@
         <v>0</v>
       </c>
       <c r="R8" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="2">
-        <v>50</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="O9" s="8">
-        <v>27</v>
-      </c>
-      <c r="P9" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>0</v>
-      </c>
-      <c r="R9" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A9">
+  <conditionalFormatting sqref="A2:A8">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B9">
+  <conditionalFormatting sqref="B2:B8">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C9">
+  <conditionalFormatting sqref="C2:C8">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
+  <conditionalFormatting sqref="D2:D8">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E9">
+  <conditionalFormatting sqref="E2:E8">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
+  <conditionalFormatting sqref="F2:F8">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G9">
+  <conditionalFormatting sqref="G2:G8">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H9">
+  <conditionalFormatting sqref="H2:H8">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I9">
+  <conditionalFormatting sqref="I2:I8">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J9">
+  <conditionalFormatting sqref="J2:J8">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K9">
+  <conditionalFormatting sqref="K2:K8">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L9">
+  <conditionalFormatting sqref="L2:L8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1441,12 +1355,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M9">
+  <conditionalFormatting sqref="M2:M8">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N9">
+  <conditionalFormatting sqref="N2:N8">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1463,22 +1377,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O9">
+  <conditionalFormatting sqref="O2:O8">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P9">
+  <conditionalFormatting sqref="P2:P8">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q9">
+  <conditionalFormatting sqref="Q2:Q8">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R9">
+  <conditionalFormatting sqref="R2:R8">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="79">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260715--01</t>
-  </si>
-  <si>
     <t>20260716--01</t>
   </si>
   <si>
@@ -91,7 +88,7 @@
     <t>20260721--01</t>
   </si>
   <si>
-    <t>06:39</t>
+    <t>06:38</t>
   </si>
   <si>
     <t>06:19</t>
@@ -106,22 +103,16 @@
     <t>06:30</t>
   </si>
   <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>02:17</t>
+    <t>02:59</t>
   </si>
   <si>
     <t>04:19</t>
   </si>
   <si>
-    <t>01:12</t>
-  </si>
-  <si>
-    <t>04:01</t>
-  </si>
-  <si>
-    <t>22:06:56</t>
+    <t>01:11</t>
+  </si>
+  <si>
+    <t>04:00</t>
   </si>
   <si>
     <t>21:19:44</t>
@@ -133,16 +124,13 @@
     <t>22:10:16</t>
   </si>
   <si>
-    <t>21:22:44</t>
-  </si>
-  <si>
-    <t>20:35:16</t>
-  </si>
-  <si>
-    <t>20:38:27</t>
-  </si>
-  <si>
-    <t>22:09:03</t>
+    <t>21:22:42</t>
+  </si>
+  <si>
+    <t>20:35:14</t>
+  </si>
+  <si>
+    <t>20:38:23</t>
   </si>
   <si>
     <t>21:21:52</t>
@@ -154,16 +142,13 @@
     <t>22:12:53</t>
   </si>
   <si>
-    <t>21:25:00</t>
-  </si>
-  <si>
-    <t>20:37:25</t>
-  </si>
-  <si>
-    <t>20:41:31</t>
-  </si>
-  <si>
-    <t>22:12:23</t>
+    <t>21:24:59</t>
+  </si>
+  <si>
+    <t>20:37:23</t>
+  </si>
+  <si>
+    <t>20:41:27</t>
   </si>
   <si>
     <t>21:25:12</t>
@@ -172,22 +157,19 @@
     <t>20:37:55</t>
   </si>
   <si>
-    <t>22:15:07</t>
-  </si>
-  <si>
-    <t>21:27:56</t>
-  </si>
-  <si>
-    <t>20:40:41</t>
-  </si>
-  <si>
-    <t>20:43:01</t>
-  </si>
-  <si>
-    <t>22:15:42</t>
-  </si>
-  <si>
-    <t>21:28:31</t>
+    <t>22:15:06</t>
+  </si>
+  <si>
+    <t>21:27:55</t>
+  </si>
+  <si>
+    <t>20:40:39</t>
+  </si>
+  <si>
+    <t>20:42:56</t>
+  </si>
+  <si>
+    <t>21:28:30</t>
   </si>
   <si>
     <t>20:41:04</t>
@@ -196,16 +178,13 @@
     <t>22:17:20</t>
   </si>
   <si>
-    <t>21:30:51</t>
-  </si>
-  <si>
-    <t>20:43:55</t>
-  </si>
-  <si>
-    <t>20:44:31</t>
-  </si>
-  <si>
-    <t>22:17:48</t>
+    <t>21:30:50</t>
+  </si>
+  <si>
+    <t>20:43:53</t>
+  </si>
+  <si>
+    <t>20:44:26</t>
   </si>
   <si>
     <t>21:30:37</t>
@@ -214,19 +193,16 @@
     <t>20:43:15</t>
   </si>
   <si>
-    <t>22:19:57</t>
-  </si>
-  <si>
-    <t>21:33:07</t>
-  </si>
-  <si>
-    <t>20:46:03</t>
-  </si>
-  <si>
-    <t>20:47:34</t>
-  </si>
-  <si>
-    <t>39°</t>
+    <t>22:19:56</t>
+  </si>
+  <si>
+    <t>21:33:05</t>
+  </si>
+  <si>
+    <t>20:46:01</t>
+  </si>
+  <si>
+    <t>20:47:29</t>
   </si>
   <si>
     <t>40°</t>
@@ -244,25 +220,22 @@
     <t>2°</t>
   </si>
   <si>
-    <t>22:11:20</t>
-  </si>
-  <si>
     <t>21:26:11</t>
   </si>
   <si>
     <t>20:41:05</t>
   </si>
   <si>
-    <t>22:14:05</t>
-  </si>
-  <si>
-    <t>21:29:01</t>
-  </si>
-  <si>
-    <t>20:43:59</t>
-  </si>
-  <si>
-    <t>20:47:03</t>
+    <t>22:14:04</t>
+  </si>
+  <si>
+    <t>21:28:59</t>
+  </si>
+  <si>
+    <t>20:43:57</t>
+  </si>
+  <si>
+    <t>20:46:59</t>
   </si>
   <si>
     <t>A+B</t>
@@ -311,7 +284,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -339,12 +312,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -385,7 +352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -409,9 +376,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -815,7 +779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -893,52 +857,52 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="K2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-16.2</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="L2" s="4">
-        <v>-24</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="O2" s="6">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="8">
-        <v>11</v>
+      <c r="Q2" s="7">
+        <v>2</v>
       </c>
       <c r="R2" s="7">
         <v>0</v>
@@ -949,52 +913,52 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="K3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-7.5</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="L3" s="4">
-        <v>-16.2</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="O3" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
       <c r="Q3" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R3" s="7">
         <v>0</v>
@@ -1005,52 +969,52 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="L4" s="4">
-        <v>-7.5</v>
+        <v>-24.6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="O4" s="6">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
       </c>
-      <c r="Q4" s="7">
-        <v>1</v>
+      <c r="Q4" s="8">
+        <v>12</v>
       </c>
       <c r="R4" s="7">
         <v>0</v>
@@ -1061,52 +1025,52 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="L5" s="4">
-        <v>-24.6</v>
+        <v>-16.8</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="O5" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
       </c>
-      <c r="Q5" s="9">
-        <v>4</v>
+      <c r="Q5" s="7">
+        <v>1</v>
       </c>
       <c r="R5" s="7">
         <v>0</v>
@@ -1117,43 +1081,43 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="L6" s="4">
-        <v>-16.9</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="O6" s="6">
         <v>0</v>
@@ -1173,7 +1137,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>29</v>
@@ -1182,37 +1146,37 @@
         <v>29</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="L7" s="4">
-        <v>-8.199999999999999</v>
+        <v>-8.9</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="O7" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P7" s="7">
         <v>0</v>
@@ -1221,122 +1185,66 @@
         <v>0</v>
       </c>
       <c r="R7" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="2">
-        <v>12</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="L8" s="4">
-        <v>-8.9</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-      <c r="R8" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A8">
+  <conditionalFormatting sqref="A2:A7">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B8">
+  <conditionalFormatting sqref="B2:B7">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C8">
+  <conditionalFormatting sqref="C2:C7">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D8">
+  <conditionalFormatting sqref="D2:D7">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E8">
+  <conditionalFormatting sqref="E2:E7">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F8">
+  <conditionalFormatting sqref="F2:F7">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G8">
+  <conditionalFormatting sqref="G2:G7">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H8">
+  <conditionalFormatting sqref="H2:H7">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I8">
+  <conditionalFormatting sqref="I2:I7">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J8">
+  <conditionalFormatting sqref="J2:J7">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K8">
+  <conditionalFormatting sqref="K2:K7">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L8">
+  <conditionalFormatting sqref="L2:L7">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1355,12 +1263,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M8">
+  <conditionalFormatting sqref="M2:M7">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N8">
+  <conditionalFormatting sqref="N2:N7">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1377,22 +1285,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O8">
+  <conditionalFormatting sqref="O2:O7">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P8">
+  <conditionalFormatting sqref="P2:P7">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q8">
+  <conditionalFormatting sqref="Q2:Q7">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R8">
+  <conditionalFormatting sqref="R2:R7">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="68">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260716--01</t>
-  </si>
-  <si>
     <t>20260717--01</t>
   </si>
   <si>
@@ -88,9 +85,6 @@
     <t>20260721--01</t>
   </si>
   <si>
-    <t>06:38</t>
-  </si>
-  <si>
     <t>06:19</t>
   </si>
   <si>
@@ -106,106 +100,85 @@
     <t>02:59</t>
   </si>
   <si>
-    <t>04:19</t>
-  </si>
-  <si>
     <t>01:11</t>
   </si>
   <si>
     <t>04:00</t>
   </si>
   <si>
-    <t>21:19:44</t>
-  </si>
-  <si>
-    <t>20:32:33</t>
-  </si>
-  <si>
-    <t>22:10:16</t>
-  </si>
-  <si>
-    <t>21:22:42</t>
-  </si>
-  <si>
-    <t>20:35:14</t>
-  </si>
-  <si>
-    <t>20:38:23</t>
-  </si>
-  <si>
-    <t>21:21:52</t>
-  </si>
-  <si>
-    <t>20:34:45</t>
-  </si>
-  <si>
-    <t>22:12:53</t>
-  </si>
-  <si>
-    <t>21:24:59</t>
-  </si>
-  <si>
-    <t>20:37:23</t>
-  </si>
-  <si>
-    <t>20:41:27</t>
-  </si>
-  <si>
-    <t>21:25:12</t>
-  </si>
-  <si>
-    <t>20:37:55</t>
-  </si>
-  <si>
-    <t>22:15:06</t>
-  </si>
-  <si>
-    <t>21:27:55</t>
-  </si>
-  <si>
-    <t>20:40:39</t>
-  </si>
-  <si>
-    <t>20:42:56</t>
-  </si>
-  <si>
-    <t>21:28:30</t>
-  </si>
-  <si>
-    <t>20:41:04</t>
-  </si>
-  <si>
-    <t>22:17:20</t>
-  </si>
-  <si>
-    <t>21:30:50</t>
-  </si>
-  <si>
-    <t>20:43:53</t>
-  </si>
-  <si>
-    <t>20:44:26</t>
-  </si>
-  <si>
-    <t>21:30:37</t>
-  </si>
-  <si>
-    <t>20:43:15</t>
-  </si>
-  <si>
-    <t>22:19:56</t>
-  </si>
-  <si>
-    <t>21:33:05</t>
-  </si>
-  <si>
-    <t>20:46:01</t>
-  </si>
-  <si>
-    <t>20:47:29</t>
-  </si>
-  <si>
-    <t>40°</t>
+    <t>20:32:34</t>
+  </si>
+  <si>
+    <t>22:10:17</t>
+  </si>
+  <si>
+    <t>21:22:45</t>
+  </si>
+  <si>
+    <t>20:35:18</t>
+  </si>
+  <si>
+    <t>20:38:30</t>
+  </si>
+  <si>
+    <t>20:34:46</t>
+  </si>
+  <si>
+    <t>22:12:54</t>
+  </si>
+  <si>
+    <t>21:25:01</t>
+  </si>
+  <si>
+    <t>20:37:26</t>
+  </si>
+  <si>
+    <t>20:41:34</t>
+  </si>
+  <si>
+    <t>20:37:56</t>
+  </si>
+  <si>
+    <t>22:15:07</t>
+  </si>
+  <si>
+    <t>21:27:57</t>
+  </si>
+  <si>
+    <t>20:40:42</t>
+  </si>
+  <si>
+    <t>20:43:04</t>
+  </si>
+  <si>
+    <t>20:41:05</t>
+  </si>
+  <si>
+    <t>22:17:21</t>
+  </si>
+  <si>
+    <t>21:30:52</t>
+  </si>
+  <si>
+    <t>20:43:56</t>
+  </si>
+  <si>
+    <t>20:44:33</t>
+  </si>
+  <si>
+    <t>20:43:16</t>
+  </si>
+  <si>
+    <t>22:19:57</t>
+  </si>
+  <si>
+    <t>21:33:07</t>
+  </si>
+  <si>
+    <t>20:46:04</t>
+  </si>
+  <si>
+    <t>20:47:36</t>
   </si>
   <si>
     <t>10°</t>
@@ -220,22 +193,16 @@
     <t>2°</t>
   </si>
   <si>
-    <t>21:26:11</t>
-  </si>
-  <si>
-    <t>20:41:05</t>
-  </si>
-  <si>
-    <t>22:14:04</t>
-  </si>
-  <si>
-    <t>21:28:59</t>
-  </si>
-  <si>
-    <t>20:43:57</t>
-  </si>
-  <si>
-    <t>20:46:59</t>
+    <t>22:14:05</t>
+  </si>
+  <si>
+    <t>21:29:01</t>
+  </si>
+  <si>
+    <t>20:44:00</t>
+  </si>
+  <si>
+    <t>20:47:06</t>
   </si>
   <si>
     <t>A+B</t>
@@ -284,7 +251,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -306,12 +273,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -352,7 +313,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -373,9 +334,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -779,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -857,52 +815,52 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>38</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-7.5</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-16.2</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="O2" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
       <c r="Q2" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R2" s="7">
         <v>0</v>
@@ -913,43 +871,43 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="L3" s="4">
-        <v>-7.5</v>
+        <v>-24.6</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="O3" s="6">
         <v>0</v>
@@ -969,52 +927,52 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-16.9</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-24.6</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="O4" s="6">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
       </c>
-      <c r="Q4" s="8">
-        <v>12</v>
+      <c r="Q4" s="7">
+        <v>2</v>
       </c>
       <c r="R4" s="7">
         <v>0</v>
@@ -1025,52 +983,52 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-16.8</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="O5" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
       </c>
       <c r="Q5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" s="7">
         <v>0</v>
@@ -1081,43 +1039,43 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="I6" s="1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-8.9</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="N6" s="1" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="O6" s="6">
         <v>0</v>
@@ -1129,122 +1087,66 @@
         <v>0</v>
       </c>
       <c r="R6" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="2">
-        <v>13</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-8.9</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="O7" s="6">
-        <v>8</v>
-      </c>
-      <c r="P7" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-      <c r="R7" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A7">
+  <conditionalFormatting sqref="A2:A6">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B7">
+  <conditionalFormatting sqref="B2:B6">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C7">
+  <conditionalFormatting sqref="C2:C6">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D7">
+  <conditionalFormatting sqref="D2:D6">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E7">
+  <conditionalFormatting sqref="E2:E6">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F7">
+  <conditionalFormatting sqref="F2:F6">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G7">
+  <conditionalFormatting sqref="G2:G6">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H7">
+  <conditionalFormatting sqref="H2:H6">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I7">
+  <conditionalFormatting sqref="I2:I6">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J7">
+  <conditionalFormatting sqref="J2:J6">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K7">
+  <conditionalFormatting sqref="K2:K6">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L7">
+  <conditionalFormatting sqref="L2:L6">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1263,12 +1165,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M7">
+  <conditionalFormatting sqref="M2:M6">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N7">
+  <conditionalFormatting sqref="N2:N6">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1285,22 +1187,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O7">
+  <conditionalFormatting sqref="O2:O6">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P7">
+  <conditionalFormatting sqref="P2:P6">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q7">
+  <conditionalFormatting sqref="Q2:Q6">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R7">
+  <conditionalFormatting sqref="R2:R6">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260717--01</t>
-  </si>
-  <si>
-    <t>20260717--02</t>
-  </si>
-  <si>
     <t>20260718--01</t>
   </si>
   <si>
@@ -85,33 +79,18 @@
     <t>20260721--01</t>
   </si>
   <si>
-    <t>06:19</t>
-  </si>
-  <si>
-    <t>04:27</t>
-  </si>
-  <si>
     <t>05:51</t>
   </si>
   <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>02:59</t>
-  </si>
-  <si>
-    <t>01:11</t>
+    <t>06:29</t>
+  </si>
+  <si>
+    <t>02:58</t>
   </si>
   <si>
     <t>04:00</t>
   </si>
   <si>
-    <t>20:32:34</t>
-  </si>
-  <si>
-    <t>22:10:17</t>
-  </si>
-  <si>
     <t>21:22:45</t>
   </si>
   <si>
@@ -121,25 +100,13 @@
     <t>20:38:30</t>
   </si>
   <si>
-    <t>20:34:46</t>
-  </si>
-  <si>
-    <t>22:12:54</t>
-  </si>
-  <si>
     <t>21:25:01</t>
   </si>
   <si>
-    <t>20:37:26</t>
-  </si>
-  <si>
-    <t>20:41:34</t>
-  </si>
-  <si>
-    <t>20:37:56</t>
-  </si>
-  <si>
-    <t>22:15:07</t>
+    <t>20:37:27</t>
+  </si>
+  <si>
+    <t>20:41:35</t>
   </si>
   <si>
     <t>21:27:57</t>
@@ -151,12 +118,6 @@
     <t>20:43:04</t>
   </si>
   <si>
-    <t>20:41:05</t>
-  </si>
-  <si>
-    <t>22:17:21</t>
-  </si>
-  <si>
     <t>21:30:52</t>
   </si>
   <si>
@@ -166,34 +127,22 @@
     <t>20:44:33</t>
   </si>
   <si>
-    <t>20:43:16</t>
-  </si>
-  <si>
-    <t>22:19:57</t>
-  </si>
-  <si>
     <t>21:33:07</t>
   </si>
   <si>
     <t>20:46:04</t>
   </si>
   <si>
-    <t>20:47:36</t>
+    <t>20:47:37</t>
+  </si>
+  <si>
+    <t>23°</t>
   </si>
   <si>
     <t>10°</t>
   </si>
   <si>
-    <t>15°</t>
-  </si>
-  <si>
-    <t>23°</t>
-  </si>
-  <si>
     <t>2°</t>
-  </si>
-  <si>
-    <t>22:14:05</t>
   </si>
   <si>
     <t>21:29:01</t>
@@ -737,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -815,52 +764,52 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L2" s="4">
-        <v>-7.5</v>
+        <v>-16.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="O2" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
       <c r="Q2" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" s="7">
         <v>0</v>
@@ -871,43 +820,43 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="L3" s="4">
-        <v>-24.6</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="O3" s="6">
         <v>0</v>
@@ -927,226 +876,114 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="K4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-8.9</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-16.9</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="N4" s="1" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="O4" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
       </c>
       <c r="Q4" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R4" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="2">
-        <v>50</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="O5" s="6">
-        <v>0</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="A6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="2">
-        <v>12</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-8.9</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A6">
+  <conditionalFormatting sqref="A2:A4">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B6">
+  <conditionalFormatting sqref="B2:B4">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C6">
+  <conditionalFormatting sqref="C2:C4">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D6">
+  <conditionalFormatting sqref="D2:D4">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E6">
+  <conditionalFormatting sqref="E2:E4">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
+  <conditionalFormatting sqref="F2:F4">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G6">
+  <conditionalFormatting sqref="G2:G4">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H6">
+  <conditionalFormatting sqref="H2:H4">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6">
+  <conditionalFormatting sqref="I2:I4">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
+  <conditionalFormatting sqref="J2:J4">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
+  <conditionalFormatting sqref="K2:K4">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
+  <conditionalFormatting sqref="L2:L4">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1165,12 +1002,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M6">
+  <conditionalFormatting sqref="M2:M4">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N6">
+  <conditionalFormatting sqref="N2:N4">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1187,22 +1024,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O6">
+  <conditionalFormatting sqref="O2:O4">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P6">
+  <conditionalFormatting sqref="P2:P4">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q6">
+  <conditionalFormatting sqref="Q2:Q4">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R6">
+  <conditionalFormatting sqref="R2:R4">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="39">
   <si>
     <t>Datum</t>
   </si>
@@ -70,73 +70,46 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260718--01</t>
-  </si>
-  <si>
     <t>20260719--01</t>
   </si>
   <si>
     <t>20260721--01</t>
   </si>
   <si>
-    <t>05:51</t>
-  </si>
-  <si>
-    <t>06:29</t>
-  </si>
-  <si>
-    <t>02:58</t>
-  </si>
-  <si>
-    <t>04:00</t>
-  </si>
-  <si>
-    <t>21:22:45</t>
-  </si>
-  <si>
-    <t>20:35:18</t>
-  </si>
-  <si>
-    <t>20:38:30</t>
-  </si>
-  <si>
-    <t>21:25:01</t>
-  </si>
-  <si>
-    <t>20:37:27</t>
-  </si>
-  <si>
-    <t>20:41:35</t>
-  </si>
-  <si>
-    <t>21:27:57</t>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>02:59</t>
+  </si>
+  <si>
+    <t>20:35:17</t>
+  </si>
+  <si>
+    <t>20:38:29</t>
+  </si>
+  <si>
+    <t>20:37:26</t>
+  </si>
+  <si>
+    <t>20:41:33</t>
   </si>
   <si>
     <t>20:40:42</t>
   </si>
   <si>
-    <t>20:43:04</t>
-  </si>
-  <si>
-    <t>21:30:52</t>
+    <t>20:43:02</t>
   </si>
   <si>
     <t>20:43:56</t>
   </si>
   <si>
-    <t>20:44:33</t>
-  </si>
-  <si>
-    <t>21:33:07</t>
-  </si>
-  <si>
-    <t>20:46:04</t>
-  </si>
-  <si>
-    <t>20:47:37</t>
-  </si>
-  <si>
-    <t>23°</t>
+    <t>20:44:32</t>
+  </si>
+  <si>
+    <t>20:46:03</t>
+  </si>
+  <si>
+    <t>20:47:35</t>
   </si>
   <si>
     <t>10°</t>
@@ -145,22 +118,13 @@
     <t>2°</t>
   </si>
   <si>
-    <t>21:29:01</t>
-  </si>
-  <si>
     <t>20:44:00</t>
   </si>
   <si>
-    <t>20:47:06</t>
-  </si>
-  <si>
-    <t>A+B</t>
+    <t>20:47:04</t>
   </si>
   <si>
     <t>A</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>1</t>
@@ -200,7 +164,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -222,6 +186,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -262,7 +232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -283,6 +253,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -686,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -764,52 +737,52 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>50</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="L2" s="4">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-16.9</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="O2" s="6">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="7">
-        <v>0</v>
+      <c r="Q2" s="8">
+        <v>7</v>
       </c>
       <c r="R2" s="7">
         <v>0</v>
@@ -820,170 +793,114 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="L3" s="4">
+        <v>-8.9</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="O3" s="6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
-      <c r="Q3" s="7">
-        <v>0</v>
+      <c r="Q3" s="8">
+        <v>4</v>
       </c>
       <c r="R3" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
-      <c r="A4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="2">
-        <v>12</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-8.9</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O4" s="6">
-        <v>0</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>0</v>
-      </c>
-      <c r="R4" s="7">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A4">
+  <conditionalFormatting sqref="A2:A3">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B4">
+  <conditionalFormatting sqref="B2:B3">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C4">
+  <conditionalFormatting sqref="C2:C3">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D4">
+  <conditionalFormatting sqref="D2:D3">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E4">
+  <conditionalFormatting sqref="E2:E3">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F4">
+  <conditionalFormatting sqref="F2:F3">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G4">
+  <conditionalFormatting sqref="G2:G3">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H4">
+  <conditionalFormatting sqref="H2:H3">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4">
+  <conditionalFormatting sqref="I2:I3">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J4">
+  <conditionalFormatting sqref="J2:J3">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K4">
+  <conditionalFormatting sqref="K2:K3">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L4">
+  <conditionalFormatting sqref="L2:L3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1002,12 +919,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M4">
+  <conditionalFormatting sqref="M2:M3">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N4">
+  <conditionalFormatting sqref="N2:N3">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1024,22 +941,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O4">
+  <conditionalFormatting sqref="O2:O3">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P4">
+  <conditionalFormatting sqref="P2:P3">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q4">
+  <conditionalFormatting sqref="Q2:Q3">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R4">
+  <conditionalFormatting sqref="R2:R3">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
   <si>
     <t>Datum</t>
   </si>
@@ -70,64 +70,34 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260719--01</t>
-  </si>
-  <si>
     <t>20260721--01</t>
   </si>
   <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>02:59</t>
-  </si>
-  <si>
-    <t>20:35:17</t>
-  </si>
-  <si>
-    <t>20:38:29</t>
-  </si>
-  <si>
-    <t>20:37:26</t>
-  </si>
-  <si>
-    <t>20:41:33</t>
-  </si>
-  <si>
-    <t>20:40:42</t>
-  </si>
-  <si>
-    <t>20:43:02</t>
-  </si>
-  <si>
-    <t>20:43:56</t>
-  </si>
-  <si>
-    <t>20:44:32</t>
-  </si>
-  <si>
-    <t>20:46:03</t>
-  </si>
-  <si>
-    <t>20:47:35</t>
-  </si>
-  <si>
-    <t>10°</t>
+    <t>02:58</t>
+  </si>
+  <si>
+    <t>20:38:30</t>
+  </si>
+  <si>
+    <t>20:41:35</t>
+  </si>
+  <si>
+    <t>20:43:04</t>
+  </si>
+  <si>
+    <t>20:44:33</t>
+  </si>
+  <si>
+    <t>20:47:36</t>
   </si>
   <si>
     <t>2°</t>
   </si>
   <si>
-    <t>20:44:00</t>
-  </si>
-  <si>
-    <t>20:47:04</t>
+    <t>20:47:06</t>
   </si>
   <si>
     <t>A</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>4</t>
@@ -164,7 +134,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -186,12 +156,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -232,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -253,9 +217,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -659,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -737,170 +698,114 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="J2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="L2" s="4">
+        <v>-8.9</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="O2" s="6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="8">
-        <v>7</v>
+      <c r="Q2" s="7">
+        <v>0</v>
       </c>
       <c r="R2" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
-      <c r="A3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="2">
-        <v>12</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-8.9</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O3" s="6">
-        <v>4</v>
-      </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>4</v>
-      </c>
-      <c r="R3" s="7">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A3">
+  <conditionalFormatting sqref="A2">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B3">
+  <conditionalFormatting sqref="B2">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C3">
+  <conditionalFormatting sqref="C2">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D3">
+  <conditionalFormatting sqref="D2">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E3">
+  <conditionalFormatting sqref="E2">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F3">
+  <conditionalFormatting sqref="F2">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G3">
+  <conditionalFormatting sqref="G2">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H3">
+  <conditionalFormatting sqref="H2">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I3">
+  <conditionalFormatting sqref="I2">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J3">
+  <conditionalFormatting sqref="J2">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K3">
+  <conditionalFormatting sqref="K2">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L3">
+  <conditionalFormatting sqref="L2">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -919,12 +824,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M3">
+  <conditionalFormatting sqref="M2">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N3">
+  <conditionalFormatting sqref="N2">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -941,22 +846,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O3">
+  <conditionalFormatting sqref="O2">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P3">
+  <conditionalFormatting sqref="P2">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q3">
+  <conditionalFormatting sqref="Q2">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R3">
+  <conditionalFormatting sqref="R2">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -73,16 +73,16 @@
     <t>20260721--01</t>
   </si>
   <si>
-    <t>02:58</t>
+    <t>02:59</t>
   </si>
   <si>
     <t>20:38:30</t>
   </si>
   <si>
-    <t>20:41:35</t>
-  </si>
-  <si>
-    <t>20:43:04</t>
+    <t>20:41:34</t>
+  </si>
+  <si>
+    <t>20:43:03</t>
   </si>
   <si>
     <t>20:44:33</t>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
   <si>
     <t>Datum</t>
   </si>
@@ -68,39 +68,6 @@
   </si>
   <si>
     <t>Vysoká</t>
-  </si>
-  <si>
-    <t>20260721--01</t>
-  </si>
-  <si>
-    <t>02:59</t>
-  </si>
-  <si>
-    <t>20:38:30</t>
-  </si>
-  <si>
-    <t>20:41:34</t>
-  </si>
-  <si>
-    <t>20:43:03</t>
-  </si>
-  <si>
-    <t>20:44:33</t>
-  </si>
-  <si>
-    <t>20:47:36</t>
-  </si>
-  <si>
-    <t>2°</t>
-  </si>
-  <si>
-    <t>20:47:06</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -110,7 +77,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0&quot;°&quot;"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,15 +93,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF333333"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -144,18 +104,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD7E4BC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -196,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -212,12 +160,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -620,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -693,119 +635,63 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
-      <c r="A2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="2">
-        <v>12</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-8.9</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="6">
-        <v>0</v>
-      </c>
-      <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="7">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2">
+  <conditionalFormatting sqref="A1:A2">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
+  <conditionalFormatting sqref="B1:B2">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2">
+  <conditionalFormatting sqref="C1:C2">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2">
+  <conditionalFormatting sqref="D1:D2">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2">
+  <conditionalFormatting sqref="E1:E2">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
+  <conditionalFormatting sqref="F1:F2">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2">
+  <conditionalFormatting sqref="G1:G2">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2">
+  <conditionalFormatting sqref="H1:H2">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2">
+  <conditionalFormatting sqref="I1:I2">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2">
+  <conditionalFormatting sqref="J1:J2">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2">
+  <conditionalFormatting sqref="K1:K2">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2">
+  <conditionalFormatting sqref="L1:L2">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -824,12 +710,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2">
+  <conditionalFormatting sqref="M1:M2">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2">
+  <conditionalFormatting sqref="N1:N2">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -846,22 +732,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2">
+  <conditionalFormatting sqref="O1:O2">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2">
+  <conditionalFormatting sqref="P1:P2">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2">
+  <conditionalFormatting sqref="Q1:Q2">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2">
+  <conditionalFormatting sqref="R1:R2">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
   <si>
     <t>Datum</t>
   </si>
@@ -68,6 +68,42 @@
   </si>
   <si>
     <t>Vysoká</t>
+  </si>
+  <si>
+    <t>20260803--01</t>
+  </si>
+  <si>
+    <t>05:21</t>
+  </si>
+  <si>
+    <t>04:57</t>
+  </si>
+  <si>
+    <t>05:19:16</t>
+  </si>
+  <si>
+    <t>05:21:39</t>
+  </si>
+  <si>
+    <t>05:24:19</t>
+  </si>
+  <si>
+    <t>05:27:00</t>
+  </si>
+  <si>
+    <t>05:29:24</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>05:22:03</t>
+  </si>
+  <si>
+    <t>A+B</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
 </sst>
 </file>
@@ -77,7 +113,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0&quot;°&quot;"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,8 +129,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -104,6 +147,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD7E4BC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -144,7 +205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -160,6 +221,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -562,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -635,63 +705,119 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2">
+        <v>22</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-13.9</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="6">
+        <v>61</v>
+      </c>
+      <c r="P2" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>61</v>
+      </c>
+      <c r="R2" s="7">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A2">
+  <conditionalFormatting sqref="A2">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B2">
+  <conditionalFormatting sqref="B2">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C2">
+  <conditionalFormatting sqref="C2">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D2">
+  <conditionalFormatting sqref="D2">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E2">
+  <conditionalFormatting sqref="E2">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F2">
+  <conditionalFormatting sqref="F2">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G1:G2">
+  <conditionalFormatting sqref="G2">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H2">
+  <conditionalFormatting sqref="H2">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I2">
+  <conditionalFormatting sqref="I2">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J2">
+  <conditionalFormatting sqref="J2">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K2">
+  <conditionalFormatting sqref="K2">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L1:L2">
+  <conditionalFormatting sqref="L2">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -710,12 +836,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1:M2">
+  <conditionalFormatting sqref="M2">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1:N2">
+  <conditionalFormatting sqref="N2">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -732,22 +858,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O1:O2">
+  <conditionalFormatting sqref="O2">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P1:P2">
+  <conditionalFormatting sqref="P2">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1:Q2">
+  <conditionalFormatting sqref="Q2">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R2">
+  <conditionalFormatting sqref="R2">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
   <si>
     <t>Datum</t>
   </si>
@@ -73,37 +73,70 @@
     <t>20260803--01</t>
   </si>
   <si>
-    <t>05:21</t>
-  </si>
-  <si>
-    <t>04:57</t>
-  </si>
-  <si>
-    <t>05:19:16</t>
-  </si>
-  <si>
-    <t>05:21:39</t>
-  </si>
-  <si>
-    <t>05:24:19</t>
-  </si>
-  <si>
-    <t>05:27:00</t>
-  </si>
-  <si>
-    <t>05:29:24</t>
+    <t>20260804--01</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>03:09</t>
+  </si>
+  <si>
+    <t>04:56</t>
+  </si>
+  <si>
+    <t>01:28</t>
+  </si>
+  <si>
+    <t>05:19:10</t>
+  </si>
+  <si>
+    <t>04:31:20</t>
+  </si>
+  <si>
+    <t>05:21:33</t>
+  </si>
+  <si>
+    <t>04:34:20</t>
+  </si>
+  <si>
+    <t>05:24:13</t>
+  </si>
+  <si>
+    <t>04:35:55</t>
+  </si>
+  <si>
+    <t>05:26:53</t>
+  </si>
+  <si>
+    <t>04:37:29</t>
+  </si>
+  <si>
+    <t>05:29:18</t>
+  </si>
+  <si>
+    <t>04:40:30</t>
   </si>
   <si>
     <t>12°</t>
   </si>
   <si>
-    <t>05:22:03</t>
+    <t>13°</t>
+  </si>
+  <si>
+    <t>05:21:57</t>
+  </si>
+  <si>
+    <t>04:36:01</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
 </sst>
 </file>
@@ -152,7 +185,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -164,7 +197,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -632,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -713,111 +746,155 @@
         <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="L2" s="4">
         <v>-13.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="O2" s="6">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
       <c r="Q2" s="8">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="R2" s="7">
         <v>0</v>
       </c>
     </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-22.9</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2">
+  <conditionalFormatting sqref="A2:A3">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
+  <conditionalFormatting sqref="B2:B3">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2">
+  <conditionalFormatting sqref="C2:C3">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2">
+  <conditionalFormatting sqref="D2:D3">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2">
+  <conditionalFormatting sqref="E2:E3">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
+  <conditionalFormatting sqref="F2:F3">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2">
+  <conditionalFormatting sqref="G2:G3">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2">
+  <conditionalFormatting sqref="H2:H3">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2">
+  <conditionalFormatting sqref="I2:I3">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2">
+  <conditionalFormatting sqref="J2:J3">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2">
+  <conditionalFormatting sqref="K2:K3">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2">
+  <conditionalFormatting sqref="L2:L3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -836,12 +913,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2">
+  <conditionalFormatting sqref="M2:M3">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2">
+  <conditionalFormatting sqref="N2:N3">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -858,22 +935,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2">
+  <conditionalFormatting sqref="O2:O3">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2">
+  <conditionalFormatting sqref="P2:P3">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2">
+  <conditionalFormatting sqref="Q2:Q3">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2">
+  <conditionalFormatting sqref="R2:R3">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="50">
   <si>
     <t>Datum</t>
   </si>
@@ -76,12 +76,18 @@
     <t>20260804--01</t>
   </si>
   <si>
+    <t>20260805--01</t>
+  </si>
+  <si>
     <t>05:20</t>
   </si>
   <si>
     <t>03:09</t>
   </si>
   <si>
+    <t>06:42</t>
+  </si>
+  <si>
     <t>04:56</t>
   </si>
   <si>
@@ -94,40 +100,61 @@
     <t>04:31:20</t>
   </si>
   <si>
+    <t>05:18:59</t>
+  </si>
+  <si>
     <t>05:21:33</t>
   </si>
   <si>
     <t>04:34:20</t>
   </si>
   <si>
+    <t>05:21:05</t>
+  </si>
+  <si>
     <t>05:24:13</t>
   </si>
   <si>
     <t>04:35:55</t>
   </si>
   <si>
+    <t>05:24:25</t>
+  </si>
+  <si>
     <t>05:26:53</t>
   </si>
   <si>
     <t>04:37:29</t>
   </si>
   <si>
+    <t>05:27:47</t>
+  </si>
+  <si>
     <t>05:29:18</t>
   </si>
   <si>
     <t>04:40:30</t>
   </si>
   <si>
+    <t>05:29:54</t>
+  </si>
+  <si>
     <t>12°</t>
   </si>
   <si>
     <t>13°</t>
   </si>
   <si>
+    <t>29°</t>
+  </si>
+  <si>
     <t>05:21:57</t>
   </si>
   <si>
     <t>04:36:01</t>
+  </si>
+  <si>
+    <t>05:22:51</t>
   </si>
   <si>
     <t>A+B</t>
@@ -170,7 +197,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -185,7 +212,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -197,7 +224,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -238,7 +277,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -262,6 +301,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -665,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -746,52 +791,52 @@
         <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="L2" s="4">
         <v>-13.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="O2" s="6">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="8">
-        <v>30</v>
-      </c>
-      <c r="R2" s="7">
-        <v>0</v>
+      <c r="Q2" s="7">
+        <v>2</v>
+      </c>
+      <c r="R2" s="8">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -802,99 +847,155 @@
         <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L3" s="4">
         <v>-22.9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="N3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="O3" s="9">
+        <v>49</v>
+      </c>
+      <c r="P3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="10">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2">
+        <v>90</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>40</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-14.1</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A3">
+  <conditionalFormatting sqref="A2:A4">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B3">
+  <conditionalFormatting sqref="B2:B4">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C3">
+  <conditionalFormatting sqref="C2:C4">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D3">
+  <conditionalFormatting sqref="D2:D4">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E3">
+  <conditionalFormatting sqref="E2:E4">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F3">
+  <conditionalFormatting sqref="F2:F4">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G3">
+  <conditionalFormatting sqref="G2:G4">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H3">
+  <conditionalFormatting sqref="H2:H4">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I3">
+  <conditionalFormatting sqref="I2:I4">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J3">
+  <conditionalFormatting sqref="J2:J4">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K3">
+  <conditionalFormatting sqref="K2:K4">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L3">
+  <conditionalFormatting sqref="L2:L4">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -913,12 +1014,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M3">
+  <conditionalFormatting sqref="M2:M4">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N3">
+  <conditionalFormatting sqref="N2:N4">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -935,22 +1036,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O3">
+  <conditionalFormatting sqref="O2:O4">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P3">
+  <conditionalFormatting sqref="P2:P4">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q3">
+  <conditionalFormatting sqref="Q2:Q4">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R3">
+  <conditionalFormatting sqref="R2:R4">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="82">
   <si>
     <t>Datum</t>
   </si>
@@ -79,64 +79,136 @@
     <t>20260805--01</t>
   </si>
   <si>
-    <t>05:20</t>
+    <t>20260806--01</t>
+  </si>
+  <si>
+    <t>20260807--01</t>
+  </si>
+  <si>
+    <t>20260807--02</t>
+  </si>
+  <si>
+    <t>05:21</t>
   </si>
   <si>
     <t>03:09</t>
   </si>
   <si>
-    <t>06:42</t>
-  </si>
-  <si>
-    <t>04:56</t>
-  </si>
-  <si>
-    <t>01:28</t>
-  </si>
-  <si>
-    <t>05:19:10</t>
-  </si>
-  <si>
-    <t>04:31:20</t>
-  </si>
-  <si>
-    <t>05:18:59</t>
-  </si>
-  <si>
-    <t>05:21:33</t>
-  </si>
-  <si>
-    <t>04:34:20</t>
-  </si>
-  <si>
-    <t>05:21:05</t>
-  </si>
-  <si>
-    <t>05:24:13</t>
-  </si>
-  <si>
-    <t>04:35:55</t>
-  </si>
-  <si>
-    <t>05:24:25</t>
-  </si>
-  <si>
-    <t>05:26:53</t>
-  </si>
-  <si>
-    <t>04:37:29</t>
-  </si>
-  <si>
-    <t>05:27:47</t>
-  </si>
-  <si>
-    <t>05:29:18</t>
-  </si>
-  <si>
-    <t>04:40:30</t>
-  </si>
-  <si>
-    <t>05:29:54</t>
+    <t>06:43</t>
+  </si>
+  <si>
+    <t>06:28</t>
+  </si>
+  <si>
+    <t>05:43</t>
+  </si>
+  <si>
+    <t>05:46</t>
+  </si>
+  <si>
+    <t>04:57</t>
+  </si>
+  <si>
+    <t>01:29</t>
+  </si>
+  <si>
+    <t>02:31</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>04:18</t>
+  </si>
+  <si>
+    <t>05:19:11</t>
+  </si>
+  <si>
+    <t>04:31:23</t>
+  </si>
+  <si>
+    <t>05:19:04</t>
+  </si>
+  <si>
+    <t>04:30:38</t>
+  </si>
+  <si>
+    <t>03:42:19</t>
+  </si>
+  <si>
+    <t>05:19:31</t>
+  </si>
+  <si>
+    <t>05:21:34</t>
+  </si>
+  <si>
+    <t>04:34:23</t>
+  </si>
+  <si>
+    <t>05:21:09</t>
+  </si>
+  <si>
+    <t>04:32:46</t>
+  </si>
+  <si>
+    <t>03:44:36</t>
+  </si>
+  <si>
+    <t>05:21:50</t>
+  </si>
+  <si>
+    <t>05:24:14</t>
+  </si>
+  <si>
+    <t>04:35:57</t>
+  </si>
+  <si>
+    <t>05:24:30</t>
+  </si>
+  <si>
+    <t>04:35:59</t>
+  </si>
+  <si>
+    <t>03:47:27</t>
+  </si>
+  <si>
+    <t>05:24:42</t>
+  </si>
+  <si>
+    <t>05:26:55</t>
+  </si>
+  <si>
+    <t>04:37:32</t>
+  </si>
+  <si>
+    <t>05:27:52</t>
+  </si>
+  <si>
+    <t>04:39:14</t>
+  </si>
+  <si>
+    <t>03:50:19</t>
+  </si>
+  <si>
+    <t>05:27:36</t>
+  </si>
+  <si>
+    <t>05:29:19</t>
+  </si>
+  <si>
+    <t>04:40:33</t>
+  </si>
+  <si>
+    <t>05:29:59</t>
+  </si>
+  <si>
+    <t>04:41:23</t>
+  </si>
+  <si>
+    <t>03:52:37</t>
+  </si>
+  <si>
+    <t>05:29:56</t>
   </si>
   <si>
     <t>12°</t>
@@ -148,22 +220,46 @@
     <t>29°</t>
   </si>
   <si>
-    <t>05:21:57</t>
-  </si>
-  <si>
-    <t>04:36:01</t>
-  </si>
-  <si>
-    <t>05:22:51</t>
+    <t>39°</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>20°</t>
+  </si>
+  <si>
+    <t>05:21:58</t>
+  </si>
+  <si>
+    <t>04:36:03</t>
+  </si>
+  <si>
+    <t>05:22:55</t>
+  </si>
+  <si>
+    <t>04:36:43</t>
+  </si>
+  <si>
+    <t>03:50:24</t>
+  </si>
+  <si>
+    <t>05:23:18</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -197,7 +293,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -212,7 +308,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -224,19 +320,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -277,7 +367,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -304,9 +394,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -710,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -791,52 +878,52 @@
         <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="L2" s="4">
         <v>-13.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="O2" s="6">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="7">
-        <v>2</v>
-      </c>
-      <c r="R2" s="8">
-        <v>7</v>
+      <c r="Q2" s="8">
+        <v>12</v>
+      </c>
+      <c r="R2" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -847,52 +934,52 @@
         <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="L3" s="4">
         <v>-22.9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="O3" s="9">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
       <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="10">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="R3" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -903,99 +990,279 @@
         <v>90</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="L4" s="4">
         <v>-14.1</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="N4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O4" s="9">
+        <v>1</v>
+      </c>
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>1</v>
+      </c>
+      <c r="R4" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="2">
         <v>48</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-23.2</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O5" s="9">
+        <v>0</v>
+      </c>
+      <c r="P5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>0</v>
+      </c>
+      <c r="R5" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="2">
+        <v>26</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-31.5</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="O6" s="9">
+        <v>0</v>
+      </c>
+      <c r="P6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>0</v>
+      </c>
+      <c r="R6" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="2">
+        <v>26</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-14.4</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O7" s="9">
+        <v>0</v>
+      </c>
+      <c r="P7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A4">
+  <conditionalFormatting sqref="A2:A7">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B4">
+  <conditionalFormatting sqref="B2:B7">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C4">
+  <conditionalFormatting sqref="C2:C7">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D4">
+  <conditionalFormatting sqref="D2:D7">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E4">
+  <conditionalFormatting sqref="E2:E7">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F4">
+  <conditionalFormatting sqref="F2:F7">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G4">
+  <conditionalFormatting sqref="G2:G7">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H4">
+  <conditionalFormatting sqref="H2:H7">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4">
+  <conditionalFormatting sqref="I2:I7">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J4">
+  <conditionalFormatting sqref="J2:J7">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K4">
+  <conditionalFormatting sqref="K2:K7">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L4">
+  <conditionalFormatting sqref="L2:L7">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1014,12 +1281,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M4">
+  <conditionalFormatting sqref="M2:M7">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N4">
+  <conditionalFormatting sqref="N2:N7">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1036,22 +1303,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O4">
+  <conditionalFormatting sqref="O2:O7">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P4">
+  <conditionalFormatting sqref="P2:P7">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q4">
+  <conditionalFormatting sqref="Q2:Q7">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R4">
+  <conditionalFormatting sqref="R2:R7">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="98">
   <si>
     <t>Datum</t>
   </si>
@@ -88,6 +88,12 @@
     <t>20260807--02</t>
   </si>
   <si>
+    <t>20260808--01</t>
+  </si>
+  <si>
+    <t>20260808--02</t>
+  </si>
+  <si>
     <t>05:21</t>
   </si>
   <si>
@@ -103,7 +109,13 @@
     <t>05:43</t>
   </si>
   <si>
-    <t>05:46</t>
+    <t>05:47</t>
+  </si>
+  <si>
+    <t>04:03</t>
+  </si>
+  <si>
+    <t>06:24</t>
   </si>
   <si>
     <t>04:57</t>
@@ -118,97 +130,124 @@
     <t>00:00</t>
   </si>
   <si>
-    <t>04:18</t>
-  </si>
-  <si>
-    <t>05:19:11</t>
-  </si>
-  <si>
-    <t>04:31:23</t>
-  </si>
-  <si>
-    <t>05:19:04</t>
-  </si>
-  <si>
-    <t>04:30:38</t>
-  </si>
-  <si>
-    <t>03:42:19</t>
-  </si>
-  <si>
-    <t>05:19:31</t>
+    <t>04:19</t>
+  </si>
+  <si>
+    <t>02:19</t>
+  </si>
+  <si>
+    <t>05:19:12</t>
+  </si>
+  <si>
+    <t>04:31:24</t>
+  </si>
+  <si>
+    <t>05:19:06</t>
+  </si>
+  <si>
+    <t>04:30:41</t>
+  </si>
+  <si>
+    <t>03:42:23</t>
+  </si>
+  <si>
+    <t>05:19:36</t>
+  </si>
+  <si>
+    <t>02:54:15</t>
+  </si>
+  <si>
+    <t>04:30:42</t>
   </si>
   <si>
     <t>05:21:34</t>
   </si>
   <si>
-    <t>04:34:23</t>
-  </si>
-  <si>
-    <t>05:21:09</t>
-  </si>
-  <si>
-    <t>04:32:46</t>
-  </si>
-  <si>
-    <t>03:44:36</t>
-  </si>
-  <si>
-    <t>05:21:50</t>
+    <t>04:34:24</t>
+  </si>
+  <si>
+    <t>05:21:11</t>
+  </si>
+  <si>
+    <t>04:32:49</t>
+  </si>
+  <si>
+    <t>03:44:40</t>
+  </si>
+  <si>
+    <t>05:21:54</t>
+  </si>
+  <si>
+    <t>02:56:57</t>
+  </si>
+  <si>
+    <t>04:32:51</t>
   </si>
   <si>
     <t>05:24:14</t>
   </si>
   <si>
-    <t>04:35:57</t>
-  </si>
-  <si>
-    <t>05:24:30</t>
-  </si>
-  <si>
-    <t>04:35:59</t>
-  </si>
-  <si>
-    <t>03:47:27</t>
-  </si>
-  <si>
-    <t>05:24:42</t>
+    <t>04:35:58</t>
+  </si>
+  <si>
+    <t>05:24:32</t>
+  </si>
+  <si>
+    <t>04:36:02</t>
+  </si>
+  <si>
+    <t>03:47:31</t>
+  </si>
+  <si>
+    <t>05:24:47</t>
+  </si>
+  <si>
+    <t>02:58:58</t>
+  </si>
+  <si>
+    <t>04:36:03</t>
   </si>
   <si>
     <t>05:26:55</t>
   </si>
   <si>
-    <t>04:37:32</t>
-  </si>
-  <si>
-    <t>05:27:52</t>
-  </si>
-  <si>
-    <t>04:39:14</t>
-  </si>
-  <si>
-    <t>03:50:19</t>
-  </si>
-  <si>
-    <t>05:27:36</t>
-  </si>
-  <si>
-    <t>05:29:19</t>
-  </si>
-  <si>
-    <t>04:40:33</t>
-  </si>
-  <si>
-    <t>05:29:59</t>
-  </si>
-  <si>
-    <t>04:41:23</t>
-  </si>
-  <si>
-    <t>03:52:37</t>
-  </si>
-  <si>
-    <t>05:29:56</t>
+    <t>04:37:33</t>
+  </si>
+  <si>
+    <t>05:27:54</t>
+  </si>
+  <si>
+    <t>04:39:17</t>
+  </si>
+  <si>
+    <t>03:50:23</t>
+  </si>
+  <si>
+    <t>05:27:41</t>
+  </si>
+  <si>
+    <t>03:01:00</t>
+  </si>
+  <si>
+    <t>04:39:15</t>
+  </si>
+  <si>
+    <t>05:29:20</t>
+  </si>
+  <si>
+    <t>04:40:34</t>
+  </si>
+  <si>
+    <t>05:30:01</t>
+  </si>
+  <si>
+    <t>04:41:26</t>
+  </si>
+  <si>
+    <t>03:52:42</t>
+  </si>
+  <si>
+    <t>03:03:44</t>
   </si>
   <si>
     <t>12°</t>
@@ -229,22 +268,31 @@
     <t>20°</t>
   </si>
   <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>33°</t>
+  </si>
+  <si>
     <t>05:21:58</t>
   </si>
   <si>
-    <t>04:36:03</t>
-  </si>
-  <si>
-    <t>05:22:55</t>
-  </si>
-  <si>
-    <t>04:36:43</t>
-  </si>
-  <si>
-    <t>03:50:24</t>
-  </si>
-  <si>
-    <t>05:23:18</t>
+    <t>04:36:04</t>
+  </si>
+  <si>
+    <t>05:22:57</t>
+  </si>
+  <si>
+    <t>04:36:46</t>
+  </si>
+  <si>
+    <t>03:50:28</t>
+  </si>
+  <si>
+    <t>05:23:22</t>
+  </si>
+  <si>
+    <t>04:36:56</t>
   </si>
   <si>
     <t>A+B</t>
@@ -293,7 +341,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -308,7 +356,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -320,13 +368,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -367,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -394,6 +460,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -797,7 +872,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -878,52 +953,52 @@
         <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="L2" s="4">
         <v>-13.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="O2" s="6">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="8">
-        <v>12</v>
-      </c>
-      <c r="R2" s="7">
-        <v>0</v>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -934,52 +1009,52 @@
         <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="L3" s="4">
         <v>-22.9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="O3" s="9">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
-      <c r="Q3" s="7">
-        <v>1</v>
-      </c>
-      <c r="R3" s="7">
-        <v>0</v>
+      <c r="Q3" s="10">
+        <v>48</v>
+      </c>
+      <c r="R3" s="11">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -990,52 +1065,52 @@
         <v>90</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="L4" s="4">
         <v>-14.1</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="O4" s="9">
+        <v>46</v>
+      </c>
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>46</v>
+      </c>
+      <c r="R4" s="7">
         <v>1</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>1</v>
-      </c>
-      <c r="R4" s="7">
-        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1046,49 +1121,49 @@
         <v>48</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="L5" s="4">
         <v>-23.2</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O5" s="9">
-        <v>0</v>
+        <v>95</v>
+      </c>
+      <c r="O5" s="6">
+        <v>10</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
       </c>
-      <c r="Q5" s="7">
-        <v>0</v>
+      <c r="Q5" s="11">
+        <v>10</v>
       </c>
       <c r="R5" s="7">
         <v>0</v>
@@ -1102,42 +1177,42 @@
         <v>26</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="L6" s="4">
-        <v>-31.5</v>
+        <v>-31.4</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="O6" s="9">
+        <v>97</v>
+      </c>
+      <c r="O6" s="6">
         <v>0</v>
       </c>
       <c r="P6" s="7">
@@ -1158,111 +1233,223 @@
         <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-14.3</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O7" s="6">
+        <v>0</v>
+      </c>
+      <c r="P7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="2">
+        <v>15</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J7" s="3" t="s">
+      <c r="F8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-14.4</v>
-      </c>
-      <c r="M7" s="3" t="s">
+      <c r="I8" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="N7" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O7" s="9">
-        <v>0</v>
-      </c>
-      <c r="P7" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-      <c r="R7" s="7">
+      <c r="J8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-38.5</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="O8" s="6">
+        <v>0</v>
+      </c>
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2">
+        <v>42</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-23.5</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O9" s="6">
+        <v>0</v>
+      </c>
+      <c r="P9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A7">
+  <conditionalFormatting sqref="A2:A9">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B7">
+  <conditionalFormatting sqref="B2:B9">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C7">
+  <conditionalFormatting sqref="C2:C9">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D7">
+  <conditionalFormatting sqref="D2:D9">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E7">
+  <conditionalFormatting sqref="E2:E9">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F7">
+  <conditionalFormatting sqref="F2:F9">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G7">
+  <conditionalFormatting sqref="G2:G9">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H7">
+  <conditionalFormatting sqref="H2:H9">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I7">
+  <conditionalFormatting sqref="I2:I9">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J7">
+  <conditionalFormatting sqref="J2:J9">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K7">
+  <conditionalFormatting sqref="K2:K9">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L7">
+  <conditionalFormatting sqref="L2:L9">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1281,12 +1468,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M7">
+  <conditionalFormatting sqref="M2:M9">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N7">
+  <conditionalFormatting sqref="N2:N9">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1303,22 +1490,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O7">
+  <conditionalFormatting sqref="O2:O9">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P7">
+  <conditionalFormatting sqref="P2:P9">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q7">
+  <conditionalFormatting sqref="Q2:Q9">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R7">
+  <conditionalFormatting sqref="R2:R9">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="130">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260803--01</t>
-  </si>
-  <si>
     <t>20260804--01</t>
   </si>
   <si>
@@ -94,7 +91,16 @@
     <t>20260808--02</t>
   </si>
   <si>
-    <t>05:21</t>
+    <t>20260809--01</t>
+  </si>
+  <si>
+    <t>20260809--02</t>
+  </si>
+  <si>
+    <t>20260810--01</t>
+  </si>
+  <si>
+    <t>20260810--02</t>
   </si>
   <si>
     <t>03:09</t>
@@ -106,193 +112,280 @@
     <t>06:28</t>
   </si>
   <si>
-    <t>05:43</t>
+    <t>05:42</t>
   </si>
   <si>
     <t>05:47</t>
   </si>
   <si>
-    <t>04:03</t>
-  </si>
-  <si>
-    <t>06:24</t>
-  </si>
-  <si>
-    <t>04:57</t>
+    <t>04:02</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>02:32</t>
+  </si>
+  <si>
+    <t>06:33</t>
+  </si>
+  <si>
+    <t>04:22</t>
   </si>
   <si>
     <t>01:29</t>
   </si>
   <si>
+    <t>04:56</t>
+  </si>
+  <si>
     <t>02:31</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>04:19</t>
-  </si>
-  <si>
-    <t>02:19</t>
-  </si>
-  <si>
-    <t>05:19:12</t>
-  </si>
-  <si>
-    <t>04:31:24</t>
-  </si>
-  <si>
-    <t>05:19:06</t>
-  </si>
-  <si>
-    <t>04:30:41</t>
-  </si>
-  <si>
-    <t>03:42:23</t>
-  </si>
-  <si>
-    <t>05:19:36</t>
-  </si>
-  <si>
-    <t>02:54:15</t>
-  </si>
-  <si>
-    <t>04:30:42</t>
-  </si>
-  <si>
-    <t>05:21:34</t>
-  </si>
-  <si>
-    <t>04:34:24</t>
-  </si>
-  <si>
-    <t>05:21:11</t>
-  </si>
-  <si>
-    <t>04:32:49</t>
-  </si>
-  <si>
-    <t>03:44:40</t>
-  </si>
-  <si>
-    <t>05:21:54</t>
-  </si>
-  <si>
-    <t>02:56:57</t>
-  </si>
-  <si>
-    <t>04:32:51</t>
-  </si>
-  <si>
-    <t>05:24:14</t>
-  </si>
-  <si>
-    <t>04:35:58</t>
-  </si>
-  <si>
-    <t>05:24:32</t>
-  </si>
-  <si>
-    <t>04:36:02</t>
-  </si>
-  <si>
-    <t>03:47:31</t>
-  </si>
-  <si>
-    <t>05:24:47</t>
-  </si>
-  <si>
-    <t>02:58:58</t>
+    <t>04:18</t>
+  </si>
+  <si>
+    <t>02:18</t>
+  </si>
+  <si>
+    <t>00:14</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>04:31:23</t>
+  </si>
+  <si>
+    <t>05:19:04</t>
+  </si>
+  <si>
+    <t>04:30:38</t>
+  </si>
+  <si>
+    <t>03:42:19</t>
+  </si>
+  <si>
+    <t>05:19:31</t>
+  </si>
+  <si>
+    <t>02:54:09</t>
+  </si>
+  <si>
+    <t>04:30:35</t>
+  </si>
+  <si>
+    <t>03:41:44</t>
+  </si>
+  <si>
+    <t>05:20:20</t>
+  </si>
+  <si>
+    <t>02:52:57</t>
+  </si>
+  <si>
+    <t>04:30:59</t>
+  </si>
+  <si>
+    <t>04:34:23</t>
+  </si>
+  <si>
+    <t>05:21:09</t>
+  </si>
+  <si>
+    <t>04:32:46</t>
+  </si>
+  <si>
+    <t>03:44:36</t>
+  </si>
+  <si>
+    <t>05:21:49</t>
+  </si>
+  <si>
+    <t>02:56:51</t>
+  </si>
+  <si>
+    <t>04:32:45</t>
+  </si>
+  <si>
+    <t>03:43:49</t>
+  </si>
+  <si>
+    <t>05:23:36</t>
+  </si>
+  <si>
+    <t>02:55:04</t>
+  </si>
+  <si>
+    <t>04:33:39</t>
+  </si>
+  <si>
+    <t>04:35:57</t>
+  </si>
+  <si>
+    <t>05:24:30</t>
+  </si>
+  <si>
+    <t>04:35:59</t>
+  </si>
+  <si>
+    <t>03:47:26</t>
+  </si>
+  <si>
+    <t>05:24:42</t>
+  </si>
+  <si>
+    <t>02:58:52</t>
+  </si>
+  <si>
+    <t>04:35:56</t>
+  </si>
+  <si>
+    <t>03:47:08</t>
+  </si>
+  <si>
+    <t>05:24:52</t>
+  </si>
+  <si>
+    <t>02:58:19</t>
+  </si>
+  <si>
+    <t>04:35:50</t>
+  </si>
+  <si>
+    <t>04:37:32</t>
+  </si>
+  <si>
+    <t>05:27:52</t>
+  </si>
+  <si>
+    <t>04:39:14</t>
+  </si>
+  <si>
+    <t>03:50:18</t>
+  </si>
+  <si>
+    <t>05:27:36</t>
+  </si>
+  <si>
+    <t>03:00:53</t>
+  </si>
+  <si>
+    <t>04:39:08</t>
+  </si>
+  <si>
+    <t>03:50:29</t>
+  </si>
+  <si>
+    <t>05:26:08</t>
+  </si>
+  <si>
+    <t>03:01:37</t>
+  </si>
+  <si>
+    <t>04:38:01</t>
+  </si>
+  <si>
+    <t>04:40:34</t>
+  </si>
+  <si>
+    <t>05:29:59</t>
+  </si>
+  <si>
+    <t>04:41:23</t>
+  </si>
+  <si>
+    <t>03:52:37</t>
+  </si>
+  <si>
+    <t>05:29:56</t>
+  </si>
+  <si>
+    <t>03:03:37</t>
+  </si>
+  <si>
+    <t>04:41:20</t>
+  </si>
+  <si>
+    <t>03:52:36</t>
+  </si>
+  <si>
+    <t>05:29:26</t>
+  </si>
+  <si>
+    <t>03:03:44</t>
+  </si>
+  <si>
+    <t>04:40:43</t>
+  </si>
+  <si>
+    <t>13°</t>
+  </si>
+  <si>
+    <t>29°</t>
+  </si>
+  <si>
+    <t>39°</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>20°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>33°</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>9°</t>
+  </si>
+  <si>
+    <t>1°</t>
+  </si>
+  <si>
+    <t>16°</t>
   </si>
   <si>
     <t>04:36:03</t>
   </si>
   <si>
-    <t>05:26:55</t>
-  </si>
-  <si>
-    <t>04:37:33</t>
-  </si>
-  <si>
-    <t>05:27:54</t>
-  </si>
-  <si>
-    <t>04:39:17</t>
+    <t>05:22:56</t>
+  </si>
+  <si>
+    <t>04:36:43</t>
   </si>
   <si>
     <t>03:50:23</t>
   </si>
   <si>
-    <t>05:27:41</t>
-  </si>
-  <si>
-    <t>03:01:00</t>
-  </si>
-  <si>
-    <t>04:39:15</t>
-  </si>
-  <si>
-    <t>05:29:20</t>
-  </si>
-  <si>
-    <t>04:40:34</t>
-  </si>
-  <si>
-    <t>05:30:01</t>
-  </si>
-  <si>
-    <t>04:41:26</t>
-  </si>
-  <si>
-    <t>03:52:42</t>
-  </si>
-  <si>
-    <t>03:03:44</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>13°</t>
-  </si>
-  <si>
-    <t>29°</t>
-  </si>
-  <si>
-    <t>39°</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
-    <t>20°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>33°</t>
-  </si>
-  <si>
-    <t>05:21:58</t>
-  </si>
-  <si>
-    <t>04:36:04</t>
-  </si>
-  <si>
-    <t>05:22:57</t>
-  </si>
-  <si>
-    <t>04:36:46</t>
-  </si>
-  <si>
-    <t>03:50:28</t>
-  </si>
-  <si>
-    <t>05:23:22</t>
-  </si>
-  <si>
-    <t>04:36:56</t>
+    <t>05:23:18</t>
+  </si>
+  <si>
+    <t>04:36:50</t>
+  </si>
+  <si>
+    <t>03:50:15</t>
+  </si>
+  <si>
+    <t>05:23:08</t>
+  </si>
+  <si>
+    <t>03:03:33</t>
+  </si>
+  <si>
+    <t>04:36:26</t>
   </si>
   <si>
     <t>A+B</t>
@@ -301,10 +394,13 @@
     <t>B</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>3</t>
@@ -341,7 +437,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -363,36 +459,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -433,7 +499,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -454,21 +520,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -872,7 +923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -950,46 +1001,46 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="L2" s="4">
-        <v>-13.9</v>
+        <v>-22.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="O2" s="6">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
@@ -997,8 +1048,8 @@
       <c r="Q2" s="7">
         <v>0</v>
       </c>
-      <c r="R2" s="8">
-        <v>5</v>
+      <c r="R2" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1006,55 +1057,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="L3" s="4">
-        <v>-22.9</v>
+        <v>-14.1</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="O3" s="9">
-        <v>79</v>
+        <v>128</v>
+      </c>
+      <c r="O3" s="6">
+        <v>2</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
-      <c r="Q3" s="10">
-        <v>48</v>
-      </c>
-      <c r="R3" s="11">
-        <v>9</v>
+      <c r="Q3" s="7">
+        <v>2</v>
+      </c>
+      <c r="R3" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1062,55 +1113,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="L4" s="4">
-        <v>-14.1</v>
+        <v>-23.2</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="O4" s="9">
-        <v>46</v>
+        <v>128</v>
+      </c>
+      <c r="O4" s="6">
+        <v>0</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
       </c>
-      <c r="Q4" s="12">
-        <v>46</v>
+      <c r="Q4" s="7">
+        <v>0</v>
       </c>
       <c r="R4" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1118,52 +1169,52 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="L5" s="4">
-        <v>-23.2</v>
+        <v>-31.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="O5" s="6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
       </c>
-      <c r="Q5" s="11">
-        <v>10</v>
+      <c r="Q5" s="7">
+        <v>0</v>
       </c>
       <c r="R5" s="7">
         <v>0</v>
@@ -1177,40 +1228,40 @@
         <v>26</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="L6" s="4">
-        <v>-31.4</v>
+        <v>-14.4</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="O6" s="6">
         <v>0</v>
@@ -1230,43 +1281,43 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="L7" s="4">
-        <v>-14.3</v>
+        <v>-38.5</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="O7" s="6">
         <v>0</v>
@@ -1286,43 +1337,43 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>46</v>
+        <v>119</v>
       </c>
       <c r="L8" s="4">
-        <v>-38.5</v>
+        <v>-23.6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="O8" s="6">
         <v>0</v>
@@ -1342,114 +1393,282 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-31.9</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="O9" s="6">
+        <v>2</v>
+      </c>
+      <c r="P9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="2">
+        <v>12</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-14.6</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="O10" s="6">
+        <v>1</v>
+      </c>
+      <c r="P10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>0</v>
+      </c>
+      <c r="R10" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="2">
+        <v>58</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-39</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="O11" s="6">
+        <v>0</v>
+      </c>
+      <c r="P11" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>0</v>
+      </c>
+      <c r="R11" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="2">
+        <v>16</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="D12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-23.5</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="O9" s="6">
-        <v>0</v>
-      </c>
-      <c r="P9" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>0</v>
-      </c>
-      <c r="R9" s="7">
+      <c r="E12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="L12" s="4">
+        <v>-23.9</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="O12" s="6">
+        <v>0</v>
+      </c>
+      <c r="P12" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>0</v>
+      </c>
+      <c r="R12" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A9">
+  <conditionalFormatting sqref="A2:A12">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B9">
+  <conditionalFormatting sqref="B2:B12">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C9">
+  <conditionalFormatting sqref="C2:C12">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
+  <conditionalFormatting sqref="D2:D12">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E9">
+  <conditionalFormatting sqref="E2:E12">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
+  <conditionalFormatting sqref="F2:F12">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G9">
+  <conditionalFormatting sqref="G2:G12">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H9">
+  <conditionalFormatting sqref="H2:H12">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I9">
+  <conditionalFormatting sqref="I2:I12">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J9">
+  <conditionalFormatting sqref="J2:J12">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K9">
+  <conditionalFormatting sqref="K2:K12">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L9">
+  <conditionalFormatting sqref="L2:L12">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1468,12 +1687,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M9">
+  <conditionalFormatting sqref="M2:M12">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N9">
+  <conditionalFormatting sqref="N2:N12">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1490,22 +1709,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O9">
+  <conditionalFormatting sqref="O2:O12">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P9">
+  <conditionalFormatting sqref="P2:P12">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q9">
+  <conditionalFormatting sqref="Q2:Q12">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R9">
+  <conditionalFormatting sqref="R2:R12">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="135">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260804--01</t>
-  </si>
-  <si>
     <t>20260805--01</t>
   </si>
   <si>
@@ -103,7 +100,10 @@
     <t>20260810--02</t>
   </si>
   <si>
-    <t>03:09</t>
+    <t>20260811--01</t>
+  </si>
+  <si>
+    <t>20260811--02</t>
   </si>
   <si>
     <t>06:43</t>
@@ -136,7 +136,10 @@
     <t>04:22</t>
   </si>
   <si>
-    <t>01:29</t>
+    <t>05:57</t>
+  </si>
+  <si>
+    <t>05:30</t>
   </si>
   <si>
     <t>04:56</t>
@@ -160,9 +163,6 @@
     <t>01:35</t>
   </si>
   <si>
-    <t>04:31:23</t>
-  </si>
-  <si>
     <t>05:19:04</t>
   </si>
   <si>
@@ -193,7 +193,10 @@
     <t>04:30:59</t>
   </si>
   <si>
-    <t>04:34:23</t>
+    <t>02:04:18</t>
+  </si>
+  <si>
+    <t>03:41:40</t>
   </si>
   <si>
     <t>05:21:09</t>
@@ -226,7 +229,10 @@
     <t>04:33:39</t>
   </si>
   <si>
-    <t>04:35:57</t>
+    <t>02:06:31</t>
+  </si>
+  <si>
+    <t>03:44:02</t>
   </si>
   <si>
     <t>05:24:30</t>
@@ -259,7 +265,10 @@
     <t>04:35:50</t>
   </si>
   <si>
-    <t>04:37:32</t>
+    <t>02:09:29</t>
+  </si>
+  <si>
+    <t>03:46:46</t>
   </si>
   <si>
     <t>05:27:52</t>
@@ -292,7 +301,10 @@
     <t>04:38:01</t>
   </si>
   <si>
-    <t>04:40:34</t>
+    <t>02:12:28</t>
+  </si>
+  <si>
+    <t>03:49:32</t>
   </si>
   <si>
     <t>05:29:59</t>
@@ -325,7 +337,10 @@
     <t>04:40:43</t>
   </si>
   <si>
-    <t>13°</t>
+    <t>02:14:43</t>
+  </si>
+  <si>
+    <t>03:51:55</t>
   </si>
   <si>
     <t>29°</t>
@@ -358,9 +373,6 @@
     <t>16°</t>
   </si>
   <si>
-    <t>04:36:03</t>
-  </si>
-  <si>
     <t>05:22:56</t>
   </si>
   <si>
@@ -388,6 +400,9 @@
     <t>04:36:26</t>
   </si>
   <si>
+    <t>03:49:39</t>
+  </si>
+  <si>
     <t>A+B</t>
   </si>
   <si>
@@ -397,13 +412,13 @@
     <t>A</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -437,7 +452,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -452,13 +467,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -499,7 +532,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -520,6 +553,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -923,7 +965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1001,54 +1043,54 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="L2" s="4">
-        <v>-22.9</v>
+        <v>-14.1</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="O2" s="6">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="7">
+        <v>26</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>5</v>
+      </c>
+      <c r="R2" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1057,54 +1099,54 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L3" s="4">
-        <v>-14.1</v>
+        <v>-23.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="O3" s="6">
-        <v>2</v>
-      </c>
-      <c r="P3" s="7">
+        <v>25</v>
+      </c>
+      <c r="P3" s="9">
         <v>0</v>
       </c>
       <c r="Q3" s="7">
-        <v>2</v>
-      </c>
-      <c r="R3" s="7">
+        <v>23</v>
+      </c>
+      <c r="R3" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1113,54 +1155,54 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="L4" s="4">
-        <v>-23.2</v>
+        <v>-31.5</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="O4" s="6">
-        <v>0</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>0</v>
-      </c>
-      <c r="R4" s="7">
+        <v>133</v>
+      </c>
+      <c r="O4" s="10">
+        <v>0</v>
+      </c>
+      <c r="P4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>0</v>
+      </c>
+      <c r="R4" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1172,51 +1214,51 @@
         <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="L5" s="4">
-        <v>-31.5</v>
+        <v>-14.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O5" s="6">
-        <v>0</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="7">
+        <v>132</v>
+      </c>
+      <c r="O5" s="10">
+        <v>0</v>
+      </c>
+      <c r="P5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>0</v>
+      </c>
+      <c r="R5" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1225,54 +1267,54 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>118</v>
+        <v>53</v>
       </c>
       <c r="L6" s="4">
-        <v>-14.4</v>
+        <v>-38.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="7">
+        <v>133</v>
+      </c>
+      <c r="O6" s="10">
+        <v>0</v>
+      </c>
+      <c r="P6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>0</v>
+      </c>
+      <c r="R6" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1281,54 +1323,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="L7" s="4">
-        <v>-38.5</v>
+        <v>-23.6</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O7" s="6">
-        <v>0</v>
-      </c>
-      <c r="P7" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-      <c r="R7" s="7">
+        <v>132</v>
+      </c>
+      <c r="O7" s="10">
+        <v>0</v>
+      </c>
+      <c r="P7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>0</v>
+      </c>
+      <c r="R7" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1337,54 +1379,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="L8" s="4">
-        <v>-23.6</v>
+        <v>-31.9</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-      <c r="R8" s="7">
+        <v>132</v>
+      </c>
+      <c r="O8" s="10">
+        <v>0</v>
+      </c>
+      <c r="P8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>0</v>
+      </c>
+      <c r="R8" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1393,55 +1435,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="L9" s="4">
-        <v>-31.9</v>
+        <v>-14.6</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="O9" s="6">
-        <v>2</v>
-      </c>
-      <c r="P9" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>0</v>
-      </c>
-      <c r="R9" s="7">
-        <v>2</v>
+        <v>134</v>
+      </c>
+      <c r="O9" s="10">
+        <v>0</v>
+      </c>
+      <c r="P9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>0</v>
+      </c>
+      <c r="R9" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1449,55 +1491,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="L10" s="4">
-        <v>-14.6</v>
+        <v>-39</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="O10" s="6">
-        <v>1</v>
-      </c>
-      <c r="P10" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>0</v>
-      </c>
-      <c r="R10" s="7">
-        <v>1</v>
+        <v>133</v>
+      </c>
+      <c r="O10" s="10">
+        <v>0</v>
+      </c>
+      <c r="P10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0</v>
+      </c>
+      <c r="R10" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1505,54 +1547,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>16</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="F11" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L11" s="4">
-        <v>-39</v>
+        <v>-23.9</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O11" s="6">
-        <v>0</v>
-      </c>
-      <c r="P11" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>0</v>
-      </c>
-      <c r="R11" s="7">
+        <v>132</v>
+      </c>
+      <c r="O11" s="10">
+        <v>0</v>
+      </c>
+      <c r="P11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>0</v>
+      </c>
+      <c r="R11" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1561,114 +1603,170 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>113</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="L12" s="4">
-        <v>-23.9</v>
+        <v>-44.2</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="N12" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O12" s="10">
+        <v>0</v>
+      </c>
+      <c r="P12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>0</v>
+      </c>
+      <c r="R12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="2">
+        <v>23</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="O12" s="6">
-        <v>0</v>
-      </c>
-      <c r="P12" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>0</v>
-      </c>
-      <c r="R12" s="7">
+      <c r="L13" s="4">
+        <v>-32.4</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O13" s="10">
+        <v>0</v>
+      </c>
+      <c r="P13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>0</v>
+      </c>
+      <c r="R13" s="9">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A12">
+  <conditionalFormatting sqref="A2:A13">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B12">
+  <conditionalFormatting sqref="B2:B13">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C12">
+  <conditionalFormatting sqref="C2:C13">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D12">
+  <conditionalFormatting sqref="D2:D13">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E12">
+  <conditionalFormatting sqref="E2:E13">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F12">
+  <conditionalFormatting sqref="F2:F13">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G12">
+  <conditionalFormatting sqref="G2:G13">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H12">
+  <conditionalFormatting sqref="H2:H13">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I12">
+  <conditionalFormatting sqref="I2:I13">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J12">
+  <conditionalFormatting sqref="J2:J13">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K12">
+  <conditionalFormatting sqref="K2:K13">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L12">
+  <conditionalFormatting sqref="L2:L13">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1687,12 +1785,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M12">
+  <conditionalFormatting sqref="M2:M13">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N12">
+  <conditionalFormatting sqref="N2:N13">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1709,22 +1807,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O12">
+  <conditionalFormatting sqref="O2:O13">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P12">
+  <conditionalFormatting sqref="P2:P13">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q12">
+  <conditionalFormatting sqref="Q2:Q13">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R12">
+  <conditionalFormatting sqref="R2:R13">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="139">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260805--01</t>
-  </si>
-  <si>
     <t>20260806--01</t>
   </si>
   <si>
@@ -106,13 +103,16 @@
     <t>20260811--02</t>
   </si>
   <si>
-    <t>06:43</t>
+    <t>20260812--01</t>
+  </si>
+  <si>
+    <t>20260812--02</t>
   </si>
   <si>
     <t>06:28</t>
   </si>
   <si>
-    <t>05:42</t>
+    <t>05:43</t>
   </si>
   <si>
     <t>05:47</t>
@@ -121,7 +121,7 @@
     <t>04:02</t>
   </si>
   <si>
-    <t>06:23</t>
+    <t>06:24</t>
   </si>
   <si>
     <t>06:40</t>
@@ -133,16 +133,19 @@
     <t>06:33</t>
   </si>
   <si>
-    <t>04:22</t>
+    <t>04:21</t>
   </si>
   <si>
     <t>05:57</t>
   </si>
   <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>04:56</t>
+    <t>05:29</t>
+  </si>
+  <si>
+    <t>04:36</t>
+  </si>
+  <si>
+    <t>06:13</t>
   </si>
   <si>
     <t>02:31</t>
@@ -151,256 +154,265 @@
     <t>00:00</t>
   </si>
   <si>
-    <t>04:18</t>
-  </si>
-  <si>
-    <t>02:18</t>
-  </si>
-  <si>
-    <t>00:14</t>
+    <t>04:19</t>
+  </si>
+  <si>
+    <t>02:19</t>
+  </si>
+  <si>
+    <t>00:15</t>
   </si>
   <si>
     <t>01:35</t>
   </si>
   <si>
-    <t>05:19:04</t>
-  </si>
-  <si>
     <t>04:30:38</t>
   </si>
   <si>
-    <t>03:42:19</t>
-  </si>
-  <si>
-    <t>05:19:31</t>
-  </si>
-  <si>
-    <t>02:54:09</t>
-  </si>
-  <si>
-    <t>04:30:35</t>
-  </si>
-  <si>
-    <t>03:41:44</t>
-  </si>
-  <si>
-    <t>05:20:20</t>
-  </si>
-  <si>
-    <t>02:52:57</t>
-  </si>
-  <si>
-    <t>04:30:59</t>
-  </si>
-  <si>
-    <t>02:04:18</t>
-  </si>
-  <si>
-    <t>03:41:40</t>
-  </si>
-  <si>
-    <t>05:21:09</t>
+    <t>03:42:20</t>
+  </si>
+  <si>
+    <t>05:19:32</t>
+  </si>
+  <si>
+    <t>02:54:13</t>
+  </si>
+  <si>
+    <t>04:30:39</t>
+  </si>
+  <si>
+    <t>03:41:51</t>
+  </si>
+  <si>
+    <t>05:20:27</t>
+  </si>
+  <si>
+    <t>02:53:09</t>
+  </si>
+  <si>
+    <t>04:31:11</t>
+  </si>
+  <si>
+    <t>02:04:35</t>
+  </si>
+  <si>
+    <t>03:41:58</t>
+  </si>
+  <si>
+    <t>01:16:09</t>
+  </si>
+  <si>
+    <t>02:52:49</t>
   </si>
   <si>
     <t>04:32:46</t>
   </si>
   <si>
-    <t>03:44:36</t>
-  </si>
-  <si>
-    <t>05:21:49</t>
-  </si>
-  <si>
-    <t>02:56:51</t>
-  </si>
-  <si>
-    <t>04:32:45</t>
-  </si>
-  <si>
-    <t>03:43:49</t>
-  </si>
-  <si>
-    <t>05:23:36</t>
-  </si>
-  <si>
-    <t>02:55:04</t>
-  </si>
-  <si>
-    <t>04:33:39</t>
-  </si>
-  <si>
-    <t>02:06:31</t>
-  </si>
-  <si>
-    <t>03:44:02</t>
-  </si>
-  <si>
-    <t>05:24:30</t>
+    <t>03:44:37</t>
+  </si>
+  <si>
+    <t>05:21:51</t>
+  </si>
+  <si>
+    <t>02:56:55</t>
+  </si>
+  <si>
+    <t>04:32:49</t>
+  </si>
+  <si>
+    <t>03:43:57</t>
+  </si>
+  <si>
+    <t>05:23:44</t>
+  </si>
+  <si>
+    <t>02:55:16</t>
+  </si>
+  <si>
+    <t>04:33:52</t>
+  </si>
+  <si>
+    <t>02:06:48</t>
+  </si>
+  <si>
+    <t>03:44:20</t>
+  </si>
+  <si>
+    <t>01:18:42</t>
+  </si>
+  <si>
+    <t>02:55:00</t>
   </si>
   <si>
     <t>04:35:59</t>
   </si>
   <si>
-    <t>03:47:26</t>
-  </si>
-  <si>
-    <t>05:24:42</t>
-  </si>
-  <si>
-    <t>02:58:52</t>
-  </si>
-  <si>
-    <t>04:35:56</t>
-  </si>
-  <si>
-    <t>03:47:08</t>
-  </si>
-  <si>
-    <t>05:24:52</t>
-  </si>
-  <si>
-    <t>02:58:19</t>
-  </si>
-  <si>
-    <t>04:35:50</t>
-  </si>
-  <si>
-    <t>02:09:29</t>
-  </si>
-  <si>
-    <t>03:46:46</t>
-  </si>
-  <si>
-    <t>05:27:52</t>
+    <t>03:47:28</t>
+  </si>
+  <si>
+    <t>05:24:44</t>
+  </si>
+  <si>
+    <t>02:58:56</t>
+  </si>
+  <si>
+    <t>04:36:00</t>
+  </si>
+  <si>
+    <t>03:47:16</t>
+  </si>
+  <si>
+    <t>05:25:00</t>
+  </si>
+  <si>
+    <t>02:58:31</t>
+  </si>
+  <si>
+    <t>04:36:02</t>
+  </si>
+  <si>
+    <t>02:09:46</t>
+  </si>
+  <si>
+    <t>03:47:04</t>
+  </si>
+  <si>
+    <t>01:21:00</t>
+  </si>
+  <si>
+    <t>02:58:06</t>
   </si>
   <si>
     <t>04:39:14</t>
   </si>
   <si>
-    <t>03:50:18</t>
-  </si>
-  <si>
-    <t>05:27:36</t>
-  </si>
-  <si>
-    <t>03:00:53</t>
-  </si>
-  <si>
-    <t>04:39:08</t>
-  </si>
-  <si>
-    <t>03:50:29</t>
-  </si>
-  <si>
-    <t>05:26:08</t>
-  </si>
-  <si>
-    <t>03:01:37</t>
-  </si>
-  <si>
-    <t>04:38:01</t>
-  </si>
-  <si>
-    <t>02:12:28</t>
-  </si>
-  <si>
-    <t>03:49:32</t>
-  </si>
-  <si>
-    <t>05:29:59</t>
-  </si>
-  <si>
-    <t>04:41:23</t>
-  </si>
-  <si>
-    <t>03:52:37</t>
-  </si>
-  <si>
-    <t>05:29:56</t>
-  </si>
-  <si>
-    <t>03:03:37</t>
-  </si>
-  <si>
-    <t>04:41:20</t>
-  </si>
-  <si>
-    <t>03:52:36</t>
-  </si>
-  <si>
-    <t>05:29:26</t>
+    <t>03:50:20</t>
+  </si>
+  <si>
+    <t>05:27:38</t>
+  </si>
+  <si>
+    <t>03:00:57</t>
+  </si>
+  <si>
+    <t>04:39:13</t>
+  </si>
+  <si>
+    <t>03:50:37</t>
+  </si>
+  <si>
+    <t>05:26:16</t>
+  </si>
+  <si>
+    <t>03:01:49</t>
+  </si>
+  <si>
+    <t>04:38:13</t>
+  </si>
+  <si>
+    <t>02:12:45</t>
+  </si>
+  <si>
+    <t>03:49:49</t>
+  </si>
+  <si>
+    <t>01:23:18</t>
+  </si>
+  <si>
+    <t>03:01:13</t>
+  </si>
+  <si>
+    <t>04:41:24</t>
+  </si>
+  <si>
+    <t>03:52:39</t>
+  </si>
+  <si>
+    <t>05:29:58</t>
+  </si>
+  <si>
+    <t>03:03:41</t>
+  </si>
+  <si>
+    <t>03:52:44</t>
+  </si>
+  <si>
+    <t>05:29:34</t>
+  </si>
+  <si>
+    <t>03:03:56</t>
+  </si>
+  <si>
+    <t>04:40:55</t>
+  </si>
+  <si>
+    <t>02:15:00</t>
+  </si>
+  <si>
+    <t>03:52:13</t>
+  </si>
+  <si>
+    <t>01:25:52</t>
+  </si>
+  <si>
+    <t>03:03:26</t>
+  </si>
+  <si>
+    <t>39°</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>20°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>33°</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>9°</t>
+  </si>
+  <si>
+    <t>1°</t>
+  </si>
+  <si>
+    <t>16°</t>
+  </si>
+  <si>
+    <t>04:36:43</t>
+  </si>
+  <si>
+    <t>03:50:25</t>
+  </si>
+  <si>
+    <t>05:23:19</t>
+  </si>
+  <si>
+    <t>04:36:54</t>
+  </si>
+  <si>
+    <t>03:50:22</t>
+  </si>
+  <si>
+    <t>05:23:15</t>
   </si>
   <si>
     <t>03:03:44</t>
   </si>
   <si>
-    <t>04:40:43</t>
-  </si>
-  <si>
-    <t>02:14:43</t>
-  </si>
-  <si>
-    <t>03:51:55</t>
-  </si>
-  <si>
-    <t>29°</t>
-  </si>
-  <si>
-    <t>39°</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
-    <t>20°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>33°</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>9°</t>
-  </si>
-  <si>
-    <t>1°</t>
-  </si>
-  <si>
-    <t>16°</t>
-  </si>
-  <si>
-    <t>05:22:56</t>
-  </si>
-  <si>
-    <t>04:36:43</t>
-  </si>
-  <si>
-    <t>03:50:23</t>
-  </si>
-  <si>
-    <t>05:23:18</t>
-  </si>
-  <si>
-    <t>04:36:50</t>
-  </si>
-  <si>
-    <t>03:50:15</t>
-  </si>
-  <si>
-    <t>05:23:08</t>
-  </si>
-  <si>
-    <t>03:03:33</t>
-  </si>
-  <si>
-    <t>04:36:26</t>
-  </si>
-  <si>
-    <t>03:49:39</t>
+    <t>04:36:38</t>
+  </si>
+  <si>
+    <t>03:49:55</t>
+  </si>
+  <si>
+    <t>03:03:08</t>
   </si>
   <si>
     <t>A+B</t>
@@ -452,7 +464,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -467,13 +479,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -486,12 +492,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -532,7 +532,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -556,12 +556,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -965,7 +959,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1043,54 +1037,54 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="L2" s="4">
-        <v>-14.1</v>
+        <v>-23.2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="O2" s="6">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="P2" s="7">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="Q2" s="8">
-        <v>5</v>
-      </c>
-      <c r="R2" s="9">
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1099,54 +1093,54 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="L3" s="4">
-        <v>-23.2</v>
+        <v>-31.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="O3" s="6">
-        <v>25</v>
-      </c>
-      <c r="P3" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>23</v>
-      </c>
-      <c r="R3" s="9">
+        <v>0</v>
+      </c>
+      <c r="P3" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>0</v>
+      </c>
+      <c r="R3" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1158,51 +1152,51 @@
         <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="L4" s="4">
-        <v>-31.5</v>
+        <v>-14.3</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O4" s="10">
-        <v>0</v>
-      </c>
-      <c r="P4" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="9">
-        <v>0</v>
-      </c>
-      <c r="R4" s="9">
+        <v>136</v>
+      </c>
+      <c r="O4" s="6">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1211,54 +1205,54 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="L5" s="4">
-        <v>-14.4</v>
+        <v>-38.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O5" s="10">
-        <v>0</v>
-      </c>
-      <c r="P5" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>0</v>
-      </c>
-      <c r="R5" s="9">
+        <v>137</v>
+      </c>
+      <c r="O5" s="6">
+        <v>0</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="R5" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1267,54 +1261,54 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="L6" s="4">
-        <v>-38.5</v>
+        <v>-23.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O6" s="10">
-        <v>0</v>
-      </c>
-      <c r="P6" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="9">
-        <v>0</v>
-      </c>
-      <c r="R6" s="9">
+        <v>136</v>
+      </c>
+      <c r="O6" s="6">
+        <v>0</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1323,54 +1317,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L7" s="4">
-        <v>-23.6</v>
+        <v>-31.9</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O7" s="10">
-        <v>0</v>
-      </c>
-      <c r="P7" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="9">
-        <v>0</v>
-      </c>
-      <c r="R7" s="9">
+        <v>136</v>
+      </c>
+      <c r="O7" s="6">
+        <v>0</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
+      <c r="R7" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1379,54 +1373,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="L8" s="4">
-        <v>-31.9</v>
+        <v>-14.6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O8" s="10">
-        <v>0</v>
-      </c>
-      <c r="P8" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="9">
-        <v>0</v>
-      </c>
-      <c r="R8" s="9">
+        <v>138</v>
+      </c>
+      <c r="O8" s="6">
+        <v>0</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1435,54 +1429,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="L9" s="4">
-        <v>-14.6</v>
+        <v>-38.9</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="O9" s="10">
-        <v>0</v>
-      </c>
-      <c r="P9" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="9">
-        <v>0</v>
-      </c>
-      <c r="R9" s="9">
+        <v>137</v>
+      </c>
+      <c r="O9" s="6">
+        <v>0</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1491,54 +1485,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>16</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="F10" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L10" s="4">
-        <v>-39</v>
+        <v>-23.9</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O10" s="10">
-        <v>0</v>
-      </c>
-      <c r="P10" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="9">
-        <v>0</v>
-      </c>
-      <c r="R10" s="9">
+        <v>136</v>
+      </c>
+      <c r="O10" s="6">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1547,54 +1541,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>127</v>
+        <v>59</v>
       </c>
       <c r="L11" s="4">
-        <v>-23.9</v>
+        <v>-44.2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O11" s="10">
-        <v>0</v>
-      </c>
-      <c r="P11" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="9">
-        <v>0</v>
-      </c>
-      <c r="R11" s="9">
+        <v>137</v>
+      </c>
+      <c r="O11" s="6">
+        <v>0</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>0</v>
+      </c>
+      <c r="R11" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1603,54 +1597,54 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="L12" s="4">
-        <v>-44.2</v>
+        <v>-32.3</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O12" s="10">
-        <v>0</v>
-      </c>
-      <c r="P12" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="9">
-        <v>0</v>
-      </c>
-      <c r="R12" s="9">
+        <v>137</v>
+      </c>
+      <c r="O12" s="6">
+        <v>0</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1659,114 +1653,170 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>128</v>
+        <v>61</v>
       </c>
       <c r="L13" s="4">
-        <v>-32.4</v>
+        <v>-46.6</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O13" s="10">
-        <v>0</v>
-      </c>
-      <c r="P13" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="9">
-        <v>0</v>
-      </c>
-      <c r="R13" s="9">
+        <v>137</v>
+      </c>
+      <c r="O13" s="6">
+        <v>0</v>
+      </c>
+      <c r="P13" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>0</v>
+      </c>
+      <c r="R13" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="2">
+        <v>36</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="L14" s="4">
+        <v>-39.5</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="O14" s="6">
+        <v>0</v>
+      </c>
+      <c r="P14" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>0</v>
+      </c>
+      <c r="R14" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A13">
+  <conditionalFormatting sqref="A2:A14">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B13">
+  <conditionalFormatting sqref="B2:B14">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C13">
+  <conditionalFormatting sqref="C2:C14">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D13">
+  <conditionalFormatting sqref="D2:D14">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E13">
+  <conditionalFormatting sqref="E2:E14">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F13">
+  <conditionalFormatting sqref="F2:F14">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G13">
+  <conditionalFormatting sqref="G2:G14">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H13">
+  <conditionalFormatting sqref="H2:H14">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I13">
+  <conditionalFormatting sqref="I2:I14">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J13">
+  <conditionalFormatting sqref="J2:J14">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K13">
+  <conditionalFormatting sqref="K2:K14">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L13">
+  <conditionalFormatting sqref="L2:L14">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1785,12 +1835,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M13">
+  <conditionalFormatting sqref="M2:M14">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N13">
+  <conditionalFormatting sqref="N2:N14">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1807,22 +1857,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O13">
+  <conditionalFormatting sqref="O2:O14">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P13">
+  <conditionalFormatting sqref="P2:P14">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q13">
+  <conditionalFormatting sqref="Q2:Q14">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R13">
+  <conditionalFormatting sqref="R2:R14">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="146">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260806--01</t>
-  </si>
-  <si>
     <t>20260807--01</t>
   </si>
   <si>
@@ -109,10 +106,13 @@
     <t>20260812--02</t>
   </si>
   <si>
-    <t>06:28</t>
-  </si>
-  <si>
-    <t>05:43</t>
+    <t>20260813--01</t>
+  </si>
+  <si>
+    <t>20260813--02</t>
+  </si>
+  <si>
+    <t>05:42</t>
   </si>
   <si>
     <t>05:47</t>
@@ -127,28 +127,31 @@
     <t>06:40</t>
   </si>
   <si>
-    <t>02:32</t>
+    <t>02:31</t>
   </si>
   <si>
     <t>06:33</t>
   </si>
   <si>
-    <t>04:21</t>
-  </si>
-  <si>
-    <t>05:57</t>
+    <t>04:22</t>
+  </si>
+  <si>
+    <t>05:58</t>
   </si>
   <si>
     <t>05:29</t>
   </si>
   <si>
-    <t>04:36</t>
+    <t>04:38</t>
   </si>
   <si>
     <t>06:13</t>
   </si>
   <si>
-    <t>02:31</t>
+    <t>06:36</t>
+  </si>
+  <si>
+    <t>01:29</t>
   </si>
   <si>
     <t>00:00</t>
@@ -157,208 +160,223 @@
     <t>04:19</t>
   </si>
   <si>
-    <t>02:19</t>
+    <t>02:20</t>
   </si>
   <si>
     <t>00:15</t>
   </si>
   <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>04:30:38</t>
-  </si>
-  <si>
-    <t>03:42:20</t>
-  </si>
-  <si>
-    <t>05:19:32</t>
-  </si>
-  <si>
-    <t>02:54:13</t>
-  </si>
-  <si>
-    <t>04:30:39</t>
-  </si>
-  <si>
-    <t>03:41:51</t>
-  </si>
-  <si>
-    <t>05:20:27</t>
-  </si>
-  <si>
-    <t>02:53:09</t>
-  </si>
-  <si>
-    <t>04:31:11</t>
-  </si>
-  <si>
-    <t>02:04:35</t>
-  </si>
-  <si>
-    <t>03:41:58</t>
-  </si>
-  <si>
-    <t>01:16:09</t>
-  </si>
-  <si>
-    <t>02:52:49</t>
-  </si>
-  <si>
-    <t>04:32:46</t>
-  </si>
-  <si>
-    <t>03:44:37</t>
-  </si>
-  <si>
-    <t>05:21:51</t>
-  </si>
-  <si>
-    <t>02:56:55</t>
-  </si>
-  <si>
-    <t>04:32:49</t>
-  </si>
-  <si>
-    <t>03:43:57</t>
-  </si>
-  <si>
-    <t>05:23:44</t>
+    <t>01:36</t>
+  </si>
+  <si>
+    <t>03:42:22</t>
+  </si>
+  <si>
+    <t>05:19:34</t>
+  </si>
+  <si>
+    <t>02:54:15</t>
+  </si>
+  <si>
+    <t>04:30:42</t>
+  </si>
+  <si>
+    <t>03:41:57</t>
+  </si>
+  <si>
+    <t>05:20:33</t>
+  </si>
+  <si>
+    <t>02:53:17</t>
+  </si>
+  <si>
+    <t>04:31:20</t>
+  </si>
+  <si>
+    <t>02:04:46</t>
+  </si>
+  <si>
+    <t>03:42:10</t>
+  </si>
+  <si>
+    <t>01:16:25</t>
+  </si>
+  <si>
+    <t>02:53:05</t>
+  </si>
+  <si>
+    <t>02:04:05</t>
+  </si>
+  <si>
+    <t>03:42:50</t>
+  </si>
+  <si>
+    <t>03:44:39</t>
+  </si>
+  <si>
+    <t>05:21:52</t>
+  </si>
+  <si>
+    <t>02:56:58</t>
+  </si>
+  <si>
+    <t>04:32:52</t>
+  </si>
+  <si>
+    <t>03:44:02</t>
+  </si>
+  <si>
+    <t>05:23:50</t>
+  </si>
+  <si>
+    <t>02:55:24</t>
+  </si>
+  <si>
+    <t>04:34:00</t>
+  </si>
+  <si>
+    <t>02:06:59</t>
+  </si>
+  <si>
+    <t>03:44:32</t>
+  </si>
+  <si>
+    <t>01:18:57</t>
   </si>
   <si>
     <t>02:55:16</t>
   </si>
   <si>
-    <t>04:33:52</t>
-  </si>
-  <si>
-    <t>02:06:48</t>
-  </si>
-  <si>
-    <t>03:44:20</t>
-  </si>
-  <si>
-    <t>01:18:42</t>
-  </si>
-  <si>
-    <t>02:55:00</t>
-  </si>
-  <si>
-    <t>04:35:59</t>
-  </si>
-  <si>
-    <t>03:47:28</t>
-  </si>
-  <si>
-    <t>05:24:44</t>
-  </si>
-  <si>
-    <t>02:58:56</t>
-  </si>
-  <si>
-    <t>04:36:00</t>
+    <t>02:06:11</t>
+  </si>
+  <si>
+    <t>03:46:31</t>
+  </si>
+  <si>
+    <t>03:47:29</t>
+  </si>
+  <si>
+    <t>05:24:45</t>
+  </si>
+  <si>
+    <t>02:58:59</t>
+  </si>
+  <si>
+    <t>04:36:03</t>
+  </si>
+  <si>
+    <t>03:47:21</t>
+  </si>
+  <si>
+    <t>05:25:05</t>
+  </si>
+  <si>
+    <t>02:58:39</t>
+  </si>
+  <si>
+    <t>04:36:10</t>
+  </si>
+  <si>
+    <t>02:09:58</t>
   </si>
   <si>
     <t>03:47:16</t>
   </si>
   <si>
-    <t>05:25:00</t>
-  </si>
-  <si>
-    <t>02:58:31</t>
-  </si>
-  <si>
-    <t>04:36:02</t>
-  </si>
-  <si>
-    <t>02:09:46</t>
-  </si>
-  <si>
-    <t>03:47:04</t>
-  </si>
-  <si>
-    <t>01:21:00</t>
-  </si>
-  <si>
-    <t>02:58:06</t>
-  </si>
-  <si>
-    <t>04:39:14</t>
-  </si>
-  <si>
-    <t>03:50:20</t>
-  </si>
-  <si>
-    <t>05:27:38</t>
-  </si>
-  <si>
-    <t>03:00:57</t>
-  </si>
-  <si>
-    <t>04:39:13</t>
-  </si>
-  <si>
-    <t>03:50:37</t>
-  </si>
-  <si>
-    <t>05:26:16</t>
-  </si>
-  <si>
-    <t>03:01:49</t>
-  </si>
-  <si>
-    <t>04:38:13</t>
-  </si>
-  <si>
-    <t>02:12:45</t>
-  </si>
-  <si>
-    <t>03:49:49</t>
-  </si>
-  <si>
-    <t>01:23:18</t>
-  </si>
-  <si>
-    <t>03:01:13</t>
-  </si>
-  <si>
-    <t>04:41:24</t>
-  </si>
-  <si>
-    <t>03:52:39</t>
-  </si>
-  <si>
-    <t>05:29:58</t>
-  </si>
-  <si>
-    <t>03:03:41</t>
-  </si>
-  <si>
-    <t>03:52:44</t>
-  </si>
-  <si>
-    <t>05:29:34</t>
-  </si>
-  <si>
-    <t>03:03:56</t>
-  </si>
-  <si>
-    <t>04:40:55</t>
-  </si>
-  <si>
-    <t>02:15:00</t>
-  </si>
-  <si>
-    <t>03:52:13</t>
-  </si>
-  <si>
-    <t>01:25:52</t>
-  </si>
-  <si>
-    <t>03:03:26</t>
-  </si>
-  <si>
-    <t>39°</t>
+    <t>01:21:15</t>
+  </si>
+  <si>
+    <t>02:58:22</t>
+  </si>
+  <si>
+    <t>02:09:28</t>
+  </si>
+  <si>
+    <t>03:47:15</t>
+  </si>
+  <si>
+    <t>03:50:21</t>
+  </si>
+  <si>
+    <t>05:27:39</t>
+  </si>
+  <si>
+    <t>03:01:00</t>
+  </si>
+  <si>
+    <t>04:39:16</t>
+  </si>
+  <si>
+    <t>03:50:42</t>
+  </si>
+  <si>
+    <t>05:26:21</t>
+  </si>
+  <si>
+    <t>03:01:57</t>
+  </si>
+  <si>
+    <t>04:38:22</t>
+  </si>
+  <si>
+    <t>02:12:57</t>
+  </si>
+  <si>
+    <t>03:50:01</t>
+  </si>
+  <si>
+    <t>01:23:35</t>
+  </si>
+  <si>
+    <t>03:01:29</t>
+  </si>
+  <si>
+    <t>02:12:47</t>
+  </si>
+  <si>
+    <t>03:48:00</t>
+  </si>
+  <si>
+    <t>03:52:40</t>
+  </si>
+  <si>
+    <t>05:29:59</t>
+  </si>
+  <si>
+    <t>03:03:44</t>
+  </si>
+  <si>
+    <t>04:41:27</t>
+  </si>
+  <si>
+    <t>03:52:49</t>
+  </si>
+  <si>
+    <t>05:29:40</t>
+  </si>
+  <si>
+    <t>03:04:05</t>
+  </si>
+  <si>
+    <t>04:41:04</t>
+  </si>
+  <si>
+    <t>02:15:12</t>
+  </si>
+  <si>
+    <t>03:52:25</t>
+  </si>
+  <si>
+    <t>01:26:08</t>
+  </si>
+  <si>
+    <t>03:03:42</t>
+  </si>
+  <si>
+    <t>02:14:54</t>
+  </si>
+  <si>
+    <t>03:51:42</t>
   </si>
   <si>
     <t>10°</t>
@@ -385,49 +403,52 @@
     <t>16°</t>
   </si>
   <si>
-    <t>04:36:43</t>
-  </si>
-  <si>
-    <t>03:50:25</t>
-  </si>
-  <si>
-    <t>05:23:19</t>
-  </si>
-  <si>
-    <t>04:36:54</t>
-  </si>
-  <si>
-    <t>03:50:22</t>
-  </si>
-  <si>
-    <t>05:23:15</t>
-  </si>
-  <si>
-    <t>03:03:44</t>
-  </si>
-  <si>
-    <t>04:36:38</t>
-  </si>
-  <si>
-    <t>03:49:55</t>
-  </si>
-  <si>
-    <t>03:03:08</t>
+    <t>7°</t>
+  </si>
+  <si>
+    <t>03:50:26</t>
+  </si>
+  <si>
+    <t>05:23:20</t>
+  </si>
+  <si>
+    <t>04:36:56</t>
+  </si>
+  <si>
+    <t>03:50:27</t>
+  </si>
+  <si>
+    <t>05:23:21</t>
+  </si>
+  <si>
+    <t>03:03:52</t>
+  </si>
+  <si>
+    <t>04:36:46</t>
+  </si>
+  <si>
+    <t>03:50:07</t>
+  </si>
+  <si>
+    <t>03:03:24</t>
+  </si>
+  <si>
+    <t>03:49:31</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>4</t>
@@ -464,7 +485,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -480,12 +501,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -532,7 +547,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -553,9 +568,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -959,7 +971,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1037,54 +1049,54 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="L2" s="4">
-        <v>-23.2</v>
+        <v>-31.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="O2" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P2" s="7">
-        <v>4</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1096,51 +1108,51 @@
         <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="L3" s="4">
-        <v>-31.5</v>
+        <v>-14.3</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="O3" s="6">
         <v>0</v>
       </c>
-      <c r="P3" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>0</v>
-      </c>
-      <c r="R3" s="8">
+      <c r="P3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1149,54 +1161,54 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>125</v>
+        <v>53</v>
       </c>
       <c r="L4" s="4">
-        <v>-14.3</v>
+        <v>-38.5</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="O4" s="6">
         <v>0</v>
       </c>
-      <c r="P4" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="8">
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>0</v>
+      </c>
+      <c r="R4" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1205,54 +1217,54 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="L5" s="4">
-        <v>-38.5</v>
+        <v>-23.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="O5" s="6">
         <v>0</v>
       </c>
-      <c r="P5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>0</v>
-      </c>
-      <c r="R5" s="8">
+      <c r="P5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>0</v>
+      </c>
+      <c r="R5" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1261,54 +1273,54 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="L6" s="4">
-        <v>-23.5</v>
+        <v>-31.9</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="O6" s="6">
         <v>0</v>
       </c>
-      <c r="P6" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>0</v>
-      </c>
-      <c r="R6" s="8">
+      <c r="P6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>0</v>
+      </c>
+      <c r="R6" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1317,54 +1329,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="L7" s="4">
-        <v>-31.9</v>
+        <v>-14.5</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="O7" s="6">
         <v>0</v>
       </c>
-      <c r="P7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>0</v>
-      </c>
-      <c r="R7" s="8">
+      <c r="P7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1373,54 +1385,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="L8" s="4">
-        <v>-14.6</v>
+        <v>-38.9</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="O8" s="6">
         <v>0</v>
       </c>
-      <c r="P8" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>0</v>
-      </c>
-      <c r="R8" s="8">
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1429,54 +1441,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>16</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="F9" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="L9" s="4">
-        <v>-38.9</v>
+        <v>-23.9</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="O9" s="6">
         <v>0</v>
       </c>
-      <c r="P9" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8">
+      <c r="P9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1485,54 +1497,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>130</v>
+        <v>59</v>
       </c>
       <c r="L10" s="4">
-        <v>-23.9</v>
+        <v>-44.1</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="O10" s="6">
         <v>0</v>
       </c>
-      <c r="P10" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>0</v>
-      </c>
-      <c r="R10" s="8">
+      <c r="P10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>0</v>
+      </c>
+      <c r="R10" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1541,54 +1553,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>59</v>
+        <v>137</v>
       </c>
       <c r="L11" s="4">
-        <v>-44.2</v>
+        <v>-32.3</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="O11" s="6">
         <v>0</v>
       </c>
-      <c r="P11" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>0</v>
-      </c>
-      <c r="R11" s="8">
+      <c r="P11" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>0</v>
+      </c>
+      <c r="R11" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1597,54 +1609,54 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>131</v>
+        <v>61</v>
       </c>
       <c r="L12" s="4">
-        <v>-32.3</v>
+        <v>-46.6</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="O12" s="6">
         <v>0</v>
       </c>
-      <c r="P12" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>0</v>
-      </c>
-      <c r="R12" s="8">
+      <c r="P12" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>0</v>
+      </c>
+      <c r="R12" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1653,54 +1665,54 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="L13" s="4">
-        <v>-46.6</v>
+        <v>-39.4</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="O13" s="6">
         <v>0</v>
       </c>
-      <c r="P13" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>0</v>
-      </c>
-      <c r="R13" s="8">
+      <c r="P13" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>0</v>
+      </c>
+      <c r="R13" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1709,114 +1721,170 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L14" s="4">
+        <v>-44.7</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="O14" s="6">
+        <v>0</v>
+      </c>
+      <c r="P14" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>0</v>
+      </c>
+      <c r="R14" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="2">
+        <v>11</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="L14" s="4">
-        <v>-39.5</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O14" s="6">
-        <v>0</v>
-      </c>
-      <c r="P14" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>0</v>
-      </c>
-      <c r="R14" s="8">
+      <c r="D15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="L15" s="4">
+        <v>-32.7</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="O15" s="6">
+        <v>0</v>
+      </c>
+      <c r="P15" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>0</v>
+      </c>
+      <c r="R15" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A14">
+  <conditionalFormatting sqref="A2:A15">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B14">
+  <conditionalFormatting sqref="B2:B15">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C14">
+  <conditionalFormatting sqref="C2:C15">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D14">
+  <conditionalFormatting sqref="D2:D15">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E14">
+  <conditionalFormatting sqref="E2:E15">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F14">
+  <conditionalFormatting sqref="F2:F15">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G14">
+  <conditionalFormatting sqref="G2:G15">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H14">
+  <conditionalFormatting sqref="H2:H15">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I14">
+  <conditionalFormatting sqref="I2:I15">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J14">
+  <conditionalFormatting sqref="J2:J15">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K14">
+  <conditionalFormatting sqref="K2:K15">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L14">
+  <conditionalFormatting sqref="L2:L15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1835,12 +1903,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M14">
+  <conditionalFormatting sqref="M2:M15">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N14">
+  <conditionalFormatting sqref="N2:N15">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1857,22 +1925,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O14">
+  <conditionalFormatting sqref="O2:O15">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P14">
+  <conditionalFormatting sqref="P2:P15">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q14">
+  <conditionalFormatting sqref="Q2:Q15">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R14">
+  <conditionalFormatting sqref="R2:R15">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="143">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260807--01</t>
-  </si>
-  <si>
-    <t>20260807--02</t>
-  </si>
-  <si>
     <t>20260808--01</t>
   </si>
   <si>
@@ -112,10 +106,10 @@
     <t>20260813--02</t>
   </si>
   <si>
-    <t>05:42</t>
-  </si>
-  <si>
-    <t>05:47</t>
+    <t>20260814--01</t>
+  </si>
+  <si>
+    <t>20260814--02</t>
   </si>
   <si>
     <t>04:02</t>
@@ -127,13 +121,13 @@
     <t>06:40</t>
   </si>
   <si>
-    <t>02:31</t>
+    <t>02:32</t>
   </si>
   <si>
     <t>06:33</t>
   </si>
   <si>
-    <t>04:22</t>
+    <t>04:21</t>
   </si>
   <si>
     <t>05:58</t>
@@ -145,21 +139,24 @@
     <t>04:38</t>
   </si>
   <si>
-    <t>06:13</t>
+    <t>06:12</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>01:28</t>
   </si>
   <si>
     <t>06:36</t>
   </si>
   <si>
-    <t>01:29</t>
+    <t>03:53</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>04:19</t>
-  </si>
-  <si>
     <t>02:20</t>
   </si>
   <si>
@@ -169,271 +166,265 @@
     <t>01:36</t>
   </si>
   <si>
-    <t>03:42:22</t>
-  </si>
-  <si>
-    <t>05:19:34</t>
-  </si>
-  <si>
-    <t>02:54:15</t>
-  </si>
-  <si>
-    <t>04:30:42</t>
-  </si>
-  <si>
-    <t>03:41:57</t>
-  </si>
-  <si>
-    <t>05:20:33</t>
-  </si>
-  <si>
-    <t>02:53:17</t>
-  </si>
-  <si>
-    <t>04:31:20</t>
-  </si>
-  <si>
-    <t>02:04:46</t>
-  </si>
-  <si>
-    <t>03:42:10</t>
-  </si>
-  <si>
-    <t>01:16:25</t>
-  </si>
-  <si>
-    <t>02:53:05</t>
-  </si>
-  <si>
-    <t>02:04:05</t>
-  </si>
-  <si>
-    <t>03:42:50</t>
-  </si>
-  <si>
-    <t>03:44:39</t>
-  </si>
-  <si>
-    <t>05:21:52</t>
-  </si>
-  <si>
-    <t>02:56:58</t>
-  </si>
-  <si>
-    <t>04:32:52</t>
-  </si>
-  <si>
-    <t>03:44:02</t>
-  </si>
-  <si>
-    <t>05:23:50</t>
+    <t>02:54:16</t>
+  </si>
+  <si>
+    <t>04:30:43</t>
+  </si>
+  <si>
+    <t>03:41:59</t>
+  </si>
+  <si>
+    <t>05:20:35</t>
+  </si>
+  <si>
+    <t>02:53:21</t>
+  </si>
+  <si>
+    <t>04:31:23</t>
+  </si>
+  <si>
+    <t>02:04:51</t>
+  </si>
+  <si>
+    <t>03:42:15</t>
+  </si>
+  <si>
+    <t>01:16:32</t>
+  </si>
+  <si>
+    <t>02:53:12</t>
+  </si>
+  <si>
+    <t>02:04:15</t>
+  </si>
+  <si>
+    <t>03:43:00</t>
+  </si>
+  <si>
+    <t>01:15:25</t>
+  </si>
+  <si>
+    <t>02:53:37</t>
+  </si>
+  <si>
+    <t>02:56:59</t>
+  </si>
+  <si>
+    <t>04:32:53</t>
+  </si>
+  <si>
+    <t>03:44:04</t>
+  </si>
+  <si>
+    <t>05:23:52</t>
+  </si>
+  <si>
+    <t>02:55:27</t>
+  </si>
+  <si>
+    <t>04:34:04</t>
+  </si>
+  <si>
+    <t>02:07:04</t>
+  </si>
+  <si>
+    <t>03:44:37</t>
+  </si>
+  <si>
+    <t>01:19:04</t>
   </si>
   <si>
     <t>02:55:24</t>
   </si>
   <si>
-    <t>04:34:00</t>
-  </si>
-  <si>
-    <t>02:06:59</t>
-  </si>
-  <si>
-    <t>03:44:32</t>
-  </si>
-  <si>
-    <t>01:18:57</t>
-  </si>
-  <si>
-    <t>02:55:16</t>
-  </si>
-  <si>
-    <t>02:06:11</t>
-  </si>
-  <si>
-    <t>03:46:31</t>
-  </si>
-  <si>
-    <t>03:47:29</t>
-  </si>
-  <si>
-    <t>05:24:45</t>
-  </si>
-  <si>
-    <t>02:58:59</t>
-  </si>
-  <si>
-    <t>04:36:03</t>
+    <t>02:06:21</t>
+  </si>
+  <si>
+    <t>03:46:41</t>
+  </si>
+  <si>
+    <t>01:17:30</t>
+  </si>
+  <si>
+    <t>02:56:25</t>
+  </si>
+  <si>
+    <t>02:59:00</t>
+  </si>
+  <si>
+    <t>04:36:04</t>
+  </si>
+  <si>
+    <t>03:47:23</t>
+  </si>
+  <si>
+    <t>05:25:08</t>
+  </si>
+  <si>
+    <t>02:58:42</t>
+  </si>
+  <si>
+    <t>04:36:14</t>
+  </si>
+  <si>
+    <t>02:10:03</t>
   </si>
   <si>
     <t>03:47:21</t>
   </si>
   <si>
-    <t>05:25:05</t>
-  </si>
-  <si>
-    <t>02:58:39</t>
-  </si>
-  <si>
-    <t>04:36:10</t>
-  </si>
-  <si>
-    <t>02:09:58</t>
-  </si>
-  <si>
-    <t>03:47:16</t>
-  </si>
-  <si>
-    <t>01:21:15</t>
-  </si>
-  <si>
-    <t>02:58:22</t>
-  </si>
-  <si>
-    <t>02:09:28</t>
-  </si>
-  <si>
-    <t>03:47:15</t>
-  </si>
-  <si>
-    <t>03:50:21</t>
-  </si>
-  <si>
-    <t>05:27:39</t>
-  </si>
-  <si>
-    <t>03:01:00</t>
-  </si>
-  <si>
-    <t>04:39:16</t>
-  </si>
-  <si>
-    <t>03:50:42</t>
-  </si>
-  <si>
-    <t>05:26:21</t>
-  </si>
-  <si>
-    <t>03:01:57</t>
-  </si>
-  <si>
-    <t>04:38:22</t>
-  </si>
-  <si>
-    <t>02:12:57</t>
-  </si>
-  <si>
-    <t>03:50:01</t>
-  </si>
-  <si>
-    <t>01:23:35</t>
-  </si>
-  <si>
-    <t>03:01:29</t>
-  </si>
-  <si>
-    <t>02:12:47</t>
-  </si>
-  <si>
-    <t>03:48:00</t>
-  </si>
-  <si>
-    <t>03:52:40</t>
-  </si>
-  <si>
-    <t>05:29:59</t>
-  </si>
-  <si>
-    <t>03:03:44</t>
-  </si>
-  <si>
-    <t>04:41:27</t>
-  </si>
-  <si>
-    <t>03:52:49</t>
-  </si>
-  <si>
-    <t>05:29:40</t>
-  </si>
-  <si>
-    <t>03:04:05</t>
-  </si>
-  <si>
-    <t>04:41:04</t>
-  </si>
-  <si>
-    <t>02:15:12</t>
-  </si>
-  <si>
-    <t>03:52:25</t>
-  </si>
-  <si>
-    <t>01:26:08</t>
-  </si>
-  <si>
-    <t>03:03:42</t>
-  </si>
-  <si>
-    <t>02:14:54</t>
-  </si>
-  <si>
-    <t>03:51:42</t>
+    <t>01:21:22</t>
+  </si>
+  <si>
+    <t>02:58:29</t>
+  </si>
+  <si>
+    <t>02:09:38</t>
+  </si>
+  <si>
+    <t>03:47:25</t>
+  </si>
+  <si>
+    <t>01:20:47</t>
+  </si>
+  <si>
+    <t>02:58:21</t>
+  </si>
+  <si>
+    <t>03:01:01</t>
+  </si>
+  <si>
+    <t>04:39:17</t>
+  </si>
+  <si>
+    <t>03:50:44</t>
+  </si>
+  <si>
+    <t>05:26:24</t>
+  </si>
+  <si>
+    <t>03:02:00</t>
+  </si>
+  <si>
+    <t>04:38:25</t>
+  </si>
+  <si>
+    <t>02:13:02</t>
+  </si>
+  <si>
+    <t>03:50:06</t>
+  </si>
+  <si>
+    <t>01:23:42</t>
+  </si>
+  <si>
+    <t>03:01:36</t>
+  </si>
+  <si>
+    <t>02:12:56</t>
+  </si>
+  <si>
+    <t>03:48:09</t>
+  </si>
+  <si>
+    <t>01:24:06</t>
+  </si>
+  <si>
+    <t>03:00:18</t>
+  </si>
+  <si>
+    <t>03:03:45</t>
+  </si>
+  <si>
+    <t>04:41:28</t>
+  </si>
+  <si>
+    <t>03:52:51</t>
+  </si>
+  <si>
+    <t>05:29:42</t>
+  </si>
+  <si>
+    <t>03:04:08</t>
+  </si>
+  <si>
+    <t>04:41:07</t>
+  </si>
+  <si>
+    <t>02:15:17</t>
+  </si>
+  <si>
+    <t>03:52:30</t>
+  </si>
+  <si>
+    <t>01:26:15</t>
+  </si>
+  <si>
+    <t>03:03:49</t>
+  </si>
+  <si>
+    <t>02:15:04</t>
+  </si>
+  <si>
+    <t>03:51:52</t>
+  </si>
+  <si>
+    <t>01:26:13</t>
+  </si>
+  <si>
+    <t>03:03:08</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>33°</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>9°</t>
+  </si>
+  <si>
+    <t>1°</t>
+  </si>
+  <si>
+    <t>16°</t>
   </si>
   <si>
     <t>10°</t>
   </si>
   <si>
-    <t>20°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>33°</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>9°</t>
-  </si>
-  <si>
-    <t>1°</t>
-  </si>
-  <si>
-    <t>16°</t>
-  </si>
-  <si>
     <t>7°</t>
   </si>
   <si>
-    <t>03:50:26</t>
-  </si>
-  <si>
-    <t>05:23:20</t>
-  </si>
-  <si>
-    <t>04:36:56</t>
-  </si>
-  <si>
-    <t>03:50:27</t>
-  </si>
-  <si>
-    <t>05:23:21</t>
-  </si>
-  <si>
-    <t>03:03:52</t>
-  </si>
-  <si>
-    <t>04:36:46</t>
-  </si>
-  <si>
-    <t>03:50:07</t>
-  </si>
-  <si>
-    <t>03:03:24</t>
-  </si>
-  <si>
-    <t>03:49:31</t>
+    <t>04:36:57</t>
+  </si>
+  <si>
+    <t>03:50:29</t>
+  </si>
+  <si>
+    <t>05:23:23</t>
+  </si>
+  <si>
+    <t>03:03:55</t>
+  </si>
+  <si>
+    <t>04:36:49</t>
+  </si>
+  <si>
+    <t>03:50:11</t>
+  </si>
+  <si>
+    <t>03:03:31</t>
+  </si>
+  <si>
+    <t>03:49:40</t>
+  </si>
+  <si>
+    <t>03:02:55</t>
   </si>
   <si>
     <t>B</t>
@@ -485,7 +476,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -507,6 +498,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -547,7 +544,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -568,6 +565,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1049,7 +1049,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>32</v>
@@ -1058,34 +1058,34 @@
         <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="L2" s="4">
-        <v>-31.4</v>
+        <v>-38.5</v>
       </c>
       <c r="M2" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="O2" s="6">
         <v>0</v>
@@ -1105,7 +1105,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>33</v>
@@ -1114,34 +1114,34 @@
         <v>47</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="L3" s="4">
-        <v>-14.3</v>
+        <v>-23.5</v>
       </c>
       <c r="M3" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="O3" s="6">
         <v>0</v>
@@ -1161,43 +1161,43 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>53</v>
+        <v>129</v>
       </c>
       <c r="L4" s="4">
-        <v>-38.5</v>
+        <v>-31.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O4" s="6">
         <v>0</v>
@@ -1217,43 +1217,43 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L5" s="4">
-        <v>-23.5</v>
+        <v>-14.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="O5" s="6">
         <v>0</v>
@@ -1273,43 +1273,43 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L6" s="4">
-        <v>-31.9</v>
+        <v>-38.9</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="O6" s="6">
         <v>0</v>
@@ -1329,49 +1329,49 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L7" s="4">
-        <v>-14.5</v>
+        <v>-23.9</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="O7" s="6">
-        <v>0</v>
-      </c>
-      <c r="P7" s="7">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="P7" s="8">
+        <v>11</v>
       </c>
       <c r="Q7" s="7">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>38</v>
@@ -1394,34 +1394,34 @@
         <v>46</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>135</v>
+        <v>56</v>
       </c>
       <c r="L8" s="4">
-        <v>-38.9</v>
+        <v>-44.1</v>
       </c>
       <c r="M8" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="O8" s="6">
         <v>0</v>
@@ -1441,43 +1441,43 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L9" s="4">
-        <v>-23.9</v>
+        <v>-32.3</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="O9" s="6">
         <v>0</v>
@@ -1497,7 +1497,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>40</v>
@@ -1506,34 +1506,34 @@
         <v>46</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L10" s="4">
-        <v>-44.1</v>
+        <v>-46.6</v>
       </c>
       <c r="M10" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="N10" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="O10" s="6">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>41</v>
@@ -1562,34 +1562,34 @@
         <v>46</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K11" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-39.4</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="L11" s="4">
-        <v>-32.3</v>
-      </c>
-      <c r="M11" s="3" t="s">
+      <c r="N11" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="O11" s="6">
         <v>0</v>
@@ -1609,7 +1609,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>42</v>
@@ -1618,34 +1618,34 @@
         <v>46</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L12" s="4">
-        <v>-46.6</v>
+        <v>-44.7</v>
       </c>
       <c r="M12" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="N12" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="O12" s="6">
         <v>0</v>
@@ -1665,7 +1665,7 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>43</v>
@@ -1674,34 +1674,34 @@
         <v>46</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>127</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="L13" s="4">
-        <v>-39.4</v>
+        <v>-32.7</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O13" s="6">
         <v>0</v>
@@ -1721,7 +1721,7 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>44</v>
@@ -1730,34 +1730,34 @@
         <v>46</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L14" s="4">
-        <v>-44.7</v>
+        <v>-47.2</v>
       </c>
       <c r="M14" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="N14" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="O14" s="6">
         <v>0</v>
@@ -1777,7 +1777,7 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>45</v>
@@ -1786,34 +1786,34 @@
         <v>46</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="L15" s="4">
-        <v>-32.7</v>
+        <v>-39.9</v>
       </c>
       <c r="M15" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>145</v>
       </c>
       <c r="O15" s="6">
         <v>0</v>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="146">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260808--01</t>
-  </si>
-  <si>
-    <t>20260808--02</t>
-  </si>
-  <si>
     <t>20260809--01</t>
   </si>
   <si>
@@ -112,10 +106,13 @@
     <t>20260814--02</t>
   </si>
   <si>
-    <t>04:02</t>
-  </si>
-  <si>
-    <t>06:24</t>
+    <t>20260815--01</t>
+  </si>
+  <si>
+    <t>20260815--02</t>
+  </si>
+  <si>
+    <t>20260815--03</t>
   </si>
   <si>
     <t>06:40</t>
@@ -127,19 +124,19 @@
     <t>06:33</t>
   </si>
   <si>
-    <t>04:21</t>
-  </si>
-  <si>
-    <t>05:58</t>
-  </si>
-  <si>
-    <t>05:29</t>
+    <t>04:22</t>
+  </si>
+  <si>
+    <t>05:59</t>
+  </si>
+  <si>
+    <t>05:30</t>
   </si>
   <si>
     <t>04:38</t>
   </si>
   <si>
-    <t>06:12</t>
+    <t>06:13</t>
   </si>
   <si>
     <t>06:35</t>
@@ -148,30 +145,27 @@
     <t>01:28</t>
   </si>
   <si>
-    <t>06:36</t>
-  </si>
-  <si>
-    <t>03:53</t>
+    <t>03:52</t>
+  </si>
+  <si>
+    <t>06:09</t>
+  </si>
+  <si>
+    <t>05:10</t>
+  </si>
+  <si>
+    <t>05:04</t>
+  </si>
+  <si>
+    <t>00:15</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
     <t>01:36</t>
   </si>
   <si>
-    <t>02:54:16</t>
-  </si>
-  <si>
-    <t>04:30:43</t>
-  </si>
-  <si>
     <t>03:41:59</t>
   </si>
   <si>
@@ -181,37 +175,40 @@
     <t>02:53:21</t>
   </si>
   <si>
-    <t>04:31:23</t>
-  </si>
-  <si>
-    <t>02:04:51</t>
-  </si>
-  <si>
-    <t>03:42:15</t>
-  </si>
-  <si>
-    <t>01:16:32</t>
-  </si>
-  <si>
-    <t>02:53:12</t>
-  </si>
-  <si>
-    <t>02:04:15</t>
-  </si>
-  <si>
-    <t>03:43:00</t>
-  </si>
-  <si>
-    <t>01:15:25</t>
-  </si>
-  <si>
-    <t>02:53:37</t>
-  </si>
-  <si>
-    <t>02:56:59</t>
-  </si>
-  <si>
-    <t>04:32:53</t>
+    <t>04:31:24</t>
+  </si>
+  <si>
+    <t>02:04:52</t>
+  </si>
+  <si>
+    <t>03:42:16</t>
+  </si>
+  <si>
+    <t>01:16:34</t>
+  </si>
+  <si>
+    <t>02:53:14</t>
+  </si>
+  <si>
+    <t>02:04:18</t>
+  </si>
+  <si>
+    <t>03:43:03</t>
+  </si>
+  <si>
+    <t>01:15:28</t>
+  </si>
+  <si>
+    <t>02:53:40</t>
+  </si>
+  <si>
+    <t>00:26:47</t>
+  </si>
+  <si>
+    <t>02:04:21</t>
+  </si>
+  <si>
+    <t>23:38:15</t>
   </si>
   <si>
     <t>03:44:04</t>
@@ -220,40 +217,43 @@
     <t>05:23:52</t>
   </si>
   <si>
-    <t>02:55:27</t>
+    <t>02:55:28</t>
   </si>
   <si>
     <t>04:34:04</t>
   </si>
   <si>
-    <t>02:07:04</t>
-  </si>
-  <si>
-    <t>03:44:37</t>
-  </si>
-  <si>
-    <t>01:19:04</t>
-  </si>
-  <si>
-    <t>02:55:24</t>
-  </si>
-  <si>
-    <t>02:06:21</t>
-  </si>
-  <si>
-    <t>03:46:41</t>
-  </si>
-  <si>
-    <t>01:17:30</t>
-  </si>
-  <si>
-    <t>02:56:25</t>
-  </si>
-  <si>
-    <t>02:59:00</t>
-  </si>
-  <si>
-    <t>04:36:04</t>
+    <t>02:07:05</t>
+  </si>
+  <si>
+    <t>03:44:38</t>
+  </si>
+  <si>
+    <t>01:19:06</t>
+  </si>
+  <si>
+    <t>02:55:25</t>
+  </si>
+  <si>
+    <t>02:06:24</t>
+  </si>
+  <si>
+    <t>03:46:44</t>
+  </si>
+  <si>
+    <t>01:17:34</t>
+  </si>
+  <si>
+    <t>02:56:29</t>
+  </si>
+  <si>
+    <t>00:28:57</t>
+  </si>
+  <si>
+    <t>02:06:48</t>
+  </si>
+  <si>
+    <t>23:40:40</t>
   </si>
   <si>
     <t>03:47:23</t>
@@ -262,40 +262,43 @@
     <t>05:25:08</t>
   </si>
   <si>
-    <t>02:58:42</t>
-  </si>
-  <si>
-    <t>04:36:14</t>
-  </si>
-  <si>
-    <t>02:10:03</t>
-  </si>
-  <si>
-    <t>03:47:21</t>
-  </si>
-  <si>
-    <t>01:21:22</t>
-  </si>
-  <si>
-    <t>02:58:29</t>
-  </si>
-  <si>
-    <t>02:09:38</t>
-  </si>
-  <si>
-    <t>03:47:25</t>
-  </si>
-  <si>
-    <t>01:20:47</t>
-  </si>
-  <si>
-    <t>02:58:21</t>
-  </si>
-  <si>
-    <t>03:01:01</t>
-  </si>
-  <si>
-    <t>04:39:17</t>
+    <t>02:58:43</t>
+  </si>
+  <si>
+    <t>04:36:15</t>
+  </si>
+  <si>
+    <t>02:10:04</t>
+  </si>
+  <si>
+    <t>03:47:22</t>
+  </si>
+  <si>
+    <t>01:21:24</t>
+  </si>
+  <si>
+    <t>02:58:31</t>
+  </si>
+  <si>
+    <t>02:09:41</t>
+  </si>
+  <si>
+    <t>03:47:28</t>
+  </si>
+  <si>
+    <t>01:20:51</t>
+  </si>
+  <si>
+    <t>02:58:25</t>
+  </si>
+  <si>
+    <t>00:32:01</t>
+  </si>
+  <si>
+    <t>02:09:22</t>
+  </si>
+  <si>
+    <t>23:43:12</t>
   </si>
   <si>
     <t>03:50:44</t>
@@ -304,145 +307,151 @@
     <t>05:26:24</t>
   </si>
   <si>
-    <t>03:02:00</t>
-  </si>
-  <si>
-    <t>04:38:25</t>
-  </si>
-  <si>
-    <t>02:13:02</t>
-  </si>
-  <si>
-    <t>03:50:06</t>
-  </si>
-  <si>
-    <t>01:23:42</t>
-  </si>
-  <si>
-    <t>03:01:36</t>
-  </si>
-  <si>
-    <t>02:12:56</t>
-  </si>
-  <si>
-    <t>03:48:09</t>
-  </si>
-  <si>
-    <t>01:24:06</t>
-  </si>
-  <si>
-    <t>03:00:18</t>
-  </si>
-  <si>
-    <t>03:03:45</t>
-  </si>
-  <si>
-    <t>04:41:28</t>
-  </si>
-  <si>
-    <t>03:52:51</t>
+    <t>03:02:01</t>
+  </si>
+  <si>
+    <t>04:38:26</t>
+  </si>
+  <si>
+    <t>02:13:04</t>
+  </si>
+  <si>
+    <t>03:50:08</t>
+  </si>
+  <si>
+    <t>01:23:44</t>
+  </si>
+  <si>
+    <t>03:01:38</t>
+  </si>
+  <si>
+    <t>02:12:59</t>
+  </si>
+  <si>
+    <t>03:48:12</t>
+  </si>
+  <si>
+    <t>01:24:09</t>
+  </si>
+  <si>
+    <t>03:00:21</t>
+  </si>
+  <si>
+    <t>00:35:06</t>
+  </si>
+  <si>
+    <t>02:11:58</t>
+  </si>
+  <si>
+    <t>23:45:44</t>
+  </si>
+  <si>
+    <t>03:52:52</t>
   </si>
   <si>
     <t>05:29:42</t>
   </si>
   <si>
-    <t>03:04:08</t>
-  </si>
-  <si>
-    <t>04:41:07</t>
-  </si>
-  <si>
-    <t>02:15:17</t>
-  </si>
-  <si>
-    <t>03:52:30</t>
-  </si>
-  <si>
-    <t>01:26:15</t>
-  </si>
-  <si>
-    <t>03:03:49</t>
-  </si>
-  <si>
-    <t>02:15:04</t>
-  </si>
-  <si>
-    <t>03:51:52</t>
-  </si>
-  <si>
-    <t>01:26:13</t>
-  </si>
-  <si>
-    <t>03:03:08</t>
+    <t>03:04:09</t>
+  </si>
+  <si>
+    <t>04:41:08</t>
+  </si>
+  <si>
+    <t>02:15:18</t>
+  </si>
+  <si>
+    <t>03:52:31</t>
+  </si>
+  <si>
+    <t>01:26:17</t>
+  </si>
+  <si>
+    <t>03:03:51</t>
+  </si>
+  <si>
+    <t>02:15:07</t>
+  </si>
+  <si>
+    <t>03:51:55</t>
+  </si>
+  <si>
+    <t>01:26:16</t>
+  </si>
+  <si>
+    <t>03:03:11</t>
+  </si>
+  <si>
+    <t>00:37:18</t>
+  </si>
+  <si>
+    <t>02:14:26</t>
+  </si>
+  <si>
+    <t>23:48:11</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>9°</t>
+  </si>
+  <si>
+    <t>1°</t>
+  </si>
+  <si>
+    <t>16°</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>33°</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>9°</t>
-  </si>
-  <si>
-    <t>1°</t>
-  </si>
-  <si>
-    <t>16°</t>
-  </si>
-  <si>
     <t>10°</t>
   </si>
   <si>
     <t>7°</t>
   </si>
   <si>
-    <t>04:36:57</t>
-  </si>
-  <si>
     <t>03:50:29</t>
   </si>
   <si>
     <t>05:23:23</t>
   </si>
   <si>
-    <t>03:03:55</t>
-  </si>
-  <si>
-    <t>04:36:49</t>
-  </si>
-  <si>
-    <t>03:50:11</t>
-  </si>
-  <si>
-    <t>03:03:31</t>
-  </si>
-  <si>
-    <t>03:49:40</t>
-  </si>
-  <si>
-    <t>03:02:55</t>
+    <t>03:03:56</t>
+  </si>
+  <si>
+    <t>04:36:50</t>
+  </si>
+  <si>
+    <t>03:50:13</t>
+  </si>
+  <si>
+    <t>03:03:32</t>
+  </si>
+  <si>
+    <t>03:49:43</t>
+  </si>
+  <si>
+    <t>03:02:58</t>
+  </si>
+  <si>
+    <t>A+B</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>A+B</t>
-  </si>
-  <si>
-    <t>A</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -476,7 +485,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -491,7 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -503,7 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -544,7 +565,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -568,6 +589,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -971,7 +998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1049,54 +1076,54 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>50</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="L2" s="4">
-        <v>-38.5</v>
+        <v>-31.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="O2" s="6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="7">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1105,54 +1132,54 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>51</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="L3" s="4">
-        <v>-23.5</v>
+        <v>-14.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="O3" s="6">
-        <v>0</v>
-      </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="7">
+        <v>144</v>
+      </c>
+      <c r="O3" s="9">
+        <v>0</v>
+      </c>
+      <c r="P3" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>0</v>
+      </c>
+      <c r="R3" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1161,10 +1188,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>48</v>
@@ -1173,42 +1200,42 @@
         <v>52</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="L4" s="4">
-        <v>-31.9</v>
+        <v>-38.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="O4" s="6">
-        <v>0</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>0</v>
-      </c>
-      <c r="R4" s="7">
+        <v>145</v>
+      </c>
+      <c r="O4" s="9">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1217,54 +1244,54 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>53</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="L5" s="4">
-        <v>-14.5</v>
+        <v>-23.8</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O5" s="6">
-        <v>0</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="7">
+        <v>22</v>
+      </c>
+      <c r="P5" s="10">
+        <v>22</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="R5" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1273,54 +1300,54 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>54</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="L6" s="4">
-        <v>-38.9</v>
+        <v>-44.1</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="7">
+        <v>145</v>
+      </c>
+      <c r="O6" s="9">
+        <v>0</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1329,54 +1356,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L7" s="4">
-        <v>-23.9</v>
+        <v>-32.3</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="O7" s="6">
-        <v>11</v>
+        <v>145</v>
+      </c>
+      <c r="O7" s="9">
+        <v>0</v>
       </c>
       <c r="P7" s="8">
-        <v>11</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-      <c r="R7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
+      <c r="R7" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1385,54 +1412,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>56</v>
       </c>
       <c r="L8" s="4">
-        <v>-44.1</v>
+        <v>-46.6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-      <c r="R8" s="7">
+        <v>145</v>
+      </c>
+      <c r="O8" s="9">
+        <v>0</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1441,54 +1468,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>57</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="L9" s="4">
-        <v>-32.3</v>
+        <v>-39.4</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="O9" s="6">
-        <v>0</v>
-      </c>
-      <c r="P9" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>0</v>
-      </c>
-      <c r="R9" s="7">
+        <v>145</v>
+      </c>
+      <c r="O9" s="9">
+        <v>0</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1497,54 +1524,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>58</v>
       </c>
       <c r="L10" s="4">
-        <v>-46.6</v>
+        <v>-44.7</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="O10" s="6">
-        <v>0</v>
-      </c>
-      <c r="P10" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>0</v>
-      </c>
-      <c r="R10" s="7">
+        <v>145</v>
+      </c>
+      <c r="O10" s="9">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1553,54 +1580,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>59</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L11" s="4">
-        <v>-39.4</v>
+        <v>-32.7</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="O11" s="6">
-        <v>0</v>
-      </c>
-      <c r="P11" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>0</v>
-      </c>
-      <c r="R11" s="7">
+        <v>144</v>
+      </c>
+      <c r="O11" s="9">
+        <v>0</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>0</v>
+      </c>
+      <c r="R11" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1609,54 +1636,54 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>60</v>
       </c>
       <c r="L12" s="4">
-        <v>-44.7</v>
+        <v>-47.2</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="O12" s="6">
-        <v>0</v>
-      </c>
-      <c r="P12" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>0</v>
-      </c>
-      <c r="R12" s="7">
+        <v>145</v>
+      </c>
+      <c r="O12" s="9">
+        <v>0</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1665,54 +1692,54 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>61</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>127</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="L13" s="4">
-        <v>-32.7</v>
+        <v>-39.9</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O13" s="6">
-        <v>0</v>
-      </c>
-      <c r="P13" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="7">
-        <v>0</v>
-      </c>
-      <c r="R13" s="7">
+        <v>145</v>
+      </c>
+      <c r="O13" s="9">
+        <v>0</v>
+      </c>
+      <c r="P13" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>0</v>
+      </c>
+      <c r="R13" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1721,54 +1748,54 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>62</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>62</v>
       </c>
       <c r="L14" s="4">
-        <v>-47.2</v>
+        <v>-46.6</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="O14" s="6">
-        <v>0</v>
-      </c>
-      <c r="P14" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="7">
-        <v>0</v>
-      </c>
-      <c r="R14" s="7">
+        <v>145</v>
+      </c>
+      <c r="O14" s="9">
+        <v>0</v>
+      </c>
+      <c r="P14" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>0</v>
+      </c>
+      <c r="R14" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1777,114 +1804,170 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="J15" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L15" s="4">
+        <v>-45.3</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="O15" s="9">
+        <v>0</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+      <c r="R15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="2">
+        <v>20</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="L15" s="4">
-        <v>-39.9</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="O15" s="6">
-        <v>0</v>
-      </c>
-      <c r="P15" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="7">
-        <v>0</v>
-      </c>
-      <c r="R15" s="7">
+      <c r="J16" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L16" s="4">
+        <v>-42.9</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="O16" s="9">
+        <v>0</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>0</v>
+      </c>
+      <c r="R16" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A15">
+  <conditionalFormatting sqref="A2:A16">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B15">
+  <conditionalFormatting sqref="B2:B16">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C15">
+  <conditionalFormatting sqref="C2:C16">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D15">
+  <conditionalFormatting sqref="D2:D16">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E15">
+  <conditionalFormatting sqref="E2:E16">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F15">
+  <conditionalFormatting sqref="F2:F16">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G15">
+  <conditionalFormatting sqref="G2:G16">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H15">
+  <conditionalFormatting sqref="H2:H16">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I15">
+  <conditionalFormatting sqref="I2:I16">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J15">
+  <conditionalFormatting sqref="J2:J16">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K15">
+  <conditionalFormatting sqref="K2:K16">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L15">
+  <conditionalFormatting sqref="L2:L16">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1903,12 +1986,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M15">
+  <conditionalFormatting sqref="M2:M16">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N15">
+  <conditionalFormatting sqref="N2:N16">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1925,22 +2008,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O15">
+  <conditionalFormatting sqref="O2:O16">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P15">
+  <conditionalFormatting sqref="P2:P16">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q15">
+  <conditionalFormatting sqref="Q2:Q16">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R15">
+  <conditionalFormatting sqref="R2:R16">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="134">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260809--01</t>
-  </si>
-  <si>
-    <t>20260809--02</t>
-  </si>
-  <si>
-    <t>20260810--01</t>
-  </si>
-  <si>
-    <t>20260810--02</t>
-  </si>
-  <si>
     <t>20260811--01</t>
   </si>
   <si>
@@ -115,19 +103,19 @@
     <t>20260815--03</t>
   </si>
   <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>02:32</t>
-  </si>
-  <si>
-    <t>06:33</t>
-  </si>
-  <si>
-    <t>04:22</t>
-  </si>
-  <si>
-    <t>05:59</t>
+    <t>20260816--01</t>
+  </si>
+  <si>
+    <t>20260816--02</t>
+  </si>
+  <si>
+    <t>20260817--01</t>
+  </si>
+  <si>
+    <t>20260817--02</t>
+  </si>
+  <si>
+    <t>05:58</t>
   </si>
   <si>
     <t>05:30</t>
@@ -139,319 +127,295 @@
     <t>06:13</t>
   </si>
   <si>
+    <t>06:36</t>
+  </si>
+  <si>
+    <t>01:29</t>
+  </si>
+  <si>
     <t>06:35</t>
   </si>
   <si>
-    <t>01:28</t>
-  </si>
-  <si>
-    <t>03:52</t>
+    <t>03:54</t>
   </si>
   <si>
     <t>06:09</t>
   </si>
   <si>
-    <t>05:10</t>
-  </si>
-  <si>
-    <t>05:04</t>
-  </si>
-  <si>
-    <t>00:15</t>
+    <t>05:11</t>
+  </si>
+  <si>
+    <t>05:03</t>
+  </si>
+  <si>
+    <t>06:01</t>
+  </si>
+  <si>
+    <t>02:21</t>
+  </si>
+  <si>
+    <t>06:30</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:36</t>
-  </si>
-  <si>
-    <t>03:41:59</t>
-  </si>
-  <si>
-    <t>05:20:35</t>
-  </si>
-  <si>
-    <t>02:53:21</t>
-  </si>
-  <si>
-    <t>04:31:24</t>
-  </si>
-  <si>
-    <t>02:04:52</t>
-  </si>
-  <si>
-    <t>03:42:16</t>
-  </si>
-  <si>
-    <t>01:16:34</t>
-  </si>
-  <si>
-    <t>02:53:14</t>
-  </si>
-  <si>
-    <t>02:04:18</t>
-  </si>
-  <si>
-    <t>03:43:03</t>
-  </si>
-  <si>
-    <t>01:15:28</t>
-  </si>
-  <si>
-    <t>02:53:40</t>
-  </si>
-  <si>
-    <t>00:26:47</t>
-  </si>
-  <si>
-    <t>02:04:21</t>
-  </si>
-  <si>
-    <t>23:38:15</t>
-  </si>
-  <si>
-    <t>03:44:04</t>
-  </si>
-  <si>
-    <t>05:23:52</t>
-  </si>
-  <si>
-    <t>02:55:28</t>
-  </si>
-  <si>
-    <t>04:34:04</t>
-  </si>
-  <si>
-    <t>02:07:05</t>
-  </si>
-  <si>
-    <t>03:44:38</t>
-  </si>
-  <si>
-    <t>01:19:06</t>
-  </si>
-  <si>
-    <t>02:55:25</t>
-  </si>
-  <si>
-    <t>02:06:24</t>
-  </si>
-  <si>
-    <t>03:46:44</t>
-  </si>
-  <si>
-    <t>01:17:34</t>
-  </si>
-  <si>
-    <t>02:56:29</t>
-  </si>
-  <si>
-    <t>00:28:57</t>
-  </si>
-  <si>
-    <t>02:06:48</t>
-  </si>
-  <si>
-    <t>23:40:40</t>
-  </si>
-  <si>
-    <t>03:47:23</t>
-  </si>
-  <si>
-    <t>05:25:08</t>
-  </si>
-  <si>
-    <t>02:58:43</t>
-  </si>
-  <si>
-    <t>04:36:15</t>
-  </si>
-  <si>
-    <t>02:10:04</t>
-  </si>
-  <si>
-    <t>03:47:22</t>
-  </si>
-  <si>
-    <t>01:21:24</t>
-  </si>
-  <si>
-    <t>02:58:31</t>
-  </si>
-  <si>
-    <t>02:09:41</t>
-  </si>
-  <si>
-    <t>03:47:28</t>
-  </si>
-  <si>
-    <t>01:20:51</t>
-  </si>
-  <si>
-    <t>02:58:25</t>
-  </si>
-  <si>
-    <t>00:32:01</t>
-  </si>
-  <si>
-    <t>02:09:22</t>
-  </si>
-  <si>
-    <t>23:43:12</t>
-  </si>
-  <si>
-    <t>03:50:44</t>
-  </si>
-  <si>
-    <t>05:26:24</t>
-  </si>
-  <si>
-    <t>03:02:01</t>
-  </si>
-  <si>
-    <t>04:38:26</t>
-  </si>
-  <si>
-    <t>02:13:04</t>
-  </si>
-  <si>
-    <t>03:50:08</t>
-  </si>
-  <si>
-    <t>01:23:44</t>
-  </si>
-  <si>
-    <t>03:01:38</t>
-  </si>
-  <si>
-    <t>02:12:59</t>
-  </si>
-  <si>
-    <t>03:48:12</t>
-  </si>
-  <si>
-    <t>01:24:09</t>
-  </si>
-  <si>
-    <t>03:00:21</t>
-  </si>
-  <si>
-    <t>00:35:06</t>
-  </si>
-  <si>
-    <t>02:11:58</t>
-  </si>
-  <si>
-    <t>23:45:44</t>
-  </si>
-  <si>
-    <t>03:52:52</t>
-  </si>
-  <si>
-    <t>05:29:42</t>
-  </si>
-  <si>
-    <t>03:04:09</t>
-  </si>
-  <si>
-    <t>04:41:08</t>
-  </si>
-  <si>
-    <t>02:15:18</t>
-  </si>
-  <si>
-    <t>03:52:31</t>
-  </si>
-  <si>
-    <t>01:26:17</t>
-  </si>
-  <si>
-    <t>03:03:51</t>
-  </si>
-  <si>
-    <t>02:15:07</t>
-  </si>
-  <si>
-    <t>03:51:55</t>
-  </si>
-  <si>
-    <t>01:26:16</t>
-  </si>
-  <si>
-    <t>03:03:11</t>
-  </si>
-  <si>
-    <t>00:37:18</t>
-  </si>
-  <si>
-    <t>02:14:26</t>
-  </si>
-  <si>
-    <t>23:48:11</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>9°</t>
+    <t>02:04:50</t>
+  </si>
+  <si>
+    <t>03:42:13</t>
+  </si>
+  <si>
+    <t>01:16:29</t>
+  </si>
+  <si>
+    <t>02:53:09</t>
+  </si>
+  <si>
+    <t>02:04:10</t>
+  </si>
+  <si>
+    <t>03:42:55</t>
+  </si>
+  <si>
+    <t>01:15:18</t>
+  </si>
+  <si>
+    <t>02:53:30</t>
+  </si>
+  <si>
+    <t>00:26:34</t>
+  </si>
+  <si>
+    <t>02:04:08</t>
+  </si>
+  <si>
+    <t>23:38:00</t>
+  </si>
+  <si>
+    <t>01:14:51</t>
+  </si>
+  <si>
+    <t>22:49:38</t>
+  </si>
+  <si>
+    <t>00:25:40</t>
+  </si>
+  <si>
+    <t>23:36:35</t>
+  </si>
+  <si>
+    <t>02:07:03</t>
+  </si>
+  <si>
+    <t>03:44:35</t>
+  </si>
+  <si>
+    <t>01:19:01</t>
+  </si>
+  <si>
+    <t>02:55:20</t>
+  </si>
+  <si>
+    <t>02:06:16</t>
+  </si>
+  <si>
+    <t>03:46:36</t>
+  </si>
+  <si>
+    <t>01:17:24</t>
+  </si>
+  <si>
+    <t>02:56:18</t>
+  </si>
+  <si>
+    <t>00:28:45</t>
+  </si>
+  <si>
+    <t>02:06:34</t>
+  </si>
+  <si>
+    <t>23:40:25</t>
+  </si>
+  <si>
+    <t>01:17:05</t>
+  </si>
+  <si>
+    <t>22:52:53</t>
+  </si>
+  <si>
+    <t>00:27:47</t>
+  </si>
+  <si>
+    <t>23:38:40</t>
+  </si>
+  <si>
+    <t>02:10:01</t>
+  </si>
+  <si>
+    <t>03:47:19</t>
+  </si>
+  <si>
+    <t>01:21:19</t>
+  </si>
+  <si>
+    <t>02:58:26</t>
+  </si>
+  <si>
+    <t>02:09:33</t>
+  </si>
+  <si>
+    <t>03:47:20</t>
+  </si>
+  <si>
+    <t>01:20:41</t>
+  </si>
+  <si>
+    <t>02:58:15</t>
+  </si>
+  <si>
+    <t>00:31:48</t>
+  </si>
+  <si>
+    <t>02:09:09</t>
+  </si>
+  <si>
+    <t>23:42:56</t>
+  </si>
+  <si>
+    <t>01:20:05</t>
+  </si>
+  <si>
+    <t>22:54:03</t>
+  </si>
+  <si>
+    <t>00:31:01</t>
+  </si>
+  <si>
+    <t>23:41:57</t>
+  </si>
+  <si>
+    <t>02:13:01</t>
+  </si>
+  <si>
+    <t>03:50:05</t>
+  </si>
+  <si>
+    <t>01:23:39</t>
+  </si>
+  <si>
+    <t>03:01:33</t>
+  </si>
+  <si>
+    <t>02:12:52</t>
+  </si>
+  <si>
+    <t>03:48:05</t>
+  </si>
+  <si>
+    <t>01:23:59</t>
+  </si>
+  <si>
+    <t>03:00:12</t>
+  </si>
+  <si>
+    <t>00:34:54</t>
+  </si>
+  <si>
+    <t>02:11:45</t>
+  </si>
+  <si>
+    <t>23:45:28</t>
+  </si>
+  <si>
+    <t>01:23:06</t>
+  </si>
+  <si>
+    <t>22:55:14</t>
+  </si>
+  <si>
+    <t>00:34:17</t>
+  </si>
+  <si>
+    <t>23:45:16</t>
+  </si>
+  <si>
+    <t>02:15:15</t>
+  </si>
+  <si>
+    <t>03:52:28</t>
+  </si>
+  <si>
+    <t>01:26:12</t>
+  </si>
+  <si>
+    <t>03:03:46</t>
+  </si>
+  <si>
+    <t>02:14:59</t>
+  </si>
+  <si>
+    <t>03:51:47</t>
+  </si>
+  <si>
+    <t>01:26:06</t>
+  </si>
+  <si>
+    <t>03:03:01</t>
+  </si>
+  <si>
+    <t>00:37:05</t>
+  </si>
+  <si>
+    <t>02:14:13</t>
+  </si>
+  <si>
+    <t>23:47:54</t>
+  </si>
+  <si>
+    <t>01:25:21</t>
+  </si>
+  <si>
+    <t>22:58:30</t>
+  </si>
+  <si>
+    <t>00:36:25</t>
+  </si>
+  <si>
+    <t>23:47:23</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>10°</t>
   </si>
   <si>
     <t>1°</t>
   </si>
   <si>
-    <t>16°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
     <t>7°</t>
   </si>
   <si>
-    <t>03:50:29</t>
-  </si>
-  <si>
-    <t>05:23:23</t>
-  </si>
-  <si>
-    <t>03:03:56</t>
-  </si>
-  <si>
-    <t>04:36:50</t>
-  </si>
-  <si>
-    <t>03:50:13</t>
-  </si>
-  <si>
-    <t>03:03:32</t>
-  </si>
-  <si>
-    <t>03:49:43</t>
-  </si>
-  <si>
-    <t>03:02:58</t>
-  </si>
-  <si>
-    <t>A+B</t>
-  </si>
-  <si>
-    <t>A</t>
+    <t>03:50:10</t>
+  </si>
+  <si>
+    <t>03:03:27</t>
+  </si>
+  <si>
+    <t>03:49:36</t>
+  </si>
+  <si>
+    <t>03:02:49</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>2</t>
+    <t>3</t>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -485,7 +449,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -506,7 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,7 +488,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -565,7 +535,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -595,6 +565,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1076,7 +1049,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>33</v>
@@ -1085,40 +1058,40 @@
         <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-44.1</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-31.9</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="O2" s="6">
         <v>32</v>
       </c>
       <c r="P2" s="7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1132,49 +1105,49 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="L3" s="4">
-        <v>-14.5</v>
+        <v>-32.3</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O3" s="9">
-        <v>0</v>
-      </c>
-      <c r="P3" s="8">
-        <v>0</v>
+        <v>132</v>
+      </c>
+      <c r="O3" s="6">
+        <v>33</v>
+      </c>
+      <c r="P3" s="7">
+        <v>26</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1188,43 +1161,43 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>134</v>
+        <v>50</v>
       </c>
       <c r="L4" s="4">
-        <v>-38.9</v>
+        <v>-46.6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O4" s="9">
         <v>0</v>
@@ -1244,49 +1217,49 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="L5" s="4">
-        <v>-23.8</v>
+        <v>-39.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O5" s="6">
-        <v>22</v>
-      </c>
-      <c r="P5" s="10">
-        <v>22</v>
+        <v>132</v>
+      </c>
+      <c r="O5" s="9">
+        <v>0</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
       </c>
       <c r="Q5" s="8">
         <v>0</v>
@@ -1300,43 +1273,43 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L6" s="4">
-        <v>-44.1</v>
+        <v>-44.7</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O6" s="9">
         <v>0</v>
@@ -1356,43 +1329,43 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="L7" s="4">
-        <v>-32.3</v>
+        <v>-32.7</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="O7" s="9">
         <v>0</v>
@@ -1412,43 +1385,43 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>39</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L8" s="4">
-        <v>-46.6</v>
+        <v>-47.2</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O8" s="9">
         <v>0</v>
@@ -1468,43 +1441,43 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="L9" s="4">
-        <v>-39.4</v>
+        <v>-39.9</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O9" s="9">
         <v>0</v>
@@ -1524,49 +1497,49 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L10" s="4">
-        <v>-44.7</v>
+        <v>-46.6</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O10" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P10" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="8">
         <v>0</v>
@@ -1580,43 +1553,43 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J11" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-45.3</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="L11" s="4">
-        <v>-32.7</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="N11" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="O11" s="9">
         <v>0</v>
@@ -1636,49 +1609,49 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L12" s="4">
-        <v>-47.2</v>
+        <v>-42.9</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O12" s="9">
-        <v>0</v>
-      </c>
-      <c r="P12" s="8">
-        <v>0</v>
+        <v>132</v>
+      </c>
+      <c r="O12" s="6">
+        <v>25</v>
+      </c>
+      <c r="P12" s="7">
+        <v>25</v>
       </c>
       <c r="Q12" s="8">
         <v>0</v>
@@ -1692,49 +1665,49 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>139</v>
+        <v>59</v>
       </c>
       <c r="L13" s="4">
-        <v>-39.9</v>
+        <v>-47.9</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O13" s="9">
-        <v>0</v>
-      </c>
-      <c r="P13" s="8">
-        <v>0</v>
+        <v>132</v>
+      </c>
+      <c r="O13" s="10">
+        <v>40</v>
+      </c>
+      <c r="P13" s="11">
+        <v>40</v>
       </c>
       <c r="Q13" s="8">
         <v>0</v>
@@ -1748,43 +1721,43 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L14" s="4">
-        <v>-46.6</v>
+        <v>-36.8</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="O14" s="9">
         <v>0</v>
@@ -1804,43 +1777,43 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I15" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="K15" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L15" s="4">
-        <v>-45.3</v>
+        <v>-47.2</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O15" s="9">
         <v>0</v>
@@ -1860,43 +1833,43 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L16" s="4">
-        <v>-42.9</v>
+        <v>-43.4</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O16" s="9">
         <v>0</v>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="132">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260811--01</t>
-  </si>
-  <si>
-    <t>20260811--02</t>
-  </si>
-  <si>
     <t>20260812--01</t>
   </si>
   <si>
@@ -115,22 +109,22 @@
     <t>20260817--02</t>
   </si>
   <si>
-    <t>05:58</t>
-  </si>
-  <si>
-    <t>05:30</t>
+    <t>20260818--01</t>
+  </si>
+  <si>
+    <t>20260818--02</t>
   </si>
   <si>
     <t>04:38</t>
   </si>
   <si>
-    <t>06:13</t>
+    <t>06:14</t>
   </si>
   <si>
     <t>06:36</t>
   </si>
   <si>
-    <t>01:29</t>
+    <t>01:30</t>
   </si>
   <si>
     <t>06:35</t>
@@ -151,262 +145,262 @@
     <t>06:01</t>
   </si>
   <si>
-    <t>02:21</t>
+    <t>02:23</t>
   </si>
   <si>
     <t>06:30</t>
   </si>
   <si>
+    <t>03:24</t>
+  </si>
+  <si>
+    <t>06:17</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:04:50</t>
-  </si>
-  <si>
-    <t>03:42:13</t>
-  </si>
-  <si>
-    <t>01:16:29</t>
-  </si>
-  <si>
-    <t>02:53:09</t>
-  </si>
-  <si>
-    <t>02:04:10</t>
-  </si>
-  <si>
-    <t>03:42:55</t>
-  </si>
-  <si>
-    <t>01:15:18</t>
-  </si>
-  <si>
-    <t>02:53:30</t>
-  </si>
-  <si>
-    <t>00:26:34</t>
-  </si>
-  <si>
-    <t>02:04:08</t>
-  </si>
-  <si>
-    <t>23:38:00</t>
-  </si>
-  <si>
-    <t>01:14:51</t>
-  </si>
-  <si>
-    <t>22:49:38</t>
-  </si>
-  <si>
-    <t>00:25:40</t>
-  </si>
-  <si>
-    <t>23:36:35</t>
-  </si>
-  <si>
-    <t>02:07:03</t>
-  </si>
-  <si>
-    <t>03:44:35</t>
-  </si>
-  <si>
-    <t>01:19:01</t>
-  </si>
-  <si>
-    <t>02:55:20</t>
-  </si>
-  <si>
-    <t>02:06:16</t>
-  </si>
-  <si>
-    <t>03:46:36</t>
-  </si>
-  <si>
-    <t>01:17:24</t>
-  </si>
-  <si>
-    <t>02:56:18</t>
-  </si>
-  <si>
-    <t>00:28:45</t>
-  </si>
-  <si>
-    <t>02:06:34</t>
-  </si>
-  <si>
-    <t>23:40:25</t>
-  </si>
-  <si>
-    <t>01:17:05</t>
-  </si>
-  <si>
-    <t>22:52:53</t>
-  </si>
-  <si>
-    <t>00:27:47</t>
-  </si>
-  <si>
-    <t>23:38:40</t>
-  </si>
-  <si>
-    <t>02:10:01</t>
-  </si>
-  <si>
-    <t>03:47:19</t>
-  </si>
-  <si>
-    <t>01:21:19</t>
-  </si>
-  <si>
-    <t>02:58:26</t>
-  </si>
-  <si>
-    <t>02:09:33</t>
-  </si>
-  <si>
-    <t>03:47:20</t>
-  </si>
-  <si>
-    <t>01:20:41</t>
-  </si>
-  <si>
-    <t>02:58:15</t>
-  </si>
-  <si>
-    <t>00:31:48</t>
-  </si>
-  <si>
-    <t>02:09:09</t>
-  </si>
-  <si>
-    <t>23:42:56</t>
-  </si>
-  <si>
-    <t>01:20:05</t>
-  </si>
-  <si>
-    <t>22:54:03</t>
-  </si>
-  <si>
-    <t>00:31:01</t>
-  </si>
-  <si>
-    <t>23:41:57</t>
-  </si>
-  <si>
-    <t>02:13:01</t>
-  </si>
-  <si>
-    <t>03:50:05</t>
-  </si>
-  <si>
-    <t>01:23:39</t>
-  </si>
-  <si>
-    <t>03:01:33</t>
-  </si>
-  <si>
-    <t>02:12:52</t>
-  </si>
-  <si>
-    <t>03:48:05</t>
-  </si>
-  <si>
-    <t>01:23:59</t>
-  </si>
-  <si>
-    <t>03:00:12</t>
-  </si>
-  <si>
-    <t>00:34:54</t>
-  </si>
-  <si>
-    <t>02:11:45</t>
-  </si>
-  <si>
-    <t>23:45:28</t>
-  </si>
-  <si>
-    <t>01:23:06</t>
-  </si>
-  <si>
-    <t>22:55:14</t>
-  </si>
-  <si>
-    <t>00:34:17</t>
-  </si>
-  <si>
-    <t>23:45:16</t>
-  </si>
-  <si>
-    <t>02:15:15</t>
-  </si>
-  <si>
-    <t>03:52:28</t>
-  </si>
-  <si>
-    <t>01:26:12</t>
-  </si>
-  <si>
-    <t>03:03:46</t>
-  </si>
-  <si>
-    <t>02:14:59</t>
-  </si>
-  <si>
-    <t>03:51:47</t>
-  </si>
-  <si>
-    <t>01:26:06</t>
-  </si>
-  <si>
-    <t>03:03:01</t>
-  </si>
-  <si>
-    <t>00:37:05</t>
-  </si>
-  <si>
-    <t>02:14:13</t>
-  </si>
-  <si>
-    <t>23:47:54</t>
-  </si>
-  <si>
-    <t>01:25:21</t>
-  </si>
-  <si>
-    <t>22:58:30</t>
-  </si>
-  <si>
-    <t>00:36:25</t>
-  </si>
-  <si>
-    <t>23:47:23</t>
+    <t>01:16:30</t>
+  </si>
+  <si>
+    <t>02:53:10</t>
+  </si>
+  <si>
+    <t>02:04:13</t>
+  </si>
+  <si>
+    <t>03:42:58</t>
+  </si>
+  <si>
+    <t>01:15:23</t>
+  </si>
+  <si>
+    <t>02:53:35</t>
+  </si>
+  <si>
+    <t>00:26:42</t>
+  </si>
+  <si>
+    <t>02:04:16</t>
+  </si>
+  <si>
+    <t>23:38:11</t>
+  </si>
+  <si>
+    <t>01:15:03</t>
+  </si>
+  <si>
+    <t>22:49:53</t>
+  </si>
+  <si>
+    <t>00:25:55</t>
+  </si>
+  <si>
+    <t>23:36:55</t>
+  </si>
+  <si>
+    <t>01:15:15</t>
+  </si>
+  <si>
+    <t>22:48:03</t>
+  </si>
+  <si>
+    <t>01:19:02</t>
+  </si>
+  <si>
+    <t>02:55:21</t>
+  </si>
+  <si>
+    <t>02:06:19</t>
+  </si>
+  <si>
+    <t>03:46:38</t>
+  </si>
+  <si>
+    <t>01:17:29</t>
+  </si>
+  <si>
+    <t>02:56:23</t>
+  </si>
+  <si>
+    <t>00:28:52</t>
+  </si>
+  <si>
+    <t>02:06:42</t>
+  </si>
+  <si>
+    <t>23:40:36</t>
+  </si>
+  <si>
+    <t>01:17:16</t>
+  </si>
+  <si>
+    <t>22:53:07</t>
+  </si>
+  <si>
+    <t>00:28:02</t>
+  </si>
+  <si>
+    <t>23:39:00</t>
+  </si>
+  <si>
+    <t>01:18:12</t>
+  </si>
+  <si>
+    <t>22:50:11</t>
+  </si>
+  <si>
+    <t>01:21:21</t>
+  </si>
+  <si>
+    <t>02:58:27</t>
+  </si>
+  <si>
+    <t>02:09:36</t>
+  </si>
+  <si>
+    <t>03:47:23</t>
+  </si>
+  <si>
+    <t>01:20:46</t>
+  </si>
+  <si>
+    <t>02:58:20</t>
+  </si>
+  <si>
+    <t>00:31:56</t>
+  </si>
+  <si>
+    <t>02:09:17</t>
+  </si>
+  <si>
+    <t>23:43:07</t>
+  </si>
+  <si>
+    <t>01:20:16</t>
+  </si>
+  <si>
+    <t>22:54:18</t>
+  </si>
+  <si>
+    <t>00:31:16</t>
+  </si>
+  <si>
+    <t>23:42:17</t>
+  </si>
+  <si>
+    <t>01:19:54</t>
+  </si>
+  <si>
+    <t>22:53:19</t>
+  </si>
+  <si>
+    <t>01:23:40</t>
+  </si>
+  <si>
+    <t>03:01:35</t>
+  </si>
+  <si>
+    <t>02:12:55</t>
+  </si>
+  <si>
+    <t>03:48:08</t>
+  </si>
+  <si>
+    <t>01:24:04</t>
+  </si>
+  <si>
+    <t>03:00:17</t>
+  </si>
+  <si>
+    <t>00:35:01</t>
+  </si>
+  <si>
+    <t>02:11:53</t>
+  </si>
+  <si>
+    <t>23:45:39</t>
+  </si>
+  <si>
+    <t>01:23:17</t>
+  </si>
+  <si>
+    <t>22:55:30</t>
+  </si>
+  <si>
+    <t>00:34:32</t>
+  </si>
+  <si>
+    <t>23:45:36</t>
+  </si>
+  <si>
+    <t>01:21:36</t>
+  </si>
+  <si>
+    <t>22:56:28</t>
+  </si>
+  <si>
+    <t>01:26:13</t>
+  </si>
+  <si>
+    <t>03:03:48</t>
+  </si>
+  <si>
+    <t>02:15:02</t>
+  </si>
+  <si>
+    <t>03:51:50</t>
+  </si>
+  <si>
+    <t>01:26:11</t>
+  </si>
+  <si>
+    <t>03:03:07</t>
+  </si>
+  <si>
+    <t>00:37:13</t>
+  </si>
+  <si>
+    <t>02:14:21</t>
+  </si>
+  <si>
+    <t>23:48:06</t>
+  </si>
+  <si>
+    <t>01:25:33</t>
+  </si>
+  <si>
+    <t>22:58:45</t>
+  </si>
+  <si>
+    <t>00:36:40</t>
+  </si>
+  <si>
+    <t>23:47:42</t>
+  </si>
+  <si>
+    <t>01:24:34</t>
+  </si>
+  <si>
+    <t>22:58:38</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>10°</t>
-  </si>
-  <si>
     <t>1°</t>
   </si>
   <si>
     <t>7°</t>
   </si>
   <si>
-    <t>03:50:10</t>
-  </si>
-  <si>
-    <t>03:03:27</t>
-  </si>
-  <si>
-    <t>03:49:36</t>
-  </si>
-  <si>
-    <t>03:02:49</t>
+    <t>03:03:29</t>
+  </si>
+  <si>
+    <t>03:49:38</t>
+  </si>
+  <si>
+    <t>03:02:53</t>
   </si>
   <si>
     <t>B</t>
@@ -449,7 +443,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -470,7 +464,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -483,6 +477,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -535,7 +559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -568,6 +592,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1049,7 +1088,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>33</v>
@@ -1079,19 +1118,19 @@
         <v>48</v>
       </c>
       <c r="L2" s="4">
-        <v>-44.1</v>
+        <v>-46.6</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="O2" s="6">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="P2" s="7">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1105,7 +1144,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>34</v>
@@ -1132,22 +1171,22 @@
         <v>124</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L3" s="4">
-        <v>-32.3</v>
+        <v>-39.4</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="O3" s="6">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="P3" s="7">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1161,7 +1200,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>35</v>
@@ -1191,13 +1230,13 @@
         <v>50</v>
       </c>
       <c r="L4" s="4">
-        <v>-46.6</v>
+        <v>-44.7</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="O4" s="9">
         <v>0</v>
@@ -1217,7 +1256,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>36</v>
@@ -1244,16 +1283,16 @@
         <v>125</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L5" s="4">
-        <v>-39.4</v>
+        <v>-32.7</v>
       </c>
       <c r="M5" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="O5" s="9">
         <v>0</v>
@@ -1273,7 +1312,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>37</v>
@@ -1303,13 +1342,13 @@
         <v>52</v>
       </c>
       <c r="L6" s="4">
-        <v>-44.7</v>
+        <v>-47.2</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="O6" s="9">
         <v>0</v>
@@ -1329,7 +1368,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>38</v>
@@ -1353,19 +1392,19 @@
         <v>113</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K7" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-39.9</v>
+      </c>
+      <c r="M7" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="L7" s="4">
-        <v>-32.7</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="N7" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="O7" s="9">
         <v>0</v>
@@ -1385,7 +1424,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>39</v>
@@ -1415,19 +1454,19 @@
         <v>54</v>
       </c>
       <c r="L8" s="4">
-        <v>-47.2</v>
+        <v>-46.6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="O8" s="9">
-        <v>0</v>
-      </c>
-      <c r="P8" s="8">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="P8" s="10">
+        <v>6</v>
       </c>
       <c r="Q8" s="8">
         <v>0</v>
@@ -1441,7 +1480,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>40</v>
@@ -1465,25 +1504,25 @@
         <v>115</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-45.3</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="L9" s="4">
-        <v>-39.9</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O9" s="9">
-        <v>0</v>
-      </c>
-      <c r="P9" s="8">
-        <v>0</v>
+      <c r="O9" s="6">
+        <v>7</v>
+      </c>
+      <c r="P9" s="10">
+        <v>7</v>
       </c>
       <c r="Q9" s="8">
         <v>0</v>
@@ -1497,7 +1536,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>41</v>
@@ -1527,19 +1566,19 @@
         <v>56</v>
       </c>
       <c r="L10" s="4">
-        <v>-46.6</v>
+        <v>-42.9</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="O10" s="9">
-        <v>2</v>
-      </c>
-      <c r="P10" s="8">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="P10" s="11">
+        <v>8</v>
       </c>
       <c r="Q10" s="8">
         <v>0</v>
@@ -1553,7 +1592,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>42</v>
@@ -1583,19 +1622,19 @@
         <v>57</v>
       </c>
       <c r="L11" s="4">
-        <v>-45.3</v>
+        <v>-47.9</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O11" s="9">
-        <v>0</v>
-      </c>
-      <c r="P11" s="8">
-        <v>0</v>
+        <v>130</v>
+      </c>
+      <c r="O11" s="6">
+        <v>18</v>
+      </c>
+      <c r="P11" s="12">
+        <v>18</v>
       </c>
       <c r="Q11" s="8">
         <v>0</v>
@@ -1609,7 +1648,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>43</v>
@@ -1639,19 +1678,19 @@
         <v>58</v>
       </c>
       <c r="L12" s="4">
-        <v>-42.9</v>
+        <v>-36.8</v>
       </c>
       <c r="M12" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="N12" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="N12" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="O12" s="6">
-        <v>25</v>
-      </c>
-      <c r="P12" s="7">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="P12" s="13">
+        <v>23</v>
       </c>
       <c r="Q12" s="8">
         <v>0</v>
@@ -1665,7 +1704,7 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>44</v>
@@ -1695,19 +1734,19 @@
         <v>59</v>
       </c>
       <c r="L13" s="4">
-        <v>-47.9</v>
+        <v>-47.2</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O13" s="10">
-        <v>40</v>
+        <v>130</v>
+      </c>
+      <c r="O13" s="6">
+        <v>10</v>
       </c>
       <c r="P13" s="11">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="Q13" s="8">
         <v>0</v>
@@ -1721,10 +1760,10 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>47</v>
@@ -1751,19 +1790,19 @@
         <v>60</v>
       </c>
       <c r="L14" s="4">
-        <v>-36.8</v>
+        <v>-43.4</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O14" s="9">
-        <v>0</v>
-      </c>
-      <c r="P14" s="8">
-        <v>0</v>
+        <v>130</v>
+      </c>
+      <c r="O14" s="6">
+        <v>19</v>
+      </c>
+      <c r="P14" s="14">
+        <v>17</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
@@ -1777,10 +1816,10 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>47</v>
@@ -1807,19 +1846,19 @@
         <v>61</v>
       </c>
       <c r="L15" s="4">
-        <v>-47.2</v>
+        <v>-48.5</v>
       </c>
       <c r="M15" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="N15" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O15" s="9">
-        <v>0</v>
-      </c>
-      <c r="P15" s="8">
-        <v>0</v>
+      <c r="O15" s="6">
+        <v>15</v>
+      </c>
+      <c r="P15" s="14">
+        <v>15</v>
       </c>
       <c r="Q15" s="8">
         <v>0</v>
@@ -1833,10 +1872,10 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>47</v>
@@ -1863,22 +1902,22 @@
         <v>62</v>
       </c>
       <c r="L16" s="4">
-        <v>-43.4</v>
+        <v>-37.2</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O16" s="9">
-        <v>0</v>
-      </c>
-      <c r="P16" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>0</v>
+        <v>130</v>
+      </c>
+      <c r="O16" s="15">
+        <v>50</v>
+      </c>
+      <c r="P16" s="16">
+        <v>40</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>6</v>
       </c>
       <c r="R16" s="8">
         <v>0</v>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="148">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260812--01</t>
-  </si>
-  <si>
-    <t>20260812--02</t>
-  </si>
-  <si>
     <t>20260813--01</t>
   </si>
   <si>
@@ -115,22 +109,28 @@
     <t>20260818--02</t>
   </si>
   <si>
-    <t>04:38</t>
-  </si>
-  <si>
-    <t>06:14</t>
+    <t>20260819--01</t>
+  </si>
+  <si>
+    <t>20260819--02</t>
+  </si>
+  <si>
+    <t>20260819--03</t>
+  </si>
+  <si>
+    <t>20260819--04</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>01:30</t>
   </si>
   <si>
     <t>06:36</t>
   </si>
   <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>03:54</t>
+    <t>03:53</t>
   </si>
   <si>
     <t>06:09</t>
@@ -145,10 +145,10 @@
     <t>06:01</t>
   </si>
   <si>
-    <t>02:23</t>
-  </si>
-  <si>
-    <t>06:30</t>
+    <t>02:22</t>
+  </si>
+  <si>
+    <t>06:29</t>
   </si>
   <si>
     <t>03:24</t>
@@ -157,15 +157,21 @@
     <t>06:17</t>
   </si>
   <si>
+    <t>04:53</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>05:22</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:16:30</t>
-  </si>
-  <si>
-    <t>02:53:10</t>
-  </si>
-  <si>
     <t>02:04:13</t>
   </si>
   <si>
@@ -175,40 +181,46 @@
     <t>01:15:23</t>
   </si>
   <si>
-    <t>02:53:35</t>
-  </si>
-  <si>
-    <t>00:26:42</t>
-  </si>
-  <si>
-    <t>02:04:16</t>
-  </si>
-  <si>
-    <t>23:38:11</t>
-  </si>
-  <si>
-    <t>01:15:03</t>
-  </si>
-  <si>
-    <t>22:49:53</t>
-  </si>
-  <si>
-    <t>00:25:55</t>
-  </si>
-  <si>
-    <t>23:36:55</t>
-  </si>
-  <si>
-    <t>01:15:15</t>
-  </si>
-  <si>
-    <t>22:48:03</t>
-  </si>
-  <si>
-    <t>01:19:02</t>
-  </si>
-  <si>
-    <t>02:55:21</t>
+    <t>02:53:34</t>
+  </si>
+  <si>
+    <t>00:26:41</t>
+  </si>
+  <si>
+    <t>02:04:15</t>
+  </si>
+  <si>
+    <t>23:38:09</t>
+  </si>
+  <si>
+    <t>01:15:00</t>
+  </si>
+  <si>
+    <t>22:49:50</t>
+  </si>
+  <si>
+    <t>00:25:52</t>
+  </si>
+  <si>
+    <t>23:36:50</t>
+  </si>
+  <si>
+    <t>01:15:10</t>
+  </si>
+  <si>
+    <t>22:47:56</t>
+  </si>
+  <si>
+    <t>00:25:40</t>
+  </si>
+  <si>
+    <t>05:21:19</t>
+  </si>
+  <si>
+    <t>21:59:12</t>
+  </si>
+  <si>
+    <t>23:36:14</t>
   </si>
   <si>
     <t>02:06:19</t>
@@ -217,91 +229,103 @@
     <t>03:46:38</t>
   </si>
   <si>
-    <t>01:17:29</t>
+    <t>01:17:28</t>
   </si>
   <si>
     <t>02:56:23</t>
   </si>
   <si>
-    <t>00:28:52</t>
-  </si>
-  <si>
-    <t>02:06:42</t>
-  </si>
-  <si>
-    <t>23:40:36</t>
-  </si>
-  <si>
-    <t>01:17:16</t>
-  </si>
-  <si>
-    <t>22:53:07</t>
-  </si>
-  <si>
-    <t>00:28:02</t>
-  </si>
-  <si>
-    <t>23:39:00</t>
-  </si>
-  <si>
-    <t>01:18:12</t>
-  </si>
-  <si>
-    <t>22:50:11</t>
-  </si>
-  <si>
-    <t>01:21:21</t>
-  </si>
-  <si>
-    <t>02:58:27</t>
-  </si>
-  <si>
-    <t>02:09:36</t>
+    <t>00:28:51</t>
+  </si>
+  <si>
+    <t>02:06:41</t>
+  </si>
+  <si>
+    <t>23:40:34</t>
+  </si>
+  <si>
+    <t>01:17:14</t>
+  </si>
+  <si>
+    <t>22:53:04</t>
+  </si>
+  <si>
+    <t>00:27:59</t>
+  </si>
+  <si>
+    <t>23:38:55</t>
+  </si>
+  <si>
+    <t>01:18:07</t>
+  </si>
+  <si>
+    <t>22:50:05</t>
+  </si>
+  <si>
+    <t>00:28:10</t>
+  </si>
+  <si>
+    <t>05:24:05</t>
+  </si>
+  <si>
+    <t>22:01:33</t>
+  </si>
+  <si>
+    <t>23:38:30</t>
+  </si>
+  <si>
+    <t>02:09:35</t>
   </si>
   <si>
     <t>03:47:23</t>
   </si>
   <si>
-    <t>01:20:46</t>
-  </si>
-  <si>
-    <t>02:58:20</t>
-  </si>
-  <si>
-    <t>00:31:56</t>
-  </si>
-  <si>
-    <t>02:09:17</t>
-  </si>
-  <si>
-    <t>23:43:07</t>
-  </si>
-  <si>
-    <t>01:20:16</t>
-  </si>
-  <si>
-    <t>22:54:18</t>
-  </si>
-  <si>
-    <t>00:31:16</t>
-  </si>
-  <si>
-    <t>23:42:17</t>
-  </si>
-  <si>
-    <t>01:19:54</t>
-  </si>
-  <si>
-    <t>22:53:19</t>
-  </si>
-  <si>
-    <t>01:23:40</t>
-  </si>
-  <si>
-    <t>03:01:35</t>
-  </si>
-  <si>
-    <t>02:12:55</t>
+    <t>01:20:45</t>
+  </si>
+  <si>
+    <t>02:58:19</t>
+  </si>
+  <si>
+    <t>00:31:55</t>
+  </si>
+  <si>
+    <t>02:09:16</t>
+  </si>
+  <si>
+    <t>23:43:05</t>
+  </si>
+  <si>
+    <t>01:20:14</t>
+  </si>
+  <si>
+    <t>22:54:15</t>
+  </si>
+  <si>
+    <t>00:31:13</t>
+  </si>
+  <si>
+    <t>23:42:12</t>
+  </si>
+  <si>
+    <t>01:19:49</t>
+  </si>
+  <si>
+    <t>22:53:13</t>
+  </si>
+  <si>
+    <t>00:30:36</t>
+  </si>
+  <si>
+    <t>05:26:07</t>
+  </si>
+  <si>
+    <t>22:04:14</t>
+  </si>
+  <si>
+    <t>23:41:25</t>
+  </si>
+  <si>
+    <t>02:12:54</t>
   </si>
   <si>
     <t>03:48:08</t>
@@ -310,40 +334,46 @@
     <t>01:24:04</t>
   </si>
   <si>
-    <t>03:00:17</t>
-  </si>
-  <si>
-    <t>00:35:01</t>
-  </si>
-  <si>
-    <t>02:11:53</t>
-  </si>
-  <si>
-    <t>23:45:39</t>
-  </si>
-  <si>
-    <t>01:23:17</t>
-  </si>
-  <si>
-    <t>22:55:30</t>
-  </si>
-  <si>
-    <t>00:34:32</t>
-  </si>
-  <si>
-    <t>23:45:36</t>
-  </si>
-  <si>
-    <t>01:21:36</t>
-  </si>
-  <si>
-    <t>22:56:28</t>
-  </si>
-  <si>
-    <t>01:26:13</t>
-  </si>
-  <si>
-    <t>03:03:48</t>
+    <t>03:00:16</t>
+  </si>
+  <si>
+    <t>00:35:00</t>
+  </si>
+  <si>
+    <t>02:11:52</t>
+  </si>
+  <si>
+    <t>23:45:37</t>
+  </si>
+  <si>
+    <t>01:23:15</t>
+  </si>
+  <si>
+    <t>22:55:26</t>
+  </si>
+  <si>
+    <t>00:34:28</t>
+  </si>
+  <si>
+    <t>23:45:31</t>
+  </si>
+  <si>
+    <t>01:21:31</t>
+  </si>
+  <si>
+    <t>22:56:22</t>
+  </si>
+  <si>
+    <t>00:33:03</t>
+  </si>
+  <si>
+    <t>05:28:10</t>
+  </si>
+  <si>
+    <t>22:06:55</t>
+  </si>
+  <si>
+    <t>23:44:20</t>
   </si>
   <si>
     <t>02:15:02</t>
@@ -355,46 +385,58 @@
     <t>01:26:11</t>
   </si>
   <si>
-    <t>03:03:07</t>
-  </si>
-  <si>
-    <t>00:37:13</t>
-  </si>
-  <si>
-    <t>02:14:21</t>
-  </si>
-  <si>
-    <t>23:48:06</t>
-  </si>
-  <si>
-    <t>01:25:33</t>
-  </si>
-  <si>
-    <t>22:58:45</t>
-  </si>
-  <si>
-    <t>00:36:40</t>
-  </si>
-  <si>
-    <t>23:47:42</t>
-  </si>
-  <si>
-    <t>01:24:34</t>
-  </si>
-  <si>
-    <t>22:58:38</t>
+    <t>03:03:06</t>
+  </si>
+  <si>
+    <t>00:37:12</t>
+  </si>
+  <si>
+    <t>02:14:20</t>
+  </si>
+  <si>
+    <t>23:48:03</t>
+  </si>
+  <si>
+    <t>01:25:30</t>
+  </si>
+  <si>
+    <t>22:58:41</t>
+  </si>
+  <si>
+    <t>00:36:37</t>
+  </si>
+  <si>
+    <t>23:47:38</t>
+  </si>
+  <si>
+    <t>01:24:30</t>
+  </si>
+  <si>
+    <t>22:58:32</t>
+  </si>
+  <si>
+    <t>00:35:35</t>
+  </si>
+  <si>
+    <t>05:30:56</t>
+  </si>
+  <si>
+    <t>22:09:17</t>
+  </si>
+  <si>
+    <t>23:46:37</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
+    <t>7°</t>
+  </si>
+  <si>
     <t>1°</t>
   </si>
   <si>
-    <t>7°</t>
-  </si>
-  <si>
-    <t>03:03:29</t>
+    <t>-</t>
   </si>
   <si>
     <t>03:49:38</t>
@@ -406,10 +448,16 @@
     <t>B</t>
   </si>
   <si>
+    <t>A+B</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
 </sst>
 </file>
@@ -443,7 +491,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -464,13 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,37 +542,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -559,7 +601,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -604,9 +646,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1010,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1088,49 +1127,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L2" s="4">
-        <v>-46.6</v>
+        <v>-44.7</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="O2" s="6">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="P2" s="7">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1144,49 +1183,49 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-32.7</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="O3" s="6">
         <v>34</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-39.4</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="O3" s="6">
-        <v>39</v>
-      </c>
-      <c r="P3" s="7">
-        <v>34</v>
+      <c r="P3" s="9">
+        <v>28</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1200,45 +1239,45 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="L4" s="4">
-        <v>-44.7</v>
+        <v>-47.2</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="O4" s="9">
+        <v>145</v>
+      </c>
+      <c r="O4" s="10">
         <v>0</v>
       </c>
       <c r="P4" s="8">
@@ -1256,52 +1295,52 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="L5" s="4">
-        <v>-32.7</v>
+        <v>-39.9</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="O5" s="9">
-        <v>0</v>
+        <v>145</v>
+      </c>
+      <c r="O5" s="10">
+        <v>3</v>
       </c>
       <c r="P5" s="8">
         <v>0</v>
       </c>
-      <c r="Q5" s="8">
-        <v>0</v>
+      <c r="Q5" s="11">
+        <v>3</v>
       </c>
       <c r="R5" s="8">
         <v>0</v>
@@ -1312,45 +1351,45 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L6" s="4">
-        <v>-47.2</v>
+        <v>-46.6</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="O6" s="9">
+        <v>145</v>
+      </c>
+      <c r="O6" s="10">
         <v>0</v>
       </c>
       <c r="P6" s="8">
@@ -1368,45 +1407,45 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>128</v>
+        <v>57</v>
       </c>
       <c r="L7" s="4">
-        <v>-39.9</v>
+        <v>-45.3</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="O7" s="9">
+        <v>145</v>
+      </c>
+      <c r="O7" s="10">
         <v>0</v>
       </c>
       <c r="P7" s="8">
@@ -1424,49 +1463,49 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L8" s="4">
-        <v>-46.6</v>
+        <v>-42.9</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="O8" s="9">
-        <v>6</v>
-      </c>
-      <c r="P8" s="10">
-        <v>6</v>
+        <v>145</v>
+      </c>
+      <c r="O8" s="10">
+        <v>0</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
       </c>
       <c r="Q8" s="8">
         <v>0</v>
@@ -1480,49 +1519,49 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L9" s="4">
-        <v>-45.3</v>
+        <v>-47.9</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="O9" s="6">
-        <v>7</v>
-      </c>
-      <c r="P9" s="10">
-        <v>7</v>
+        <v>145</v>
+      </c>
+      <c r="O9" s="10">
+        <v>0</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0</v>
       </c>
       <c r="Q9" s="8">
         <v>0</v>
@@ -1536,49 +1575,49 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L10" s="4">
-        <v>-42.9</v>
+        <v>-36.8</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="O10" s="9">
-        <v>8</v>
-      </c>
-      <c r="P10" s="11">
-        <v>8</v>
+        <v>146</v>
+      </c>
+      <c r="O10" s="6">
+        <v>12</v>
+      </c>
+      <c r="P10" s="8">
+        <v>1</v>
       </c>
       <c r="Q10" s="8">
         <v>0</v>
@@ -1592,49 +1631,49 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L11" s="4">
-        <v>-47.9</v>
+        <v>-47.2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="O11" s="6">
-        <v>18</v>
-      </c>
-      <c r="P11" s="12">
-        <v>18</v>
+        <v>34</v>
+      </c>
+      <c r="P11" s="11">
+        <v>3</v>
       </c>
       <c r="Q11" s="8">
         <v>0</v>
@@ -1648,49 +1687,49 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="L12" s="4">
-        <v>-36.8</v>
+        <v>-43.4</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="O12" s="6">
-        <v>23</v>
+        <v>145</v>
+      </c>
+      <c r="O12" s="12">
+        <v>53</v>
       </c>
       <c r="P12" s="13">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="Q12" s="8">
         <v>0</v>
@@ -1704,49 +1743,49 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="L13" s="4">
-        <v>-47.2</v>
+        <v>-48.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="O13" s="6">
-        <v>10</v>
-      </c>
-      <c r="P13" s="11">
-        <v>10</v>
+        <v>41</v>
+      </c>
+      <c r="P13" s="14">
+        <v>41</v>
       </c>
       <c r="Q13" s="8">
         <v>0</v>
@@ -1760,49 +1799,49 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L14" s="4">
-        <v>-43.4</v>
+        <v>-37.2</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="O14" s="6">
-        <v>19</v>
-      </c>
-      <c r="P14" s="14">
-        <v>17</v>
+        <v>145</v>
+      </c>
+      <c r="O14" s="12">
+        <v>72</v>
+      </c>
+      <c r="P14" s="15">
+        <v>63</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
@@ -1816,49 +1855,49 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="L15" s="4">
-        <v>-48.5</v>
+        <v>-47.8</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="O15" s="6">
-        <v>15</v>
+        <v>145</v>
+      </c>
+      <c r="O15" s="12">
+        <v>39</v>
       </c>
       <c r="P15" s="14">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="Q15" s="8">
         <v>0</v>
@@ -1872,114 +1911,226 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>62</v>
+        <v>140</v>
       </c>
       <c r="L16" s="4">
-        <v>-37.2</v>
+        <v>-15.7</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="O16" s="15">
+        <v>147</v>
+      </c>
+      <c r="O16" s="10">
+        <v>0</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>0</v>
+      </c>
+      <c r="R16" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2">
+        <v>23</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-29.4</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="O17" s="6">
+        <v>13</v>
+      </c>
+      <c r="P17" s="11">
+        <v>6</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0</v>
+      </c>
+      <c r="R17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="2">
+        <v>28</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="P16" s="16">
-        <v>40</v>
-      </c>
-      <c r="Q16" s="10">
+      <c r="D18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L18" s="4">
+        <v>-44</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="O18" s="10">
         <v>6</v>
       </c>
-      <c r="R16" s="8">
+      <c r="P18" s="8">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>0</v>
+      </c>
+      <c r="R18" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A16">
+  <conditionalFormatting sqref="A2:A18">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B16">
+  <conditionalFormatting sqref="B2:B18">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C16">
+  <conditionalFormatting sqref="C2:C18">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D16">
+  <conditionalFormatting sqref="D2:D18">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E16">
+  <conditionalFormatting sqref="E2:E18">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F16">
+  <conditionalFormatting sqref="F2:F18">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G16">
+  <conditionalFormatting sqref="G2:G18">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H16">
+  <conditionalFormatting sqref="H2:H18">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I16">
+  <conditionalFormatting sqref="I2:I18">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J16">
+  <conditionalFormatting sqref="J2:J18">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K16">
+  <conditionalFormatting sqref="K2:K18">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L16">
+  <conditionalFormatting sqref="L2:L18">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1998,12 +2149,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M16">
+  <conditionalFormatting sqref="M2:M18">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N16">
+  <conditionalFormatting sqref="N2:N18">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2020,22 +2171,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O16">
+  <conditionalFormatting sqref="O2:O18">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P16">
+  <conditionalFormatting sqref="P2:P18">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q16">
+  <conditionalFormatting sqref="Q2:Q18">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R16">
+  <conditionalFormatting sqref="R2:R18">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="155">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260813--01</t>
-  </si>
-  <si>
-    <t>20260813--02</t>
-  </si>
-  <si>
     <t>20260814--01</t>
   </si>
   <si>
@@ -121,10 +115,13 @@
     <t>20260819--04</t>
   </si>
   <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>01:30</t>
+    <t>20260820--01</t>
+  </si>
+  <si>
+    <t>20260820--02</t>
+  </si>
+  <si>
+    <t>20260820--03</t>
   </si>
   <si>
     <t>06:36</t>
@@ -169,15 +166,18 @@
     <t>05:50</t>
   </si>
   <si>
+    <t>01:50</t>
+  </si>
+  <si>
+    <t>03:17</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:04:13</t>
-  </si>
-  <si>
-    <t>03:42:58</t>
-  </si>
-  <si>
     <t>01:15:23</t>
   </si>
   <si>
@@ -223,10 +223,13 @@
     <t>23:36:14</t>
   </si>
   <si>
-    <t>02:06:19</t>
-  </si>
-  <si>
-    <t>03:46:38</t>
+    <t>04:32:22</t>
+  </si>
+  <si>
+    <t>21:10:40</t>
+  </si>
+  <si>
+    <t>22:46:55</t>
   </si>
   <si>
     <t>01:17:28</t>
@@ -274,10 +277,13 @@
     <t>23:38:30</t>
   </si>
   <si>
-    <t>02:09:35</t>
-  </si>
-  <si>
-    <t>03:47:23</t>
+    <t>04:35:55</t>
+  </si>
+  <si>
+    <t>21:13:36</t>
+  </si>
+  <si>
+    <t>22:49:03</t>
   </si>
   <si>
     <t>01:20:45</t>
@@ -325,10 +331,13 @@
     <t>23:41:25</t>
   </si>
   <si>
-    <t>02:12:54</t>
-  </si>
-  <si>
-    <t>03:48:08</t>
+    <t>04:36:50</t>
+  </si>
+  <si>
+    <t>21:15:14</t>
+  </si>
+  <si>
+    <t>22:52:14</t>
   </si>
   <si>
     <t>01:24:04</t>
@@ -376,10 +385,10 @@
     <t>23:44:20</t>
   </si>
   <si>
-    <t>02:15:02</t>
-  </si>
-  <si>
-    <t>03:51:50</t>
+    <t>04:37:45</t>
+  </si>
+  <si>
+    <t>21:16:53</t>
   </si>
   <si>
     <t>01:26:11</t>
@@ -400,7 +409,7 @@
     <t>01:25:30</t>
   </si>
   <si>
-    <t>22:58:41</t>
+    <t>22:58:42</t>
   </si>
   <si>
     <t>00:36:37</t>
@@ -427,28 +436,40 @@
     <t>23:46:37</t>
   </si>
   <si>
+    <t>04:41:18</t>
+  </si>
+  <si>
+    <t>21:19:49</t>
+  </si>
+  <si>
+    <t>22:57:36</t>
+  </si>
+  <si>
     <t>0°</t>
   </si>
   <si>
+    <t>1°</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>7°</t>
   </si>
   <si>
-    <t>1°</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>03:49:38</t>
-  </si>
-  <si>
     <t>03:02:53</t>
   </si>
   <si>
+    <t>04:34:48</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
     <t>A+B</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
   <si>
     <t>3</t>
@@ -491,7 +512,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -512,7 +533,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,7 +545,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,31 +557,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -601,7 +628,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -646,6 +673,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1049,7 +1079,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1127,49 +1157,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L2" s="4">
-        <v>-44.7</v>
+        <v>-47.2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="O2" s="6">
         <v>27</v>
       </c>
       <c r="P2" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1183,49 +1213,49 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="L3" s="4">
-        <v>-32.7</v>
+        <v>-39.9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="O3" s="6">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="P3" s="9">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1239,43 +1269,43 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L4" s="4">
-        <v>-47.2</v>
+        <v>-46.6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="O4" s="10">
         <v>0</v>
@@ -1295,52 +1325,52 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>142</v>
+        <v>57</v>
       </c>
       <c r="L5" s="4">
-        <v>-39.9</v>
+        <v>-45.3</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="O5" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P5" s="8">
         <v>0</v>
       </c>
-      <c r="Q5" s="11">
-        <v>3</v>
+      <c r="Q5" s="8">
+        <v>0</v>
       </c>
       <c r="R5" s="8">
         <v>0</v>
@@ -1351,49 +1381,49 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L6" s="4">
-        <v>-46.6</v>
+        <v>-42.9</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="O6" s="10">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P6" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="8">
         <v>0</v>
@@ -1407,49 +1437,49 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L7" s="4">
-        <v>-45.3</v>
+        <v>-47.9</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O7" s="10">
-        <v>0</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
+        <v>152</v>
+      </c>
+      <c r="O7" s="6">
+        <v>18</v>
+      </c>
+      <c r="P7" s="9">
+        <v>18</v>
       </c>
       <c r="Q7" s="8">
         <v>0</v>
@@ -1463,49 +1493,49 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L8" s="4">
-        <v>-42.9</v>
+        <v>-36.8</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O8" s="10">
-        <v>0</v>
-      </c>
-      <c r="P8" s="8">
-        <v>0</v>
+        <v>153</v>
+      </c>
+      <c r="O8" s="11">
+        <v>48</v>
+      </c>
+      <c r="P8" s="12">
+        <v>48</v>
       </c>
       <c r="Q8" s="8">
         <v>0</v>
@@ -1519,49 +1549,49 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L9" s="4">
-        <v>-47.9</v>
+        <v>-47.2</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O9" s="10">
-        <v>0</v>
-      </c>
-      <c r="P9" s="8">
-        <v>0</v>
+        <v>152</v>
+      </c>
+      <c r="O9" s="11">
+        <v>49</v>
+      </c>
+      <c r="P9" s="12">
+        <v>49</v>
       </c>
       <c r="Q9" s="8">
         <v>0</v>
@@ -1575,49 +1605,49 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L10" s="4">
-        <v>-36.8</v>
+        <v>-43.4</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="O10" s="6">
-        <v>12</v>
-      </c>
-      <c r="P10" s="8">
-        <v>1</v>
+        <v>44</v>
+      </c>
+      <c r="P10" s="13">
+        <v>44</v>
       </c>
       <c r="Q10" s="8">
         <v>0</v>
@@ -1631,49 +1661,49 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L11" s="4">
-        <v>-47.2</v>
+        <v>-48.5</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="O11" s="6">
-        <v>34</v>
-      </c>
-      <c r="P11" s="11">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="P11" s="14">
+        <v>14</v>
       </c>
       <c r="Q11" s="8">
         <v>0</v>
@@ -1687,49 +1717,49 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
+        <v>42</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="G12" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L12" s="4">
-        <v>-43.4</v>
+        <v>-37.2</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O12" s="12">
-        <v>53</v>
-      </c>
-      <c r="P12" s="13">
-        <v>53</v>
+        <v>152</v>
+      </c>
+      <c r="O12" s="10">
+        <v>9</v>
+      </c>
+      <c r="P12" s="8">
+        <v>1</v>
       </c>
       <c r="Q12" s="8">
         <v>0</v>
@@ -1743,49 +1773,49 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L13" s="4">
-        <v>-48.5</v>
+        <v>-47.8</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="O13" s="6">
-        <v>41</v>
-      </c>
-      <c r="P13" s="14">
-        <v>41</v>
+        <v>14</v>
+      </c>
+      <c r="P13" s="8">
+        <v>0</v>
       </c>
       <c r="Q13" s="8">
         <v>0</v>
@@ -1799,52 +1829,52 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="L14" s="4">
-        <v>-37.2</v>
+        <v>-15.7</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O14" s="12">
-        <v>72</v>
-      </c>
-      <c r="P14" s="15">
-        <v>63</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>0</v>
+        <v>154</v>
+      </c>
+      <c r="O14" s="10">
+        <v>11</v>
+      </c>
+      <c r="P14" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="15">
+        <v>11</v>
       </c>
       <c r="R14" s="8">
         <v>0</v>
@@ -1855,49 +1885,49 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L15" s="4">
-        <v>-47.8</v>
+        <v>-29.4</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O15" s="12">
-        <v>39</v>
-      </c>
-      <c r="P15" s="14">
-        <v>38</v>
+        <v>152</v>
+      </c>
+      <c r="O15" s="6">
+        <v>14</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0</v>
       </c>
       <c r="Q15" s="8">
         <v>0</v>
@@ -1911,46 +1941,46 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>140</v>
+        <v>68</v>
       </c>
       <c r="L16" s="4">
-        <v>-15.7</v>
+        <v>-44</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="O16" s="10">
-        <v>0</v>
+        <v>152</v>
+      </c>
+      <c r="O16" s="6">
+        <v>18</v>
       </c>
       <c r="P16" s="8">
         <v>0</v>
@@ -1967,49 +1997,49 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>67</v>
+        <v>148</v>
       </c>
       <c r="L17" s="4">
-        <v>-29.4</v>
+        <v>-25.5</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O17" s="6">
-        <v>13</v>
-      </c>
-      <c r="P17" s="11">
-        <v>6</v>
+        <v>153</v>
+      </c>
+      <c r="O17" s="10">
+        <v>5</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
       </c>
       <c r="Q17" s="8">
         <v>0</v>
@@ -2023,114 +2053,170 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L18" s="4">
-        <v>-44</v>
+        <v>-20.4</v>
       </c>
       <c r="M18" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="O18" s="10">
+        <v>2</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>2</v>
+      </c>
+      <c r="R18" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="2">
+        <v>47</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="N18" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O18" s="10">
-        <v>6</v>
-      </c>
-      <c r="P18" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>0</v>
-      </c>
-      <c r="R18" s="8">
+      <c r="K19" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L19" s="4">
+        <v>-37.7</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="O19" s="10">
+        <v>3</v>
+      </c>
+      <c r="P19" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="16">
+        <v>3</v>
+      </c>
+      <c r="R19" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A18">
+  <conditionalFormatting sqref="A2:A19">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B18">
+  <conditionalFormatting sqref="B2:B19">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C18">
+  <conditionalFormatting sqref="C2:C19">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D18">
+  <conditionalFormatting sqref="D2:D19">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E18">
+  <conditionalFormatting sqref="E2:E19">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F18">
+  <conditionalFormatting sqref="F2:F19">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G18">
+  <conditionalFormatting sqref="G2:G19">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H18">
+  <conditionalFormatting sqref="H2:H19">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I18">
+  <conditionalFormatting sqref="I2:I19">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J18">
+  <conditionalFormatting sqref="J2:J19">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K18">
+  <conditionalFormatting sqref="K2:K19">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L18">
+  <conditionalFormatting sqref="L2:L19">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2149,12 +2235,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M18">
+  <conditionalFormatting sqref="M2:M19">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N18">
+  <conditionalFormatting sqref="N2:N19">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2171,22 +2257,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O18">
+  <conditionalFormatting sqref="O2:O19">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P18">
+  <conditionalFormatting sqref="P2:P19">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q18">
+  <conditionalFormatting sqref="Q2:Q19">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R18">
+  <conditionalFormatting sqref="R2:R19">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="161">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260814--01</t>
-  </si>
-  <si>
-    <t>20260814--02</t>
-  </si>
-  <si>
     <t>20260815--01</t>
   </si>
   <si>
@@ -124,30 +118,36 @@
     <t>20260820--03</t>
   </si>
   <si>
+    <t>20260821--01</t>
+  </si>
+  <si>
+    <t>20260821--02</t>
+  </si>
+  <si>
+    <t>20260821--03</t>
+  </si>
+  <si>
+    <t>06:09</t>
+  </si>
+  <si>
+    <t>05:11</t>
+  </si>
+  <si>
+    <t>05:03</t>
+  </si>
+  <si>
+    <t>06:01</t>
+  </si>
+  <si>
+    <t>02:22</t>
+  </si>
+  <si>
+    <t>06:29</t>
+  </si>
+  <si>
     <t>06:36</t>
   </si>
   <si>
-    <t>03:53</t>
-  </si>
-  <si>
-    <t>06:09</t>
-  </si>
-  <si>
-    <t>05:11</t>
-  </si>
-  <si>
-    <t>05:03</t>
-  </si>
-  <si>
-    <t>06:01</t>
-  </si>
-  <si>
-    <t>02:22</t>
-  </si>
-  <si>
-    <t>06:29</t>
-  </si>
-  <si>
     <t>03:24</t>
   </si>
   <si>
@@ -166,76 +166,76 @@
     <t>05:50</t>
   </si>
   <si>
-    <t>01:50</t>
-  </si>
-  <si>
-    <t>03:17</t>
-  </si>
-  <si>
-    <t>06:23</t>
+    <t>01:49</t>
+  </si>
+  <si>
+    <t>03:16</t>
+  </si>
+  <si>
+    <t>06:24</t>
+  </si>
+  <si>
+    <t>02:54</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:15:23</t>
-  </si>
-  <si>
-    <t>02:53:34</t>
-  </si>
-  <si>
     <t>00:26:41</t>
   </si>
   <si>
     <t>02:04:15</t>
   </si>
   <si>
-    <t>23:38:09</t>
+    <t>23:38:08</t>
   </si>
   <si>
     <t>01:15:00</t>
   </si>
   <si>
-    <t>22:49:50</t>
-  </si>
-  <si>
-    <t>00:25:52</t>
-  </si>
-  <si>
-    <t>23:36:50</t>
-  </si>
-  <si>
-    <t>01:15:10</t>
-  </si>
-  <si>
-    <t>22:47:56</t>
-  </si>
-  <si>
-    <t>00:25:40</t>
-  </si>
-  <si>
-    <t>05:21:19</t>
-  </si>
-  <si>
-    <t>21:59:12</t>
-  </si>
-  <si>
-    <t>23:36:14</t>
-  </si>
-  <si>
-    <t>04:32:22</t>
-  </si>
-  <si>
-    <t>21:10:40</t>
-  </si>
-  <si>
-    <t>22:46:55</t>
-  </si>
-  <si>
-    <t>01:17:28</t>
-  </si>
-  <si>
-    <t>02:56:23</t>
+    <t>22:49:49</t>
+  </si>
+  <si>
+    <t>00:25:51</t>
+  </si>
+  <si>
+    <t>23:36:48</t>
+  </si>
+  <si>
+    <t>01:15:08</t>
+  </si>
+  <si>
+    <t>22:47:53</t>
+  </si>
+  <si>
+    <t>00:25:37</t>
+  </si>
+  <si>
+    <t>05:21:15</t>
+  </si>
+  <si>
+    <t>21:59:08</t>
+  </si>
+  <si>
+    <t>23:36:09</t>
+  </si>
+  <si>
+    <t>04:32:17</t>
+  </si>
+  <si>
+    <t>21:10:34</t>
+  </si>
+  <si>
+    <t>22:46:48</t>
+  </si>
+  <si>
+    <t>05:19:58</t>
+  </si>
+  <si>
+    <t>21:57:33</t>
+  </si>
+  <si>
+    <t>23:36:00</t>
   </si>
   <si>
     <t>00:28:51</t>
@@ -250,46 +250,49 @@
     <t>01:17:14</t>
   </si>
   <si>
-    <t>22:53:04</t>
-  </si>
-  <si>
-    <t>00:27:59</t>
-  </si>
-  <si>
-    <t>23:38:55</t>
-  </si>
-  <si>
-    <t>01:18:07</t>
-  </si>
-  <si>
-    <t>22:50:05</t>
-  </si>
-  <si>
-    <t>00:28:10</t>
-  </si>
-  <si>
-    <t>05:24:05</t>
-  </si>
-  <si>
-    <t>22:01:33</t>
-  </si>
-  <si>
-    <t>23:38:30</t>
-  </si>
-  <si>
-    <t>04:35:55</t>
-  </si>
-  <si>
-    <t>21:13:36</t>
-  </si>
-  <si>
-    <t>22:49:03</t>
-  </si>
-  <si>
-    <t>01:20:45</t>
-  </si>
-  <si>
-    <t>02:58:19</t>
+    <t>22:53:03</t>
+  </si>
+  <si>
+    <t>00:27:58</t>
+  </si>
+  <si>
+    <t>23:38:53</t>
+  </si>
+  <si>
+    <t>01:18:05</t>
+  </si>
+  <si>
+    <t>22:50:02</t>
+  </si>
+  <si>
+    <t>00:28:07</t>
+  </si>
+  <si>
+    <t>05:24:01</t>
+  </si>
+  <si>
+    <t>22:01:28</t>
+  </si>
+  <si>
+    <t>23:38:25</t>
+  </si>
+  <si>
+    <t>04:35:50</t>
+  </si>
+  <si>
+    <t>21:13:30</t>
+  </si>
+  <si>
+    <t>22:48:56</t>
+  </si>
+  <si>
+    <t>05:22:09</t>
+  </si>
+  <si>
+    <t>21:59:38</t>
+  </si>
+  <si>
+    <t>23:39:07</t>
   </si>
   <si>
     <t>00:31:55</t>
@@ -304,46 +307,46 @@
     <t>01:20:14</t>
   </si>
   <si>
-    <t>22:54:15</t>
-  </si>
-  <si>
-    <t>00:31:13</t>
-  </si>
-  <si>
-    <t>23:42:12</t>
-  </si>
-  <si>
-    <t>01:19:49</t>
-  </si>
-  <si>
-    <t>22:53:13</t>
-  </si>
-  <si>
-    <t>00:30:36</t>
-  </si>
-  <si>
-    <t>05:26:07</t>
-  </si>
-  <si>
-    <t>22:04:14</t>
-  </si>
-  <si>
-    <t>23:41:25</t>
-  </si>
-  <si>
-    <t>04:36:50</t>
-  </si>
-  <si>
-    <t>21:15:14</t>
-  </si>
-  <si>
-    <t>22:52:14</t>
-  </si>
-  <si>
-    <t>01:24:04</t>
-  </si>
-  <si>
-    <t>03:00:16</t>
+    <t>22:54:14</t>
+  </si>
+  <si>
+    <t>00:31:12</t>
+  </si>
+  <si>
+    <t>23:42:11</t>
+  </si>
+  <si>
+    <t>01:19:47</t>
+  </si>
+  <si>
+    <t>22:53:10</t>
+  </si>
+  <si>
+    <t>00:30:33</t>
+  </si>
+  <si>
+    <t>05:26:04</t>
+  </si>
+  <si>
+    <t>22:04:09</t>
+  </si>
+  <si>
+    <t>23:41:20</t>
+  </si>
+  <si>
+    <t>04:36:45</t>
+  </si>
+  <si>
+    <t>21:15:08</t>
+  </si>
+  <si>
+    <t>22:52:07</t>
+  </si>
+  <si>
+    <t>05:25:18</t>
+  </si>
+  <si>
+    <t>22:02:55</t>
   </si>
   <si>
     <t>00:35:00</t>
@@ -358,43 +361,49 @@
     <t>01:23:15</t>
   </si>
   <si>
-    <t>22:55:26</t>
-  </si>
-  <si>
-    <t>00:34:28</t>
-  </si>
-  <si>
-    <t>23:45:31</t>
-  </si>
-  <si>
-    <t>01:21:31</t>
-  </si>
-  <si>
-    <t>22:56:22</t>
-  </si>
-  <si>
-    <t>00:33:03</t>
-  </si>
-  <si>
-    <t>05:28:10</t>
-  </si>
-  <si>
-    <t>22:06:55</t>
-  </si>
-  <si>
-    <t>23:44:20</t>
-  </si>
-  <si>
-    <t>04:37:45</t>
-  </si>
-  <si>
-    <t>21:16:53</t>
-  </si>
-  <si>
-    <t>01:26:11</t>
-  </si>
-  <si>
-    <t>03:03:06</t>
+    <t>22:55:25</t>
+  </si>
+  <si>
+    <t>00:34:27</t>
+  </si>
+  <si>
+    <t>23:45:29</t>
+  </si>
+  <si>
+    <t>01:21:29</t>
+  </si>
+  <si>
+    <t>22:56:19</t>
+  </si>
+  <si>
+    <t>00:33:00</t>
+  </si>
+  <si>
+    <t>05:28:06</t>
+  </si>
+  <si>
+    <t>22:06:50</t>
+  </si>
+  <si>
+    <t>23:44:15</t>
+  </si>
+  <si>
+    <t>04:37:39</t>
+  </si>
+  <si>
+    <t>21:16:46</t>
+  </si>
+  <si>
+    <t>22:55:20</t>
+  </si>
+  <si>
+    <t>05:28:26</t>
+  </si>
+  <si>
+    <t>22:06:14</t>
+  </si>
+  <si>
+    <t>23:42:01</t>
   </si>
   <si>
     <t>00:37:12</t>
@@ -409,58 +418,64 @@
     <t>01:25:30</t>
   </si>
   <si>
-    <t>22:58:42</t>
-  </si>
-  <si>
-    <t>00:36:37</t>
-  </si>
-  <si>
-    <t>23:47:38</t>
-  </si>
-  <si>
-    <t>01:24:30</t>
-  </si>
-  <si>
-    <t>22:58:32</t>
-  </si>
-  <si>
-    <t>00:35:35</t>
-  </si>
-  <si>
-    <t>05:30:56</t>
-  </si>
-  <si>
-    <t>22:09:17</t>
-  </si>
-  <si>
-    <t>23:46:37</t>
-  </si>
-  <si>
-    <t>04:41:18</t>
-  </si>
-  <si>
-    <t>21:19:49</t>
-  </si>
-  <si>
-    <t>22:57:36</t>
+    <t>22:58:40</t>
+  </si>
+  <si>
+    <t>00:36:36</t>
+  </si>
+  <si>
+    <t>23:47:36</t>
+  </si>
+  <si>
+    <t>01:24:28</t>
+  </si>
+  <si>
+    <t>22:58:28</t>
+  </si>
+  <si>
+    <t>00:35:32</t>
+  </si>
+  <si>
+    <t>05:30:53</t>
+  </si>
+  <si>
+    <t>22:09:12</t>
+  </si>
+  <si>
+    <t>23:46:33</t>
+  </si>
+  <si>
+    <t>04:41:13</t>
+  </si>
+  <si>
+    <t>21:19:42</t>
+  </si>
+  <si>
+    <t>22:57:29</t>
+  </si>
+  <si>
+    <t>05:30:38</t>
+  </si>
+  <si>
+    <t>22:08:20</t>
+  </si>
+  <si>
+    <t>23:45:09</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>1°</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
     <t>7°</t>
   </si>
   <si>
-    <t>03:02:53</t>
-  </si>
-  <si>
-    <t>04:34:48</t>
+    <t>04:34:44</t>
+  </si>
+  <si>
+    <t>05:21:35</t>
   </si>
   <si>
     <t>B</t>
@@ -479,6 +494,9 @@
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
@@ -512,7 +530,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -527,13 +545,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -545,7 +563,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -557,19 +575,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -581,13 +599,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -628,7 +652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -676,6 +700,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1079,7 +1106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1157,49 +1184,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>36</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-46.6</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="O2" s="6">
         <v>70</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-47.2</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="O2" s="6">
-        <v>27</v>
-      </c>
       <c r="P2" s="7">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1213,49 +1240,49 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>147</v>
+        <v>56</v>
       </c>
       <c r="L3" s="4">
-        <v>-39.9</v>
+        <v>-45.3</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O3" s="6">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="P3" s="9">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -1269,49 +1296,49 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L4" s="4">
-        <v>-46.6</v>
+        <v>-42.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O4" s="10">
-        <v>0</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="P4" s="11">
+        <v>9</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
@@ -1325,49 +1352,49 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L5" s="4">
-        <v>-45.3</v>
+        <v>-47.9</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="O5" s="10">
-        <v>0</v>
-      </c>
-      <c r="P5" s="8">
-        <v>0</v>
+        <v>157</v>
+      </c>
+      <c r="O5" s="12">
+        <v>31</v>
+      </c>
+      <c r="P5" s="13">
+        <v>31</v>
       </c>
       <c r="Q5" s="8">
         <v>0</v>
@@ -1381,49 +1408,49 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L6" s="4">
-        <v>-42.9</v>
+        <v>-36.8</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="O6" s="10">
+        <v>158</v>
+      </c>
+      <c r="O6" s="12">
+        <v>18</v>
+      </c>
+      <c r="P6" s="14">
         <v>14</v>
-      </c>
-      <c r="P6" s="8">
-        <v>2</v>
       </c>
       <c r="Q6" s="8">
         <v>0</v>
@@ -1437,55 +1464,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L7" s="4">
-        <v>-47.9</v>
+        <v>-47.2</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O7" s="6">
-        <v>18</v>
-      </c>
-      <c r="P7" s="9">
-        <v>18</v>
+        <v>40</v>
+      </c>
+      <c r="P7" s="15">
+        <v>40</v>
       </c>
       <c r="Q7" s="8">
         <v>0</v>
       </c>
       <c r="R7" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1493,49 +1520,49 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L8" s="4">
-        <v>-36.8</v>
+        <v>-43.4</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="O8" s="11">
-        <v>48</v>
-      </c>
-      <c r="P8" s="12">
-        <v>48</v>
+        <v>157</v>
+      </c>
+      <c r="O8" s="12">
+        <v>15</v>
+      </c>
+      <c r="P8" s="8">
+        <v>2</v>
       </c>
       <c r="Q8" s="8">
         <v>0</v>
@@ -1549,49 +1576,49 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>13</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L9" s="4">
-        <v>-47.2</v>
+        <v>-48.5</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="O9" s="11">
-        <v>49</v>
-      </c>
-      <c r="P9" s="12">
-        <v>49</v>
+        <v>158</v>
+      </c>
+      <c r="O9" s="12">
+        <v>13</v>
+      </c>
+      <c r="P9" s="8">
+        <v>2</v>
       </c>
       <c r="Q9" s="8">
         <v>0</v>
@@ -1605,49 +1632,49 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>42</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="G10" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L10" s="4">
-        <v>-43.4</v>
+        <v>-37.2</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O10" s="6">
-        <v>44</v>
-      </c>
-      <c r="P10" s="13">
-        <v>44</v>
+        <v>67</v>
+      </c>
+      <c r="P10" s="16">
+        <v>3</v>
       </c>
       <c r="Q10" s="8">
         <v>0</v>
@@ -1661,49 +1688,49 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L11" s="4">
-        <v>-48.5</v>
+        <v>-47.8</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="O11" s="6">
-        <v>14</v>
-      </c>
-      <c r="P11" s="14">
-        <v>14</v>
+        <v>157</v>
+      </c>
+      <c r="O11" s="10">
+        <v>6</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0</v>
       </c>
       <c r="Q11" s="8">
         <v>0</v>
@@ -1717,49 +1744,49 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="L12" s="4">
-        <v>-37.2</v>
+        <v>-15.7</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="O12" s="10">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P12" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="8">
         <v>0</v>
@@ -1773,46 +1800,46 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L13" s="4">
-        <v>-47.8</v>
+        <v>-29.4</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="O13" s="6">
-        <v>14</v>
+        <v>157</v>
+      </c>
+      <c r="O13" s="10">
+        <v>11</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
@@ -1829,52 +1856,52 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>145</v>
+        <v>67</v>
       </c>
       <c r="L14" s="4">
-        <v>-15.7</v>
+        <v>-43.9</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O14" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P14" s="8">
         <v>0</v>
       </c>
-      <c r="Q14" s="15">
-        <v>11</v>
+      <c r="Q14" s="8">
+        <v>0</v>
       </c>
       <c r="R14" s="8">
         <v>0</v>
@@ -1885,52 +1912,52 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>67</v>
+        <v>152</v>
       </c>
       <c r="L15" s="4">
-        <v>-29.4</v>
+        <v>-25.5</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="O15" s="6">
-        <v>14</v>
+        <v>158</v>
+      </c>
+      <c r="O15" s="10">
+        <v>8</v>
       </c>
       <c r="P15" s="8">
         <v>0</v>
       </c>
-      <c r="Q15" s="8">
-        <v>0</v>
+      <c r="Q15" s="11">
+        <v>8</v>
       </c>
       <c r="R15" s="8">
         <v>0</v>
@@ -1941,49 +1968,49 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L16" s="4">
-        <v>-44</v>
+        <v>-20.4</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="O16" s="6">
-        <v>18</v>
-      </c>
-      <c r="P16" s="8">
-        <v>0</v>
+        <v>158</v>
+      </c>
+      <c r="O16" s="10">
+        <v>17</v>
+      </c>
+      <c r="P16" s="16">
+        <v>3</v>
       </c>
       <c r="Q16" s="8">
         <v>0</v>
@@ -1997,49 +2024,49 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="L17" s="4">
-        <v>-25.5</v>
+        <v>-37.6</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O17" s="10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P17" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="8">
         <v>0</v>
@@ -2053,52 +2080,52 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>70</v>
+        <v>153</v>
       </c>
       <c r="L18" s="4">
-        <v>-20.4</v>
+        <v>-16.3</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="O18" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P18" s="8">
         <v>0</v>
       </c>
       <c r="Q18" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R18" s="8">
         <v>0</v>
@@ -2109,114 +2136,170 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L19" s="4">
+        <v>-29.7</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="O19" s="12">
+        <v>37</v>
+      </c>
+      <c r="P19" s="17">
+        <v>37</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>0</v>
+      </c>
+      <c r="R19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="2">
+        <v>12</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="L19" s="4">
-        <v>-37.7</v>
-      </c>
-      <c r="M19" s="3" t="s">
+      <c r="D20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="N19" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="O19" s="10">
-        <v>3</v>
-      </c>
-      <c r="P19" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="16">
-        <v>3</v>
-      </c>
-      <c r="R19" s="8">
+      <c r="K20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L20" s="4">
+        <v>-44.5</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="O20" s="6">
+        <v>40</v>
+      </c>
+      <c r="P20" s="15">
+        <v>40</v>
+      </c>
+      <c r="Q20" s="8">
+        <v>0</v>
+      </c>
+      <c r="R20" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A19">
+  <conditionalFormatting sqref="A2:A20">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B19">
+  <conditionalFormatting sqref="B2:B20">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C19">
+  <conditionalFormatting sqref="C2:C20">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D19">
+  <conditionalFormatting sqref="D2:D20">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E19">
+  <conditionalFormatting sqref="E2:E20">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F19">
+  <conditionalFormatting sqref="F2:F20">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G19">
+  <conditionalFormatting sqref="G2:G20">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H19">
+  <conditionalFormatting sqref="H2:H20">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I19">
+  <conditionalFormatting sqref="I2:I20">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J19">
+  <conditionalFormatting sqref="J2:J20">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K19">
+  <conditionalFormatting sqref="K2:K20">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L19">
+  <conditionalFormatting sqref="L2:L20">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2235,12 +2318,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M19">
+  <conditionalFormatting sqref="M2:M20">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N19">
+  <conditionalFormatting sqref="N2:N20">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2257,22 +2340,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O19">
+  <conditionalFormatting sqref="O2:O20">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P19">
+  <conditionalFormatting sqref="P2:P20">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q19">
+  <conditionalFormatting sqref="Q2:Q20">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R19">
+  <conditionalFormatting sqref="R2:R20">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="169">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260815--01</t>
-  </si>
-  <si>
-    <t>20260815--02</t>
-  </si>
-  <si>
-    <t>20260815--03</t>
-  </si>
-  <si>
     <t>20260816--01</t>
   </si>
   <si>
@@ -127,22 +118,22 @@
     <t>20260821--03</t>
   </si>
   <si>
-    <t>06:09</t>
-  </si>
-  <si>
-    <t>05:11</t>
-  </si>
-  <si>
-    <t>05:03</t>
-  </si>
-  <si>
-    <t>06:01</t>
-  </si>
-  <si>
-    <t>02:22</t>
-  </si>
-  <si>
-    <t>06:29</t>
+    <t>20260822--01</t>
+  </si>
+  <si>
+    <t>20260822--02</t>
+  </si>
+  <si>
+    <t>20260822--03</t>
+  </si>
+  <si>
+    <t>06:02</t>
+  </si>
+  <si>
+    <t>02:21</t>
+  </si>
+  <si>
+    <t>06:30</t>
   </si>
   <si>
     <t>06:36</t>
@@ -151,268 +142,280 @@
     <t>03:24</t>
   </si>
   <si>
+    <t>06:16</t>
+  </si>
+  <si>
+    <t>04:53</t>
+  </si>
+  <si>
+    <t>04:04</t>
+  </si>
+  <si>
+    <t>05:21</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>01:49</t>
+  </si>
+  <si>
+    <t>03:15</t>
+  </si>
+  <si>
+    <t>06:24</t>
+  </si>
+  <si>
     <t>06:17</t>
   </si>
   <si>
-    <t>04:53</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>05:22</t>
-  </si>
-  <si>
-    <t>05:50</t>
-  </si>
-  <si>
-    <t>01:49</t>
-  </si>
-  <si>
-    <t>03:16</t>
-  </si>
-  <si>
-    <t>06:24</t>
-  </si>
-  <si>
     <t>02:54</t>
   </si>
   <si>
+    <t>05:31</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>04:36</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:26:41</t>
-  </si>
-  <si>
-    <t>02:04:15</t>
-  </si>
-  <si>
-    <t>23:38:08</t>
+    <t>02:56</t>
+  </si>
+  <si>
+    <t>01:09</t>
   </si>
   <si>
     <t>01:15:00</t>
   </si>
   <si>
-    <t>22:49:49</t>
-  </si>
-  <si>
-    <t>00:25:51</t>
-  </si>
-  <si>
-    <t>23:36:48</t>
-  </si>
-  <si>
-    <t>01:15:08</t>
-  </si>
-  <si>
-    <t>22:47:53</t>
-  </si>
-  <si>
-    <t>00:25:37</t>
-  </si>
-  <si>
-    <t>05:21:15</t>
-  </si>
-  <si>
-    <t>21:59:08</t>
-  </si>
-  <si>
-    <t>23:36:09</t>
-  </si>
-  <si>
-    <t>04:32:17</t>
-  </si>
-  <si>
-    <t>21:10:34</t>
-  </si>
-  <si>
-    <t>22:46:48</t>
-  </si>
-  <si>
-    <t>05:19:58</t>
-  </si>
-  <si>
-    <t>21:57:33</t>
-  </si>
-  <si>
-    <t>23:36:00</t>
-  </si>
-  <si>
-    <t>00:28:51</t>
-  </si>
-  <si>
-    <t>02:06:41</t>
-  </si>
-  <si>
-    <t>23:40:34</t>
-  </si>
-  <si>
-    <t>01:17:14</t>
+    <t>22:49:48</t>
+  </si>
+  <si>
+    <t>00:25:50</t>
+  </si>
+  <si>
+    <t>23:36:47</t>
+  </si>
+  <si>
+    <t>01:15:07</t>
+  </si>
+  <si>
+    <t>22:47:51</t>
+  </si>
+  <si>
+    <t>00:25:34</t>
+  </si>
+  <si>
+    <t>05:21:12</t>
+  </si>
+  <si>
+    <t>21:59:04</t>
+  </si>
+  <si>
+    <t>23:36:06</t>
+  </si>
+  <si>
+    <t>04:32:13</t>
+  </si>
+  <si>
+    <t>21:10:29</t>
+  </si>
+  <si>
+    <t>22:46:42</t>
+  </si>
+  <si>
+    <t>05:19:51</t>
+  </si>
+  <si>
+    <t>21:57:25</t>
+  </si>
+  <si>
+    <t>23:35:52</t>
+  </si>
+  <si>
+    <t>04:30:44</t>
+  </si>
+  <si>
+    <t>21:08:16</t>
+  </si>
+  <si>
+    <t>22:46:06</t>
+  </si>
+  <si>
+    <t>01:17:13</t>
   </si>
   <si>
     <t>22:53:03</t>
   </si>
   <si>
-    <t>00:27:58</t>
-  </si>
-  <si>
-    <t>23:38:53</t>
-  </si>
-  <si>
-    <t>01:18:05</t>
-  </si>
-  <si>
-    <t>22:50:02</t>
-  </si>
-  <si>
-    <t>00:28:07</t>
-  </si>
-  <si>
-    <t>05:24:01</t>
-  </si>
-  <si>
-    <t>22:01:28</t>
-  </si>
-  <si>
-    <t>23:38:25</t>
-  </si>
-  <si>
-    <t>04:35:50</t>
-  </si>
-  <si>
-    <t>21:13:30</t>
-  </si>
-  <si>
-    <t>22:48:56</t>
-  </si>
-  <si>
-    <t>05:22:09</t>
-  </si>
-  <si>
-    <t>21:59:38</t>
-  </si>
-  <si>
-    <t>23:39:07</t>
-  </si>
-  <si>
-    <t>00:31:55</t>
-  </si>
-  <si>
-    <t>02:09:16</t>
-  </si>
-  <si>
-    <t>23:43:05</t>
-  </si>
-  <si>
-    <t>01:20:14</t>
+    <t>00:27:57</t>
+  </si>
+  <si>
+    <t>23:38:52</t>
+  </si>
+  <si>
+    <t>01:18:04</t>
+  </si>
+  <si>
+    <t>22:50:00</t>
+  </si>
+  <si>
+    <t>00:28:04</t>
+  </si>
+  <si>
+    <t>05:23:59</t>
+  </si>
+  <si>
+    <t>22:01:25</t>
+  </si>
+  <si>
+    <t>23:38:21</t>
+  </si>
+  <si>
+    <t>04:35:46</t>
+  </si>
+  <si>
+    <t>21:13:25</t>
+  </si>
+  <si>
+    <t>22:48:50</t>
+  </si>
+  <si>
+    <t>05:22:03</t>
+  </si>
+  <si>
+    <t>21:59:30</t>
+  </si>
+  <si>
+    <t>23:38:59</t>
+  </si>
+  <si>
+    <t>04:33:07</t>
+  </si>
+  <si>
+    <t>21:10:23</t>
+  </si>
+  <si>
+    <t>22:48:41</t>
+  </si>
+  <si>
+    <t>01:20:13</t>
   </si>
   <si>
     <t>22:54:14</t>
   </si>
   <si>
-    <t>00:31:12</t>
-  </si>
-  <si>
-    <t>23:42:11</t>
-  </si>
-  <si>
-    <t>01:19:47</t>
-  </si>
-  <si>
-    <t>22:53:10</t>
-  </si>
-  <si>
-    <t>00:30:33</t>
-  </si>
-  <si>
-    <t>05:26:04</t>
-  </si>
-  <si>
-    <t>22:04:09</t>
-  </si>
-  <si>
-    <t>23:41:20</t>
-  </si>
-  <si>
-    <t>04:36:45</t>
-  </si>
-  <si>
-    <t>21:15:08</t>
-  </si>
-  <si>
-    <t>22:52:07</t>
-  </si>
-  <si>
-    <t>05:25:18</t>
-  </si>
-  <si>
-    <t>22:02:55</t>
-  </si>
-  <si>
-    <t>00:35:00</t>
-  </si>
-  <si>
-    <t>02:11:52</t>
-  </si>
-  <si>
-    <t>23:45:37</t>
+    <t>00:31:11</t>
+  </si>
+  <si>
+    <t>23:42:09</t>
+  </si>
+  <si>
+    <t>01:19:45</t>
+  </si>
+  <si>
+    <t>22:53:07</t>
+  </si>
+  <si>
+    <t>00:30:30</t>
+  </si>
+  <si>
+    <t>05:26:01</t>
+  </si>
+  <si>
+    <t>22:04:05</t>
+  </si>
+  <si>
+    <t>23:41:16</t>
+  </si>
+  <si>
+    <t>04:36:40</t>
+  </si>
+  <si>
+    <t>21:15:02</t>
+  </si>
+  <si>
+    <t>22:52:02</t>
+  </si>
+  <si>
+    <t>05:25:11</t>
+  </si>
+  <si>
+    <t>22:02:48</t>
+  </si>
+  <si>
+    <t>23:40:26</t>
+  </si>
+  <si>
+    <t>04:35:52</t>
+  </si>
+  <si>
+    <t>21:13:34</t>
+  </si>
+  <si>
+    <t>22:50:59</t>
   </si>
   <si>
     <t>01:23:15</t>
   </si>
   <si>
-    <t>22:55:25</t>
+    <t>22:55:24</t>
   </si>
   <si>
     <t>00:34:27</t>
   </si>
   <si>
-    <t>23:45:29</t>
-  </si>
-  <si>
-    <t>01:21:29</t>
-  </si>
-  <si>
-    <t>22:56:19</t>
-  </si>
-  <si>
-    <t>00:33:00</t>
-  </si>
-  <si>
-    <t>05:28:06</t>
-  </si>
-  <si>
-    <t>22:06:50</t>
-  </si>
-  <si>
-    <t>23:44:15</t>
-  </si>
-  <si>
-    <t>04:37:39</t>
+    <t>23:45:28</t>
+  </si>
+  <si>
+    <t>01:21:28</t>
+  </si>
+  <si>
+    <t>22:56:16</t>
+  </si>
+  <si>
+    <t>00:32:57</t>
+  </si>
+  <si>
+    <t>05:28:03</t>
+  </si>
+  <si>
+    <t>22:06:46</t>
+  </si>
+  <si>
+    <t>23:44:11</t>
+  </si>
+  <si>
+    <t>04:37:35</t>
+  </si>
+  <si>
+    <t>21:16:40</t>
+  </si>
+  <si>
+    <t>22:55:14</t>
+  </si>
+  <si>
+    <t>05:28:20</t>
+  </si>
+  <si>
+    <t>22:06:06</t>
+  </si>
+  <si>
+    <t>23:41:53</t>
+  </si>
+  <si>
+    <t>04:38:38</t>
   </si>
   <si>
     <t>21:16:46</t>
   </si>
   <si>
-    <t>22:55:20</t>
-  </si>
-  <si>
-    <t>05:28:26</t>
-  </si>
-  <si>
-    <t>22:06:14</t>
-  </si>
-  <si>
-    <t>23:42:01</t>
-  </si>
-  <si>
-    <t>00:37:12</t>
-  </si>
-  <si>
-    <t>02:14:20</t>
-  </si>
-  <si>
-    <t>23:48:03</t>
+    <t>22:53:17</t>
   </si>
   <si>
     <t>01:25:30</t>
@@ -421,46 +424,55 @@
     <t>22:58:40</t>
   </si>
   <si>
-    <t>00:36:36</t>
-  </si>
-  <si>
-    <t>23:47:36</t>
-  </si>
-  <si>
-    <t>01:24:28</t>
-  </si>
-  <si>
-    <t>22:58:28</t>
-  </si>
-  <si>
-    <t>00:35:32</t>
-  </si>
-  <si>
-    <t>05:30:53</t>
-  </si>
-  <si>
-    <t>22:09:12</t>
-  </si>
-  <si>
-    <t>23:46:33</t>
-  </si>
-  <si>
-    <t>04:41:13</t>
-  </si>
-  <si>
-    <t>21:19:42</t>
-  </si>
-  <si>
-    <t>22:57:29</t>
-  </si>
-  <si>
-    <t>05:30:38</t>
-  </si>
-  <si>
-    <t>22:08:20</t>
-  </si>
-  <si>
-    <t>23:45:09</t>
+    <t>00:36:35</t>
+  </si>
+  <si>
+    <t>23:47:34</t>
+  </si>
+  <si>
+    <t>01:24:26</t>
+  </si>
+  <si>
+    <t>22:58:26</t>
+  </si>
+  <si>
+    <t>00:35:29</t>
+  </si>
+  <si>
+    <t>05:30:50</t>
+  </si>
+  <si>
+    <t>22:09:08</t>
+  </si>
+  <si>
+    <t>23:46:29</t>
+  </si>
+  <si>
+    <t>04:41:08</t>
+  </si>
+  <si>
+    <t>21:19:37</t>
+  </si>
+  <si>
+    <t>22:57:23</t>
+  </si>
+  <si>
+    <t>05:30:31</t>
+  </si>
+  <si>
+    <t>22:08:12</t>
+  </si>
+  <si>
+    <t>23:45:01</t>
+  </si>
+  <si>
+    <t>04:41:00</t>
+  </si>
+  <si>
+    <t>21:18:54</t>
+  </si>
+  <si>
+    <t>22:55:53</t>
   </si>
   <si>
     <t>0°</t>
@@ -472,10 +484,22 @@
     <t>7°</t>
   </si>
   <si>
-    <t>04:34:44</t>
-  </si>
-  <si>
-    <t>05:21:35</t>
+    <t>23°</t>
+  </si>
+  <si>
+    <t>20°</t>
+  </si>
+  <si>
+    <t>04:34:40</t>
+  </si>
+  <si>
+    <t>05:21:29</t>
+  </si>
+  <si>
+    <t>04:35:42</t>
+  </si>
+  <si>
+    <t>21:11:32</t>
   </si>
   <si>
     <t>B</t>
@@ -530,7 +554,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -551,7 +575,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -563,7 +587,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -581,37 +611,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -652,7 +670,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -700,9 +718,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1184,49 +1199,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L2" s="4">
-        <v>-46.6</v>
+        <v>-47.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="O2" s="6">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="P2" s="7">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1240,55 +1255,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-36.8</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="O3" s="6">
+        <v>55</v>
+      </c>
+      <c r="P3" s="9">
         <v>54</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-45.3</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="O3" s="6">
-        <v>76</v>
-      </c>
-      <c r="P3" s="9">
-        <v>77</v>
-      </c>
       <c r="Q3" s="8">
         <v>0</v>
       </c>
       <c r="R3" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1296,55 +1311,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>39</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L4" s="4">
-        <v>-42.9</v>
+        <v>-47.2</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="O4" s="10">
-        <v>9</v>
-      </c>
-      <c r="P4" s="11">
-        <v>9</v>
+        <v>165</v>
+      </c>
+      <c r="O4" s="6">
+        <v>59</v>
+      </c>
+      <c r="P4" s="10">
+        <v>59</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
       </c>
       <c r="R4" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1352,49 +1367,49 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L5" s="4">
-        <v>-47.9</v>
+        <v>-43.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="O5" s="12">
-        <v>31</v>
-      </c>
-      <c r="P5" s="13">
-        <v>31</v>
+        <v>165</v>
+      </c>
+      <c r="O5" s="11">
+        <v>2</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
       </c>
       <c r="Q5" s="8">
         <v>0</v>
@@ -1408,49 +1423,49 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L6" s="4">
-        <v>-36.8</v>
+        <v>-48.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="O6" s="12">
-        <v>18</v>
-      </c>
-      <c r="P6" s="14">
-        <v>14</v>
+        <v>166</v>
+      </c>
+      <c r="O6" s="11">
+        <v>0</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
       </c>
       <c r="Q6" s="8">
         <v>0</v>
@@ -1464,55 +1479,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="L7" s="4">
-        <v>-47.2</v>
+        <v>-37.2</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="O7" s="6">
-        <v>40</v>
-      </c>
-      <c r="P7" s="15">
-        <v>40</v>
+        <v>165</v>
+      </c>
+      <c r="O7" s="11">
+        <v>0</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
       </c>
       <c r="Q7" s="8">
         <v>0</v>
       </c>
       <c r="R7" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1520,55 +1535,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L8" s="4">
-        <v>-43.4</v>
+        <v>-47.8</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="O8" s="12">
-        <v>15</v>
+        <v>165</v>
+      </c>
+      <c r="O8" s="6">
+        <v>60</v>
       </c>
       <c r="P8" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="8">
         <v>0</v>
       </c>
-      <c r="R8" s="8">
-        <v>0</v>
+      <c r="R8" s="12">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1576,49 +1591,49 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="L9" s="4">
-        <v>-48.5</v>
+        <v>-15.7</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="O9" s="12">
-        <v>13</v>
+        <v>167</v>
+      </c>
+      <c r="O9" s="11">
+        <v>0</v>
       </c>
       <c r="P9" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="8">
         <v>0</v>
@@ -1632,49 +1647,49 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L10" s="4">
-        <v>-37.2</v>
+        <v>-29.3</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="O10" s="6">
-        <v>67</v>
-      </c>
-      <c r="P10" s="16">
-        <v>3</v>
+        <v>165</v>
+      </c>
+      <c r="O10" s="11">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0</v>
       </c>
       <c r="Q10" s="8">
         <v>0</v>
@@ -1688,46 +1703,46 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L11" s="4">
-        <v>-47.8</v>
+        <v>-43.9</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="O11" s="10">
-        <v>6</v>
+        <v>165</v>
+      </c>
+      <c r="O11" s="11">
+        <v>0</v>
       </c>
       <c r="P11" s="8">
         <v>0</v>
@@ -1744,45 +1759,45 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="L12" s="4">
-        <v>-15.7</v>
+        <v>-25.5</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O12" s="10">
+        <v>166</v>
+      </c>
+      <c r="O12" s="11">
         <v>0</v>
       </c>
       <c r="P12" s="8">
@@ -1800,49 +1815,49 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L13" s="4">
-        <v>-29.4</v>
+        <v>-20.4</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="O13" s="10">
-        <v>11</v>
-      </c>
-      <c r="P13" s="8">
-        <v>0</v>
+        <v>166</v>
+      </c>
+      <c r="O13" s="11">
+        <v>12</v>
+      </c>
+      <c r="P13" s="12">
+        <v>12</v>
       </c>
       <c r="Q13" s="8">
         <v>0</v>
@@ -1856,49 +1871,49 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L14" s="4">
-        <v>-43.9</v>
+        <v>-37.6</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="O14" s="10">
-        <v>13</v>
-      </c>
-      <c r="P14" s="8">
-        <v>0</v>
+        <v>165</v>
+      </c>
+      <c r="O14" s="11">
+        <v>8</v>
+      </c>
+      <c r="P14" s="12">
+        <v>8</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
@@ -1912,7 +1927,7 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>50</v>
@@ -1921,43 +1936,43 @@
         <v>50</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="L15" s="4">
-        <v>-25.5</v>
+        <v>-16.3</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="O15" s="10">
-        <v>8</v>
-      </c>
-      <c r="P15" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="11">
-        <v>8</v>
+        <v>168</v>
+      </c>
+      <c r="O15" s="6">
+        <v>35</v>
+      </c>
+      <c r="P15" s="13">
+        <v>35</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0</v>
       </c>
       <c r="R15" s="8">
         <v>0</v>
@@ -1968,49 +1983,49 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L16" s="4">
-        <v>-20.4</v>
+        <v>-29.7</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="O16" s="10">
-        <v>17</v>
-      </c>
-      <c r="P16" s="16">
-        <v>3</v>
+        <v>165</v>
+      </c>
+      <c r="O16" s="6">
+        <v>38</v>
+      </c>
+      <c r="P16" s="13">
+        <v>36</v>
       </c>
       <c r="Q16" s="8">
         <v>0</v>
@@ -2024,49 +2039,49 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L17" s="4">
-        <v>-37.6</v>
+        <v>-44.5</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="O17" s="10">
-        <v>10</v>
-      </c>
-      <c r="P17" s="8">
-        <v>1</v>
+        <v>166</v>
+      </c>
+      <c r="O17" s="6">
+        <v>37</v>
+      </c>
+      <c r="P17" s="13">
+        <v>37</v>
       </c>
       <c r="Q17" s="8">
         <v>0</v>
@@ -2080,49 +2095,49 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="L18" s="4">
-        <v>-16.3</v>
+        <v>-26</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="O18" s="10">
-        <v>0</v>
-      </c>
-      <c r="P18" s="8">
-        <v>0</v>
+        <v>167</v>
+      </c>
+      <c r="O18" s="6">
+        <v>43</v>
+      </c>
+      <c r="P18" s="14">
+        <v>43</v>
       </c>
       <c r="Q18" s="8">
         <v>0</v>
@@ -2136,49 +2151,49 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>72</v>
+        <v>161</v>
       </c>
       <c r="L19" s="4">
-        <v>-29.7</v>
+        <v>-20.5</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="O19" s="12">
-        <v>37</v>
-      </c>
-      <c r="P19" s="17">
-        <v>37</v>
+        <v>167</v>
+      </c>
+      <c r="O19" s="15">
+        <v>35</v>
+      </c>
+      <c r="P19" s="13">
+        <v>35</v>
       </c>
       <c r="Q19" s="8">
         <v>0</v>
@@ -2192,49 +2207,49 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="L20" s="4">
-        <v>-44.5</v>
+        <v>-38.1</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="O20" s="6">
-        <v>40</v>
-      </c>
-      <c r="P20" s="15">
-        <v>40</v>
+        <v>165</v>
+      </c>
+      <c r="O20" s="15">
+        <v>23</v>
+      </c>
+      <c r="P20" s="16">
+        <v>23</v>
       </c>
       <c r="Q20" s="8">
         <v>0</v>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="195">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260816--01</t>
-  </si>
-  <si>
-    <t>20260816--02</t>
-  </si>
-  <si>
     <t>20260817--01</t>
   </si>
   <si>
@@ -127,10 +121,16 @@
     <t>20260822--03</t>
   </si>
   <si>
-    <t>06:02</t>
-  </si>
-  <si>
-    <t>02:21</t>
+    <t>20260823--01</t>
+  </si>
+  <si>
+    <t>20260823--02</t>
+  </si>
+  <si>
+    <t>20260823--03</t>
+  </si>
+  <si>
+    <t>20260823--04</t>
   </si>
   <si>
     <t>06:30</t>
@@ -139,34 +139,37 @@
     <t>06:36</t>
   </si>
   <si>
-    <t>03:24</t>
+    <t>03:25</t>
+  </si>
+  <si>
+    <t>06:17</t>
+  </si>
+  <si>
+    <t>04:53</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>05:22</t>
+  </si>
+  <si>
+    <t>05:49</t>
+  </si>
+  <si>
+    <t>01:49</t>
+  </si>
+  <si>
+    <t>03:15</t>
+  </si>
+  <si>
+    <t>06:24</t>
   </si>
   <si>
     <t>06:16</t>
   </si>
   <si>
-    <t>04:53</t>
-  </si>
-  <si>
-    <t>04:04</t>
-  </si>
-  <si>
-    <t>05:21</t>
-  </si>
-  <si>
-    <t>05:50</t>
-  </si>
-  <si>
-    <t>01:49</t>
-  </si>
-  <si>
-    <t>03:15</t>
-  </si>
-  <si>
-    <t>06:24</t>
-  </si>
-  <si>
-    <t>06:17</t>
+    <t>06:35</t>
   </si>
   <si>
     <t>02:54</t>
@@ -178,7 +181,19 @@
     <t>06:23</t>
   </si>
   <si>
-    <t>04:36</t>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>04:21</t>
+  </si>
+  <si>
+    <t>06:34</t>
+  </si>
+  <si>
+    <t>05:36</t>
+  </si>
+  <si>
+    <t>05:39</t>
   </si>
   <si>
     <t>00:00</t>
@@ -187,319 +202,382 @@
     <t>02:56</t>
   </si>
   <si>
-    <t>01:09</t>
-  </si>
-  <si>
-    <t>01:15:00</t>
-  </si>
-  <si>
-    <t>22:49:48</t>
-  </si>
-  <si>
-    <t>00:25:50</t>
-  </si>
-  <si>
-    <t>23:36:47</t>
-  </si>
-  <si>
-    <t>01:15:07</t>
-  </si>
-  <si>
-    <t>22:47:51</t>
-  </si>
-  <si>
-    <t>00:25:34</t>
-  </si>
-  <si>
-    <t>05:21:12</t>
-  </si>
-  <si>
-    <t>21:59:04</t>
-  </si>
-  <si>
-    <t>23:36:06</t>
-  </si>
-  <si>
-    <t>04:32:13</t>
-  </si>
-  <si>
-    <t>21:10:29</t>
-  </si>
-  <si>
-    <t>22:46:42</t>
-  </si>
-  <si>
-    <t>05:19:51</t>
-  </si>
-  <si>
-    <t>21:57:25</t>
-  </si>
-  <si>
-    <t>23:35:52</t>
-  </si>
-  <si>
-    <t>04:30:44</t>
-  </si>
-  <si>
-    <t>21:08:16</t>
-  </si>
-  <si>
-    <t>22:46:06</t>
-  </si>
-  <si>
-    <t>01:17:13</t>
-  </si>
-  <si>
-    <t>22:53:03</t>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>04:02</t>
+  </si>
+  <si>
+    <t>04:34</t>
+  </si>
+  <si>
+    <t>00:21</t>
+  </si>
+  <si>
+    <t>00:25:51</t>
+  </si>
+  <si>
+    <t>23:36:48</t>
+  </si>
+  <si>
+    <t>01:15:08</t>
+  </si>
+  <si>
+    <t>22:47:52</t>
+  </si>
+  <si>
+    <t>00:25:35</t>
+  </si>
+  <si>
+    <t>05:21:14</t>
+  </si>
+  <si>
+    <t>21:59:06</t>
+  </si>
+  <si>
+    <t>23:36:08</t>
+  </si>
+  <si>
+    <t>04:32:15</t>
+  </si>
+  <si>
+    <t>21:10:32</t>
+  </si>
+  <si>
+    <t>22:46:45</t>
+  </si>
+  <si>
+    <t>05:19:55</t>
+  </si>
+  <si>
+    <t>21:57:29</t>
+  </si>
+  <si>
+    <t>23:35:56</t>
+  </si>
+  <si>
+    <t>04:30:49</t>
+  </si>
+  <si>
+    <t>21:08:21</t>
+  </si>
+  <si>
+    <t>22:46:12</t>
+  </si>
+  <si>
+    <t>03:41:41</t>
+  </si>
+  <si>
+    <t>05:18:37</t>
+  </si>
+  <si>
+    <t>20:19:21</t>
+  </si>
+  <si>
+    <t>21:56:31</t>
   </si>
   <si>
     <t>00:27:57</t>
   </si>
   <si>
-    <t>23:38:52</t>
+    <t>23:38:53</t>
   </si>
   <si>
     <t>01:18:04</t>
   </si>
   <si>
-    <t>22:50:00</t>
-  </si>
-  <si>
-    <t>00:28:04</t>
-  </si>
-  <si>
-    <t>05:23:59</t>
-  </si>
-  <si>
-    <t>22:01:25</t>
-  </si>
-  <si>
-    <t>23:38:21</t>
+    <t>22:50:01</t>
+  </si>
+  <si>
+    <t>00:28:06</t>
+  </si>
+  <si>
+    <t>05:24:00</t>
+  </si>
+  <si>
+    <t>22:01:27</t>
+  </si>
+  <si>
+    <t>23:38:24</t>
+  </si>
+  <si>
+    <t>04:35:48</t>
+  </si>
+  <si>
+    <t>21:13:28</t>
+  </si>
+  <si>
+    <t>22:48:53</t>
+  </si>
+  <si>
+    <t>05:22:07</t>
+  </si>
+  <si>
+    <t>21:59:35</t>
+  </si>
+  <si>
+    <t>23:39:03</t>
+  </si>
+  <si>
+    <t>04:33:11</t>
+  </si>
+  <si>
+    <t>21:10:28</t>
+  </si>
+  <si>
+    <t>22:48:47</t>
+  </si>
+  <si>
+    <t>03:44:22</t>
+  </si>
+  <si>
+    <t>05:20:44</t>
+  </si>
+  <si>
+    <t>20:21:39</t>
+  </si>
+  <si>
+    <t>21:58:50</t>
+  </si>
+  <si>
+    <t>00:31:11</t>
+  </si>
+  <si>
+    <t>23:42:10</t>
+  </si>
+  <si>
+    <t>01:19:46</t>
+  </si>
+  <si>
+    <t>22:53:09</t>
+  </si>
+  <si>
+    <t>00:30:32</t>
+  </si>
+  <si>
+    <t>05:26:02</t>
+  </si>
+  <si>
+    <t>22:04:07</t>
+  </si>
+  <si>
+    <t>23:41:18</t>
+  </si>
+  <si>
+    <t>04:36:43</t>
+  </si>
+  <si>
+    <t>21:15:05</t>
+  </si>
+  <si>
+    <t>22:52:05</t>
+  </si>
+  <si>
+    <t>05:25:15</t>
+  </si>
+  <si>
+    <t>22:02:52</t>
+  </si>
+  <si>
+    <t>23:40:30</t>
+  </si>
+  <si>
+    <t>04:35:57</t>
+  </si>
+  <si>
+    <t>21:13:39</t>
+  </si>
+  <si>
+    <t>22:51:04</t>
+  </si>
+  <si>
+    <t>03:46:33</t>
+  </si>
+  <si>
+    <t>05:24:01</t>
+  </si>
+  <si>
+    <t>20:24:27</t>
+  </si>
+  <si>
+    <t>22:01:39</t>
+  </si>
+  <si>
+    <t>00:34:27</t>
+  </si>
+  <si>
+    <t>23:45:29</t>
+  </si>
+  <si>
+    <t>01:21:29</t>
+  </si>
+  <si>
+    <t>22:56:18</t>
+  </si>
+  <si>
+    <t>00:32:59</t>
+  </si>
+  <si>
+    <t>05:28:05</t>
+  </si>
+  <si>
+    <t>22:06:49</t>
+  </si>
+  <si>
+    <t>23:44:13</t>
+  </si>
+  <si>
+    <t>04:37:37</t>
+  </si>
+  <si>
+    <t>21:16:43</t>
+  </si>
+  <si>
+    <t>22:55:17</t>
+  </si>
+  <si>
+    <t>05:28:23</t>
+  </si>
+  <si>
+    <t>22:06:10</t>
+  </si>
+  <si>
+    <t>23:41:57</t>
+  </si>
+  <si>
+    <t>04:38:42</t>
+  </si>
+  <si>
+    <t>21:16:51</t>
+  </si>
+  <si>
+    <t>22:53:22</t>
+  </si>
+  <si>
+    <t>03:48:43</t>
+  </si>
+  <si>
+    <t>05:27:18</t>
+  </si>
+  <si>
+    <t>20:27:15</t>
+  </si>
+  <si>
+    <t>22:04:29</t>
+  </si>
+  <si>
+    <t>00:36:35</t>
+  </si>
+  <si>
+    <t>23:47:35</t>
+  </si>
+  <si>
+    <t>01:24:27</t>
+  </si>
+  <si>
+    <t>22:58:27</t>
+  </si>
+  <si>
+    <t>00:35:30</t>
+  </si>
+  <si>
+    <t>05:30:51</t>
+  </si>
+  <si>
+    <t>22:09:10</t>
+  </si>
+  <si>
+    <t>23:46:31</t>
+  </si>
+  <si>
+    <t>04:41:11</t>
+  </si>
+  <si>
+    <t>21:19:40</t>
+  </si>
+  <si>
+    <t>22:57:26</t>
+  </si>
+  <si>
+    <t>05:30:35</t>
+  </si>
+  <si>
+    <t>22:08:16</t>
+  </si>
+  <si>
+    <t>23:45:05</t>
+  </si>
+  <si>
+    <t>04:41:05</t>
+  </si>
+  <si>
+    <t>21:18:59</t>
+  </si>
+  <si>
+    <t>22:55:58</t>
+  </si>
+  <si>
+    <t>03:51:24</t>
+  </si>
+  <si>
+    <t>05:29:25</t>
+  </si>
+  <si>
+    <t>20:29:33</t>
+  </si>
+  <si>
+    <t>22:06:48</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>7°</t>
+  </si>
+  <si>
+    <t>23°</t>
+  </si>
+  <si>
+    <t>20°</t>
+  </si>
+  <si>
+    <t>4°</t>
+  </si>
+  <si>
+    <t>44°</t>
+  </si>
+  <si>
+    <t>17°</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>04:34:42</t>
+  </si>
+  <si>
+    <t>05:21:33</t>
   </si>
   <si>
     <t>04:35:46</t>
   </si>
   <si>
-    <t>21:13:25</t>
-  </si>
-  <si>
-    <t>22:48:50</t>
-  </si>
-  <si>
-    <t>05:22:03</t>
-  </si>
-  <si>
-    <t>21:59:30</t>
-  </si>
-  <si>
-    <t>23:38:59</t>
-  </si>
-  <si>
-    <t>04:33:07</t>
-  </si>
-  <si>
-    <t>21:10:23</t>
-  </si>
-  <si>
-    <t>22:48:41</t>
-  </si>
-  <si>
-    <t>01:20:13</t>
-  </si>
-  <si>
-    <t>22:54:14</t>
-  </si>
-  <si>
-    <t>00:31:11</t>
-  </si>
-  <si>
-    <t>23:42:09</t>
-  </si>
-  <si>
-    <t>01:19:45</t>
-  </si>
-  <si>
-    <t>22:53:07</t>
-  </si>
-  <si>
-    <t>00:30:30</t>
-  </si>
-  <si>
-    <t>05:26:01</t>
-  </si>
-  <si>
-    <t>22:04:05</t>
-  </si>
-  <si>
-    <t>23:41:16</t>
-  </si>
-  <si>
-    <t>04:36:40</t>
-  </si>
-  <si>
-    <t>21:15:02</t>
-  </si>
-  <si>
-    <t>22:52:02</t>
-  </si>
-  <si>
-    <t>05:25:11</t>
-  </si>
-  <si>
-    <t>22:02:48</t>
-  </si>
-  <si>
-    <t>23:40:26</t>
-  </si>
-  <si>
-    <t>04:35:52</t>
-  </si>
-  <si>
-    <t>21:13:34</t>
-  </si>
-  <si>
-    <t>22:50:59</t>
-  </si>
-  <si>
-    <t>01:23:15</t>
-  </si>
-  <si>
-    <t>22:55:24</t>
-  </si>
-  <si>
-    <t>00:34:27</t>
-  </si>
-  <si>
-    <t>23:45:28</t>
-  </si>
-  <si>
-    <t>01:21:28</t>
-  </si>
-  <si>
-    <t>22:56:16</t>
-  </si>
-  <si>
-    <t>00:32:57</t>
-  </si>
-  <si>
-    <t>05:28:03</t>
-  </si>
-  <si>
-    <t>22:06:46</t>
-  </si>
-  <si>
-    <t>23:44:11</t>
-  </si>
-  <si>
-    <t>04:37:35</t>
-  </si>
-  <si>
-    <t>21:16:40</t>
-  </si>
-  <si>
-    <t>22:55:14</t>
-  </si>
-  <si>
-    <t>05:28:20</t>
-  </si>
-  <si>
-    <t>22:06:06</t>
-  </si>
-  <si>
-    <t>23:41:53</t>
-  </si>
-  <si>
-    <t>04:38:38</t>
-  </si>
-  <si>
-    <t>21:16:46</t>
-  </si>
-  <si>
-    <t>22:53:17</t>
-  </si>
-  <si>
-    <t>01:25:30</t>
-  </si>
-  <si>
-    <t>22:58:40</t>
-  </si>
-  <si>
-    <t>00:36:35</t>
-  </si>
-  <si>
-    <t>23:47:34</t>
-  </si>
-  <si>
-    <t>01:24:26</t>
-  </si>
-  <si>
-    <t>22:58:26</t>
-  </si>
-  <si>
-    <t>00:35:29</t>
-  </si>
-  <si>
-    <t>05:30:50</t>
-  </si>
-  <si>
-    <t>22:09:08</t>
-  </si>
-  <si>
-    <t>23:46:29</t>
-  </si>
-  <si>
-    <t>04:41:08</t>
-  </si>
-  <si>
-    <t>21:19:37</t>
-  </si>
-  <si>
-    <t>22:57:23</t>
-  </si>
-  <si>
-    <t>05:30:31</t>
-  </si>
-  <si>
-    <t>22:08:12</t>
-  </si>
-  <si>
-    <t>23:45:01</t>
-  </si>
-  <si>
-    <t>04:41:00</t>
-  </si>
-  <si>
-    <t>21:18:54</t>
-  </si>
-  <si>
-    <t>22:55:53</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>7°</t>
-  </si>
-  <si>
-    <t>23°</t>
-  </si>
-  <si>
-    <t>20°</t>
-  </si>
-  <si>
-    <t>04:34:40</t>
-  </si>
-  <si>
-    <t>05:21:29</t>
-  </si>
-  <si>
-    <t>04:35:42</t>
-  </si>
-  <si>
-    <t>21:11:32</t>
+    <t>21:11:38</t>
+  </si>
+  <si>
+    <t>03:50:17</t>
+  </si>
+  <si>
+    <t>05:23:16</t>
+  </si>
+  <si>
+    <t>20:26:13</t>
+  </si>
+  <si>
+    <t>21:59:11</t>
   </si>
   <si>
     <t>B</t>
@@ -569,13 +647,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,49 +665,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1121,7 +1199,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1199,49 +1277,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-47.2</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="O2" s="6">
+        <v>41</v>
+      </c>
+      <c r="P2" s="7">
         <v>37</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-47.9</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O2" s="6">
-        <v>84</v>
-      </c>
-      <c r="P2" s="7">
-        <v>84</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1255,55 +1333,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="L3" s="4">
-        <v>-36.8</v>
+        <v>-43.4</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="O3" s="6">
-        <v>55</v>
-      </c>
-      <c r="P3" s="9">
-        <v>54</v>
+        <v>191</v>
+      </c>
+      <c r="O3" s="9">
+        <v>0</v>
+      </c>
+      <c r="P3" s="8">
+        <v>0</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
       </c>
       <c r="R3" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1311,55 +1389,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="L4" s="4">
-        <v>-47.2</v>
+        <v>-48.5</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O4" s="6">
-        <v>59</v>
-      </c>
-      <c r="P4" s="10">
-        <v>59</v>
+        <v>192</v>
+      </c>
+      <c r="O4" s="9">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
       </c>
       <c r="R4" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1367,55 +1445,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="L5" s="4">
-        <v>-43.4</v>
+        <v>-37.2</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O5" s="11">
+        <v>191</v>
+      </c>
+      <c r="O5" s="6">
+        <v>32</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="8">
         <v>2</v>
       </c>
-      <c r="P5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>0</v>
-      </c>
-      <c r="R5" s="8">
-        <v>0</v>
+      <c r="R5" s="10">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1423,46 +1501,46 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="L6" s="4">
-        <v>-48.5</v>
+        <v>-47.8</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="O6" s="11">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P6" s="8">
         <v>0</v>
@@ -1470,8 +1548,8 @@
       <c r="Q6" s="8">
         <v>0</v>
       </c>
-      <c r="R6" s="8">
-        <v>0</v>
+      <c r="R6" s="10">
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1479,45 +1557,45 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>63</v>
+        <v>172</v>
       </c>
       <c r="L7" s="4">
-        <v>-37.2</v>
+        <v>-15.7</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O7" s="11">
+        <v>193</v>
+      </c>
+      <c r="O7" s="9">
         <v>0</v>
       </c>
       <c r="P7" s="8">
@@ -1535,46 +1613,46 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="L8" s="4">
-        <v>-47.8</v>
+        <v>-29.4</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O8" s="6">
-        <v>60</v>
+        <v>191</v>
+      </c>
+      <c r="O8" s="9">
+        <v>0</v>
       </c>
       <c r="P8" s="8">
         <v>0</v>
@@ -1582,8 +1660,8 @@
       <c r="Q8" s="8">
         <v>0</v>
       </c>
-      <c r="R8" s="12">
-        <v>10</v>
+      <c r="R8" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1591,45 +1669,45 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="L9" s="4">
-        <v>-15.7</v>
+        <v>-43.9</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="O9" s="11">
+        <v>191</v>
+      </c>
+      <c r="O9" s="9">
         <v>0</v>
       </c>
       <c r="P9" s="8">
@@ -1647,45 +1725,45 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>66</v>
+        <v>180</v>
       </c>
       <c r="L10" s="4">
-        <v>-29.3</v>
+        <v>-25.5</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O10" s="11">
+        <v>192</v>
+      </c>
+      <c r="O10" s="9">
         <v>0</v>
       </c>
       <c r="P10" s="8">
@@ -1703,49 +1781,49 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L11" s="4">
-        <v>-43.9</v>
+        <v>-20.4</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O11" s="11">
-        <v>0</v>
-      </c>
-      <c r="P11" s="8">
-        <v>0</v>
+        <v>192</v>
+      </c>
+      <c r="O11" s="6">
+        <v>15</v>
+      </c>
+      <c r="P11" s="12">
+        <v>15</v>
       </c>
       <c r="Q11" s="8">
         <v>0</v>
@@ -1759,49 +1837,49 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>158</v>
+        <v>76</v>
       </c>
       <c r="L12" s="4">
-        <v>-25.5</v>
+        <v>-37.6</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="O12" s="11">
-        <v>0</v>
-      </c>
-      <c r="P12" s="8">
-        <v>0</v>
+        <v>191</v>
+      </c>
+      <c r="O12" s="6">
+        <v>16</v>
+      </c>
+      <c r="P12" s="12">
+        <v>16</v>
       </c>
       <c r="Q12" s="8">
         <v>0</v>
@@ -1815,49 +1893,49 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>69</v>
+        <v>181</v>
       </c>
       <c r="L13" s="4">
-        <v>-20.4</v>
+        <v>-16.3</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="O13" s="11">
-        <v>12</v>
-      </c>
-      <c r="P13" s="12">
-        <v>12</v>
+        <v>194</v>
+      </c>
+      <c r="O13" s="6">
+        <v>23</v>
+      </c>
+      <c r="P13" s="13">
+        <v>23</v>
       </c>
       <c r="Q13" s="8">
         <v>0</v>
@@ -1871,49 +1949,49 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="L14" s="4">
-        <v>-37.6</v>
+        <v>-29.7</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O14" s="11">
-        <v>8</v>
-      </c>
-      <c r="P14" s="12">
-        <v>8</v>
+        <v>191</v>
+      </c>
+      <c r="O14" s="6">
+        <v>30</v>
+      </c>
+      <c r="P14" s="14">
+        <v>30</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
@@ -1927,49 +2005,49 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="L15" s="4">
-        <v>-16.3</v>
+        <v>-44.5</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="O15" s="6">
-        <v>35</v>
-      </c>
-      <c r="P15" s="13">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="P15" s="15">
+        <v>18</v>
       </c>
       <c r="Q15" s="8">
         <v>0</v>
@@ -1983,49 +2061,49 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>72</v>
+        <v>182</v>
       </c>
       <c r="L16" s="4">
-        <v>-29.7</v>
+        <v>-25.9</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="O16" s="6">
-        <v>38</v>
-      </c>
-      <c r="P16" s="13">
-        <v>36</v>
+        <v>20</v>
+      </c>
+      <c r="P16" s="15">
+        <v>20</v>
       </c>
       <c r="Q16" s="8">
         <v>0</v>
@@ -2039,49 +2117,49 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>73</v>
+        <v>183</v>
       </c>
       <c r="L17" s="4">
-        <v>-44.5</v>
+        <v>-20.6</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="O17" s="6">
-        <v>37</v>
-      </c>
-      <c r="P17" s="13">
-        <v>37</v>
+        <v>193</v>
+      </c>
+      <c r="O17" s="9">
+        <v>14</v>
+      </c>
+      <c r="P17" s="12">
+        <v>14</v>
       </c>
       <c r="Q17" s="8">
         <v>0</v>
@@ -2095,49 +2173,49 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="L18" s="4">
-        <v>-26</v>
+        <v>-38.1</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="O18" s="6">
-        <v>43</v>
-      </c>
-      <c r="P18" s="14">
-        <v>43</v>
+        <v>191</v>
+      </c>
+      <c r="O18" s="9">
+        <v>13</v>
+      </c>
+      <c r="P18" s="12">
+        <v>13</v>
       </c>
       <c r="Q18" s="8">
         <v>0</v>
@@ -2151,49 +2229,49 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="L19" s="4">
-        <v>-20.5</v>
+        <v>-34.8</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="O19" s="15">
-        <v>35</v>
-      </c>
-      <c r="P19" s="13">
-        <v>35</v>
+        <v>191</v>
+      </c>
+      <c r="O19" s="9">
+        <v>0</v>
+      </c>
+      <c r="P19" s="8">
+        <v>0</v>
       </c>
       <c r="Q19" s="8">
         <v>0</v>
@@ -2207,114 +2285,226 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>76</v>
+        <v>185</v>
       </c>
       <c r="L20" s="4">
-        <v>-38.1</v>
+        <v>-16.7</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O20" s="15">
-        <v>23</v>
-      </c>
-      <c r="P20" s="16">
-        <v>23</v>
+        <v>193</v>
+      </c>
+      <c r="O20" s="9">
+        <v>0</v>
+      </c>
+      <c r="P20" s="8">
+        <v>0</v>
       </c>
       <c r="Q20" s="8">
         <v>0</v>
       </c>
       <c r="R20" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="2">
+        <v>26</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="L21" s="4">
+        <v>-10.9</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="O21" s="11">
+        <v>47</v>
+      </c>
+      <c r="P21" s="16">
+        <v>42</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>0</v>
+      </c>
+      <c r="R21" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="2">
+        <v>26</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L22" s="4">
+        <v>-29.9</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="O22" s="6">
+        <v>22</v>
+      </c>
+      <c r="P22" s="15">
+        <v>18</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>0</v>
+      </c>
+      <c r="R22" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A20">
+  <conditionalFormatting sqref="A2:A22">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B20">
+  <conditionalFormatting sqref="B2:B22">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C20">
+  <conditionalFormatting sqref="C2:C22">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D20">
+  <conditionalFormatting sqref="D2:D22">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E20">
+  <conditionalFormatting sqref="E2:E22">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F20">
+  <conditionalFormatting sqref="F2:F22">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G20">
+  <conditionalFormatting sqref="G2:G22">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H20">
+  <conditionalFormatting sqref="H2:H22">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I20">
+  <conditionalFormatting sqref="I2:I22">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J20">
+  <conditionalFormatting sqref="J2:J22">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K20">
+  <conditionalFormatting sqref="K2:K22">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L20">
+  <conditionalFormatting sqref="L2:L22">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2333,12 +2523,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M20">
+  <conditionalFormatting sqref="M2:M22">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N20">
+  <conditionalFormatting sqref="N2:N22">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2355,22 +2545,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O20">
+  <conditionalFormatting sqref="O2:O22">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P20">
+  <conditionalFormatting sqref="P2:P22">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q20">
+  <conditionalFormatting sqref="Q2:Q22">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R20">
+  <conditionalFormatting sqref="R2:R22">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="208">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260817--01</t>
-  </si>
-  <si>
-    <t>20260817--02</t>
-  </si>
-  <si>
     <t>20260818--01</t>
   </si>
   <si>
@@ -133,94 +127,106 @@
     <t>20260823--04</t>
   </si>
   <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>06:36</t>
-  </si>
-  <si>
-    <t>03:25</t>
+    <t>20260824--01</t>
+  </si>
+  <si>
+    <t>20260824--02</t>
+  </si>
+  <si>
+    <t>20260824--03</t>
+  </si>
+  <si>
+    <t>03:24</t>
+  </si>
+  <si>
+    <t>06:16</t>
+  </si>
+  <si>
+    <t>04:53</t>
+  </si>
+  <si>
+    <t>04:04</t>
+  </si>
+  <si>
+    <t>05:22</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>01:48</t>
+  </si>
+  <si>
+    <t>03:16</t>
+  </si>
+  <si>
+    <t>06:24</t>
   </si>
   <si>
     <t>06:17</t>
   </si>
   <si>
-    <t>04:53</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>05:22</t>
-  </si>
-  <si>
-    <t>05:49</t>
-  </si>
-  <si>
-    <t>01:49</t>
-  </si>
-  <si>
-    <t>03:15</t>
-  </si>
-  <si>
-    <t>06:24</t>
-  </si>
-  <si>
-    <t>06:16</t>
-  </si>
-  <si>
     <t>06:35</t>
   </si>
   <si>
-    <t>02:54</t>
+    <t>02:55</t>
   </si>
   <si>
     <t>05:31</t>
   </si>
   <si>
-    <t>06:23</t>
+    <t>06:22</t>
+  </si>
+  <si>
+    <t>04:36</t>
+  </si>
+  <si>
+    <t>04:20</t>
+  </si>
+  <si>
+    <t>06:34</t>
+  </si>
+  <si>
+    <t>05:37</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>02:21</t>
+  </si>
+  <si>
+    <t>06:39</t>
+  </si>
+  <si>
+    <t>06:19</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>02:56</t>
+  </si>
+  <si>
+    <t>01:09</t>
+  </si>
+  <si>
+    <t>04:02</t>
   </si>
   <si>
     <t>04:35</t>
   </si>
   <si>
-    <t>04:21</t>
-  </si>
-  <si>
-    <t>06:34</t>
-  </si>
-  <si>
-    <t>05:36</t>
-  </si>
-  <si>
-    <t>05:39</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>02:56</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>04:02</t>
-  </si>
-  <si>
-    <t>04:34</t>
-  </si>
-  <si>
-    <t>00:21</t>
-  </si>
-  <si>
-    <t>00:25:51</t>
-  </si>
-  <si>
-    <t>23:36:48</t>
-  </si>
-  <si>
-    <t>01:15:08</t>
+    <t>00:22</t>
+  </si>
+  <si>
+    <t>00:01</t>
+  </si>
+  <si>
+    <t>04:18</t>
+  </si>
+  <si>
+    <t>01:15:07</t>
   </si>
   <si>
     <t>22:47:52</t>
@@ -229,58 +235,61 @@
     <t>00:25:35</t>
   </si>
   <si>
-    <t>05:21:14</t>
-  </si>
-  <si>
-    <t>21:59:06</t>
-  </si>
-  <si>
-    <t>23:36:08</t>
-  </si>
-  <si>
-    <t>04:32:15</t>
-  </si>
-  <si>
-    <t>21:10:32</t>
-  </si>
-  <si>
-    <t>22:46:45</t>
-  </si>
-  <si>
-    <t>05:19:55</t>
-  </si>
-  <si>
-    <t>21:57:29</t>
-  </si>
-  <si>
-    <t>23:35:56</t>
-  </si>
-  <si>
-    <t>04:30:49</t>
-  </si>
-  <si>
-    <t>21:08:21</t>
-  </si>
-  <si>
-    <t>22:46:12</t>
-  </si>
-  <si>
-    <t>03:41:41</t>
-  </si>
-  <si>
-    <t>05:18:37</t>
-  </si>
-  <si>
-    <t>20:19:21</t>
-  </si>
-  <si>
-    <t>21:56:31</t>
-  </si>
-  <si>
-    <t>00:27:57</t>
-  </si>
-  <si>
-    <t>23:38:53</t>
+    <t>05:21:13</t>
+  </si>
+  <si>
+    <t>21:59:05</t>
+  </si>
+  <si>
+    <t>23:36:07</t>
+  </si>
+  <si>
+    <t>04:32:14</t>
+  </si>
+  <si>
+    <t>21:10:31</t>
+  </si>
+  <si>
+    <t>22:46:44</t>
+  </si>
+  <si>
+    <t>05:19:53</t>
+  </si>
+  <si>
+    <t>21:57:28</t>
+  </si>
+  <si>
+    <t>23:35:54</t>
+  </si>
+  <si>
+    <t>04:30:47</t>
+  </si>
+  <si>
+    <t>21:08:18</t>
+  </si>
+  <si>
+    <t>22:46:09</t>
+  </si>
+  <si>
+    <t>03:41:39</t>
+  </si>
+  <si>
+    <t>05:18:34</t>
+  </si>
+  <si>
+    <t>20:19:18</t>
+  </si>
+  <si>
+    <t>21:56:28</t>
+  </si>
+  <si>
+    <t>02:52:28</t>
+  </si>
+  <si>
+    <t>04:29:14</t>
+  </si>
+  <si>
+    <t>21:06:52</t>
   </si>
   <si>
     <t>01:18:04</t>
@@ -289,70 +298,73 @@
     <t>22:50:01</t>
   </si>
   <si>
-    <t>00:28:06</t>
+    <t>00:28:05</t>
   </si>
   <si>
     <t>05:24:00</t>
   </si>
   <si>
-    <t>22:01:27</t>
-  </si>
-  <si>
-    <t>23:38:24</t>
+    <t>22:01:26</t>
+  </si>
+  <si>
+    <t>23:38:23</t>
   </si>
   <si>
     <t>04:35:48</t>
   </si>
   <si>
-    <t>21:13:28</t>
-  </si>
-  <si>
-    <t>22:48:53</t>
-  </si>
-  <si>
-    <t>05:22:07</t>
-  </si>
-  <si>
-    <t>21:59:35</t>
-  </si>
-  <si>
-    <t>23:39:03</t>
-  </si>
-  <si>
-    <t>04:33:11</t>
-  </si>
-  <si>
-    <t>21:10:28</t>
-  </si>
-  <si>
-    <t>22:48:47</t>
-  </si>
-  <si>
-    <t>03:44:22</t>
-  </si>
-  <si>
-    <t>05:20:44</t>
-  </si>
-  <si>
-    <t>20:21:39</t>
-  </si>
-  <si>
-    <t>21:58:50</t>
-  </si>
-  <si>
-    <t>00:31:11</t>
-  </si>
-  <si>
-    <t>23:42:10</t>
+    <t>21:13:26</t>
+  </si>
+  <si>
+    <t>22:48:52</t>
+  </si>
+  <si>
+    <t>05:22:05</t>
+  </si>
+  <si>
+    <t>21:59:33</t>
+  </si>
+  <si>
+    <t>23:39:01</t>
+  </si>
+  <si>
+    <t>04:33:09</t>
+  </si>
+  <si>
+    <t>21:10:26</t>
+  </si>
+  <si>
+    <t>22:48:44</t>
+  </si>
+  <si>
+    <t>03:44:20</t>
+  </si>
+  <si>
+    <t>05:20:41</t>
+  </si>
+  <si>
+    <t>20:21:35</t>
+  </si>
+  <si>
+    <t>21:58:46</t>
+  </si>
+  <si>
+    <t>02:55:48</t>
+  </si>
+  <si>
+    <t>04:31:20</t>
+  </si>
+  <si>
+    <t>21:09:01</t>
   </si>
   <si>
     <t>01:19:46</t>
   </si>
   <si>
-    <t>22:53:09</t>
-  </si>
-  <si>
-    <t>00:30:32</t>
+    <t>22:53:08</t>
+  </si>
+  <si>
+    <t>00:30:31</t>
   </si>
   <si>
     <t>05:26:02</t>
@@ -361,115 +373,121 @@
     <t>22:04:07</t>
   </si>
   <si>
-    <t>23:41:18</t>
-  </si>
-  <si>
-    <t>04:36:43</t>
-  </si>
-  <si>
-    <t>21:15:05</t>
-  </si>
-  <si>
-    <t>22:52:05</t>
-  </si>
-  <si>
-    <t>05:25:15</t>
-  </si>
-  <si>
-    <t>22:02:52</t>
-  </si>
-  <si>
-    <t>23:40:30</t>
-  </si>
-  <si>
-    <t>04:35:57</t>
-  </si>
-  <si>
-    <t>21:13:39</t>
-  </si>
-  <si>
-    <t>22:51:04</t>
-  </si>
-  <si>
-    <t>03:46:33</t>
-  </si>
-  <si>
-    <t>05:24:01</t>
-  </si>
-  <si>
-    <t>20:24:27</t>
-  </si>
-  <si>
-    <t>22:01:39</t>
-  </si>
-  <si>
-    <t>00:34:27</t>
-  </si>
-  <si>
-    <t>23:45:29</t>
-  </si>
-  <si>
-    <t>01:21:29</t>
-  </si>
-  <si>
-    <t>22:56:18</t>
-  </si>
-  <si>
-    <t>00:32:59</t>
-  </si>
-  <si>
-    <t>05:28:05</t>
-  </si>
-  <si>
-    <t>22:06:49</t>
+    <t>23:41:17</t>
+  </si>
+  <si>
+    <t>04:36:42</t>
+  </si>
+  <si>
+    <t>21:15:04</t>
+  </si>
+  <si>
+    <t>22:52:03</t>
+  </si>
+  <si>
+    <t>05:25:13</t>
+  </si>
+  <si>
+    <t>22:02:50</t>
+  </si>
+  <si>
+    <t>23:40:28</t>
+  </si>
+  <si>
+    <t>04:35:55</t>
+  </si>
+  <si>
+    <t>21:13:37</t>
+  </si>
+  <si>
+    <t>22:51:02</t>
+  </si>
+  <si>
+    <t>03:46:30</t>
+  </si>
+  <si>
+    <t>05:23:58</t>
+  </si>
+  <si>
+    <t>20:24:23</t>
+  </si>
+  <si>
+    <t>22:01:36</t>
+  </si>
+  <si>
+    <t>02:56:59</t>
+  </si>
+  <si>
+    <t>04:34:40</t>
+  </si>
+  <si>
+    <t>21:12:10</t>
+  </si>
+  <si>
+    <t>01:21:28</t>
+  </si>
+  <si>
+    <t>22:56:17</t>
+  </si>
+  <si>
+    <t>00:32:58</t>
+  </si>
+  <si>
+    <t>05:28:04</t>
+  </si>
+  <si>
+    <t>22:06:48</t>
   </si>
   <si>
     <t>23:44:13</t>
   </si>
   <si>
-    <t>04:37:37</t>
-  </si>
-  <si>
-    <t>21:16:43</t>
-  </si>
-  <si>
-    <t>22:55:17</t>
-  </si>
-  <si>
-    <t>05:28:23</t>
-  </si>
-  <si>
-    <t>22:06:10</t>
-  </si>
-  <si>
-    <t>23:41:57</t>
-  </si>
-  <si>
-    <t>04:38:42</t>
-  </si>
-  <si>
-    <t>21:16:51</t>
-  </si>
-  <si>
-    <t>22:53:22</t>
-  </si>
-  <si>
-    <t>03:48:43</t>
-  </si>
-  <si>
-    <t>05:27:18</t>
-  </si>
-  <si>
-    <t>20:27:15</t>
-  </si>
-  <si>
-    <t>22:04:29</t>
-  </si>
-  <si>
-    <t>00:36:35</t>
-  </si>
-  <si>
-    <t>23:47:35</t>
+    <t>04:37:36</t>
+  </si>
+  <si>
+    <t>21:16:42</t>
+  </si>
+  <si>
+    <t>22:55:16</t>
+  </si>
+  <si>
+    <t>05:28:22</t>
+  </si>
+  <si>
+    <t>22:06:08</t>
+  </si>
+  <si>
+    <t>23:41:56</t>
+  </si>
+  <si>
+    <t>04:38:40</t>
+  </si>
+  <si>
+    <t>21:16:48</t>
+  </si>
+  <si>
+    <t>22:53:20</t>
+  </si>
+  <si>
+    <t>03:48:40</t>
+  </si>
+  <si>
+    <t>05:27:15</t>
+  </si>
+  <si>
+    <t>20:27:12</t>
+  </si>
+  <si>
+    <t>22:04:26</t>
+  </si>
+  <si>
+    <t>02:58:09</t>
+  </si>
+  <si>
+    <t>04:37:59</t>
+  </si>
+  <si>
+    <t>21:15:20</t>
   </si>
   <si>
     <t>01:24:27</t>
@@ -484,49 +502,58 @@
     <t>05:30:51</t>
   </si>
   <si>
-    <t>22:09:10</t>
-  </si>
-  <si>
-    <t>23:46:31</t>
-  </si>
-  <si>
-    <t>04:41:11</t>
-  </si>
-  <si>
-    <t>21:19:40</t>
-  </si>
-  <si>
-    <t>22:57:26</t>
-  </si>
-  <si>
-    <t>05:30:35</t>
-  </si>
-  <si>
-    <t>22:08:16</t>
-  </si>
-  <si>
-    <t>23:45:05</t>
-  </si>
-  <si>
-    <t>04:41:05</t>
-  </si>
-  <si>
-    <t>21:18:59</t>
-  </si>
-  <si>
-    <t>22:55:58</t>
-  </si>
-  <si>
-    <t>03:51:24</t>
-  </si>
-  <si>
-    <t>05:29:25</t>
-  </si>
-  <si>
-    <t>20:29:33</t>
-  </si>
-  <si>
-    <t>22:06:48</t>
+    <t>22:09:09</t>
+  </si>
+  <si>
+    <t>23:46:30</t>
+  </si>
+  <si>
+    <t>04:41:10</t>
+  </si>
+  <si>
+    <t>21:19:38</t>
+  </si>
+  <si>
+    <t>22:57:25</t>
+  </si>
+  <si>
+    <t>05:30:33</t>
+  </si>
+  <si>
+    <t>22:08:15</t>
+  </si>
+  <si>
+    <t>23:45:03</t>
+  </si>
+  <si>
+    <t>04:41:02</t>
+  </si>
+  <si>
+    <t>21:18:57</t>
+  </si>
+  <si>
+    <t>22:55:56</t>
+  </si>
+  <si>
+    <t>03:51:21</t>
+  </si>
+  <si>
+    <t>05:29:22</t>
+  </si>
+  <si>
+    <t>20:29:30</t>
+  </si>
+  <si>
+    <t>22:06:45</t>
+  </si>
+  <si>
+    <t>03:01:30</t>
+  </si>
+  <si>
+    <t>04:40:05</t>
+  </si>
+  <si>
+    <t>21:17:30</t>
   </si>
   <si>
     <t>0°</t>
@@ -550,34 +577,46 @@
     <t>44°</t>
   </si>
   <si>
-    <t>17°</t>
+    <t>16°</t>
   </si>
   <si>
     <t>12°</t>
   </si>
   <si>
-    <t>04:34:42</t>
-  </si>
-  <si>
-    <t>05:21:33</t>
-  </si>
-  <si>
-    <t>04:35:46</t>
-  </si>
-  <si>
-    <t>21:11:38</t>
-  </si>
-  <si>
-    <t>03:50:17</t>
-  </si>
-  <si>
-    <t>05:23:16</t>
-  </si>
-  <si>
-    <t>20:26:13</t>
-  </si>
-  <si>
-    <t>21:59:11</t>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>29°</t>
+  </si>
+  <si>
+    <t>04:34:41</t>
+  </si>
+  <si>
+    <t>05:21:31</t>
+  </si>
+  <si>
+    <t>04:35:44</t>
+  </si>
+  <si>
+    <t>21:11:35</t>
+  </si>
+  <si>
+    <t>03:50:15</t>
+  </si>
+  <si>
+    <t>05:23:13</t>
+  </si>
+  <si>
+    <t>20:26:10</t>
+  </si>
+  <si>
+    <t>21:59:08</t>
+  </si>
+  <si>
+    <t>04:37:58</t>
+  </si>
+  <si>
+    <t>21:13:19</t>
   </si>
   <si>
     <t>B</t>
@@ -589,10 +628,10 @@
     <t>A</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>2</t>
@@ -632,7 +671,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -647,13 +686,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -665,13 +704,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -683,31 +728,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -748,7 +781,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -793,9 +826,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1199,7 +1229,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1277,49 +1307,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="L2" s="4">
-        <v>-47.2</v>
+        <v>-48.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="O2" s="6">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="P2" s="7">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1333,46 +1363,46 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="L3" s="4">
-        <v>-43.4</v>
+        <v>-37.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O3" s="9">
-        <v>0</v>
+        <v>205</v>
+      </c>
+      <c r="O3" s="6">
+        <v>1</v>
       </c>
       <c r="P3" s="8">
         <v>0</v>
@@ -1381,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="R3" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1389,52 +1419,52 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="L4" s="4">
-        <v>-48.5</v>
+        <v>-47.8</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O4" s="9">
-        <v>0</v>
+        <v>205</v>
+      </c>
+      <c r="O4" s="6">
+        <v>1</v>
       </c>
       <c r="P4" s="8">
         <v>0</v>
       </c>
       <c r="Q4" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="8">
         <v>0</v>
@@ -1445,46 +1475,46 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>69</v>
+        <v>181</v>
       </c>
       <c r="L5" s="4">
-        <v>-37.2</v>
+        <v>-15.7</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="O5" s="6">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="P5" s="8">
         <v>0</v>
@@ -1492,8 +1522,8 @@
       <c r="Q5" s="8">
         <v>2</v>
       </c>
-      <c r="R5" s="10">
-        <v>3</v>
+      <c r="R5" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1501,46 +1531,46 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="L6" s="4">
-        <v>-47.8</v>
+        <v>-29.3</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O6" s="11">
-        <v>60</v>
+        <v>205</v>
+      </c>
+      <c r="O6" s="6">
+        <v>0</v>
       </c>
       <c r="P6" s="8">
         <v>0</v>
@@ -1548,8 +1578,8 @@
       <c r="Q6" s="8">
         <v>0</v>
       </c>
-      <c r="R6" s="10">
-        <v>5</v>
+      <c r="R6" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1557,45 +1587,45 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>172</v>
+        <v>75</v>
       </c>
       <c r="L7" s="4">
-        <v>-15.7</v>
+        <v>-43.9</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O7" s="9">
+        <v>205</v>
+      </c>
+      <c r="O7" s="6">
         <v>0</v>
       </c>
       <c r="P7" s="8">
@@ -1613,45 +1643,45 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>72</v>
+        <v>191</v>
       </c>
       <c r="L8" s="4">
-        <v>-29.4</v>
+        <v>-25.5</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O8" s="9">
+        <v>204</v>
+      </c>
+      <c r="O8" s="6">
         <v>0</v>
       </c>
       <c r="P8" s="8">
@@ -1669,45 +1699,45 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L9" s="4">
-        <v>-43.9</v>
+        <v>-20.4</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O9" s="9">
+        <v>204</v>
+      </c>
+      <c r="O9" s="6">
         <v>0</v>
       </c>
       <c r="P9" s="8">
@@ -1725,49 +1755,49 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="L10" s="4">
-        <v>-25.5</v>
+        <v>-37.6</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O10" s="9">
-        <v>0</v>
-      </c>
-      <c r="P10" s="8">
-        <v>0</v>
+        <v>205</v>
+      </c>
+      <c r="O10" s="6">
+        <v>4</v>
+      </c>
+      <c r="P10" s="9">
+        <v>3</v>
       </c>
       <c r="Q10" s="8">
         <v>0</v>
@@ -1781,49 +1811,49 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>75</v>
+        <v>192</v>
       </c>
       <c r="L11" s="4">
-        <v>-20.4</v>
+        <v>-16.3</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O11" s="6">
-        <v>15</v>
-      </c>
-      <c r="P11" s="12">
-        <v>15</v>
+        <v>207</v>
+      </c>
+      <c r="O11" s="10">
+        <v>26</v>
+      </c>
+      <c r="P11" s="11">
+        <v>26</v>
       </c>
       <c r="Q11" s="8">
         <v>0</v>
@@ -1837,49 +1867,49 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L12" s="4">
-        <v>-37.6</v>
+        <v>-29.7</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="O12" s="6">
-        <v>16</v>
-      </c>
-      <c r="P12" s="12">
-        <v>16</v>
+        <v>1</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0</v>
       </c>
       <c r="Q12" s="8">
         <v>0</v>
@@ -1893,49 +1923,49 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="L13" s="4">
-        <v>-16.3</v>
+        <v>-44.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="O13" s="6">
-        <v>23</v>
-      </c>
-      <c r="P13" s="13">
-        <v>23</v>
+        <v>0</v>
+      </c>
+      <c r="P13" s="8">
+        <v>0</v>
       </c>
       <c r="Q13" s="8">
         <v>0</v>
@@ -1949,49 +1979,49 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>78</v>
+        <v>193</v>
       </c>
       <c r="L14" s="4">
-        <v>-29.7</v>
+        <v>-25.9</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O14" s="6">
-        <v>30</v>
-      </c>
-      <c r="P14" s="14">
-        <v>30</v>
+        <v>206</v>
+      </c>
+      <c r="O14" s="10">
+        <v>24</v>
+      </c>
+      <c r="P14" s="11">
+        <v>24</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
@@ -2005,49 +2035,49 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>79</v>
+        <v>194</v>
       </c>
       <c r="L15" s="4">
-        <v>-44.5</v>
+        <v>-20.5</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O15" s="6">
-        <v>18</v>
-      </c>
-      <c r="P15" s="15">
-        <v>18</v>
+        <v>206</v>
+      </c>
+      <c r="O15" s="10">
+        <v>17</v>
+      </c>
+      <c r="P15" s="9">
+        <v>5</v>
       </c>
       <c r="Q15" s="8">
         <v>0</v>
@@ -2061,49 +2091,49 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>182</v>
+        <v>84</v>
       </c>
       <c r="L16" s="4">
-        <v>-25.9</v>
+        <v>-38.1</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O16" s="6">
-        <v>20</v>
-      </c>
-      <c r="P16" s="15">
-        <v>20</v>
+        <v>205</v>
+      </c>
+      <c r="O16" s="10">
+        <v>16</v>
+      </c>
+      <c r="P16" s="7">
+        <v>9</v>
       </c>
       <c r="Q16" s="8">
         <v>0</v>
@@ -2117,49 +2147,49 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>62</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="L17" s="4">
-        <v>-20.6</v>
+        <v>-34.8</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O17" s="9">
-        <v>14</v>
-      </c>
-      <c r="P17" s="12">
-        <v>14</v>
+        <v>205</v>
+      </c>
+      <c r="O17" s="6">
+        <v>12</v>
+      </c>
+      <c r="P17" s="7">
+        <v>12</v>
       </c>
       <c r="Q17" s="8">
         <v>0</v>
@@ -2173,49 +2203,49 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="L18" s="4">
-        <v>-38.1</v>
+        <v>-16.7</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O18" s="9">
-        <v>13</v>
-      </c>
-      <c r="P18" s="12">
-        <v>13</v>
+        <v>206</v>
+      </c>
+      <c r="O18" s="6">
+        <v>4</v>
+      </c>
+      <c r="P18" s="9">
+        <v>4</v>
       </c>
       <c r="Q18" s="8">
         <v>0</v>
@@ -2229,49 +2259,49 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="L19" s="4">
-        <v>-34.8</v>
+        <v>-10.9</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O19" s="9">
-        <v>0</v>
-      </c>
-      <c r="P19" s="8">
-        <v>0</v>
+        <v>206</v>
+      </c>
+      <c r="O19" s="12">
+        <v>85</v>
+      </c>
+      <c r="P19" s="13">
+        <v>58</v>
       </c>
       <c r="Q19" s="8">
         <v>0</v>
@@ -2285,49 +2315,49 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="L20" s="4">
-        <v>-16.7</v>
+        <v>-29.9</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O20" s="9">
-        <v>0</v>
-      </c>
-      <c r="P20" s="8">
-        <v>0</v>
+        <v>206</v>
+      </c>
+      <c r="O20" s="12">
+        <v>77</v>
+      </c>
+      <c r="P20" s="14">
+        <v>56</v>
       </c>
       <c r="Q20" s="8">
         <v>0</v>
@@ -2341,49 +2371,49 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>186</v>
+        <v>89</v>
       </c>
       <c r="L21" s="4">
-        <v>-10.9</v>
+        <v>-42.6</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O21" s="11">
-        <v>47</v>
-      </c>
-      <c r="P21" s="16">
-        <v>42</v>
+        <v>204</v>
+      </c>
+      <c r="O21" s="12">
+        <v>70</v>
+      </c>
+      <c r="P21" s="13">
+        <v>62</v>
       </c>
       <c r="Q21" s="8">
         <v>0</v>
@@ -2397,114 +2427,170 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="J22" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="L22" s="4">
+        <v>-26.4</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="O22" s="12">
+        <v>61</v>
+      </c>
+      <c r="P22" s="14">
+        <v>55</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>0</v>
+      </c>
+      <c r="R22" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="2">
+        <v>42</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="L22" s="4">
-        <v>-29.9</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O22" s="6">
-        <v>22</v>
-      </c>
-      <c r="P22" s="15">
-        <v>18</v>
-      </c>
-      <c r="Q22" s="8">
-        <v>0</v>
-      </c>
-      <c r="R22" s="8">
+      <c r="J23" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="L23" s="4">
+        <v>-20.9</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="O23" s="12">
+        <v>68</v>
+      </c>
+      <c r="P23" s="15">
+        <v>66</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>0</v>
+      </c>
+      <c r="R23" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A22">
+  <conditionalFormatting sqref="A2:A23">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B22">
+  <conditionalFormatting sqref="B2:B23">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C22">
+  <conditionalFormatting sqref="C2:C23">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D22">
+  <conditionalFormatting sqref="D2:D23">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E22">
+  <conditionalFormatting sqref="E2:E23">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F22">
+  <conditionalFormatting sqref="F2:F23">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G22">
+  <conditionalFormatting sqref="G2:G23">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H22">
+  <conditionalFormatting sqref="H2:H23">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I22">
+  <conditionalFormatting sqref="I2:I23">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J22">
+  <conditionalFormatting sqref="J2:J23">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K22">
+  <conditionalFormatting sqref="K2:K23">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L22">
+  <conditionalFormatting sqref="L2:L23">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2523,12 +2609,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M22">
+  <conditionalFormatting sqref="M2:M23">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N22">
+  <conditionalFormatting sqref="N2:N23">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2545,22 +2631,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O22">
+  <conditionalFormatting sqref="O2:O23">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P22">
+  <conditionalFormatting sqref="P2:P23">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q22">
+  <conditionalFormatting sqref="Q2:Q23">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R22">
+  <conditionalFormatting sqref="R2:R23">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/Izana.xlsx
+++ b/output/Izana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="221">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260818--01</t>
-  </si>
-  <si>
-    <t>20260818--02</t>
-  </si>
-  <si>
     <t>20260819--01</t>
   </si>
   <si>
@@ -136,424 +130,463 @@
     <t>20260824--03</t>
   </si>
   <si>
-    <t>03:24</t>
+    <t>20260825--01</t>
+  </si>
+  <si>
+    <t>20260825--02</t>
+  </si>
+  <si>
+    <t>20260825--03</t>
+  </si>
+  <si>
+    <t>20260825--04</t>
+  </si>
+  <si>
+    <t>04:53</t>
+  </si>
+  <si>
+    <t>04:04</t>
+  </si>
+  <si>
+    <t>05:21</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>01:47</t>
+  </si>
+  <si>
+    <t>03:14</t>
+  </si>
+  <si>
+    <t>06:24</t>
   </si>
   <si>
     <t>06:16</t>
   </si>
   <si>
-    <t>04:53</t>
-  </si>
-  <si>
-    <t>04:04</t>
-  </si>
-  <si>
-    <t>05:22</t>
-  </si>
-  <si>
-    <t>05:50</t>
-  </si>
-  <si>
-    <t>01:48</t>
-  </si>
-  <si>
-    <t>03:16</t>
-  </si>
-  <si>
-    <t>06:24</t>
-  </si>
-  <si>
-    <t>06:17</t>
+    <t>06:36</t>
+  </si>
+  <si>
+    <t>02:56</t>
+  </si>
+  <si>
+    <t>05:31</t>
+  </si>
+  <si>
+    <t>06:22</t>
+  </si>
+  <si>
+    <t>04:37</t>
+  </si>
+  <si>
+    <t>04:18</t>
+  </si>
+  <si>
+    <t>06:34</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>02:17</t>
+  </si>
+  <si>
+    <t>06:39</t>
+  </si>
+  <si>
+    <t>06:19</t>
+  </si>
+  <si>
+    <t>04:10</t>
   </si>
   <si>
     <t>06:35</t>
   </si>
   <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
     <t>02:55</t>
   </si>
   <si>
-    <t>05:31</t>
-  </si>
-  <si>
-    <t>06:22</t>
-  </si>
-  <si>
-    <t>04:36</t>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>04:01</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>00:23</t>
   </si>
   <si>
     <t>04:20</t>
   </si>
   <si>
-    <t>06:34</t>
-  </si>
-  <si>
-    <t>05:37</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>02:21</t>
-  </si>
-  <si>
-    <t>06:39</t>
-  </si>
-  <si>
-    <t>06:19</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>02:56</t>
-  </si>
-  <si>
-    <t>01:09</t>
-  </si>
-  <si>
-    <t>04:02</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>00:22</t>
-  </si>
-  <si>
-    <t>00:01</t>
-  </si>
-  <si>
-    <t>04:18</t>
-  </si>
-  <si>
-    <t>01:15:07</t>
-  </si>
-  <si>
-    <t>22:47:52</t>
-  </si>
-  <si>
-    <t>00:25:35</t>
-  </si>
-  <si>
-    <t>05:21:13</t>
-  </si>
-  <si>
-    <t>21:59:05</t>
-  </si>
-  <si>
-    <t>23:36:07</t>
-  </si>
-  <si>
-    <t>04:32:14</t>
-  </si>
-  <si>
-    <t>21:10:31</t>
-  </si>
-  <si>
-    <t>22:46:44</t>
-  </si>
-  <si>
-    <t>05:19:53</t>
-  </si>
-  <si>
-    <t>21:57:28</t>
-  </si>
-  <si>
-    <t>23:35:54</t>
-  </si>
-  <si>
-    <t>04:30:47</t>
-  </si>
-  <si>
-    <t>21:08:18</t>
-  </si>
-  <si>
-    <t>22:46:09</t>
-  </si>
-  <si>
-    <t>03:41:39</t>
-  </si>
-  <si>
-    <t>05:18:34</t>
-  </si>
-  <si>
-    <t>20:19:18</t>
-  </si>
-  <si>
-    <t>21:56:28</t>
-  </si>
-  <si>
-    <t>02:52:28</t>
-  </si>
-  <si>
-    <t>04:29:14</t>
-  </si>
-  <si>
-    <t>21:06:52</t>
-  </si>
-  <si>
-    <t>01:18:04</t>
-  </si>
-  <si>
-    <t>22:50:01</t>
-  </si>
-  <si>
-    <t>00:28:05</t>
-  </si>
-  <si>
-    <t>05:24:00</t>
-  </si>
-  <si>
-    <t>22:01:26</t>
-  </si>
-  <si>
-    <t>23:38:23</t>
-  </si>
-  <si>
-    <t>04:35:48</t>
-  </si>
-  <si>
-    <t>21:13:26</t>
-  </si>
-  <si>
-    <t>22:48:52</t>
-  </si>
-  <si>
-    <t>05:22:05</t>
-  </si>
-  <si>
-    <t>21:59:33</t>
-  </si>
-  <si>
-    <t>23:39:01</t>
-  </si>
-  <si>
-    <t>04:33:09</t>
-  </si>
-  <si>
-    <t>21:10:26</t>
-  </si>
-  <si>
-    <t>22:48:44</t>
-  </si>
-  <si>
-    <t>03:44:20</t>
-  </si>
-  <si>
-    <t>05:20:41</t>
-  </si>
-  <si>
-    <t>20:21:35</t>
-  </si>
-  <si>
-    <t>21:58:46</t>
-  </si>
-  <si>
-    <t>02:55:48</t>
-  </si>
-  <si>
-    <t>04:31:20</t>
-  </si>
-  <si>
-    <t>21:09:01</t>
-  </si>
-  <si>
-    <t>01:19:46</t>
-  </si>
-  <si>
-    <t>22:53:08</t>
+    <t>00:54</t>
+  </si>
+  <si>
+    <t>00:25:34</t>
+  </si>
+  <si>
+    <t>05:21:12</t>
+  </si>
+  <si>
+    <t>21:59:03</t>
+  </si>
+  <si>
+    <t>23:36:04</t>
+  </si>
+  <si>
+    <t>04:32:11</t>
+  </si>
+  <si>
+    <t>21:10:25</t>
+  </si>
+  <si>
+    <t>22:46:38</t>
+  </si>
+  <si>
+    <t>05:19:47</t>
+  </si>
+  <si>
+    <t>21:57:18</t>
+  </si>
+  <si>
+    <t>23:35:44</t>
+  </si>
+  <si>
+    <t>04:30:36</t>
+  </si>
+  <si>
+    <t>21:08:04</t>
+  </si>
+  <si>
+    <t>22:45:53</t>
+  </si>
+  <si>
+    <t>03:41:22</t>
+  </si>
+  <si>
+    <t>05:18:17</t>
+  </si>
+  <si>
+    <t>20:18:57</t>
+  </si>
+  <si>
+    <t>21:56:06</t>
+  </si>
+  <si>
+    <t>02:52:06</t>
+  </si>
+  <si>
+    <t>04:28:51</t>
+  </si>
+  <si>
+    <t>21:06:23</t>
+  </si>
+  <si>
+    <t>03:39:25</t>
+  </si>
+  <si>
+    <t>05:17:01</t>
+  </si>
+  <si>
+    <t>20:16:45</t>
+  </si>
+  <si>
+    <t>21:55:16</t>
+  </si>
+  <si>
+    <t>00:28:04</t>
+  </si>
+  <si>
+    <t>05:23:59</t>
+  </si>
+  <si>
+    <t>22:01:24</t>
+  </si>
+  <si>
+    <t>23:38:20</t>
+  </si>
+  <si>
+    <t>04:35:45</t>
+  </si>
+  <si>
+    <t>21:13:22</t>
+  </si>
+  <si>
+    <t>22:48:46</t>
+  </si>
+  <si>
+    <t>05:21:59</t>
+  </si>
+  <si>
+    <t>21:59:23</t>
+  </si>
+  <si>
+    <t>23:38:50</t>
+  </si>
+  <si>
+    <t>04:32:58</t>
+  </si>
+  <si>
+    <t>21:10:11</t>
+  </si>
+  <si>
+    <t>22:48:28</t>
+  </si>
+  <si>
+    <t>03:44:04</t>
+  </si>
+  <si>
+    <t>05:20:24</t>
+  </si>
+  <si>
+    <t>20:21:15</t>
+  </si>
+  <si>
+    <t>21:58:24</t>
+  </si>
+  <si>
+    <t>02:55:27</t>
+  </si>
+  <si>
+    <t>04:30:57</t>
+  </si>
+  <si>
+    <t>21:08:32</t>
+  </si>
+  <si>
+    <t>03:41:36</t>
+  </si>
+  <si>
+    <t>05:19:42</t>
+  </si>
+  <si>
+    <t>20:18:50</t>
+  </si>
+  <si>
+    <t>21:58:31</t>
   </si>
   <si>
     <t>00:30:31</t>
   </si>
   <si>
-    <t>05:26:02</t>
-  </si>
-  <si>
-    <t>22:04:07</t>
-  </si>
-  <si>
-    <t>23:41:17</t>
-  </si>
-  <si>
-    <t>04:36:42</t>
-  </si>
-  <si>
-    <t>21:15:04</t>
-  </si>
-  <si>
-    <t>22:52:03</t>
-  </si>
-  <si>
-    <t>05:25:13</t>
-  </si>
-  <si>
-    <t>22:02:50</t>
-  </si>
-  <si>
-    <t>23:40:28</t>
-  </si>
-  <si>
-    <t>04:35:55</t>
-  </si>
-  <si>
-    <t>21:13:37</t>
-  </si>
-  <si>
-    <t>22:51:02</t>
-  </si>
-  <si>
-    <t>03:46:30</t>
-  </si>
-  <si>
-    <t>05:23:58</t>
-  </si>
-  <si>
-    <t>20:24:23</t>
-  </si>
-  <si>
-    <t>22:01:36</t>
-  </si>
-  <si>
-    <t>02:56:59</t>
-  </si>
-  <si>
-    <t>04:34:40</t>
-  </si>
-  <si>
-    <t>21:12:10</t>
-  </si>
-  <si>
-    <t>01:21:28</t>
-  </si>
-  <si>
-    <t>22:56:17</t>
-  </si>
-  <si>
-    <t>00:32:58</t>
-  </si>
-  <si>
-    <t>05:28:04</t>
-  </si>
-  <si>
-    <t>22:06:48</t>
-  </si>
-  <si>
-    <t>23:44:13</t>
+    <t>05:26:01</t>
+  </si>
+  <si>
+    <t>22:04:04</t>
+  </si>
+  <si>
+    <t>23:41:14</t>
+  </si>
+  <si>
+    <t>04:36:38</t>
+  </si>
+  <si>
+    <t>21:14:58</t>
+  </si>
+  <si>
+    <t>22:51:58</t>
+  </si>
+  <si>
+    <t>05:25:07</t>
+  </si>
+  <si>
+    <t>22:02:40</t>
+  </si>
+  <si>
+    <t>23:40:18</t>
+  </si>
+  <si>
+    <t>04:35:43</t>
+  </si>
+  <si>
+    <t>22:50:46</t>
+  </si>
+  <si>
+    <t>03:46:13</t>
+  </si>
+  <si>
+    <t>05:23:41</t>
+  </si>
+  <si>
+    <t>20:24:02</t>
+  </si>
+  <si>
+    <t>22:01:14</t>
+  </si>
+  <si>
+    <t>02:56:36</t>
+  </si>
+  <si>
+    <t>04:34:16</t>
+  </si>
+  <si>
+    <t>21:11:41</t>
+  </si>
+  <si>
+    <t>03:44:45</t>
+  </si>
+  <si>
+    <t>05:21:47</t>
+  </si>
+  <si>
+    <t>20:22:07</t>
+  </si>
+  <si>
+    <t>21:59:46</t>
+  </si>
+  <si>
+    <t>00:32:57</t>
+  </si>
+  <si>
+    <t>05:28:03</t>
+  </si>
+  <si>
+    <t>22:06:45</t>
+  </si>
+  <si>
+    <t>23:44:10</t>
+  </si>
+  <si>
+    <t>04:37:32</t>
+  </si>
+  <si>
+    <t>21:16:36</t>
+  </si>
+  <si>
+    <t>22:55:10</t>
+  </si>
+  <si>
+    <t>05:28:15</t>
+  </si>
+  <si>
+    <t>22:05:59</t>
+  </si>
+  <si>
+    <t>23:41:46</t>
+  </si>
+  <si>
+    <t>04:38:29</t>
+  </si>
+  <si>
+    <t>21:16:33</t>
+  </si>
+  <si>
+    <t>22:53:05</t>
+  </si>
+  <si>
+    <t>03:48:22</t>
+  </si>
+  <si>
+    <t>05:26:58</t>
+  </si>
+  <si>
+    <t>20:26:50</t>
+  </si>
+  <si>
+    <t>02:57:44</t>
   </si>
   <si>
     <t>04:37:36</t>
   </si>
   <si>
-    <t>21:16:42</t>
-  </si>
-  <si>
-    <t>22:55:16</t>
-  </si>
-  <si>
-    <t>05:28:22</t>
-  </si>
-  <si>
-    <t>22:06:08</t>
-  </si>
-  <si>
-    <t>23:41:56</t>
-  </si>
-  <si>
-    <t>04:38:40</t>
-  </si>
-  <si>
-    <t>21:16:48</t>
-  </si>
-  <si>
-    <t>22:53:20</t>
-  </si>
-  <si>
-    <t>03:48:40</t>
-  </si>
-  <si>
-    <t>05:27:15</t>
-  </si>
-  <si>
-    <t>20:27:12</t>
-  </si>
-  <si>
-    <t>22:04:26</t>
-  </si>
-  <si>
-    <t>02:58:09</t>
-  </si>
-  <si>
-    <t>04:37:59</t>
-  </si>
-  <si>
-    <t>21:15:20</t>
-  </si>
-  <si>
-    <t>01:24:27</t>
-  </si>
-  <si>
-    <t>22:58:27</t>
-  </si>
-  <si>
-    <t>00:35:30</t>
-  </si>
-  <si>
-    <t>05:30:51</t>
-  </si>
-  <si>
-    <t>22:09:09</t>
-  </si>
-  <si>
-    <t>23:46:30</t>
-  </si>
-  <si>
-    <t>04:41:10</t>
-  </si>
-  <si>
-    <t>21:19:38</t>
-  </si>
-  <si>
-    <t>22:57:25</t>
-  </si>
-  <si>
-    <t>05:30:33</t>
-  </si>
-  <si>
-    <t>22:08:15</t>
-  </si>
-  <si>
-    <t>23:45:03</t>
-  </si>
-  <si>
-    <t>04:41:02</t>
-  </si>
-  <si>
-    <t>21:18:57</t>
-  </si>
-  <si>
-    <t>22:55:56</t>
-  </si>
-  <si>
-    <t>03:51:21</t>
-  </si>
-  <si>
-    <t>05:29:22</t>
-  </si>
-  <si>
-    <t>20:29:30</t>
-  </si>
-  <si>
-    <t>22:06:45</t>
-  </si>
-  <si>
-    <t>03:01:30</t>
-  </si>
-  <si>
-    <t>04:40:05</t>
-  </si>
-  <si>
-    <t>21:17:30</t>
+    <t>21:14:51</t>
+  </si>
+  <si>
+    <t>03:47:55</t>
+  </si>
+  <si>
+    <t>05:23:52</t>
+  </si>
+  <si>
+    <t>20:25:25</t>
+  </si>
+  <si>
+    <t>22:01:01</t>
+  </si>
+  <si>
+    <t>00:35:29</t>
+  </si>
+  <si>
+    <t>05:30:50</t>
+  </si>
+  <si>
+    <t>22:09:06</t>
+  </si>
+  <si>
+    <t>23:46:27</t>
+  </si>
+  <si>
+    <t>04:41:06</t>
+  </si>
+  <si>
+    <t>21:19:33</t>
+  </si>
+  <si>
+    <t>22:57:19</t>
+  </si>
+  <si>
+    <t>05:30:26</t>
+  </si>
+  <si>
+    <t>22:08:05</t>
+  </si>
+  <si>
+    <t>23:44:53</t>
+  </si>
+  <si>
+    <t>04:40:51</t>
+  </si>
+  <si>
+    <t>21:18:42</t>
+  </si>
+  <si>
+    <t>22:55:41</t>
+  </si>
+  <si>
+    <t>03:51:04</t>
+  </si>
+  <si>
+    <t>05:29:05</t>
+  </si>
+  <si>
+    <t>20:29:08</t>
+  </si>
+  <si>
+    <t>22:06:23</t>
+  </si>
+  <si>
+    <t>03:01:06</t>
+  </si>
+  <si>
+    <t>04:39:42</t>
+  </si>
+  <si>
+    <t>21:17:01</t>
+  </si>
+  <si>
+    <t>03:50:05</t>
+  </si>
+  <si>
+    <t>05:26:33</t>
+  </si>
+  <si>
+    <t>20:27:31</t>
+  </si>
+  <si>
+    <t>22:04:17</t>
   </si>
   <si>
     <t>0°</t>
@@ -574,7 +607,7 @@
     <t>4°</t>
   </si>
   <si>
-    <t>44°</t>
+    <t>45°</t>
   </si>
   <si>
     <t>16°</t>
@@ -589,34 +622,40 @@
     <t>29°</t>
   </si>
   <si>
-    <t>04:34:41</t>
-  </si>
-  <si>
-    <t>05:21:31</t>
-  </si>
-  <si>
-    <t>04:35:44</t>
-  </si>
-  <si>
-    <t>21:11:35</t>
-  </si>
-  <si>
-    <t>03:50:15</t>
-  </si>
-  <si>
-    <t>05:23:13</t>
-  </si>
-  <si>
-    <t>20:26:10</t>
-  </si>
-  <si>
-    <t>21:59:08</t>
-  </si>
-  <si>
-    <t>04:37:58</t>
-  </si>
-  <si>
-    <t>21:13:19</t>
+    <t>04:34:38</t>
+  </si>
+  <si>
+    <t>05:21:25</t>
+  </si>
+  <si>
+    <t>04:35:34</t>
+  </si>
+  <si>
+    <t>21:11:21</t>
+  </si>
+  <si>
+    <t>03:49:59</t>
+  </si>
+  <si>
+    <t>05:22:57</t>
+  </si>
+  <si>
+    <t>20:25:50</t>
+  </si>
+  <si>
+    <t>21:58:47</t>
+  </si>
+  <si>
+    <t>21:12:52</t>
+  </si>
+  <si>
+    <t>05:25:16</t>
+  </si>
+  <si>
+    <t>20:26:32</t>
+  </si>
+  <si>
+    <t>21:59:25</t>
   </si>
   <si>
     <t>B</t>
@@ -628,13 +667,13 @@
     <t>A</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>1</t>
@@ -671,7 +710,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -686,7 +725,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -698,7 +779,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -710,37 +791,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -781,7 +838,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -826,6 +883,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1229,7 +1295,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1307,49 +1373,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L2" s="4">
-        <v>-48.5</v>
+        <v>-47.8</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="O2" s="6">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="P2" s="7">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1363,46 +1429,46 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>71</v>
+        <v>192</v>
       </c>
       <c r="L3" s="4">
-        <v>-37.2</v>
+        <v>-15.7</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O3" s="6">
-        <v>1</v>
+        <v>218</v>
+      </c>
+      <c r="O3" s="9">
+        <v>0</v>
       </c>
       <c r="P3" s="8">
         <v>0</v>
@@ -1411,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="R3" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1419,52 +1485,52 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L4" s="4">
-        <v>-47.8</v>
+        <v>-29.3</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O4" s="6">
-        <v>1</v>
+        <v>217</v>
+      </c>
+      <c r="O4" s="9">
+        <v>0</v>
       </c>
       <c r="P4" s="8">
         <v>0</v>
       </c>
       <c r="Q4" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" s="8">
         <v>0</v>
@@ -1475,52 +1541,52 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>181</v>
+        <v>76</v>
       </c>
       <c r="L5" s="4">
-        <v>-15.7</v>
+        <v>-43.9</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O5" s="6">
-        <v>2</v>
+        <v>217</v>
+      </c>
+      <c r="O5" s="9">
+        <v>0</v>
       </c>
       <c r="P5" s="8">
         <v>0</v>
       </c>
       <c r="Q5" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R5" s="8">
         <v>0</v>
@@ -1531,45 +1597,45 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>74</v>
+        <v>202</v>
       </c>
       <c r="L6" s="4">
-        <v>-29.3</v>
+        <v>-25.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O6" s="6">
+        <v>219</v>
+      </c>
+      <c r="O6" s="9">
         <v>0</v>
       </c>
       <c r="P6" s="8">
@@ -1587,45 +1653,45 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L7" s="4">
-        <v>-43.9</v>
+        <v>-20.4</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O7" s="6">
+        <v>219</v>
+      </c>
+      <c r="O7" s="9">
         <v>0</v>
       </c>
       <c r="P7" s="8">
@@ -1643,45 +1709,45 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>191</v>
+        <v>79</v>
       </c>
       <c r="L8" s="4">
-        <v>-25.5</v>
+        <v>-37.6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O8" s="6">
+        <v>217</v>
+      </c>
+      <c r="O8" s="9">
         <v>0</v>
       </c>
       <c r="P8" s="8">
@@ -1699,49 +1765,49 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="L9" s="4">
-        <v>-20.4</v>
+        <v>-16.3</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O9" s="6">
-        <v>0</v>
-      </c>
-      <c r="P9" s="8">
-        <v>0</v>
+        <v>220</v>
+      </c>
+      <c r="O9" s="10">
+        <v>28</v>
+      </c>
+      <c r="P9" s="11">
+        <v>28</v>
       </c>
       <c r="Q9" s="8">
         <v>0</v>
@@ -1755,49 +1821,49 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L10" s="4">
-        <v>-37.6</v>
+        <v>-29.6</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="O10" s="6">
-        <v>4</v>
-      </c>
-      <c r="P10" s="9">
-        <v>3</v>
+        <v>45</v>
+      </c>
+      <c r="P10" s="12">
+        <v>45</v>
       </c>
       <c r="Q10" s="8">
         <v>0</v>
@@ -1811,49 +1877,49 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>192</v>
+        <v>82</v>
       </c>
       <c r="L11" s="4">
-        <v>-16.3</v>
+        <v>-44.5</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="O11" s="10">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P11" s="11">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q11" s="8">
         <v>0</v>
@@ -1867,46 +1933,46 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>80</v>
+        <v>204</v>
       </c>
       <c r="L12" s="4">
-        <v>-29.7</v>
+        <v>-26</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O12" s="6">
-        <v>1</v>
+        <v>218</v>
+      </c>
+      <c r="O12" s="9">
+        <v>0</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
@@ -1923,49 +1989,49 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-20.5</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="O13" s="6">
         <v>62</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-44.5</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O13" s="6">
-        <v>0</v>
-      </c>
-      <c r="P13" s="8">
-        <v>0</v>
+      <c r="P13" s="13">
+        <v>24</v>
       </c>
       <c r="Q13" s="8">
         <v>0</v>
@@ -1979,49 +2045,49 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>193</v>
+        <v>85</v>
       </c>
       <c r="L14" s="4">
-        <v>-25.9</v>
+        <v>-38</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="O14" s="10">
-        <v>24</v>
-      </c>
-      <c r="P14" s="11">
-        <v>24</v>
+        <v>39</v>
+      </c>
+      <c r="P14" s="14">
+        <v>9</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
@@ -2035,49 +2101,49 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="L15" s="4">
-        <v>-20.5</v>
+        <v>-34.9</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O15" s="10">
-        <v>17</v>
-      </c>
-      <c r="P15" s="9">
-        <v>5</v>
+        <v>217</v>
+      </c>
+      <c r="O15" s="9">
+        <v>0</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0</v>
       </c>
       <c r="Q15" s="8">
         <v>0</v>
@@ -2091,49 +2157,49 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>84</v>
+        <v>207</v>
       </c>
       <c r="L16" s="4">
-        <v>-38.1</v>
+        <v>-16.8</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O16" s="10">
-        <v>16</v>
-      </c>
-      <c r="P16" s="7">
-        <v>9</v>
+        <v>218</v>
+      </c>
+      <c r="O16" s="9">
+        <v>0</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
       </c>
       <c r="Q16" s="8">
         <v>0</v>
@@ -2147,49 +2213,49 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="L17" s="4">
-        <v>-34.8</v>
+        <v>-10.8</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="O17" s="6">
-        <v>12</v>
-      </c>
-      <c r="P17" s="7">
-        <v>12</v>
+        <v>66</v>
+      </c>
+      <c r="P17" s="15">
+        <v>66</v>
       </c>
       <c r="Q17" s="8">
         <v>0</v>
@@ -2203,49 +2269,49 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
+        <v>26</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="D18" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="L18" s="4">
-        <v>-16.7</v>
+        <v>-29.9</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O18" s="6">
-        <v>4</v>
-      </c>
-      <c r="P18" s="9">
-        <v>4</v>
+        <v>218</v>
+      </c>
+      <c r="O18" s="10">
+        <v>45</v>
+      </c>
+      <c r="P18" s="12">
+        <v>45</v>
       </c>
       <c r="Q18" s="8">
         <v>0</v>
@@ -2259,49 +2325,49 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>197</v>
+        <v>90</v>
       </c>
       <c r="L19" s="4">
-        <v>-10.9</v>
+        <v>-42.7</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O19" s="12">
-        <v>85</v>
-      </c>
-      <c r="P19" s="13">
-        <v>58</v>
+        <v>219</v>
+      </c>
+      <c r="O19" s="9">
+        <v>6</v>
+      </c>
+      <c r="P19" s="16">
+        <v>6</v>
       </c>
       <c r="Q19" s="8">
         <v>0</v>
@@ -2315,49 +2381,49 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c r="L20" s="4">
-        <v>-29.9</v>
+        <v>-26.5</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O20" s="12">
-        <v>77</v>
-      </c>
-      <c r="P20" s="14">
-        <v>56</v>
+        <v>218</v>
+      </c>
+      <c r="O20" s="9">
+        <v>0</v>
+      </c>
+      <c r="P20" s="8">
+        <v>0</v>
       </c>
       <c r="Q20" s="8">
         <v>0</v>
@@ -2371,49 +2437,49 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="H21" s="3" t="s">